--- a/SW_Required_Provided_DOEE_EISA438.xlsx
+++ b/SW_Required_Provided_DOEE_EISA438.xlsx
@@ -3931,11 +3931,11 @@
         </is>
       </c>
       <c r="B15" s="16">
-        <f>SUM(B4:B14)</f>
+        <f>SUM(B4:B13)</f>
         <v/>
       </c>
       <c r="C15" s="16">
-        <f>SUM(C4:C14)</f>
+        <f>SUM(C4:C13)</f>
         <v/>
       </c>
       <c r="D15" s="22">

--- a/SW_Required_Provided_DOEE_EISA438.xlsx
+++ b/SW_Required_Provided_DOEE_EISA438.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SDA" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CDA" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BMP" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MEP_SUMMARY" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CORRECT_MEP_SUMMARY" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EISA_DIRECT" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EISA_TR55" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DOEE_SDA" sheetId="9" state="visible" r:id="rId9"/>
@@ -201,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -239,7 +239,13 @@
     <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3677,7 +3683,7 @@
         <f>SUMIFS('BMP'!$AM$4:$AM$53,'BMP'!$B$4:$B$53,A4)</f>
         <v/>
       </c>
-      <c r="D4" s="22">
+      <c r="D4" s="24">
         <f>IFERROR(C4/B4,0)</f>
         <v/>
       </c>
@@ -3703,7 +3709,7 @@
         <f>SUMIFS('BMP'!$AM$4:$AM$53,'BMP'!$B$4:$B$53,A5)</f>
         <v/>
       </c>
-      <c r="D5" s="22">
+      <c r="D5" s="24">
         <f>IFERROR(C5/B5,0)</f>
         <v/>
       </c>
@@ -3729,7 +3735,7 @@
         <f>SUMIFS('BMP'!$AM$4:$AM$53,'BMP'!$B$4:$B$53,A6)</f>
         <v/>
       </c>
-      <c r="D6" s="22">
+      <c r="D6" s="24">
         <f>IFERROR(C6/B6,0)</f>
         <v/>
       </c>
@@ -3755,7 +3761,7 @@
         <f>SUMIFS('BMP'!$AM$4:$AM$53,'BMP'!$B$4:$B$53,A7)</f>
         <v/>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="24">
         <f>IFERROR(C7/B7,0)</f>
         <v/>
       </c>
@@ -3781,7 +3787,7 @@
         <f>SUMIFS('BMP'!$AM$4:$AM$53,'BMP'!$B$4:$B$53,A8)</f>
         <v/>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="24">
         <f>IFERROR(C8/B8,0)</f>
         <v/>
       </c>
@@ -3807,7 +3813,7 @@
         <f>SUMIFS('BMP'!$AM$4:$AM$53,'BMP'!$B$4:$B$53,A9)</f>
         <v/>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="24">
         <f>IFERROR(C9/B9,0)</f>
         <v/>
       </c>
@@ -3833,7 +3839,7 @@
         <f>SUMIFS('BMP'!$AM$4:$AM$53,'BMP'!$B$4:$B$53,A10)</f>
         <v/>
       </c>
-      <c r="D10" s="22">
+      <c r="D10" s="24">
         <f>IFERROR(C10/B10,0)</f>
         <v/>
       </c>
@@ -3859,7 +3865,7 @@
         <f>SUMIFS('BMP'!$AM$4:$AM$53,'BMP'!$B$4:$B$53,A11)</f>
         <v/>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="24">
         <f>IFERROR(C11/B11,0)</f>
         <v/>
       </c>
@@ -3885,7 +3891,7 @@
         <f>SUMIFS('BMP'!$AM$4:$AM$53,'BMP'!$B$4:$B$53,A12)</f>
         <v/>
       </c>
-      <c r="D12" s="22">
+      <c r="D12" s="24">
         <f>IFERROR(C12/B12,0)</f>
         <v/>
       </c>
@@ -3911,7 +3917,7 @@
         <f>SUMIFS('BMP'!$AM$4:$AM$53,'BMP'!$B$4:$B$53,A13)</f>
         <v/>
       </c>
-      <c r="D13" s="22">
+      <c r="D13" s="24">
         <f>IFERROR(C13/B13,0)</f>
         <v/>
       </c>
@@ -3938,7 +3944,7 @@
         <f>SUM(C4:C13)</f>
         <v/>
       </c>
-      <c r="D15" s="22">
+      <c r="D15" s="24">
         <f>IFERROR(C15/B15,0)</f>
         <v/>
       </c>
@@ -13540,4314 +13546,3686 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G338"/>
+  <dimension ref="A1:AQ45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="10.46" customWidth="1" min="1" max="1"/>
+    <col width="10.66" customWidth="1" min="2" max="2"/>
+    <col width="13.13" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12.53" customWidth="1" min="5" max="5"/>
+    <col width="13.86" customWidth="1" min="6" max="6"/>
+    <col width="12.86" customWidth="1" min="7" max="7"/>
+    <col width="13.86" customWidth="1" min="8" max="8"/>
+    <col width="12.86" customWidth="1" min="9" max="9"/>
+    <col width="12.46" customWidth="1" min="10" max="10"/>
+    <col width="10.66" customWidth="1" min="11" max="11"/>
+    <col width="16.53" customWidth="1" min="12" max="12"/>
+    <col width="11.33" customWidth="1" min="13" max="13"/>
+    <col width="13.46" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10.33" customWidth="1" min="16" max="16"/>
+    <col width="11.8" customWidth="1" min="17" max="17"/>
+    <col width="12.33" customWidth="1" min="18" max="18"/>
+    <col width="11.8" customWidth="1" min="19" max="19"/>
+    <col width="12.33" customWidth="1" min="20" max="20"/>
+    <col width="14.33" customWidth="1" min="21" max="21"/>
+    <col width="12.33" customWidth="1" min="22" max="22"/>
+    <col width="14.86" customWidth="1" min="23" max="23"/>
+    <col width="13" customWidth="1" min="24" max="24"/>
+    <col width="14.46" customWidth="1" min="25" max="25"/>
+    <col width="13.46" customWidth="1" min="26" max="26"/>
+    <col width="13.86" customWidth="1" min="27" max="27"/>
+    <col width="14.13" customWidth="1" min="28" max="28"/>
+    <col width="13.53" customWidth="1" min="29" max="29"/>
+    <col width="13.86" customWidth="1" min="30" max="30"/>
+    <col width="12" customWidth="1" min="31" max="31"/>
+    <col width="11.86" customWidth="1" min="32" max="32"/>
+    <col width="19.13" customWidth="1" min="33" max="33"/>
+    <col width="19.53" customWidth="1" min="34" max="34"/>
+    <col width="17.46" customWidth="1" min="35" max="35"/>
+    <col width="12.66" customWidth="1" min="36" max="36"/>
+    <col width="12.66" customWidth="1" min="37" max="37"/>
+    <col width="19.66" customWidth="1" min="38" max="38"/>
+    <col width="16.53" customWidth="1" min="39" max="39"/>
+    <col width="19.33" customWidth="1" min="40" max="40"/>
+    <col width="16.86" customWidth="1" min="41" max="41"/>
+    <col width="9.130000000000001" customWidth="1" min="42" max="42"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>MEP SUMMARY — DDOT 90% Phase (auto-populated)</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="n"/>
-      <c r="C1" s="5" t="n"/>
-      <c r="D1" s="5" t="n"/>
-      <c r="E1" s="5" t="n"/>
-      <c r="F1" s="5" t="n"/>
-      <c r="G1" s="2" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Project Name</t>
-        </is>
-      </c>
-      <c r="B2" s="16">
+    <row r="1" ht="24" customHeight="1">
+      <c r="B1" s="17" t="inlineStr">
+        <is>
+          <t>Project Name:</t>
+        </is>
+      </c>
+      <c r="D1">
         <f>PROJECT_Name</f>
         <v/>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Project Number</t>
-        </is>
-      </c>
-      <c r="B3" s="16">
-        <f>PROJECT_Number</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>MS4 / CSS</t>
-        </is>
-      </c>
-      <c r="B4" s="16">
+      <c r="H1" s="17" t="inlineStr">
+        <is>
+          <t>Project No:</t>
+        </is>
+      </c>
+      <c r="L1" s="17" t="inlineStr">
+        <is>
+          <t>Check One: MS4         CSS</t>
+        </is>
+      </c>
+      <c r="N1">
         <f>PROJECT_MS4</f>
         <v/>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>AWDZ?</t>
-        </is>
-      </c>
-      <c r="B5" s="16">
+      <c r="P1" s="17" t="inlineStr">
+        <is>
+          <t>Check if in AWDZ:</t>
+        </is>
+      </c>
+      <c r="R1">
         <f>PROJECT_AWDZ</f>
         <v/>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>DOEE Plan Review #</t>
-        </is>
-      </c>
-      <c r="B6" s="16">
+      <c r="S1" s="17" t="inlineStr">
+        <is>
+          <t>DOEE Plan Review No.:</t>
+        </is>
+      </c>
+      <c r="T1">
         <f>PROJECT_DOEEReview</f>
         <v/>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Total LOD Area (SF)</t>
-        </is>
-      </c>
-      <c r="B7" s="16">
-        <f>PROJECT_TotalLOD</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>95th % Storm (in)</t>
-        </is>
-      </c>
-      <c r="B8" s="16">
-        <f>PROJECT_Rainfall</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>SDA-1</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="2" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Step 1 — Drainage Area &amp; Regulated Volumes</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="7" t="n"/>
-      <c r="G11" s="8" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>Drainage Area ID</t>
-        </is>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Project Name:</t>
+        </is>
+      </c>
+      <c r="Y1">
+        <f>IF(D1="","",D1)</f>
+        <v/>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>DOEE Plan Review No.:</t>
+        </is>
+      </c>
+      <c r="AF1">
+        <f>IF(T1="","",T1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="2" ht="24.75" customHeight="1">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Summary Data: 90%/Final Design Phase</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Notes:</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>B2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="17.45" customHeight="1">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Regulated Retention Volume (1.2"):</t>
+        </is>
+      </c>
+      <c r="J3">
+        <f>J45</f>
+        <v/>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>CF</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Blocks in the worksheet that are not shaded are data entry fields for the designer.</t>
+        </is>
+      </c>
+      <c r="AE3">
+        <f>I3</f>
+        <v/>
+      </c>
+      <c r="AF3">
+        <f>J3</f>
+        <v/>
+      </c>
+      <c r="AG3">
+        <f>K3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="19.25" customHeight="1">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Disturbance Area (ac.): </t>
+        </is>
+      </c>
+      <c r="E4">
+        <f>E45/43560</f>
+        <v/>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Volume Retained:</t>
+        </is>
+      </c>
+      <c r="J4">
+        <f>AL45</f>
+        <v/>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>CF</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>All shaded blocks are computations internal to the worksheet and should not be edited.</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>B4</f>
+        <v/>
+      </c>
+      <c r="Z4">
+        <f>E4</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>I4</f>
+        <v/>
+      </c>
+      <c r="AF4">
+        <f>J4</f>
+        <v/>
+      </c>
+      <c r="AG4">
+        <f>K4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="19.25" customHeight="1">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>No. of Drainage Areas:</t>
+        </is>
+      </c>
+      <c r="E5">
+        <f>COUNTA(A12:A44)</f>
+        <v/>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Difference:</t>
+        </is>
+      </c>
+      <c r="J5">
+        <f>J4-J3</f>
+        <v/>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>CF</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>B5</f>
+        <v/>
+      </c>
+      <c r="Z5">
+        <f>E5</f>
+        <v/>
+      </c>
+      <c r="AE5">
+        <f>I5</f>
+        <v/>
+      </c>
+      <c r="AF5">
+        <f>J5</f>
+        <v/>
+      </c>
+      <c r="AG5">
+        <f>K5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="9.75" customHeight="1"/>
+    <row r="7" ht="16.9" customHeight="1">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Step 1:  Drainage Area and Regulated Volumes</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Step 2:  Consider Infiltration</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Step 3:  Evaluate Existing Infrastructure Constraints</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Step 4:  Identify Land Conversion and BMP Placement Opportunities</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Step 5: Size BMPs and Compute Achieved Retention Volumes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="102.75" customHeight="1">
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>Update from 65% based on refined or revised design: 
+Number and list each drainage area within the project limits of disturbance (LOD). Provide the drainage area square footage that contributes runoff in the LOD and outside the LOD. The SWRv is calculated for each drainage area. Provide corresponding drainage area identifications on the SWMP.</t>
+        </is>
+      </c>
+      <c r="L8" s="17" t="inlineStr">
+        <is>
+          <t>Record the water table, bedrock concerns, infiltration rate, and hotspot concerns within the LOD for each drainage area.</t>
+        </is>
+      </c>
+      <c r="Q8" s="17" t="inlineStr">
+        <is>
+          <t>On the SWMP, depict utility locations and conveyance infrastructure to confirm/adjust opportunities for land conversions and BMPs. Delineate areas of potential conflict, and areas without conflict, including areas where minimum depths for BMPs can not be met.  Delineate trees (size, species, condition) and tree protection.</t>
+        </is>
+      </c>
+      <c r="W8" s="17" t="inlineStr">
+        <is>
+          <t>For land conversion and BMP opportunities already defined at 30%, and for new opportunities added, provide the areas below.  Land Conversion and BMP surface areas within the LOD must be reflected in the SWRv computation; update those columns as necessary. Additional allowable BMPs such as impervious surface disconnection, swales, and infiltration should also be considered and described in the narrative. Describe the reason for eliminated Land Conversion/BMP locations.</t>
+        </is>
+      </c>
+      <c r="AC8" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provide the contributing drainage area to the BMP locations. The ceiling stormwater runoff volume reaching the BMPs is calculated. </t>
+        </is>
+      </c>
+      <c r="AG8" s="17" t="inlineStr">
+        <is>
+          <t>Calculate and sum the total maximum possible BMP storage volumes. Total the number of proposed trees meeting the required soil volume to be considered for stormwater retention volume.  Total the maximum retention volume capacity of all facilities and compare to the required regulated volume. If a deficit exists, review BMP placements/sizes to determine if additional volume can be captured.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42.6" customHeight="1">
+      <c r="A9" s="18" t="inlineStr">
+        <is>
+          <t>Drainage Area
+ID</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Drainage Area </t>
+        </is>
+      </c>
+      <c r="J9" s="18" t="inlineStr">
+        <is>
+          <t>SWRv</t>
+        </is>
+      </c>
+      <c r="L9" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Hydrologic Soil Group</t>
+        </is>
+      </c>
+      <c r="M9" s="18" t="inlineStr">
+        <is>
+          <t>Water Table OK?</t>
+        </is>
+      </c>
+      <c r="N9" s="18" t="inlineStr">
+        <is>
+          <t>Bedrock Elevation OK?</t>
+        </is>
+      </c>
+      <c r="O9" s="18" t="inlineStr">
+        <is>
+          <t>Infiltration Rate</t>
+        </is>
+      </c>
+      <c r="P9" s="18" t="inlineStr">
+        <is>
+          <t>Hotspot Concern Found?</t>
+        </is>
+      </c>
+      <c r="Q9" s="18" t="inlineStr">
+        <is>
+          <t>Preservation of Small, Large, and/or Special/Heritage Trees which are in fair or better condition</t>
+        </is>
+      </c>
+      <c r="W9" s="18" t="inlineStr">
+        <is>
+          <t>Land Conversion Area</t>
+        </is>
+      </c>
+      <c r="Y9" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bioretention Opportunity Areas </t>
+        </is>
+      </c>
+      <c r="AA9" s="18" t="inlineStr">
+        <is>
+          <t>Permeable Pavement Opportunity Areas</t>
+        </is>
+      </c>
+      <c r="AC9" s="18" t="inlineStr">
+        <is>
+          <t>Total BMP Contributing Drainage Area</t>
+        </is>
+      </c>
+      <c r="AE9" s="18" t="inlineStr">
+        <is>
+          <t>1.7 inch (ceiling) stormwater runoff reaching BMPs</t>
+        </is>
+      </c>
+      <c r="AG9" s="18" t="inlineStr">
+        <is>
+          <t>Max. Storage Volume of Bioretention Based on Size (Total in DA - See separate sizing computations)</t>
+        </is>
+      </c>
+      <c r="AH9" s="18" t="inlineStr">
+        <is>
+          <t>Max. Storage Volume of Permeable Pavement. Based on Size (Total in DA - See separate sizing computations)</t>
+        </is>
+      </c>
+      <c r="AI9" s="18" t="inlineStr">
+        <is>
+          <t>Max. "Other" Storage Volume - (Total in DA - See separate sizing computations)</t>
+        </is>
+      </c>
+      <c r="AJ9" s="18" t="inlineStr">
+        <is>
+          <t>No. of proposed small trees meeting soil volume requirement</t>
+        </is>
+      </c>
+      <c r="AK9" s="18" t="inlineStr">
+        <is>
+          <t>No. of proposed large trees meeting soil volume requirement</t>
+        </is>
+      </c>
+      <c r="AL9" s="18" t="inlineStr">
+        <is>
+          <t>Total Sv Practice -Maximum Retention Volume Achievable (BMPs and Trees)</t>
+        </is>
+      </c>
+      <c r="AM9" s="18" t="inlineStr">
+        <is>
+          <t>Overage / (Deficit) Volume (as compared to SWRv)</t>
+        </is>
+      </c>
+      <c r="AP9" s="18" t="inlineStr">
+        <is>
+          <t>Runoff Coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48.75" customHeight="1">
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>Impervious 
+within LOD</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>Compacted    within LOD</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>Natural 
+within LOD</t>
+        </is>
+      </c>
+      <c r="E10" s="18" t="inlineStr">
+        <is>
+          <t>Total within LOD</t>
+        </is>
+      </c>
+      <c r="F10" s="18" t="inlineStr">
+        <is>
+          <t>Impervious outside LOD</t>
+        </is>
+      </c>
+      <c r="G10" s="18" t="inlineStr">
+        <is>
+          <t>Compacted outside LOD</t>
+        </is>
+      </c>
+      <c r="H10" s="18" t="inlineStr">
+        <is>
+          <t>Natural outside LOD</t>
+        </is>
+      </c>
+      <c r="I10" s="18" t="inlineStr">
+        <is>
+          <t>Total outside LOD</t>
+        </is>
+      </c>
+      <c r="J10" s="18" t="inlineStr">
+        <is>
+          <t>Within LOD</t>
+        </is>
+      </c>
+      <c r="K10" s="18" t="inlineStr">
+        <is>
+          <t>Outside LOD</t>
+        </is>
+      </c>
+      <c r="W10" s="18" t="inlineStr">
+        <is>
+          <t>Within LOD</t>
+        </is>
+      </c>
+      <c r="X10" s="18" t="inlineStr">
+        <is>
+          <t>Adjacent to LOD</t>
+        </is>
+      </c>
+      <c r="Y10" s="18" t="inlineStr">
+        <is>
+          <t>Within LOD</t>
+        </is>
+      </c>
+      <c r="Z10" s="18" t="inlineStr">
+        <is>
+          <t>Adjacent to LOD</t>
+        </is>
+      </c>
+      <c r="AA10" s="18" t="inlineStr">
+        <is>
+          <t>Within LOD</t>
+        </is>
+      </c>
+      <c r="AB10" s="18" t="inlineStr">
+        <is>
+          <t>Adjacent to LOD</t>
+        </is>
+      </c>
+      <c r="AC10" s="18" t="inlineStr">
+        <is>
+          <t>Within LOD</t>
+        </is>
+      </c>
+      <c r="AD10" s="18" t="inlineStr">
+        <is>
+          <t>Adjacent to LOD</t>
+        </is>
+      </c>
+      <c r="AE10" s="18" t="inlineStr">
+        <is>
+          <t>Within LOD</t>
+        </is>
+      </c>
+      <c r="AF10" s="18" t="inlineStr">
+        <is>
+          <t>Adjacent to LOD</t>
+        </is>
+      </c>
+      <c r="AP10" s="18" t="inlineStr">
+        <is>
+          <t>Within LOD</t>
+        </is>
+      </c>
+      <c r="AQ10" s="18" t="inlineStr">
+        <is>
+          <t>Outside LOD</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="32.45" customHeight="1">
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="E11" s="18" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="F11" s="18" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="G11" s="18" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="H11" s="18" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="I11" s="18" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="J11" s="18" t="inlineStr">
+        <is>
+          <t>CF</t>
+        </is>
+      </c>
+      <c r="K11" s="18" t="inlineStr">
+        <is>
+          <t>CF</t>
+        </is>
+      </c>
+      <c r="L11" s="18" t="inlineStr">
+        <is>
+          <t>A, B, C, D, or Urban Land</t>
+        </is>
+      </c>
+      <c r="M11" s="18" t="inlineStr">
+        <is>
+          <t>Y/N</t>
+        </is>
+      </c>
+      <c r="N11" s="18" t="inlineStr">
+        <is>
+          <t>Y/N</t>
+        </is>
+      </c>
+      <c r="O11" s="18" t="inlineStr">
+        <is>
+          <t>in-hr</t>
+        </is>
+      </c>
+      <c r="P11" s="18" t="inlineStr">
+        <is>
+          <t>Y/N</t>
+        </is>
+      </c>
+      <c r="Q11" s="18" t="inlineStr">
+        <is>
+          <t># of Small Trees</t>
+        </is>
+      </c>
+      <c r="R11" s="18" t="inlineStr">
+        <is>
+          <t>Tree Volume Credit (CF)</t>
+        </is>
+      </c>
+      <c r="S11" s="18" t="inlineStr">
+        <is>
+          <t># of Large Trees</t>
+        </is>
+      </c>
+      <c r="T11" s="18" t="inlineStr">
+        <is>
+          <t>Tree Volume Credit (CF)</t>
+        </is>
+      </c>
+      <c r="U11" s="18" t="inlineStr">
+        <is>
+          <t># of Special/ Heritage Trees</t>
+        </is>
+      </c>
+      <c r="V11" s="18" t="inlineStr">
+        <is>
+          <t>Tree Volume Credit (CF)</t>
+        </is>
+      </c>
+      <c r="W11" s="18" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="X11" s="18" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="Y11" s="18" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="Z11" s="18" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="AA11" s="18" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="AB11" s="18" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="AC11" s="18" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="AD11" s="18" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="AE11" s="18" t="inlineStr">
+        <is>
+          <t>CF</t>
+        </is>
+      </c>
+      <c r="AF11" s="18" t="inlineStr">
+        <is>
+          <t>CF</t>
+        </is>
+      </c>
+      <c r="AG11" s="18" t="inlineStr">
+        <is>
+          <t>CF</t>
+        </is>
+      </c>
+      <c r="AH11" s="18" t="inlineStr">
+        <is>
+          <t>CF</t>
+        </is>
+      </c>
+      <c r="AI11" s="18" t="inlineStr">
+        <is>
+          <t>CF</t>
+        </is>
+      </c>
+      <c r="AJ11" s="18" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="AK11" s="18" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="AL11" s="18" t="inlineStr">
+        <is>
+          <t>CF</t>
+        </is>
+      </c>
+      <c r="AM11" s="18" t="inlineStr">
+        <is>
+          <t>CF</t>
+        </is>
+      </c>
+      <c r="AP11" s="18" t="inlineStr">
+        <is>
+          <t>(unitless)</t>
+        </is>
+      </c>
+      <c r="AQ11" s="18" t="inlineStr">
+        <is>
+          <t>(unitless)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16.25" customHeight="1">
+      <c r="A12" s="16">
+        <f>'SDA'!A58</f>
+        <v/>
       </c>
       <c r="B12" s="16">
-        <f>'SDA'!A58</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>Impervious within LOD (SF)</t>
-        </is>
+        <f>'SDA'!F58</f>
+        <v/>
+      </c>
+      <c r="C12" s="16">
+        <f>'SDA'!G58</f>
+        <v/>
+      </c>
+      <c r="D12" s="16">
+        <f>'SDA'!H58</f>
+        <v/>
+      </c>
+      <c r="E12" s="16">
+        <f>SUM(B12:D12)</f>
+        <v/>
+      </c>
+      <c r="F12" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A12,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A12,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <v/>
+      </c>
+      <c r="G12" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A12,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <v/>
+      </c>
+      <c r="H12" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A12,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <v/>
+      </c>
+      <c r="I12" s="16">
+        <f>SUM(F12:H12)</f>
+        <v/>
+      </c>
+      <c r="J12" s="16">
+        <f>IF(E12=0,0,AP12*1.2/12*E12)</f>
+        <v/>
+      </c>
+      <c r="K12" s="16">
+        <f>IF(I12=0,0,AQ12*1.2/12*I12)</f>
+        <v/>
+      </c>
+      <c r="L12" s="16">
+        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A12,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A12,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A12,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A12,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <v/>
+      </c>
+      <c r="M12" s="4" t="n"/>
+      <c r="N12" s="4" t="n"/>
+      <c r="O12" s="16">
+        <f>IFERROR(IFS(L12="A",2.5,L12="B",0.3,L12="C",0.1,L12="D",0.05,TRUE,""),"")</f>
+        <v/>
+      </c>
+      <c r="P12" s="4" t="n"/>
+      <c r="Q12" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A12),0)</f>
+        <v/>
+      </c>
+      <c r="R12" s="16">
+        <f>Q12*10</f>
+        <v/>
+      </c>
+      <c r="S12" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A12),0)</f>
+        <v/>
+      </c>
+      <c r="T12" s="16">
+        <f>S12*20</f>
+        <v/>
+      </c>
+      <c r="U12" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A12)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A12),0)</f>
+        <v/>
+      </c>
+      <c r="V12" s="16">
+        <f>U12*40</f>
+        <v/>
+      </c>
+      <c r="W12" s="4" t="n"/>
+      <c r="X12" s="4" t="n"/>
+      <c r="Y12" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A12,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A12,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="Z12" s="4" t="n"/>
+      <c r="AA12" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A12,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
+      <c r="AB12" s="4" t="n"/>
+      <c r="AC12" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A12),0)</f>
+        <v/>
+      </c>
+      <c r="AD12" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A12),0)</f>
+        <v/>
+      </c>
+      <c r="AE12" s="16">
+        <f>IF(AC12=0,0,AC12*1.7/12*AP12)</f>
+        <v/>
+      </c>
+      <c r="AF12" s="16">
+        <f>IF(AD12=0,0,AD12*1.7/12*AQ12)</f>
+        <v/>
+      </c>
+      <c r="AG12" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A12,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A12,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AH12" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A12,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
+      <c r="AI12" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A12,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AJ12" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A12),0)</f>
+        <v/>
+      </c>
+      <c r="AK12" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A12),0)</f>
+        <v/>
+      </c>
+      <c r="AL12" s="16">
+        <f>(IF((AE12)&lt;(AG12+AH12+AI12),(AE12),(AG12+AH12+AI12)))+AJ12*5+AK12*10+R12+T12+V12</f>
+        <v/>
+      </c>
+      <c r="AM12" s="16">
+        <f>AL12-J12</f>
+        <v/>
+      </c>
+      <c r="AP12" s="16">
+        <f>IF(E12=0,"",(B12*0.95+C12*0.25+D12*0)/E12)</f>
+        <v/>
+      </c>
+      <c r="AQ12" s="16">
+        <f>IF(I12=0,"",(F12*0.95+G12*0.25+H12*0)/I12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="16.25" customHeight="1">
+      <c r="A13" s="16">
+        <f>'SDA'!A59</f>
+        <v/>
       </c>
       <c r="B13" s="16">
-        <f>SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,'SDA'!A58,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,'SDA'!A58,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>Compacted within LOD (SF)</t>
-        </is>
+        <f>'SDA'!F59</f>
+        <v/>
+      </c>
+      <c r="C13" s="16">
+        <f>'SDA'!G59</f>
+        <v/>
+      </c>
+      <c r="D13" s="16">
+        <f>'SDA'!H59</f>
+        <v/>
+      </c>
+      <c r="E13" s="16">
+        <f>SUM(B13:D13)</f>
+        <v/>
+      </c>
+      <c r="F13" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A13,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A13,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <v/>
+      </c>
+      <c r="G13" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A13,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <v/>
+      </c>
+      <c r="H13" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A13,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <v/>
+      </c>
+      <c r="I13" s="16">
+        <f>SUM(F13:H13)</f>
+        <v/>
+      </c>
+      <c r="J13" s="16">
+        <f>IF(E13=0,0,AP13*1.2/12*E13)</f>
+        <v/>
+      </c>
+      <c r="K13" s="16">
+        <f>IF(I13=0,0,AQ13*1.2/12*I13)</f>
+        <v/>
+      </c>
+      <c r="L13" s="16">
+        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A13,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A13,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A13,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A13,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <v/>
+      </c>
+      <c r="M13" s="4" t="n"/>
+      <c r="N13" s="4" t="n"/>
+      <c r="O13" s="16">
+        <f>IFERROR(IFS(L13="A",2.5,L13="B",0.3,L13="C",0.1,L13="D",0.05,TRUE,""),"")</f>
+        <v/>
+      </c>
+      <c r="P13" s="4" t="n"/>
+      <c r="Q13" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A13),0)</f>
+        <v/>
+      </c>
+      <c r="R13" s="16">
+        <f>Q13*10</f>
+        <v/>
+      </c>
+      <c r="S13" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A13),0)</f>
+        <v/>
+      </c>
+      <c r="T13" s="16">
+        <f>S13*20</f>
+        <v/>
+      </c>
+      <c r="U13" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A13)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A13),0)</f>
+        <v/>
+      </c>
+      <c r="V13" s="16">
+        <f>U13*40</f>
+        <v/>
+      </c>
+      <c r="W13" s="4" t="n"/>
+      <c r="X13" s="4" t="n"/>
+      <c r="Y13" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A13,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A13,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="Z13" s="4" t="n"/>
+      <c r="AA13" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A13,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
+      <c r="AB13" s="4" t="n"/>
+      <c r="AC13" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A13),0)</f>
+        <v/>
+      </c>
+      <c r="AD13" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A13),0)</f>
+        <v/>
+      </c>
+      <c r="AE13" s="16">
+        <f>IF(AC13=0,0,AC13*1.7/12*AP13)</f>
+        <v/>
+      </c>
+      <c r="AF13" s="16">
+        <f>IF(AD13=0,0,AD13*1.7/12*AQ13)</f>
+        <v/>
+      </c>
+      <c r="AG13" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A13,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A13,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AH13" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A13,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
+      <c r="AI13" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A13,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AJ13" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A13),0)</f>
+        <v/>
+      </c>
+      <c r="AK13" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A13),0)</f>
+        <v/>
+      </c>
+      <c r="AL13" s="16">
+        <f>(IF((AE13)&lt;(AG13+AH13+AI13),(AE13),(AG13+AH13+AI13)))+AJ13*5+AK13*10+R13+T13+V13</f>
+        <v/>
+      </c>
+      <c r="AM13" s="16">
+        <f>AL13-J13</f>
+        <v/>
+      </c>
+      <c r="AP13" s="16">
+        <f>IF(E13=0,"",(B13*0.95+C13*0.25+D13*0)/E13)</f>
+        <v/>
+      </c>
+      <c r="AQ13" s="16">
+        <f>IF(I13=0,"",(F13*0.95+G13*0.25+H13*0)/I13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="16.25" customHeight="1">
+      <c r="A14" s="16">
+        <f>'SDA'!A60</f>
+        <v/>
       </c>
       <c r="B14" s="16">
-        <f>SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,'SDA'!A58,'SDA'!$C$4:$C$53,"Compacted (Open Space)")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>Natural within LOD (SF)</t>
-        </is>
+        <f>'SDA'!F60</f>
+        <v/>
+      </c>
+      <c r="C14" s="16">
+        <f>'SDA'!G60</f>
+        <v/>
+      </c>
+      <c r="D14" s="16">
+        <f>'SDA'!H60</f>
+        <v/>
+      </c>
+      <c r="E14" s="16">
+        <f>SUM(B14:D14)</f>
+        <v/>
+      </c>
+      <c r="F14" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A14,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A14,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <v/>
+      </c>
+      <c r="G14" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A14,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <v/>
+      </c>
+      <c r="H14" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A14,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <v/>
+      </c>
+      <c r="I14" s="16">
+        <f>SUM(F14:H14)</f>
+        <v/>
+      </c>
+      <c r="J14" s="16">
+        <f>IF(E14=0,0,AP14*1.2/12*E14)</f>
+        <v/>
+      </c>
+      <c r="K14" s="16">
+        <f>IF(I14=0,0,AQ14*1.2/12*I14)</f>
+        <v/>
+      </c>
+      <c r="L14" s="16">
+        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A14,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A14,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A14,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A14,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <v/>
+      </c>
+      <c r="M14" s="4" t="n"/>
+      <c r="N14" s="4" t="n"/>
+      <c r="O14" s="16">
+        <f>IFERROR(IFS(L14="A",2.5,L14="B",0.3,L14="C",0.1,L14="D",0.05,TRUE,""),"")</f>
+        <v/>
+      </c>
+      <c r="P14" s="4" t="n"/>
+      <c r="Q14" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A14),0)</f>
+        <v/>
+      </c>
+      <c r="R14" s="16">
+        <f>Q14*10</f>
+        <v/>
+      </c>
+      <c r="S14" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A14),0)</f>
+        <v/>
+      </c>
+      <c r="T14" s="16">
+        <f>S14*20</f>
+        <v/>
+      </c>
+      <c r="U14" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A14)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A14),0)</f>
+        <v/>
+      </c>
+      <c r="V14" s="16">
+        <f>U14*40</f>
+        <v/>
+      </c>
+      <c r="W14" s="4" t="n"/>
+      <c r="X14" s="4" t="n"/>
+      <c r="Y14" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A14,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A14,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="Z14" s="4" t="n"/>
+      <c r="AA14" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A14,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
+      <c r="AB14" s="4" t="n"/>
+      <c r="AC14" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A14),0)</f>
+        <v/>
+      </c>
+      <c r="AD14" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A14),0)</f>
+        <v/>
+      </c>
+      <c r="AE14" s="16">
+        <f>IF(AC14=0,0,AC14*1.7/12*AP14)</f>
+        <v/>
+      </c>
+      <c r="AF14" s="16">
+        <f>IF(AD14=0,0,AD14*1.7/12*AQ14)</f>
+        <v/>
+      </c>
+      <c r="AG14" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A14,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A14,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AH14" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A14,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
+      <c r="AI14" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A14,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AJ14" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A14),0)</f>
+        <v/>
+      </c>
+      <c r="AK14" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A14),0)</f>
+        <v/>
+      </c>
+      <c r="AL14" s="16">
+        <f>(IF((AE14)&lt;(AG14+AH14+AI14),(AE14),(AG14+AH14+AI14)))+AJ14*5+AK14*10+R14+T14+V14</f>
+        <v/>
+      </c>
+      <c r="AM14" s="16">
+        <f>AL14-J14</f>
+        <v/>
+      </c>
+      <c r="AP14" s="16">
+        <f>IF(E14=0,"",(B14*0.95+C14*0.25+D14*0)/E14)</f>
+        <v/>
+      </c>
+      <c r="AQ14" s="16">
+        <f>IF(I14=0,"",(F14*0.95+G14*0.25+H14*0)/I14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="16.25" customHeight="1">
+      <c r="A15" s="16">
+        <f>'SDA'!A61</f>
+        <v/>
       </c>
       <c r="B15" s="16">
-        <f>SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,'SDA'!A58,'SDA'!$C$4:$C$53,"Natural (Woods)")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Total within LOD (SF)</t>
-        </is>
+        <f>'SDA'!F61</f>
+        <v/>
+      </c>
+      <c r="C15" s="16">
+        <f>'SDA'!G61</f>
+        <v/>
+      </c>
+      <c r="D15" s="16">
+        <f>'SDA'!H61</f>
+        <v/>
+      </c>
+      <c r="E15" s="16">
+        <f>SUM(B15:D15)</f>
+        <v/>
+      </c>
+      <c r="F15" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A15,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A15,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <v/>
+      </c>
+      <c r="G15" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A15,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <v/>
+      </c>
+      <c r="H15" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A15,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <v/>
+      </c>
+      <c r="I15" s="16">
+        <f>SUM(F15:H15)</f>
+        <v/>
+      </c>
+      <c r="J15" s="16">
+        <f>IF(E15=0,0,AP15*1.2/12*E15)</f>
+        <v/>
+      </c>
+      <c r="K15" s="16">
+        <f>IF(I15=0,0,AQ15*1.2/12*I15)</f>
+        <v/>
+      </c>
+      <c r="L15" s="16">
+        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A15,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A15,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A15,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A15,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <v/>
+      </c>
+      <c r="M15" s="4" t="n"/>
+      <c r="N15" s="4" t="n"/>
+      <c r="O15" s="16">
+        <f>IFERROR(IFS(L15="A",2.5,L15="B",0.3,L15="C",0.1,L15="D",0.05,TRUE,""),"")</f>
+        <v/>
+      </c>
+      <c r="P15" s="4" t="n"/>
+      <c r="Q15" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A15),0)</f>
+        <v/>
+      </c>
+      <c r="R15" s="16">
+        <f>Q15*10</f>
+        <v/>
+      </c>
+      <c r="S15" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A15),0)</f>
+        <v/>
+      </c>
+      <c r="T15" s="16">
+        <f>S15*20</f>
+        <v/>
+      </c>
+      <c r="U15" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A15)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A15),0)</f>
+        <v/>
+      </c>
+      <c r="V15" s="16">
+        <f>U15*40</f>
+        <v/>
+      </c>
+      <c r="W15" s="4" t="n"/>
+      <c r="X15" s="4" t="n"/>
+      <c r="Y15" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A15,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A15,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="Z15" s="4" t="n"/>
+      <c r="AA15" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A15,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
+      <c r="AB15" s="4" t="n"/>
+      <c r="AC15" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A15),0)</f>
+        <v/>
+      </c>
+      <c r="AD15" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A15),0)</f>
+        <v/>
+      </c>
+      <c r="AE15" s="16">
+        <f>IF(AC15=0,0,AC15*1.7/12*AP15)</f>
+        <v/>
+      </c>
+      <c r="AF15" s="16">
+        <f>IF(AD15=0,0,AD15*1.7/12*AQ15)</f>
+        <v/>
+      </c>
+      <c r="AG15" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A15,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A15,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AH15" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A15,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
+      <c r="AI15" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A15,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AJ15" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A15),0)</f>
+        <v/>
+      </c>
+      <c r="AK15" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A15),0)</f>
+        <v/>
+      </c>
+      <c r="AL15" s="16">
+        <f>(IF((AE15)&lt;(AG15+AH15+AI15),(AE15),(AG15+AH15+AI15)))+AJ15*5+AK15*10+R15+T15+V15</f>
+        <v/>
+      </c>
+      <c r="AM15" s="16">
+        <f>AL15-J15</f>
+        <v/>
+      </c>
+      <c r="AP15" s="16">
+        <f>IF(E15=0,"",(B15*0.95+C15*0.25+D15*0)/E15)</f>
+        <v/>
+      </c>
+      <c r="AQ15" s="16">
+        <f>IF(I15=0,"",(F15*0.95+G15*0.25+H15*0)/I15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="16.25" customHeight="1">
+      <c r="A16" s="16">
+        <f>'SDA'!A62</f>
+        <v/>
       </c>
       <c r="B16" s="16">
-        <f>SUM(B13:B15)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>Impervious outside LOD (SF)</t>
-        </is>
+        <f>'SDA'!F62</f>
+        <v/>
+      </c>
+      <c r="C16" s="16">
+        <f>'SDA'!G62</f>
+        <v/>
+      </c>
+      <c r="D16" s="16">
+        <f>'SDA'!H62</f>
+        <v/>
+      </c>
+      <c r="E16" s="16">
+        <f>SUM(B16:D16)</f>
+        <v/>
+      </c>
+      <c r="F16" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A16,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A16,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <v/>
+      </c>
+      <c r="G16" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A16,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <v/>
+      </c>
+      <c r="H16" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A16,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <v/>
+      </c>
+      <c r="I16" s="16">
+        <f>SUM(F16:H16)</f>
+        <v/>
+      </c>
+      <c r="J16" s="16">
+        <f>IF(E16=0,0,AP16*1.2/12*E16)</f>
+        <v/>
+      </c>
+      <c r="K16" s="16">
+        <f>IF(I16=0,0,AQ16*1.2/12*I16)</f>
+        <v/>
+      </c>
+      <c r="L16" s="16">
+        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A16,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A16,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A16,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A16,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <v/>
+      </c>
+      <c r="M16" s="4" t="n"/>
+      <c r="N16" s="4" t="n"/>
+      <c r="O16" s="16">
+        <f>IFERROR(IFS(L16="A",2.5,L16="B",0.3,L16="C",0.1,L16="D",0.05,TRUE,""),"")</f>
+        <v/>
+      </c>
+      <c r="P16" s="4" t="n"/>
+      <c r="Q16" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A16),0)</f>
+        <v/>
+      </c>
+      <c r="R16" s="16">
+        <f>Q16*10</f>
+        <v/>
+      </c>
+      <c r="S16" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A16),0)</f>
+        <v/>
+      </c>
+      <c r="T16" s="16">
+        <f>S16*20</f>
+        <v/>
+      </c>
+      <c r="U16" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A16)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A16),0)</f>
+        <v/>
+      </c>
+      <c r="V16" s="16">
+        <f>U16*40</f>
+        <v/>
+      </c>
+      <c r="W16" s="4" t="n"/>
+      <c r="X16" s="4" t="n"/>
+      <c r="Y16" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A16,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A16,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="Z16" s="4" t="n"/>
+      <c r="AA16" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A16,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
+      <c r="AB16" s="4" t="n"/>
+      <c r="AC16" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A16),0)</f>
+        <v/>
+      </c>
+      <c r="AD16" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A16),0)</f>
+        <v/>
+      </c>
+      <c r="AE16" s="16">
+        <f>IF(AC16=0,0,AC16*1.7/12*AP16)</f>
+        <v/>
+      </c>
+      <c r="AF16" s="16">
+        <f>IF(AD16=0,0,AD16*1.7/12*AQ16)</f>
+        <v/>
+      </c>
+      <c r="AG16" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A16,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A16,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AH16" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A16,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
+      <c r="AI16" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A16,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AJ16" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A16),0)</f>
+        <v/>
+      </c>
+      <c r="AK16" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A16),0)</f>
+        <v/>
+      </c>
+      <c r="AL16" s="16">
+        <f>(IF((AE16)&lt;(AG16+AH16+AI16),(AE16),(AG16+AH16+AI16)))+AJ16*5+AK16*10+R16+T16+V16</f>
+        <v/>
+      </c>
+      <c r="AM16" s="16">
+        <f>AL16-J16</f>
+        <v/>
+      </c>
+      <c r="AP16" s="16">
+        <f>IF(E16=0,"",(B16*0.95+C16*0.25+D16*0)/E16)</f>
+        <v/>
+      </c>
+      <c r="AQ16" s="16">
+        <f>IF(I16=0,"",(F16*0.95+G16*0.25+H16*0)/I16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="16.25" customHeight="1">
+      <c r="A17" s="16">
+        <f>'SDA'!A63</f>
+        <v/>
       </c>
       <c r="B17" s="16">
-        <f>SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,'SDA'!A58,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,'SDA'!A58,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>Compacted outside LOD (SF)</t>
-        </is>
+        <f>'SDA'!F63</f>
+        <v/>
+      </c>
+      <c r="C17" s="16">
+        <f>'SDA'!G63</f>
+        <v/>
+      </c>
+      <c r="D17" s="16">
+        <f>'SDA'!H63</f>
+        <v/>
+      </c>
+      <c r="E17" s="16">
+        <f>SUM(B17:D17)</f>
+        <v/>
+      </c>
+      <c r="F17" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A17,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A17,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <v/>
+      </c>
+      <c r="G17" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A17,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <v/>
+      </c>
+      <c r="H17" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A17,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <v/>
+      </c>
+      <c r="I17" s="16">
+        <f>SUM(F17:H17)</f>
+        <v/>
+      </c>
+      <c r="J17" s="16">
+        <f>IF(E17=0,0,AP17*1.2/12*E17)</f>
+        <v/>
+      </c>
+      <c r="K17" s="16">
+        <f>IF(I17=0,0,AQ17*1.2/12*I17)</f>
+        <v/>
+      </c>
+      <c r="L17" s="16">
+        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A17,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A17,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A17,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A17,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <v/>
+      </c>
+      <c r="M17" s="4" t="n"/>
+      <c r="N17" s="4" t="n"/>
+      <c r="O17" s="16">
+        <f>IFERROR(IFS(L17="A",2.5,L17="B",0.3,L17="C",0.1,L17="D",0.05,TRUE,""),"")</f>
+        <v/>
+      </c>
+      <c r="P17" s="4" t="n"/>
+      <c r="Q17" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A17),0)</f>
+        <v/>
+      </c>
+      <c r="R17" s="16">
+        <f>Q17*10</f>
+        <v/>
+      </c>
+      <c r="S17" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A17),0)</f>
+        <v/>
+      </c>
+      <c r="T17" s="16">
+        <f>S17*20</f>
+        <v/>
+      </c>
+      <c r="U17" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A17)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A17),0)</f>
+        <v/>
+      </c>
+      <c r="V17" s="16">
+        <f>U17*40</f>
+        <v/>
+      </c>
+      <c r="W17" s="4" t="n"/>
+      <c r="X17" s="4" t="n"/>
+      <c r="Y17" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A17,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A17,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="Z17" s="4" t="n"/>
+      <c r="AA17" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A17,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
+      <c r="AB17" s="4" t="n"/>
+      <c r="AC17" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A17),0)</f>
+        <v/>
+      </c>
+      <c r="AD17" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A17),0)</f>
+        <v/>
+      </c>
+      <c r="AE17" s="16">
+        <f>IF(AC17=0,0,AC17*1.7/12*AP17)</f>
+        <v/>
+      </c>
+      <c r="AF17" s="16">
+        <f>IF(AD17=0,0,AD17*1.7/12*AQ17)</f>
+        <v/>
+      </c>
+      <c r="AG17" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A17,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A17,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AH17" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A17,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
+      <c r="AI17" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A17,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AJ17" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A17),0)</f>
+        <v/>
+      </c>
+      <c r="AK17" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A17),0)</f>
+        <v/>
+      </c>
+      <c r="AL17" s="16">
+        <f>(IF((AE17)&lt;(AG17+AH17+AI17),(AE17),(AG17+AH17+AI17)))+AJ17*5+AK17*10+R17+T17+V17</f>
+        <v/>
+      </c>
+      <c r="AM17" s="16">
+        <f>AL17-J17</f>
+        <v/>
+      </c>
+      <c r="AP17" s="16">
+        <f>IF(E17=0,"",(B17*0.95+C17*0.25+D17*0)/E17)</f>
+        <v/>
+      </c>
+      <c r="AQ17" s="16">
+        <f>IF(I17=0,"",(F17*0.95+G17*0.25+H17*0)/I17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="16.25" customHeight="1">
+      <c r="A18" s="16">
+        <f>'SDA'!A64</f>
+        <v/>
       </c>
       <c r="B18" s="16">
-        <f>SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,'SDA'!A58,'SDA'!$C$4:$C$53,"Compacted (Open Space)")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>Natural outside LOD (SF)</t>
-        </is>
+        <f>'SDA'!F64</f>
+        <v/>
+      </c>
+      <c r="C18" s="16">
+        <f>'SDA'!G64</f>
+        <v/>
+      </c>
+      <c r="D18" s="16">
+        <f>'SDA'!H64</f>
+        <v/>
+      </c>
+      <c r="E18" s="16">
+        <f>SUM(B18:D18)</f>
+        <v/>
+      </c>
+      <c r="F18" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A18,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A18,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <v/>
+      </c>
+      <c r="G18" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A18,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <v/>
+      </c>
+      <c r="H18" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A18,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <v/>
+      </c>
+      <c r="I18" s="16">
+        <f>SUM(F18:H18)</f>
+        <v/>
+      </c>
+      <c r="J18" s="16">
+        <f>IF(E18=0,0,AP18*1.2/12*E18)</f>
+        <v/>
+      </c>
+      <c r="K18" s="16">
+        <f>IF(I18=0,0,AQ18*1.2/12*I18)</f>
+        <v/>
+      </c>
+      <c r="L18" s="16">
+        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A18,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A18,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A18,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A18,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <v/>
+      </c>
+      <c r="M18" s="4" t="n"/>
+      <c r="N18" s="4" t="n"/>
+      <c r="O18" s="16">
+        <f>IFERROR(IFS(L18="A",2.5,L18="B",0.3,L18="C",0.1,L18="D",0.05,TRUE,""),"")</f>
+        <v/>
+      </c>
+      <c r="P18" s="4" t="n"/>
+      <c r="Q18" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A18),0)</f>
+        <v/>
+      </c>
+      <c r="R18" s="16">
+        <f>Q18*10</f>
+        <v/>
+      </c>
+      <c r="S18" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A18),0)</f>
+        <v/>
+      </c>
+      <c r="T18" s="16">
+        <f>S18*20</f>
+        <v/>
+      </c>
+      <c r="U18" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A18)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A18),0)</f>
+        <v/>
+      </c>
+      <c r="V18" s="16">
+        <f>U18*40</f>
+        <v/>
+      </c>
+      <c r="W18" s="4" t="n"/>
+      <c r="X18" s="4" t="n"/>
+      <c r="Y18" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A18,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A18,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="Z18" s="4" t="n"/>
+      <c r="AA18" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A18,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
+      <c r="AB18" s="4" t="n"/>
+      <c r="AC18" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A18),0)</f>
+        <v/>
+      </c>
+      <c r="AD18" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A18),0)</f>
+        <v/>
+      </c>
+      <c r="AE18" s="16">
+        <f>IF(AC18=0,0,AC18*1.7/12*AP18)</f>
+        <v/>
+      </c>
+      <c r="AF18" s="16">
+        <f>IF(AD18=0,0,AD18*1.7/12*AQ18)</f>
+        <v/>
+      </c>
+      <c r="AG18" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A18,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A18,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AH18" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A18,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
+      <c r="AI18" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A18,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AJ18" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A18),0)</f>
+        <v/>
+      </c>
+      <c r="AK18" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A18),0)</f>
+        <v/>
+      </c>
+      <c r="AL18" s="16">
+        <f>(IF((AE18)&lt;(AG18+AH18+AI18),(AE18),(AG18+AH18+AI18)))+AJ18*5+AK18*10+R18+T18+V18</f>
+        <v/>
+      </c>
+      <c r="AM18" s="16">
+        <f>AL18-J18</f>
+        <v/>
+      </c>
+      <c r="AP18" s="16">
+        <f>IF(E18=0,"",(B18*0.95+C18*0.25+D18*0)/E18)</f>
+        <v/>
+      </c>
+      <c r="AQ18" s="16">
+        <f>IF(I18=0,"",(F18*0.95+G18*0.25+H18*0)/I18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="16.25" customHeight="1">
+      <c r="A19" s="16">
+        <f>'SDA'!A65</f>
+        <v/>
       </c>
       <c r="B19" s="16">
-        <f>SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,'SDA'!A58,'SDA'!$C$4:$C$53,"Natural (Woods)")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Total outside LOD (SF)</t>
-        </is>
+        <f>'SDA'!F65</f>
+        <v/>
+      </c>
+      <c r="C19" s="16">
+        <f>'SDA'!G65</f>
+        <v/>
+      </c>
+      <c r="D19" s="16">
+        <f>'SDA'!H65</f>
+        <v/>
+      </c>
+      <c r="E19" s="16">
+        <f>SUM(B19:D19)</f>
+        <v/>
+      </c>
+      <c r="F19" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A19,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A19,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <v/>
+      </c>
+      <c r="G19" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A19,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <v/>
+      </c>
+      <c r="H19" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A19,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <v/>
+      </c>
+      <c r="I19" s="16">
+        <f>SUM(F19:H19)</f>
+        <v/>
+      </c>
+      <c r="J19" s="16">
+        <f>IF(E19=0,0,AP19*1.2/12*E19)</f>
+        <v/>
+      </c>
+      <c r="K19" s="16">
+        <f>IF(I19=0,0,AQ19*1.2/12*I19)</f>
+        <v/>
+      </c>
+      <c r="L19" s="16">
+        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A19,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A19,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A19,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A19,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <v/>
+      </c>
+      <c r="M19" s="4" t="n"/>
+      <c r="N19" s="4" t="n"/>
+      <c r="O19" s="16">
+        <f>IFERROR(IFS(L19="A",2.5,L19="B",0.3,L19="C",0.1,L19="D",0.05,TRUE,""),"")</f>
+        <v/>
+      </c>
+      <c r="P19" s="4" t="n"/>
+      <c r="Q19" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A19),0)</f>
+        <v/>
+      </c>
+      <c r="R19" s="16">
+        <f>Q19*10</f>
+        <v/>
+      </c>
+      <c r="S19" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A19),0)</f>
+        <v/>
+      </c>
+      <c r="T19" s="16">
+        <f>S19*20</f>
+        <v/>
+      </c>
+      <c r="U19" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A19)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A19),0)</f>
+        <v/>
+      </c>
+      <c r="V19" s="16">
+        <f>U19*40</f>
+        <v/>
+      </c>
+      <c r="W19" s="4" t="n"/>
+      <c r="X19" s="4" t="n"/>
+      <c r="Y19" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A19,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A19,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="Z19" s="4" t="n"/>
+      <c r="AA19" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A19,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
+      <c r="AB19" s="4" t="n"/>
+      <c r="AC19" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A19),0)</f>
+        <v/>
+      </c>
+      <c r="AD19" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A19),0)</f>
+        <v/>
+      </c>
+      <c r="AE19" s="16">
+        <f>IF(AC19=0,0,AC19*1.7/12*AP19)</f>
+        <v/>
+      </c>
+      <c r="AF19" s="16">
+        <f>IF(AD19=0,0,AD19*1.7/12*AQ19)</f>
+        <v/>
+      </c>
+      <c r="AG19" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A19,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A19,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AH19" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A19,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
+      <c r="AI19" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A19,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AJ19" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A19),0)</f>
+        <v/>
+      </c>
+      <c r="AK19" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A19),0)</f>
+        <v/>
+      </c>
+      <c r="AL19" s="16">
+        <f>(IF((AE19)&lt;(AG19+AH19+AI19),(AE19),(AG19+AH19+AI19)))+AJ19*5+AK19*10+R19+T19+V19</f>
+        <v/>
+      </c>
+      <c r="AM19" s="16">
+        <f>AL19-J19</f>
+        <v/>
+      </c>
+      <c r="AP19" s="16">
+        <f>IF(E19=0,"",(B19*0.95+C19*0.25+D19*0)/E19)</f>
+        <v/>
+      </c>
+      <c r="AQ19" s="16">
+        <f>IF(I19=0,"",(F19*0.95+G19*0.25+H19*0)/I19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="16.25" customHeight="1">
+      <c r="A20" s="16">
+        <f>'SDA'!A66</f>
+        <v/>
       </c>
       <c r="B20" s="16">
-        <f>SUM(B17:B19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>SWRv Within LOD (CF)</t>
-        </is>
+        <f>'SDA'!F66</f>
+        <v/>
+      </c>
+      <c r="C20" s="16">
+        <f>'SDA'!G66</f>
+        <v/>
+      </c>
+      <c r="D20" s="16">
+        <f>'SDA'!H66</f>
+        <v/>
+      </c>
+      <c r="E20" s="16">
+        <f>SUM(B20:D20)</f>
+        <v/>
+      </c>
+      <c r="F20" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A20,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A20,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <v/>
+      </c>
+      <c r="G20" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A20,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <v/>
+      </c>
+      <c r="H20" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A20,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <v/>
+      </c>
+      <c r="I20" s="16">
+        <f>SUM(F20:H20)</f>
+        <v/>
+      </c>
+      <c r="J20" s="16">
+        <f>IF(E20=0,0,AP20*1.2/12*E20)</f>
+        <v/>
+      </c>
+      <c r="K20" s="16">
+        <f>IF(I20=0,0,AQ20*1.2/12*I20)</f>
+        <v/>
+      </c>
+      <c r="L20" s="16">
+        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A20,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A20,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A20,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A20,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <v/>
+      </c>
+      <c r="M20" s="4" t="n"/>
+      <c r="N20" s="4" t="n"/>
+      <c r="O20" s="16">
+        <f>IFERROR(IFS(L20="A",2.5,L20="B",0.3,L20="C",0.1,L20="D",0.05,TRUE,""),"")</f>
+        <v/>
+      </c>
+      <c r="P20" s="4" t="n"/>
+      <c r="Q20" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A20),0)</f>
+        <v/>
+      </c>
+      <c r="R20" s="16">
+        <f>Q20*10</f>
+        <v/>
+      </c>
+      <c r="S20" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A20),0)</f>
+        <v/>
+      </c>
+      <c r="T20" s="16">
+        <f>S20*20</f>
+        <v/>
+      </c>
+      <c r="U20" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A20)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A20),0)</f>
+        <v/>
+      </c>
+      <c r="V20" s="16">
+        <f>U20*40</f>
+        <v/>
+      </c>
+      <c r="W20" s="4" t="n"/>
+      <c r="X20" s="4" t="n"/>
+      <c r="Y20" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A20,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A20,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="Z20" s="4" t="n"/>
+      <c r="AA20" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A20,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
+      <c r="AB20" s="4" t="n"/>
+      <c r="AC20" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A20),0)</f>
+        <v/>
+      </c>
+      <c r="AD20" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A20),0)</f>
+        <v/>
+      </c>
+      <c r="AE20" s="16">
+        <f>IF(AC20=0,0,AC20*1.7/12*AP20)</f>
+        <v/>
+      </c>
+      <c r="AF20" s="16">
+        <f>IF(AD20=0,0,AD20*1.7/12*AQ20)</f>
+        <v/>
+      </c>
+      <c r="AG20" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A20,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A20,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AH20" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A20,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
+      <c r="AI20" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A20,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AJ20" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A20),0)</f>
+        <v/>
+      </c>
+      <c r="AK20" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A20),0)</f>
+        <v/>
+      </c>
+      <c r="AL20" s="16">
+        <f>(IF((AE20)&lt;(AG20+AH20+AI20),(AE20),(AG20+AH20+AI20)))+AJ20*5+AK20*10+R20+T20+V20</f>
+        <v/>
+      </c>
+      <c r="AM20" s="16">
+        <f>AL20-J20</f>
+        <v/>
+      </c>
+      <c r="AP20" s="16">
+        <f>IF(E20=0,"",(B20*0.95+C20*0.25+D20*0)/E20)</f>
+        <v/>
+      </c>
+      <c r="AQ20" s="16">
+        <f>IF(I20=0,"",(F20*0.95+G20*0.25+H20*0)/I20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="16.25" customHeight="1">
+      <c r="A21" s="16">
+        <f>'SDA'!A67</f>
+        <v/>
       </c>
       <c r="B21" s="16">
-        <f>'SDA'!J58</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>Step 2 — Infiltration</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="n"/>
-      <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
-      <c r="E22" s="7" t="n"/>
-      <c r="F22" s="7" t="n"/>
-      <c r="G22" s="8" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>Hydrologic Soil Group</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>Water Table OK?</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>Bedrock OK?</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>Infiltration Rate (in/hr)</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>Step 3 — Constraints</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="n"/>
-      <c r="C27" s="7" t="n"/>
-      <c r="D27" s="7" t="n"/>
-      <c r="E27" s="7" t="n"/>
-      <c r="F27" s="7" t="n"/>
-      <c r="G27" s="8" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>Hotspot Concern?</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>Step 4 — Tree Credits (DDOT)</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="n"/>
-      <c r="C29" s="7" t="n"/>
-      <c r="D29" s="7" t="n"/>
-      <c r="E29" s="7" t="n"/>
-      <c r="F29" s="7" t="n"/>
-      <c r="G29" s="8" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>Small Trees (preserved+planted)</t>
-        </is>
-      </c>
-      <c r="B30" s="16">
-        <f>(5)*(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,'SDA'!A58)+SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,'SDA'!A58))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>Large Trees (preserved+planted)</t>
-        </is>
-      </c>
-      <c r="B31" s="16">
-        <f>(20)*(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,'SDA'!A58)+SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,'SDA'!A58))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="10" t="inlineStr">
-        <is>
-          <t>Special Trees preserved</t>
-        </is>
-      </c>
-      <c r="B32" s="16">
-        <f>(30)*SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,'SDA'!A58)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="10" t="inlineStr">
-        <is>
-          <t>Heritage Trees preserved</t>
-        </is>
-      </c>
-      <c r="B33" s="16">
-        <f>(40)*SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,'SDA'!A58)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>Step 4 — BMP Placement</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="n"/>
-      <c r="C34" s="7" t="n"/>
-      <c r="D34" s="7" t="n"/>
-      <c r="E34" s="7" t="n"/>
-      <c r="F34" s="7" t="n"/>
-      <c r="G34" s="8" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="17" t="inlineStr">
-        <is>
-          <t>BMP Name</t>
-        </is>
-      </c>
-      <c r="B35" s="17" t="inlineStr">
-        <is>
-          <t>BMP Type</t>
-        </is>
-      </c>
-      <c r="C35" s="17" t="inlineStr">
-        <is>
-          <t>CDA_ID</t>
-        </is>
-      </c>
-      <c r="D35" s="17" t="inlineStr">
-        <is>
-          <t>CDA Within LOD (SF)</t>
-        </is>
-      </c>
-      <c r="E35" s="17" t="inlineStr">
-        <is>
-          <t>CDA Outside LOD (SF)</t>
-        </is>
-      </c>
-      <c r="F35" s="17" t="inlineStr">
-        <is>
-          <t>BMP Rv (CF)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="16">
-        <f>IFERROR(INDEX('BMP'!$A$4:$A$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A58,ROW('BMP'!$B$4:$B$53)-3),1)),"")</f>
-        <v/>
-      </c>
-      <c r="B36" s="16">
-        <f>IFERROR(INDEX('BMP'!$D$4:$D$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A58,ROW('BMP'!$B$4:$B$53)-3),1)),"")</f>
-        <v/>
-      </c>
-      <c r="C36" s="16">
-        <f>IFERROR(INDEX('BMP'!$C$4:$C$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A58,ROW('BMP'!$B$4:$B$53)-3),1)),"")</f>
-        <v/>
-      </c>
-      <c r="F36" s="16">
-        <f>IFERROR(INDEX('BMP'!$AM$4:$AM$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A58,ROW('BMP'!$B$4:$B$53)-3),1)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="16">
-        <f>IFERROR(INDEX('BMP'!$A$4:$A$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A58,ROW('BMP'!$B$4:$B$53)-3),2)),"")</f>
-        <v/>
-      </c>
-      <c r="B37" s="16">
-        <f>IFERROR(INDEX('BMP'!$D$4:$D$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A58,ROW('BMP'!$B$4:$B$53)-3),2)),"")</f>
-        <v/>
-      </c>
-      <c r="C37" s="16">
-        <f>IFERROR(INDEX('BMP'!$C$4:$C$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A58,ROW('BMP'!$B$4:$B$53)-3),2)),"")</f>
-        <v/>
-      </c>
-      <c r="F37" s="16">
-        <f>IFERROR(INDEX('BMP'!$AM$4:$AM$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A58,ROW('BMP'!$B$4:$B$53)-3),2)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="16">
-        <f>IFERROR(INDEX('BMP'!$A$4:$A$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A58,ROW('BMP'!$B$4:$B$53)-3),3)),"")</f>
-        <v/>
-      </c>
-      <c r="B38" s="16">
-        <f>IFERROR(INDEX('BMP'!$D$4:$D$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A58,ROW('BMP'!$B$4:$B$53)-3),3)),"")</f>
-        <v/>
-      </c>
-      <c r="C38" s="16">
-        <f>IFERROR(INDEX('BMP'!$C$4:$C$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A58,ROW('BMP'!$B$4:$B$53)-3),3)),"")</f>
-        <v/>
-      </c>
-      <c r="F38" s="16">
-        <f>IFERROR(INDEX('BMP'!$AM$4:$AM$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A58,ROW('BMP'!$B$4:$B$53)-3),3)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="16">
-        <f>IFERROR(INDEX('BMP'!$A$4:$A$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A58,ROW('BMP'!$B$4:$B$53)-3),4)),"")</f>
-        <v/>
-      </c>
-      <c r="B39" s="16">
-        <f>IFERROR(INDEX('BMP'!$D$4:$D$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A58,ROW('BMP'!$B$4:$B$53)-3),4)),"")</f>
-        <v/>
-      </c>
-      <c r="C39" s="16">
-        <f>IFERROR(INDEX('BMP'!$C$4:$C$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A58,ROW('BMP'!$B$4:$B$53)-3),4)),"")</f>
-        <v/>
-      </c>
-      <c r="F39" s="16">
-        <f>IFERROR(INDEX('BMP'!$AM$4:$AM$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A58,ROW('BMP'!$B$4:$B$53)-3),4)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="16">
-        <f>IFERROR(INDEX('BMP'!$A$4:$A$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A58,ROW('BMP'!$B$4:$B$53)-3),5)),"")</f>
-        <v/>
-      </c>
-      <c r="B40" s="16">
-        <f>IFERROR(INDEX('BMP'!$D$4:$D$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A58,ROW('BMP'!$B$4:$B$53)-3),5)),"")</f>
-        <v/>
-      </c>
-      <c r="C40" s="16">
-        <f>IFERROR(INDEX('BMP'!$C$4:$C$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A58,ROW('BMP'!$B$4:$B$53)-3),5)),"")</f>
-        <v/>
-      </c>
-      <c r="F40" s="16">
-        <f>IFERROR(INDEX('BMP'!$AM$4:$AM$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A58,ROW('BMP'!$B$4:$B$53)-3),5)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>Cumulative Surplus / Deficit (CF)</t>
-        </is>
-      </c>
-      <c r="B41" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AM$4:$AM$53,'BMP'!$B$4:$B$53,'SDA'!A58)-'SDA'!J58,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="inlineStr">
-        <is>
-          <t>SDA-2</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="n"/>
-      <c r="C43" s="5" t="n"/>
-      <c r="D43" s="5" t="n"/>
-      <c r="E43" s="5" t="n"/>
-      <c r="F43" s="5" t="n"/>
-      <c r="G43" s="2" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>Step 1 — Drainage Area &amp; Regulated Volumes</t>
-        </is>
-      </c>
-      <c r="B44" s="7" t="n"/>
-      <c r="C44" s="7" t="n"/>
-      <c r="D44" s="7" t="n"/>
-      <c r="E44" s="7" t="n"/>
-      <c r="F44" s="7" t="n"/>
-      <c r="G44" s="8" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>Drainage Area ID</t>
-        </is>
-      </c>
-      <c r="B45" s="16">
-        <f>'SDA'!A59</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="10" t="inlineStr">
-        <is>
-          <t>Impervious within LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B46" s="16">
-        <f>SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,'SDA'!A59,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,'SDA'!A59,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="10" t="inlineStr">
-        <is>
-          <t>Compacted within LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B47" s="16">
-        <f>SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,'SDA'!A59,'SDA'!$C$4:$C$53,"Compacted (Open Space)")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="10" t="inlineStr">
-        <is>
-          <t>Natural within LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B48" s="16">
-        <f>SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,'SDA'!A59,'SDA'!$C$4:$C$53,"Natural (Woods)")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>Total within LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B49" s="16">
-        <f>SUM(B46:B48)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="10" t="inlineStr">
-        <is>
-          <t>Impervious outside LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B50" s="16">
-        <f>SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,'SDA'!A59,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,'SDA'!A59,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="10" t="inlineStr">
-        <is>
-          <t>Compacted outside LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B51" s="16">
-        <f>SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,'SDA'!A59,'SDA'!$C$4:$C$53,"Compacted (Open Space)")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="10" t="inlineStr">
-        <is>
-          <t>Natural outside LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B52" s="16">
-        <f>SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,'SDA'!A59,'SDA'!$C$4:$C$53,"Natural (Woods)")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>Total outside LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B53" s="16">
-        <f>SUM(B50:B52)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>SWRv Within LOD (CF)</t>
-        </is>
-      </c>
-      <c r="B54" s="16">
-        <f>'SDA'!J59</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>Step 2 — Infiltration</t>
-        </is>
-      </c>
-      <c r="B55" s="7" t="n"/>
-      <c r="C55" s="7" t="n"/>
-      <c r="D55" s="7" t="n"/>
-      <c r="E55" s="7" t="n"/>
-      <c r="F55" s="7" t="n"/>
-      <c r="G55" s="8" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="10" t="inlineStr">
-        <is>
-          <t>Hydrologic Soil Group</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="10" t="inlineStr">
-        <is>
-          <t>Water Table OK?</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="10" t="inlineStr">
-        <is>
-          <t>Bedrock OK?</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="10" t="inlineStr">
-        <is>
-          <t>Infiltration Rate (in/hr)</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>Step 3 — Constraints</t>
-        </is>
-      </c>
-      <c r="B60" s="7" t="n"/>
-      <c r="C60" s="7" t="n"/>
-      <c r="D60" s="7" t="n"/>
-      <c r="E60" s="7" t="n"/>
-      <c r="F60" s="7" t="n"/>
-      <c r="G60" s="8" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="10" t="inlineStr">
-        <is>
-          <t>Hotspot Concern?</t>
-        </is>
-      </c>
-      <c r="B61" s="4" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="6" t="inlineStr">
-        <is>
-          <t>Step 4 — Tree Credits (DDOT)</t>
-        </is>
-      </c>
-      <c r="B62" s="7" t="n"/>
-      <c r="C62" s="7" t="n"/>
-      <c r="D62" s="7" t="n"/>
-      <c r="E62" s="7" t="n"/>
-      <c r="F62" s="7" t="n"/>
-      <c r="G62" s="8" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="10" t="inlineStr">
-        <is>
-          <t>Small Trees (preserved+planted)</t>
-        </is>
-      </c>
-      <c r="B63" s="16">
-        <f>(5)*(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,'SDA'!A59)+SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,'SDA'!A59))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="10" t="inlineStr">
-        <is>
-          <t>Large Trees (preserved+planted)</t>
-        </is>
-      </c>
-      <c r="B64" s="16">
-        <f>(20)*(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,'SDA'!A59)+SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,'SDA'!A59))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="10" t="inlineStr">
-        <is>
-          <t>Special Trees preserved</t>
-        </is>
-      </c>
-      <c r="B65" s="16">
-        <f>(30)*SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,'SDA'!A59)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="10" t="inlineStr">
-        <is>
-          <t>Heritage Trees preserved</t>
-        </is>
-      </c>
-      <c r="B66" s="16">
-        <f>(40)*SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,'SDA'!A59)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="6" t="inlineStr">
-        <is>
-          <t>Step 4 — BMP Placement</t>
-        </is>
-      </c>
-      <c r="B67" s="7" t="n"/>
-      <c r="C67" s="7" t="n"/>
-      <c r="D67" s="7" t="n"/>
-      <c r="E67" s="7" t="n"/>
-      <c r="F67" s="7" t="n"/>
-      <c r="G67" s="8" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="17" t="inlineStr">
-        <is>
-          <t>BMP Name</t>
-        </is>
-      </c>
-      <c r="B68" s="17" t="inlineStr">
-        <is>
-          <t>BMP Type</t>
-        </is>
-      </c>
-      <c r="C68" s="17" t="inlineStr">
-        <is>
-          <t>CDA_ID</t>
-        </is>
-      </c>
-      <c r="D68" s="17" t="inlineStr">
-        <is>
-          <t>CDA Within LOD (SF)</t>
-        </is>
-      </c>
-      <c r="E68" s="17" t="inlineStr">
-        <is>
-          <t>CDA Outside LOD (SF)</t>
-        </is>
-      </c>
-      <c r="F68" s="17" t="inlineStr">
-        <is>
-          <t>BMP Rv (CF)</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="16">
-        <f>IFERROR(INDEX('BMP'!$A$4:$A$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A59,ROW('BMP'!$B$4:$B$53)-3),1)),"")</f>
-        <v/>
-      </c>
-      <c r="B69" s="16">
-        <f>IFERROR(INDEX('BMP'!$D$4:$D$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A59,ROW('BMP'!$B$4:$B$53)-3),1)),"")</f>
-        <v/>
-      </c>
-      <c r="C69" s="16">
-        <f>IFERROR(INDEX('BMP'!$C$4:$C$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A59,ROW('BMP'!$B$4:$B$53)-3),1)),"")</f>
-        <v/>
-      </c>
-      <c r="F69" s="16">
-        <f>IFERROR(INDEX('BMP'!$AM$4:$AM$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A59,ROW('BMP'!$B$4:$B$53)-3),1)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="16">
-        <f>IFERROR(INDEX('BMP'!$A$4:$A$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A59,ROW('BMP'!$B$4:$B$53)-3),2)),"")</f>
-        <v/>
-      </c>
-      <c r="B70" s="16">
-        <f>IFERROR(INDEX('BMP'!$D$4:$D$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A59,ROW('BMP'!$B$4:$B$53)-3),2)),"")</f>
-        <v/>
-      </c>
-      <c r="C70" s="16">
-        <f>IFERROR(INDEX('BMP'!$C$4:$C$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A59,ROW('BMP'!$B$4:$B$53)-3),2)),"")</f>
-        <v/>
-      </c>
-      <c r="F70" s="16">
-        <f>IFERROR(INDEX('BMP'!$AM$4:$AM$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A59,ROW('BMP'!$B$4:$B$53)-3),2)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="16">
-        <f>IFERROR(INDEX('BMP'!$A$4:$A$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A59,ROW('BMP'!$B$4:$B$53)-3),3)),"")</f>
-        <v/>
-      </c>
-      <c r="B71" s="16">
-        <f>IFERROR(INDEX('BMP'!$D$4:$D$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A59,ROW('BMP'!$B$4:$B$53)-3),3)),"")</f>
-        <v/>
-      </c>
-      <c r="C71" s="16">
-        <f>IFERROR(INDEX('BMP'!$C$4:$C$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A59,ROW('BMP'!$B$4:$B$53)-3),3)),"")</f>
-        <v/>
-      </c>
-      <c r="F71" s="16">
-        <f>IFERROR(INDEX('BMP'!$AM$4:$AM$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A59,ROW('BMP'!$B$4:$B$53)-3),3)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="16">
-        <f>IFERROR(INDEX('BMP'!$A$4:$A$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A59,ROW('BMP'!$B$4:$B$53)-3),4)),"")</f>
-        <v/>
-      </c>
-      <c r="B72" s="16">
-        <f>IFERROR(INDEX('BMP'!$D$4:$D$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A59,ROW('BMP'!$B$4:$B$53)-3),4)),"")</f>
-        <v/>
-      </c>
-      <c r="C72" s="16">
-        <f>IFERROR(INDEX('BMP'!$C$4:$C$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A59,ROW('BMP'!$B$4:$B$53)-3),4)),"")</f>
-        <v/>
-      </c>
-      <c r="F72" s="16">
-        <f>IFERROR(INDEX('BMP'!$AM$4:$AM$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A59,ROW('BMP'!$B$4:$B$53)-3),4)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="16">
-        <f>IFERROR(INDEX('BMP'!$A$4:$A$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A59,ROW('BMP'!$B$4:$B$53)-3),5)),"")</f>
-        <v/>
-      </c>
-      <c r="B73" s="16">
-        <f>IFERROR(INDEX('BMP'!$D$4:$D$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A59,ROW('BMP'!$B$4:$B$53)-3),5)),"")</f>
-        <v/>
-      </c>
-      <c r="C73" s="16">
-        <f>IFERROR(INDEX('BMP'!$C$4:$C$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A59,ROW('BMP'!$B$4:$B$53)-3),5)),"")</f>
-        <v/>
-      </c>
-      <c r="F73" s="16">
-        <f>IFERROR(INDEX('BMP'!$AM$4:$AM$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A59,ROW('BMP'!$B$4:$B$53)-3),5)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="3" t="inlineStr">
-        <is>
-          <t>Cumulative Surplus / Deficit (CF)</t>
-        </is>
-      </c>
-      <c r="B74" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AM$4:$AM$53,'BMP'!$B$4:$B$53,'SDA'!A59)-'SDA'!J59,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="1" t="inlineStr">
-        <is>
-          <t>SDA-3</t>
-        </is>
-      </c>
-      <c r="B76" s="5" t="n"/>
-      <c r="C76" s="5" t="n"/>
-      <c r="D76" s="5" t="n"/>
-      <c r="E76" s="5" t="n"/>
-      <c r="F76" s="5" t="n"/>
-      <c r="G76" s="2" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>Step 1 — Drainage Area &amp; Regulated Volumes</t>
-        </is>
-      </c>
-      <c r="B77" s="7" t="n"/>
-      <c r="C77" s="7" t="n"/>
-      <c r="D77" s="7" t="n"/>
-      <c r="E77" s="7" t="n"/>
-      <c r="F77" s="7" t="n"/>
-      <c r="G77" s="8" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="10" t="inlineStr">
-        <is>
-          <t>Drainage Area ID</t>
-        </is>
-      </c>
-      <c r="B78" s="16">
-        <f>'SDA'!A60</f>
-        <v/>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="10" t="inlineStr">
-        <is>
-          <t>Impervious within LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B79" s="16">
-        <f>SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,'SDA'!A60,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,'SDA'!A60,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="10" t="inlineStr">
-        <is>
-          <t>Compacted within LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B80" s="16">
-        <f>SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,'SDA'!A60,'SDA'!$C$4:$C$53,"Compacted (Open Space)")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="10" t="inlineStr">
-        <is>
-          <t>Natural within LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B81" s="16">
-        <f>SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,'SDA'!A60,'SDA'!$C$4:$C$53,"Natural (Woods)")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="3" t="inlineStr">
-        <is>
-          <t>Total within LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B82" s="16">
-        <f>SUM(B79:B81)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="10" t="inlineStr">
-        <is>
-          <t>Impervious outside LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B83" s="16">
-        <f>SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,'SDA'!A60,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,'SDA'!A60,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="10" t="inlineStr">
-        <is>
-          <t>Compacted outside LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B84" s="16">
-        <f>SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,'SDA'!A60,'SDA'!$C$4:$C$53,"Compacted (Open Space)")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="10" t="inlineStr">
-        <is>
-          <t>Natural outside LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B85" s="16">
-        <f>SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,'SDA'!A60,'SDA'!$C$4:$C$53,"Natural (Woods)")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="3" t="inlineStr">
-        <is>
-          <t>Total outside LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B86" s="16">
-        <f>SUM(B83:B85)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="3" t="inlineStr">
-        <is>
-          <t>SWRv Within LOD (CF)</t>
-        </is>
-      </c>
-      <c r="B87" s="16">
-        <f>'SDA'!J60</f>
-        <v/>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="6" t="inlineStr">
-        <is>
-          <t>Step 2 — Infiltration</t>
-        </is>
-      </c>
-      <c r="B88" s="7" t="n"/>
-      <c r="C88" s="7" t="n"/>
-      <c r="D88" s="7" t="n"/>
-      <c r="E88" s="7" t="n"/>
-      <c r="F88" s="7" t="n"/>
-      <c r="G88" s="8" t="n"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="10" t="inlineStr">
-        <is>
-          <t>Hydrologic Soil Group</t>
-        </is>
-      </c>
-      <c r="B89" s="4" t="n"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="10" t="inlineStr">
-        <is>
-          <t>Water Table OK?</t>
-        </is>
-      </c>
-      <c r="B90" s="4" t="n"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="10" t="inlineStr">
-        <is>
-          <t>Bedrock OK?</t>
-        </is>
-      </c>
-      <c r="B91" s="4" t="n"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="10" t="inlineStr">
-        <is>
-          <t>Infiltration Rate (in/hr)</t>
-        </is>
-      </c>
-      <c r="B92" s="4" t="n"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="6" t="inlineStr">
-        <is>
-          <t>Step 3 — Constraints</t>
-        </is>
-      </c>
-      <c r="B93" s="7" t="n"/>
-      <c r="C93" s="7" t="n"/>
-      <c r="D93" s="7" t="n"/>
-      <c r="E93" s="7" t="n"/>
-      <c r="F93" s="7" t="n"/>
-      <c r="G93" s="8" t="n"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="10" t="inlineStr">
-        <is>
-          <t>Hotspot Concern?</t>
-        </is>
-      </c>
-      <c r="B94" s="4" t="n"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="6" t="inlineStr">
-        <is>
-          <t>Step 4 — Tree Credits (DDOT)</t>
-        </is>
-      </c>
-      <c r="B95" s="7" t="n"/>
-      <c r="C95" s="7" t="n"/>
-      <c r="D95" s="7" t="n"/>
-      <c r="E95" s="7" t="n"/>
-      <c r="F95" s="7" t="n"/>
-      <c r="G95" s="8" t="n"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="10" t="inlineStr">
-        <is>
-          <t>Small Trees (preserved+planted)</t>
-        </is>
-      </c>
-      <c r="B96" s="16">
-        <f>(5)*(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,'SDA'!A60)+SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,'SDA'!A60))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="10" t="inlineStr">
-        <is>
-          <t>Large Trees (preserved+planted)</t>
-        </is>
-      </c>
-      <c r="B97" s="16">
-        <f>(20)*(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,'SDA'!A60)+SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,'SDA'!A60))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="10" t="inlineStr">
-        <is>
-          <t>Special Trees preserved</t>
-        </is>
-      </c>
-      <c r="B98" s="16">
-        <f>(30)*SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,'SDA'!A60)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="10" t="inlineStr">
-        <is>
-          <t>Heritage Trees preserved</t>
-        </is>
-      </c>
-      <c r="B99" s="16">
-        <f>(40)*SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,'SDA'!A60)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="6" t="inlineStr">
-        <is>
-          <t>Step 4 — BMP Placement</t>
-        </is>
-      </c>
-      <c r="B100" s="7" t="n"/>
-      <c r="C100" s="7" t="n"/>
-      <c r="D100" s="7" t="n"/>
-      <c r="E100" s="7" t="n"/>
-      <c r="F100" s="7" t="n"/>
-      <c r="G100" s="8" t="n"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="17" t="inlineStr">
-        <is>
-          <t>BMP Name</t>
-        </is>
-      </c>
-      <c r="B101" s="17" t="inlineStr">
-        <is>
-          <t>BMP Type</t>
-        </is>
-      </c>
-      <c r="C101" s="17" t="inlineStr">
-        <is>
-          <t>CDA_ID</t>
-        </is>
-      </c>
-      <c r="D101" s="17" t="inlineStr">
-        <is>
-          <t>CDA Within LOD (SF)</t>
-        </is>
-      </c>
-      <c r="E101" s="17" t="inlineStr">
-        <is>
-          <t>CDA Outside LOD (SF)</t>
-        </is>
-      </c>
-      <c r="F101" s="17" t="inlineStr">
-        <is>
-          <t>BMP Rv (CF)</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="16">
-        <f>IFERROR(INDEX('BMP'!$A$4:$A$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A60,ROW('BMP'!$B$4:$B$53)-3),1)),"")</f>
-        <v/>
-      </c>
-      <c r="B102" s="16">
-        <f>IFERROR(INDEX('BMP'!$D$4:$D$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A60,ROW('BMP'!$B$4:$B$53)-3),1)),"")</f>
-        <v/>
-      </c>
-      <c r="C102" s="16">
-        <f>IFERROR(INDEX('BMP'!$C$4:$C$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A60,ROW('BMP'!$B$4:$B$53)-3),1)),"")</f>
-        <v/>
-      </c>
-      <c r="F102" s="16">
-        <f>IFERROR(INDEX('BMP'!$AM$4:$AM$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A60,ROW('BMP'!$B$4:$B$53)-3),1)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="16">
-        <f>IFERROR(INDEX('BMP'!$A$4:$A$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A60,ROW('BMP'!$B$4:$B$53)-3),2)),"")</f>
-        <v/>
-      </c>
-      <c r="B103" s="16">
-        <f>IFERROR(INDEX('BMP'!$D$4:$D$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A60,ROW('BMP'!$B$4:$B$53)-3),2)),"")</f>
-        <v/>
-      </c>
-      <c r="C103" s="16">
-        <f>IFERROR(INDEX('BMP'!$C$4:$C$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A60,ROW('BMP'!$B$4:$B$53)-3),2)),"")</f>
-        <v/>
-      </c>
-      <c r="F103" s="16">
-        <f>IFERROR(INDEX('BMP'!$AM$4:$AM$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A60,ROW('BMP'!$B$4:$B$53)-3),2)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="16">
-        <f>IFERROR(INDEX('BMP'!$A$4:$A$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A60,ROW('BMP'!$B$4:$B$53)-3),3)),"")</f>
-        <v/>
-      </c>
-      <c r="B104" s="16">
-        <f>IFERROR(INDEX('BMP'!$D$4:$D$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A60,ROW('BMP'!$B$4:$B$53)-3),3)),"")</f>
-        <v/>
-      </c>
-      <c r="C104" s="16">
-        <f>IFERROR(INDEX('BMP'!$C$4:$C$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A60,ROW('BMP'!$B$4:$B$53)-3),3)),"")</f>
-        <v/>
-      </c>
-      <c r="F104" s="16">
-        <f>IFERROR(INDEX('BMP'!$AM$4:$AM$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A60,ROW('BMP'!$B$4:$B$53)-3),3)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="16">
-        <f>IFERROR(INDEX('BMP'!$A$4:$A$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A60,ROW('BMP'!$B$4:$B$53)-3),4)),"")</f>
-        <v/>
-      </c>
-      <c r="B105" s="16">
-        <f>IFERROR(INDEX('BMP'!$D$4:$D$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A60,ROW('BMP'!$B$4:$B$53)-3),4)),"")</f>
-        <v/>
-      </c>
-      <c r="C105" s="16">
-        <f>IFERROR(INDEX('BMP'!$C$4:$C$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A60,ROW('BMP'!$B$4:$B$53)-3),4)),"")</f>
-        <v/>
-      </c>
-      <c r="F105" s="16">
-        <f>IFERROR(INDEX('BMP'!$AM$4:$AM$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A60,ROW('BMP'!$B$4:$B$53)-3),4)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="16">
-        <f>IFERROR(INDEX('BMP'!$A$4:$A$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A60,ROW('BMP'!$B$4:$B$53)-3),5)),"")</f>
-        <v/>
-      </c>
-      <c r="B106" s="16">
-        <f>IFERROR(INDEX('BMP'!$D$4:$D$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A60,ROW('BMP'!$B$4:$B$53)-3),5)),"")</f>
-        <v/>
-      </c>
-      <c r="C106" s="16">
-        <f>IFERROR(INDEX('BMP'!$C$4:$C$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A60,ROW('BMP'!$B$4:$B$53)-3),5)),"")</f>
-        <v/>
-      </c>
-      <c r="F106" s="16">
-        <f>IFERROR(INDEX('BMP'!$AM$4:$AM$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A60,ROW('BMP'!$B$4:$B$53)-3),5)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="3" t="inlineStr">
-        <is>
-          <t>Cumulative Surplus / Deficit (CF)</t>
-        </is>
-      </c>
-      <c r="B107" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AM$4:$AM$53,'BMP'!$B$4:$B$53,'SDA'!A60)-'SDA'!J60,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="1" t="inlineStr">
-        <is>
-          <t>SDA-4</t>
-        </is>
-      </c>
-      <c r="B109" s="5" t="n"/>
-      <c r="C109" s="5" t="n"/>
-      <c r="D109" s="5" t="n"/>
-      <c r="E109" s="5" t="n"/>
-      <c r="F109" s="5" t="n"/>
-      <c r="G109" s="2" t="n"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="6" t="inlineStr">
-        <is>
-          <t>Step 1 — Drainage Area &amp; Regulated Volumes</t>
-        </is>
-      </c>
-      <c r="B110" s="7" t="n"/>
-      <c r="C110" s="7" t="n"/>
-      <c r="D110" s="7" t="n"/>
-      <c r="E110" s="7" t="n"/>
-      <c r="F110" s="7" t="n"/>
-      <c r="G110" s="8" t="n"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="10" t="inlineStr">
-        <is>
-          <t>Drainage Area ID</t>
-        </is>
-      </c>
-      <c r="B111" s="16">
-        <f>'SDA'!A61</f>
-        <v/>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="10" t="inlineStr">
-        <is>
-          <t>Impervious within LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B112" s="16">
-        <f>SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,'SDA'!A61,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,'SDA'!A61,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="10" t="inlineStr">
-        <is>
-          <t>Compacted within LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B113" s="16">
-        <f>SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,'SDA'!A61,'SDA'!$C$4:$C$53,"Compacted (Open Space)")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="10" t="inlineStr">
-        <is>
-          <t>Natural within LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B114" s="16">
-        <f>SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,'SDA'!A61,'SDA'!$C$4:$C$53,"Natural (Woods)")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="3" t="inlineStr">
-        <is>
-          <t>Total within LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B115" s="16">
-        <f>SUM(B112:B114)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="10" t="inlineStr">
-        <is>
-          <t>Impervious outside LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B116" s="16">
-        <f>SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,'SDA'!A61,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,'SDA'!A61,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="10" t="inlineStr">
-        <is>
-          <t>Compacted outside LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B117" s="16">
-        <f>SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,'SDA'!A61,'SDA'!$C$4:$C$53,"Compacted (Open Space)")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="10" t="inlineStr">
-        <is>
-          <t>Natural outside LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B118" s="16">
-        <f>SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,'SDA'!A61,'SDA'!$C$4:$C$53,"Natural (Woods)")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="3" t="inlineStr">
-        <is>
-          <t>Total outside LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B119" s="16">
-        <f>SUM(B116:B118)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="3" t="inlineStr">
-        <is>
-          <t>SWRv Within LOD (CF)</t>
-        </is>
-      </c>
-      <c r="B120" s="16">
-        <f>'SDA'!J61</f>
-        <v/>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="6" t="inlineStr">
-        <is>
-          <t>Step 2 — Infiltration</t>
-        </is>
-      </c>
-      <c r="B121" s="7" t="n"/>
-      <c r="C121" s="7" t="n"/>
-      <c r="D121" s="7" t="n"/>
-      <c r="E121" s="7" t="n"/>
-      <c r="F121" s="7" t="n"/>
-      <c r="G121" s="8" t="n"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="10" t="inlineStr">
-        <is>
-          <t>Hydrologic Soil Group</t>
-        </is>
-      </c>
-      <c r="B122" s="4" t="n"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="10" t="inlineStr">
-        <is>
-          <t>Water Table OK?</t>
-        </is>
-      </c>
-      <c r="B123" s="4" t="n"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="10" t="inlineStr">
-        <is>
-          <t>Bedrock OK?</t>
-        </is>
-      </c>
-      <c r="B124" s="4" t="n"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="10" t="inlineStr">
-        <is>
-          <t>Infiltration Rate (in/hr)</t>
-        </is>
-      </c>
-      <c r="B125" s="4" t="n"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="6" t="inlineStr">
-        <is>
-          <t>Step 3 — Constraints</t>
-        </is>
-      </c>
-      <c r="B126" s="7" t="n"/>
-      <c r="C126" s="7" t="n"/>
-      <c r="D126" s="7" t="n"/>
-      <c r="E126" s="7" t="n"/>
-      <c r="F126" s="7" t="n"/>
-      <c r="G126" s="8" t="n"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="10" t="inlineStr">
-        <is>
-          <t>Hotspot Concern?</t>
-        </is>
-      </c>
-      <c r="B127" s="4" t="n"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="6" t="inlineStr">
-        <is>
-          <t>Step 4 — Tree Credits (DDOT)</t>
-        </is>
-      </c>
-      <c r="B128" s="7" t="n"/>
-      <c r="C128" s="7" t="n"/>
-      <c r="D128" s="7" t="n"/>
-      <c r="E128" s="7" t="n"/>
-      <c r="F128" s="7" t="n"/>
-      <c r="G128" s="8" t="n"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="10" t="inlineStr">
-        <is>
-          <t>Small Trees (preserved+planted)</t>
-        </is>
-      </c>
-      <c r="B129" s="16">
-        <f>(5)*(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,'SDA'!A61)+SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,'SDA'!A61))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="10" t="inlineStr">
-        <is>
-          <t>Large Trees (preserved+planted)</t>
-        </is>
-      </c>
-      <c r="B130" s="16">
-        <f>(20)*(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,'SDA'!A61)+SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,'SDA'!A61))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="10" t="inlineStr">
-        <is>
-          <t>Special Trees preserved</t>
-        </is>
-      </c>
-      <c r="B131" s="16">
-        <f>(30)*SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,'SDA'!A61)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="10" t="inlineStr">
-        <is>
-          <t>Heritage Trees preserved</t>
-        </is>
-      </c>
-      <c r="B132" s="16">
-        <f>(40)*SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,'SDA'!A61)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="6" t="inlineStr">
-        <is>
-          <t>Step 4 — BMP Placement</t>
-        </is>
-      </c>
-      <c r="B133" s="7" t="n"/>
-      <c r="C133" s="7" t="n"/>
-      <c r="D133" s="7" t="n"/>
-      <c r="E133" s="7" t="n"/>
-      <c r="F133" s="7" t="n"/>
-      <c r="G133" s="8" t="n"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="17" t="inlineStr">
-        <is>
-          <t>BMP Name</t>
-        </is>
-      </c>
-      <c r="B134" s="17" t="inlineStr">
-        <is>
-          <t>BMP Type</t>
-        </is>
-      </c>
-      <c r="C134" s="17" t="inlineStr">
-        <is>
-          <t>CDA_ID</t>
-        </is>
-      </c>
-      <c r="D134" s="17" t="inlineStr">
-        <is>
-          <t>CDA Within LOD (SF)</t>
-        </is>
-      </c>
-      <c r="E134" s="17" t="inlineStr">
-        <is>
-          <t>CDA Outside LOD (SF)</t>
-        </is>
-      </c>
-      <c r="F134" s="17" t="inlineStr">
-        <is>
-          <t>BMP Rv (CF)</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="16">
-        <f>IFERROR(INDEX('BMP'!$A$4:$A$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A61,ROW('BMP'!$B$4:$B$53)-3),1)),"")</f>
-        <v/>
-      </c>
-      <c r="B135" s="16">
-        <f>IFERROR(INDEX('BMP'!$D$4:$D$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A61,ROW('BMP'!$B$4:$B$53)-3),1)),"")</f>
-        <v/>
-      </c>
-      <c r="C135" s="16">
-        <f>IFERROR(INDEX('BMP'!$C$4:$C$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A61,ROW('BMP'!$B$4:$B$53)-3),1)),"")</f>
-        <v/>
-      </c>
-      <c r="F135" s="16">
-        <f>IFERROR(INDEX('BMP'!$AM$4:$AM$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A61,ROW('BMP'!$B$4:$B$53)-3),1)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="16">
-        <f>IFERROR(INDEX('BMP'!$A$4:$A$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A61,ROW('BMP'!$B$4:$B$53)-3),2)),"")</f>
-        <v/>
-      </c>
-      <c r="B136" s="16">
-        <f>IFERROR(INDEX('BMP'!$D$4:$D$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A61,ROW('BMP'!$B$4:$B$53)-3),2)),"")</f>
-        <v/>
-      </c>
-      <c r="C136" s="16">
-        <f>IFERROR(INDEX('BMP'!$C$4:$C$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A61,ROW('BMP'!$B$4:$B$53)-3),2)),"")</f>
-        <v/>
-      </c>
-      <c r="F136" s="16">
-        <f>IFERROR(INDEX('BMP'!$AM$4:$AM$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A61,ROW('BMP'!$B$4:$B$53)-3),2)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="16">
-        <f>IFERROR(INDEX('BMP'!$A$4:$A$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A61,ROW('BMP'!$B$4:$B$53)-3),3)),"")</f>
-        <v/>
-      </c>
-      <c r="B137" s="16">
-        <f>IFERROR(INDEX('BMP'!$D$4:$D$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A61,ROW('BMP'!$B$4:$B$53)-3),3)),"")</f>
-        <v/>
-      </c>
-      <c r="C137" s="16">
-        <f>IFERROR(INDEX('BMP'!$C$4:$C$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A61,ROW('BMP'!$B$4:$B$53)-3),3)),"")</f>
-        <v/>
-      </c>
-      <c r="F137" s="16">
-        <f>IFERROR(INDEX('BMP'!$AM$4:$AM$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A61,ROW('BMP'!$B$4:$B$53)-3),3)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="16">
-        <f>IFERROR(INDEX('BMP'!$A$4:$A$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A61,ROW('BMP'!$B$4:$B$53)-3),4)),"")</f>
-        <v/>
-      </c>
-      <c r="B138" s="16">
-        <f>IFERROR(INDEX('BMP'!$D$4:$D$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A61,ROW('BMP'!$B$4:$B$53)-3),4)),"")</f>
-        <v/>
-      </c>
-      <c r="C138" s="16">
-        <f>IFERROR(INDEX('BMP'!$C$4:$C$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A61,ROW('BMP'!$B$4:$B$53)-3),4)),"")</f>
-        <v/>
-      </c>
-      <c r="F138" s="16">
-        <f>IFERROR(INDEX('BMP'!$AM$4:$AM$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A61,ROW('BMP'!$B$4:$B$53)-3),4)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="16">
-        <f>IFERROR(INDEX('BMP'!$A$4:$A$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A61,ROW('BMP'!$B$4:$B$53)-3),5)),"")</f>
-        <v/>
-      </c>
-      <c r="B139" s="16">
-        <f>IFERROR(INDEX('BMP'!$D$4:$D$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A61,ROW('BMP'!$B$4:$B$53)-3),5)),"")</f>
-        <v/>
-      </c>
-      <c r="C139" s="16">
-        <f>IFERROR(INDEX('BMP'!$C$4:$C$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A61,ROW('BMP'!$B$4:$B$53)-3),5)),"")</f>
-        <v/>
-      </c>
-      <c r="F139" s="16">
-        <f>IFERROR(INDEX('BMP'!$AM$4:$AM$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A61,ROW('BMP'!$B$4:$B$53)-3),5)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="3" t="inlineStr">
-        <is>
-          <t>Cumulative Surplus / Deficit (CF)</t>
-        </is>
-      </c>
-      <c r="B140" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AM$4:$AM$53,'BMP'!$B$4:$B$53,'SDA'!A61)-'SDA'!J61,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="1" t="inlineStr">
-        <is>
-          <t>SDA-5</t>
-        </is>
-      </c>
-      <c r="B142" s="5" t="n"/>
-      <c r="C142" s="5" t="n"/>
-      <c r="D142" s="5" t="n"/>
-      <c r="E142" s="5" t="n"/>
-      <c r="F142" s="5" t="n"/>
-      <c r="G142" s="2" t="n"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="6" t="inlineStr">
-        <is>
-          <t>Step 1 — Drainage Area &amp; Regulated Volumes</t>
-        </is>
-      </c>
-      <c r="B143" s="7" t="n"/>
-      <c r="C143" s="7" t="n"/>
-      <c r="D143" s="7" t="n"/>
-      <c r="E143" s="7" t="n"/>
-      <c r="F143" s="7" t="n"/>
-      <c r="G143" s="8" t="n"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="10" t="inlineStr">
-        <is>
-          <t>Drainage Area ID</t>
-        </is>
-      </c>
-      <c r="B144" s="16">
-        <f>'SDA'!A62</f>
-        <v/>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="10" t="inlineStr">
-        <is>
-          <t>Impervious within LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B145" s="16">
-        <f>SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,'SDA'!A62,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,'SDA'!A62,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="10" t="inlineStr">
-        <is>
-          <t>Compacted within LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B146" s="16">
-        <f>SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,'SDA'!A62,'SDA'!$C$4:$C$53,"Compacted (Open Space)")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="10" t="inlineStr">
-        <is>
-          <t>Natural within LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B147" s="16">
-        <f>SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,'SDA'!A62,'SDA'!$C$4:$C$53,"Natural (Woods)")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="3" t="inlineStr">
-        <is>
-          <t>Total within LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B148" s="16">
-        <f>SUM(B145:B147)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="10" t="inlineStr">
-        <is>
-          <t>Impervious outside LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B149" s="16">
-        <f>SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,'SDA'!A62,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,'SDA'!A62,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="10" t="inlineStr">
-        <is>
-          <t>Compacted outside LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B150" s="16">
-        <f>SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,'SDA'!A62,'SDA'!$C$4:$C$53,"Compacted (Open Space)")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="10" t="inlineStr">
-        <is>
-          <t>Natural outside LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B151" s="16">
-        <f>SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,'SDA'!A62,'SDA'!$C$4:$C$53,"Natural (Woods)")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="3" t="inlineStr">
-        <is>
-          <t>Total outside LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B152" s="16">
-        <f>SUM(B149:B151)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="3" t="inlineStr">
-        <is>
-          <t>SWRv Within LOD (CF)</t>
-        </is>
-      </c>
-      <c r="B153" s="16">
-        <f>'SDA'!J62</f>
-        <v/>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="6" t="inlineStr">
-        <is>
-          <t>Step 2 — Infiltration</t>
-        </is>
-      </c>
-      <c r="B154" s="7" t="n"/>
-      <c r="C154" s="7" t="n"/>
-      <c r="D154" s="7" t="n"/>
-      <c r="E154" s="7" t="n"/>
-      <c r="F154" s="7" t="n"/>
-      <c r="G154" s="8" t="n"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="10" t="inlineStr">
-        <is>
-          <t>Hydrologic Soil Group</t>
-        </is>
-      </c>
-      <c r="B155" s="4" t="n"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="10" t="inlineStr">
-        <is>
-          <t>Water Table OK?</t>
-        </is>
-      </c>
-      <c r="B156" s="4" t="n"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="10" t="inlineStr">
-        <is>
-          <t>Bedrock OK?</t>
-        </is>
-      </c>
-      <c r="B157" s="4" t="n"/>
-    </row>
-    <row r="158">
-      <c r="A158" s="10" t="inlineStr">
-        <is>
-          <t>Infiltration Rate (in/hr)</t>
-        </is>
-      </c>
-      <c r="B158" s="4" t="n"/>
-    </row>
-    <row r="159">
-      <c r="A159" s="6" t="inlineStr">
-        <is>
-          <t>Step 3 — Constraints</t>
-        </is>
-      </c>
-      <c r="B159" s="7" t="n"/>
-      <c r="C159" s="7" t="n"/>
-      <c r="D159" s="7" t="n"/>
-      <c r="E159" s="7" t="n"/>
-      <c r="F159" s="7" t="n"/>
-      <c r="G159" s="8" t="n"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="10" t="inlineStr">
-        <is>
-          <t>Hotspot Concern?</t>
-        </is>
-      </c>
-      <c r="B160" s="4" t="n"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="6" t="inlineStr">
-        <is>
-          <t>Step 4 — Tree Credits (DDOT)</t>
-        </is>
-      </c>
-      <c r="B161" s="7" t="n"/>
-      <c r="C161" s="7" t="n"/>
-      <c r="D161" s="7" t="n"/>
-      <c r="E161" s="7" t="n"/>
-      <c r="F161" s="7" t="n"/>
-      <c r="G161" s="8" t="n"/>
-    </row>
-    <row r="162">
-      <c r="A162" s="10" t="inlineStr">
-        <is>
-          <t>Small Trees (preserved+planted)</t>
-        </is>
-      </c>
-      <c r="B162" s="16">
-        <f>(5)*(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,'SDA'!A62)+SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,'SDA'!A62))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="10" t="inlineStr">
-        <is>
-          <t>Large Trees (preserved+planted)</t>
-        </is>
-      </c>
-      <c r="B163" s="16">
-        <f>(20)*(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,'SDA'!A62)+SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,'SDA'!A62))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="10" t="inlineStr">
-        <is>
-          <t>Special Trees preserved</t>
-        </is>
-      </c>
-      <c r="B164" s="16">
-        <f>(30)*SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,'SDA'!A62)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="10" t="inlineStr">
-        <is>
-          <t>Heritage Trees preserved</t>
-        </is>
-      </c>
-      <c r="B165" s="16">
-        <f>(40)*SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,'SDA'!A62)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="6" t="inlineStr">
-        <is>
-          <t>Step 4 — BMP Placement</t>
-        </is>
-      </c>
-      <c r="B166" s="7" t="n"/>
-      <c r="C166" s="7" t="n"/>
-      <c r="D166" s="7" t="n"/>
-      <c r="E166" s="7" t="n"/>
-      <c r="F166" s="7" t="n"/>
-      <c r="G166" s="8" t="n"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="17" t="inlineStr">
-        <is>
-          <t>BMP Name</t>
-        </is>
-      </c>
-      <c r="B167" s="17" t="inlineStr">
-        <is>
-          <t>BMP Type</t>
-        </is>
-      </c>
-      <c r="C167" s="17" t="inlineStr">
-        <is>
-          <t>CDA_ID</t>
-        </is>
-      </c>
-      <c r="D167" s="17" t="inlineStr">
-        <is>
-          <t>CDA Within LOD (SF)</t>
-        </is>
-      </c>
-      <c r="E167" s="17" t="inlineStr">
-        <is>
-          <t>CDA Outside LOD (SF)</t>
-        </is>
-      </c>
-      <c r="F167" s="17" t="inlineStr">
-        <is>
-          <t>BMP Rv (CF)</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="16">
-        <f>IFERROR(INDEX('BMP'!$A$4:$A$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A62,ROW('BMP'!$B$4:$B$53)-3),1)),"")</f>
-        <v/>
-      </c>
-      <c r="B168" s="16">
-        <f>IFERROR(INDEX('BMP'!$D$4:$D$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A62,ROW('BMP'!$B$4:$B$53)-3),1)),"")</f>
-        <v/>
-      </c>
-      <c r="C168" s="16">
-        <f>IFERROR(INDEX('BMP'!$C$4:$C$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A62,ROW('BMP'!$B$4:$B$53)-3),1)),"")</f>
-        <v/>
-      </c>
-      <c r="F168" s="16">
-        <f>IFERROR(INDEX('BMP'!$AM$4:$AM$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A62,ROW('BMP'!$B$4:$B$53)-3),1)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="16">
-        <f>IFERROR(INDEX('BMP'!$A$4:$A$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A62,ROW('BMP'!$B$4:$B$53)-3),2)),"")</f>
-        <v/>
-      </c>
-      <c r="B169" s="16">
-        <f>IFERROR(INDEX('BMP'!$D$4:$D$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A62,ROW('BMP'!$B$4:$B$53)-3),2)),"")</f>
-        <v/>
-      </c>
-      <c r="C169" s="16">
-        <f>IFERROR(INDEX('BMP'!$C$4:$C$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A62,ROW('BMP'!$B$4:$B$53)-3),2)),"")</f>
-        <v/>
-      </c>
-      <c r="F169" s="16">
-        <f>IFERROR(INDEX('BMP'!$AM$4:$AM$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A62,ROW('BMP'!$B$4:$B$53)-3),2)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="16">
-        <f>IFERROR(INDEX('BMP'!$A$4:$A$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A62,ROW('BMP'!$B$4:$B$53)-3),3)),"")</f>
-        <v/>
-      </c>
-      <c r="B170" s="16">
-        <f>IFERROR(INDEX('BMP'!$D$4:$D$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A62,ROW('BMP'!$B$4:$B$53)-3),3)),"")</f>
-        <v/>
-      </c>
-      <c r="C170" s="16">
-        <f>IFERROR(INDEX('BMP'!$C$4:$C$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A62,ROW('BMP'!$B$4:$B$53)-3),3)),"")</f>
-        <v/>
-      </c>
-      <c r="F170" s="16">
-        <f>IFERROR(INDEX('BMP'!$AM$4:$AM$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A62,ROW('BMP'!$B$4:$B$53)-3),3)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="16">
-        <f>IFERROR(INDEX('BMP'!$A$4:$A$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A62,ROW('BMP'!$B$4:$B$53)-3),4)),"")</f>
-        <v/>
-      </c>
-      <c r="B171" s="16">
-        <f>IFERROR(INDEX('BMP'!$D$4:$D$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A62,ROW('BMP'!$B$4:$B$53)-3),4)),"")</f>
-        <v/>
-      </c>
-      <c r="C171" s="16">
-        <f>IFERROR(INDEX('BMP'!$C$4:$C$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A62,ROW('BMP'!$B$4:$B$53)-3),4)),"")</f>
-        <v/>
-      </c>
-      <c r="F171" s="16">
-        <f>IFERROR(INDEX('BMP'!$AM$4:$AM$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A62,ROW('BMP'!$B$4:$B$53)-3),4)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="16">
-        <f>IFERROR(INDEX('BMP'!$A$4:$A$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A62,ROW('BMP'!$B$4:$B$53)-3),5)),"")</f>
-        <v/>
-      </c>
-      <c r="B172" s="16">
-        <f>IFERROR(INDEX('BMP'!$D$4:$D$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A62,ROW('BMP'!$B$4:$B$53)-3),5)),"")</f>
-        <v/>
-      </c>
-      <c r="C172" s="16">
-        <f>IFERROR(INDEX('BMP'!$C$4:$C$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A62,ROW('BMP'!$B$4:$B$53)-3),5)),"")</f>
-        <v/>
-      </c>
-      <c r="F172" s="16">
-        <f>IFERROR(INDEX('BMP'!$AM$4:$AM$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A62,ROW('BMP'!$B$4:$B$53)-3),5)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="3" t="inlineStr">
-        <is>
-          <t>Cumulative Surplus / Deficit (CF)</t>
-        </is>
-      </c>
-      <c r="B173" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AM$4:$AM$53,'BMP'!$B$4:$B$53,'SDA'!A62)-'SDA'!J62,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="1" t="inlineStr">
-        <is>
-          <t>SDA-6</t>
-        </is>
-      </c>
-      <c r="B175" s="5" t="n"/>
-      <c r="C175" s="5" t="n"/>
-      <c r="D175" s="5" t="n"/>
-      <c r="E175" s="5" t="n"/>
-      <c r="F175" s="5" t="n"/>
-      <c r="G175" s="2" t="n"/>
-    </row>
-    <row r="176">
-      <c r="A176" s="6" t="inlineStr">
-        <is>
-          <t>Step 1 — Drainage Area &amp; Regulated Volumes</t>
-        </is>
-      </c>
-      <c r="B176" s="7" t="n"/>
-      <c r="C176" s="7" t="n"/>
-      <c r="D176" s="7" t="n"/>
-      <c r="E176" s="7" t="n"/>
-      <c r="F176" s="7" t="n"/>
-      <c r="G176" s="8" t="n"/>
-    </row>
-    <row r="177">
-      <c r="A177" s="10" t="inlineStr">
-        <is>
-          <t>Drainage Area ID</t>
-        </is>
-      </c>
-      <c r="B177" s="16">
-        <f>'SDA'!A63</f>
-        <v/>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="10" t="inlineStr">
-        <is>
-          <t>Impervious within LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B178" s="16">
-        <f>SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,'SDA'!A63,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,'SDA'!A63,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="10" t="inlineStr">
-        <is>
-          <t>Compacted within LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B179" s="16">
-        <f>SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,'SDA'!A63,'SDA'!$C$4:$C$53,"Compacted (Open Space)")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="10" t="inlineStr">
-        <is>
-          <t>Natural within LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B180" s="16">
-        <f>SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,'SDA'!A63,'SDA'!$C$4:$C$53,"Natural (Woods)")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="3" t="inlineStr">
-        <is>
-          <t>Total within LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B181" s="16">
-        <f>SUM(B178:B180)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="10" t="inlineStr">
-        <is>
-          <t>Impervious outside LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B182" s="16">
-        <f>SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,'SDA'!A63,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,'SDA'!A63,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="10" t="inlineStr">
-        <is>
-          <t>Compacted outside LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B183" s="16">
-        <f>SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,'SDA'!A63,'SDA'!$C$4:$C$53,"Compacted (Open Space)")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="10" t="inlineStr">
-        <is>
-          <t>Natural outside LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B184" s="16">
-        <f>SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,'SDA'!A63,'SDA'!$C$4:$C$53,"Natural (Woods)")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="3" t="inlineStr">
-        <is>
-          <t>Total outside LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B185" s="16">
-        <f>SUM(B182:B184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="3" t="inlineStr">
-        <is>
-          <t>SWRv Within LOD (CF)</t>
-        </is>
-      </c>
-      <c r="B186" s="16">
-        <f>'SDA'!J63</f>
-        <v/>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="6" t="inlineStr">
-        <is>
-          <t>Step 2 — Infiltration</t>
-        </is>
-      </c>
-      <c r="B187" s="7" t="n"/>
-      <c r="C187" s="7" t="n"/>
-      <c r="D187" s="7" t="n"/>
-      <c r="E187" s="7" t="n"/>
-      <c r="F187" s="7" t="n"/>
-      <c r="G187" s="8" t="n"/>
-    </row>
-    <row r="188">
-      <c r="A188" s="10" t="inlineStr">
-        <is>
-          <t>Hydrologic Soil Group</t>
-        </is>
-      </c>
-      <c r="B188" s="4" t="n"/>
-    </row>
-    <row r="189">
-      <c r="A189" s="10" t="inlineStr">
-        <is>
-          <t>Water Table OK?</t>
-        </is>
-      </c>
-      <c r="B189" s="4" t="n"/>
-    </row>
-    <row r="190">
-      <c r="A190" s="10" t="inlineStr">
-        <is>
-          <t>Bedrock OK?</t>
-        </is>
-      </c>
-      <c r="B190" s="4" t="n"/>
-    </row>
-    <row r="191">
-      <c r="A191" s="10" t="inlineStr">
-        <is>
-          <t>Infiltration Rate (in/hr)</t>
-        </is>
-      </c>
-      <c r="B191" s="4" t="n"/>
-    </row>
-    <row r="192">
-      <c r="A192" s="6" t="inlineStr">
-        <is>
-          <t>Step 3 — Constraints</t>
-        </is>
-      </c>
-      <c r="B192" s="7" t="n"/>
-      <c r="C192" s="7" t="n"/>
-      <c r="D192" s="7" t="n"/>
-      <c r="E192" s="7" t="n"/>
-      <c r="F192" s="7" t="n"/>
-      <c r="G192" s="8" t="n"/>
-    </row>
-    <row r="193">
-      <c r="A193" s="10" t="inlineStr">
-        <is>
-          <t>Hotspot Concern?</t>
-        </is>
-      </c>
-      <c r="B193" s="4" t="n"/>
-    </row>
-    <row r="194">
-      <c r="A194" s="6" t="inlineStr">
-        <is>
-          <t>Step 4 — Tree Credits (DDOT)</t>
-        </is>
-      </c>
-      <c r="B194" s="7" t="n"/>
-      <c r="C194" s="7" t="n"/>
-      <c r="D194" s="7" t="n"/>
-      <c r="E194" s="7" t="n"/>
-      <c r="F194" s="7" t="n"/>
-      <c r="G194" s="8" t="n"/>
-    </row>
-    <row r="195">
-      <c r="A195" s="10" t="inlineStr">
-        <is>
-          <t>Small Trees (preserved+planted)</t>
-        </is>
-      </c>
-      <c r="B195" s="16">
-        <f>(5)*(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,'SDA'!A63)+SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,'SDA'!A63))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="10" t="inlineStr">
-        <is>
-          <t>Large Trees (preserved+planted)</t>
-        </is>
-      </c>
-      <c r="B196" s="16">
-        <f>(20)*(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,'SDA'!A63)+SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,'SDA'!A63))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="10" t="inlineStr">
-        <is>
-          <t>Special Trees preserved</t>
-        </is>
-      </c>
-      <c r="B197" s="16">
-        <f>(30)*SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,'SDA'!A63)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="10" t="inlineStr">
-        <is>
-          <t>Heritage Trees preserved</t>
-        </is>
-      </c>
-      <c r="B198" s="16">
-        <f>(40)*SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,'SDA'!A63)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="6" t="inlineStr">
-        <is>
-          <t>Step 4 — BMP Placement</t>
-        </is>
-      </c>
-      <c r="B199" s="7" t="n"/>
-      <c r="C199" s="7" t="n"/>
-      <c r="D199" s="7" t="n"/>
-      <c r="E199" s="7" t="n"/>
-      <c r="F199" s="7" t="n"/>
-      <c r="G199" s="8" t="n"/>
-    </row>
-    <row r="200">
-      <c r="A200" s="17" t="inlineStr">
-        <is>
-          <t>BMP Name</t>
-        </is>
-      </c>
-      <c r="B200" s="17" t="inlineStr">
-        <is>
-          <t>BMP Type</t>
-        </is>
-      </c>
-      <c r="C200" s="17" t="inlineStr">
-        <is>
-          <t>CDA_ID</t>
-        </is>
-      </c>
-      <c r="D200" s="17" t="inlineStr">
-        <is>
-          <t>CDA Within LOD (SF)</t>
-        </is>
-      </c>
-      <c r="E200" s="17" t="inlineStr">
-        <is>
-          <t>CDA Outside LOD (SF)</t>
-        </is>
-      </c>
-      <c r="F200" s="17" t="inlineStr">
-        <is>
-          <t>BMP Rv (CF)</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="16">
-        <f>IFERROR(INDEX('BMP'!$A$4:$A$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A63,ROW('BMP'!$B$4:$B$53)-3),1)),"")</f>
-        <v/>
-      </c>
-      <c r="B201" s="16">
-        <f>IFERROR(INDEX('BMP'!$D$4:$D$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A63,ROW('BMP'!$B$4:$B$53)-3),1)),"")</f>
-        <v/>
-      </c>
-      <c r="C201" s="16">
-        <f>IFERROR(INDEX('BMP'!$C$4:$C$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A63,ROW('BMP'!$B$4:$B$53)-3),1)),"")</f>
-        <v/>
-      </c>
-      <c r="F201" s="16">
-        <f>IFERROR(INDEX('BMP'!$AM$4:$AM$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A63,ROW('BMP'!$B$4:$B$53)-3),1)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="16">
-        <f>IFERROR(INDEX('BMP'!$A$4:$A$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A63,ROW('BMP'!$B$4:$B$53)-3),2)),"")</f>
-        <v/>
-      </c>
-      <c r="B202" s="16">
-        <f>IFERROR(INDEX('BMP'!$D$4:$D$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A63,ROW('BMP'!$B$4:$B$53)-3),2)),"")</f>
-        <v/>
-      </c>
-      <c r="C202" s="16">
-        <f>IFERROR(INDEX('BMP'!$C$4:$C$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A63,ROW('BMP'!$B$4:$B$53)-3),2)),"")</f>
-        <v/>
-      </c>
-      <c r="F202" s="16">
-        <f>IFERROR(INDEX('BMP'!$AM$4:$AM$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A63,ROW('BMP'!$B$4:$B$53)-3),2)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="16">
-        <f>IFERROR(INDEX('BMP'!$A$4:$A$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A63,ROW('BMP'!$B$4:$B$53)-3),3)),"")</f>
-        <v/>
-      </c>
-      <c r="B203" s="16">
-        <f>IFERROR(INDEX('BMP'!$D$4:$D$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A63,ROW('BMP'!$B$4:$B$53)-3),3)),"")</f>
-        <v/>
-      </c>
-      <c r="C203" s="16">
-        <f>IFERROR(INDEX('BMP'!$C$4:$C$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A63,ROW('BMP'!$B$4:$B$53)-3),3)),"")</f>
-        <v/>
-      </c>
-      <c r="F203" s="16">
-        <f>IFERROR(INDEX('BMP'!$AM$4:$AM$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A63,ROW('BMP'!$B$4:$B$53)-3),3)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="16">
-        <f>IFERROR(INDEX('BMP'!$A$4:$A$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A63,ROW('BMP'!$B$4:$B$53)-3),4)),"")</f>
-        <v/>
-      </c>
-      <c r="B204" s="16">
-        <f>IFERROR(INDEX('BMP'!$D$4:$D$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A63,ROW('BMP'!$B$4:$B$53)-3),4)),"")</f>
-        <v/>
-      </c>
-      <c r="C204" s="16">
-        <f>IFERROR(INDEX('BMP'!$C$4:$C$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A63,ROW('BMP'!$B$4:$B$53)-3),4)),"")</f>
-        <v/>
-      </c>
-      <c r="F204" s="16">
-        <f>IFERROR(INDEX('BMP'!$AM$4:$AM$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A63,ROW('BMP'!$B$4:$B$53)-3),4)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="16">
-        <f>IFERROR(INDEX('BMP'!$A$4:$A$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A63,ROW('BMP'!$B$4:$B$53)-3),5)),"")</f>
-        <v/>
-      </c>
-      <c r="B205" s="16">
-        <f>IFERROR(INDEX('BMP'!$D$4:$D$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A63,ROW('BMP'!$B$4:$B$53)-3),5)),"")</f>
-        <v/>
-      </c>
-      <c r="C205" s="16">
-        <f>IFERROR(INDEX('BMP'!$C$4:$C$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A63,ROW('BMP'!$B$4:$B$53)-3),5)),"")</f>
-        <v/>
-      </c>
-      <c r="F205" s="16">
-        <f>IFERROR(INDEX('BMP'!$AM$4:$AM$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A63,ROW('BMP'!$B$4:$B$53)-3),5)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" s="3" t="inlineStr">
-        <is>
-          <t>Cumulative Surplus / Deficit (CF)</t>
-        </is>
-      </c>
-      <c r="B206" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AM$4:$AM$53,'BMP'!$B$4:$B$53,'SDA'!A63)-'SDA'!J63,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="1" t="inlineStr">
-        <is>
-          <t>SDA-7</t>
-        </is>
-      </c>
-      <c r="B208" s="5" t="n"/>
-      <c r="C208" s="5" t="n"/>
-      <c r="D208" s="5" t="n"/>
-      <c r="E208" s="5" t="n"/>
-      <c r="F208" s="5" t="n"/>
-      <c r="G208" s="2" t="n"/>
-    </row>
-    <row r="209">
-      <c r="A209" s="6" t="inlineStr">
-        <is>
-          <t>Step 1 — Drainage Area &amp; Regulated Volumes</t>
-        </is>
-      </c>
-      <c r="B209" s="7" t="n"/>
-      <c r="C209" s="7" t="n"/>
-      <c r="D209" s="7" t="n"/>
-      <c r="E209" s="7" t="n"/>
-      <c r="F209" s="7" t="n"/>
-      <c r="G209" s="8" t="n"/>
-    </row>
-    <row r="210">
-      <c r="A210" s="10" t="inlineStr">
-        <is>
-          <t>Drainage Area ID</t>
-        </is>
-      </c>
-      <c r="B210" s="16">
-        <f>'SDA'!A64</f>
-        <v/>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="10" t="inlineStr">
-        <is>
-          <t>Impervious within LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B211" s="16">
-        <f>SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,'SDA'!A64,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,'SDA'!A64,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="10" t="inlineStr">
-        <is>
-          <t>Compacted within LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B212" s="16">
-        <f>SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,'SDA'!A64,'SDA'!$C$4:$C$53,"Compacted (Open Space)")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" s="10" t="inlineStr">
-        <is>
-          <t>Natural within LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B213" s="16">
-        <f>SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,'SDA'!A64,'SDA'!$C$4:$C$53,"Natural (Woods)")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" s="3" t="inlineStr">
-        <is>
-          <t>Total within LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B214" s="16">
-        <f>SUM(B211:B213)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" s="10" t="inlineStr">
-        <is>
-          <t>Impervious outside LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B215" s="16">
-        <f>SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,'SDA'!A64,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,'SDA'!A64,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" s="10" t="inlineStr">
-        <is>
-          <t>Compacted outside LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B216" s="16">
-        <f>SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,'SDA'!A64,'SDA'!$C$4:$C$53,"Compacted (Open Space)")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" s="10" t="inlineStr">
-        <is>
-          <t>Natural outside LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B217" s="16">
-        <f>SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,'SDA'!A64,'SDA'!$C$4:$C$53,"Natural (Woods)")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="3" t="inlineStr">
-        <is>
-          <t>Total outside LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B218" s="16">
-        <f>SUM(B215:B217)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="3" t="inlineStr">
-        <is>
-          <t>SWRv Within LOD (CF)</t>
-        </is>
-      </c>
-      <c r="B219" s="16">
-        <f>'SDA'!J64</f>
-        <v/>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="6" t="inlineStr">
-        <is>
-          <t>Step 2 — Infiltration</t>
-        </is>
-      </c>
-      <c r="B220" s="7" t="n"/>
-      <c r="C220" s="7" t="n"/>
-      <c r="D220" s="7" t="n"/>
-      <c r="E220" s="7" t="n"/>
-      <c r="F220" s="7" t="n"/>
-      <c r="G220" s="8" t="n"/>
-    </row>
-    <row r="221">
-      <c r="A221" s="10" t="inlineStr">
-        <is>
-          <t>Hydrologic Soil Group</t>
-        </is>
-      </c>
-      <c r="B221" s="4" t="n"/>
-    </row>
-    <row r="222">
-      <c r="A222" s="10" t="inlineStr">
-        <is>
-          <t>Water Table OK?</t>
-        </is>
-      </c>
-      <c r="B222" s="4" t="n"/>
-    </row>
-    <row r="223">
-      <c r="A223" s="10" t="inlineStr">
-        <is>
-          <t>Bedrock OK?</t>
-        </is>
-      </c>
-      <c r="B223" s="4" t="n"/>
-    </row>
-    <row r="224">
-      <c r="A224" s="10" t="inlineStr">
-        <is>
-          <t>Infiltration Rate (in/hr)</t>
-        </is>
-      </c>
-      <c r="B224" s="4" t="n"/>
-    </row>
-    <row r="225">
-      <c r="A225" s="6" t="inlineStr">
-        <is>
-          <t>Step 3 — Constraints</t>
-        </is>
-      </c>
-      <c r="B225" s="7" t="n"/>
-      <c r="C225" s="7" t="n"/>
-      <c r="D225" s="7" t="n"/>
-      <c r="E225" s="7" t="n"/>
-      <c r="F225" s="7" t="n"/>
-      <c r="G225" s="8" t="n"/>
-    </row>
-    <row r="226">
-      <c r="A226" s="10" t="inlineStr">
-        <is>
-          <t>Hotspot Concern?</t>
-        </is>
-      </c>
-      <c r="B226" s="4" t="n"/>
-    </row>
-    <row r="227">
-      <c r="A227" s="6" t="inlineStr">
-        <is>
-          <t>Step 4 — Tree Credits (DDOT)</t>
-        </is>
-      </c>
-      <c r="B227" s="7" t="n"/>
-      <c r="C227" s="7" t="n"/>
-      <c r="D227" s="7" t="n"/>
-      <c r="E227" s="7" t="n"/>
-      <c r="F227" s="7" t="n"/>
-      <c r="G227" s="8" t="n"/>
-    </row>
-    <row r="228">
-      <c r="A228" s="10" t="inlineStr">
-        <is>
-          <t>Small Trees (preserved+planted)</t>
-        </is>
-      </c>
-      <c r="B228" s="16">
-        <f>(5)*(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,'SDA'!A64)+SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,'SDA'!A64))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="10" t="inlineStr">
-        <is>
-          <t>Large Trees (preserved+planted)</t>
-        </is>
-      </c>
-      <c r="B229" s="16">
-        <f>(20)*(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,'SDA'!A64)+SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,'SDA'!A64))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="10" t="inlineStr">
-        <is>
-          <t>Special Trees preserved</t>
-        </is>
-      </c>
-      <c r="B230" s="16">
-        <f>(30)*SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,'SDA'!A64)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="10" t="inlineStr">
-        <is>
-          <t>Heritage Trees preserved</t>
-        </is>
-      </c>
-      <c r="B231" s="16">
-        <f>(40)*SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,'SDA'!A64)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="6" t="inlineStr">
-        <is>
-          <t>Step 4 — BMP Placement</t>
-        </is>
-      </c>
-      <c r="B232" s="7" t="n"/>
-      <c r="C232" s="7" t="n"/>
-      <c r="D232" s="7" t="n"/>
-      <c r="E232" s="7" t="n"/>
-      <c r="F232" s="7" t="n"/>
-      <c r="G232" s="8" t="n"/>
-    </row>
-    <row r="233">
-      <c r="A233" s="17" t="inlineStr">
-        <is>
-          <t>BMP Name</t>
-        </is>
-      </c>
-      <c r="B233" s="17" t="inlineStr">
-        <is>
-          <t>BMP Type</t>
-        </is>
-      </c>
-      <c r="C233" s="17" t="inlineStr">
-        <is>
-          <t>CDA_ID</t>
-        </is>
-      </c>
-      <c r="D233" s="17" t="inlineStr">
-        <is>
-          <t>CDA Within LOD (SF)</t>
-        </is>
-      </c>
-      <c r="E233" s="17" t="inlineStr">
-        <is>
-          <t>CDA Outside LOD (SF)</t>
-        </is>
-      </c>
-      <c r="F233" s="17" t="inlineStr">
-        <is>
-          <t>BMP Rv (CF)</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="16">
-        <f>IFERROR(INDEX('BMP'!$A$4:$A$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A64,ROW('BMP'!$B$4:$B$53)-3),1)),"")</f>
-        <v/>
-      </c>
-      <c r="B234" s="16">
-        <f>IFERROR(INDEX('BMP'!$D$4:$D$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A64,ROW('BMP'!$B$4:$B$53)-3),1)),"")</f>
-        <v/>
-      </c>
-      <c r="C234" s="16">
-        <f>IFERROR(INDEX('BMP'!$C$4:$C$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A64,ROW('BMP'!$B$4:$B$53)-3),1)),"")</f>
-        <v/>
-      </c>
-      <c r="F234" s="16">
-        <f>IFERROR(INDEX('BMP'!$AM$4:$AM$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A64,ROW('BMP'!$B$4:$B$53)-3),1)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="16">
-        <f>IFERROR(INDEX('BMP'!$A$4:$A$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A64,ROW('BMP'!$B$4:$B$53)-3),2)),"")</f>
-        <v/>
-      </c>
-      <c r="B235" s="16">
-        <f>IFERROR(INDEX('BMP'!$D$4:$D$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A64,ROW('BMP'!$B$4:$B$53)-3),2)),"")</f>
-        <v/>
-      </c>
-      <c r="C235" s="16">
-        <f>IFERROR(INDEX('BMP'!$C$4:$C$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A64,ROW('BMP'!$B$4:$B$53)-3),2)),"")</f>
-        <v/>
-      </c>
-      <c r="F235" s="16">
-        <f>IFERROR(INDEX('BMP'!$AM$4:$AM$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A64,ROW('BMP'!$B$4:$B$53)-3),2)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="16">
-        <f>IFERROR(INDEX('BMP'!$A$4:$A$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A64,ROW('BMP'!$B$4:$B$53)-3),3)),"")</f>
-        <v/>
-      </c>
-      <c r="B236" s="16">
-        <f>IFERROR(INDEX('BMP'!$D$4:$D$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A64,ROW('BMP'!$B$4:$B$53)-3),3)),"")</f>
-        <v/>
-      </c>
-      <c r="C236" s="16">
-        <f>IFERROR(INDEX('BMP'!$C$4:$C$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A64,ROW('BMP'!$B$4:$B$53)-3),3)),"")</f>
-        <v/>
-      </c>
-      <c r="F236" s="16">
-        <f>IFERROR(INDEX('BMP'!$AM$4:$AM$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A64,ROW('BMP'!$B$4:$B$53)-3),3)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="16">
-        <f>IFERROR(INDEX('BMP'!$A$4:$A$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A64,ROW('BMP'!$B$4:$B$53)-3),4)),"")</f>
-        <v/>
-      </c>
-      <c r="B237" s="16">
-        <f>IFERROR(INDEX('BMP'!$D$4:$D$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A64,ROW('BMP'!$B$4:$B$53)-3),4)),"")</f>
-        <v/>
-      </c>
-      <c r="C237" s="16">
-        <f>IFERROR(INDEX('BMP'!$C$4:$C$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A64,ROW('BMP'!$B$4:$B$53)-3),4)),"")</f>
-        <v/>
-      </c>
-      <c r="F237" s="16">
-        <f>IFERROR(INDEX('BMP'!$AM$4:$AM$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A64,ROW('BMP'!$B$4:$B$53)-3),4)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" s="16">
-        <f>IFERROR(INDEX('BMP'!$A$4:$A$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A64,ROW('BMP'!$B$4:$B$53)-3),5)),"")</f>
-        <v/>
-      </c>
-      <c r="B238" s="16">
-        <f>IFERROR(INDEX('BMP'!$D$4:$D$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A64,ROW('BMP'!$B$4:$B$53)-3),5)),"")</f>
-        <v/>
-      </c>
-      <c r="C238" s="16">
-        <f>IFERROR(INDEX('BMP'!$C$4:$C$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A64,ROW('BMP'!$B$4:$B$53)-3),5)),"")</f>
-        <v/>
-      </c>
-      <c r="F238" s="16">
-        <f>IFERROR(INDEX('BMP'!$AM$4:$AM$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A64,ROW('BMP'!$B$4:$B$53)-3),5)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="3" t="inlineStr">
-        <is>
-          <t>Cumulative Surplus / Deficit (CF)</t>
-        </is>
-      </c>
-      <c r="B239" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AM$4:$AM$53,'BMP'!$B$4:$B$53,'SDA'!A64)-'SDA'!J64,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="1" t="inlineStr">
-        <is>
-          <t>SDA-8</t>
-        </is>
-      </c>
-      <c r="B241" s="5" t="n"/>
-      <c r="C241" s="5" t="n"/>
-      <c r="D241" s="5" t="n"/>
-      <c r="E241" s="5" t="n"/>
-      <c r="F241" s="5" t="n"/>
-      <c r="G241" s="2" t="n"/>
-    </row>
-    <row r="242">
-      <c r="A242" s="6" t="inlineStr">
-        <is>
-          <t>Step 1 — Drainage Area &amp; Regulated Volumes</t>
-        </is>
-      </c>
-      <c r="B242" s="7" t="n"/>
-      <c r="C242" s="7" t="n"/>
-      <c r="D242" s="7" t="n"/>
-      <c r="E242" s="7" t="n"/>
-      <c r="F242" s="7" t="n"/>
-      <c r="G242" s="8" t="n"/>
-    </row>
-    <row r="243">
-      <c r="A243" s="10" t="inlineStr">
-        <is>
-          <t>Drainage Area ID</t>
-        </is>
-      </c>
-      <c r="B243" s="16">
-        <f>'SDA'!A65</f>
-        <v/>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" s="10" t="inlineStr">
-        <is>
-          <t>Impervious within LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B244" s="16">
-        <f>SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,'SDA'!A65,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,'SDA'!A65,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="10" t="inlineStr">
-        <is>
-          <t>Compacted within LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B245" s="16">
-        <f>SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,'SDA'!A65,'SDA'!$C$4:$C$53,"Compacted (Open Space)")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" s="10" t="inlineStr">
-        <is>
-          <t>Natural within LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B246" s="16">
-        <f>SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,'SDA'!A65,'SDA'!$C$4:$C$53,"Natural (Woods)")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" s="3" t="inlineStr">
-        <is>
-          <t>Total within LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B247" s="16">
-        <f>SUM(B244:B246)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" s="10" t="inlineStr">
-        <is>
-          <t>Impervious outside LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B248" s="16">
-        <f>SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,'SDA'!A65,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,'SDA'!A65,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" s="10" t="inlineStr">
-        <is>
-          <t>Compacted outside LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B249" s="16">
-        <f>SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,'SDA'!A65,'SDA'!$C$4:$C$53,"Compacted (Open Space)")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" s="10" t="inlineStr">
-        <is>
-          <t>Natural outside LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B250" s="16">
-        <f>SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,'SDA'!A65,'SDA'!$C$4:$C$53,"Natural (Woods)")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" s="3" t="inlineStr">
-        <is>
-          <t>Total outside LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B251" s="16">
-        <f>SUM(B248:B250)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="3" t="inlineStr">
-        <is>
-          <t>SWRv Within LOD (CF)</t>
-        </is>
-      </c>
-      <c r="B252" s="16">
-        <f>'SDA'!J65</f>
-        <v/>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="6" t="inlineStr">
-        <is>
-          <t>Step 2 — Infiltration</t>
-        </is>
-      </c>
-      <c r="B253" s="7" t="n"/>
-      <c r="C253" s="7" t="n"/>
-      <c r="D253" s="7" t="n"/>
-      <c r="E253" s="7" t="n"/>
-      <c r="F253" s="7" t="n"/>
-      <c r="G253" s="8" t="n"/>
-    </row>
-    <row r="254">
-      <c r="A254" s="10" t="inlineStr">
-        <is>
-          <t>Hydrologic Soil Group</t>
-        </is>
-      </c>
-      <c r="B254" s="4" t="n"/>
-    </row>
-    <row r="255">
-      <c r="A255" s="10" t="inlineStr">
-        <is>
-          <t>Water Table OK?</t>
-        </is>
-      </c>
-      <c r="B255" s="4" t="n"/>
-    </row>
-    <row r="256">
-      <c r="A256" s="10" t="inlineStr">
-        <is>
-          <t>Bedrock OK?</t>
-        </is>
-      </c>
-      <c r="B256" s="4" t="n"/>
-    </row>
-    <row r="257">
-      <c r="A257" s="10" t="inlineStr">
-        <is>
-          <t>Infiltration Rate (in/hr)</t>
-        </is>
-      </c>
-      <c r="B257" s="4" t="n"/>
-    </row>
-    <row r="258">
-      <c r="A258" s="6" t="inlineStr">
-        <is>
-          <t>Step 3 — Constraints</t>
-        </is>
-      </c>
-      <c r="B258" s="7" t="n"/>
-      <c r="C258" s="7" t="n"/>
-      <c r="D258" s="7" t="n"/>
-      <c r="E258" s="7" t="n"/>
-      <c r="F258" s="7" t="n"/>
-      <c r="G258" s="8" t="n"/>
-    </row>
-    <row r="259">
-      <c r="A259" s="10" t="inlineStr">
-        <is>
-          <t>Hotspot Concern?</t>
-        </is>
-      </c>
-      <c r="B259" s="4" t="n"/>
-    </row>
-    <row r="260">
-      <c r="A260" s="6" t="inlineStr">
-        <is>
-          <t>Step 4 — Tree Credits (DDOT)</t>
-        </is>
-      </c>
-      <c r="B260" s="7" t="n"/>
-      <c r="C260" s="7" t="n"/>
-      <c r="D260" s="7" t="n"/>
-      <c r="E260" s="7" t="n"/>
-      <c r="F260" s="7" t="n"/>
-      <c r="G260" s="8" t="n"/>
-    </row>
-    <row r="261">
-      <c r="A261" s="10" t="inlineStr">
-        <is>
-          <t>Small Trees (preserved+planted)</t>
-        </is>
-      </c>
-      <c r="B261" s="16">
-        <f>(5)*(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,'SDA'!A65)+SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,'SDA'!A65))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" s="10" t="inlineStr">
-        <is>
-          <t>Large Trees (preserved+planted)</t>
-        </is>
-      </c>
-      <c r="B262" s="16">
-        <f>(20)*(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,'SDA'!A65)+SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,'SDA'!A65))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" s="10" t="inlineStr">
-        <is>
-          <t>Special Trees preserved</t>
-        </is>
-      </c>
-      <c r="B263" s="16">
-        <f>(30)*SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,'SDA'!A65)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" s="10" t="inlineStr">
-        <is>
-          <t>Heritage Trees preserved</t>
-        </is>
-      </c>
-      <c r="B264" s="16">
-        <f>(40)*SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,'SDA'!A65)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" s="6" t="inlineStr">
-        <is>
-          <t>Step 4 — BMP Placement</t>
-        </is>
-      </c>
-      <c r="B265" s="7" t="n"/>
-      <c r="C265" s="7" t="n"/>
-      <c r="D265" s="7" t="n"/>
-      <c r="E265" s="7" t="n"/>
-      <c r="F265" s="7" t="n"/>
-      <c r="G265" s="8" t="n"/>
-    </row>
-    <row r="266">
-      <c r="A266" s="17" t="inlineStr">
-        <is>
-          <t>BMP Name</t>
-        </is>
-      </c>
-      <c r="B266" s="17" t="inlineStr">
-        <is>
-          <t>BMP Type</t>
-        </is>
-      </c>
-      <c r="C266" s="17" t="inlineStr">
-        <is>
-          <t>CDA_ID</t>
-        </is>
-      </c>
-      <c r="D266" s="17" t="inlineStr">
-        <is>
-          <t>CDA Within LOD (SF)</t>
-        </is>
-      </c>
-      <c r="E266" s="17" t="inlineStr">
-        <is>
-          <t>CDA Outside LOD (SF)</t>
-        </is>
-      </c>
-      <c r="F266" s="17" t="inlineStr">
-        <is>
-          <t>BMP Rv (CF)</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" s="16">
-        <f>IFERROR(INDEX('BMP'!$A$4:$A$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A65,ROW('BMP'!$B$4:$B$53)-3),1)),"")</f>
-        <v/>
-      </c>
-      <c r="B267" s="16">
-        <f>IFERROR(INDEX('BMP'!$D$4:$D$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A65,ROW('BMP'!$B$4:$B$53)-3),1)),"")</f>
-        <v/>
-      </c>
-      <c r="C267" s="16">
-        <f>IFERROR(INDEX('BMP'!$C$4:$C$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A65,ROW('BMP'!$B$4:$B$53)-3),1)),"")</f>
-        <v/>
-      </c>
-      <c r="F267" s="16">
-        <f>IFERROR(INDEX('BMP'!$AM$4:$AM$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A65,ROW('BMP'!$B$4:$B$53)-3),1)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" s="16">
-        <f>IFERROR(INDEX('BMP'!$A$4:$A$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A65,ROW('BMP'!$B$4:$B$53)-3),2)),"")</f>
-        <v/>
-      </c>
-      <c r="B268" s="16">
-        <f>IFERROR(INDEX('BMP'!$D$4:$D$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A65,ROW('BMP'!$B$4:$B$53)-3),2)),"")</f>
-        <v/>
-      </c>
-      <c r="C268" s="16">
-        <f>IFERROR(INDEX('BMP'!$C$4:$C$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A65,ROW('BMP'!$B$4:$B$53)-3),2)),"")</f>
-        <v/>
-      </c>
-      <c r="F268" s="16">
-        <f>IFERROR(INDEX('BMP'!$AM$4:$AM$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A65,ROW('BMP'!$B$4:$B$53)-3),2)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" s="16">
-        <f>IFERROR(INDEX('BMP'!$A$4:$A$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A65,ROW('BMP'!$B$4:$B$53)-3),3)),"")</f>
-        <v/>
-      </c>
-      <c r="B269" s="16">
-        <f>IFERROR(INDEX('BMP'!$D$4:$D$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A65,ROW('BMP'!$B$4:$B$53)-3),3)),"")</f>
-        <v/>
-      </c>
-      <c r="C269" s="16">
-        <f>IFERROR(INDEX('BMP'!$C$4:$C$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A65,ROW('BMP'!$B$4:$B$53)-3),3)),"")</f>
-        <v/>
-      </c>
-      <c r="F269" s="16">
-        <f>IFERROR(INDEX('BMP'!$AM$4:$AM$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A65,ROW('BMP'!$B$4:$B$53)-3),3)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" s="16">
-        <f>IFERROR(INDEX('BMP'!$A$4:$A$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A65,ROW('BMP'!$B$4:$B$53)-3),4)),"")</f>
-        <v/>
-      </c>
-      <c r="B270" s="16">
-        <f>IFERROR(INDEX('BMP'!$D$4:$D$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A65,ROW('BMP'!$B$4:$B$53)-3),4)),"")</f>
-        <v/>
-      </c>
-      <c r="C270" s="16">
-        <f>IFERROR(INDEX('BMP'!$C$4:$C$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A65,ROW('BMP'!$B$4:$B$53)-3),4)),"")</f>
-        <v/>
-      </c>
-      <c r="F270" s="16">
-        <f>IFERROR(INDEX('BMP'!$AM$4:$AM$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A65,ROW('BMP'!$B$4:$B$53)-3),4)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" s="16">
-        <f>IFERROR(INDEX('BMP'!$A$4:$A$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A65,ROW('BMP'!$B$4:$B$53)-3),5)),"")</f>
-        <v/>
-      </c>
-      <c r="B271" s="16">
-        <f>IFERROR(INDEX('BMP'!$D$4:$D$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A65,ROW('BMP'!$B$4:$B$53)-3),5)),"")</f>
-        <v/>
-      </c>
-      <c r="C271" s="16">
-        <f>IFERROR(INDEX('BMP'!$C$4:$C$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A65,ROW('BMP'!$B$4:$B$53)-3),5)),"")</f>
-        <v/>
-      </c>
-      <c r="F271" s="16">
-        <f>IFERROR(INDEX('BMP'!$AM$4:$AM$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A65,ROW('BMP'!$B$4:$B$53)-3),5)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" s="3" t="inlineStr">
-        <is>
-          <t>Cumulative Surplus / Deficit (CF)</t>
-        </is>
-      </c>
-      <c r="B272" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AM$4:$AM$53,'BMP'!$B$4:$B$53,'SDA'!A65)-'SDA'!J65,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" s="1" t="inlineStr">
-        <is>
-          <t>SDA-9</t>
-        </is>
-      </c>
-      <c r="B274" s="5" t="n"/>
-      <c r="C274" s="5" t="n"/>
-      <c r="D274" s="5" t="n"/>
-      <c r="E274" s="5" t="n"/>
-      <c r="F274" s="5" t="n"/>
-      <c r="G274" s="2" t="n"/>
-    </row>
-    <row r="275">
-      <c r="A275" s="6" t="inlineStr">
-        <is>
-          <t>Step 1 — Drainage Area &amp; Regulated Volumes</t>
-        </is>
-      </c>
-      <c r="B275" s="7" t="n"/>
-      <c r="C275" s="7" t="n"/>
-      <c r="D275" s="7" t="n"/>
-      <c r="E275" s="7" t="n"/>
-      <c r="F275" s="7" t="n"/>
-      <c r="G275" s="8" t="n"/>
-    </row>
-    <row r="276">
-      <c r="A276" s="10" t="inlineStr">
-        <is>
-          <t>Drainage Area ID</t>
-        </is>
-      </c>
-      <c r="B276" s="16">
-        <f>'SDA'!A66</f>
-        <v/>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" s="10" t="inlineStr">
-        <is>
-          <t>Impervious within LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B277" s="16">
-        <f>SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,'SDA'!A66,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,'SDA'!A66,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" s="10" t="inlineStr">
-        <is>
-          <t>Compacted within LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B278" s="16">
-        <f>SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,'SDA'!A66,'SDA'!$C$4:$C$53,"Compacted (Open Space)")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" s="10" t="inlineStr">
-        <is>
-          <t>Natural within LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B279" s="16">
-        <f>SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,'SDA'!A66,'SDA'!$C$4:$C$53,"Natural (Woods)")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" s="3" t="inlineStr">
-        <is>
-          <t>Total within LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B280" s="16">
-        <f>SUM(B277:B279)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" s="10" t="inlineStr">
-        <is>
-          <t>Impervious outside LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B281" s="16">
-        <f>SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,'SDA'!A66,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,'SDA'!A66,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" s="10" t="inlineStr">
-        <is>
-          <t>Compacted outside LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B282" s="16">
-        <f>SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,'SDA'!A66,'SDA'!$C$4:$C$53,"Compacted (Open Space)")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" s="10" t="inlineStr">
-        <is>
-          <t>Natural outside LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B283" s="16">
-        <f>SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,'SDA'!A66,'SDA'!$C$4:$C$53,"Natural (Woods)")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" s="3" t="inlineStr">
-        <is>
-          <t>Total outside LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B284" s="16">
-        <f>SUM(B281:B283)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" s="3" t="inlineStr">
-        <is>
-          <t>SWRv Within LOD (CF)</t>
-        </is>
-      </c>
-      <c r="B285" s="16">
-        <f>'SDA'!J66</f>
-        <v/>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" s="6" t="inlineStr">
-        <is>
-          <t>Step 2 — Infiltration</t>
-        </is>
-      </c>
-      <c r="B286" s="7" t="n"/>
-      <c r="C286" s="7" t="n"/>
-      <c r="D286" s="7" t="n"/>
-      <c r="E286" s="7" t="n"/>
-      <c r="F286" s="7" t="n"/>
-      <c r="G286" s="8" t="n"/>
-    </row>
-    <row r="287">
-      <c r="A287" s="10" t="inlineStr">
-        <is>
-          <t>Hydrologic Soil Group</t>
-        </is>
-      </c>
-      <c r="B287" s="4" t="n"/>
-    </row>
-    <row r="288">
-      <c r="A288" s="10" t="inlineStr">
-        <is>
-          <t>Water Table OK?</t>
-        </is>
-      </c>
-      <c r="B288" s="4" t="n"/>
-    </row>
-    <row r="289">
-      <c r="A289" s="10" t="inlineStr">
-        <is>
-          <t>Bedrock OK?</t>
-        </is>
-      </c>
-      <c r="B289" s="4" t="n"/>
-    </row>
-    <row r="290">
-      <c r="A290" s="10" t="inlineStr">
-        <is>
-          <t>Infiltration Rate (in/hr)</t>
-        </is>
-      </c>
-      <c r="B290" s="4" t="n"/>
-    </row>
-    <row r="291">
-      <c r="A291" s="6" t="inlineStr">
-        <is>
-          <t>Step 3 — Constraints</t>
-        </is>
-      </c>
-      <c r="B291" s="7" t="n"/>
-      <c r="C291" s="7" t="n"/>
-      <c r="D291" s="7" t="n"/>
-      <c r="E291" s="7" t="n"/>
-      <c r="F291" s="7" t="n"/>
-      <c r="G291" s="8" t="n"/>
-    </row>
-    <row r="292">
-      <c r="A292" s="10" t="inlineStr">
-        <is>
-          <t>Hotspot Concern?</t>
-        </is>
-      </c>
-      <c r="B292" s="4" t="n"/>
-    </row>
-    <row r="293">
-      <c r="A293" s="6" t="inlineStr">
-        <is>
-          <t>Step 4 — Tree Credits (DDOT)</t>
-        </is>
-      </c>
-      <c r="B293" s="7" t="n"/>
-      <c r="C293" s="7" t="n"/>
-      <c r="D293" s="7" t="n"/>
-      <c r="E293" s="7" t="n"/>
-      <c r="F293" s="7" t="n"/>
-      <c r="G293" s="8" t="n"/>
-    </row>
-    <row r="294">
-      <c r="A294" s="10" t="inlineStr">
-        <is>
-          <t>Small Trees (preserved+planted)</t>
-        </is>
-      </c>
-      <c r="B294" s="16">
-        <f>(5)*(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,'SDA'!A66)+SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,'SDA'!A66))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" s="10" t="inlineStr">
-        <is>
-          <t>Large Trees (preserved+planted)</t>
-        </is>
-      </c>
-      <c r="B295" s="16">
-        <f>(20)*(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,'SDA'!A66)+SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,'SDA'!A66))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" s="10" t="inlineStr">
-        <is>
-          <t>Special Trees preserved</t>
-        </is>
-      </c>
-      <c r="B296" s="16">
-        <f>(30)*SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,'SDA'!A66)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" s="10" t="inlineStr">
-        <is>
-          <t>Heritage Trees preserved</t>
-        </is>
-      </c>
-      <c r="B297" s="16">
-        <f>(40)*SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,'SDA'!A66)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" s="6" t="inlineStr">
-        <is>
-          <t>Step 4 — BMP Placement</t>
-        </is>
-      </c>
-      <c r="B298" s="7" t="n"/>
-      <c r="C298" s="7" t="n"/>
-      <c r="D298" s="7" t="n"/>
-      <c r="E298" s="7" t="n"/>
-      <c r="F298" s="7" t="n"/>
-      <c r="G298" s="8" t="n"/>
-    </row>
-    <row r="299">
-      <c r="A299" s="17" t="inlineStr">
-        <is>
-          <t>BMP Name</t>
-        </is>
-      </c>
-      <c r="B299" s="17" t="inlineStr">
-        <is>
-          <t>BMP Type</t>
-        </is>
-      </c>
-      <c r="C299" s="17" t="inlineStr">
-        <is>
-          <t>CDA_ID</t>
-        </is>
-      </c>
-      <c r="D299" s="17" t="inlineStr">
-        <is>
-          <t>CDA Within LOD (SF)</t>
-        </is>
-      </c>
-      <c r="E299" s="17" t="inlineStr">
-        <is>
-          <t>CDA Outside LOD (SF)</t>
-        </is>
-      </c>
-      <c r="F299" s="17" t="inlineStr">
-        <is>
-          <t>BMP Rv (CF)</t>
-        </is>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" s="16">
-        <f>IFERROR(INDEX('BMP'!$A$4:$A$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A66,ROW('BMP'!$B$4:$B$53)-3),1)),"")</f>
-        <v/>
-      </c>
-      <c r="B300" s="16">
-        <f>IFERROR(INDEX('BMP'!$D$4:$D$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A66,ROW('BMP'!$B$4:$B$53)-3),1)),"")</f>
-        <v/>
-      </c>
-      <c r="C300" s="16">
-        <f>IFERROR(INDEX('BMP'!$C$4:$C$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A66,ROW('BMP'!$B$4:$B$53)-3),1)),"")</f>
-        <v/>
-      </c>
-      <c r="F300" s="16">
-        <f>IFERROR(INDEX('BMP'!$AM$4:$AM$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A66,ROW('BMP'!$B$4:$B$53)-3),1)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" s="16">
-        <f>IFERROR(INDEX('BMP'!$A$4:$A$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A66,ROW('BMP'!$B$4:$B$53)-3),2)),"")</f>
-        <v/>
-      </c>
-      <c r="B301" s="16">
-        <f>IFERROR(INDEX('BMP'!$D$4:$D$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A66,ROW('BMP'!$B$4:$B$53)-3),2)),"")</f>
-        <v/>
-      </c>
-      <c r="C301" s="16">
-        <f>IFERROR(INDEX('BMP'!$C$4:$C$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A66,ROW('BMP'!$B$4:$B$53)-3),2)),"")</f>
-        <v/>
-      </c>
-      <c r="F301" s="16">
-        <f>IFERROR(INDEX('BMP'!$AM$4:$AM$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A66,ROW('BMP'!$B$4:$B$53)-3),2)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" s="16">
-        <f>IFERROR(INDEX('BMP'!$A$4:$A$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A66,ROW('BMP'!$B$4:$B$53)-3),3)),"")</f>
-        <v/>
-      </c>
-      <c r="B302" s="16">
-        <f>IFERROR(INDEX('BMP'!$D$4:$D$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A66,ROW('BMP'!$B$4:$B$53)-3),3)),"")</f>
-        <v/>
-      </c>
-      <c r="C302" s="16">
-        <f>IFERROR(INDEX('BMP'!$C$4:$C$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A66,ROW('BMP'!$B$4:$B$53)-3),3)),"")</f>
-        <v/>
-      </c>
-      <c r="F302" s="16">
-        <f>IFERROR(INDEX('BMP'!$AM$4:$AM$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A66,ROW('BMP'!$B$4:$B$53)-3),3)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" s="16">
-        <f>IFERROR(INDEX('BMP'!$A$4:$A$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A66,ROW('BMP'!$B$4:$B$53)-3),4)),"")</f>
-        <v/>
-      </c>
-      <c r="B303" s="16">
-        <f>IFERROR(INDEX('BMP'!$D$4:$D$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A66,ROW('BMP'!$B$4:$B$53)-3),4)),"")</f>
-        <v/>
-      </c>
-      <c r="C303" s="16">
-        <f>IFERROR(INDEX('BMP'!$C$4:$C$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A66,ROW('BMP'!$B$4:$B$53)-3),4)),"")</f>
-        <v/>
-      </c>
-      <c r="F303" s="16">
-        <f>IFERROR(INDEX('BMP'!$AM$4:$AM$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A66,ROW('BMP'!$B$4:$B$53)-3),4)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" s="16">
-        <f>IFERROR(INDEX('BMP'!$A$4:$A$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A66,ROW('BMP'!$B$4:$B$53)-3),5)),"")</f>
-        <v/>
-      </c>
-      <c r="B304" s="16">
-        <f>IFERROR(INDEX('BMP'!$D$4:$D$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A66,ROW('BMP'!$B$4:$B$53)-3),5)),"")</f>
-        <v/>
-      </c>
-      <c r="C304" s="16">
-        <f>IFERROR(INDEX('BMP'!$C$4:$C$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A66,ROW('BMP'!$B$4:$B$53)-3),5)),"")</f>
-        <v/>
-      </c>
-      <c r="F304" s="16">
-        <f>IFERROR(INDEX('BMP'!$AM$4:$AM$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A66,ROW('BMP'!$B$4:$B$53)-3),5)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" s="3" t="inlineStr">
-        <is>
-          <t>Cumulative Surplus / Deficit (CF)</t>
-        </is>
-      </c>
-      <c r="B305" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AM$4:$AM$53,'BMP'!$B$4:$B$53,'SDA'!A66)-'SDA'!J66,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" s="1" t="inlineStr">
-        <is>
-          <t>SDA-10</t>
-        </is>
-      </c>
-      <c r="B307" s="5" t="n"/>
-      <c r="C307" s="5" t="n"/>
-      <c r="D307" s="5" t="n"/>
-      <c r="E307" s="5" t="n"/>
-      <c r="F307" s="5" t="n"/>
-      <c r="G307" s="2" t="n"/>
-    </row>
-    <row r="308">
-      <c r="A308" s="6" t="inlineStr">
-        <is>
-          <t>Step 1 — Drainage Area &amp; Regulated Volumes</t>
-        </is>
-      </c>
-      <c r="B308" s="7" t="n"/>
-      <c r="C308" s="7" t="n"/>
-      <c r="D308" s="7" t="n"/>
-      <c r="E308" s="7" t="n"/>
-      <c r="F308" s="7" t="n"/>
-      <c r="G308" s="8" t="n"/>
-    </row>
-    <row r="309">
-      <c r="A309" s="10" t="inlineStr">
-        <is>
-          <t>Drainage Area ID</t>
-        </is>
-      </c>
-      <c r="B309" s="16">
-        <f>'SDA'!A67</f>
-        <v/>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" s="10" t="inlineStr">
-        <is>
-          <t>Impervious within LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B310" s="16">
-        <f>SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,'SDA'!A67,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,'SDA'!A67,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" s="10" t="inlineStr">
-        <is>
-          <t>Compacted within LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B311" s="16">
-        <f>SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,'SDA'!A67,'SDA'!$C$4:$C$53,"Compacted (Open Space)")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" s="10" t="inlineStr">
-        <is>
-          <t>Natural within LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B312" s="16">
-        <f>SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,'SDA'!A67,'SDA'!$C$4:$C$53,"Natural (Woods)")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" s="3" t="inlineStr">
-        <is>
-          <t>Total within LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B313" s="16">
-        <f>SUM(B310:B312)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" s="10" t="inlineStr">
-        <is>
-          <t>Impervious outside LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B314" s="16">
-        <f>SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,'SDA'!A67,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,'SDA'!A67,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" s="10" t="inlineStr">
-        <is>
-          <t>Compacted outside LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B315" s="16">
-        <f>SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,'SDA'!A67,'SDA'!$C$4:$C$53,"Compacted (Open Space)")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" s="10" t="inlineStr">
-        <is>
-          <t>Natural outside LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B316" s="16">
-        <f>SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,'SDA'!A67,'SDA'!$C$4:$C$53,"Natural (Woods)")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" s="3" t="inlineStr">
-        <is>
-          <t>Total outside LOD (SF)</t>
-        </is>
-      </c>
-      <c r="B317" s="16">
-        <f>SUM(B314:B316)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" s="3" t="inlineStr">
-        <is>
-          <t>SWRv Within LOD (CF)</t>
-        </is>
-      </c>
-      <c r="B318" s="16">
-        <f>'SDA'!J67</f>
-        <v/>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" s="6" t="inlineStr">
-        <is>
-          <t>Step 2 — Infiltration</t>
-        </is>
-      </c>
-      <c r="B319" s="7" t="n"/>
-      <c r="C319" s="7" t="n"/>
-      <c r="D319" s="7" t="n"/>
-      <c r="E319" s="7" t="n"/>
-      <c r="F319" s="7" t="n"/>
-      <c r="G319" s="8" t="n"/>
-    </row>
-    <row r="320">
-      <c r="A320" s="10" t="inlineStr">
-        <is>
-          <t>Hydrologic Soil Group</t>
-        </is>
-      </c>
-      <c r="B320" s="4" t="n"/>
-    </row>
-    <row r="321">
-      <c r="A321" s="10" t="inlineStr">
-        <is>
-          <t>Water Table OK?</t>
-        </is>
-      </c>
-      <c r="B321" s="4" t="n"/>
-    </row>
-    <row r="322">
-      <c r="A322" s="10" t="inlineStr">
-        <is>
-          <t>Bedrock OK?</t>
-        </is>
-      </c>
-      <c r="B322" s="4" t="n"/>
-    </row>
-    <row r="323">
-      <c r="A323" s="10" t="inlineStr">
-        <is>
-          <t>Infiltration Rate (in/hr)</t>
-        </is>
-      </c>
-      <c r="B323" s="4" t="n"/>
-    </row>
-    <row r="324">
-      <c r="A324" s="6" t="inlineStr">
-        <is>
-          <t>Step 3 — Constraints</t>
-        </is>
-      </c>
-      <c r="B324" s="7" t="n"/>
-      <c r="C324" s="7" t="n"/>
-      <c r="D324" s="7" t="n"/>
-      <c r="E324" s="7" t="n"/>
-      <c r="F324" s="7" t="n"/>
-      <c r="G324" s="8" t="n"/>
-    </row>
-    <row r="325">
-      <c r="A325" s="10" t="inlineStr">
-        <is>
-          <t>Hotspot Concern?</t>
-        </is>
-      </c>
-      <c r="B325" s="4" t="n"/>
-    </row>
-    <row r="326">
-      <c r="A326" s="6" t="inlineStr">
-        <is>
-          <t>Step 4 — Tree Credits (DDOT)</t>
-        </is>
-      </c>
-      <c r="B326" s="7" t="n"/>
-      <c r="C326" s="7" t="n"/>
-      <c r="D326" s="7" t="n"/>
-      <c r="E326" s="7" t="n"/>
-      <c r="F326" s="7" t="n"/>
-      <c r="G326" s="8" t="n"/>
-    </row>
-    <row r="327">
-      <c r="A327" s="10" t="inlineStr">
-        <is>
-          <t>Small Trees (preserved+planted)</t>
-        </is>
-      </c>
-      <c r="B327" s="16">
-        <f>(5)*(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,'SDA'!A67)+SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,'SDA'!A67))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" s="10" t="inlineStr">
-        <is>
-          <t>Large Trees (preserved+planted)</t>
-        </is>
-      </c>
-      <c r="B328" s="16">
-        <f>(20)*(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,'SDA'!A67)+SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,'SDA'!A67))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" s="10" t="inlineStr">
-        <is>
-          <t>Special Trees preserved</t>
-        </is>
-      </c>
-      <c r="B329" s="16">
-        <f>(30)*SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,'SDA'!A67)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" s="10" t="inlineStr">
-        <is>
-          <t>Heritage Trees preserved</t>
-        </is>
-      </c>
-      <c r="B330" s="16">
-        <f>(40)*SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,'SDA'!A67)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" s="6" t="inlineStr">
-        <is>
-          <t>Step 4 — BMP Placement</t>
-        </is>
-      </c>
-      <c r="B331" s="7" t="n"/>
-      <c r="C331" s="7" t="n"/>
-      <c r="D331" s="7" t="n"/>
-      <c r="E331" s="7" t="n"/>
-      <c r="F331" s="7" t="n"/>
-      <c r="G331" s="8" t="n"/>
-    </row>
-    <row r="332">
-      <c r="A332" s="17" t="inlineStr">
-        <is>
-          <t>BMP Name</t>
-        </is>
-      </c>
-      <c r="B332" s="17" t="inlineStr">
-        <is>
-          <t>BMP Type</t>
-        </is>
-      </c>
-      <c r="C332" s="17" t="inlineStr">
-        <is>
-          <t>CDA_ID</t>
-        </is>
-      </c>
-      <c r="D332" s="17" t="inlineStr">
-        <is>
-          <t>CDA Within LOD (SF)</t>
-        </is>
-      </c>
-      <c r="E332" s="17" t="inlineStr">
-        <is>
-          <t>CDA Outside LOD (SF)</t>
-        </is>
-      </c>
-      <c r="F332" s="17" t="inlineStr">
-        <is>
-          <t>BMP Rv (CF)</t>
-        </is>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" s="16">
-        <f>IFERROR(INDEX('BMP'!$A$4:$A$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A67,ROW('BMP'!$B$4:$B$53)-3),1)),"")</f>
-        <v/>
-      </c>
-      <c r="B333" s="16">
-        <f>IFERROR(INDEX('BMP'!$D$4:$D$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A67,ROW('BMP'!$B$4:$B$53)-3),1)),"")</f>
-        <v/>
-      </c>
-      <c r="C333" s="16">
-        <f>IFERROR(INDEX('BMP'!$C$4:$C$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A67,ROW('BMP'!$B$4:$B$53)-3),1)),"")</f>
-        <v/>
-      </c>
-      <c r="F333" s="16">
-        <f>IFERROR(INDEX('BMP'!$AM$4:$AM$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A67,ROW('BMP'!$B$4:$B$53)-3),1)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" s="16">
-        <f>IFERROR(INDEX('BMP'!$A$4:$A$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A67,ROW('BMP'!$B$4:$B$53)-3),2)),"")</f>
-        <v/>
-      </c>
-      <c r="B334" s="16">
-        <f>IFERROR(INDEX('BMP'!$D$4:$D$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A67,ROW('BMP'!$B$4:$B$53)-3),2)),"")</f>
-        <v/>
-      </c>
-      <c r="C334" s="16">
-        <f>IFERROR(INDEX('BMP'!$C$4:$C$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A67,ROW('BMP'!$B$4:$B$53)-3),2)),"")</f>
-        <v/>
-      </c>
-      <c r="F334" s="16">
-        <f>IFERROR(INDEX('BMP'!$AM$4:$AM$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A67,ROW('BMP'!$B$4:$B$53)-3),2)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" s="16">
-        <f>IFERROR(INDEX('BMP'!$A$4:$A$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A67,ROW('BMP'!$B$4:$B$53)-3),3)),"")</f>
-        <v/>
-      </c>
-      <c r="B335" s="16">
-        <f>IFERROR(INDEX('BMP'!$D$4:$D$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A67,ROW('BMP'!$B$4:$B$53)-3),3)),"")</f>
-        <v/>
-      </c>
-      <c r="C335" s="16">
-        <f>IFERROR(INDEX('BMP'!$C$4:$C$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A67,ROW('BMP'!$B$4:$B$53)-3),3)),"")</f>
-        <v/>
-      </c>
-      <c r="F335" s="16">
-        <f>IFERROR(INDEX('BMP'!$AM$4:$AM$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A67,ROW('BMP'!$B$4:$B$53)-3),3)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" s="16">
-        <f>IFERROR(INDEX('BMP'!$A$4:$A$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A67,ROW('BMP'!$B$4:$B$53)-3),4)),"")</f>
-        <v/>
-      </c>
-      <c r="B336" s="16">
-        <f>IFERROR(INDEX('BMP'!$D$4:$D$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A67,ROW('BMP'!$B$4:$B$53)-3),4)),"")</f>
-        <v/>
-      </c>
-      <c r="C336" s="16">
-        <f>IFERROR(INDEX('BMP'!$C$4:$C$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A67,ROW('BMP'!$B$4:$B$53)-3),4)),"")</f>
-        <v/>
-      </c>
-      <c r="F336" s="16">
-        <f>IFERROR(INDEX('BMP'!$AM$4:$AM$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A67,ROW('BMP'!$B$4:$B$53)-3),4)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" s="16">
-        <f>IFERROR(INDEX('BMP'!$A$4:$A$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A67,ROW('BMP'!$B$4:$B$53)-3),5)),"")</f>
-        <v/>
-      </c>
-      <c r="B337" s="16">
-        <f>IFERROR(INDEX('BMP'!$D$4:$D$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A67,ROW('BMP'!$B$4:$B$53)-3),5)),"")</f>
-        <v/>
-      </c>
-      <c r="C337" s="16">
-        <f>IFERROR(INDEX('BMP'!$C$4:$C$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A67,ROW('BMP'!$B$4:$B$53)-3),5)),"")</f>
-        <v/>
-      </c>
-      <c r="F337" s="16">
-        <f>IFERROR(INDEX('BMP'!$AM$4:$AM$53,SMALL(IF('BMP'!$B$4:$B$53='SDA'!A67,ROW('BMP'!$B$4:$B$53)-3),5)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" s="3" t="inlineStr">
-        <is>
-          <t>Cumulative Surplus / Deficit (CF)</t>
-        </is>
-      </c>
-      <c r="B338" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AM$4:$AM$53,'BMP'!$B$4:$B$53,'SDA'!A67)-'SDA'!J67,"")</f>
+        <f>'SDA'!F67</f>
+        <v/>
+      </c>
+      <c r="C21" s="16">
+        <f>'SDA'!G67</f>
+        <v/>
+      </c>
+      <c r="D21" s="16">
+        <f>'SDA'!H67</f>
+        <v/>
+      </c>
+      <c r="E21" s="16">
+        <f>SUM(B21:D21)</f>
+        <v/>
+      </c>
+      <c r="F21" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A21,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A21,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <v/>
+      </c>
+      <c r="G21" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A21,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <v/>
+      </c>
+      <c r="H21" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A21,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <v/>
+      </c>
+      <c r="I21" s="16">
+        <f>SUM(F21:H21)</f>
+        <v/>
+      </c>
+      <c r="J21" s="16">
+        <f>IF(E21=0,0,AP21*1.2/12*E21)</f>
+        <v/>
+      </c>
+      <c r="K21" s="16">
+        <f>IF(I21=0,0,AQ21*1.2/12*I21)</f>
+        <v/>
+      </c>
+      <c r="L21" s="16">
+        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A21,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A21,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A21,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A21,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <v/>
+      </c>
+      <c r="M21" s="4" t="n"/>
+      <c r="N21" s="4" t="n"/>
+      <c r="O21" s="16">
+        <f>IFERROR(IFS(L21="A",2.5,L21="B",0.3,L21="C",0.1,L21="D",0.05,TRUE,""),"")</f>
+        <v/>
+      </c>
+      <c r="P21" s="4" t="n"/>
+      <c r="Q21" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A21),0)</f>
+        <v/>
+      </c>
+      <c r="R21" s="16">
+        <f>Q21*10</f>
+        <v/>
+      </c>
+      <c r="S21" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A21),0)</f>
+        <v/>
+      </c>
+      <c r="T21" s="16">
+        <f>S21*20</f>
+        <v/>
+      </c>
+      <c r="U21" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A21)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A21),0)</f>
+        <v/>
+      </c>
+      <c r="V21" s="16">
+        <f>U21*40</f>
+        <v/>
+      </c>
+      <c r="W21" s="4" t="n"/>
+      <c r="X21" s="4" t="n"/>
+      <c r="Y21" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A21,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A21,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="Z21" s="4" t="n"/>
+      <c r="AA21" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A21,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
+      <c r="AB21" s="4" t="n"/>
+      <c r="AC21" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A21),0)</f>
+        <v/>
+      </c>
+      <c r="AD21" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A21),0)</f>
+        <v/>
+      </c>
+      <c r="AE21" s="16">
+        <f>IF(AC21=0,0,AC21*1.7/12*AP21)</f>
+        <v/>
+      </c>
+      <c r="AF21" s="16">
+        <f>IF(AD21=0,0,AD21*1.7/12*AQ21)</f>
+        <v/>
+      </c>
+      <c r="AG21" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A21,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A21,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AH21" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A21,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
+      <c r="AI21" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A21,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AJ21" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A21),0)</f>
+        <v/>
+      </c>
+      <c r="AK21" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A21),0)</f>
+        <v/>
+      </c>
+      <c r="AL21" s="16">
+        <f>(IF((AE21)&lt;(AG21+AH21+AI21),(AE21),(AG21+AH21+AI21)))+AJ21*5+AK21*10+R21+T21+V21</f>
+        <v/>
+      </c>
+      <c r="AM21" s="16">
+        <f>AL21-J21</f>
+        <v/>
+      </c>
+      <c r="AP21" s="16">
+        <f>IF(E21=0,"",(B21*0.95+C21*0.25+D21*0)/E21)</f>
+        <v/>
+      </c>
+      <c r="AQ21" s="16">
+        <f>IF(I21=0,"",(F21*0.95+G21*0.25+H21*0)/I21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="16.25" customHeight="1">
+      <c r="E22" s="16">
+        <f>SUM(B22:D22)</f>
+        <v/>
+      </c>
+      <c r="I22" s="16">
+        <f>SUM(F22:H22)</f>
+        <v/>
+      </c>
+      <c r="J22" s="16">
+        <f>IF(E22=0,0,AP22*1.2/12*E22)</f>
+        <v/>
+      </c>
+      <c r="K22" s="16">
+        <f>IF(I22=0,0,AQ22*1.2/12*I22)</f>
+        <v/>
+      </c>
+      <c r="M22" s="4" t="n"/>
+      <c r="N22" s="4" t="n"/>
+      <c r="P22" s="4" t="n"/>
+      <c r="R22" s="16">
+        <f>Q22*10</f>
+        <v/>
+      </c>
+      <c r="T22" s="16">
+        <f>S22*20</f>
+        <v/>
+      </c>
+      <c r="V22" s="16">
+        <f>U22*40</f>
+        <v/>
+      </c>
+      <c r="W22" s="4" t="n"/>
+      <c r="X22" s="4" t="n"/>
+      <c r="Z22" s="4" t="n"/>
+      <c r="AB22" s="4" t="n"/>
+      <c r="AE22" s="16">
+        <f>IF(AC22=0,0,AC22*1.7/12*AP22)</f>
+        <v/>
+      </c>
+      <c r="AF22" s="16">
+        <f>IF(AD22=0,0,AD22*1.7/12*AQ22)</f>
+        <v/>
+      </c>
+      <c r="AL22" s="16">
+        <f>(IF((AE22)&lt;(AG22+AH22+AI22),(AE22),(AG22+AH22+AI22)))+AJ22*5+AK22*10+R22+T22+V22</f>
+        <v/>
+      </c>
+      <c r="AM22" s="16">
+        <f>AL22-J22</f>
+        <v/>
+      </c>
+      <c r="AP22" s="16">
+        <f>IF(E22=0,"",(B22*0.95+C22*0.25+D22*0)/E22)</f>
+        <v/>
+      </c>
+      <c r="AQ22" s="16">
+        <f>IF(I22=0,"",(F22*0.95+G22*0.25+H22*0)/I22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="16.25" customHeight="1">
+      <c r="E23" s="16">
+        <f>SUM(B23:D23)</f>
+        <v/>
+      </c>
+      <c r="I23" s="16">
+        <f>SUM(F23:H23)</f>
+        <v/>
+      </c>
+      <c r="J23" s="16">
+        <f>IF(E23=0,0,AP23*1.2/12*E23)</f>
+        <v/>
+      </c>
+      <c r="K23" s="16">
+        <f>IF(I23=0,0,AQ23*1.2/12*I23)</f>
+        <v/>
+      </c>
+      <c r="M23" s="4" t="n"/>
+      <c r="N23" s="4" t="n"/>
+      <c r="P23" s="4" t="n"/>
+      <c r="R23" s="16">
+        <f>Q23*10</f>
+        <v/>
+      </c>
+      <c r="T23" s="16">
+        <f>S23*20</f>
+        <v/>
+      </c>
+      <c r="V23" s="16">
+        <f>U23*40</f>
+        <v/>
+      </c>
+      <c r="W23" s="4" t="n"/>
+      <c r="X23" s="4" t="n"/>
+      <c r="Z23" s="4" t="n"/>
+      <c r="AB23" s="4" t="n"/>
+      <c r="AE23" s="16">
+        <f>IF(AC23=0,0,AC23*1.7/12*AP23)</f>
+        <v/>
+      </c>
+      <c r="AF23" s="16">
+        <f>IF(AD23=0,0,AD23*1.7/12*AQ23)</f>
+        <v/>
+      </c>
+      <c r="AL23" s="16">
+        <f>(IF((AE23)&lt;(AG23+AH23+AI23),(AE23),(AG23+AH23+AI23)))+AJ23*5+AK23*10+R23+T23+V23</f>
+        <v/>
+      </c>
+      <c r="AM23" s="16">
+        <f>AL23-J23</f>
+        <v/>
+      </c>
+      <c r="AP23" s="16">
+        <f>IF(E23=0,"",(B23*0.95+C23*0.25+D23*0)/E23)</f>
+        <v/>
+      </c>
+      <c r="AQ23" s="16">
+        <f>IF(I23=0,"",(F23*0.95+G23*0.25+H23*0)/I23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="16.25" customHeight="1">
+      <c r="E24" s="16">
+        <f>SUM(B24:D24)</f>
+        <v/>
+      </c>
+      <c r="I24" s="16">
+        <f>SUM(F24:H24)</f>
+        <v/>
+      </c>
+      <c r="J24" s="16">
+        <f>IF(E24=0,0,AP24*1.2/12*E24)</f>
+        <v/>
+      </c>
+      <c r="K24" s="16">
+        <f>IF(I24=0,0,AQ24*1.2/12*I24)</f>
+        <v/>
+      </c>
+      <c r="M24" s="4" t="n"/>
+      <c r="N24" s="4" t="n"/>
+      <c r="P24" s="4" t="n"/>
+      <c r="R24" s="16">
+        <f>Q24*10</f>
+        <v/>
+      </c>
+      <c r="T24" s="16">
+        <f>S24*20</f>
+        <v/>
+      </c>
+      <c r="V24" s="16">
+        <f>U24*40</f>
+        <v/>
+      </c>
+      <c r="W24" s="4" t="n"/>
+      <c r="X24" s="4" t="n"/>
+      <c r="Z24" s="4" t="n"/>
+      <c r="AB24" s="4" t="n"/>
+      <c r="AE24" s="16">
+        <f>IF(AC24=0,0,AC24*1.7/12*AP24)</f>
+        <v/>
+      </c>
+      <c r="AF24" s="16">
+        <f>IF(AD24=0,0,AD24*1.7/12*AQ24)</f>
+        <v/>
+      </c>
+      <c r="AL24" s="16">
+        <f>(IF((AE24)&lt;(AG24+AH24+AI24),(AE24),(AG24+AH24+AI24)))+AJ24*5+AK24*10+R24+T24+V24</f>
+        <v/>
+      </c>
+      <c r="AM24" s="16">
+        <f>AL24-J24</f>
+        <v/>
+      </c>
+      <c r="AP24" s="16">
+        <f>IF(E24=0,"",(B24*0.95+C24*0.25+D24*0)/E24)</f>
+        <v/>
+      </c>
+      <c r="AQ24" s="16">
+        <f>IF(I24=0,"",(F24*0.95+G24*0.25+H24*0)/I24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="16.25" customHeight="1">
+      <c r="E25" s="16">
+        <f>SUM(B25:D25)</f>
+        <v/>
+      </c>
+      <c r="I25" s="16">
+        <f>SUM(F25:H25)</f>
+        <v/>
+      </c>
+      <c r="J25" s="16">
+        <f>IF(E25=0,0,AP25*1.2/12*E25)</f>
+        <v/>
+      </c>
+      <c r="K25" s="16">
+        <f>IF(I25=0,0,AQ25*1.2/12*I25)</f>
+        <v/>
+      </c>
+      <c r="M25" s="4" t="n"/>
+      <c r="N25" s="4" t="n"/>
+      <c r="P25" s="4" t="n"/>
+      <c r="R25" s="16">
+        <f>Q25*10</f>
+        <v/>
+      </c>
+      <c r="T25" s="16">
+        <f>S25*20</f>
+        <v/>
+      </c>
+      <c r="V25" s="16">
+        <f>U25*40</f>
+        <v/>
+      </c>
+      <c r="W25" s="4" t="n"/>
+      <c r="X25" s="4" t="n"/>
+      <c r="Z25" s="4" t="n"/>
+      <c r="AB25" s="4" t="n"/>
+      <c r="AE25" s="16">
+        <f>IF(AC25=0,0,AC25*1.7/12*AP25)</f>
+        <v/>
+      </c>
+      <c r="AF25" s="16">
+        <f>IF(AD25=0,0,AD25*1.7/12*AQ25)</f>
+        <v/>
+      </c>
+      <c r="AL25" s="16">
+        <f>(IF((AE25)&lt;(AG25+AH25+AI25),(AE25),(AG25+AH25+AI25)))+AJ25*5+AK25*10+R25+T25+V25</f>
+        <v/>
+      </c>
+      <c r="AM25" s="16">
+        <f>AL25-J25</f>
+        <v/>
+      </c>
+      <c r="AP25" s="16">
+        <f>IF(E25=0,"",(B25*0.95+C25*0.25+D25*0)/E25)</f>
+        <v/>
+      </c>
+      <c r="AQ25" s="16">
+        <f>IF(I25=0,"",(F25*0.95+G25*0.25+H25*0)/I25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="16.25" customHeight="1">
+      <c r="E26" s="16">
+        <f>SUM(B26:D26)</f>
+        <v/>
+      </c>
+      <c r="I26" s="16">
+        <f>SUM(F26:H26)</f>
+        <v/>
+      </c>
+      <c r="J26" s="16">
+        <f>IF(E26=0,0,AP26*1.2/12*E26)</f>
+        <v/>
+      </c>
+      <c r="K26" s="16">
+        <f>IF(I26=0,0,AQ26*1.2/12*I26)</f>
+        <v/>
+      </c>
+      <c r="M26" s="4" t="n"/>
+      <c r="N26" s="4" t="n"/>
+      <c r="P26" s="4" t="n"/>
+      <c r="R26" s="16">
+        <f>Q26*10</f>
+        <v/>
+      </c>
+      <c r="T26" s="16">
+        <f>S26*20</f>
+        <v/>
+      </c>
+      <c r="V26" s="16">
+        <f>U26*40</f>
+        <v/>
+      </c>
+      <c r="W26" s="4" t="n"/>
+      <c r="X26" s="4" t="n"/>
+      <c r="Z26" s="4" t="n"/>
+      <c r="AB26" s="4" t="n"/>
+      <c r="AE26" s="16">
+        <f>IF(AC26=0,0,AC26*1.7/12*AP26)</f>
+        <v/>
+      </c>
+      <c r="AF26" s="16">
+        <f>IF(AD26=0,0,AD26*1.7/12*AQ26)</f>
+        <v/>
+      </c>
+      <c r="AL26" s="16">
+        <f>(IF((AE26)&lt;(AG26+AH26+AI26),(AE26),(AG26+AH26+AI26)))+AJ26*5+AK26*10+R26+T26+V26</f>
+        <v/>
+      </c>
+      <c r="AM26" s="16">
+        <f>AL26-J26</f>
+        <v/>
+      </c>
+      <c r="AP26" s="16">
+        <f>IF(E26=0,"",(B26*0.95+C26*0.25+D26*0)/E26)</f>
+        <v/>
+      </c>
+      <c r="AQ26" s="16">
+        <f>IF(I26=0,"",(F26*0.95+G26*0.25+H26*0)/I26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="16.25" customHeight="1">
+      <c r="E27" s="16">
+        <f>SUM(B27:D27)</f>
+        <v/>
+      </c>
+      <c r="I27" s="16">
+        <f>SUM(F27:H27)</f>
+        <v/>
+      </c>
+      <c r="J27" s="16">
+        <f>IF(E27=0,0,AP27*1.2/12*E27)</f>
+        <v/>
+      </c>
+      <c r="K27" s="16">
+        <f>IF(I27=0,0,AQ27*1.2/12*I27)</f>
+        <v/>
+      </c>
+      <c r="M27" s="4" t="n"/>
+      <c r="N27" s="4" t="n"/>
+      <c r="P27" s="4" t="n"/>
+      <c r="R27" s="16">
+        <f>Q27*10</f>
+        <v/>
+      </c>
+      <c r="T27" s="16">
+        <f>S27*20</f>
+        <v/>
+      </c>
+      <c r="V27" s="16">
+        <f>U27*40</f>
+        <v/>
+      </c>
+      <c r="W27" s="4" t="n"/>
+      <c r="X27" s="4" t="n"/>
+      <c r="Z27" s="4" t="n"/>
+      <c r="AB27" s="4" t="n"/>
+      <c r="AE27" s="16">
+        <f>IF(AC27=0,0,AC27*1.7/12*AP27)</f>
+        <v/>
+      </c>
+      <c r="AF27" s="16">
+        <f>IF(AD27=0,0,AD27*1.7/12*AQ27)</f>
+        <v/>
+      </c>
+      <c r="AL27" s="16">
+        <f>(IF((AE27)&lt;(AG27+AH27+AI27),(AE27),(AG27+AH27+AI27)))+AJ27*5+AK27*10+R27+T27+V27</f>
+        <v/>
+      </c>
+      <c r="AM27" s="16">
+        <f>AL27-J27</f>
+        <v/>
+      </c>
+      <c r="AP27" s="16">
+        <f>IF(E27=0,"",(B27*0.95+C27*0.25+D27*0)/E27)</f>
+        <v/>
+      </c>
+      <c r="AQ27" s="16">
+        <f>IF(I27=0,"",(F27*0.95+G27*0.25+H27*0)/I27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="16.25" customHeight="1">
+      <c r="E28" s="16">
+        <f>SUM(B28:D28)</f>
+        <v/>
+      </c>
+      <c r="I28" s="16">
+        <f>SUM(F28:H28)</f>
+        <v/>
+      </c>
+      <c r="J28" s="16">
+        <f>IF(E28=0,0,AP28*1.2/12*E28)</f>
+        <v/>
+      </c>
+      <c r="K28" s="16">
+        <f>IF(I28=0,0,AQ28*1.2/12*I28)</f>
+        <v/>
+      </c>
+      <c r="M28" s="4" t="n"/>
+      <c r="N28" s="4" t="n"/>
+      <c r="P28" s="4" t="n"/>
+      <c r="R28" s="16">
+        <f>Q28*10</f>
+        <v/>
+      </c>
+      <c r="T28" s="16">
+        <f>S28*20</f>
+        <v/>
+      </c>
+      <c r="V28" s="16">
+        <f>U28*40</f>
+        <v/>
+      </c>
+      <c r="W28" s="4" t="n"/>
+      <c r="X28" s="4" t="n"/>
+      <c r="Z28" s="4" t="n"/>
+      <c r="AB28" s="4" t="n"/>
+      <c r="AE28" s="16">
+        <f>IF(AC28=0,0,AC28*1.7/12*AP28)</f>
+        <v/>
+      </c>
+      <c r="AF28" s="16">
+        <f>IF(AD28=0,0,AD28*1.7/12*AQ28)</f>
+        <v/>
+      </c>
+      <c r="AL28" s="16">
+        <f>(IF((AE28)&lt;(AG28+AH28+AI28),(AE28),(AG28+AH28+AI28)))+AJ28*5+AK28*10+R28+T28+V28</f>
+        <v/>
+      </c>
+      <c r="AM28" s="16">
+        <f>AL28-J28</f>
+        <v/>
+      </c>
+      <c r="AP28" s="16">
+        <f>IF(E28=0,"",(B28*0.95+C28*0.25+D28*0)/E28)</f>
+        <v/>
+      </c>
+      <c r="AQ28" s="16">
+        <f>IF(I28=0,"",(F28*0.95+G28*0.25+H28*0)/I28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="16.25" customHeight="1">
+      <c r="E29" s="16">
+        <f>SUM(B29:D29)</f>
+        <v/>
+      </c>
+      <c r="I29" s="16">
+        <f>SUM(F29:H29)</f>
+        <v/>
+      </c>
+      <c r="J29" s="16">
+        <f>IF(E29=0,0,AP29*1.2/12*E29)</f>
+        <v/>
+      </c>
+      <c r="K29" s="16">
+        <f>IF(I29=0,0,AQ29*1.2/12*I29)</f>
+        <v/>
+      </c>
+      <c r="M29" s="4" t="n"/>
+      <c r="N29" s="4" t="n"/>
+      <c r="P29" s="4" t="n"/>
+      <c r="R29" s="16">
+        <f>Q29*10</f>
+        <v/>
+      </c>
+      <c r="T29" s="16">
+        <f>S29*20</f>
+        <v/>
+      </c>
+      <c r="V29" s="16">
+        <f>U29*40</f>
+        <v/>
+      </c>
+      <c r="W29" s="4" t="n"/>
+      <c r="X29" s="4" t="n"/>
+      <c r="Z29" s="4" t="n"/>
+      <c r="AB29" s="4" t="n"/>
+      <c r="AE29" s="16">
+        <f>IF(AC29=0,0,AC29*1.7/12*AP29)</f>
+        <v/>
+      </c>
+      <c r="AF29" s="16">
+        <f>IF(AD29=0,0,AD29*1.7/12*AQ29)</f>
+        <v/>
+      </c>
+      <c r="AL29" s="16">
+        <f>(IF((AE29)&lt;(AG29+AH29+AI29),(AE29),(AG29+AH29+AI29)))+AJ29*5+AK29*10+R29+T29+V29</f>
+        <v/>
+      </c>
+      <c r="AM29" s="16">
+        <f>AL29-J29</f>
+        <v/>
+      </c>
+      <c r="AP29" s="16">
+        <f>IF(E29=0,"",(B29*0.95+C29*0.25+D29*0)/E29)</f>
+        <v/>
+      </c>
+      <c r="AQ29" s="16">
+        <f>IF(I29=0,"",(F29*0.95+G29*0.25+H29*0)/I29)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="16.25" customHeight="1">
+      <c r="E30" s="16">
+        <f>SUM(B30:D30)</f>
+        <v/>
+      </c>
+      <c r="I30" s="16">
+        <f>SUM(F30:H30)</f>
+        <v/>
+      </c>
+      <c r="J30" s="16">
+        <f>IF(E30=0,0,AP30*1.2/12*E30)</f>
+        <v/>
+      </c>
+      <c r="K30" s="16">
+        <f>IF(I30=0,0,AQ30*1.2/12*I30)</f>
+        <v/>
+      </c>
+      <c r="M30" s="4" t="n"/>
+      <c r="N30" s="4" t="n"/>
+      <c r="P30" s="4" t="n"/>
+      <c r="R30" s="16">
+        <f>Q30*10</f>
+        <v/>
+      </c>
+      <c r="T30" s="16">
+        <f>S30*20</f>
+        <v/>
+      </c>
+      <c r="V30" s="16">
+        <f>U30*40</f>
+        <v/>
+      </c>
+      <c r="W30" s="4" t="n"/>
+      <c r="X30" s="4" t="n"/>
+      <c r="Z30" s="4" t="n"/>
+      <c r="AB30" s="4" t="n"/>
+      <c r="AE30" s="16">
+        <f>IF(AC30=0,0,AC30*1.7/12*AP30)</f>
+        <v/>
+      </c>
+      <c r="AF30" s="16">
+        <f>IF(AD30=0,0,AD30*1.7/12*AQ30)</f>
+        <v/>
+      </c>
+      <c r="AL30" s="16">
+        <f>(IF((AE30)&lt;(AG30+AH30+AI30),(AE30),(AG30+AH30+AI30)))+AJ30*5+AK30*10+R30+T30+V30</f>
+        <v/>
+      </c>
+      <c r="AM30" s="16">
+        <f>AL30-J30</f>
+        <v/>
+      </c>
+      <c r="AP30" s="16">
+        <f>IF(E30=0,"",(B30*0.95+C30*0.25+D30*0)/E30)</f>
+        <v/>
+      </c>
+      <c r="AQ30" s="16">
+        <f>IF(I30=0,"",(F30*0.95+G30*0.25+H30*0)/I30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="16.25" customHeight="1">
+      <c r="E31" s="16">
+        <f>SUM(B31:D31)</f>
+        <v/>
+      </c>
+      <c r="I31" s="16">
+        <f>SUM(F31:H31)</f>
+        <v/>
+      </c>
+      <c r="J31" s="16">
+        <f>IF(E31=0,0,AP31*1.2/12*E31)</f>
+        <v/>
+      </c>
+      <c r="K31" s="16">
+        <f>IF(I31=0,0,AQ31*1.2/12*I31)</f>
+        <v/>
+      </c>
+      <c r="M31" s="4" t="n"/>
+      <c r="N31" s="4" t="n"/>
+      <c r="P31" s="4" t="n"/>
+      <c r="R31" s="16">
+        <f>Q31*10</f>
+        <v/>
+      </c>
+      <c r="T31" s="16">
+        <f>S31*20</f>
+        <v/>
+      </c>
+      <c r="V31" s="16">
+        <f>U31*40</f>
+        <v/>
+      </c>
+      <c r="W31" s="4" t="n"/>
+      <c r="X31" s="4" t="n"/>
+      <c r="Z31" s="4" t="n"/>
+      <c r="AB31" s="4" t="n"/>
+      <c r="AE31" s="16">
+        <f>IF(AC31=0,0,AC31*1.7/12*AP31)</f>
+        <v/>
+      </c>
+      <c r="AF31" s="16">
+        <f>IF(AD31=0,0,AD31*1.7/12*AQ31)</f>
+        <v/>
+      </c>
+      <c r="AL31" s="16">
+        <f>(IF((AE31)&lt;(AG31+AH31+AI31),(AE31),(AG31+AH31+AI31)))+AJ31*5+AK31*10+R31+T31+V31</f>
+        <v/>
+      </c>
+      <c r="AM31" s="16">
+        <f>AL31-J31</f>
+        <v/>
+      </c>
+      <c r="AP31" s="16">
+        <f>IF(E31=0,"",(B31*0.95+C31*0.25+D31*0)/E31)</f>
+        <v/>
+      </c>
+      <c r="AQ31" s="16">
+        <f>IF(I31=0,"",(F31*0.95+G31*0.25+H31*0)/I31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="16.25" customHeight="1">
+      <c r="E32" s="16">
+        <f>SUM(B32:D32)</f>
+        <v/>
+      </c>
+      <c r="I32" s="16">
+        <f>SUM(F32:H32)</f>
+        <v/>
+      </c>
+      <c r="J32" s="16">
+        <f>IF(E32=0,0,AP32*1.2/12*E32)</f>
+        <v/>
+      </c>
+      <c r="K32" s="16">
+        <f>IF(I32=0,0,AQ32*1.2/12*I32)</f>
+        <v/>
+      </c>
+      <c r="M32" s="4" t="n"/>
+      <c r="N32" s="4" t="n"/>
+      <c r="P32" s="4" t="n"/>
+      <c r="R32" s="16">
+        <f>Q32*10</f>
+        <v/>
+      </c>
+      <c r="T32" s="16">
+        <f>S32*20</f>
+        <v/>
+      </c>
+      <c r="V32" s="16">
+        <f>U32*40</f>
+        <v/>
+      </c>
+      <c r="W32" s="4" t="n"/>
+      <c r="X32" s="4" t="n"/>
+      <c r="Z32" s="4" t="n"/>
+      <c r="AB32" s="4" t="n"/>
+      <c r="AE32" s="16">
+        <f>IF(AC32=0,0,AC32*1.7/12*AP32)</f>
+        <v/>
+      </c>
+      <c r="AF32" s="16">
+        <f>IF(AD32=0,0,AD32*1.7/12*AQ32)</f>
+        <v/>
+      </c>
+      <c r="AL32" s="16">
+        <f>(IF((AE32)&lt;(AG32+AH32+AI32),(AE32),(AG32+AH32+AI32)))+AJ32*5+AK32*10+R32+T32+V32</f>
+        <v/>
+      </c>
+      <c r="AM32" s="16">
+        <f>AL32-J32</f>
+        <v/>
+      </c>
+      <c r="AP32" s="16">
+        <f>IF(E32=0,"",(B32*0.95+C32*0.25+D32*0)/E32)</f>
+        <v/>
+      </c>
+      <c r="AQ32" s="16">
+        <f>IF(I32=0,"",(F32*0.95+G32*0.25+H32*0)/I32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="16.25" customHeight="1">
+      <c r="E33" s="16">
+        <f>SUM(B33:D33)</f>
+        <v/>
+      </c>
+      <c r="I33" s="16">
+        <f>SUM(F33:H33)</f>
+        <v/>
+      </c>
+      <c r="J33" s="16">
+        <f>IF(E33=0,0,AP33*1.2/12*E33)</f>
+        <v/>
+      </c>
+      <c r="K33" s="16">
+        <f>IF(I33=0,0,AQ33*1.2/12*I33)</f>
+        <v/>
+      </c>
+      <c r="M33" s="4" t="n"/>
+      <c r="N33" s="4" t="n"/>
+      <c r="P33" s="4" t="n"/>
+      <c r="R33" s="16">
+        <f>Q33*10</f>
+        <v/>
+      </c>
+      <c r="T33" s="16">
+        <f>S33*20</f>
+        <v/>
+      </c>
+      <c r="V33" s="16">
+        <f>U33*40</f>
+        <v/>
+      </c>
+      <c r="W33" s="4" t="n"/>
+      <c r="X33" s="4" t="n"/>
+      <c r="Z33" s="4" t="n"/>
+      <c r="AB33" s="4" t="n"/>
+      <c r="AE33" s="16">
+        <f>IF(AC33=0,0,AC33*1.7/12*AP33)</f>
+        <v/>
+      </c>
+      <c r="AF33" s="16">
+        <f>IF(AD33=0,0,AD33*1.7/12*AQ33)</f>
+        <v/>
+      </c>
+      <c r="AL33" s="16">
+        <f>(IF((AE33)&lt;(AG33+AH33+AI33),(AE33),(AG33+AH33+AI33)))+AJ33*5+AK33*10+R33+T33+V33</f>
+        <v/>
+      </c>
+      <c r="AM33" s="16">
+        <f>AL33-J33</f>
+        <v/>
+      </c>
+      <c r="AP33" s="16">
+        <f>IF(E33=0,"",(B33*0.95+C33*0.25+D33*0)/E33)</f>
+        <v/>
+      </c>
+      <c r="AQ33" s="16">
+        <f>IF(I33=0,"",(F33*0.95+G33*0.25+H33*0)/I33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="16.25" customHeight="1">
+      <c r="E34" s="16">
+        <f>SUM(B34:D34)</f>
+        <v/>
+      </c>
+      <c r="I34" s="16">
+        <f>SUM(F34:H34)</f>
+        <v/>
+      </c>
+      <c r="J34" s="16">
+        <f>IF(E34=0,0,AP34*1.2/12*E34)</f>
+        <v/>
+      </c>
+      <c r="K34" s="16">
+        <f>IF(I34=0,0,AQ34*1.2/12*I34)</f>
+        <v/>
+      </c>
+      <c r="M34" s="4" t="n"/>
+      <c r="N34" s="4" t="n"/>
+      <c r="P34" s="4" t="n"/>
+      <c r="R34" s="16">
+        <f>Q34*10</f>
+        <v/>
+      </c>
+      <c r="T34" s="16">
+        <f>S34*20</f>
+        <v/>
+      </c>
+      <c r="V34" s="16">
+        <f>U34*40</f>
+        <v/>
+      </c>
+      <c r="W34" s="4" t="n"/>
+      <c r="X34" s="4" t="n"/>
+      <c r="Z34" s="4" t="n"/>
+      <c r="AB34" s="4" t="n"/>
+      <c r="AE34" s="16">
+        <f>IF(AC34=0,0,AC34*1.7/12*AP34)</f>
+        <v/>
+      </c>
+      <c r="AF34" s="16">
+        <f>IF(AD34=0,0,AD34*1.7/12*AQ34)</f>
+        <v/>
+      </c>
+      <c r="AL34" s="16">
+        <f>(IF((AE34)&lt;(AG34+AH34+AI34),(AE34),(AG34+AH34+AI34)))+AJ34*5+AK34*10+R34+T34+V34</f>
+        <v/>
+      </c>
+      <c r="AM34" s="16">
+        <f>AL34-J34</f>
+        <v/>
+      </c>
+      <c r="AP34" s="16">
+        <f>IF(E34=0,"",(B34*0.95+C34*0.25+D34*0)/E34)</f>
+        <v/>
+      </c>
+      <c r="AQ34" s="16">
+        <f>IF(I34=0,"",(F34*0.95+G34*0.25+H34*0)/I34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="16.25" customHeight="1">
+      <c r="E35" s="16">
+        <f>SUM(B35:D35)</f>
+        <v/>
+      </c>
+      <c r="I35" s="16">
+        <f>SUM(F35:H35)</f>
+        <v/>
+      </c>
+      <c r="J35" s="16">
+        <f>IF(E35=0,0,AP35*1.2/12*E35)</f>
+        <v/>
+      </c>
+      <c r="K35" s="16">
+        <f>IF(I35=0,0,AQ35*1.2/12*I35)</f>
+        <v/>
+      </c>
+      <c r="M35" s="4" t="n"/>
+      <c r="N35" s="4" t="n"/>
+      <c r="P35" s="4" t="n"/>
+      <c r="R35" s="16">
+        <f>Q35*10</f>
+        <v/>
+      </c>
+      <c r="T35" s="16">
+        <f>S35*20</f>
+        <v/>
+      </c>
+      <c r="V35" s="16">
+        <f>U35*40</f>
+        <v/>
+      </c>
+      <c r="W35" s="4" t="n"/>
+      <c r="X35" s="4" t="n"/>
+      <c r="Z35" s="4" t="n"/>
+      <c r="AB35" s="4" t="n"/>
+      <c r="AE35" s="16">
+        <f>IF(AC35=0,0,AC35*1.7/12*AP35)</f>
+        <v/>
+      </c>
+      <c r="AF35" s="16">
+        <f>IF(AD35=0,0,AD35*1.7/12*AQ35)</f>
+        <v/>
+      </c>
+      <c r="AL35" s="16">
+        <f>(IF((AE35)&lt;(AG35+AH35+AI35),(AE35),(AG35+AH35+AI35)))+AJ35*5+AK35*10+R35+T35+V35</f>
+        <v/>
+      </c>
+      <c r="AM35" s="16">
+        <f>AL35-J35</f>
+        <v/>
+      </c>
+      <c r="AP35" s="16">
+        <f>IF(E35=0,"",(B35*0.95+C35*0.25+D35*0)/E35)</f>
+        <v/>
+      </c>
+      <c r="AQ35" s="16">
+        <f>IF(I35=0,"",(F35*0.95+G35*0.25+H35*0)/I35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="16.25" customHeight="1">
+      <c r="E36" s="16">
+        <f>SUM(B36:D36)</f>
+        <v/>
+      </c>
+      <c r="I36" s="16">
+        <f>SUM(F36:H36)</f>
+        <v/>
+      </c>
+      <c r="J36" s="16">
+        <f>IF(E36=0,0,AP36*1.2/12*E36)</f>
+        <v/>
+      </c>
+      <c r="K36" s="16">
+        <f>IF(I36=0,0,AQ36*1.2/12*I36)</f>
+        <v/>
+      </c>
+      <c r="M36" s="4" t="n"/>
+      <c r="N36" s="4" t="n"/>
+      <c r="P36" s="4" t="n"/>
+      <c r="R36" s="16">
+        <f>Q36*10</f>
+        <v/>
+      </c>
+      <c r="T36" s="16">
+        <f>S36*20</f>
+        <v/>
+      </c>
+      <c r="V36" s="16">
+        <f>U36*40</f>
+        <v/>
+      </c>
+      <c r="W36" s="4" t="n"/>
+      <c r="X36" s="4" t="n"/>
+      <c r="Z36" s="4" t="n"/>
+      <c r="AB36" s="4" t="n"/>
+      <c r="AE36" s="16">
+        <f>IF(AC36=0,0,AC36*1.7/12*AP36)</f>
+        <v/>
+      </c>
+      <c r="AF36" s="16">
+        <f>IF(AD36=0,0,AD36*1.7/12*AQ36)</f>
+        <v/>
+      </c>
+      <c r="AL36" s="16">
+        <f>(IF((AE36)&lt;(AG36+AH36+AI36),(AE36),(AG36+AH36+AI36)))+AJ36*5+AK36*10+R36+T36+V36</f>
+        <v/>
+      </c>
+      <c r="AM36" s="16">
+        <f>AL36-J36</f>
+        <v/>
+      </c>
+      <c r="AP36" s="16">
+        <f>IF(E36=0,"",(B36*0.95+C36*0.25+D36*0)/E36)</f>
+        <v/>
+      </c>
+      <c r="AQ36" s="16">
+        <f>IF(I36=0,"",(F36*0.95+G36*0.25+H36*0)/I36)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="16.25" customHeight="1">
+      <c r="E37" s="16">
+        <f>SUM(B37:D37)</f>
+        <v/>
+      </c>
+      <c r="I37" s="16">
+        <f>SUM(F37:H37)</f>
+        <v/>
+      </c>
+      <c r="J37" s="16">
+        <f>IF(E37=0,0,AP37*1.2/12*E37)</f>
+        <v/>
+      </c>
+      <c r="K37" s="16">
+        <f>IF(I37=0,0,AQ37*1.2/12*I37)</f>
+        <v/>
+      </c>
+      <c r="M37" s="4" t="n"/>
+      <c r="N37" s="4" t="n"/>
+      <c r="P37" s="4" t="n"/>
+      <c r="R37" s="16">
+        <f>Q37*10</f>
+        <v/>
+      </c>
+      <c r="T37" s="16">
+        <f>S37*20</f>
+        <v/>
+      </c>
+      <c r="V37" s="16">
+        <f>U37*40</f>
+        <v/>
+      </c>
+      <c r="W37" s="4" t="n"/>
+      <c r="X37" s="4" t="n"/>
+      <c r="Z37" s="4" t="n"/>
+      <c r="AB37" s="4" t="n"/>
+      <c r="AE37" s="16">
+        <f>IF(AC37=0,0,AC37*1.7/12*AP37)</f>
+        <v/>
+      </c>
+      <c r="AF37" s="16">
+        <f>IF(AD37=0,0,AD37*1.7/12*AQ37)</f>
+        <v/>
+      </c>
+      <c r="AL37" s="16">
+        <f>(IF((AE37)&lt;(AG37+AH37+AI37),(AE37),(AG37+AH37+AI37)))+AJ37*5+AK37*10+R37+T37+V37</f>
+        <v/>
+      </c>
+      <c r="AM37" s="16">
+        <f>AL37-J37</f>
+        <v/>
+      </c>
+      <c r="AP37" s="16">
+        <f>IF(E37=0,"",(B37*0.95+C37*0.25+D37*0)/E37)</f>
+        <v/>
+      </c>
+      <c r="AQ37" s="16">
+        <f>IF(I37=0,"",(F37*0.95+G37*0.25+H37*0)/I37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="16.25" customHeight="1">
+      <c r="E38" s="16">
+        <f>SUM(B38:D38)</f>
+        <v/>
+      </c>
+      <c r="I38" s="16">
+        <f>SUM(F38:H38)</f>
+        <v/>
+      </c>
+      <c r="J38" s="16">
+        <f>IF(E38=0,0,AP38*1.2/12*E38)</f>
+        <v/>
+      </c>
+      <c r="K38" s="16">
+        <f>IF(I38=0,0,AQ38*1.2/12*I38)</f>
+        <v/>
+      </c>
+      <c r="M38" s="4" t="n"/>
+      <c r="N38" s="4" t="n"/>
+      <c r="P38" s="4" t="n"/>
+      <c r="R38" s="16">
+        <f>Q38*10</f>
+        <v/>
+      </c>
+      <c r="T38" s="16">
+        <f>S38*20</f>
+        <v/>
+      </c>
+      <c r="V38" s="16">
+        <f>U38*40</f>
+        <v/>
+      </c>
+      <c r="W38" s="4" t="n"/>
+      <c r="X38" s="4" t="n"/>
+      <c r="Z38" s="4" t="n"/>
+      <c r="AB38" s="4" t="n"/>
+      <c r="AE38" s="16">
+        <f>IF(AC38=0,0,AC38*1.7/12*AP38)</f>
+        <v/>
+      </c>
+      <c r="AF38" s="16">
+        <f>IF(AD38=0,0,AD38*1.7/12*AQ38)</f>
+        <v/>
+      </c>
+      <c r="AL38" s="16">
+        <f>(IF((AE38)&lt;(AG38+AH38+AI38),(AE38),(AG38+AH38+AI38)))+AJ38*5+AK38*10+R38+T38+V38</f>
+        <v/>
+      </c>
+      <c r="AM38" s="16">
+        <f>AL38-J38</f>
+        <v/>
+      </c>
+      <c r="AP38" s="16">
+        <f>IF(E38=0,"",(B38*0.95+C38*0.25+D38*0)/E38)</f>
+        <v/>
+      </c>
+      <c r="AQ38" s="16">
+        <f>IF(I38=0,"",(F38*0.95+G38*0.25+H38*0)/I38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="16.25" customHeight="1">
+      <c r="E39" s="16">
+        <f>SUM(B39:D39)</f>
+        <v/>
+      </c>
+      <c r="I39" s="16">
+        <f>SUM(F39:H39)</f>
+        <v/>
+      </c>
+      <c r="J39" s="16">
+        <f>IF(E39=0,0,AP39*1.2/12*E39)</f>
+        <v/>
+      </c>
+      <c r="K39" s="16">
+        <f>IF(I39=0,0,AQ39*1.2/12*I39)</f>
+        <v/>
+      </c>
+      <c r="M39" s="4" t="n"/>
+      <c r="N39" s="4" t="n"/>
+      <c r="P39" s="4" t="n"/>
+      <c r="R39" s="16">
+        <f>Q39*10</f>
+        <v/>
+      </c>
+      <c r="T39" s="16">
+        <f>S39*20</f>
+        <v/>
+      </c>
+      <c r="V39" s="16">
+        <f>U39*40</f>
+        <v/>
+      </c>
+      <c r="W39" s="4" t="n"/>
+      <c r="X39" s="4" t="n"/>
+      <c r="Z39" s="4" t="n"/>
+      <c r="AB39" s="4" t="n"/>
+      <c r="AE39" s="16">
+        <f>IF(AC39=0,0,AC39*1.7/12*AP39)</f>
+        <v/>
+      </c>
+      <c r="AF39" s="16">
+        <f>IF(AD39=0,0,AD39*1.7/12*AQ39)</f>
+        <v/>
+      </c>
+      <c r="AL39" s="16">
+        <f>(IF((AE39)&lt;(AG39+AH39+AI39),(AE39),(AG39+AH39+AI39)))+AJ39*5+AK39*10+R39+T39+V39</f>
+        <v/>
+      </c>
+      <c r="AM39" s="16">
+        <f>AL39-J39</f>
+        <v/>
+      </c>
+      <c r="AP39" s="16">
+        <f>IF(E39=0,"",(B39*0.95+C39*0.25+D39*0)/E39)</f>
+        <v/>
+      </c>
+      <c r="AQ39" s="16">
+        <f>IF(I39=0,"",(F39*0.95+G39*0.25+H39*0)/I39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="16.25" customHeight="1">
+      <c r="E40" s="16">
+        <f>SUM(B40:D40)</f>
+        <v/>
+      </c>
+      <c r="I40" s="16">
+        <f>SUM(F40:H40)</f>
+        <v/>
+      </c>
+      <c r="J40" s="16">
+        <f>IF(E40=0,0,AP40*1.2/12*E40)</f>
+        <v/>
+      </c>
+      <c r="K40" s="16">
+        <f>IF(I40=0,0,AQ40*1.2/12*I40)</f>
+        <v/>
+      </c>
+      <c r="M40" s="4" t="n"/>
+      <c r="N40" s="4" t="n"/>
+      <c r="P40" s="4" t="n"/>
+      <c r="R40" s="16">
+        <f>Q40*10</f>
+        <v/>
+      </c>
+      <c r="T40" s="16">
+        <f>S40*20</f>
+        <v/>
+      </c>
+      <c r="V40" s="16">
+        <f>U40*40</f>
+        <v/>
+      </c>
+      <c r="W40" s="4" t="n"/>
+      <c r="X40" s="4" t="n"/>
+      <c r="Z40" s="4" t="n"/>
+      <c r="AB40" s="4" t="n"/>
+      <c r="AE40" s="16">
+        <f>IF(AC40=0,0,AC40*1.7/12*AP40)</f>
+        <v/>
+      </c>
+      <c r="AF40" s="16">
+        <f>IF(AD40=0,0,AD40*1.7/12*AQ40)</f>
+        <v/>
+      </c>
+      <c r="AL40" s="16">
+        <f>(IF((AE40)&lt;(AG40+AH40+AI40),(AE40),(AG40+AH40+AI40)))+AJ40*5+AK40*10+R40+T40+V40</f>
+        <v/>
+      </c>
+      <c r="AM40" s="16">
+        <f>AL40-J40</f>
+        <v/>
+      </c>
+      <c r="AP40" s="16">
+        <f>IF(E40=0,"",(B40*0.95+C40*0.25+D40*0)/E40)</f>
+        <v/>
+      </c>
+      <c r="AQ40" s="16">
+        <f>IF(I40=0,"",(F40*0.95+G40*0.25+H40*0)/I40)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="16.25" customHeight="1">
+      <c r="E41" s="16">
+        <f>SUM(B41:D41)</f>
+        <v/>
+      </c>
+      <c r="I41" s="16">
+        <f>SUM(F41:H41)</f>
+        <v/>
+      </c>
+      <c r="J41" s="16">
+        <f>IF(E41=0,0,AP41*1.2/12*E41)</f>
+        <v/>
+      </c>
+      <c r="K41" s="16">
+        <f>IF(I41=0,0,AQ41*1.2/12*I41)</f>
+        <v/>
+      </c>
+      <c r="M41" s="4" t="n"/>
+      <c r="N41" s="4" t="n"/>
+      <c r="P41" s="4" t="n"/>
+      <c r="R41" s="16">
+        <f>Q41*10</f>
+        <v/>
+      </c>
+      <c r="T41" s="16">
+        <f>S41*20</f>
+        <v/>
+      </c>
+      <c r="V41" s="16">
+        <f>U41*40</f>
+        <v/>
+      </c>
+      <c r="W41" s="4" t="n"/>
+      <c r="X41" s="4" t="n"/>
+      <c r="Z41" s="4" t="n"/>
+      <c r="AB41" s="4" t="n"/>
+      <c r="AE41" s="16">
+        <f>IF(AC41=0,0,AC41*1.7/12*AP41)</f>
+        <v/>
+      </c>
+      <c r="AF41" s="16">
+        <f>IF(AD41=0,0,AD41*1.7/12*AQ41)</f>
+        <v/>
+      </c>
+      <c r="AL41" s="16">
+        <f>(IF((AE41)&lt;(AG41+AH41+AI41),(AE41),(AG41+AH41+AI41)))+AJ41*5+AK41*10+R41+T41+V41</f>
+        <v/>
+      </c>
+      <c r="AM41" s="16">
+        <f>AL41-J41</f>
+        <v/>
+      </c>
+      <c r="AP41" s="16">
+        <f>IF(E41=0,"",(B41*0.95+C41*0.25+D41*0)/E41)</f>
+        <v/>
+      </c>
+      <c r="AQ41" s="16">
+        <f>IF(I41=0,"",(F41*0.95+G41*0.25+H41*0)/I41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="16.25" customHeight="1">
+      <c r="E42" s="16">
+        <f>SUM(B42:D42)</f>
+        <v/>
+      </c>
+      <c r="I42" s="16">
+        <f>SUM(F42:H42)</f>
+        <v/>
+      </c>
+      <c r="J42" s="16">
+        <f>IF(E42=0,0,AP42*1.2/12*E42)</f>
+        <v/>
+      </c>
+      <c r="K42" s="16">
+        <f>IF(I42=0,0,AQ42*1.2/12*I42)</f>
+        <v/>
+      </c>
+      <c r="M42" s="4" t="n"/>
+      <c r="N42" s="4" t="n"/>
+      <c r="P42" s="4" t="n"/>
+      <c r="R42" s="16">
+        <f>Q42*10</f>
+        <v/>
+      </c>
+      <c r="T42" s="16">
+        <f>S42*20</f>
+        <v/>
+      </c>
+      <c r="V42" s="16">
+        <f>U42*40</f>
+        <v/>
+      </c>
+      <c r="W42" s="4" t="n"/>
+      <c r="X42" s="4" t="n"/>
+      <c r="Z42" s="4" t="n"/>
+      <c r="AB42" s="4" t="n"/>
+      <c r="AE42" s="16">
+        <f>IF(AC42=0,0,AC42*1.7/12*AP42)</f>
+        <v/>
+      </c>
+      <c r="AF42" s="16">
+        <f>IF(AD42=0,0,AD42*1.7/12*AQ42)</f>
+        <v/>
+      </c>
+      <c r="AL42" s="16">
+        <f>(IF((AE42)&lt;(AG42+AH42+AI42),(AE42),(AG42+AH42+AI42)))+AJ42*5+AK42*10+R42+T42+V42</f>
+        <v/>
+      </c>
+      <c r="AM42" s="16">
+        <f>AL42-J42</f>
+        <v/>
+      </c>
+      <c r="AP42" s="16">
+        <f>IF(E42=0,"",(B42*0.95+C42*0.25+D42*0)/E42)</f>
+        <v/>
+      </c>
+      <c r="AQ42" s="16">
+        <f>IF(I42=0,"",(F42*0.95+G42*0.25+H42*0)/I42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="16.25" customHeight="1">
+      <c r="E43" s="16">
+        <f>SUM(B43:D43)</f>
+        <v/>
+      </c>
+      <c r="I43" s="16">
+        <f>SUM(F43:H43)</f>
+        <v/>
+      </c>
+      <c r="J43" s="16">
+        <f>IF(E43=0,0,AP43*1.2/12*E43)</f>
+        <v/>
+      </c>
+      <c r="K43" s="16">
+        <f>IF(I43=0,0,AQ43*1.2/12*I43)</f>
+        <v/>
+      </c>
+      <c r="M43" s="4" t="n"/>
+      <c r="N43" s="4" t="n"/>
+      <c r="P43" s="4" t="n"/>
+      <c r="R43" s="16">
+        <f>Q43*10</f>
+        <v/>
+      </c>
+      <c r="T43" s="16">
+        <f>S43*20</f>
+        <v/>
+      </c>
+      <c r="V43" s="16">
+        <f>U43*40</f>
+        <v/>
+      </c>
+      <c r="W43" s="4" t="n"/>
+      <c r="X43" s="4" t="n"/>
+      <c r="Z43" s="4" t="n"/>
+      <c r="AB43" s="4" t="n"/>
+      <c r="AE43" s="16">
+        <f>IF(AC43=0,0,AC43*1.7/12*AP43)</f>
+        <v/>
+      </c>
+      <c r="AF43" s="16">
+        <f>IF(AD43=0,0,AD43*1.7/12*AQ43)</f>
+        <v/>
+      </c>
+      <c r="AL43" s="16">
+        <f>(IF((AE43)&lt;(AG43+AH43+AI43),(AE43),(AG43+AH43+AI43)))+AJ43*5+AK43*10+R43+T43+V43</f>
+        <v/>
+      </c>
+      <c r="AM43" s="16">
+        <f>AL43-J43</f>
+        <v/>
+      </c>
+      <c r="AP43" s="16">
+        <f>IF(E43=0,"",(B43*0.95+C43*0.25+D43*0)/E43)</f>
+        <v/>
+      </c>
+      <c r="AQ43" s="16">
+        <f>IF(I43=0,"",(F43*0.95+G43*0.25+H43*0)/I43)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="16.25" customHeight="1">
+      <c r="E44" s="16">
+        <f>SUM(B44:D44)</f>
+        <v/>
+      </c>
+      <c r="I44" s="16">
+        <f>SUM(F44:H44)</f>
+        <v/>
+      </c>
+      <c r="J44" s="16">
+        <f>IF(E44=0,0,AP44*1.2/12*E44)</f>
+        <v/>
+      </c>
+      <c r="K44" s="16">
+        <f>IF(I44=0,0,AQ44*1.2/12*I44)</f>
+        <v/>
+      </c>
+      <c r="M44" s="4" t="n"/>
+      <c r="N44" s="4" t="n"/>
+      <c r="P44" s="4" t="n"/>
+      <c r="R44" s="16">
+        <f>Q44*10</f>
+        <v/>
+      </c>
+      <c r="T44" s="16">
+        <f>S44*20</f>
+        <v/>
+      </c>
+      <c r="V44" s="16">
+        <f>U44*40</f>
+        <v/>
+      </c>
+      <c r="W44" s="4" t="n"/>
+      <c r="X44" s="4" t="n"/>
+      <c r="Z44" s="4" t="n"/>
+      <c r="AB44" s="4" t="n"/>
+      <c r="AE44" s="16">
+        <f>IF(AC44=0,0,AC44*1.7/12*AP44)</f>
+        <v/>
+      </c>
+      <c r="AF44" s="16">
+        <f>IF(AD44=0,0,AD44*1.7/12*AQ44)</f>
+        <v/>
+      </c>
+      <c r="AL44" s="16">
+        <f>(IF((AE44)&lt;(AG44+AH44+AI44),(AE44),(AG44+AH44+AI44)))+AJ44*5+AK44*10+R44+T44+V44</f>
+        <v/>
+      </c>
+      <c r="AM44" s="16">
+        <f>AL44-J44</f>
+        <v/>
+      </c>
+      <c r="AP44" s="16">
+        <f>IF(E44=0,"",(B44*0.95+C44*0.25+D44*0)/E44)</f>
+        <v/>
+      </c>
+      <c r="AQ44" s="16">
+        <f>IF(I44=0,"",(F44*0.95+G44*0.25+H44*0)/I44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="16.25" customHeight="1">
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>DATOTAL</t>
+        </is>
+      </c>
+      <c r="E45" s="19">
+        <f>SUM(E12:E44)</f>
+        <v/>
+      </c>
+      <c r="I45" s="19">
+        <f>SUM(I12:I44)</f>
+        <v/>
+      </c>
+      <c r="J45" s="19">
+        <f>SUM(J12:J44)</f>
+        <v/>
+      </c>
+      <c r="K45" s="19">
+        <f>SUM(K12:K44)</f>
+        <v/>
+      </c>
+      <c r="Q45" s="19">
+        <f>SUM(Q12:Q44)</f>
+        <v/>
+      </c>
+      <c r="R45" s="19">
+        <f>SUM(R12:R44)</f>
+        <v/>
+      </c>
+      <c r="S45" s="19">
+        <f>SUM(S12:S44)</f>
+        <v/>
+      </c>
+      <c r="T45" s="19">
+        <f>SUM(T12:T44)</f>
+        <v/>
+      </c>
+      <c r="U45" s="19">
+        <f>SUM(U12:U44)</f>
+        <v/>
+      </c>
+      <c r="V45" s="19">
+        <f>SUM(V12:V44)</f>
+        <v/>
+      </c>
+      <c r="AL45" s="19">
+        <f>SUM(AL12:AL44)</f>
+        <v/>
+      </c>
+      <c r="AM45" s="19">
+        <f>SUM(AM12:AM44)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="61">
-    <mergeCell ref="A159:G159"/>
-    <mergeCell ref="A126:G126"/>
-    <mergeCell ref="A253:G253"/>
-    <mergeCell ref="A22:G22"/>
-    <mergeCell ref="A109:G109"/>
-    <mergeCell ref="A324:G324"/>
-    <mergeCell ref="A62:G62"/>
-    <mergeCell ref="A100:G100"/>
-    <mergeCell ref="A209:G209"/>
-    <mergeCell ref="A29:G29"/>
-    <mergeCell ref="A161:G161"/>
-    <mergeCell ref="A43:G43"/>
-    <mergeCell ref="A199:G199"/>
-    <mergeCell ref="A265:G265"/>
-    <mergeCell ref="A274:G274"/>
-    <mergeCell ref="A121:G121"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A293:G293"/>
-    <mergeCell ref="A93:G93"/>
-    <mergeCell ref="A308:G308"/>
-    <mergeCell ref="A44:G44"/>
-    <mergeCell ref="A220:G220"/>
-    <mergeCell ref="A258:G258"/>
-    <mergeCell ref="A67:G67"/>
-    <mergeCell ref="A143:G143"/>
-    <mergeCell ref="A176:G176"/>
-    <mergeCell ref="A77:G77"/>
-    <mergeCell ref="A34:G34"/>
-    <mergeCell ref="A319:G319"/>
-    <mergeCell ref="A232:G232"/>
-    <mergeCell ref="A166:G166"/>
-    <mergeCell ref="A260:G260"/>
-    <mergeCell ref="A60:G60"/>
-    <mergeCell ref="A142:G142"/>
-    <mergeCell ref="A275:G275"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A291:G291"/>
-    <mergeCell ref="A225:G225"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A88:G88"/>
-    <mergeCell ref="A110:G110"/>
-    <mergeCell ref="A241:G241"/>
-    <mergeCell ref="A307:G307"/>
-    <mergeCell ref="A187:G187"/>
-    <mergeCell ref="A227:G227"/>
-    <mergeCell ref="A128:G128"/>
-    <mergeCell ref="A133:G133"/>
-    <mergeCell ref="A208:G208"/>
-    <mergeCell ref="A286:G286"/>
-    <mergeCell ref="A326:G326"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A154:G154"/>
-    <mergeCell ref="A192:G192"/>
-    <mergeCell ref="A55:G55"/>
-    <mergeCell ref="A95:G95"/>
-    <mergeCell ref="A331:G331"/>
-    <mergeCell ref="A175:G175"/>
-    <mergeCell ref="A76:G76"/>
-    <mergeCell ref="A242:G242"/>
-    <mergeCell ref="A298:G298"/>
-    <mergeCell ref="A194:G194"/>
+  <mergeCells count="27">
+    <mergeCell ref="P9:P10"/>
+    <mergeCell ref="AG9:AG10"/>
+    <mergeCell ref="AI9:AI10"/>
+    <mergeCell ref="AK9:AK10"/>
+    <mergeCell ref="AM9:AM10"/>
+    <mergeCell ref="Y9:Z9"/>
+    <mergeCell ref="AP9:AQ9"/>
+    <mergeCell ref="AA9:AB9"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="AH9:AH10"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="N9:N10"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="Q9:V10"/>
+    <mergeCell ref="W9:X9"/>
+    <mergeCell ref="Y1:AB1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="B9:I9"/>
+    <mergeCell ref="AE9:AF9"/>
+    <mergeCell ref="AC9:AD9"/>
+    <mergeCell ref="AF1:AG1"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="M9:M10"/>
+    <mergeCell ref="AJ9:AJ10"/>
+    <mergeCell ref="O9:O10"/>
+    <mergeCell ref="AL9:AL10"/>
   </mergeCells>
-  <dataValidations count="30">
-    <dataValidation sqref="B24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B90" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B91" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B94" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B123" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B124" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B127" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B156" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B157" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B160" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B189" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B190" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B193" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B222" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B223" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B226" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B255" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B256" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B259" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B288" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B289" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B292" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B321" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B322" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B325" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17871,17 +17249,17 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="18" t="inlineStr">
+      <c r="A1" s="20" t="inlineStr">
         <is>
           <t>EISA Section 438 — Direct Determination (Horton infiltration)</t>
         </is>
       </c>
-      <c r="B1" s="19" t="n"/>
-      <c r="C1" s="19" t="n"/>
-      <c r="D1" s="19" t="n"/>
-      <c r="E1" s="19" t="n"/>
-      <c r="F1" s="19" t="n"/>
-      <c r="G1" s="20" t="n"/>
+      <c r="B1" s="21" t="n"/>
+      <c r="C1" s="21" t="n"/>
+      <c r="D1" s="21" t="n"/>
+      <c r="E1" s="21" t="n"/>
+      <c r="F1" s="21" t="n"/>
+      <c r="G1" s="22" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
@@ -18031,37 +17409,37 @@
       <c r="G15" s="8" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>Surface</t>
         </is>
       </c>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>HSG</t>
         </is>
       </c>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="C16" s="18" t="inlineStr">
         <is>
           <t>Area (SF)</t>
         </is>
       </c>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="D16" s="18" t="inlineStr">
         <is>
           <t>Runoff HSG B (in)</t>
         </is>
       </c>
-      <c r="E16" s="17" t="inlineStr">
+      <c r="E16" s="18" t="inlineStr">
         <is>
           <t>Runoff HSG C (in)</t>
         </is>
       </c>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="F16" s="18" t="inlineStr">
         <is>
           <t>Vol HSG B (CF)</t>
         </is>
       </c>
-      <c r="G16" s="17" t="inlineStr">
+      <c r="G16" s="18" t="inlineStr">
         <is>
           <t>Vol HSG C (CF)</t>
         </is>
@@ -18452,37 +17830,37 @@
       <c r="G30" s="8" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="17" t="inlineStr">
+      <c r="A31" s="18" t="inlineStr">
         <is>
           <t>Surface</t>
         </is>
       </c>
-      <c r="B31" s="17" t="inlineStr">
+      <c r="B31" s="18" t="inlineStr">
         <is>
           <t>HSG</t>
         </is>
       </c>
-      <c r="C31" s="17" t="inlineStr">
+      <c r="C31" s="18" t="inlineStr">
         <is>
           <t>Area (SF)</t>
         </is>
       </c>
-      <c r="D31" s="17" t="inlineStr">
+      <c r="D31" s="18" t="inlineStr">
         <is>
           <t>Runoff HSG B (in)</t>
         </is>
       </c>
-      <c r="E31" s="17" t="inlineStr">
+      <c r="E31" s="18" t="inlineStr">
         <is>
           <t>Runoff HSG C (in)</t>
         </is>
       </c>
-      <c r="F31" s="17" t="inlineStr">
+      <c r="F31" s="18" t="inlineStr">
         <is>
           <t>Vol HSG B (CF)</t>
         </is>
       </c>
-      <c r="G31" s="17" t="inlineStr">
+      <c r="G31" s="18" t="inlineStr">
         <is>
           <t>Vol HSG C (CF)</t>
         </is>
@@ -18860,26 +18238,26 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="18" t="inlineStr">
+      <c r="A45" s="20" t="inlineStr">
         <is>
           <t>Compliance Check</t>
         </is>
       </c>
-      <c r="B45" s="19" t="n"/>
-      <c r="C45" s="20" t="n"/>
+      <c r="B45" s="21" t="n"/>
+      <c r="C45" s="22" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="21" t="inlineStr">
+      <c r="A46" s="23" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B46" s="21" t="inlineStr">
+      <c r="B46" s="23" t="inlineStr">
         <is>
           <t>HSG B</t>
         </is>
       </c>
-      <c r="C46" s="21" t="inlineStr">
+      <c r="C46" s="23" t="inlineStr">
         <is>
           <t>HSG C</t>
         </is>
@@ -18993,16 +18371,16 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="18" t="inlineStr">
+      <c r="A1" s="20" t="inlineStr">
         <is>
           <t>EISA Section 438 — TR-55 CN Method (Method A primary)</t>
         </is>
       </c>
-      <c r="B1" s="19" t="n"/>
-      <c r="C1" s="19" t="n"/>
-      <c r="D1" s="19" t="n"/>
-      <c r="E1" s="19" t="n"/>
-      <c r="F1" s="20" t="n"/>
+      <c r="B1" s="21" t="n"/>
+      <c r="C1" s="21" t="n"/>
+      <c r="D1" s="21" t="n"/>
+      <c r="E1" s="21" t="n"/>
+      <c r="F1" s="22" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
@@ -19062,32 +18440,32 @@
       <c r="F8" s="13" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="inlineStr">
+      <c r="A9" s="23" t="inlineStr">
         <is>
           <t>Surface</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>HSG</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t>Area (SF)</t>
         </is>
       </c>
-      <c r="E9" s="21" t="inlineStr">
+      <c r="E9" s="23" t="inlineStr">
         <is>
           <t>Q (in)</t>
         </is>
       </c>
-      <c r="F9" s="21" t="inlineStr">
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t>Vol (CF)</t>
         </is>
@@ -19427,32 +18805,32 @@
       <c r="F23" s="13" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="21" t="inlineStr">
+      <c r="A24" s="23" t="inlineStr">
         <is>
           <t>Surface</t>
         </is>
       </c>
-      <c r="B24" s="21" t="inlineStr">
+      <c r="B24" s="23" t="inlineStr">
         <is>
           <t>HSG</t>
         </is>
       </c>
-      <c r="C24" s="21" t="inlineStr">
+      <c r="C24" s="23" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="D24" s="21" t="inlineStr">
+      <c r="D24" s="23" t="inlineStr">
         <is>
           <t>Area (SF)</t>
         </is>
       </c>
-      <c r="E24" s="21" t="inlineStr">
+      <c r="E24" s="23" t="inlineStr">
         <is>
           <t>Q (in)</t>
         </is>
       </c>
-      <c r="F24" s="21" t="inlineStr">
+      <c r="F24" s="23" t="inlineStr">
         <is>
           <t>Vol (CF)</t>
         </is>
@@ -19780,12 +19158,12 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="inlineStr">
+      <c r="A38" s="20" t="inlineStr">
         <is>
           <t>Compliance Check (Method A)</t>
         </is>
       </c>
-      <c r="B38" s="20" t="n"/>
+      <c r="B38" s="22" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">

--- a/SW_Required_Provided_DOEE_EISA438.xlsx
+++ b/SW_Required_Provided_DOEE_EISA438.xlsx
@@ -40,6 +40,7 @@
     <definedName name="PARAMS_DetentionCN">'PARAMS'!$A$61:$B$64</definedName>
     <definedName name="PARAMS_HortonLossB">'PARAMS'!$B$26</definedName>
     <definedName name="PARAMS_HortonLossC">'PARAMS'!$C$26</definedName>
+    <definedName name="PARAMS_Ksat">'PARAMS'!$A$68:$B$71</definedName>
     <definedName name="SDA_IDs">'SDA'!$A$58:$A$67</definedName>
     <definedName name="CDA_IDs">'CDA'!$A$58:$A$67</definedName>
   </definedNames>
@@ -73,7 +74,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -127,11 +128,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00375623"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -197,11 +203,45 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="medium">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00000000"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -239,6 +279,22 @@
     <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -248,11 +304,11 @@
     <xf numFmtId="0" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3683,7 +3739,7 @@
         <f>SUMIFS('BMP'!$AM$4:$AM$53,'BMP'!$B$4:$B$53,A4)</f>
         <v/>
       </c>
-      <c r="D4" s="24">
+      <c r="D4" s="32">
         <f>IFERROR(C4/B4,0)</f>
         <v/>
       </c>
@@ -3709,7 +3765,7 @@
         <f>SUMIFS('BMP'!$AM$4:$AM$53,'BMP'!$B$4:$B$53,A5)</f>
         <v/>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="32">
         <f>IFERROR(C5/B5,0)</f>
         <v/>
       </c>
@@ -3735,7 +3791,7 @@
         <f>SUMIFS('BMP'!$AM$4:$AM$53,'BMP'!$B$4:$B$53,A6)</f>
         <v/>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="32">
         <f>IFERROR(C6/B6,0)</f>
         <v/>
       </c>
@@ -3761,7 +3817,7 @@
         <f>SUMIFS('BMP'!$AM$4:$AM$53,'BMP'!$B$4:$B$53,A7)</f>
         <v/>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="32">
         <f>IFERROR(C7/B7,0)</f>
         <v/>
       </c>
@@ -3787,7 +3843,7 @@
         <f>SUMIFS('BMP'!$AM$4:$AM$53,'BMP'!$B$4:$B$53,A8)</f>
         <v/>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="32">
         <f>IFERROR(C8/B8,0)</f>
         <v/>
       </c>
@@ -3813,7 +3869,7 @@
         <f>SUMIFS('BMP'!$AM$4:$AM$53,'BMP'!$B$4:$B$53,A9)</f>
         <v/>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="32">
         <f>IFERROR(C9/B9,0)</f>
         <v/>
       </c>
@@ -3839,7 +3895,7 @@
         <f>SUMIFS('BMP'!$AM$4:$AM$53,'BMP'!$B$4:$B$53,A10)</f>
         <v/>
       </c>
-      <c r="D10" s="24">
+      <c r="D10" s="32">
         <f>IFERROR(C10/B10,0)</f>
         <v/>
       </c>
@@ -3865,7 +3921,7 @@
         <f>SUMIFS('BMP'!$AM$4:$AM$53,'BMP'!$B$4:$B$53,A11)</f>
         <v/>
       </c>
-      <c r="D11" s="24">
+      <c r="D11" s="32">
         <f>IFERROR(C11/B11,0)</f>
         <v/>
       </c>
@@ -3891,7 +3947,7 @@
         <f>SUMIFS('BMP'!$AM$4:$AM$53,'BMP'!$B$4:$B$53,A12)</f>
         <v/>
       </c>
-      <c r="D12" s="24">
+      <c r="D12" s="32">
         <f>IFERROR(C12/B12,0)</f>
         <v/>
       </c>
@@ -3917,7 +3973,7 @@
         <f>SUMIFS('BMP'!$AM$4:$AM$53,'BMP'!$B$4:$B$53,A13)</f>
         <v/>
       </c>
-      <c r="D13" s="24">
+      <c r="D13" s="32">
         <f>IFERROR(C13/B13,0)</f>
         <v/>
       </c>
@@ -3944,7 +4000,7 @@
         <f>SUM(C4:C13)</f>
         <v/>
       </c>
-      <c r="D15" s="24">
+      <c r="D15" s="32">
         <f>IFERROR(C15/B15,0)</f>
         <v/>
       </c>
@@ -3967,7 +4023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -4836,9 +4892,75 @@
         <v>98</v>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>Default Ksat by HSG (ft/day)</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="n"/>
+      <c r="C66" s="7" t="n"/>
+      <c r="D66" s="7" t="n"/>
+      <c r="E66" s="7" t="n"/>
+      <c r="F66" s="7" t="n"/>
+      <c r="G66" s="8" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="9" t="inlineStr">
+        <is>
+          <t>HSG</t>
+        </is>
+      </c>
+      <c r="B67" s="9" t="inlineStr">
+        <is>
+          <t>Ksat (ft/day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B68" s="10" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B69" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B70" s="10" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B71" s="10" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A66:G66"/>
     <mergeCell ref="A44:G44"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A53:G53"/>
@@ -8615,6 +8737,51 @@
       <c r="AL1" s="5" t="n"/>
       <c r="AM1" s="2" t="n"/>
     </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>Ksat auto-populates from PARAMS_Ksat (by CDA dominant HSG) only for Enhanced sub-types. Standard/lined BMPs show 0 (no native-soil infiltration). Override with a site-measured value if testing is available.</t>
+        </is>
+      </c>
+      <c r="B2" s="18" t="n"/>
+      <c r="C2" s="18" t="n"/>
+      <c r="D2" s="18" t="n"/>
+      <c r="E2" s="18" t="n"/>
+      <c r="F2" s="18" t="n"/>
+      <c r="G2" s="18" t="n"/>
+      <c r="H2" s="18" t="n"/>
+      <c r="I2" s="18" t="n"/>
+      <c r="J2" s="18" t="n"/>
+      <c r="K2" s="18" t="n"/>
+      <c r="L2" s="18" t="n"/>
+      <c r="M2" s="18" t="n"/>
+      <c r="N2" s="18" t="n"/>
+      <c r="O2" s="18" t="n"/>
+      <c r="P2" s="18" t="n"/>
+      <c r="Q2" s="18" t="n"/>
+      <c r="R2" s="18" t="n"/>
+      <c r="S2" s="18" t="n"/>
+      <c r="T2" s="18" t="n"/>
+      <c r="U2" s="18" t="n"/>
+      <c r="V2" s="18" t="n"/>
+      <c r="W2" s="18" t="n"/>
+      <c r="X2" s="18" t="n"/>
+      <c r="Y2" s="18" t="n"/>
+      <c r="Z2" s="18" t="n"/>
+      <c r="AA2" s="18" t="n"/>
+      <c r="AB2" s="18" t="n"/>
+      <c r="AC2" s="18" t="n"/>
+      <c r="AD2" s="18" t="n"/>
+      <c r="AE2" s="18" t="n"/>
+      <c r="AF2" s="18" t="n"/>
+      <c r="AG2" s="18" t="n"/>
+      <c r="AH2" s="18" t="n"/>
+      <c r="AI2" s="18" t="n"/>
+      <c r="AJ2" s="18" t="n"/>
+      <c r="AK2" s="18" t="n"/>
+      <c r="AL2" s="18" t="n"/>
+      <c r="AM2" s="19" t="n"/>
+    </row>
     <row r="3" ht="48" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -8636,7 +8803,7 @@
           <t>BMP Type</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="20" t="inlineStr">
         <is>
           <t>Sub-Type</t>
         </is>
@@ -8676,7 +8843,7 @@
           <t>PP Drawdown (days)</t>
         </is>
       </c>
-      <c r="M3" s="6" t="inlineStr">
+      <c r="M3" s="20" t="inlineStr">
         <is>
           <t>PP Drawdown ≤ 2?</t>
         </is>
@@ -8731,7 +8898,7 @@
           <t>Bio Sv (CF)</t>
         </is>
       </c>
-      <c r="X3" s="6" t="inlineStr">
+      <c r="X3" s="20" t="inlineStr">
         <is>
           <t>Bio Drawdown (days)</t>
         </is>
@@ -8746,7 +8913,7 @@
           <t>WS ED Vol (CF)</t>
         </is>
       </c>
-      <c r="AA3" s="6" t="inlineStr">
+      <c r="AA3" s="20" t="inlineStr">
         <is>
           <t>WS Sv (CF)</t>
         </is>
@@ -8781,7 +8948,7 @@
           <t># Preserved Heritage</t>
         </is>
       </c>
-      <c r="AH3" s="6" t="inlineStr">
+      <c r="AH3" s="20" t="inlineStr">
         <is>
           <t>Tree Rv Total (CF)</t>
         </is>
@@ -8806,7 +8973,7 @@
           <t>Max BMP Credit (CF)</t>
         </is>
       </c>
-      <c r="AM3" s="6" t="inlineStr">
+      <c r="AM3" s="20" t="inlineStr">
         <is>
           <t>Rv Applied (CF)</t>
         </is>
@@ -8817,11 +8984,14 @@
       <c r="B4" s="4" t="n"/>
       <c r="C4" s="4" t="n"/>
       <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="n"/>
+      <c r="E4" s="21" t="n"/>
       <c r="F4" s="4" t="n"/>
       <c r="G4" s="4" t="n"/>
       <c r="H4" s="4" t="n"/>
-      <c r="I4" s="4" t="n"/>
+      <c r="I4" s="4">
+        <f>IFERROR(IF(OR(E4="Enhanced",E4="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C4,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C4,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C4,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C4,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="J4" s="16">
         <f>IFERROR(IFS(AND(D4="Permeable Pavement",E4="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D4="Permeable Pavement",E4="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D4="Bioretention",E4="Standard"),INDEX(PARAMS_BMP,3,5),AND(D4="Bioretention",E4="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D4="Bioretention",E4="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D4="Dry Swale",E4="—"),INDEX(PARAMS_BMP,6,5),AND(D4="Wet Swale",E4="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
         <v/>
@@ -8834,7 +9004,7 @@
         <f>IFERROR(IF(I4=0,"",G4/I4),"")</f>
         <v/>
       </c>
-      <c r="M4" s="16">
+      <c r="M4" s="22">
         <f>IFERROR(IF(L4="","",IF(L4&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
@@ -8855,18 +9025,21 @@
         <v/>
       </c>
       <c r="U4" s="4" t="n"/>
-      <c r="V4" s="4" t="n"/>
+      <c r="V4" s="4">
+        <f>IFERROR(IF(OR(E4="Enhanced",E4="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C4,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C4,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C4,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C4,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="W4" s="16">
         <f>IFERROR(P4*(Q4*R4+S4*T4+U4),0)</f>
         <v/>
       </c>
-      <c r="X4" s="16">
+      <c r="X4" s="22">
         <f>IFERROR(IF(V4=0,"",(Q4+S4)/V4),"")</f>
         <v/>
       </c>
       <c r="Y4" s="4" t="n"/>
       <c r="Z4" s="4" t="n"/>
-      <c r="AA4" s="16">
+      <c r="AA4" s="22">
         <f>IFERROR(Y4+Z4,0)</f>
         <v/>
       </c>
@@ -8876,7 +9049,7 @@
       <c r="AE4" s="4" t="n"/>
       <c r="AF4" s="4" t="n"/>
       <c r="AG4" s="4" t="n"/>
-      <c r="AH4" s="16">
+      <c r="AH4" s="22">
         <f>IFERROR(AB4*INDEX(PARAMS_Trees,1,3)+AC4*INDEX(PARAMS_Trees,2,3)+AD4*INDEX(PARAMS_Trees,3,3)+AE4*INDEX(PARAMS_Trees,4,3)+AF4*INDEX(PARAMS_Trees,5,3)+AG4*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
       </c>
@@ -8896,7 +9069,7 @@
         <f>IFERROR(VLOOKUP(C4,'CDA'!$A$58:$D$67,4,FALSE),0)</f>
         <v/>
       </c>
-      <c r="AM4" s="16">
+      <c r="AM4" s="22">
         <f>IFERROR(IF(AL4=0,AK4,MIN(AK4,AL4)),0)</f>
         <v/>
       </c>
@@ -8906,11 +9079,14 @@
       <c r="B5" s="4" t="n"/>
       <c r="C5" s="4" t="n"/>
       <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
+      <c r="E5" s="21" t="n"/>
       <c r="F5" s="4" t="n"/>
       <c r="G5" s="4" t="n"/>
       <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="n"/>
+      <c r="I5" s="4">
+        <f>IFERROR(IF(OR(E5="Enhanced",E5="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C5,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C5,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C5,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C5,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="J5" s="16">
         <f>IFERROR(IFS(AND(D5="Permeable Pavement",E5="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D5="Permeable Pavement",E5="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D5="Bioretention",E5="Standard"),INDEX(PARAMS_BMP,3,5),AND(D5="Bioretention",E5="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D5="Bioretention",E5="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D5="Dry Swale",E5="—"),INDEX(PARAMS_BMP,6,5),AND(D5="Wet Swale",E5="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
         <v/>
@@ -8923,7 +9099,7 @@
         <f>IFERROR(IF(I5=0,"",G5/I5),"")</f>
         <v/>
       </c>
-      <c r="M5" s="16">
+      <c r="M5" s="22">
         <f>IFERROR(IF(L5="","",IF(L5&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
@@ -8944,18 +9120,21 @@
         <v/>
       </c>
       <c r="U5" s="4" t="n"/>
-      <c r="V5" s="4" t="n"/>
+      <c r="V5" s="4">
+        <f>IFERROR(IF(OR(E5="Enhanced",E5="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C5,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C5,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C5,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C5,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="W5" s="16">
         <f>IFERROR(P5*(Q5*R5+S5*T5+U5),0)</f>
         <v/>
       </c>
-      <c r="X5" s="16">
+      <c r="X5" s="22">
         <f>IFERROR(IF(V5=0,"",(Q5+S5)/V5),"")</f>
         <v/>
       </c>
       <c r="Y5" s="4" t="n"/>
       <c r="Z5" s="4" t="n"/>
-      <c r="AA5" s="16">
+      <c r="AA5" s="22">
         <f>IFERROR(Y5+Z5,0)</f>
         <v/>
       </c>
@@ -8965,7 +9144,7 @@
       <c r="AE5" s="4" t="n"/>
       <c r="AF5" s="4" t="n"/>
       <c r="AG5" s="4" t="n"/>
-      <c r="AH5" s="16">
+      <c r="AH5" s="22">
         <f>IFERROR(AB5*INDEX(PARAMS_Trees,1,3)+AC5*INDEX(PARAMS_Trees,2,3)+AD5*INDEX(PARAMS_Trees,3,3)+AE5*INDEX(PARAMS_Trees,4,3)+AF5*INDEX(PARAMS_Trees,5,3)+AG5*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
       </c>
@@ -8985,7 +9164,7 @@
         <f>IFERROR(VLOOKUP(C5,'CDA'!$A$58:$D$67,4,FALSE),0)</f>
         <v/>
       </c>
-      <c r="AM5" s="16">
+      <c r="AM5" s="22">
         <f>IFERROR(IF(AL5=0,AK5,MIN(AK5,AL5)),0)</f>
         <v/>
       </c>
@@ -8995,11 +9174,14 @@
       <c r="B6" s="4" t="n"/>
       <c r="C6" s="4" t="n"/>
       <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="n"/>
+      <c r="E6" s="21" t="n"/>
       <c r="F6" s="4" t="n"/>
       <c r="G6" s="4" t="n"/>
       <c r="H6" s="4" t="n"/>
-      <c r="I6" s="4" t="n"/>
+      <c r="I6" s="4">
+        <f>IFERROR(IF(OR(E6="Enhanced",E6="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C6,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C6,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C6,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C6,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="J6" s="16">
         <f>IFERROR(IFS(AND(D6="Permeable Pavement",E6="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D6="Permeable Pavement",E6="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D6="Bioretention",E6="Standard"),INDEX(PARAMS_BMP,3,5),AND(D6="Bioretention",E6="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D6="Bioretention",E6="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D6="Dry Swale",E6="—"),INDEX(PARAMS_BMP,6,5),AND(D6="Wet Swale",E6="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
         <v/>
@@ -9012,7 +9194,7 @@
         <f>IFERROR(IF(I6=0,"",G6/I6),"")</f>
         <v/>
       </c>
-      <c r="M6" s="16">
+      <c r="M6" s="22">
         <f>IFERROR(IF(L6="","",IF(L6&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
@@ -9033,18 +9215,21 @@
         <v/>
       </c>
       <c r="U6" s="4" t="n"/>
-      <c r="V6" s="4" t="n"/>
+      <c r="V6" s="4">
+        <f>IFERROR(IF(OR(E6="Enhanced",E6="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C6,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C6,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C6,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C6,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="W6" s="16">
         <f>IFERROR(P6*(Q6*R6+S6*T6+U6),0)</f>
         <v/>
       </c>
-      <c r="X6" s="16">
+      <c r="X6" s="22">
         <f>IFERROR(IF(V6=0,"",(Q6+S6)/V6),"")</f>
         <v/>
       </c>
       <c r="Y6" s="4" t="n"/>
       <c r="Z6" s="4" t="n"/>
-      <c r="AA6" s="16">
+      <c r="AA6" s="22">
         <f>IFERROR(Y6+Z6,0)</f>
         <v/>
       </c>
@@ -9054,7 +9239,7 @@
       <c r="AE6" s="4" t="n"/>
       <c r="AF6" s="4" t="n"/>
       <c r="AG6" s="4" t="n"/>
-      <c r="AH6" s="16">
+      <c r="AH6" s="22">
         <f>IFERROR(AB6*INDEX(PARAMS_Trees,1,3)+AC6*INDEX(PARAMS_Trees,2,3)+AD6*INDEX(PARAMS_Trees,3,3)+AE6*INDEX(PARAMS_Trees,4,3)+AF6*INDEX(PARAMS_Trees,5,3)+AG6*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
       </c>
@@ -9074,7 +9259,7 @@
         <f>IFERROR(VLOOKUP(C6,'CDA'!$A$58:$D$67,4,FALSE),0)</f>
         <v/>
       </c>
-      <c r="AM6" s="16">
+      <c r="AM6" s="22">
         <f>IFERROR(IF(AL6=0,AK6,MIN(AK6,AL6)),0)</f>
         <v/>
       </c>
@@ -9084,11 +9269,14 @@
       <c r="B7" s="4" t="n"/>
       <c r="C7" s="4" t="n"/>
       <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n"/>
+      <c r="E7" s="21" t="n"/>
       <c r="F7" s="4" t="n"/>
       <c r="G7" s="4" t="n"/>
       <c r="H7" s="4" t="n"/>
-      <c r="I7" s="4" t="n"/>
+      <c r="I7" s="4">
+        <f>IFERROR(IF(OR(E7="Enhanced",E7="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C7,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C7,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C7,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C7,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="J7" s="16">
         <f>IFERROR(IFS(AND(D7="Permeable Pavement",E7="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D7="Permeable Pavement",E7="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D7="Bioretention",E7="Standard"),INDEX(PARAMS_BMP,3,5),AND(D7="Bioretention",E7="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D7="Bioretention",E7="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D7="Dry Swale",E7="—"),INDEX(PARAMS_BMP,6,5),AND(D7="Wet Swale",E7="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
         <v/>
@@ -9101,7 +9289,7 @@
         <f>IFERROR(IF(I7=0,"",G7/I7),"")</f>
         <v/>
       </c>
-      <c r="M7" s="16">
+      <c r="M7" s="22">
         <f>IFERROR(IF(L7="","",IF(L7&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
@@ -9122,18 +9310,21 @@
         <v/>
       </c>
       <c r="U7" s="4" t="n"/>
-      <c r="V7" s="4" t="n"/>
+      <c r="V7" s="4">
+        <f>IFERROR(IF(OR(E7="Enhanced",E7="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C7,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C7,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C7,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C7,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="W7" s="16">
         <f>IFERROR(P7*(Q7*R7+S7*T7+U7),0)</f>
         <v/>
       </c>
-      <c r="X7" s="16">
+      <c r="X7" s="22">
         <f>IFERROR(IF(V7=0,"",(Q7+S7)/V7),"")</f>
         <v/>
       </c>
       <c r="Y7" s="4" t="n"/>
       <c r="Z7" s="4" t="n"/>
-      <c r="AA7" s="16">
+      <c r="AA7" s="22">
         <f>IFERROR(Y7+Z7,0)</f>
         <v/>
       </c>
@@ -9143,7 +9334,7 @@
       <c r="AE7" s="4" t="n"/>
       <c r="AF7" s="4" t="n"/>
       <c r="AG7" s="4" t="n"/>
-      <c r="AH7" s="16">
+      <c r="AH7" s="22">
         <f>IFERROR(AB7*INDEX(PARAMS_Trees,1,3)+AC7*INDEX(PARAMS_Trees,2,3)+AD7*INDEX(PARAMS_Trees,3,3)+AE7*INDEX(PARAMS_Trees,4,3)+AF7*INDEX(PARAMS_Trees,5,3)+AG7*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
       </c>
@@ -9163,7 +9354,7 @@
         <f>IFERROR(VLOOKUP(C7,'CDA'!$A$58:$D$67,4,FALSE),0)</f>
         <v/>
       </c>
-      <c r="AM7" s="16">
+      <c r="AM7" s="22">
         <f>IFERROR(IF(AL7=0,AK7,MIN(AK7,AL7)),0)</f>
         <v/>
       </c>
@@ -9173,11 +9364,14 @@
       <c r="B8" s="4" t="n"/>
       <c r="C8" s="4" t="n"/>
       <c r="D8" s="4" t="n"/>
-      <c r="E8" s="4" t="n"/>
+      <c r="E8" s="21" t="n"/>
       <c r="F8" s="4" t="n"/>
       <c r="G8" s="4" t="n"/>
       <c r="H8" s="4" t="n"/>
-      <c r="I8" s="4" t="n"/>
+      <c r="I8" s="4">
+        <f>IFERROR(IF(OR(E8="Enhanced",E8="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C8,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C8,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C8,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C8,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="J8" s="16">
         <f>IFERROR(IFS(AND(D8="Permeable Pavement",E8="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D8="Permeable Pavement",E8="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D8="Bioretention",E8="Standard"),INDEX(PARAMS_BMP,3,5),AND(D8="Bioretention",E8="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D8="Bioretention",E8="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D8="Dry Swale",E8="—"),INDEX(PARAMS_BMP,6,5),AND(D8="Wet Swale",E8="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
         <v/>
@@ -9190,7 +9384,7 @@
         <f>IFERROR(IF(I8=0,"",G8/I8),"")</f>
         <v/>
       </c>
-      <c r="M8" s="16">
+      <c r="M8" s="22">
         <f>IFERROR(IF(L8="","",IF(L8&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
@@ -9211,18 +9405,21 @@
         <v/>
       </c>
       <c r="U8" s="4" t="n"/>
-      <c r="V8" s="4" t="n"/>
+      <c r="V8" s="4">
+        <f>IFERROR(IF(OR(E8="Enhanced",E8="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C8,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C8,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C8,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C8,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="W8" s="16">
         <f>IFERROR(P8*(Q8*R8+S8*T8+U8),0)</f>
         <v/>
       </c>
-      <c r="X8" s="16">
+      <c r="X8" s="22">
         <f>IFERROR(IF(V8=0,"",(Q8+S8)/V8),"")</f>
         <v/>
       </c>
       <c r="Y8" s="4" t="n"/>
       <c r="Z8" s="4" t="n"/>
-      <c r="AA8" s="16">
+      <c r="AA8" s="22">
         <f>IFERROR(Y8+Z8,0)</f>
         <v/>
       </c>
@@ -9232,7 +9429,7 @@
       <c r="AE8" s="4" t="n"/>
       <c r="AF8" s="4" t="n"/>
       <c r="AG8" s="4" t="n"/>
-      <c r="AH8" s="16">
+      <c r="AH8" s="22">
         <f>IFERROR(AB8*INDEX(PARAMS_Trees,1,3)+AC8*INDEX(PARAMS_Trees,2,3)+AD8*INDEX(PARAMS_Trees,3,3)+AE8*INDEX(PARAMS_Trees,4,3)+AF8*INDEX(PARAMS_Trees,5,3)+AG8*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
       </c>
@@ -9252,7 +9449,7 @@
         <f>IFERROR(VLOOKUP(C8,'CDA'!$A$58:$D$67,4,FALSE),0)</f>
         <v/>
       </c>
-      <c r="AM8" s="16">
+      <c r="AM8" s="22">
         <f>IFERROR(IF(AL8=0,AK8,MIN(AK8,AL8)),0)</f>
         <v/>
       </c>
@@ -9262,11 +9459,14 @@
       <c r="B9" s="4" t="n"/>
       <c r="C9" s="4" t="n"/>
       <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="n"/>
+      <c r="E9" s="21" t="n"/>
       <c r="F9" s="4" t="n"/>
       <c r="G9" s="4" t="n"/>
       <c r="H9" s="4" t="n"/>
-      <c r="I9" s="4" t="n"/>
+      <c r="I9" s="4">
+        <f>IFERROR(IF(OR(E9="Enhanced",E9="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C9,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C9,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C9,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C9,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="J9" s="16">
         <f>IFERROR(IFS(AND(D9="Permeable Pavement",E9="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D9="Permeable Pavement",E9="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D9="Bioretention",E9="Standard"),INDEX(PARAMS_BMP,3,5),AND(D9="Bioretention",E9="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D9="Bioretention",E9="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D9="Dry Swale",E9="—"),INDEX(PARAMS_BMP,6,5),AND(D9="Wet Swale",E9="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
         <v/>
@@ -9279,7 +9479,7 @@
         <f>IFERROR(IF(I9=0,"",G9/I9),"")</f>
         <v/>
       </c>
-      <c r="M9" s="16">
+      <c r="M9" s="22">
         <f>IFERROR(IF(L9="","",IF(L9&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
@@ -9300,18 +9500,21 @@
         <v/>
       </c>
       <c r="U9" s="4" t="n"/>
-      <c r="V9" s="4" t="n"/>
+      <c r="V9" s="4">
+        <f>IFERROR(IF(OR(E9="Enhanced",E9="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C9,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C9,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C9,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C9,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="W9" s="16">
         <f>IFERROR(P9*(Q9*R9+S9*T9+U9),0)</f>
         <v/>
       </c>
-      <c r="X9" s="16">
+      <c r="X9" s="22">
         <f>IFERROR(IF(V9=0,"",(Q9+S9)/V9),"")</f>
         <v/>
       </c>
       <c r="Y9" s="4" t="n"/>
       <c r="Z9" s="4" t="n"/>
-      <c r="AA9" s="16">
+      <c r="AA9" s="22">
         <f>IFERROR(Y9+Z9,0)</f>
         <v/>
       </c>
@@ -9321,7 +9524,7 @@
       <c r="AE9" s="4" t="n"/>
       <c r="AF9" s="4" t="n"/>
       <c r="AG9" s="4" t="n"/>
-      <c r="AH9" s="16">
+      <c r="AH9" s="22">
         <f>IFERROR(AB9*INDEX(PARAMS_Trees,1,3)+AC9*INDEX(PARAMS_Trees,2,3)+AD9*INDEX(PARAMS_Trees,3,3)+AE9*INDEX(PARAMS_Trees,4,3)+AF9*INDEX(PARAMS_Trees,5,3)+AG9*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
       </c>
@@ -9341,7 +9544,7 @@
         <f>IFERROR(VLOOKUP(C9,'CDA'!$A$58:$D$67,4,FALSE),0)</f>
         <v/>
       </c>
-      <c r="AM9" s="16">
+      <c r="AM9" s="22">
         <f>IFERROR(IF(AL9=0,AK9,MIN(AK9,AL9)),0)</f>
         <v/>
       </c>
@@ -9351,11 +9554,14 @@
       <c r="B10" s="4" t="n"/>
       <c r="C10" s="4" t="n"/>
       <c r="D10" s="4" t="n"/>
-      <c r="E10" s="4" t="n"/>
+      <c r="E10" s="21" t="n"/>
       <c r="F10" s="4" t="n"/>
       <c r="G10" s="4" t="n"/>
       <c r="H10" s="4" t="n"/>
-      <c r="I10" s="4" t="n"/>
+      <c r="I10" s="4">
+        <f>IFERROR(IF(OR(E10="Enhanced",E10="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C10,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C10,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C10,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C10,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="J10" s="16">
         <f>IFERROR(IFS(AND(D10="Permeable Pavement",E10="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D10="Permeable Pavement",E10="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D10="Bioretention",E10="Standard"),INDEX(PARAMS_BMP,3,5),AND(D10="Bioretention",E10="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D10="Bioretention",E10="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D10="Dry Swale",E10="—"),INDEX(PARAMS_BMP,6,5),AND(D10="Wet Swale",E10="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
         <v/>
@@ -9368,7 +9574,7 @@
         <f>IFERROR(IF(I10=0,"",G10/I10),"")</f>
         <v/>
       </c>
-      <c r="M10" s="16">
+      <c r="M10" s="22">
         <f>IFERROR(IF(L10="","",IF(L10&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
@@ -9389,18 +9595,21 @@
         <v/>
       </c>
       <c r="U10" s="4" t="n"/>
-      <c r="V10" s="4" t="n"/>
+      <c r="V10" s="4">
+        <f>IFERROR(IF(OR(E10="Enhanced",E10="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C10,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C10,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C10,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C10,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="W10" s="16">
         <f>IFERROR(P10*(Q10*R10+S10*T10+U10),0)</f>
         <v/>
       </c>
-      <c r="X10" s="16">
+      <c r="X10" s="22">
         <f>IFERROR(IF(V10=0,"",(Q10+S10)/V10),"")</f>
         <v/>
       </c>
       <c r="Y10" s="4" t="n"/>
       <c r="Z10" s="4" t="n"/>
-      <c r="AA10" s="16">
+      <c r="AA10" s="22">
         <f>IFERROR(Y10+Z10,0)</f>
         <v/>
       </c>
@@ -9410,7 +9619,7 @@
       <c r="AE10" s="4" t="n"/>
       <c r="AF10" s="4" t="n"/>
       <c r="AG10" s="4" t="n"/>
-      <c r="AH10" s="16">
+      <c r="AH10" s="22">
         <f>IFERROR(AB10*INDEX(PARAMS_Trees,1,3)+AC10*INDEX(PARAMS_Trees,2,3)+AD10*INDEX(PARAMS_Trees,3,3)+AE10*INDEX(PARAMS_Trees,4,3)+AF10*INDEX(PARAMS_Trees,5,3)+AG10*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
       </c>
@@ -9430,7 +9639,7 @@
         <f>IFERROR(VLOOKUP(C10,'CDA'!$A$58:$D$67,4,FALSE),0)</f>
         <v/>
       </c>
-      <c r="AM10" s="16">
+      <c r="AM10" s="22">
         <f>IFERROR(IF(AL10=0,AK10,MIN(AK10,AL10)),0)</f>
         <v/>
       </c>
@@ -9440,11 +9649,14 @@
       <c r="B11" s="4" t="n"/>
       <c r="C11" s="4" t="n"/>
       <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="n"/>
+      <c r="E11" s="21" t="n"/>
       <c r="F11" s="4" t="n"/>
       <c r="G11" s="4" t="n"/>
       <c r="H11" s="4" t="n"/>
-      <c r="I11" s="4" t="n"/>
+      <c r="I11" s="4">
+        <f>IFERROR(IF(OR(E11="Enhanced",E11="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C11,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C11,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C11,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C11,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="J11" s="16">
         <f>IFERROR(IFS(AND(D11="Permeable Pavement",E11="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D11="Permeable Pavement",E11="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D11="Bioretention",E11="Standard"),INDEX(PARAMS_BMP,3,5),AND(D11="Bioretention",E11="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D11="Bioretention",E11="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D11="Dry Swale",E11="—"),INDEX(PARAMS_BMP,6,5),AND(D11="Wet Swale",E11="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
         <v/>
@@ -9457,7 +9669,7 @@
         <f>IFERROR(IF(I11=0,"",G11/I11),"")</f>
         <v/>
       </c>
-      <c r="M11" s="16">
+      <c r="M11" s="22">
         <f>IFERROR(IF(L11="","",IF(L11&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
@@ -9478,18 +9690,21 @@
         <v/>
       </c>
       <c r="U11" s="4" t="n"/>
-      <c r="V11" s="4" t="n"/>
+      <c r="V11" s="4">
+        <f>IFERROR(IF(OR(E11="Enhanced",E11="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C11,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C11,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C11,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C11,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="W11" s="16">
         <f>IFERROR(P11*(Q11*R11+S11*T11+U11),0)</f>
         <v/>
       </c>
-      <c r="X11" s="16">
+      <c r="X11" s="22">
         <f>IFERROR(IF(V11=0,"",(Q11+S11)/V11),"")</f>
         <v/>
       </c>
       <c r="Y11" s="4" t="n"/>
       <c r="Z11" s="4" t="n"/>
-      <c r="AA11" s="16">
+      <c r="AA11" s="22">
         <f>IFERROR(Y11+Z11,0)</f>
         <v/>
       </c>
@@ -9499,7 +9714,7 @@
       <c r="AE11" s="4" t="n"/>
       <c r="AF11" s="4" t="n"/>
       <c r="AG11" s="4" t="n"/>
-      <c r="AH11" s="16">
+      <c r="AH11" s="22">
         <f>IFERROR(AB11*INDEX(PARAMS_Trees,1,3)+AC11*INDEX(PARAMS_Trees,2,3)+AD11*INDEX(PARAMS_Trees,3,3)+AE11*INDEX(PARAMS_Trees,4,3)+AF11*INDEX(PARAMS_Trees,5,3)+AG11*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
       </c>
@@ -9519,7 +9734,7 @@
         <f>IFERROR(VLOOKUP(C11,'CDA'!$A$58:$D$67,4,FALSE),0)</f>
         <v/>
       </c>
-      <c r="AM11" s="16">
+      <c r="AM11" s="22">
         <f>IFERROR(IF(AL11=0,AK11,MIN(AK11,AL11)),0)</f>
         <v/>
       </c>
@@ -9529,11 +9744,14 @@
       <c r="B12" s="4" t="n"/>
       <c r="C12" s="4" t="n"/>
       <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="n"/>
+      <c r="E12" s="21" t="n"/>
       <c r="F12" s="4" t="n"/>
       <c r="G12" s="4" t="n"/>
       <c r="H12" s="4" t="n"/>
-      <c r="I12" s="4" t="n"/>
+      <c r="I12" s="4">
+        <f>IFERROR(IF(OR(E12="Enhanced",E12="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C12,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C12,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C12,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C12,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="J12" s="16">
         <f>IFERROR(IFS(AND(D12="Permeable Pavement",E12="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D12="Permeable Pavement",E12="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D12="Bioretention",E12="Standard"),INDEX(PARAMS_BMP,3,5),AND(D12="Bioretention",E12="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D12="Bioretention",E12="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D12="Dry Swale",E12="—"),INDEX(PARAMS_BMP,6,5),AND(D12="Wet Swale",E12="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
         <v/>
@@ -9546,7 +9764,7 @@
         <f>IFERROR(IF(I12=0,"",G12/I12),"")</f>
         <v/>
       </c>
-      <c r="M12" s="16">
+      <c r="M12" s="22">
         <f>IFERROR(IF(L12="","",IF(L12&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
@@ -9567,18 +9785,21 @@
         <v/>
       </c>
       <c r="U12" s="4" t="n"/>
-      <c r="V12" s="4" t="n"/>
+      <c r="V12" s="4">
+        <f>IFERROR(IF(OR(E12="Enhanced",E12="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C12,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C12,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C12,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C12,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="W12" s="16">
         <f>IFERROR(P12*(Q12*R12+S12*T12+U12),0)</f>
         <v/>
       </c>
-      <c r="X12" s="16">
+      <c r="X12" s="22">
         <f>IFERROR(IF(V12=0,"",(Q12+S12)/V12),"")</f>
         <v/>
       </c>
       <c r="Y12" s="4" t="n"/>
       <c r="Z12" s="4" t="n"/>
-      <c r="AA12" s="16">
+      <c r="AA12" s="22">
         <f>IFERROR(Y12+Z12,0)</f>
         <v/>
       </c>
@@ -9588,7 +9809,7 @@
       <c r="AE12" s="4" t="n"/>
       <c r="AF12" s="4" t="n"/>
       <c r="AG12" s="4" t="n"/>
-      <c r="AH12" s="16">
+      <c r="AH12" s="22">
         <f>IFERROR(AB12*INDEX(PARAMS_Trees,1,3)+AC12*INDEX(PARAMS_Trees,2,3)+AD12*INDEX(PARAMS_Trees,3,3)+AE12*INDEX(PARAMS_Trees,4,3)+AF12*INDEX(PARAMS_Trees,5,3)+AG12*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
       </c>
@@ -9608,7 +9829,7 @@
         <f>IFERROR(VLOOKUP(C12,'CDA'!$A$58:$D$67,4,FALSE),0)</f>
         <v/>
       </c>
-      <c r="AM12" s="16">
+      <c r="AM12" s="22">
         <f>IFERROR(IF(AL12=0,AK12,MIN(AK12,AL12)),0)</f>
         <v/>
       </c>
@@ -9618,11 +9839,14 @@
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="4" t="n"/>
       <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="n"/>
+      <c r="E13" s="21" t="n"/>
       <c r="F13" s="4" t="n"/>
       <c r="G13" s="4" t="n"/>
       <c r="H13" s="4" t="n"/>
-      <c r="I13" s="4" t="n"/>
+      <c r="I13" s="4">
+        <f>IFERROR(IF(OR(E13="Enhanced",E13="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C13,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C13,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C13,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C13,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="J13" s="16">
         <f>IFERROR(IFS(AND(D13="Permeable Pavement",E13="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D13="Permeable Pavement",E13="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D13="Bioretention",E13="Standard"),INDEX(PARAMS_BMP,3,5),AND(D13="Bioretention",E13="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D13="Bioretention",E13="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D13="Dry Swale",E13="—"),INDEX(PARAMS_BMP,6,5),AND(D13="Wet Swale",E13="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
         <v/>
@@ -9635,7 +9859,7 @@
         <f>IFERROR(IF(I13=0,"",G13/I13),"")</f>
         <v/>
       </c>
-      <c r="M13" s="16">
+      <c r="M13" s="22">
         <f>IFERROR(IF(L13="","",IF(L13&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
@@ -9656,18 +9880,21 @@
         <v/>
       </c>
       <c r="U13" s="4" t="n"/>
-      <c r="V13" s="4" t="n"/>
+      <c r="V13" s="4">
+        <f>IFERROR(IF(OR(E13="Enhanced",E13="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C13,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C13,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C13,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C13,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="W13" s="16">
         <f>IFERROR(P13*(Q13*R13+S13*T13+U13),0)</f>
         <v/>
       </c>
-      <c r="X13" s="16">
+      <c r="X13" s="22">
         <f>IFERROR(IF(V13=0,"",(Q13+S13)/V13),"")</f>
         <v/>
       </c>
       <c r="Y13" s="4" t="n"/>
       <c r="Z13" s="4" t="n"/>
-      <c r="AA13" s="16">
+      <c r="AA13" s="22">
         <f>IFERROR(Y13+Z13,0)</f>
         <v/>
       </c>
@@ -9677,7 +9904,7 @@
       <c r="AE13" s="4" t="n"/>
       <c r="AF13" s="4" t="n"/>
       <c r="AG13" s="4" t="n"/>
-      <c r="AH13" s="16">
+      <c r="AH13" s="22">
         <f>IFERROR(AB13*INDEX(PARAMS_Trees,1,3)+AC13*INDEX(PARAMS_Trees,2,3)+AD13*INDEX(PARAMS_Trees,3,3)+AE13*INDEX(PARAMS_Trees,4,3)+AF13*INDEX(PARAMS_Trees,5,3)+AG13*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
       </c>
@@ -9697,7 +9924,7 @@
         <f>IFERROR(VLOOKUP(C13,'CDA'!$A$58:$D$67,4,FALSE),0)</f>
         <v/>
       </c>
-      <c r="AM13" s="16">
+      <c r="AM13" s="22">
         <f>IFERROR(IF(AL13=0,AK13,MIN(AK13,AL13)),0)</f>
         <v/>
       </c>
@@ -9707,11 +9934,14 @@
       <c r="B14" s="4" t="n"/>
       <c r="C14" s="4" t="n"/>
       <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="n"/>
+      <c r="E14" s="21" t="n"/>
       <c r="F14" s="4" t="n"/>
       <c r="G14" s="4" t="n"/>
       <c r="H14" s="4" t="n"/>
-      <c r="I14" s="4" t="n"/>
+      <c r="I14" s="4">
+        <f>IFERROR(IF(OR(E14="Enhanced",E14="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C14,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C14,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C14,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C14,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="J14" s="16">
         <f>IFERROR(IFS(AND(D14="Permeable Pavement",E14="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D14="Permeable Pavement",E14="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D14="Bioretention",E14="Standard"),INDEX(PARAMS_BMP,3,5),AND(D14="Bioretention",E14="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D14="Bioretention",E14="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D14="Dry Swale",E14="—"),INDEX(PARAMS_BMP,6,5),AND(D14="Wet Swale",E14="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
         <v/>
@@ -9724,7 +9954,7 @@
         <f>IFERROR(IF(I14=0,"",G14/I14),"")</f>
         <v/>
       </c>
-      <c r="M14" s="16">
+      <c r="M14" s="22">
         <f>IFERROR(IF(L14="","",IF(L14&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
@@ -9745,18 +9975,21 @@
         <v/>
       </c>
       <c r="U14" s="4" t="n"/>
-      <c r="V14" s="4" t="n"/>
+      <c r="V14" s="4">
+        <f>IFERROR(IF(OR(E14="Enhanced",E14="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C14,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C14,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C14,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C14,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="W14" s="16">
         <f>IFERROR(P14*(Q14*R14+S14*T14+U14),0)</f>
         <v/>
       </c>
-      <c r="X14" s="16">
+      <c r="X14" s="22">
         <f>IFERROR(IF(V14=0,"",(Q14+S14)/V14),"")</f>
         <v/>
       </c>
       <c r="Y14" s="4" t="n"/>
       <c r="Z14" s="4" t="n"/>
-      <c r="AA14" s="16">
+      <c r="AA14" s="22">
         <f>IFERROR(Y14+Z14,0)</f>
         <v/>
       </c>
@@ -9766,7 +9999,7 @@
       <c r="AE14" s="4" t="n"/>
       <c r="AF14" s="4" t="n"/>
       <c r="AG14" s="4" t="n"/>
-      <c r="AH14" s="16">
+      <c r="AH14" s="22">
         <f>IFERROR(AB14*INDEX(PARAMS_Trees,1,3)+AC14*INDEX(PARAMS_Trees,2,3)+AD14*INDEX(PARAMS_Trees,3,3)+AE14*INDEX(PARAMS_Trees,4,3)+AF14*INDEX(PARAMS_Trees,5,3)+AG14*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
       </c>
@@ -9786,7 +10019,7 @@
         <f>IFERROR(VLOOKUP(C14,'CDA'!$A$58:$D$67,4,FALSE),0)</f>
         <v/>
       </c>
-      <c r="AM14" s="16">
+      <c r="AM14" s="22">
         <f>IFERROR(IF(AL14=0,AK14,MIN(AK14,AL14)),0)</f>
         <v/>
       </c>
@@ -9796,11 +10029,14 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="4" t="n"/>
       <c r="D15" s="4" t="n"/>
-      <c r="E15" s="4" t="n"/>
+      <c r="E15" s="21" t="n"/>
       <c r="F15" s="4" t="n"/>
       <c r="G15" s="4" t="n"/>
       <c r="H15" s="4" t="n"/>
-      <c r="I15" s="4" t="n"/>
+      <c r="I15" s="4">
+        <f>IFERROR(IF(OR(E15="Enhanced",E15="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C15,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C15,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C15,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C15,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="J15" s="16">
         <f>IFERROR(IFS(AND(D15="Permeable Pavement",E15="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D15="Permeable Pavement",E15="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D15="Bioretention",E15="Standard"),INDEX(PARAMS_BMP,3,5),AND(D15="Bioretention",E15="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D15="Bioretention",E15="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D15="Dry Swale",E15="—"),INDEX(PARAMS_BMP,6,5),AND(D15="Wet Swale",E15="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
         <v/>
@@ -9813,7 +10049,7 @@
         <f>IFERROR(IF(I15=0,"",G15/I15),"")</f>
         <v/>
       </c>
-      <c r="M15" s="16">
+      <c r="M15" s="22">
         <f>IFERROR(IF(L15="","",IF(L15&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
@@ -9834,18 +10070,21 @@
         <v/>
       </c>
       <c r="U15" s="4" t="n"/>
-      <c r="V15" s="4" t="n"/>
+      <c r="V15" s="4">
+        <f>IFERROR(IF(OR(E15="Enhanced",E15="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C15,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C15,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C15,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C15,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="W15" s="16">
         <f>IFERROR(P15*(Q15*R15+S15*T15+U15),0)</f>
         <v/>
       </c>
-      <c r="X15" s="16">
+      <c r="X15" s="22">
         <f>IFERROR(IF(V15=0,"",(Q15+S15)/V15),"")</f>
         <v/>
       </c>
       <c r="Y15" s="4" t="n"/>
       <c r="Z15" s="4" t="n"/>
-      <c r="AA15" s="16">
+      <c r="AA15" s="22">
         <f>IFERROR(Y15+Z15,0)</f>
         <v/>
       </c>
@@ -9855,7 +10094,7 @@
       <c r="AE15" s="4" t="n"/>
       <c r="AF15" s="4" t="n"/>
       <c r="AG15" s="4" t="n"/>
-      <c r="AH15" s="16">
+      <c r="AH15" s="22">
         <f>IFERROR(AB15*INDEX(PARAMS_Trees,1,3)+AC15*INDEX(PARAMS_Trees,2,3)+AD15*INDEX(PARAMS_Trees,3,3)+AE15*INDEX(PARAMS_Trees,4,3)+AF15*INDEX(PARAMS_Trees,5,3)+AG15*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
       </c>
@@ -9875,7 +10114,7 @@
         <f>IFERROR(VLOOKUP(C15,'CDA'!$A$58:$D$67,4,FALSE),0)</f>
         <v/>
       </c>
-      <c r="AM15" s="16">
+      <c r="AM15" s="22">
         <f>IFERROR(IF(AL15=0,AK15,MIN(AK15,AL15)),0)</f>
         <v/>
       </c>
@@ -9885,11 +10124,14 @@
       <c r="B16" s="4" t="n"/>
       <c r="C16" s="4" t="n"/>
       <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="n"/>
+      <c r="E16" s="21" t="n"/>
       <c r="F16" s="4" t="n"/>
       <c r="G16" s="4" t="n"/>
       <c r="H16" s="4" t="n"/>
-      <c r="I16" s="4" t="n"/>
+      <c r="I16" s="4">
+        <f>IFERROR(IF(OR(E16="Enhanced",E16="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C16,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C16,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C16,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C16,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="J16" s="16">
         <f>IFERROR(IFS(AND(D16="Permeable Pavement",E16="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D16="Permeable Pavement",E16="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D16="Bioretention",E16="Standard"),INDEX(PARAMS_BMP,3,5),AND(D16="Bioretention",E16="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D16="Bioretention",E16="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D16="Dry Swale",E16="—"),INDEX(PARAMS_BMP,6,5),AND(D16="Wet Swale",E16="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
         <v/>
@@ -9902,7 +10144,7 @@
         <f>IFERROR(IF(I16=0,"",G16/I16),"")</f>
         <v/>
       </c>
-      <c r="M16" s="16">
+      <c r="M16" s="22">
         <f>IFERROR(IF(L16="","",IF(L16&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
@@ -9923,18 +10165,21 @@
         <v/>
       </c>
       <c r="U16" s="4" t="n"/>
-      <c r="V16" s="4" t="n"/>
+      <c r="V16" s="4">
+        <f>IFERROR(IF(OR(E16="Enhanced",E16="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C16,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C16,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C16,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C16,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="W16" s="16">
         <f>IFERROR(P16*(Q16*R16+S16*T16+U16),0)</f>
         <v/>
       </c>
-      <c r="X16" s="16">
+      <c r="X16" s="22">
         <f>IFERROR(IF(V16=0,"",(Q16+S16)/V16),"")</f>
         <v/>
       </c>
       <c r="Y16" s="4" t="n"/>
       <c r="Z16" s="4" t="n"/>
-      <c r="AA16" s="16">
+      <c r="AA16" s="22">
         <f>IFERROR(Y16+Z16,0)</f>
         <v/>
       </c>
@@ -9944,7 +10189,7 @@
       <c r="AE16" s="4" t="n"/>
       <c r="AF16" s="4" t="n"/>
       <c r="AG16" s="4" t="n"/>
-      <c r="AH16" s="16">
+      <c r="AH16" s="22">
         <f>IFERROR(AB16*INDEX(PARAMS_Trees,1,3)+AC16*INDEX(PARAMS_Trees,2,3)+AD16*INDEX(PARAMS_Trees,3,3)+AE16*INDEX(PARAMS_Trees,4,3)+AF16*INDEX(PARAMS_Trees,5,3)+AG16*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
       </c>
@@ -9964,7 +10209,7 @@
         <f>IFERROR(VLOOKUP(C16,'CDA'!$A$58:$D$67,4,FALSE),0)</f>
         <v/>
       </c>
-      <c r="AM16" s="16">
+      <c r="AM16" s="22">
         <f>IFERROR(IF(AL16=0,AK16,MIN(AK16,AL16)),0)</f>
         <v/>
       </c>
@@ -9974,11 +10219,14 @@
       <c r="B17" s="4" t="n"/>
       <c r="C17" s="4" t="n"/>
       <c r="D17" s="4" t="n"/>
-      <c r="E17" s="4" t="n"/>
+      <c r="E17" s="21" t="n"/>
       <c r="F17" s="4" t="n"/>
       <c r="G17" s="4" t="n"/>
       <c r="H17" s="4" t="n"/>
-      <c r="I17" s="4" t="n"/>
+      <c r="I17" s="4">
+        <f>IFERROR(IF(OR(E17="Enhanced",E17="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C17,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C17,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C17,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C17,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="J17" s="16">
         <f>IFERROR(IFS(AND(D17="Permeable Pavement",E17="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D17="Permeable Pavement",E17="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D17="Bioretention",E17="Standard"),INDEX(PARAMS_BMP,3,5),AND(D17="Bioretention",E17="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D17="Bioretention",E17="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D17="Dry Swale",E17="—"),INDEX(PARAMS_BMP,6,5),AND(D17="Wet Swale",E17="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
         <v/>
@@ -9991,7 +10239,7 @@
         <f>IFERROR(IF(I17=0,"",G17/I17),"")</f>
         <v/>
       </c>
-      <c r="M17" s="16">
+      <c r="M17" s="22">
         <f>IFERROR(IF(L17="","",IF(L17&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
@@ -10012,18 +10260,21 @@
         <v/>
       </c>
       <c r="U17" s="4" t="n"/>
-      <c r="V17" s="4" t="n"/>
+      <c r="V17" s="4">
+        <f>IFERROR(IF(OR(E17="Enhanced",E17="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C17,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C17,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C17,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C17,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="W17" s="16">
         <f>IFERROR(P17*(Q17*R17+S17*T17+U17),0)</f>
         <v/>
       </c>
-      <c r="X17" s="16">
+      <c r="X17" s="22">
         <f>IFERROR(IF(V17=0,"",(Q17+S17)/V17),"")</f>
         <v/>
       </c>
       <c r="Y17" s="4" t="n"/>
       <c r="Z17" s="4" t="n"/>
-      <c r="AA17" s="16">
+      <c r="AA17" s="22">
         <f>IFERROR(Y17+Z17,0)</f>
         <v/>
       </c>
@@ -10033,7 +10284,7 @@
       <c r="AE17" s="4" t="n"/>
       <c r="AF17" s="4" t="n"/>
       <c r="AG17" s="4" t="n"/>
-      <c r="AH17" s="16">
+      <c r="AH17" s="22">
         <f>IFERROR(AB17*INDEX(PARAMS_Trees,1,3)+AC17*INDEX(PARAMS_Trees,2,3)+AD17*INDEX(PARAMS_Trees,3,3)+AE17*INDEX(PARAMS_Trees,4,3)+AF17*INDEX(PARAMS_Trees,5,3)+AG17*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
       </c>
@@ -10053,7 +10304,7 @@
         <f>IFERROR(VLOOKUP(C17,'CDA'!$A$58:$D$67,4,FALSE),0)</f>
         <v/>
       </c>
-      <c r="AM17" s="16">
+      <c r="AM17" s="22">
         <f>IFERROR(IF(AL17=0,AK17,MIN(AK17,AL17)),0)</f>
         <v/>
       </c>
@@ -10063,11 +10314,14 @@
       <c r="B18" s="4" t="n"/>
       <c r="C18" s="4" t="n"/>
       <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="n"/>
+      <c r="E18" s="21" t="n"/>
       <c r="F18" s="4" t="n"/>
       <c r="G18" s="4" t="n"/>
       <c r="H18" s="4" t="n"/>
-      <c r="I18" s="4" t="n"/>
+      <c r="I18" s="4">
+        <f>IFERROR(IF(OR(E18="Enhanced",E18="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C18,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C18,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C18,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C18,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="J18" s="16">
         <f>IFERROR(IFS(AND(D18="Permeable Pavement",E18="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D18="Permeable Pavement",E18="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D18="Bioretention",E18="Standard"),INDEX(PARAMS_BMP,3,5),AND(D18="Bioretention",E18="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D18="Bioretention",E18="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D18="Dry Swale",E18="—"),INDEX(PARAMS_BMP,6,5),AND(D18="Wet Swale",E18="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
         <v/>
@@ -10080,7 +10334,7 @@
         <f>IFERROR(IF(I18=0,"",G18/I18),"")</f>
         <v/>
       </c>
-      <c r="M18" s="16">
+      <c r="M18" s="22">
         <f>IFERROR(IF(L18="","",IF(L18&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
@@ -10101,18 +10355,21 @@
         <v/>
       </c>
       <c r="U18" s="4" t="n"/>
-      <c r="V18" s="4" t="n"/>
+      <c r="V18" s="4">
+        <f>IFERROR(IF(OR(E18="Enhanced",E18="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C18,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C18,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C18,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C18,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="W18" s="16">
         <f>IFERROR(P18*(Q18*R18+S18*T18+U18),0)</f>
         <v/>
       </c>
-      <c r="X18" s="16">
+      <c r="X18" s="22">
         <f>IFERROR(IF(V18=0,"",(Q18+S18)/V18),"")</f>
         <v/>
       </c>
       <c r="Y18" s="4" t="n"/>
       <c r="Z18" s="4" t="n"/>
-      <c r="AA18" s="16">
+      <c r="AA18" s="22">
         <f>IFERROR(Y18+Z18,0)</f>
         <v/>
       </c>
@@ -10122,7 +10379,7 @@
       <c r="AE18" s="4" t="n"/>
       <c r="AF18" s="4" t="n"/>
       <c r="AG18" s="4" t="n"/>
-      <c r="AH18" s="16">
+      <c r="AH18" s="22">
         <f>IFERROR(AB18*INDEX(PARAMS_Trees,1,3)+AC18*INDEX(PARAMS_Trees,2,3)+AD18*INDEX(PARAMS_Trees,3,3)+AE18*INDEX(PARAMS_Trees,4,3)+AF18*INDEX(PARAMS_Trees,5,3)+AG18*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
       </c>
@@ -10142,7 +10399,7 @@
         <f>IFERROR(VLOOKUP(C18,'CDA'!$A$58:$D$67,4,FALSE),0)</f>
         <v/>
       </c>
-      <c r="AM18" s="16">
+      <c r="AM18" s="22">
         <f>IFERROR(IF(AL18=0,AK18,MIN(AK18,AL18)),0)</f>
         <v/>
       </c>
@@ -10152,11 +10409,14 @@
       <c r="B19" s="4" t="n"/>
       <c r="C19" s="4" t="n"/>
       <c r="D19" s="4" t="n"/>
-      <c r="E19" s="4" t="n"/>
+      <c r="E19" s="21" t="n"/>
       <c r="F19" s="4" t="n"/>
       <c r="G19" s="4" t="n"/>
       <c r="H19" s="4" t="n"/>
-      <c r="I19" s="4" t="n"/>
+      <c r="I19" s="4">
+        <f>IFERROR(IF(OR(E19="Enhanced",E19="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C19,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C19,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C19,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C19,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="J19" s="16">
         <f>IFERROR(IFS(AND(D19="Permeable Pavement",E19="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D19="Permeable Pavement",E19="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D19="Bioretention",E19="Standard"),INDEX(PARAMS_BMP,3,5),AND(D19="Bioretention",E19="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D19="Bioretention",E19="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D19="Dry Swale",E19="—"),INDEX(PARAMS_BMP,6,5),AND(D19="Wet Swale",E19="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
         <v/>
@@ -10169,7 +10429,7 @@
         <f>IFERROR(IF(I19=0,"",G19/I19),"")</f>
         <v/>
       </c>
-      <c r="M19" s="16">
+      <c r="M19" s="22">
         <f>IFERROR(IF(L19="","",IF(L19&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
@@ -10190,18 +10450,21 @@
         <v/>
       </c>
       <c r="U19" s="4" t="n"/>
-      <c r="V19" s="4" t="n"/>
+      <c r="V19" s="4">
+        <f>IFERROR(IF(OR(E19="Enhanced",E19="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C19,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C19,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C19,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C19,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="W19" s="16">
         <f>IFERROR(P19*(Q19*R19+S19*T19+U19),0)</f>
         <v/>
       </c>
-      <c r="X19" s="16">
+      <c r="X19" s="22">
         <f>IFERROR(IF(V19=0,"",(Q19+S19)/V19),"")</f>
         <v/>
       </c>
       <c r="Y19" s="4" t="n"/>
       <c r="Z19" s="4" t="n"/>
-      <c r="AA19" s="16">
+      <c r="AA19" s="22">
         <f>IFERROR(Y19+Z19,0)</f>
         <v/>
       </c>
@@ -10211,7 +10474,7 @@
       <c r="AE19" s="4" t="n"/>
       <c r="AF19" s="4" t="n"/>
       <c r="AG19" s="4" t="n"/>
-      <c r="AH19" s="16">
+      <c r="AH19" s="22">
         <f>IFERROR(AB19*INDEX(PARAMS_Trees,1,3)+AC19*INDEX(PARAMS_Trees,2,3)+AD19*INDEX(PARAMS_Trees,3,3)+AE19*INDEX(PARAMS_Trees,4,3)+AF19*INDEX(PARAMS_Trees,5,3)+AG19*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
       </c>
@@ -10231,7 +10494,7 @@
         <f>IFERROR(VLOOKUP(C19,'CDA'!$A$58:$D$67,4,FALSE),0)</f>
         <v/>
       </c>
-      <c r="AM19" s="16">
+      <c r="AM19" s="22">
         <f>IFERROR(IF(AL19=0,AK19,MIN(AK19,AL19)),0)</f>
         <v/>
       </c>
@@ -10241,11 +10504,14 @@
       <c r="B20" s="4" t="n"/>
       <c r="C20" s="4" t="n"/>
       <c r="D20" s="4" t="n"/>
-      <c r="E20" s="4" t="n"/>
+      <c r="E20" s="21" t="n"/>
       <c r="F20" s="4" t="n"/>
       <c r="G20" s="4" t="n"/>
       <c r="H20" s="4" t="n"/>
-      <c r="I20" s="4" t="n"/>
+      <c r="I20" s="4">
+        <f>IFERROR(IF(OR(E20="Enhanced",E20="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C20,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C20,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C20,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C20,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="J20" s="16">
         <f>IFERROR(IFS(AND(D20="Permeable Pavement",E20="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D20="Permeable Pavement",E20="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D20="Bioretention",E20="Standard"),INDEX(PARAMS_BMP,3,5),AND(D20="Bioretention",E20="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D20="Bioretention",E20="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D20="Dry Swale",E20="—"),INDEX(PARAMS_BMP,6,5),AND(D20="Wet Swale",E20="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
         <v/>
@@ -10258,7 +10524,7 @@
         <f>IFERROR(IF(I20=0,"",G20/I20),"")</f>
         <v/>
       </c>
-      <c r="M20" s="16">
+      <c r="M20" s="22">
         <f>IFERROR(IF(L20="","",IF(L20&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
@@ -10279,18 +10545,21 @@
         <v/>
       </c>
       <c r="U20" s="4" t="n"/>
-      <c r="V20" s="4" t="n"/>
+      <c r="V20" s="4">
+        <f>IFERROR(IF(OR(E20="Enhanced",E20="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C20,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C20,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C20,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C20,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="W20" s="16">
         <f>IFERROR(P20*(Q20*R20+S20*T20+U20),0)</f>
         <v/>
       </c>
-      <c r="X20" s="16">
+      <c r="X20" s="22">
         <f>IFERROR(IF(V20=0,"",(Q20+S20)/V20),"")</f>
         <v/>
       </c>
       <c r="Y20" s="4" t="n"/>
       <c r="Z20" s="4" t="n"/>
-      <c r="AA20" s="16">
+      <c r="AA20" s="22">
         <f>IFERROR(Y20+Z20,0)</f>
         <v/>
       </c>
@@ -10300,7 +10569,7 @@
       <c r="AE20" s="4" t="n"/>
       <c r="AF20" s="4" t="n"/>
       <c r="AG20" s="4" t="n"/>
-      <c r="AH20" s="16">
+      <c r="AH20" s="22">
         <f>IFERROR(AB20*INDEX(PARAMS_Trees,1,3)+AC20*INDEX(PARAMS_Trees,2,3)+AD20*INDEX(PARAMS_Trees,3,3)+AE20*INDEX(PARAMS_Trees,4,3)+AF20*INDEX(PARAMS_Trees,5,3)+AG20*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
       </c>
@@ -10320,7 +10589,7 @@
         <f>IFERROR(VLOOKUP(C20,'CDA'!$A$58:$D$67,4,FALSE),0)</f>
         <v/>
       </c>
-      <c r="AM20" s="16">
+      <c r="AM20" s="22">
         <f>IFERROR(IF(AL20=0,AK20,MIN(AK20,AL20)),0)</f>
         <v/>
       </c>
@@ -10330,11 +10599,14 @@
       <c r="B21" s="4" t="n"/>
       <c r="C21" s="4" t="n"/>
       <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="n"/>
+      <c r="E21" s="21" t="n"/>
       <c r="F21" s="4" t="n"/>
       <c r="G21" s="4" t="n"/>
       <c r="H21" s="4" t="n"/>
-      <c r="I21" s="4" t="n"/>
+      <c r="I21" s="4">
+        <f>IFERROR(IF(OR(E21="Enhanced",E21="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C21,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C21,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C21,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C21,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="J21" s="16">
         <f>IFERROR(IFS(AND(D21="Permeable Pavement",E21="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D21="Permeable Pavement",E21="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D21="Bioretention",E21="Standard"),INDEX(PARAMS_BMP,3,5),AND(D21="Bioretention",E21="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D21="Bioretention",E21="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D21="Dry Swale",E21="—"),INDEX(PARAMS_BMP,6,5),AND(D21="Wet Swale",E21="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
         <v/>
@@ -10347,7 +10619,7 @@
         <f>IFERROR(IF(I21=0,"",G21/I21),"")</f>
         <v/>
       </c>
-      <c r="M21" s="16">
+      <c r="M21" s="22">
         <f>IFERROR(IF(L21="","",IF(L21&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
@@ -10368,18 +10640,21 @@
         <v/>
       </c>
       <c r="U21" s="4" t="n"/>
-      <c r="V21" s="4" t="n"/>
+      <c r="V21" s="4">
+        <f>IFERROR(IF(OR(E21="Enhanced",E21="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C21,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C21,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C21,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C21,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="W21" s="16">
         <f>IFERROR(P21*(Q21*R21+S21*T21+U21),0)</f>
         <v/>
       </c>
-      <c r="X21" s="16">
+      <c r="X21" s="22">
         <f>IFERROR(IF(V21=0,"",(Q21+S21)/V21),"")</f>
         <v/>
       </c>
       <c r="Y21" s="4" t="n"/>
       <c r="Z21" s="4" t="n"/>
-      <c r="AA21" s="16">
+      <c r="AA21" s="22">
         <f>IFERROR(Y21+Z21,0)</f>
         <v/>
       </c>
@@ -10389,7 +10664,7 @@
       <c r="AE21" s="4" t="n"/>
       <c r="AF21" s="4" t="n"/>
       <c r="AG21" s="4" t="n"/>
-      <c r="AH21" s="16">
+      <c r="AH21" s="22">
         <f>IFERROR(AB21*INDEX(PARAMS_Trees,1,3)+AC21*INDEX(PARAMS_Trees,2,3)+AD21*INDEX(PARAMS_Trees,3,3)+AE21*INDEX(PARAMS_Trees,4,3)+AF21*INDEX(PARAMS_Trees,5,3)+AG21*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
       </c>
@@ -10409,7 +10684,7 @@
         <f>IFERROR(VLOOKUP(C21,'CDA'!$A$58:$D$67,4,FALSE),0)</f>
         <v/>
       </c>
-      <c r="AM21" s="16">
+      <c r="AM21" s="22">
         <f>IFERROR(IF(AL21=0,AK21,MIN(AK21,AL21)),0)</f>
         <v/>
       </c>
@@ -10419,11 +10694,14 @@
       <c r="B22" s="4" t="n"/>
       <c r="C22" s="4" t="n"/>
       <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="n"/>
+      <c r="E22" s="21" t="n"/>
       <c r="F22" s="4" t="n"/>
       <c r="G22" s="4" t="n"/>
       <c r="H22" s="4" t="n"/>
-      <c r="I22" s="4" t="n"/>
+      <c r="I22" s="4">
+        <f>IFERROR(IF(OR(E22="Enhanced",E22="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C22,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C22,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C22,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C22,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="J22" s="16">
         <f>IFERROR(IFS(AND(D22="Permeable Pavement",E22="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D22="Permeable Pavement",E22="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D22="Bioretention",E22="Standard"),INDEX(PARAMS_BMP,3,5),AND(D22="Bioretention",E22="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D22="Bioretention",E22="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D22="Dry Swale",E22="—"),INDEX(PARAMS_BMP,6,5),AND(D22="Wet Swale",E22="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
         <v/>
@@ -10436,7 +10714,7 @@
         <f>IFERROR(IF(I22=0,"",G22/I22),"")</f>
         <v/>
       </c>
-      <c r="M22" s="16">
+      <c r="M22" s="22">
         <f>IFERROR(IF(L22="","",IF(L22&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
@@ -10457,18 +10735,21 @@
         <v/>
       </c>
       <c r="U22" s="4" t="n"/>
-      <c r="V22" s="4" t="n"/>
+      <c r="V22" s="4">
+        <f>IFERROR(IF(OR(E22="Enhanced",E22="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C22,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C22,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C22,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C22,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="W22" s="16">
         <f>IFERROR(P22*(Q22*R22+S22*T22+U22),0)</f>
         <v/>
       </c>
-      <c r="X22" s="16">
+      <c r="X22" s="22">
         <f>IFERROR(IF(V22=0,"",(Q22+S22)/V22),"")</f>
         <v/>
       </c>
       <c r="Y22" s="4" t="n"/>
       <c r="Z22" s="4" t="n"/>
-      <c r="AA22" s="16">
+      <c r="AA22" s="22">
         <f>IFERROR(Y22+Z22,0)</f>
         <v/>
       </c>
@@ -10478,7 +10759,7 @@
       <c r="AE22" s="4" t="n"/>
       <c r="AF22" s="4" t="n"/>
       <c r="AG22" s="4" t="n"/>
-      <c r="AH22" s="16">
+      <c r="AH22" s="22">
         <f>IFERROR(AB22*INDEX(PARAMS_Trees,1,3)+AC22*INDEX(PARAMS_Trees,2,3)+AD22*INDEX(PARAMS_Trees,3,3)+AE22*INDEX(PARAMS_Trees,4,3)+AF22*INDEX(PARAMS_Trees,5,3)+AG22*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
       </c>
@@ -10498,7 +10779,7 @@
         <f>IFERROR(VLOOKUP(C22,'CDA'!$A$58:$D$67,4,FALSE),0)</f>
         <v/>
       </c>
-      <c r="AM22" s="16">
+      <c r="AM22" s="22">
         <f>IFERROR(IF(AL22=0,AK22,MIN(AK22,AL22)),0)</f>
         <v/>
       </c>
@@ -10508,11 +10789,14 @@
       <c r="B23" s="4" t="n"/>
       <c r="C23" s="4" t="n"/>
       <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="n"/>
+      <c r="E23" s="21" t="n"/>
       <c r="F23" s="4" t="n"/>
       <c r="G23" s="4" t="n"/>
       <c r="H23" s="4" t="n"/>
-      <c r="I23" s="4" t="n"/>
+      <c r="I23" s="4">
+        <f>IFERROR(IF(OR(E23="Enhanced",E23="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C23,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C23,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C23,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C23,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="J23" s="16">
         <f>IFERROR(IFS(AND(D23="Permeable Pavement",E23="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D23="Permeable Pavement",E23="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D23="Bioretention",E23="Standard"),INDEX(PARAMS_BMP,3,5),AND(D23="Bioretention",E23="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D23="Bioretention",E23="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D23="Dry Swale",E23="—"),INDEX(PARAMS_BMP,6,5),AND(D23="Wet Swale",E23="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
         <v/>
@@ -10525,7 +10809,7 @@
         <f>IFERROR(IF(I23=0,"",G23/I23),"")</f>
         <v/>
       </c>
-      <c r="M23" s="16">
+      <c r="M23" s="22">
         <f>IFERROR(IF(L23="","",IF(L23&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
@@ -10546,18 +10830,21 @@
         <v/>
       </c>
       <c r="U23" s="4" t="n"/>
-      <c r="V23" s="4" t="n"/>
+      <c r="V23" s="4">
+        <f>IFERROR(IF(OR(E23="Enhanced",E23="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C23,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C23,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C23,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C23,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="W23" s="16">
         <f>IFERROR(P23*(Q23*R23+S23*T23+U23),0)</f>
         <v/>
       </c>
-      <c r="X23" s="16">
+      <c r="X23" s="22">
         <f>IFERROR(IF(V23=0,"",(Q23+S23)/V23),"")</f>
         <v/>
       </c>
       <c r="Y23" s="4" t="n"/>
       <c r="Z23" s="4" t="n"/>
-      <c r="AA23" s="16">
+      <c r="AA23" s="22">
         <f>IFERROR(Y23+Z23,0)</f>
         <v/>
       </c>
@@ -10567,7 +10854,7 @@
       <c r="AE23" s="4" t="n"/>
       <c r="AF23" s="4" t="n"/>
       <c r="AG23" s="4" t="n"/>
-      <c r="AH23" s="16">
+      <c r="AH23" s="22">
         <f>IFERROR(AB23*INDEX(PARAMS_Trees,1,3)+AC23*INDEX(PARAMS_Trees,2,3)+AD23*INDEX(PARAMS_Trees,3,3)+AE23*INDEX(PARAMS_Trees,4,3)+AF23*INDEX(PARAMS_Trees,5,3)+AG23*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
       </c>
@@ -10587,7 +10874,7 @@
         <f>IFERROR(VLOOKUP(C23,'CDA'!$A$58:$D$67,4,FALSE),0)</f>
         <v/>
       </c>
-      <c r="AM23" s="16">
+      <c r="AM23" s="22">
         <f>IFERROR(IF(AL23=0,AK23,MIN(AK23,AL23)),0)</f>
         <v/>
       </c>
@@ -10597,11 +10884,14 @@
       <c r="B24" s="4" t="n"/>
       <c r="C24" s="4" t="n"/>
       <c r="D24" s="4" t="n"/>
-      <c r="E24" s="4" t="n"/>
+      <c r="E24" s="21" t="n"/>
       <c r="F24" s="4" t="n"/>
       <c r="G24" s="4" t="n"/>
       <c r="H24" s="4" t="n"/>
-      <c r="I24" s="4" t="n"/>
+      <c r="I24" s="4">
+        <f>IFERROR(IF(OR(E24="Enhanced",E24="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C24,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C24,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C24,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C24,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="J24" s="16">
         <f>IFERROR(IFS(AND(D24="Permeable Pavement",E24="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D24="Permeable Pavement",E24="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D24="Bioretention",E24="Standard"),INDEX(PARAMS_BMP,3,5),AND(D24="Bioretention",E24="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D24="Bioretention",E24="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D24="Dry Swale",E24="—"),INDEX(PARAMS_BMP,6,5),AND(D24="Wet Swale",E24="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
         <v/>
@@ -10614,7 +10904,7 @@
         <f>IFERROR(IF(I24=0,"",G24/I24),"")</f>
         <v/>
       </c>
-      <c r="M24" s="16">
+      <c r="M24" s="22">
         <f>IFERROR(IF(L24="","",IF(L24&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
@@ -10635,18 +10925,21 @@
         <v/>
       </c>
       <c r="U24" s="4" t="n"/>
-      <c r="V24" s="4" t="n"/>
+      <c r="V24" s="4">
+        <f>IFERROR(IF(OR(E24="Enhanced",E24="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C24,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C24,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C24,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C24,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="W24" s="16">
         <f>IFERROR(P24*(Q24*R24+S24*T24+U24),0)</f>
         <v/>
       </c>
-      <c r="X24" s="16">
+      <c r="X24" s="22">
         <f>IFERROR(IF(V24=0,"",(Q24+S24)/V24),"")</f>
         <v/>
       </c>
       <c r="Y24" s="4" t="n"/>
       <c r="Z24" s="4" t="n"/>
-      <c r="AA24" s="16">
+      <c r="AA24" s="22">
         <f>IFERROR(Y24+Z24,0)</f>
         <v/>
       </c>
@@ -10656,7 +10949,7 @@
       <c r="AE24" s="4" t="n"/>
       <c r="AF24" s="4" t="n"/>
       <c r="AG24" s="4" t="n"/>
-      <c r="AH24" s="16">
+      <c r="AH24" s="22">
         <f>IFERROR(AB24*INDEX(PARAMS_Trees,1,3)+AC24*INDEX(PARAMS_Trees,2,3)+AD24*INDEX(PARAMS_Trees,3,3)+AE24*INDEX(PARAMS_Trees,4,3)+AF24*INDEX(PARAMS_Trees,5,3)+AG24*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
       </c>
@@ -10676,7 +10969,7 @@
         <f>IFERROR(VLOOKUP(C24,'CDA'!$A$58:$D$67,4,FALSE),0)</f>
         <v/>
       </c>
-      <c r="AM24" s="16">
+      <c r="AM24" s="22">
         <f>IFERROR(IF(AL24=0,AK24,MIN(AK24,AL24)),0)</f>
         <v/>
       </c>
@@ -10686,11 +10979,14 @@
       <c r="B25" s="4" t="n"/>
       <c r="C25" s="4" t="n"/>
       <c r="D25" s="4" t="n"/>
-      <c r="E25" s="4" t="n"/>
+      <c r="E25" s="21" t="n"/>
       <c r="F25" s="4" t="n"/>
       <c r="G25" s="4" t="n"/>
       <c r="H25" s="4" t="n"/>
-      <c r="I25" s="4" t="n"/>
+      <c r="I25" s="4">
+        <f>IFERROR(IF(OR(E25="Enhanced",E25="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C25,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C25,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C25,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C25,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="J25" s="16">
         <f>IFERROR(IFS(AND(D25="Permeable Pavement",E25="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D25="Permeable Pavement",E25="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D25="Bioretention",E25="Standard"),INDEX(PARAMS_BMP,3,5),AND(D25="Bioretention",E25="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D25="Bioretention",E25="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D25="Dry Swale",E25="—"),INDEX(PARAMS_BMP,6,5),AND(D25="Wet Swale",E25="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
         <v/>
@@ -10703,7 +10999,7 @@
         <f>IFERROR(IF(I25=0,"",G25/I25),"")</f>
         <v/>
       </c>
-      <c r="M25" s="16">
+      <c r="M25" s="22">
         <f>IFERROR(IF(L25="","",IF(L25&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
@@ -10724,18 +11020,21 @@
         <v/>
       </c>
       <c r="U25" s="4" t="n"/>
-      <c r="V25" s="4" t="n"/>
+      <c r="V25" s="4">
+        <f>IFERROR(IF(OR(E25="Enhanced",E25="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C25,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C25,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C25,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C25,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="W25" s="16">
         <f>IFERROR(P25*(Q25*R25+S25*T25+U25),0)</f>
         <v/>
       </c>
-      <c r="X25" s="16">
+      <c r="X25" s="22">
         <f>IFERROR(IF(V25=0,"",(Q25+S25)/V25),"")</f>
         <v/>
       </c>
       <c r="Y25" s="4" t="n"/>
       <c r="Z25" s="4" t="n"/>
-      <c r="AA25" s="16">
+      <c r="AA25" s="22">
         <f>IFERROR(Y25+Z25,0)</f>
         <v/>
       </c>
@@ -10745,7 +11044,7 @@
       <c r="AE25" s="4" t="n"/>
       <c r="AF25" s="4" t="n"/>
       <c r="AG25" s="4" t="n"/>
-      <c r="AH25" s="16">
+      <c r="AH25" s="22">
         <f>IFERROR(AB25*INDEX(PARAMS_Trees,1,3)+AC25*INDEX(PARAMS_Trees,2,3)+AD25*INDEX(PARAMS_Trees,3,3)+AE25*INDEX(PARAMS_Trees,4,3)+AF25*INDEX(PARAMS_Trees,5,3)+AG25*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
       </c>
@@ -10765,7 +11064,7 @@
         <f>IFERROR(VLOOKUP(C25,'CDA'!$A$58:$D$67,4,FALSE),0)</f>
         <v/>
       </c>
-      <c r="AM25" s="16">
+      <c r="AM25" s="22">
         <f>IFERROR(IF(AL25=0,AK25,MIN(AK25,AL25)),0)</f>
         <v/>
       </c>
@@ -10775,11 +11074,14 @@
       <c r="B26" s="4" t="n"/>
       <c r="C26" s="4" t="n"/>
       <c r="D26" s="4" t="n"/>
-      <c r="E26" s="4" t="n"/>
+      <c r="E26" s="21" t="n"/>
       <c r="F26" s="4" t="n"/>
       <c r="G26" s="4" t="n"/>
       <c r="H26" s="4" t="n"/>
-      <c r="I26" s="4" t="n"/>
+      <c r="I26" s="4">
+        <f>IFERROR(IF(OR(E26="Enhanced",E26="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C26,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C26,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C26,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C26,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="J26" s="16">
         <f>IFERROR(IFS(AND(D26="Permeable Pavement",E26="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D26="Permeable Pavement",E26="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D26="Bioretention",E26="Standard"),INDEX(PARAMS_BMP,3,5),AND(D26="Bioretention",E26="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D26="Bioretention",E26="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D26="Dry Swale",E26="—"),INDEX(PARAMS_BMP,6,5),AND(D26="Wet Swale",E26="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
         <v/>
@@ -10792,7 +11094,7 @@
         <f>IFERROR(IF(I26=0,"",G26/I26),"")</f>
         <v/>
       </c>
-      <c r="M26" s="16">
+      <c r="M26" s="22">
         <f>IFERROR(IF(L26="","",IF(L26&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
@@ -10813,18 +11115,21 @@
         <v/>
       </c>
       <c r="U26" s="4" t="n"/>
-      <c r="V26" s="4" t="n"/>
+      <c r="V26" s="4">
+        <f>IFERROR(IF(OR(E26="Enhanced",E26="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C26,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C26,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C26,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C26,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="W26" s="16">
         <f>IFERROR(P26*(Q26*R26+S26*T26+U26),0)</f>
         <v/>
       </c>
-      <c r="X26" s="16">
+      <c r="X26" s="22">
         <f>IFERROR(IF(V26=0,"",(Q26+S26)/V26),"")</f>
         <v/>
       </c>
       <c r="Y26" s="4" t="n"/>
       <c r="Z26" s="4" t="n"/>
-      <c r="AA26" s="16">
+      <c r="AA26" s="22">
         <f>IFERROR(Y26+Z26,0)</f>
         <v/>
       </c>
@@ -10834,7 +11139,7 @@
       <c r="AE26" s="4" t="n"/>
       <c r="AF26" s="4" t="n"/>
       <c r="AG26" s="4" t="n"/>
-      <c r="AH26" s="16">
+      <c r="AH26" s="22">
         <f>IFERROR(AB26*INDEX(PARAMS_Trees,1,3)+AC26*INDEX(PARAMS_Trees,2,3)+AD26*INDEX(PARAMS_Trees,3,3)+AE26*INDEX(PARAMS_Trees,4,3)+AF26*INDEX(PARAMS_Trees,5,3)+AG26*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
       </c>
@@ -10854,7 +11159,7 @@
         <f>IFERROR(VLOOKUP(C26,'CDA'!$A$58:$D$67,4,FALSE),0)</f>
         <v/>
       </c>
-      <c r="AM26" s="16">
+      <c r="AM26" s="22">
         <f>IFERROR(IF(AL26=0,AK26,MIN(AK26,AL26)),0)</f>
         <v/>
       </c>
@@ -10864,11 +11169,14 @@
       <c r="B27" s="4" t="n"/>
       <c r="C27" s="4" t="n"/>
       <c r="D27" s="4" t="n"/>
-      <c r="E27" s="4" t="n"/>
+      <c r="E27" s="21" t="n"/>
       <c r="F27" s="4" t="n"/>
       <c r="G27" s="4" t="n"/>
       <c r="H27" s="4" t="n"/>
-      <c r="I27" s="4" t="n"/>
+      <c r="I27" s="4">
+        <f>IFERROR(IF(OR(E27="Enhanced",E27="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C27,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C27,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C27,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C27,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="J27" s="16">
         <f>IFERROR(IFS(AND(D27="Permeable Pavement",E27="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D27="Permeable Pavement",E27="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D27="Bioretention",E27="Standard"),INDEX(PARAMS_BMP,3,5),AND(D27="Bioretention",E27="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D27="Bioretention",E27="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D27="Dry Swale",E27="—"),INDEX(PARAMS_BMP,6,5),AND(D27="Wet Swale",E27="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
         <v/>
@@ -10881,7 +11189,7 @@
         <f>IFERROR(IF(I27=0,"",G27/I27),"")</f>
         <v/>
       </c>
-      <c r="M27" s="16">
+      <c r="M27" s="22">
         <f>IFERROR(IF(L27="","",IF(L27&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
@@ -10902,18 +11210,21 @@
         <v/>
       </c>
       <c r="U27" s="4" t="n"/>
-      <c r="V27" s="4" t="n"/>
+      <c r="V27" s="4">
+        <f>IFERROR(IF(OR(E27="Enhanced",E27="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C27,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C27,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C27,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C27,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="W27" s="16">
         <f>IFERROR(P27*(Q27*R27+S27*T27+U27),0)</f>
         <v/>
       </c>
-      <c r="X27" s="16">
+      <c r="X27" s="22">
         <f>IFERROR(IF(V27=0,"",(Q27+S27)/V27),"")</f>
         <v/>
       </c>
       <c r="Y27" s="4" t="n"/>
       <c r="Z27" s="4" t="n"/>
-      <c r="AA27" s="16">
+      <c r="AA27" s="22">
         <f>IFERROR(Y27+Z27,0)</f>
         <v/>
       </c>
@@ -10923,7 +11234,7 @@
       <c r="AE27" s="4" t="n"/>
       <c r="AF27" s="4" t="n"/>
       <c r="AG27" s="4" t="n"/>
-      <c r="AH27" s="16">
+      <c r="AH27" s="22">
         <f>IFERROR(AB27*INDEX(PARAMS_Trees,1,3)+AC27*INDEX(PARAMS_Trees,2,3)+AD27*INDEX(PARAMS_Trees,3,3)+AE27*INDEX(PARAMS_Trees,4,3)+AF27*INDEX(PARAMS_Trees,5,3)+AG27*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
       </c>
@@ -10943,7 +11254,7 @@
         <f>IFERROR(VLOOKUP(C27,'CDA'!$A$58:$D$67,4,FALSE),0)</f>
         <v/>
       </c>
-      <c r="AM27" s="16">
+      <c r="AM27" s="22">
         <f>IFERROR(IF(AL27=0,AK27,MIN(AK27,AL27)),0)</f>
         <v/>
       </c>
@@ -10953,11 +11264,14 @@
       <c r="B28" s="4" t="n"/>
       <c r="C28" s="4" t="n"/>
       <c r="D28" s="4" t="n"/>
-      <c r="E28" s="4" t="n"/>
+      <c r="E28" s="21" t="n"/>
       <c r="F28" s="4" t="n"/>
       <c r="G28" s="4" t="n"/>
       <c r="H28" s="4" t="n"/>
-      <c r="I28" s="4" t="n"/>
+      <c r="I28" s="4">
+        <f>IFERROR(IF(OR(E28="Enhanced",E28="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C28,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C28,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C28,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C28,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="J28" s="16">
         <f>IFERROR(IFS(AND(D28="Permeable Pavement",E28="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D28="Permeable Pavement",E28="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D28="Bioretention",E28="Standard"),INDEX(PARAMS_BMP,3,5),AND(D28="Bioretention",E28="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D28="Bioretention",E28="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D28="Dry Swale",E28="—"),INDEX(PARAMS_BMP,6,5),AND(D28="Wet Swale",E28="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
         <v/>
@@ -10970,7 +11284,7 @@
         <f>IFERROR(IF(I28=0,"",G28/I28),"")</f>
         <v/>
       </c>
-      <c r="M28" s="16">
+      <c r="M28" s="22">
         <f>IFERROR(IF(L28="","",IF(L28&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
@@ -10991,18 +11305,21 @@
         <v/>
       </c>
       <c r="U28" s="4" t="n"/>
-      <c r="V28" s="4" t="n"/>
+      <c r="V28" s="4">
+        <f>IFERROR(IF(OR(E28="Enhanced",E28="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C28,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C28,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C28,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C28,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="W28" s="16">
         <f>IFERROR(P28*(Q28*R28+S28*T28+U28),0)</f>
         <v/>
       </c>
-      <c r="X28" s="16">
+      <c r="X28" s="22">
         <f>IFERROR(IF(V28=0,"",(Q28+S28)/V28),"")</f>
         <v/>
       </c>
       <c r="Y28" s="4" t="n"/>
       <c r="Z28" s="4" t="n"/>
-      <c r="AA28" s="16">
+      <c r="AA28" s="22">
         <f>IFERROR(Y28+Z28,0)</f>
         <v/>
       </c>
@@ -11012,7 +11329,7 @@
       <c r="AE28" s="4" t="n"/>
       <c r="AF28" s="4" t="n"/>
       <c r="AG28" s="4" t="n"/>
-      <c r="AH28" s="16">
+      <c r="AH28" s="22">
         <f>IFERROR(AB28*INDEX(PARAMS_Trees,1,3)+AC28*INDEX(PARAMS_Trees,2,3)+AD28*INDEX(PARAMS_Trees,3,3)+AE28*INDEX(PARAMS_Trees,4,3)+AF28*INDEX(PARAMS_Trees,5,3)+AG28*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
       </c>
@@ -11032,7 +11349,7 @@
         <f>IFERROR(VLOOKUP(C28,'CDA'!$A$58:$D$67,4,FALSE),0)</f>
         <v/>
       </c>
-      <c r="AM28" s="16">
+      <c r="AM28" s="22">
         <f>IFERROR(IF(AL28=0,AK28,MIN(AK28,AL28)),0)</f>
         <v/>
       </c>
@@ -11042,11 +11359,14 @@
       <c r="B29" s="4" t="n"/>
       <c r="C29" s="4" t="n"/>
       <c r="D29" s="4" t="n"/>
-      <c r="E29" s="4" t="n"/>
+      <c r="E29" s="21" t="n"/>
       <c r="F29" s="4" t="n"/>
       <c r="G29" s="4" t="n"/>
       <c r="H29" s="4" t="n"/>
-      <c r="I29" s="4" t="n"/>
+      <c r="I29" s="4">
+        <f>IFERROR(IF(OR(E29="Enhanced",E29="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C29,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C29,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C29,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C29,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="J29" s="16">
         <f>IFERROR(IFS(AND(D29="Permeable Pavement",E29="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D29="Permeable Pavement",E29="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D29="Bioretention",E29="Standard"),INDEX(PARAMS_BMP,3,5),AND(D29="Bioretention",E29="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D29="Bioretention",E29="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D29="Dry Swale",E29="—"),INDEX(PARAMS_BMP,6,5),AND(D29="Wet Swale",E29="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
         <v/>
@@ -11059,7 +11379,7 @@
         <f>IFERROR(IF(I29=0,"",G29/I29),"")</f>
         <v/>
       </c>
-      <c r="M29" s="16">
+      <c r="M29" s="22">
         <f>IFERROR(IF(L29="","",IF(L29&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
@@ -11080,18 +11400,21 @@
         <v/>
       </c>
       <c r="U29" s="4" t="n"/>
-      <c r="V29" s="4" t="n"/>
+      <c r="V29" s="4">
+        <f>IFERROR(IF(OR(E29="Enhanced",E29="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C29,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C29,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C29,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C29,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="W29" s="16">
         <f>IFERROR(P29*(Q29*R29+S29*T29+U29),0)</f>
         <v/>
       </c>
-      <c r="X29" s="16">
+      <c r="X29" s="22">
         <f>IFERROR(IF(V29=0,"",(Q29+S29)/V29),"")</f>
         <v/>
       </c>
       <c r="Y29" s="4" t="n"/>
       <c r="Z29" s="4" t="n"/>
-      <c r="AA29" s="16">
+      <c r="AA29" s="22">
         <f>IFERROR(Y29+Z29,0)</f>
         <v/>
       </c>
@@ -11101,7 +11424,7 @@
       <c r="AE29" s="4" t="n"/>
       <c r="AF29" s="4" t="n"/>
       <c r="AG29" s="4" t="n"/>
-      <c r="AH29" s="16">
+      <c r="AH29" s="22">
         <f>IFERROR(AB29*INDEX(PARAMS_Trees,1,3)+AC29*INDEX(PARAMS_Trees,2,3)+AD29*INDEX(PARAMS_Trees,3,3)+AE29*INDEX(PARAMS_Trees,4,3)+AF29*INDEX(PARAMS_Trees,5,3)+AG29*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
       </c>
@@ -11121,7 +11444,7 @@
         <f>IFERROR(VLOOKUP(C29,'CDA'!$A$58:$D$67,4,FALSE),0)</f>
         <v/>
       </c>
-      <c r="AM29" s="16">
+      <c r="AM29" s="22">
         <f>IFERROR(IF(AL29=0,AK29,MIN(AK29,AL29)),0)</f>
         <v/>
       </c>
@@ -11131,11 +11454,14 @@
       <c r="B30" s="4" t="n"/>
       <c r="C30" s="4" t="n"/>
       <c r="D30" s="4" t="n"/>
-      <c r="E30" s="4" t="n"/>
+      <c r="E30" s="21" t="n"/>
       <c r="F30" s="4" t="n"/>
       <c r="G30" s="4" t="n"/>
       <c r="H30" s="4" t="n"/>
-      <c r="I30" s="4" t="n"/>
+      <c r="I30" s="4">
+        <f>IFERROR(IF(OR(E30="Enhanced",E30="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C30,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C30,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C30,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C30,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="J30" s="16">
         <f>IFERROR(IFS(AND(D30="Permeable Pavement",E30="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D30="Permeable Pavement",E30="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D30="Bioretention",E30="Standard"),INDEX(PARAMS_BMP,3,5),AND(D30="Bioretention",E30="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D30="Bioretention",E30="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D30="Dry Swale",E30="—"),INDEX(PARAMS_BMP,6,5),AND(D30="Wet Swale",E30="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
         <v/>
@@ -11148,7 +11474,7 @@
         <f>IFERROR(IF(I30=0,"",G30/I30),"")</f>
         <v/>
       </c>
-      <c r="M30" s="16">
+      <c r="M30" s="22">
         <f>IFERROR(IF(L30="","",IF(L30&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
@@ -11169,18 +11495,21 @@
         <v/>
       </c>
       <c r="U30" s="4" t="n"/>
-      <c r="V30" s="4" t="n"/>
+      <c r="V30" s="4">
+        <f>IFERROR(IF(OR(E30="Enhanced",E30="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C30,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C30,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C30,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C30,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="W30" s="16">
         <f>IFERROR(P30*(Q30*R30+S30*T30+U30),0)</f>
         <v/>
       </c>
-      <c r="X30" s="16">
+      <c r="X30" s="22">
         <f>IFERROR(IF(V30=0,"",(Q30+S30)/V30),"")</f>
         <v/>
       </c>
       <c r="Y30" s="4" t="n"/>
       <c r="Z30" s="4" t="n"/>
-      <c r="AA30" s="16">
+      <c r="AA30" s="22">
         <f>IFERROR(Y30+Z30,0)</f>
         <v/>
       </c>
@@ -11190,7 +11519,7 @@
       <c r="AE30" s="4" t="n"/>
       <c r="AF30" s="4" t="n"/>
       <c r="AG30" s="4" t="n"/>
-      <c r="AH30" s="16">
+      <c r="AH30" s="22">
         <f>IFERROR(AB30*INDEX(PARAMS_Trees,1,3)+AC30*INDEX(PARAMS_Trees,2,3)+AD30*INDEX(PARAMS_Trees,3,3)+AE30*INDEX(PARAMS_Trees,4,3)+AF30*INDEX(PARAMS_Trees,5,3)+AG30*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
       </c>
@@ -11210,7 +11539,7 @@
         <f>IFERROR(VLOOKUP(C30,'CDA'!$A$58:$D$67,4,FALSE),0)</f>
         <v/>
       </c>
-      <c r="AM30" s="16">
+      <c r="AM30" s="22">
         <f>IFERROR(IF(AL30=0,AK30,MIN(AK30,AL30)),0)</f>
         <v/>
       </c>
@@ -11220,11 +11549,14 @@
       <c r="B31" s="4" t="n"/>
       <c r="C31" s="4" t="n"/>
       <c r="D31" s="4" t="n"/>
-      <c r="E31" s="4" t="n"/>
+      <c r="E31" s="21" t="n"/>
       <c r="F31" s="4" t="n"/>
       <c r="G31" s="4" t="n"/>
       <c r="H31" s="4" t="n"/>
-      <c r="I31" s="4" t="n"/>
+      <c r="I31" s="4">
+        <f>IFERROR(IF(OR(E31="Enhanced",E31="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C31,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C31,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C31,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C31,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="J31" s="16">
         <f>IFERROR(IFS(AND(D31="Permeable Pavement",E31="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D31="Permeable Pavement",E31="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D31="Bioretention",E31="Standard"),INDEX(PARAMS_BMP,3,5),AND(D31="Bioretention",E31="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D31="Bioretention",E31="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D31="Dry Swale",E31="—"),INDEX(PARAMS_BMP,6,5),AND(D31="Wet Swale",E31="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
         <v/>
@@ -11237,7 +11569,7 @@
         <f>IFERROR(IF(I31=0,"",G31/I31),"")</f>
         <v/>
       </c>
-      <c r="M31" s="16">
+      <c r="M31" s="22">
         <f>IFERROR(IF(L31="","",IF(L31&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
@@ -11258,18 +11590,21 @@
         <v/>
       </c>
       <c r="U31" s="4" t="n"/>
-      <c r="V31" s="4" t="n"/>
+      <c r="V31" s="4">
+        <f>IFERROR(IF(OR(E31="Enhanced",E31="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C31,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C31,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C31,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C31,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="W31" s="16">
         <f>IFERROR(P31*(Q31*R31+S31*T31+U31),0)</f>
         <v/>
       </c>
-      <c r="X31" s="16">
+      <c r="X31" s="22">
         <f>IFERROR(IF(V31=0,"",(Q31+S31)/V31),"")</f>
         <v/>
       </c>
       <c r="Y31" s="4" t="n"/>
       <c r="Z31" s="4" t="n"/>
-      <c r="AA31" s="16">
+      <c r="AA31" s="22">
         <f>IFERROR(Y31+Z31,0)</f>
         <v/>
       </c>
@@ -11279,7 +11614,7 @@
       <c r="AE31" s="4" t="n"/>
       <c r="AF31" s="4" t="n"/>
       <c r="AG31" s="4" t="n"/>
-      <c r="AH31" s="16">
+      <c r="AH31" s="22">
         <f>IFERROR(AB31*INDEX(PARAMS_Trees,1,3)+AC31*INDEX(PARAMS_Trees,2,3)+AD31*INDEX(PARAMS_Trees,3,3)+AE31*INDEX(PARAMS_Trees,4,3)+AF31*INDEX(PARAMS_Trees,5,3)+AG31*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
       </c>
@@ -11299,7 +11634,7 @@
         <f>IFERROR(VLOOKUP(C31,'CDA'!$A$58:$D$67,4,FALSE),0)</f>
         <v/>
       </c>
-      <c r="AM31" s="16">
+      <c r="AM31" s="22">
         <f>IFERROR(IF(AL31=0,AK31,MIN(AK31,AL31)),0)</f>
         <v/>
       </c>
@@ -11309,11 +11644,14 @@
       <c r="B32" s="4" t="n"/>
       <c r="C32" s="4" t="n"/>
       <c r="D32" s="4" t="n"/>
-      <c r="E32" s="4" t="n"/>
+      <c r="E32" s="21" t="n"/>
       <c r="F32" s="4" t="n"/>
       <c r="G32" s="4" t="n"/>
       <c r="H32" s="4" t="n"/>
-      <c r="I32" s="4" t="n"/>
+      <c r="I32" s="4">
+        <f>IFERROR(IF(OR(E32="Enhanced",E32="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C32,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C32,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C32,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C32,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="J32" s="16">
         <f>IFERROR(IFS(AND(D32="Permeable Pavement",E32="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D32="Permeable Pavement",E32="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D32="Bioretention",E32="Standard"),INDEX(PARAMS_BMP,3,5),AND(D32="Bioretention",E32="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D32="Bioretention",E32="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D32="Dry Swale",E32="—"),INDEX(PARAMS_BMP,6,5),AND(D32="Wet Swale",E32="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
         <v/>
@@ -11326,7 +11664,7 @@
         <f>IFERROR(IF(I32=0,"",G32/I32),"")</f>
         <v/>
       </c>
-      <c r="M32" s="16">
+      <c r="M32" s="22">
         <f>IFERROR(IF(L32="","",IF(L32&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
@@ -11347,18 +11685,21 @@
         <v/>
       </c>
       <c r="U32" s="4" t="n"/>
-      <c r="V32" s="4" t="n"/>
+      <c r="V32" s="4">
+        <f>IFERROR(IF(OR(E32="Enhanced",E32="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C32,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C32,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C32,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C32,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="W32" s="16">
         <f>IFERROR(P32*(Q32*R32+S32*T32+U32),0)</f>
         <v/>
       </c>
-      <c r="X32" s="16">
+      <c r="X32" s="22">
         <f>IFERROR(IF(V32=0,"",(Q32+S32)/V32),"")</f>
         <v/>
       </c>
       <c r="Y32" s="4" t="n"/>
       <c r="Z32" s="4" t="n"/>
-      <c r="AA32" s="16">
+      <c r="AA32" s="22">
         <f>IFERROR(Y32+Z32,0)</f>
         <v/>
       </c>
@@ -11368,7 +11709,7 @@
       <c r="AE32" s="4" t="n"/>
       <c r="AF32" s="4" t="n"/>
       <c r="AG32" s="4" t="n"/>
-      <c r="AH32" s="16">
+      <c r="AH32" s="22">
         <f>IFERROR(AB32*INDEX(PARAMS_Trees,1,3)+AC32*INDEX(PARAMS_Trees,2,3)+AD32*INDEX(PARAMS_Trees,3,3)+AE32*INDEX(PARAMS_Trees,4,3)+AF32*INDEX(PARAMS_Trees,5,3)+AG32*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
       </c>
@@ -11388,7 +11729,7 @@
         <f>IFERROR(VLOOKUP(C32,'CDA'!$A$58:$D$67,4,FALSE),0)</f>
         <v/>
       </c>
-      <c r="AM32" s="16">
+      <c r="AM32" s="22">
         <f>IFERROR(IF(AL32=0,AK32,MIN(AK32,AL32)),0)</f>
         <v/>
       </c>
@@ -11398,11 +11739,14 @@
       <c r="B33" s="4" t="n"/>
       <c r="C33" s="4" t="n"/>
       <c r="D33" s="4" t="n"/>
-      <c r="E33" s="4" t="n"/>
+      <c r="E33" s="21" t="n"/>
       <c r="F33" s="4" t="n"/>
       <c r="G33" s="4" t="n"/>
       <c r="H33" s="4" t="n"/>
-      <c r="I33" s="4" t="n"/>
+      <c r="I33" s="4">
+        <f>IFERROR(IF(OR(E33="Enhanced",E33="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C33,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C33,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C33,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C33,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="J33" s="16">
         <f>IFERROR(IFS(AND(D33="Permeable Pavement",E33="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D33="Permeable Pavement",E33="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D33="Bioretention",E33="Standard"),INDEX(PARAMS_BMP,3,5),AND(D33="Bioretention",E33="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D33="Bioretention",E33="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D33="Dry Swale",E33="—"),INDEX(PARAMS_BMP,6,5),AND(D33="Wet Swale",E33="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
         <v/>
@@ -11415,7 +11759,7 @@
         <f>IFERROR(IF(I33=0,"",G33/I33),"")</f>
         <v/>
       </c>
-      <c r="M33" s="16">
+      <c r="M33" s="22">
         <f>IFERROR(IF(L33="","",IF(L33&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
@@ -11436,18 +11780,21 @@
         <v/>
       </c>
       <c r="U33" s="4" t="n"/>
-      <c r="V33" s="4" t="n"/>
+      <c r="V33" s="4">
+        <f>IFERROR(IF(OR(E33="Enhanced",E33="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C33,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C33,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C33,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C33,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="W33" s="16">
         <f>IFERROR(P33*(Q33*R33+S33*T33+U33),0)</f>
         <v/>
       </c>
-      <c r="X33" s="16">
+      <c r="X33" s="22">
         <f>IFERROR(IF(V33=0,"",(Q33+S33)/V33),"")</f>
         <v/>
       </c>
       <c r="Y33" s="4" t="n"/>
       <c r="Z33" s="4" t="n"/>
-      <c r="AA33" s="16">
+      <c r="AA33" s="22">
         <f>IFERROR(Y33+Z33,0)</f>
         <v/>
       </c>
@@ -11457,7 +11804,7 @@
       <c r="AE33" s="4" t="n"/>
       <c r="AF33" s="4" t="n"/>
       <c r="AG33" s="4" t="n"/>
-      <c r="AH33" s="16">
+      <c r="AH33" s="22">
         <f>IFERROR(AB33*INDEX(PARAMS_Trees,1,3)+AC33*INDEX(PARAMS_Trees,2,3)+AD33*INDEX(PARAMS_Trees,3,3)+AE33*INDEX(PARAMS_Trees,4,3)+AF33*INDEX(PARAMS_Trees,5,3)+AG33*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
       </c>
@@ -11477,7 +11824,7 @@
         <f>IFERROR(VLOOKUP(C33,'CDA'!$A$58:$D$67,4,FALSE),0)</f>
         <v/>
       </c>
-      <c r="AM33" s="16">
+      <c r="AM33" s="22">
         <f>IFERROR(IF(AL33=0,AK33,MIN(AK33,AL33)),0)</f>
         <v/>
       </c>
@@ -11487,11 +11834,14 @@
       <c r="B34" s="4" t="n"/>
       <c r="C34" s="4" t="n"/>
       <c r="D34" s="4" t="n"/>
-      <c r="E34" s="4" t="n"/>
+      <c r="E34" s="21" t="n"/>
       <c r="F34" s="4" t="n"/>
       <c r="G34" s="4" t="n"/>
       <c r="H34" s="4" t="n"/>
-      <c r="I34" s="4" t="n"/>
+      <c r="I34" s="4">
+        <f>IFERROR(IF(OR(E34="Enhanced",E34="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C34,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C34,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C34,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C34,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="J34" s="16">
         <f>IFERROR(IFS(AND(D34="Permeable Pavement",E34="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D34="Permeable Pavement",E34="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D34="Bioretention",E34="Standard"),INDEX(PARAMS_BMP,3,5),AND(D34="Bioretention",E34="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D34="Bioretention",E34="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D34="Dry Swale",E34="—"),INDEX(PARAMS_BMP,6,5),AND(D34="Wet Swale",E34="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
         <v/>
@@ -11504,7 +11854,7 @@
         <f>IFERROR(IF(I34=0,"",G34/I34),"")</f>
         <v/>
       </c>
-      <c r="M34" s="16">
+      <c r="M34" s="22">
         <f>IFERROR(IF(L34="","",IF(L34&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
@@ -11525,18 +11875,21 @@
         <v/>
       </c>
       <c r="U34" s="4" t="n"/>
-      <c r="V34" s="4" t="n"/>
+      <c r="V34" s="4">
+        <f>IFERROR(IF(OR(E34="Enhanced",E34="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C34,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C34,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C34,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C34,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="W34" s="16">
         <f>IFERROR(P34*(Q34*R34+S34*T34+U34),0)</f>
         <v/>
       </c>
-      <c r="X34" s="16">
+      <c r="X34" s="22">
         <f>IFERROR(IF(V34=0,"",(Q34+S34)/V34),"")</f>
         <v/>
       </c>
       <c r="Y34" s="4" t="n"/>
       <c r="Z34" s="4" t="n"/>
-      <c r="AA34" s="16">
+      <c r="AA34" s="22">
         <f>IFERROR(Y34+Z34,0)</f>
         <v/>
       </c>
@@ -11546,7 +11899,7 @@
       <c r="AE34" s="4" t="n"/>
       <c r="AF34" s="4" t="n"/>
       <c r="AG34" s="4" t="n"/>
-      <c r="AH34" s="16">
+      <c r="AH34" s="22">
         <f>IFERROR(AB34*INDEX(PARAMS_Trees,1,3)+AC34*INDEX(PARAMS_Trees,2,3)+AD34*INDEX(PARAMS_Trees,3,3)+AE34*INDEX(PARAMS_Trees,4,3)+AF34*INDEX(PARAMS_Trees,5,3)+AG34*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
       </c>
@@ -11566,7 +11919,7 @@
         <f>IFERROR(VLOOKUP(C34,'CDA'!$A$58:$D$67,4,FALSE),0)</f>
         <v/>
       </c>
-      <c r="AM34" s="16">
+      <c r="AM34" s="22">
         <f>IFERROR(IF(AL34=0,AK34,MIN(AK34,AL34)),0)</f>
         <v/>
       </c>
@@ -11576,11 +11929,14 @@
       <c r="B35" s="4" t="n"/>
       <c r="C35" s="4" t="n"/>
       <c r="D35" s="4" t="n"/>
-      <c r="E35" s="4" t="n"/>
+      <c r="E35" s="21" t="n"/>
       <c r="F35" s="4" t="n"/>
       <c r="G35" s="4" t="n"/>
       <c r="H35" s="4" t="n"/>
-      <c r="I35" s="4" t="n"/>
+      <c r="I35" s="4">
+        <f>IFERROR(IF(OR(E35="Enhanced",E35="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C35,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C35,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C35,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C35,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="J35" s="16">
         <f>IFERROR(IFS(AND(D35="Permeable Pavement",E35="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D35="Permeable Pavement",E35="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D35="Bioretention",E35="Standard"),INDEX(PARAMS_BMP,3,5),AND(D35="Bioretention",E35="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D35="Bioretention",E35="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D35="Dry Swale",E35="—"),INDEX(PARAMS_BMP,6,5),AND(D35="Wet Swale",E35="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
         <v/>
@@ -11593,7 +11949,7 @@
         <f>IFERROR(IF(I35=0,"",G35/I35),"")</f>
         <v/>
       </c>
-      <c r="M35" s="16">
+      <c r="M35" s="22">
         <f>IFERROR(IF(L35="","",IF(L35&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
@@ -11614,18 +11970,21 @@
         <v/>
       </c>
       <c r="U35" s="4" t="n"/>
-      <c r="V35" s="4" t="n"/>
+      <c r="V35" s="4">
+        <f>IFERROR(IF(OR(E35="Enhanced",E35="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C35,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C35,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C35,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C35,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="W35" s="16">
         <f>IFERROR(P35*(Q35*R35+S35*T35+U35),0)</f>
         <v/>
       </c>
-      <c r="X35" s="16">
+      <c r="X35" s="22">
         <f>IFERROR(IF(V35=0,"",(Q35+S35)/V35),"")</f>
         <v/>
       </c>
       <c r="Y35" s="4" t="n"/>
       <c r="Z35" s="4" t="n"/>
-      <c r="AA35" s="16">
+      <c r="AA35" s="22">
         <f>IFERROR(Y35+Z35,0)</f>
         <v/>
       </c>
@@ -11635,7 +11994,7 @@
       <c r="AE35" s="4" t="n"/>
       <c r="AF35" s="4" t="n"/>
       <c r="AG35" s="4" t="n"/>
-      <c r="AH35" s="16">
+      <c r="AH35" s="22">
         <f>IFERROR(AB35*INDEX(PARAMS_Trees,1,3)+AC35*INDEX(PARAMS_Trees,2,3)+AD35*INDEX(PARAMS_Trees,3,3)+AE35*INDEX(PARAMS_Trees,4,3)+AF35*INDEX(PARAMS_Trees,5,3)+AG35*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
       </c>
@@ -11655,7 +12014,7 @@
         <f>IFERROR(VLOOKUP(C35,'CDA'!$A$58:$D$67,4,FALSE),0)</f>
         <v/>
       </c>
-      <c r="AM35" s="16">
+      <c r="AM35" s="22">
         <f>IFERROR(IF(AL35=0,AK35,MIN(AK35,AL35)),0)</f>
         <v/>
       </c>
@@ -11665,11 +12024,14 @@
       <c r="B36" s="4" t="n"/>
       <c r="C36" s="4" t="n"/>
       <c r="D36" s="4" t="n"/>
-      <c r="E36" s="4" t="n"/>
+      <c r="E36" s="21" t="n"/>
       <c r="F36" s="4" t="n"/>
       <c r="G36" s="4" t="n"/>
       <c r="H36" s="4" t="n"/>
-      <c r="I36" s="4" t="n"/>
+      <c r="I36" s="4">
+        <f>IFERROR(IF(OR(E36="Enhanced",E36="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C36,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C36,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C36,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C36,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="J36" s="16">
         <f>IFERROR(IFS(AND(D36="Permeable Pavement",E36="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D36="Permeable Pavement",E36="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D36="Bioretention",E36="Standard"),INDEX(PARAMS_BMP,3,5),AND(D36="Bioretention",E36="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D36="Bioretention",E36="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D36="Dry Swale",E36="—"),INDEX(PARAMS_BMP,6,5),AND(D36="Wet Swale",E36="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
         <v/>
@@ -11682,7 +12044,7 @@
         <f>IFERROR(IF(I36=0,"",G36/I36),"")</f>
         <v/>
       </c>
-      <c r="M36" s="16">
+      <c r="M36" s="22">
         <f>IFERROR(IF(L36="","",IF(L36&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
@@ -11703,18 +12065,21 @@
         <v/>
       </c>
       <c r="U36" s="4" t="n"/>
-      <c r="V36" s="4" t="n"/>
+      <c r="V36" s="4">
+        <f>IFERROR(IF(OR(E36="Enhanced",E36="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C36,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C36,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C36,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C36,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="W36" s="16">
         <f>IFERROR(P36*(Q36*R36+S36*T36+U36),0)</f>
         <v/>
       </c>
-      <c r="X36" s="16">
+      <c r="X36" s="22">
         <f>IFERROR(IF(V36=0,"",(Q36+S36)/V36),"")</f>
         <v/>
       </c>
       <c r="Y36" s="4" t="n"/>
       <c r="Z36" s="4" t="n"/>
-      <c r="AA36" s="16">
+      <c r="AA36" s="22">
         <f>IFERROR(Y36+Z36,0)</f>
         <v/>
       </c>
@@ -11724,7 +12089,7 @@
       <c r="AE36" s="4" t="n"/>
       <c r="AF36" s="4" t="n"/>
       <c r="AG36" s="4" t="n"/>
-      <c r="AH36" s="16">
+      <c r="AH36" s="22">
         <f>IFERROR(AB36*INDEX(PARAMS_Trees,1,3)+AC36*INDEX(PARAMS_Trees,2,3)+AD36*INDEX(PARAMS_Trees,3,3)+AE36*INDEX(PARAMS_Trees,4,3)+AF36*INDEX(PARAMS_Trees,5,3)+AG36*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
       </c>
@@ -11744,7 +12109,7 @@
         <f>IFERROR(VLOOKUP(C36,'CDA'!$A$58:$D$67,4,FALSE),0)</f>
         <v/>
       </c>
-      <c r="AM36" s="16">
+      <c r="AM36" s="22">
         <f>IFERROR(IF(AL36=0,AK36,MIN(AK36,AL36)),0)</f>
         <v/>
       </c>
@@ -11754,11 +12119,14 @@
       <c r="B37" s="4" t="n"/>
       <c r="C37" s="4" t="n"/>
       <c r="D37" s="4" t="n"/>
-      <c r="E37" s="4" t="n"/>
+      <c r="E37" s="21" t="n"/>
       <c r="F37" s="4" t="n"/>
       <c r="G37" s="4" t="n"/>
       <c r="H37" s="4" t="n"/>
-      <c r="I37" s="4" t="n"/>
+      <c r="I37" s="4">
+        <f>IFERROR(IF(OR(E37="Enhanced",E37="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C37,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C37,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C37,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C37,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="J37" s="16">
         <f>IFERROR(IFS(AND(D37="Permeable Pavement",E37="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D37="Permeable Pavement",E37="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D37="Bioretention",E37="Standard"),INDEX(PARAMS_BMP,3,5),AND(D37="Bioretention",E37="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D37="Bioretention",E37="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D37="Dry Swale",E37="—"),INDEX(PARAMS_BMP,6,5),AND(D37="Wet Swale",E37="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
         <v/>
@@ -11771,7 +12139,7 @@
         <f>IFERROR(IF(I37=0,"",G37/I37),"")</f>
         <v/>
       </c>
-      <c r="M37" s="16">
+      <c r="M37" s="22">
         <f>IFERROR(IF(L37="","",IF(L37&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
@@ -11792,18 +12160,21 @@
         <v/>
       </c>
       <c r="U37" s="4" t="n"/>
-      <c r="V37" s="4" t="n"/>
+      <c r="V37" s="4">
+        <f>IFERROR(IF(OR(E37="Enhanced",E37="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C37,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C37,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C37,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C37,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="W37" s="16">
         <f>IFERROR(P37*(Q37*R37+S37*T37+U37),0)</f>
         <v/>
       </c>
-      <c r="X37" s="16">
+      <c r="X37" s="22">
         <f>IFERROR(IF(V37=0,"",(Q37+S37)/V37),"")</f>
         <v/>
       </c>
       <c r="Y37" s="4" t="n"/>
       <c r="Z37" s="4" t="n"/>
-      <c r="AA37" s="16">
+      <c r="AA37" s="22">
         <f>IFERROR(Y37+Z37,0)</f>
         <v/>
       </c>
@@ -11813,7 +12184,7 @@
       <c r="AE37" s="4" t="n"/>
       <c r="AF37" s="4" t="n"/>
       <c r="AG37" s="4" t="n"/>
-      <c r="AH37" s="16">
+      <c r="AH37" s="22">
         <f>IFERROR(AB37*INDEX(PARAMS_Trees,1,3)+AC37*INDEX(PARAMS_Trees,2,3)+AD37*INDEX(PARAMS_Trees,3,3)+AE37*INDEX(PARAMS_Trees,4,3)+AF37*INDEX(PARAMS_Trees,5,3)+AG37*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
       </c>
@@ -11833,7 +12204,7 @@
         <f>IFERROR(VLOOKUP(C37,'CDA'!$A$58:$D$67,4,FALSE),0)</f>
         <v/>
       </c>
-      <c r="AM37" s="16">
+      <c r="AM37" s="22">
         <f>IFERROR(IF(AL37=0,AK37,MIN(AK37,AL37)),0)</f>
         <v/>
       </c>
@@ -11843,11 +12214,14 @@
       <c r="B38" s="4" t="n"/>
       <c r="C38" s="4" t="n"/>
       <c r="D38" s="4" t="n"/>
-      <c r="E38" s="4" t="n"/>
+      <c r="E38" s="21" t="n"/>
       <c r="F38" s="4" t="n"/>
       <c r="G38" s="4" t="n"/>
       <c r="H38" s="4" t="n"/>
-      <c r="I38" s="4" t="n"/>
+      <c r="I38" s="4">
+        <f>IFERROR(IF(OR(E38="Enhanced",E38="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C38,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C38,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C38,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C38,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="J38" s="16">
         <f>IFERROR(IFS(AND(D38="Permeable Pavement",E38="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D38="Permeable Pavement",E38="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D38="Bioretention",E38="Standard"),INDEX(PARAMS_BMP,3,5),AND(D38="Bioretention",E38="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D38="Bioretention",E38="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D38="Dry Swale",E38="—"),INDEX(PARAMS_BMP,6,5),AND(D38="Wet Swale",E38="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
         <v/>
@@ -11860,7 +12234,7 @@
         <f>IFERROR(IF(I38=0,"",G38/I38),"")</f>
         <v/>
       </c>
-      <c r="M38" s="16">
+      <c r="M38" s="22">
         <f>IFERROR(IF(L38="","",IF(L38&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
@@ -11881,18 +12255,21 @@
         <v/>
       </c>
       <c r="U38" s="4" t="n"/>
-      <c r="V38" s="4" t="n"/>
+      <c r="V38" s="4">
+        <f>IFERROR(IF(OR(E38="Enhanced",E38="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C38,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C38,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C38,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C38,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="W38" s="16">
         <f>IFERROR(P38*(Q38*R38+S38*T38+U38),0)</f>
         <v/>
       </c>
-      <c r="X38" s="16">
+      <c r="X38" s="22">
         <f>IFERROR(IF(V38=0,"",(Q38+S38)/V38),"")</f>
         <v/>
       </c>
       <c r="Y38" s="4" t="n"/>
       <c r="Z38" s="4" t="n"/>
-      <c r="AA38" s="16">
+      <c r="AA38" s="22">
         <f>IFERROR(Y38+Z38,0)</f>
         <v/>
       </c>
@@ -11902,7 +12279,7 @@
       <c r="AE38" s="4" t="n"/>
       <c r="AF38" s="4" t="n"/>
       <c r="AG38" s="4" t="n"/>
-      <c r="AH38" s="16">
+      <c r="AH38" s="22">
         <f>IFERROR(AB38*INDEX(PARAMS_Trees,1,3)+AC38*INDEX(PARAMS_Trees,2,3)+AD38*INDEX(PARAMS_Trees,3,3)+AE38*INDEX(PARAMS_Trees,4,3)+AF38*INDEX(PARAMS_Trees,5,3)+AG38*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
       </c>
@@ -11922,7 +12299,7 @@
         <f>IFERROR(VLOOKUP(C38,'CDA'!$A$58:$D$67,4,FALSE),0)</f>
         <v/>
       </c>
-      <c r="AM38" s="16">
+      <c r="AM38" s="22">
         <f>IFERROR(IF(AL38=0,AK38,MIN(AK38,AL38)),0)</f>
         <v/>
       </c>
@@ -11932,11 +12309,14 @@
       <c r="B39" s="4" t="n"/>
       <c r="C39" s="4" t="n"/>
       <c r="D39" s="4" t="n"/>
-      <c r="E39" s="4" t="n"/>
+      <c r="E39" s="21" t="n"/>
       <c r="F39" s="4" t="n"/>
       <c r="G39" s="4" t="n"/>
       <c r="H39" s="4" t="n"/>
-      <c r="I39" s="4" t="n"/>
+      <c r="I39" s="4">
+        <f>IFERROR(IF(OR(E39="Enhanced",E39="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C39,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C39,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C39,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C39,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="J39" s="16">
         <f>IFERROR(IFS(AND(D39="Permeable Pavement",E39="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D39="Permeable Pavement",E39="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D39="Bioretention",E39="Standard"),INDEX(PARAMS_BMP,3,5),AND(D39="Bioretention",E39="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D39="Bioretention",E39="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D39="Dry Swale",E39="—"),INDEX(PARAMS_BMP,6,5),AND(D39="Wet Swale",E39="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
         <v/>
@@ -11949,7 +12329,7 @@
         <f>IFERROR(IF(I39=0,"",G39/I39),"")</f>
         <v/>
       </c>
-      <c r="M39" s="16">
+      <c r="M39" s="22">
         <f>IFERROR(IF(L39="","",IF(L39&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
@@ -11970,18 +12350,21 @@
         <v/>
       </c>
       <c r="U39" s="4" t="n"/>
-      <c r="V39" s="4" t="n"/>
+      <c r="V39" s="4">
+        <f>IFERROR(IF(OR(E39="Enhanced",E39="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C39,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C39,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C39,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C39,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="W39" s="16">
         <f>IFERROR(P39*(Q39*R39+S39*T39+U39),0)</f>
         <v/>
       </c>
-      <c r="X39" s="16">
+      <c r="X39" s="22">
         <f>IFERROR(IF(V39=0,"",(Q39+S39)/V39),"")</f>
         <v/>
       </c>
       <c r="Y39" s="4" t="n"/>
       <c r="Z39" s="4" t="n"/>
-      <c r="AA39" s="16">
+      <c r="AA39" s="22">
         <f>IFERROR(Y39+Z39,0)</f>
         <v/>
       </c>
@@ -11991,7 +12374,7 @@
       <c r="AE39" s="4" t="n"/>
       <c r="AF39" s="4" t="n"/>
       <c r="AG39" s="4" t="n"/>
-      <c r="AH39" s="16">
+      <c r="AH39" s="22">
         <f>IFERROR(AB39*INDEX(PARAMS_Trees,1,3)+AC39*INDEX(PARAMS_Trees,2,3)+AD39*INDEX(PARAMS_Trees,3,3)+AE39*INDEX(PARAMS_Trees,4,3)+AF39*INDEX(PARAMS_Trees,5,3)+AG39*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
       </c>
@@ -12011,7 +12394,7 @@
         <f>IFERROR(VLOOKUP(C39,'CDA'!$A$58:$D$67,4,FALSE),0)</f>
         <v/>
       </c>
-      <c r="AM39" s="16">
+      <c r="AM39" s="22">
         <f>IFERROR(IF(AL39=0,AK39,MIN(AK39,AL39)),0)</f>
         <v/>
       </c>
@@ -12021,11 +12404,14 @@
       <c r="B40" s="4" t="n"/>
       <c r="C40" s="4" t="n"/>
       <c r="D40" s="4" t="n"/>
-      <c r="E40" s="4" t="n"/>
+      <c r="E40" s="21" t="n"/>
       <c r="F40" s="4" t="n"/>
       <c r="G40" s="4" t="n"/>
       <c r="H40" s="4" t="n"/>
-      <c r="I40" s="4" t="n"/>
+      <c r="I40" s="4">
+        <f>IFERROR(IF(OR(E40="Enhanced",E40="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C40,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C40,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C40,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C40,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="J40" s="16">
         <f>IFERROR(IFS(AND(D40="Permeable Pavement",E40="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D40="Permeable Pavement",E40="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D40="Bioretention",E40="Standard"),INDEX(PARAMS_BMP,3,5),AND(D40="Bioretention",E40="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D40="Bioretention",E40="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D40="Dry Swale",E40="—"),INDEX(PARAMS_BMP,6,5),AND(D40="Wet Swale",E40="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
         <v/>
@@ -12038,7 +12424,7 @@
         <f>IFERROR(IF(I40=0,"",G40/I40),"")</f>
         <v/>
       </c>
-      <c r="M40" s="16">
+      <c r="M40" s="22">
         <f>IFERROR(IF(L40="","",IF(L40&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
@@ -12059,18 +12445,21 @@
         <v/>
       </c>
       <c r="U40" s="4" t="n"/>
-      <c r="V40" s="4" t="n"/>
+      <c r="V40" s="4">
+        <f>IFERROR(IF(OR(E40="Enhanced",E40="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C40,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C40,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C40,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C40,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="W40" s="16">
         <f>IFERROR(P40*(Q40*R40+S40*T40+U40),0)</f>
         <v/>
       </c>
-      <c r="X40" s="16">
+      <c r="X40" s="22">
         <f>IFERROR(IF(V40=0,"",(Q40+S40)/V40),"")</f>
         <v/>
       </c>
       <c r="Y40" s="4" t="n"/>
       <c r="Z40" s="4" t="n"/>
-      <c r="AA40" s="16">
+      <c r="AA40" s="22">
         <f>IFERROR(Y40+Z40,0)</f>
         <v/>
       </c>
@@ -12080,7 +12469,7 @@
       <c r="AE40" s="4" t="n"/>
       <c r="AF40" s="4" t="n"/>
       <c r="AG40" s="4" t="n"/>
-      <c r="AH40" s="16">
+      <c r="AH40" s="22">
         <f>IFERROR(AB40*INDEX(PARAMS_Trees,1,3)+AC40*INDEX(PARAMS_Trees,2,3)+AD40*INDEX(PARAMS_Trees,3,3)+AE40*INDEX(PARAMS_Trees,4,3)+AF40*INDEX(PARAMS_Trees,5,3)+AG40*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
       </c>
@@ -12100,7 +12489,7 @@
         <f>IFERROR(VLOOKUP(C40,'CDA'!$A$58:$D$67,4,FALSE),0)</f>
         <v/>
       </c>
-      <c r="AM40" s="16">
+      <c r="AM40" s="22">
         <f>IFERROR(IF(AL40=0,AK40,MIN(AK40,AL40)),0)</f>
         <v/>
       </c>
@@ -12110,11 +12499,14 @@
       <c r="B41" s="4" t="n"/>
       <c r="C41" s="4" t="n"/>
       <c r="D41" s="4" t="n"/>
-      <c r="E41" s="4" t="n"/>
+      <c r="E41" s="21" t="n"/>
       <c r="F41" s="4" t="n"/>
       <c r="G41" s="4" t="n"/>
       <c r="H41" s="4" t="n"/>
-      <c r="I41" s="4" t="n"/>
+      <c r="I41" s="4">
+        <f>IFERROR(IF(OR(E41="Enhanced",E41="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C41,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C41,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C41,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C41,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="J41" s="16">
         <f>IFERROR(IFS(AND(D41="Permeable Pavement",E41="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D41="Permeable Pavement",E41="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D41="Bioretention",E41="Standard"),INDEX(PARAMS_BMP,3,5),AND(D41="Bioretention",E41="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D41="Bioretention",E41="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D41="Dry Swale",E41="—"),INDEX(PARAMS_BMP,6,5),AND(D41="Wet Swale",E41="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
         <v/>
@@ -12127,7 +12519,7 @@
         <f>IFERROR(IF(I41=0,"",G41/I41),"")</f>
         <v/>
       </c>
-      <c r="M41" s="16">
+      <c r="M41" s="22">
         <f>IFERROR(IF(L41="","",IF(L41&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
@@ -12148,18 +12540,21 @@
         <v/>
       </c>
       <c r="U41" s="4" t="n"/>
-      <c r="V41" s="4" t="n"/>
+      <c r="V41" s="4">
+        <f>IFERROR(IF(OR(E41="Enhanced",E41="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C41,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C41,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C41,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C41,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="W41" s="16">
         <f>IFERROR(P41*(Q41*R41+S41*T41+U41),0)</f>
         <v/>
       </c>
-      <c r="X41" s="16">
+      <c r="X41" s="22">
         <f>IFERROR(IF(V41=0,"",(Q41+S41)/V41),"")</f>
         <v/>
       </c>
       <c r="Y41" s="4" t="n"/>
       <c r="Z41" s="4" t="n"/>
-      <c r="AA41" s="16">
+      <c r="AA41" s="22">
         <f>IFERROR(Y41+Z41,0)</f>
         <v/>
       </c>
@@ -12169,7 +12564,7 @@
       <c r="AE41" s="4" t="n"/>
       <c r="AF41" s="4" t="n"/>
       <c r="AG41" s="4" t="n"/>
-      <c r="AH41" s="16">
+      <c r="AH41" s="22">
         <f>IFERROR(AB41*INDEX(PARAMS_Trees,1,3)+AC41*INDEX(PARAMS_Trees,2,3)+AD41*INDEX(PARAMS_Trees,3,3)+AE41*INDEX(PARAMS_Trees,4,3)+AF41*INDEX(PARAMS_Trees,5,3)+AG41*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
       </c>
@@ -12189,7 +12584,7 @@
         <f>IFERROR(VLOOKUP(C41,'CDA'!$A$58:$D$67,4,FALSE),0)</f>
         <v/>
       </c>
-      <c r="AM41" s="16">
+      <c r="AM41" s="22">
         <f>IFERROR(IF(AL41=0,AK41,MIN(AK41,AL41)),0)</f>
         <v/>
       </c>
@@ -12199,11 +12594,14 @@
       <c r="B42" s="4" t="n"/>
       <c r="C42" s="4" t="n"/>
       <c r="D42" s="4" t="n"/>
-      <c r="E42" s="4" t="n"/>
+      <c r="E42" s="21" t="n"/>
       <c r="F42" s="4" t="n"/>
       <c r="G42" s="4" t="n"/>
       <c r="H42" s="4" t="n"/>
-      <c r="I42" s="4" t="n"/>
+      <c r="I42" s="4">
+        <f>IFERROR(IF(OR(E42="Enhanced",E42="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C42,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C42,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C42,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C42,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="J42" s="16">
         <f>IFERROR(IFS(AND(D42="Permeable Pavement",E42="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D42="Permeable Pavement",E42="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D42="Bioretention",E42="Standard"),INDEX(PARAMS_BMP,3,5),AND(D42="Bioretention",E42="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D42="Bioretention",E42="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D42="Dry Swale",E42="—"),INDEX(PARAMS_BMP,6,5),AND(D42="Wet Swale",E42="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
         <v/>
@@ -12216,7 +12614,7 @@
         <f>IFERROR(IF(I42=0,"",G42/I42),"")</f>
         <v/>
       </c>
-      <c r="M42" s="16">
+      <c r="M42" s="22">
         <f>IFERROR(IF(L42="","",IF(L42&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
@@ -12237,18 +12635,21 @@
         <v/>
       </c>
       <c r="U42" s="4" t="n"/>
-      <c r="V42" s="4" t="n"/>
+      <c r="V42" s="4">
+        <f>IFERROR(IF(OR(E42="Enhanced",E42="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C42,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C42,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C42,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C42,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="W42" s="16">
         <f>IFERROR(P42*(Q42*R42+S42*T42+U42),0)</f>
         <v/>
       </c>
-      <c r="X42" s="16">
+      <c r="X42" s="22">
         <f>IFERROR(IF(V42=0,"",(Q42+S42)/V42),"")</f>
         <v/>
       </c>
       <c r="Y42" s="4" t="n"/>
       <c r="Z42" s="4" t="n"/>
-      <c r="AA42" s="16">
+      <c r="AA42" s="22">
         <f>IFERROR(Y42+Z42,0)</f>
         <v/>
       </c>
@@ -12258,7 +12659,7 @@
       <c r="AE42" s="4" t="n"/>
       <c r="AF42" s="4" t="n"/>
       <c r="AG42" s="4" t="n"/>
-      <c r="AH42" s="16">
+      <c r="AH42" s="22">
         <f>IFERROR(AB42*INDEX(PARAMS_Trees,1,3)+AC42*INDEX(PARAMS_Trees,2,3)+AD42*INDEX(PARAMS_Trees,3,3)+AE42*INDEX(PARAMS_Trees,4,3)+AF42*INDEX(PARAMS_Trees,5,3)+AG42*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
       </c>
@@ -12278,7 +12679,7 @@
         <f>IFERROR(VLOOKUP(C42,'CDA'!$A$58:$D$67,4,FALSE),0)</f>
         <v/>
       </c>
-      <c r="AM42" s="16">
+      <c r="AM42" s="22">
         <f>IFERROR(IF(AL42=0,AK42,MIN(AK42,AL42)),0)</f>
         <v/>
       </c>
@@ -12288,11 +12689,14 @@
       <c r="B43" s="4" t="n"/>
       <c r="C43" s="4" t="n"/>
       <c r="D43" s="4" t="n"/>
-      <c r="E43" s="4" t="n"/>
+      <c r="E43" s="21" t="n"/>
       <c r="F43" s="4" t="n"/>
       <c r="G43" s="4" t="n"/>
       <c r="H43" s="4" t="n"/>
-      <c r="I43" s="4" t="n"/>
+      <c r="I43" s="4">
+        <f>IFERROR(IF(OR(E43="Enhanced",E43="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C43,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C43,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C43,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C43,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="J43" s="16">
         <f>IFERROR(IFS(AND(D43="Permeable Pavement",E43="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D43="Permeable Pavement",E43="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D43="Bioretention",E43="Standard"),INDEX(PARAMS_BMP,3,5),AND(D43="Bioretention",E43="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D43="Bioretention",E43="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D43="Dry Swale",E43="—"),INDEX(PARAMS_BMP,6,5),AND(D43="Wet Swale",E43="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
         <v/>
@@ -12305,7 +12709,7 @@
         <f>IFERROR(IF(I43=0,"",G43/I43),"")</f>
         <v/>
       </c>
-      <c r="M43" s="16">
+      <c r="M43" s="22">
         <f>IFERROR(IF(L43="","",IF(L43&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
@@ -12326,18 +12730,21 @@
         <v/>
       </c>
       <c r="U43" s="4" t="n"/>
-      <c r="V43" s="4" t="n"/>
+      <c r="V43" s="4">
+        <f>IFERROR(IF(OR(E43="Enhanced",E43="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C43,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C43,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C43,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C43,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="W43" s="16">
         <f>IFERROR(P43*(Q43*R43+S43*T43+U43),0)</f>
         <v/>
       </c>
-      <c r="X43" s="16">
+      <c r="X43" s="22">
         <f>IFERROR(IF(V43=0,"",(Q43+S43)/V43),"")</f>
         <v/>
       </c>
       <c r="Y43" s="4" t="n"/>
       <c r="Z43" s="4" t="n"/>
-      <c r="AA43" s="16">
+      <c r="AA43" s="22">
         <f>IFERROR(Y43+Z43,0)</f>
         <v/>
       </c>
@@ -12347,7 +12754,7 @@
       <c r="AE43" s="4" t="n"/>
       <c r="AF43" s="4" t="n"/>
       <c r="AG43" s="4" t="n"/>
-      <c r="AH43" s="16">
+      <c r="AH43" s="22">
         <f>IFERROR(AB43*INDEX(PARAMS_Trees,1,3)+AC43*INDEX(PARAMS_Trees,2,3)+AD43*INDEX(PARAMS_Trees,3,3)+AE43*INDEX(PARAMS_Trees,4,3)+AF43*INDEX(PARAMS_Trees,5,3)+AG43*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
       </c>
@@ -12367,7 +12774,7 @@
         <f>IFERROR(VLOOKUP(C43,'CDA'!$A$58:$D$67,4,FALSE),0)</f>
         <v/>
       </c>
-      <c r="AM43" s="16">
+      <c r="AM43" s="22">
         <f>IFERROR(IF(AL43=0,AK43,MIN(AK43,AL43)),0)</f>
         <v/>
       </c>
@@ -12377,11 +12784,14 @@
       <c r="B44" s="4" t="n"/>
       <c r="C44" s="4" t="n"/>
       <c r="D44" s="4" t="n"/>
-      <c r="E44" s="4" t="n"/>
+      <c r="E44" s="21" t="n"/>
       <c r="F44" s="4" t="n"/>
       <c r="G44" s="4" t="n"/>
       <c r="H44" s="4" t="n"/>
-      <c r="I44" s="4" t="n"/>
+      <c r="I44" s="4">
+        <f>IFERROR(IF(OR(E44="Enhanced",E44="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C44,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C44,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C44,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C44,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="J44" s="16">
         <f>IFERROR(IFS(AND(D44="Permeable Pavement",E44="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D44="Permeable Pavement",E44="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D44="Bioretention",E44="Standard"),INDEX(PARAMS_BMP,3,5),AND(D44="Bioretention",E44="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D44="Bioretention",E44="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D44="Dry Swale",E44="—"),INDEX(PARAMS_BMP,6,5),AND(D44="Wet Swale",E44="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
         <v/>
@@ -12394,7 +12804,7 @@
         <f>IFERROR(IF(I44=0,"",G44/I44),"")</f>
         <v/>
       </c>
-      <c r="M44" s="16">
+      <c r="M44" s="22">
         <f>IFERROR(IF(L44="","",IF(L44&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
@@ -12415,18 +12825,21 @@
         <v/>
       </c>
       <c r="U44" s="4" t="n"/>
-      <c r="V44" s="4" t="n"/>
+      <c r="V44" s="4">
+        <f>IFERROR(IF(OR(E44="Enhanced",E44="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C44,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C44,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C44,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C44,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="W44" s="16">
         <f>IFERROR(P44*(Q44*R44+S44*T44+U44),0)</f>
         <v/>
       </c>
-      <c r="X44" s="16">
+      <c r="X44" s="22">
         <f>IFERROR(IF(V44=0,"",(Q44+S44)/V44),"")</f>
         <v/>
       </c>
       <c r="Y44" s="4" t="n"/>
       <c r="Z44" s="4" t="n"/>
-      <c r="AA44" s="16">
+      <c r="AA44" s="22">
         <f>IFERROR(Y44+Z44,0)</f>
         <v/>
       </c>
@@ -12436,7 +12849,7 @@
       <c r="AE44" s="4" t="n"/>
       <c r="AF44" s="4" t="n"/>
       <c r="AG44" s="4" t="n"/>
-      <c r="AH44" s="16">
+      <c r="AH44" s="22">
         <f>IFERROR(AB44*INDEX(PARAMS_Trees,1,3)+AC44*INDEX(PARAMS_Trees,2,3)+AD44*INDEX(PARAMS_Trees,3,3)+AE44*INDEX(PARAMS_Trees,4,3)+AF44*INDEX(PARAMS_Trees,5,3)+AG44*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
       </c>
@@ -12456,7 +12869,7 @@
         <f>IFERROR(VLOOKUP(C44,'CDA'!$A$58:$D$67,4,FALSE),0)</f>
         <v/>
       </c>
-      <c r="AM44" s="16">
+      <c r="AM44" s="22">
         <f>IFERROR(IF(AL44=0,AK44,MIN(AK44,AL44)),0)</f>
         <v/>
       </c>
@@ -12466,11 +12879,14 @@
       <c r="B45" s="4" t="n"/>
       <c r="C45" s="4" t="n"/>
       <c r="D45" s="4" t="n"/>
-      <c r="E45" s="4" t="n"/>
+      <c r="E45" s="21" t="n"/>
       <c r="F45" s="4" t="n"/>
       <c r="G45" s="4" t="n"/>
       <c r="H45" s="4" t="n"/>
-      <c r="I45" s="4" t="n"/>
+      <c r="I45" s="4">
+        <f>IFERROR(IF(OR(E45="Enhanced",E45="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C45,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C45,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C45,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C45,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="J45" s="16">
         <f>IFERROR(IFS(AND(D45="Permeable Pavement",E45="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D45="Permeable Pavement",E45="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D45="Bioretention",E45="Standard"),INDEX(PARAMS_BMP,3,5),AND(D45="Bioretention",E45="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D45="Bioretention",E45="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D45="Dry Swale",E45="—"),INDEX(PARAMS_BMP,6,5),AND(D45="Wet Swale",E45="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
         <v/>
@@ -12483,7 +12899,7 @@
         <f>IFERROR(IF(I45=0,"",G45/I45),"")</f>
         <v/>
       </c>
-      <c r="M45" s="16">
+      <c r="M45" s="22">
         <f>IFERROR(IF(L45="","",IF(L45&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
@@ -12504,18 +12920,21 @@
         <v/>
       </c>
       <c r="U45" s="4" t="n"/>
-      <c r="V45" s="4" t="n"/>
+      <c r="V45" s="4">
+        <f>IFERROR(IF(OR(E45="Enhanced",E45="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C45,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C45,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C45,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C45,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="W45" s="16">
         <f>IFERROR(P45*(Q45*R45+S45*T45+U45),0)</f>
         <v/>
       </c>
-      <c r="X45" s="16">
+      <c r="X45" s="22">
         <f>IFERROR(IF(V45=0,"",(Q45+S45)/V45),"")</f>
         <v/>
       </c>
       <c r="Y45" s="4" t="n"/>
       <c r="Z45" s="4" t="n"/>
-      <c r="AA45" s="16">
+      <c r="AA45" s="22">
         <f>IFERROR(Y45+Z45,0)</f>
         <v/>
       </c>
@@ -12525,7 +12944,7 @@
       <c r="AE45" s="4" t="n"/>
       <c r="AF45" s="4" t="n"/>
       <c r="AG45" s="4" t="n"/>
-      <c r="AH45" s="16">
+      <c r="AH45" s="22">
         <f>IFERROR(AB45*INDEX(PARAMS_Trees,1,3)+AC45*INDEX(PARAMS_Trees,2,3)+AD45*INDEX(PARAMS_Trees,3,3)+AE45*INDEX(PARAMS_Trees,4,3)+AF45*INDEX(PARAMS_Trees,5,3)+AG45*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
       </c>
@@ -12545,7 +12964,7 @@
         <f>IFERROR(VLOOKUP(C45,'CDA'!$A$58:$D$67,4,FALSE),0)</f>
         <v/>
       </c>
-      <c r="AM45" s="16">
+      <c r="AM45" s="22">
         <f>IFERROR(IF(AL45=0,AK45,MIN(AK45,AL45)),0)</f>
         <v/>
       </c>
@@ -12555,11 +12974,14 @@
       <c r="B46" s="4" t="n"/>
       <c r="C46" s="4" t="n"/>
       <c r="D46" s="4" t="n"/>
-      <c r="E46" s="4" t="n"/>
+      <c r="E46" s="21" t="n"/>
       <c r="F46" s="4" t="n"/>
       <c r="G46" s="4" t="n"/>
       <c r="H46" s="4" t="n"/>
-      <c r="I46" s="4" t="n"/>
+      <c r="I46" s="4">
+        <f>IFERROR(IF(OR(E46="Enhanced",E46="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C46,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C46,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C46,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C46,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="J46" s="16">
         <f>IFERROR(IFS(AND(D46="Permeable Pavement",E46="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D46="Permeable Pavement",E46="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D46="Bioretention",E46="Standard"),INDEX(PARAMS_BMP,3,5),AND(D46="Bioretention",E46="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D46="Bioretention",E46="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D46="Dry Swale",E46="—"),INDEX(PARAMS_BMP,6,5),AND(D46="Wet Swale",E46="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
         <v/>
@@ -12572,7 +12994,7 @@
         <f>IFERROR(IF(I46=0,"",G46/I46),"")</f>
         <v/>
       </c>
-      <c r="M46" s="16">
+      <c r="M46" s="22">
         <f>IFERROR(IF(L46="","",IF(L46&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
@@ -12593,18 +13015,21 @@
         <v/>
       </c>
       <c r="U46" s="4" t="n"/>
-      <c r="V46" s="4" t="n"/>
+      <c r="V46" s="4">
+        <f>IFERROR(IF(OR(E46="Enhanced",E46="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C46,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C46,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C46,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C46,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="W46" s="16">
         <f>IFERROR(P46*(Q46*R46+S46*T46+U46),0)</f>
         <v/>
       </c>
-      <c r="X46" s="16">
+      <c r="X46" s="22">
         <f>IFERROR(IF(V46=0,"",(Q46+S46)/V46),"")</f>
         <v/>
       </c>
       <c r="Y46" s="4" t="n"/>
       <c r="Z46" s="4" t="n"/>
-      <c r="AA46" s="16">
+      <c r="AA46" s="22">
         <f>IFERROR(Y46+Z46,0)</f>
         <v/>
       </c>
@@ -12614,7 +13039,7 @@
       <c r="AE46" s="4" t="n"/>
       <c r="AF46" s="4" t="n"/>
       <c r="AG46" s="4" t="n"/>
-      <c r="AH46" s="16">
+      <c r="AH46" s="22">
         <f>IFERROR(AB46*INDEX(PARAMS_Trees,1,3)+AC46*INDEX(PARAMS_Trees,2,3)+AD46*INDEX(PARAMS_Trees,3,3)+AE46*INDEX(PARAMS_Trees,4,3)+AF46*INDEX(PARAMS_Trees,5,3)+AG46*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
       </c>
@@ -12634,7 +13059,7 @@
         <f>IFERROR(VLOOKUP(C46,'CDA'!$A$58:$D$67,4,FALSE),0)</f>
         <v/>
       </c>
-      <c r="AM46" s="16">
+      <c r="AM46" s="22">
         <f>IFERROR(IF(AL46=0,AK46,MIN(AK46,AL46)),0)</f>
         <v/>
       </c>
@@ -12644,11 +13069,14 @@
       <c r="B47" s="4" t="n"/>
       <c r="C47" s="4" t="n"/>
       <c r="D47" s="4" t="n"/>
-      <c r="E47" s="4" t="n"/>
+      <c r="E47" s="21" t="n"/>
       <c r="F47" s="4" t="n"/>
       <c r="G47" s="4" t="n"/>
       <c r="H47" s="4" t="n"/>
-      <c r="I47" s="4" t="n"/>
+      <c r="I47" s="4">
+        <f>IFERROR(IF(OR(E47="Enhanced",E47="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C47,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C47,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C47,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C47,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="J47" s="16">
         <f>IFERROR(IFS(AND(D47="Permeable Pavement",E47="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D47="Permeable Pavement",E47="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D47="Bioretention",E47="Standard"),INDEX(PARAMS_BMP,3,5),AND(D47="Bioretention",E47="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D47="Bioretention",E47="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D47="Dry Swale",E47="—"),INDEX(PARAMS_BMP,6,5),AND(D47="Wet Swale",E47="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
         <v/>
@@ -12661,7 +13089,7 @@
         <f>IFERROR(IF(I47=0,"",G47/I47),"")</f>
         <v/>
       </c>
-      <c r="M47" s="16">
+      <c r="M47" s="22">
         <f>IFERROR(IF(L47="","",IF(L47&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
@@ -12682,18 +13110,21 @@
         <v/>
       </c>
       <c r="U47" s="4" t="n"/>
-      <c r="V47" s="4" t="n"/>
+      <c r="V47" s="4">
+        <f>IFERROR(IF(OR(E47="Enhanced",E47="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C47,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C47,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C47,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C47,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="W47" s="16">
         <f>IFERROR(P47*(Q47*R47+S47*T47+U47),0)</f>
         <v/>
       </c>
-      <c r="X47" s="16">
+      <c r="X47" s="22">
         <f>IFERROR(IF(V47=0,"",(Q47+S47)/V47),"")</f>
         <v/>
       </c>
       <c r="Y47" s="4" t="n"/>
       <c r="Z47" s="4" t="n"/>
-      <c r="AA47" s="16">
+      <c r="AA47" s="22">
         <f>IFERROR(Y47+Z47,0)</f>
         <v/>
       </c>
@@ -12703,7 +13134,7 @@
       <c r="AE47" s="4" t="n"/>
       <c r="AF47" s="4" t="n"/>
       <c r="AG47" s="4" t="n"/>
-      <c r="AH47" s="16">
+      <c r="AH47" s="22">
         <f>IFERROR(AB47*INDEX(PARAMS_Trees,1,3)+AC47*INDEX(PARAMS_Trees,2,3)+AD47*INDEX(PARAMS_Trees,3,3)+AE47*INDEX(PARAMS_Trees,4,3)+AF47*INDEX(PARAMS_Trees,5,3)+AG47*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
       </c>
@@ -12723,7 +13154,7 @@
         <f>IFERROR(VLOOKUP(C47,'CDA'!$A$58:$D$67,4,FALSE),0)</f>
         <v/>
       </c>
-      <c r="AM47" s="16">
+      <c r="AM47" s="22">
         <f>IFERROR(IF(AL47=0,AK47,MIN(AK47,AL47)),0)</f>
         <v/>
       </c>
@@ -12733,11 +13164,14 @@
       <c r="B48" s="4" t="n"/>
       <c r="C48" s="4" t="n"/>
       <c r="D48" s="4" t="n"/>
-      <c r="E48" s="4" t="n"/>
+      <c r="E48" s="21" t="n"/>
       <c r="F48" s="4" t="n"/>
       <c r="G48" s="4" t="n"/>
       <c r="H48" s="4" t="n"/>
-      <c r="I48" s="4" t="n"/>
+      <c r="I48" s="4">
+        <f>IFERROR(IF(OR(E48="Enhanced",E48="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C48,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C48,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C48,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C48,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="J48" s="16">
         <f>IFERROR(IFS(AND(D48="Permeable Pavement",E48="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D48="Permeable Pavement",E48="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D48="Bioretention",E48="Standard"),INDEX(PARAMS_BMP,3,5),AND(D48="Bioretention",E48="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D48="Bioretention",E48="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D48="Dry Swale",E48="—"),INDEX(PARAMS_BMP,6,5),AND(D48="Wet Swale",E48="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
         <v/>
@@ -12750,7 +13184,7 @@
         <f>IFERROR(IF(I48=0,"",G48/I48),"")</f>
         <v/>
       </c>
-      <c r="M48" s="16">
+      <c r="M48" s="22">
         <f>IFERROR(IF(L48="","",IF(L48&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
@@ -12771,18 +13205,21 @@
         <v/>
       </c>
       <c r="U48" s="4" t="n"/>
-      <c r="V48" s="4" t="n"/>
+      <c r="V48" s="4">
+        <f>IFERROR(IF(OR(E48="Enhanced",E48="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C48,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C48,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C48,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C48,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="W48" s="16">
         <f>IFERROR(P48*(Q48*R48+S48*T48+U48),0)</f>
         <v/>
       </c>
-      <c r="X48" s="16">
+      <c r="X48" s="22">
         <f>IFERROR(IF(V48=0,"",(Q48+S48)/V48),"")</f>
         <v/>
       </c>
       <c r="Y48" s="4" t="n"/>
       <c r="Z48" s="4" t="n"/>
-      <c r="AA48" s="16">
+      <c r="AA48" s="22">
         <f>IFERROR(Y48+Z48,0)</f>
         <v/>
       </c>
@@ -12792,7 +13229,7 @@
       <c r="AE48" s="4" t="n"/>
       <c r="AF48" s="4" t="n"/>
       <c r="AG48" s="4" t="n"/>
-      <c r="AH48" s="16">
+      <c r="AH48" s="22">
         <f>IFERROR(AB48*INDEX(PARAMS_Trees,1,3)+AC48*INDEX(PARAMS_Trees,2,3)+AD48*INDEX(PARAMS_Trees,3,3)+AE48*INDEX(PARAMS_Trees,4,3)+AF48*INDEX(PARAMS_Trees,5,3)+AG48*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
       </c>
@@ -12812,7 +13249,7 @@
         <f>IFERROR(VLOOKUP(C48,'CDA'!$A$58:$D$67,4,FALSE),0)</f>
         <v/>
       </c>
-      <c r="AM48" s="16">
+      <c r="AM48" s="22">
         <f>IFERROR(IF(AL48=0,AK48,MIN(AK48,AL48)),0)</f>
         <v/>
       </c>
@@ -12822,11 +13259,14 @@
       <c r="B49" s="4" t="n"/>
       <c r="C49" s="4" t="n"/>
       <c r="D49" s="4" t="n"/>
-      <c r="E49" s="4" t="n"/>
+      <c r="E49" s="21" t="n"/>
       <c r="F49" s="4" t="n"/>
       <c r="G49" s="4" t="n"/>
       <c r="H49" s="4" t="n"/>
-      <c r="I49" s="4" t="n"/>
+      <c r="I49" s="4">
+        <f>IFERROR(IF(OR(E49="Enhanced",E49="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C49,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C49,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C49,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C49,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="J49" s="16">
         <f>IFERROR(IFS(AND(D49="Permeable Pavement",E49="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D49="Permeable Pavement",E49="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D49="Bioretention",E49="Standard"),INDEX(PARAMS_BMP,3,5),AND(D49="Bioretention",E49="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D49="Bioretention",E49="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D49="Dry Swale",E49="—"),INDEX(PARAMS_BMP,6,5),AND(D49="Wet Swale",E49="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
         <v/>
@@ -12839,7 +13279,7 @@
         <f>IFERROR(IF(I49=0,"",G49/I49),"")</f>
         <v/>
       </c>
-      <c r="M49" s="16">
+      <c r="M49" s="22">
         <f>IFERROR(IF(L49="","",IF(L49&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
@@ -12860,18 +13300,21 @@
         <v/>
       </c>
       <c r="U49" s="4" t="n"/>
-      <c r="V49" s="4" t="n"/>
+      <c r="V49" s="4">
+        <f>IFERROR(IF(OR(E49="Enhanced",E49="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C49,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C49,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C49,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C49,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="W49" s="16">
         <f>IFERROR(P49*(Q49*R49+S49*T49+U49),0)</f>
         <v/>
       </c>
-      <c r="X49" s="16">
+      <c r="X49" s="22">
         <f>IFERROR(IF(V49=0,"",(Q49+S49)/V49),"")</f>
         <v/>
       </c>
       <c r="Y49" s="4" t="n"/>
       <c r="Z49" s="4" t="n"/>
-      <c r="AA49" s="16">
+      <c r="AA49" s="22">
         <f>IFERROR(Y49+Z49,0)</f>
         <v/>
       </c>
@@ -12881,7 +13324,7 @@
       <c r="AE49" s="4" t="n"/>
       <c r="AF49" s="4" t="n"/>
       <c r="AG49" s="4" t="n"/>
-      <c r="AH49" s="16">
+      <c r="AH49" s="22">
         <f>IFERROR(AB49*INDEX(PARAMS_Trees,1,3)+AC49*INDEX(PARAMS_Trees,2,3)+AD49*INDEX(PARAMS_Trees,3,3)+AE49*INDEX(PARAMS_Trees,4,3)+AF49*INDEX(PARAMS_Trees,5,3)+AG49*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
       </c>
@@ -12901,7 +13344,7 @@
         <f>IFERROR(VLOOKUP(C49,'CDA'!$A$58:$D$67,4,FALSE),0)</f>
         <v/>
       </c>
-      <c r="AM49" s="16">
+      <c r="AM49" s="22">
         <f>IFERROR(IF(AL49=0,AK49,MIN(AK49,AL49)),0)</f>
         <v/>
       </c>
@@ -12911,11 +13354,14 @@
       <c r="B50" s="4" t="n"/>
       <c r="C50" s="4" t="n"/>
       <c r="D50" s="4" t="n"/>
-      <c r="E50" s="4" t="n"/>
+      <c r="E50" s="21" t="n"/>
       <c r="F50" s="4" t="n"/>
       <c r="G50" s="4" t="n"/>
       <c r="H50" s="4" t="n"/>
-      <c r="I50" s="4" t="n"/>
+      <c r="I50" s="4">
+        <f>IFERROR(IF(OR(E50="Enhanced",E50="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C50,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C50,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C50,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C50,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="J50" s="16">
         <f>IFERROR(IFS(AND(D50="Permeable Pavement",E50="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D50="Permeable Pavement",E50="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D50="Bioretention",E50="Standard"),INDEX(PARAMS_BMP,3,5),AND(D50="Bioretention",E50="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D50="Bioretention",E50="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D50="Dry Swale",E50="—"),INDEX(PARAMS_BMP,6,5),AND(D50="Wet Swale",E50="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
         <v/>
@@ -12928,7 +13374,7 @@
         <f>IFERROR(IF(I50=0,"",G50/I50),"")</f>
         <v/>
       </c>
-      <c r="M50" s="16">
+      <c r="M50" s="22">
         <f>IFERROR(IF(L50="","",IF(L50&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
@@ -12949,18 +13395,21 @@
         <v/>
       </c>
       <c r="U50" s="4" t="n"/>
-      <c r="V50" s="4" t="n"/>
+      <c r="V50" s="4">
+        <f>IFERROR(IF(OR(E50="Enhanced",E50="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C50,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C50,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C50,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C50,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="W50" s="16">
         <f>IFERROR(P50*(Q50*R50+S50*T50+U50),0)</f>
         <v/>
       </c>
-      <c r="X50" s="16">
+      <c r="X50" s="22">
         <f>IFERROR(IF(V50=0,"",(Q50+S50)/V50),"")</f>
         <v/>
       </c>
       <c r="Y50" s="4" t="n"/>
       <c r="Z50" s="4" t="n"/>
-      <c r="AA50" s="16">
+      <c r="AA50" s="22">
         <f>IFERROR(Y50+Z50,0)</f>
         <v/>
       </c>
@@ -12970,7 +13419,7 @@
       <c r="AE50" s="4" t="n"/>
       <c r="AF50" s="4" t="n"/>
       <c r="AG50" s="4" t="n"/>
-      <c r="AH50" s="16">
+      <c r="AH50" s="22">
         <f>IFERROR(AB50*INDEX(PARAMS_Trees,1,3)+AC50*INDEX(PARAMS_Trees,2,3)+AD50*INDEX(PARAMS_Trees,3,3)+AE50*INDEX(PARAMS_Trees,4,3)+AF50*INDEX(PARAMS_Trees,5,3)+AG50*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
       </c>
@@ -12990,7 +13439,7 @@
         <f>IFERROR(VLOOKUP(C50,'CDA'!$A$58:$D$67,4,FALSE),0)</f>
         <v/>
       </c>
-      <c r="AM50" s="16">
+      <c r="AM50" s="22">
         <f>IFERROR(IF(AL50=0,AK50,MIN(AK50,AL50)),0)</f>
         <v/>
       </c>
@@ -13000,11 +13449,14 @@
       <c r="B51" s="4" t="n"/>
       <c r="C51" s="4" t="n"/>
       <c r="D51" s="4" t="n"/>
-      <c r="E51" s="4" t="n"/>
+      <c r="E51" s="21" t="n"/>
       <c r="F51" s="4" t="n"/>
       <c r="G51" s="4" t="n"/>
       <c r="H51" s="4" t="n"/>
-      <c r="I51" s="4" t="n"/>
+      <c r="I51" s="4">
+        <f>IFERROR(IF(OR(E51="Enhanced",E51="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C51,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C51,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C51,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C51,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="J51" s="16">
         <f>IFERROR(IFS(AND(D51="Permeable Pavement",E51="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D51="Permeable Pavement",E51="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D51="Bioretention",E51="Standard"),INDEX(PARAMS_BMP,3,5),AND(D51="Bioretention",E51="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D51="Bioretention",E51="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D51="Dry Swale",E51="—"),INDEX(PARAMS_BMP,6,5),AND(D51="Wet Swale",E51="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
         <v/>
@@ -13017,7 +13469,7 @@
         <f>IFERROR(IF(I51=0,"",G51/I51),"")</f>
         <v/>
       </c>
-      <c r="M51" s="16">
+      <c r="M51" s="22">
         <f>IFERROR(IF(L51="","",IF(L51&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
@@ -13038,18 +13490,21 @@
         <v/>
       </c>
       <c r="U51" s="4" t="n"/>
-      <c r="V51" s="4" t="n"/>
+      <c r="V51" s="4">
+        <f>IFERROR(IF(OR(E51="Enhanced",E51="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C51,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C51,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C51,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C51,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="W51" s="16">
         <f>IFERROR(P51*(Q51*R51+S51*T51+U51),0)</f>
         <v/>
       </c>
-      <c r="X51" s="16">
+      <c r="X51" s="22">
         <f>IFERROR(IF(V51=0,"",(Q51+S51)/V51),"")</f>
         <v/>
       </c>
       <c r="Y51" s="4" t="n"/>
       <c r="Z51" s="4" t="n"/>
-      <c r="AA51" s="16">
+      <c r="AA51" s="22">
         <f>IFERROR(Y51+Z51,0)</f>
         <v/>
       </c>
@@ -13059,7 +13514,7 @@
       <c r="AE51" s="4" t="n"/>
       <c r="AF51" s="4" t="n"/>
       <c r="AG51" s="4" t="n"/>
-      <c r="AH51" s="16">
+      <c r="AH51" s="22">
         <f>IFERROR(AB51*INDEX(PARAMS_Trees,1,3)+AC51*INDEX(PARAMS_Trees,2,3)+AD51*INDEX(PARAMS_Trees,3,3)+AE51*INDEX(PARAMS_Trees,4,3)+AF51*INDEX(PARAMS_Trees,5,3)+AG51*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
       </c>
@@ -13079,7 +13534,7 @@
         <f>IFERROR(VLOOKUP(C51,'CDA'!$A$58:$D$67,4,FALSE),0)</f>
         <v/>
       </c>
-      <c r="AM51" s="16">
+      <c r="AM51" s="22">
         <f>IFERROR(IF(AL51=0,AK51,MIN(AK51,AL51)),0)</f>
         <v/>
       </c>
@@ -13089,11 +13544,14 @@
       <c r="B52" s="4" t="n"/>
       <c r="C52" s="4" t="n"/>
       <c r="D52" s="4" t="n"/>
-      <c r="E52" s="4" t="n"/>
+      <c r="E52" s="21" t="n"/>
       <c r="F52" s="4" t="n"/>
       <c r="G52" s="4" t="n"/>
       <c r="H52" s="4" t="n"/>
-      <c r="I52" s="4" t="n"/>
+      <c r="I52" s="4">
+        <f>IFERROR(IF(OR(E52="Enhanced",E52="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C52,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C52,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C52,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C52,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="J52" s="16">
         <f>IFERROR(IFS(AND(D52="Permeable Pavement",E52="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D52="Permeable Pavement",E52="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D52="Bioretention",E52="Standard"),INDEX(PARAMS_BMP,3,5),AND(D52="Bioretention",E52="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D52="Bioretention",E52="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D52="Dry Swale",E52="—"),INDEX(PARAMS_BMP,6,5),AND(D52="Wet Swale",E52="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
         <v/>
@@ -13106,7 +13564,7 @@
         <f>IFERROR(IF(I52=0,"",G52/I52),"")</f>
         <v/>
       </c>
-      <c r="M52" s="16">
+      <c r="M52" s="22">
         <f>IFERROR(IF(L52="","",IF(L52&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
@@ -13127,18 +13585,21 @@
         <v/>
       </c>
       <c r="U52" s="4" t="n"/>
-      <c r="V52" s="4" t="n"/>
+      <c r="V52" s="4">
+        <f>IFERROR(IF(OR(E52="Enhanced",E52="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C52,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C52,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C52,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C52,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="W52" s="16">
         <f>IFERROR(P52*(Q52*R52+S52*T52+U52),0)</f>
         <v/>
       </c>
-      <c r="X52" s="16">
+      <c r="X52" s="22">
         <f>IFERROR(IF(V52=0,"",(Q52+S52)/V52),"")</f>
         <v/>
       </c>
       <c r="Y52" s="4" t="n"/>
       <c r="Z52" s="4" t="n"/>
-      <c r="AA52" s="16">
+      <c r="AA52" s="22">
         <f>IFERROR(Y52+Z52,0)</f>
         <v/>
       </c>
@@ -13148,7 +13609,7 @@
       <c r="AE52" s="4" t="n"/>
       <c r="AF52" s="4" t="n"/>
       <c r="AG52" s="4" t="n"/>
-      <c r="AH52" s="16">
+      <c r="AH52" s="22">
         <f>IFERROR(AB52*INDEX(PARAMS_Trees,1,3)+AC52*INDEX(PARAMS_Trees,2,3)+AD52*INDEX(PARAMS_Trees,3,3)+AE52*INDEX(PARAMS_Trees,4,3)+AF52*INDEX(PARAMS_Trees,5,3)+AG52*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
       </c>
@@ -13168,7 +13629,7 @@
         <f>IFERROR(VLOOKUP(C52,'CDA'!$A$58:$D$67,4,FALSE),0)</f>
         <v/>
       </c>
-      <c r="AM52" s="16">
+      <c r="AM52" s="22">
         <f>IFERROR(IF(AL52=0,AK52,MIN(AK52,AL52)),0)</f>
         <v/>
       </c>
@@ -13178,11 +13639,14 @@
       <c r="B53" s="4" t="n"/>
       <c r="C53" s="4" t="n"/>
       <c r="D53" s="4" t="n"/>
-      <c r="E53" s="4" t="n"/>
+      <c r="E53" s="21" t="n"/>
       <c r="F53" s="4" t="n"/>
       <c r="G53" s="4" t="n"/>
       <c r="H53" s="4" t="n"/>
-      <c r="I53" s="4" t="n"/>
+      <c r="I53" s="4">
+        <f>IFERROR(IF(OR(E53="Enhanced",E53="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C53,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C53,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C53,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C53,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="J53" s="16">
         <f>IFERROR(IFS(AND(D53="Permeable Pavement",E53="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D53="Permeable Pavement",E53="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D53="Bioretention",E53="Standard"),INDEX(PARAMS_BMP,3,5),AND(D53="Bioretention",E53="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D53="Bioretention",E53="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D53="Dry Swale",E53="—"),INDEX(PARAMS_BMP,6,5),AND(D53="Wet Swale",E53="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
         <v/>
@@ -13195,7 +13659,7 @@
         <f>IFERROR(IF(I53=0,"",G53/I53),"")</f>
         <v/>
       </c>
-      <c r="M53" s="16">
+      <c r="M53" s="22">
         <f>IFERROR(IF(L53="","",IF(L53&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
@@ -13216,18 +13680,21 @@
         <v/>
       </c>
       <c r="U53" s="4" t="n"/>
-      <c r="V53" s="4" t="n"/>
+      <c r="V53" s="4">
+        <f>IFERROR(IF(OR(E53="Enhanced",E53="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C53,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C53,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C53,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C53,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <v/>
+      </c>
       <c r="W53" s="16">
         <f>IFERROR(P53*(Q53*R53+S53*T53+U53),0)</f>
         <v/>
       </c>
-      <c r="X53" s="16">
+      <c r="X53" s="22">
         <f>IFERROR(IF(V53=0,"",(Q53+S53)/V53),"")</f>
         <v/>
       </c>
       <c r="Y53" s="4" t="n"/>
       <c r="Z53" s="4" t="n"/>
-      <c r="AA53" s="16">
+      <c r="AA53" s="22">
         <f>IFERROR(Y53+Z53,0)</f>
         <v/>
       </c>
@@ -13237,7 +13704,7 @@
       <c r="AE53" s="4" t="n"/>
       <c r="AF53" s="4" t="n"/>
       <c r="AG53" s="4" t="n"/>
-      <c r="AH53" s="16">
+      <c r="AH53" s="22">
         <f>IFERROR(AB53*INDEX(PARAMS_Trees,1,3)+AC53*INDEX(PARAMS_Trees,2,3)+AD53*INDEX(PARAMS_Trees,3,3)+AE53*INDEX(PARAMS_Trees,4,3)+AF53*INDEX(PARAMS_Trees,5,3)+AG53*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
       </c>
@@ -13257,7 +13724,7 @@
         <f>IFERROR(VLOOKUP(C53,'CDA'!$A$58:$D$67,4,FALSE),0)</f>
         <v/>
       </c>
-      <c r="AM53" s="16">
+      <c r="AM53" s="22">
         <f>IFERROR(IF(AL53=0,AK53,MIN(AK53,AL53)),0)</f>
         <v/>
       </c>
@@ -13271,7 +13738,12 @@
       <c r="B56" s="5" t="n"/>
       <c r="C56" s="5" t="n"/>
       <c r="D56" s="5" t="n"/>
-      <c r="E56" s="2" t="n"/>
+      <c r="E56" s="23" t="n"/>
+      <c r="M56" s="24" t="n"/>
+      <c r="X56" s="24" t="n"/>
+      <c r="AA56" s="24" t="n"/>
+      <c r="AH56" s="24" t="n"/>
+      <c r="AM56" s="24" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
@@ -13294,11 +13766,16 @@
           <t>Surplus / Deficit (CF)</t>
         </is>
       </c>
-      <c r="E57" s="6" t="inlineStr">
+      <c r="E57" s="20" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
+      <c r="M57" s="24" t="n"/>
+      <c r="X57" s="24" t="n"/>
+      <c r="AA57" s="24" t="n"/>
+      <c r="AH57" s="24" t="n"/>
+      <c r="AM57" s="24" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="16">
@@ -13317,10 +13794,15 @@
         <f>IFERROR(C58-B58,"")</f>
         <v/>
       </c>
-      <c r="E58" s="16">
+      <c r="E58" s="22">
         <f>IFERROR(IF(B58=0,"—",IF(D58&gt;=0,"✓","✗")),"")</f>
         <v/>
       </c>
+      <c r="M58" s="24" t="n"/>
+      <c r="X58" s="24" t="n"/>
+      <c r="AA58" s="24" t="n"/>
+      <c r="AH58" s="24" t="n"/>
+      <c r="AM58" s="24" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="16">
@@ -13339,10 +13821,15 @@
         <f>IFERROR(C59-B59,"")</f>
         <v/>
       </c>
-      <c r="E59" s="16">
+      <c r="E59" s="22">
         <f>IFERROR(IF(B59=0,"—",IF(D59&gt;=0,"✓","✗")),"")</f>
         <v/>
       </c>
+      <c r="M59" s="24" t="n"/>
+      <c r="X59" s="24" t="n"/>
+      <c r="AA59" s="24" t="n"/>
+      <c r="AH59" s="24" t="n"/>
+      <c r="AM59" s="24" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="16">
@@ -13361,10 +13848,15 @@
         <f>IFERROR(C60-B60,"")</f>
         <v/>
       </c>
-      <c r="E60" s="16">
+      <c r="E60" s="22">
         <f>IFERROR(IF(B60=0,"—",IF(D60&gt;=0,"✓","✗")),"")</f>
         <v/>
       </c>
+      <c r="M60" s="24" t="n"/>
+      <c r="X60" s="24" t="n"/>
+      <c r="AA60" s="24" t="n"/>
+      <c r="AH60" s="24" t="n"/>
+      <c r="AM60" s="24" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="16">
@@ -13383,10 +13875,15 @@
         <f>IFERROR(C61-B61,"")</f>
         <v/>
       </c>
-      <c r="E61" s="16">
+      <c r="E61" s="22">
         <f>IFERROR(IF(B61=0,"—",IF(D61&gt;=0,"✓","✗")),"")</f>
         <v/>
       </c>
+      <c r="M61" s="24" t="n"/>
+      <c r="X61" s="24" t="n"/>
+      <c r="AA61" s="24" t="n"/>
+      <c r="AH61" s="24" t="n"/>
+      <c r="AM61" s="24" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="16">
@@ -13405,10 +13902,15 @@
         <f>IFERROR(C62-B62,"")</f>
         <v/>
       </c>
-      <c r="E62" s="16">
+      <c r="E62" s="22">
         <f>IFERROR(IF(B62=0,"—",IF(D62&gt;=0,"✓","✗")),"")</f>
         <v/>
       </c>
+      <c r="M62" s="24" t="n"/>
+      <c r="X62" s="24" t="n"/>
+      <c r="AA62" s="24" t="n"/>
+      <c r="AH62" s="24" t="n"/>
+      <c r="AM62" s="24" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="16">
@@ -13427,10 +13929,15 @@
         <f>IFERROR(C63-B63,"")</f>
         <v/>
       </c>
-      <c r="E63" s="16">
+      <c r="E63" s="22">
         <f>IFERROR(IF(B63=0,"—",IF(D63&gt;=0,"✓","✗")),"")</f>
         <v/>
       </c>
+      <c r="M63" s="24" t="n"/>
+      <c r="X63" s="24" t="n"/>
+      <c r="AA63" s="24" t="n"/>
+      <c r="AH63" s="24" t="n"/>
+      <c r="AM63" s="24" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="16">
@@ -13449,10 +13956,15 @@
         <f>IFERROR(C64-B64,"")</f>
         <v/>
       </c>
-      <c r="E64" s="16">
+      <c r="E64" s="22">
         <f>IFERROR(IF(B64=0,"—",IF(D64&gt;=0,"✓","✗")),"")</f>
         <v/>
       </c>
+      <c r="M64" s="24" t="n"/>
+      <c r="X64" s="24" t="n"/>
+      <c r="AA64" s="24" t="n"/>
+      <c r="AH64" s="24" t="n"/>
+      <c r="AM64" s="24" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="16">
@@ -13471,10 +13983,15 @@
         <f>IFERROR(C65-B65,"")</f>
         <v/>
       </c>
-      <c r="E65" s="16">
+      <c r="E65" s="22">
         <f>IFERROR(IF(B65=0,"—",IF(D65&gt;=0,"✓","✗")),"")</f>
         <v/>
       </c>
+      <c r="M65" s="24" t="n"/>
+      <c r="X65" s="24" t="n"/>
+      <c r="AA65" s="24" t="n"/>
+      <c r="AH65" s="24" t="n"/>
+      <c r="AM65" s="24" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="16">
@@ -13493,10 +14010,15 @@
         <f>IFERROR(C66-B66,"")</f>
         <v/>
       </c>
-      <c r="E66" s="16">
+      <c r="E66" s="22">
         <f>IFERROR(IF(B66=0,"—",IF(D66&gt;=0,"✓","✗")),"")</f>
         <v/>
       </c>
+      <c r="M66" s="24" t="n"/>
+      <c r="X66" s="24" t="n"/>
+      <c r="AA66" s="24" t="n"/>
+      <c r="AH66" s="24" t="n"/>
+      <c r="AM66" s="24" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="16">
@@ -13515,13 +14037,19 @@
         <f>IFERROR(C67-B67,"")</f>
         <v/>
       </c>
-      <c r="E67" s="16">
+      <c r="E67" s="22">
         <f>IFERROR(IF(B67=0,"—",IF(D67&gt;=0,"✓","✗")),"")</f>
         <v/>
       </c>
+      <c r="M67" s="24" t="n"/>
+      <c r="X67" s="24" t="n"/>
+      <c r="AA67" s="24" t="n"/>
+      <c r="AH67" s="24" t="n"/>
+      <c r="AM67" s="24" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
+    <mergeCell ref="A2:AM2"/>
     <mergeCell ref="A1:AM1"/>
     <mergeCell ref="A56:E56"/>
   </mergeCells>
@@ -13594,7 +14122,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="B1" s="17" t="inlineStr">
+      <c r="B1" s="25" t="inlineStr">
         <is>
           <t>Project Name:</t>
         </is>
@@ -13603,12 +14131,12 @@
         <f>PROJECT_Name</f>
         <v/>
       </c>
-      <c r="H1" s="17" t="inlineStr">
+      <c r="H1" s="25" t="inlineStr">
         <is>
           <t>Project No:</t>
         </is>
       </c>
-      <c r="L1" s="17" t="inlineStr">
+      <c r="L1" s="25" t="inlineStr">
         <is>
           <t>Check One: MS4         CSS</t>
         </is>
@@ -13617,7 +14145,7 @@
         <f>PROJECT_MS4</f>
         <v/>
       </c>
-      <c r="P1" s="17" t="inlineStr">
+      <c r="P1" s="25" t="inlineStr">
         <is>
           <t>Check if in AWDZ:</t>
         </is>
@@ -13626,7 +14154,7 @@
         <f>PROJECT_AWDZ</f>
         <v/>
       </c>
-      <c r="S1" s="17" t="inlineStr">
+      <c r="S1" s="25" t="inlineStr">
         <is>
           <t>DOEE Plan Review No.:</t>
         </is>
@@ -13827,462 +14355,462 @@
       </c>
     </row>
     <row r="8" ht="102.75" customHeight="1">
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>Update from 65% based on refined or revised design: 
 Number and list each drainage area within the project limits of disturbance (LOD). Provide the drainage area square footage that contributes runoff in the LOD and outside the LOD. The SWRv is calculated for each drainage area. Provide corresponding drainage area identifications on the SWMP.</t>
         </is>
       </c>
-      <c r="L8" s="17" t="inlineStr">
+      <c r="L8" s="25" t="inlineStr">
         <is>
           <t>Record the water table, bedrock concerns, infiltration rate, and hotspot concerns within the LOD for each drainage area.</t>
         </is>
       </c>
-      <c r="Q8" s="17" t="inlineStr">
+      <c r="Q8" s="25" t="inlineStr">
         <is>
           <t>On the SWMP, depict utility locations and conveyance infrastructure to confirm/adjust opportunities for land conversions and BMPs. Delineate areas of potential conflict, and areas without conflict, including areas where minimum depths for BMPs can not be met.  Delineate trees (size, species, condition) and tree protection.</t>
         </is>
       </c>
-      <c r="W8" s="17" t="inlineStr">
+      <c r="W8" s="25" t="inlineStr">
         <is>
           <t>For land conversion and BMP opportunities already defined at 30%, and for new opportunities added, provide the areas below.  Land Conversion and BMP surface areas within the LOD must be reflected in the SWRv computation; update those columns as necessary. Additional allowable BMPs such as impervious surface disconnection, swales, and infiltration should also be considered and described in the narrative. Describe the reason for eliminated Land Conversion/BMP locations.</t>
         </is>
       </c>
-      <c r="AC8" s="17" t="inlineStr">
+      <c r="AC8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">Provide the contributing drainage area to the BMP locations. The ceiling stormwater runoff volume reaching the BMPs is calculated. </t>
         </is>
       </c>
-      <c r="AG8" s="17" t="inlineStr">
+      <c r="AG8" s="25" t="inlineStr">
         <is>
           <t>Calculate and sum the total maximum possible BMP storage volumes. Total the number of proposed trees meeting the required soil volume to be considered for stormwater retention volume.  Total the maximum retention volume capacity of all facilities and compare to the required regulated volume. If a deficit exists, review BMP placements/sizes to determine if additional volume can be captured.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="42.6" customHeight="1">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="26" t="inlineStr">
         <is>
           <t>Drainage Area
 ID</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">Drainage Area </t>
         </is>
       </c>
-      <c r="J9" s="18" t="inlineStr">
+      <c r="J9" s="26" t="inlineStr">
         <is>
           <t>SWRv</t>
         </is>
       </c>
-      <c r="L9" s="18" t="inlineStr">
+      <c r="L9" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve"> Hydrologic Soil Group</t>
         </is>
       </c>
-      <c r="M9" s="18" t="inlineStr">
+      <c r="M9" s="26" t="inlineStr">
         <is>
           <t>Water Table OK?</t>
         </is>
       </c>
-      <c r="N9" s="18" t="inlineStr">
+      <c r="N9" s="26" t="inlineStr">
         <is>
           <t>Bedrock Elevation OK?</t>
         </is>
       </c>
-      <c r="O9" s="18" t="inlineStr">
+      <c r="O9" s="26" t="inlineStr">
         <is>
           <t>Infiltration Rate</t>
         </is>
       </c>
-      <c r="P9" s="18" t="inlineStr">
+      <c r="P9" s="26" t="inlineStr">
         <is>
           <t>Hotspot Concern Found?</t>
         </is>
       </c>
-      <c r="Q9" s="18" t="inlineStr">
+      <c r="Q9" s="26" t="inlineStr">
         <is>
           <t>Preservation of Small, Large, and/or Special/Heritage Trees which are in fair or better condition</t>
         </is>
       </c>
-      <c r="W9" s="18" t="inlineStr">
+      <c r="W9" s="26" t="inlineStr">
         <is>
           <t>Land Conversion Area</t>
         </is>
       </c>
-      <c r="Y9" s="18" t="inlineStr">
+      <c r="Y9" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">Bioretention Opportunity Areas </t>
         </is>
       </c>
-      <c r="AA9" s="18" t="inlineStr">
+      <c r="AA9" s="26" t="inlineStr">
         <is>
           <t>Permeable Pavement Opportunity Areas</t>
         </is>
       </c>
-      <c r="AC9" s="18" t="inlineStr">
+      <c r="AC9" s="26" t="inlineStr">
         <is>
           <t>Total BMP Contributing Drainage Area</t>
         </is>
       </c>
-      <c r="AE9" s="18" t="inlineStr">
+      <c r="AE9" s="26" t="inlineStr">
         <is>
           <t>1.7 inch (ceiling) stormwater runoff reaching BMPs</t>
         </is>
       </c>
-      <c r="AG9" s="18" t="inlineStr">
+      <c r="AG9" s="26" t="inlineStr">
         <is>
           <t>Max. Storage Volume of Bioretention Based on Size (Total in DA - See separate sizing computations)</t>
         </is>
       </c>
-      <c r="AH9" s="18" t="inlineStr">
+      <c r="AH9" s="26" t="inlineStr">
         <is>
           <t>Max. Storage Volume of Permeable Pavement. Based on Size (Total in DA - See separate sizing computations)</t>
         </is>
       </c>
-      <c r="AI9" s="18" t="inlineStr">
+      <c r="AI9" s="26" t="inlineStr">
         <is>
           <t>Max. "Other" Storage Volume - (Total in DA - See separate sizing computations)</t>
         </is>
       </c>
-      <c r="AJ9" s="18" t="inlineStr">
+      <c r="AJ9" s="26" t="inlineStr">
         <is>
           <t>No. of proposed small trees meeting soil volume requirement</t>
         </is>
       </c>
-      <c r="AK9" s="18" t="inlineStr">
+      <c r="AK9" s="26" t="inlineStr">
         <is>
           <t>No. of proposed large trees meeting soil volume requirement</t>
         </is>
       </c>
-      <c r="AL9" s="18" t="inlineStr">
+      <c r="AL9" s="26" t="inlineStr">
         <is>
           <t>Total Sv Practice -Maximum Retention Volume Achievable (BMPs and Trees)</t>
         </is>
       </c>
-      <c r="AM9" s="18" t="inlineStr">
+      <c r="AM9" s="26" t="inlineStr">
         <is>
           <t>Overage / (Deficit) Volume (as compared to SWRv)</t>
         </is>
       </c>
-      <c r="AP9" s="18" t="inlineStr">
+      <c r="AP9" s="26" t="inlineStr">
         <is>
           <t>Runoff Coefficient</t>
         </is>
       </c>
     </row>
     <row r="10" ht="48.75" customHeight="1">
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>Impervious 
 within LOD</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" s="26" t="inlineStr">
         <is>
           <t>Compacted    within LOD</t>
         </is>
       </c>
-      <c r="D10" s="18" t="inlineStr">
+      <c r="D10" s="26" t="inlineStr">
         <is>
           <t>Natural 
 within LOD</t>
         </is>
       </c>
-      <c r="E10" s="18" t="inlineStr">
+      <c r="E10" s="26" t="inlineStr">
         <is>
           <t>Total within LOD</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="F10" s="26" t="inlineStr">
         <is>
           <t>Impervious outside LOD</t>
         </is>
       </c>
-      <c r="G10" s="18" t="inlineStr">
+      <c r="G10" s="26" t="inlineStr">
         <is>
           <t>Compacted outside LOD</t>
         </is>
       </c>
-      <c r="H10" s="18" t="inlineStr">
+      <c r="H10" s="26" t="inlineStr">
         <is>
           <t>Natural outside LOD</t>
         </is>
       </c>
-      <c r="I10" s="18" t="inlineStr">
+      <c r="I10" s="26" t="inlineStr">
         <is>
           <t>Total outside LOD</t>
         </is>
       </c>
-      <c r="J10" s="18" t="inlineStr">
+      <c r="J10" s="26" t="inlineStr">
         <is>
           <t>Within LOD</t>
         </is>
       </c>
-      <c r="K10" s="18" t="inlineStr">
+      <c r="K10" s="26" t="inlineStr">
         <is>
           <t>Outside LOD</t>
         </is>
       </c>
-      <c r="W10" s="18" t="inlineStr">
+      <c r="W10" s="26" t="inlineStr">
         <is>
           <t>Within LOD</t>
         </is>
       </c>
-      <c r="X10" s="18" t="inlineStr">
+      <c r="X10" s="26" t="inlineStr">
         <is>
           <t>Adjacent to LOD</t>
         </is>
       </c>
-      <c r="Y10" s="18" t="inlineStr">
+      <c r="Y10" s="26" t="inlineStr">
         <is>
           <t>Within LOD</t>
         </is>
       </c>
-      <c r="Z10" s="18" t="inlineStr">
+      <c r="Z10" s="26" t="inlineStr">
         <is>
           <t>Adjacent to LOD</t>
         </is>
       </c>
-      <c r="AA10" s="18" t="inlineStr">
+      <c r="AA10" s="26" t="inlineStr">
         <is>
           <t>Within LOD</t>
         </is>
       </c>
-      <c r="AB10" s="18" t="inlineStr">
+      <c r="AB10" s="26" t="inlineStr">
         <is>
           <t>Adjacent to LOD</t>
         </is>
       </c>
-      <c r="AC10" s="18" t="inlineStr">
+      <c r="AC10" s="26" t="inlineStr">
         <is>
           <t>Within LOD</t>
         </is>
       </c>
-      <c r="AD10" s="18" t="inlineStr">
+      <c r="AD10" s="26" t="inlineStr">
         <is>
           <t>Adjacent to LOD</t>
         </is>
       </c>
-      <c r="AE10" s="18" t="inlineStr">
+      <c r="AE10" s="26" t="inlineStr">
         <is>
           <t>Within LOD</t>
         </is>
       </c>
-      <c r="AF10" s="18" t="inlineStr">
+      <c r="AF10" s="26" t="inlineStr">
         <is>
           <t>Adjacent to LOD</t>
         </is>
       </c>
-      <c r="AP10" s="18" t="inlineStr">
+      <c r="AP10" s="26" t="inlineStr">
         <is>
           <t>Within LOD</t>
         </is>
       </c>
-      <c r="AQ10" s="18" t="inlineStr">
+      <c r="AQ10" s="26" t="inlineStr">
         <is>
           <t>Outside LOD</t>
         </is>
       </c>
     </row>
     <row r="11" ht="32.45" customHeight="1">
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="26" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="26" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D11" s="26" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="E11" s="18" t="inlineStr">
+      <c r="E11" s="26" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="F11" s="26" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="G11" s="18" t="inlineStr">
+      <c r="G11" s="26" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="H11" s="18" t="inlineStr">
+      <c r="H11" s="26" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="I11" s="18" t="inlineStr">
+      <c r="I11" s="26" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="J11" s="18" t="inlineStr">
+      <c r="J11" s="26" t="inlineStr">
         <is>
           <t>CF</t>
         </is>
       </c>
-      <c r="K11" s="18" t="inlineStr">
+      <c r="K11" s="26" t="inlineStr">
         <is>
           <t>CF</t>
         </is>
       </c>
-      <c r="L11" s="18" t="inlineStr">
+      <c r="L11" s="26" t="inlineStr">
         <is>
           <t>A, B, C, D, or Urban Land</t>
         </is>
       </c>
-      <c r="M11" s="18" t="inlineStr">
+      <c r="M11" s="26" t="inlineStr">
         <is>
           <t>Y/N</t>
         </is>
       </c>
-      <c r="N11" s="18" t="inlineStr">
+      <c r="N11" s="26" t="inlineStr">
         <is>
           <t>Y/N</t>
         </is>
       </c>
-      <c r="O11" s="18" t="inlineStr">
+      <c r="O11" s="26" t="inlineStr">
         <is>
           <t>in-hr</t>
         </is>
       </c>
-      <c r="P11" s="18" t="inlineStr">
+      <c r="P11" s="26" t="inlineStr">
         <is>
           <t>Y/N</t>
         </is>
       </c>
-      <c r="Q11" s="18" t="inlineStr">
+      <c r="Q11" s="26" t="inlineStr">
         <is>
           <t># of Small Trees</t>
         </is>
       </c>
-      <c r="R11" s="18" t="inlineStr">
+      <c r="R11" s="26" t="inlineStr">
         <is>
           <t>Tree Volume Credit (CF)</t>
         </is>
       </c>
-      <c r="S11" s="18" t="inlineStr">
+      <c r="S11" s="26" t="inlineStr">
         <is>
           <t># of Large Trees</t>
         </is>
       </c>
-      <c r="T11" s="18" t="inlineStr">
+      <c r="T11" s="26" t="inlineStr">
         <is>
           <t>Tree Volume Credit (CF)</t>
         </is>
       </c>
-      <c r="U11" s="18" t="inlineStr">
+      <c r="U11" s="26" t="inlineStr">
         <is>
           <t># of Special/ Heritage Trees</t>
         </is>
       </c>
-      <c r="V11" s="18" t="inlineStr">
+      <c r="V11" s="26" t="inlineStr">
         <is>
           <t>Tree Volume Credit (CF)</t>
         </is>
       </c>
-      <c r="W11" s="18" t="inlineStr">
+      <c r="W11" s="26" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="X11" s="18" t="inlineStr">
+      <c r="X11" s="26" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="Y11" s="18" t="inlineStr">
+      <c r="Y11" s="26" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="Z11" s="18" t="inlineStr">
+      <c r="Z11" s="26" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="AA11" s="18" t="inlineStr">
+      <c r="AA11" s="26" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="AB11" s="18" t="inlineStr">
+      <c r="AB11" s="26" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="AC11" s="18" t="inlineStr">
+      <c r="AC11" s="26" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="AD11" s="18" t="inlineStr">
+      <c r="AD11" s="26" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="AE11" s="18" t="inlineStr">
+      <c r="AE11" s="26" t="inlineStr">
         <is>
           <t>CF</t>
         </is>
       </c>
-      <c r="AF11" s="18" t="inlineStr">
+      <c r="AF11" s="26" t="inlineStr">
         <is>
           <t>CF</t>
         </is>
       </c>
-      <c r="AG11" s="18" t="inlineStr">
+      <c r="AG11" s="26" t="inlineStr">
         <is>
           <t>CF</t>
         </is>
       </c>
-      <c r="AH11" s="18" t="inlineStr">
+      <c r="AH11" s="26" t="inlineStr">
         <is>
           <t>CF</t>
         </is>
       </c>
-      <c r="AI11" s="18" t="inlineStr">
+      <c r="AI11" s="26" t="inlineStr">
         <is>
           <t>CF</t>
         </is>
       </c>
-      <c r="AJ11" s="18" t="inlineStr">
+      <c r="AJ11" s="26" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="AK11" s="18" t="inlineStr">
+      <c r="AK11" s="26" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="AL11" s="18" t="inlineStr">
+      <c r="AL11" s="26" t="inlineStr">
         <is>
           <t>CF</t>
         </is>
       </c>
-      <c r="AM11" s="18" t="inlineStr">
+      <c r="AM11" s="26" t="inlineStr">
         <is>
           <t>CF</t>
         </is>
       </c>
-      <c r="AP11" s="18" t="inlineStr">
+      <c r="AP11" s="26" t="inlineStr">
         <is>
           <t>(unitless)</t>
         </is>
       </c>
-      <c r="AQ11" s="18" t="inlineStr">
+      <c r="AQ11" s="26" t="inlineStr">
         <is>
           <t>(unitless)</t>
         </is>
@@ -14290,19 +14818,19 @@
     </row>
     <row r="12" ht="16.25" customHeight="1">
       <c r="A12" s="16">
-        <f>'SDA'!A58</f>
+        <f>IFERROR('SDA'!A58,"")</f>
         <v/>
       </c>
       <c r="B12" s="16">
-        <f>'SDA'!F58</f>
+        <f>IFERROR('SDA'!F58,0)</f>
         <v/>
       </c>
       <c r="C12" s="16">
-        <f>'SDA'!G58</f>
+        <f>IFERROR('SDA'!G58,0)</f>
         <v/>
       </c>
       <c r="D12" s="16">
-        <f>'SDA'!H58</f>
+        <f>IFERROR('SDA'!H58,0)</f>
         <v/>
       </c>
       <c r="E12" s="16">
@@ -14435,19 +14963,19 @@
     </row>
     <row r="13" ht="16.25" customHeight="1">
       <c r="A13" s="16">
-        <f>'SDA'!A59</f>
+        <f>IFERROR('SDA'!A59,"")</f>
         <v/>
       </c>
       <c r="B13" s="16">
-        <f>'SDA'!F59</f>
+        <f>IFERROR('SDA'!F59,0)</f>
         <v/>
       </c>
       <c r="C13" s="16">
-        <f>'SDA'!G59</f>
+        <f>IFERROR('SDA'!G59,0)</f>
         <v/>
       </c>
       <c r="D13" s="16">
-        <f>'SDA'!H59</f>
+        <f>IFERROR('SDA'!H59,0)</f>
         <v/>
       </c>
       <c r="E13" s="16">
@@ -14580,19 +15108,19 @@
     </row>
     <row r="14" ht="16.25" customHeight="1">
       <c r="A14" s="16">
-        <f>'SDA'!A60</f>
+        <f>IFERROR('SDA'!A60,"")</f>
         <v/>
       </c>
       <c r="B14" s="16">
-        <f>'SDA'!F60</f>
+        <f>IFERROR('SDA'!F60,0)</f>
         <v/>
       </c>
       <c r="C14" s="16">
-        <f>'SDA'!G60</f>
+        <f>IFERROR('SDA'!G60,0)</f>
         <v/>
       </c>
       <c r="D14" s="16">
-        <f>'SDA'!H60</f>
+        <f>IFERROR('SDA'!H60,0)</f>
         <v/>
       </c>
       <c r="E14" s="16">
@@ -14725,19 +15253,19 @@
     </row>
     <row r="15" ht="16.25" customHeight="1">
       <c r="A15" s="16">
-        <f>'SDA'!A61</f>
+        <f>IFERROR('SDA'!A61,"")</f>
         <v/>
       </c>
       <c r="B15" s="16">
-        <f>'SDA'!F61</f>
+        <f>IFERROR('SDA'!F61,0)</f>
         <v/>
       </c>
       <c r="C15" s="16">
-        <f>'SDA'!G61</f>
+        <f>IFERROR('SDA'!G61,0)</f>
         <v/>
       </c>
       <c r="D15" s="16">
-        <f>'SDA'!H61</f>
+        <f>IFERROR('SDA'!H61,0)</f>
         <v/>
       </c>
       <c r="E15" s="16">
@@ -14870,19 +15398,19 @@
     </row>
     <row r="16" ht="16.25" customHeight="1">
       <c r="A16" s="16">
-        <f>'SDA'!A62</f>
+        <f>IFERROR('SDA'!A62,"")</f>
         <v/>
       </c>
       <c r="B16" s="16">
-        <f>'SDA'!F62</f>
+        <f>IFERROR('SDA'!F62,0)</f>
         <v/>
       </c>
       <c r="C16" s="16">
-        <f>'SDA'!G62</f>
+        <f>IFERROR('SDA'!G62,0)</f>
         <v/>
       </c>
       <c r="D16" s="16">
-        <f>'SDA'!H62</f>
+        <f>IFERROR('SDA'!H62,0)</f>
         <v/>
       </c>
       <c r="E16" s="16">
@@ -15015,19 +15543,19 @@
     </row>
     <row r="17" ht="16.25" customHeight="1">
       <c r="A17" s="16">
-        <f>'SDA'!A63</f>
+        <f>IFERROR('SDA'!A63,"")</f>
         <v/>
       </c>
       <c r="B17" s="16">
-        <f>'SDA'!F63</f>
+        <f>IFERROR('SDA'!F63,0)</f>
         <v/>
       </c>
       <c r="C17" s="16">
-        <f>'SDA'!G63</f>
+        <f>IFERROR('SDA'!G63,0)</f>
         <v/>
       </c>
       <c r="D17" s="16">
-        <f>'SDA'!H63</f>
+        <f>IFERROR('SDA'!H63,0)</f>
         <v/>
       </c>
       <c r="E17" s="16">
@@ -15160,19 +15688,19 @@
     </row>
     <row r="18" ht="16.25" customHeight="1">
       <c r="A18" s="16">
-        <f>'SDA'!A64</f>
+        <f>IFERROR('SDA'!A64,"")</f>
         <v/>
       </c>
       <c r="B18" s="16">
-        <f>'SDA'!F64</f>
+        <f>IFERROR('SDA'!F64,0)</f>
         <v/>
       </c>
       <c r="C18" s="16">
-        <f>'SDA'!G64</f>
+        <f>IFERROR('SDA'!G64,0)</f>
         <v/>
       </c>
       <c r="D18" s="16">
-        <f>'SDA'!H64</f>
+        <f>IFERROR('SDA'!H64,0)</f>
         <v/>
       </c>
       <c r="E18" s="16">
@@ -15305,19 +15833,19 @@
     </row>
     <row r="19" ht="16.25" customHeight="1">
       <c r="A19" s="16">
-        <f>'SDA'!A65</f>
+        <f>IFERROR('SDA'!A65,"")</f>
         <v/>
       </c>
       <c r="B19" s="16">
-        <f>'SDA'!F65</f>
+        <f>IFERROR('SDA'!F65,0)</f>
         <v/>
       </c>
       <c r="C19" s="16">
-        <f>'SDA'!G65</f>
+        <f>IFERROR('SDA'!G65,0)</f>
         <v/>
       </c>
       <c r="D19" s="16">
-        <f>'SDA'!H65</f>
+        <f>IFERROR('SDA'!H65,0)</f>
         <v/>
       </c>
       <c r="E19" s="16">
@@ -15450,19 +15978,19 @@
     </row>
     <row r="20" ht="16.25" customHeight="1">
       <c r="A20" s="16">
-        <f>'SDA'!A66</f>
+        <f>IFERROR('SDA'!A66,"")</f>
         <v/>
       </c>
       <c r="B20" s="16">
-        <f>'SDA'!F66</f>
+        <f>IFERROR('SDA'!F66,0)</f>
         <v/>
       </c>
       <c r="C20" s="16">
-        <f>'SDA'!G66</f>
+        <f>IFERROR('SDA'!G66,0)</f>
         <v/>
       </c>
       <c r="D20" s="16">
-        <f>'SDA'!H66</f>
+        <f>IFERROR('SDA'!H66,0)</f>
         <v/>
       </c>
       <c r="E20" s="16">
@@ -15595,19 +16123,19 @@
     </row>
     <row r="21" ht="16.25" customHeight="1">
       <c r="A21" s="16">
-        <f>'SDA'!A67</f>
+        <f>IFERROR('SDA'!A67,"")</f>
         <v/>
       </c>
       <c r="B21" s="16">
-        <f>'SDA'!F67</f>
+        <f>IFERROR('SDA'!F67,0)</f>
         <v/>
       </c>
       <c r="C21" s="16">
-        <f>'SDA'!G67</f>
+        <f>IFERROR('SDA'!G67,0)</f>
         <v/>
       </c>
       <c r="D21" s="16">
-        <f>'SDA'!H67</f>
+        <f>IFERROR('SDA'!H67,0)</f>
         <v/>
       </c>
       <c r="E21" s="16">
@@ -15739,10 +16267,38 @@
       </c>
     </row>
     <row r="22" ht="16.25" customHeight="1">
+      <c r="A22" s="16">
+        <f>IFERROR('SDA'!A68,"")</f>
+        <v/>
+      </c>
+      <c r="B22" s="16">
+        <f>IFERROR('SDA'!F68,0)</f>
+        <v/>
+      </c>
+      <c r="C22" s="16">
+        <f>IFERROR('SDA'!G68,0)</f>
+        <v/>
+      </c>
+      <c r="D22" s="16">
+        <f>IFERROR('SDA'!H68,0)</f>
+        <v/>
+      </c>
       <c r="E22" s="16">
         <f>SUM(B22:D22)</f>
         <v/>
       </c>
+      <c r="F22" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A22,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A22,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <v/>
+      </c>
+      <c r="G22" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A22,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <v/>
+      </c>
+      <c r="H22" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A22,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <v/>
+      </c>
       <c r="I22" s="16">
         <f>SUM(F22:H22)</f>
         <v/>
@@ -15755,25 +16311,61 @@
         <f>IF(I22=0,0,AQ22*1.2/12*I22)</f>
         <v/>
       </c>
+      <c r="L22" s="16">
+        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A22,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A22,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A22,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A22,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <v/>
+      </c>
       <c r="M22" s="4" t="n"/>
       <c r="N22" s="4" t="n"/>
+      <c r="O22" s="16">
+        <f>IFERROR(IFS(L22="A",2.5,L22="B",0.3,L22="C",0.1,L22="D",0.05,TRUE,""),"")</f>
+        <v/>
+      </c>
       <c r="P22" s="4" t="n"/>
+      <c r="Q22" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A22),0)</f>
+        <v/>
+      </c>
       <c r="R22" s="16">
         <f>Q22*10</f>
         <v/>
       </c>
+      <c r="S22" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A22),0)</f>
+        <v/>
+      </c>
       <c r="T22" s="16">
         <f>S22*20</f>
         <v/>
       </c>
+      <c r="U22" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A22)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A22),0)</f>
+        <v/>
+      </c>
       <c r="V22" s="16">
         <f>U22*40</f>
         <v/>
       </c>
       <c r="W22" s="4" t="n"/>
       <c r="X22" s="4" t="n"/>
+      <c r="Y22" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A22,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A22,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
       <c r="Z22" s="4" t="n"/>
+      <c r="AA22" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A22,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
       <c r="AB22" s="4" t="n"/>
+      <c r="AC22" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A22),0)</f>
+        <v/>
+      </c>
+      <c r="AD22" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A22),0)</f>
+        <v/>
+      </c>
       <c r="AE22" s="16">
         <f>IF(AC22=0,0,AC22*1.7/12*AP22)</f>
         <v/>
@@ -15782,6 +16374,26 @@
         <f>IF(AD22=0,0,AD22*1.7/12*AQ22)</f>
         <v/>
       </c>
+      <c r="AG22" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A22,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A22,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AH22" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A22,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
+      <c r="AI22" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A22,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AJ22" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A22),0)</f>
+        <v/>
+      </c>
+      <c r="AK22" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A22),0)</f>
+        <v/>
+      </c>
       <c r="AL22" s="16">
         <f>(IF((AE22)&lt;(AG22+AH22+AI22),(AE22),(AG22+AH22+AI22)))+AJ22*5+AK22*10+R22+T22+V22</f>
         <v/>
@@ -15800,10 +16412,38 @@
       </c>
     </row>
     <row r="23" ht="16.25" customHeight="1">
+      <c r="A23" s="16">
+        <f>IFERROR('SDA'!A69,"")</f>
+        <v/>
+      </c>
+      <c r="B23" s="16">
+        <f>IFERROR('SDA'!F69,0)</f>
+        <v/>
+      </c>
+      <c r="C23" s="16">
+        <f>IFERROR('SDA'!G69,0)</f>
+        <v/>
+      </c>
+      <c r="D23" s="16">
+        <f>IFERROR('SDA'!H69,0)</f>
+        <v/>
+      </c>
       <c r="E23" s="16">
         <f>SUM(B23:D23)</f>
         <v/>
       </c>
+      <c r="F23" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A23,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A23,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <v/>
+      </c>
+      <c r="G23" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A23,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <v/>
+      </c>
+      <c r="H23" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A23,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <v/>
+      </c>
       <c r="I23" s="16">
         <f>SUM(F23:H23)</f>
         <v/>
@@ -15816,25 +16456,61 @@
         <f>IF(I23=0,0,AQ23*1.2/12*I23)</f>
         <v/>
       </c>
+      <c r="L23" s="16">
+        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A23,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A23,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A23,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A23,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <v/>
+      </c>
       <c r="M23" s="4" t="n"/>
       <c r="N23" s="4" t="n"/>
+      <c r="O23" s="16">
+        <f>IFERROR(IFS(L23="A",2.5,L23="B",0.3,L23="C",0.1,L23="D",0.05,TRUE,""),"")</f>
+        <v/>
+      </c>
       <c r="P23" s="4" t="n"/>
+      <c r="Q23" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A23),0)</f>
+        <v/>
+      </c>
       <c r="R23" s="16">
         <f>Q23*10</f>
         <v/>
       </c>
+      <c r="S23" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A23),0)</f>
+        <v/>
+      </c>
       <c r="T23" s="16">
         <f>S23*20</f>
         <v/>
       </c>
+      <c r="U23" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A23)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A23),0)</f>
+        <v/>
+      </c>
       <c r="V23" s="16">
         <f>U23*40</f>
         <v/>
       </c>
       <c r="W23" s="4" t="n"/>
       <c r="X23" s="4" t="n"/>
+      <c r="Y23" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A23,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A23,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
       <c r="Z23" s="4" t="n"/>
+      <c r="AA23" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A23,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
       <c r="AB23" s="4" t="n"/>
+      <c r="AC23" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A23),0)</f>
+        <v/>
+      </c>
+      <c r="AD23" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A23),0)</f>
+        <v/>
+      </c>
       <c r="AE23" s="16">
         <f>IF(AC23=0,0,AC23*1.7/12*AP23)</f>
         <v/>
@@ -15843,6 +16519,26 @@
         <f>IF(AD23=0,0,AD23*1.7/12*AQ23)</f>
         <v/>
       </c>
+      <c r="AG23" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A23,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A23,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AH23" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A23,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
+      <c r="AI23" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A23,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AJ23" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A23),0)</f>
+        <v/>
+      </c>
+      <c r="AK23" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A23),0)</f>
+        <v/>
+      </c>
       <c r="AL23" s="16">
         <f>(IF((AE23)&lt;(AG23+AH23+AI23),(AE23),(AG23+AH23+AI23)))+AJ23*5+AK23*10+R23+T23+V23</f>
         <v/>
@@ -15861,10 +16557,38 @@
       </c>
     </row>
     <row r="24" ht="16.25" customHeight="1">
+      <c r="A24" s="16">
+        <f>IFERROR('SDA'!A70,"")</f>
+        <v/>
+      </c>
+      <c r="B24" s="16">
+        <f>IFERROR('SDA'!F70,0)</f>
+        <v/>
+      </c>
+      <c r="C24" s="16">
+        <f>IFERROR('SDA'!G70,0)</f>
+        <v/>
+      </c>
+      <c r="D24" s="16">
+        <f>IFERROR('SDA'!H70,0)</f>
+        <v/>
+      </c>
       <c r="E24" s="16">
         <f>SUM(B24:D24)</f>
         <v/>
       </c>
+      <c r="F24" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A24,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A24,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <v/>
+      </c>
+      <c r="G24" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A24,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <v/>
+      </c>
+      <c r="H24" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A24,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <v/>
+      </c>
       <c r="I24" s="16">
         <f>SUM(F24:H24)</f>
         <v/>
@@ -15877,25 +16601,61 @@
         <f>IF(I24=0,0,AQ24*1.2/12*I24)</f>
         <v/>
       </c>
+      <c r="L24" s="16">
+        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A24,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A24,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A24,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A24,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <v/>
+      </c>
       <c r="M24" s="4" t="n"/>
       <c r="N24" s="4" t="n"/>
+      <c r="O24" s="16">
+        <f>IFERROR(IFS(L24="A",2.5,L24="B",0.3,L24="C",0.1,L24="D",0.05,TRUE,""),"")</f>
+        <v/>
+      </c>
       <c r="P24" s="4" t="n"/>
+      <c r="Q24" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A24),0)</f>
+        <v/>
+      </c>
       <c r="R24" s="16">
         <f>Q24*10</f>
         <v/>
       </c>
+      <c r="S24" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A24),0)</f>
+        <v/>
+      </c>
       <c r="T24" s="16">
         <f>S24*20</f>
         <v/>
       </c>
+      <c r="U24" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A24)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A24),0)</f>
+        <v/>
+      </c>
       <c r="V24" s="16">
         <f>U24*40</f>
         <v/>
       </c>
       <c r="W24" s="4" t="n"/>
       <c r="X24" s="4" t="n"/>
+      <c r="Y24" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A24,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A24,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
       <c r="Z24" s="4" t="n"/>
+      <c r="AA24" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A24,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
       <c r="AB24" s="4" t="n"/>
+      <c r="AC24" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A24),0)</f>
+        <v/>
+      </c>
+      <c r="AD24" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A24),0)</f>
+        <v/>
+      </c>
       <c r="AE24" s="16">
         <f>IF(AC24=0,0,AC24*1.7/12*AP24)</f>
         <v/>
@@ -15904,6 +16664,26 @@
         <f>IF(AD24=0,0,AD24*1.7/12*AQ24)</f>
         <v/>
       </c>
+      <c r="AG24" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A24,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A24,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AH24" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A24,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
+      <c r="AI24" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A24,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AJ24" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A24),0)</f>
+        <v/>
+      </c>
+      <c r="AK24" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A24),0)</f>
+        <v/>
+      </c>
       <c r="AL24" s="16">
         <f>(IF((AE24)&lt;(AG24+AH24+AI24),(AE24),(AG24+AH24+AI24)))+AJ24*5+AK24*10+R24+T24+V24</f>
         <v/>
@@ -15922,10 +16702,38 @@
       </c>
     </row>
     <row r="25" ht="16.25" customHeight="1">
+      <c r="A25" s="16">
+        <f>IFERROR('SDA'!A71,"")</f>
+        <v/>
+      </c>
+      <c r="B25" s="16">
+        <f>IFERROR('SDA'!F71,0)</f>
+        <v/>
+      </c>
+      <c r="C25" s="16">
+        <f>IFERROR('SDA'!G71,0)</f>
+        <v/>
+      </c>
+      <c r="D25" s="16">
+        <f>IFERROR('SDA'!H71,0)</f>
+        <v/>
+      </c>
       <c r="E25" s="16">
         <f>SUM(B25:D25)</f>
         <v/>
       </c>
+      <c r="F25" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A25,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A25,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <v/>
+      </c>
+      <c r="G25" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A25,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <v/>
+      </c>
+      <c r="H25" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A25,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <v/>
+      </c>
       <c r="I25" s="16">
         <f>SUM(F25:H25)</f>
         <v/>
@@ -15938,25 +16746,61 @@
         <f>IF(I25=0,0,AQ25*1.2/12*I25)</f>
         <v/>
       </c>
+      <c r="L25" s="16">
+        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A25,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A25,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A25,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A25,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <v/>
+      </c>
       <c r="M25" s="4" t="n"/>
       <c r="N25" s="4" t="n"/>
+      <c r="O25" s="16">
+        <f>IFERROR(IFS(L25="A",2.5,L25="B",0.3,L25="C",0.1,L25="D",0.05,TRUE,""),"")</f>
+        <v/>
+      </c>
       <c r="P25" s="4" t="n"/>
+      <c r="Q25" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A25),0)</f>
+        <v/>
+      </c>
       <c r="R25" s="16">
         <f>Q25*10</f>
         <v/>
       </c>
+      <c r="S25" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A25),0)</f>
+        <v/>
+      </c>
       <c r="T25" s="16">
         <f>S25*20</f>
         <v/>
       </c>
+      <c r="U25" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A25)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A25),0)</f>
+        <v/>
+      </c>
       <c r="V25" s="16">
         <f>U25*40</f>
         <v/>
       </c>
       <c r="W25" s="4" t="n"/>
       <c r="X25" s="4" t="n"/>
+      <c r="Y25" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A25,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A25,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
       <c r="Z25" s="4" t="n"/>
+      <c r="AA25" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A25,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
       <c r="AB25" s="4" t="n"/>
+      <c r="AC25" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A25),0)</f>
+        <v/>
+      </c>
+      <c r="AD25" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A25),0)</f>
+        <v/>
+      </c>
       <c r="AE25" s="16">
         <f>IF(AC25=0,0,AC25*1.7/12*AP25)</f>
         <v/>
@@ -15965,6 +16809,26 @@
         <f>IF(AD25=0,0,AD25*1.7/12*AQ25)</f>
         <v/>
       </c>
+      <c r="AG25" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A25,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A25,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AH25" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A25,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
+      <c r="AI25" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A25,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AJ25" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A25),0)</f>
+        <v/>
+      </c>
+      <c r="AK25" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A25),0)</f>
+        <v/>
+      </c>
       <c r="AL25" s="16">
         <f>(IF((AE25)&lt;(AG25+AH25+AI25),(AE25),(AG25+AH25+AI25)))+AJ25*5+AK25*10+R25+T25+V25</f>
         <v/>
@@ -15983,10 +16847,38 @@
       </c>
     </row>
     <row r="26" ht="16.25" customHeight="1">
+      <c r="A26" s="16">
+        <f>IFERROR('SDA'!A72,"")</f>
+        <v/>
+      </c>
+      <c r="B26" s="16">
+        <f>IFERROR('SDA'!F72,0)</f>
+        <v/>
+      </c>
+      <c r="C26" s="16">
+        <f>IFERROR('SDA'!G72,0)</f>
+        <v/>
+      </c>
+      <c r="D26" s="16">
+        <f>IFERROR('SDA'!H72,0)</f>
+        <v/>
+      </c>
       <c r="E26" s="16">
         <f>SUM(B26:D26)</f>
         <v/>
       </c>
+      <c r="F26" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A26,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A26,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <v/>
+      </c>
+      <c r="G26" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A26,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <v/>
+      </c>
+      <c r="H26" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A26,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <v/>
+      </c>
       <c r="I26" s="16">
         <f>SUM(F26:H26)</f>
         <v/>
@@ -15999,25 +16891,61 @@
         <f>IF(I26=0,0,AQ26*1.2/12*I26)</f>
         <v/>
       </c>
+      <c r="L26" s="16">
+        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A26,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A26,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A26,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A26,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <v/>
+      </c>
       <c r="M26" s="4" t="n"/>
       <c r="N26" s="4" t="n"/>
+      <c r="O26" s="16">
+        <f>IFERROR(IFS(L26="A",2.5,L26="B",0.3,L26="C",0.1,L26="D",0.05,TRUE,""),"")</f>
+        <v/>
+      </c>
       <c r="P26" s="4" t="n"/>
+      <c r="Q26" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A26),0)</f>
+        <v/>
+      </c>
       <c r="R26" s="16">
         <f>Q26*10</f>
         <v/>
       </c>
+      <c r="S26" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A26),0)</f>
+        <v/>
+      </c>
       <c r="T26" s="16">
         <f>S26*20</f>
         <v/>
       </c>
+      <c r="U26" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A26)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A26),0)</f>
+        <v/>
+      </c>
       <c r="V26" s="16">
         <f>U26*40</f>
         <v/>
       </c>
       <c r="W26" s="4" t="n"/>
       <c r="X26" s="4" t="n"/>
+      <c r="Y26" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A26,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A26,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
       <c r="Z26" s="4" t="n"/>
+      <c r="AA26" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A26,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
       <c r="AB26" s="4" t="n"/>
+      <c r="AC26" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A26),0)</f>
+        <v/>
+      </c>
+      <c r="AD26" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A26),0)</f>
+        <v/>
+      </c>
       <c r="AE26" s="16">
         <f>IF(AC26=0,0,AC26*1.7/12*AP26)</f>
         <v/>
@@ -16026,6 +16954,26 @@
         <f>IF(AD26=0,0,AD26*1.7/12*AQ26)</f>
         <v/>
       </c>
+      <c r="AG26" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A26,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A26,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AH26" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A26,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
+      <c r="AI26" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A26,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AJ26" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A26),0)</f>
+        <v/>
+      </c>
+      <c r="AK26" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A26),0)</f>
+        <v/>
+      </c>
       <c r="AL26" s="16">
         <f>(IF((AE26)&lt;(AG26+AH26+AI26),(AE26),(AG26+AH26+AI26)))+AJ26*5+AK26*10+R26+T26+V26</f>
         <v/>
@@ -16044,10 +16992,38 @@
       </c>
     </row>
     <row r="27" ht="16.25" customHeight="1">
+      <c r="A27" s="16">
+        <f>IFERROR('SDA'!A73,"")</f>
+        <v/>
+      </c>
+      <c r="B27" s="16">
+        <f>IFERROR('SDA'!F73,0)</f>
+        <v/>
+      </c>
+      <c r="C27" s="16">
+        <f>IFERROR('SDA'!G73,0)</f>
+        <v/>
+      </c>
+      <c r="D27" s="16">
+        <f>IFERROR('SDA'!H73,0)</f>
+        <v/>
+      </c>
       <c r="E27" s="16">
         <f>SUM(B27:D27)</f>
         <v/>
       </c>
+      <c r="F27" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A27,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A27,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <v/>
+      </c>
+      <c r="G27" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A27,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <v/>
+      </c>
+      <c r="H27" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A27,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <v/>
+      </c>
       <c r="I27" s="16">
         <f>SUM(F27:H27)</f>
         <v/>
@@ -16060,25 +17036,61 @@
         <f>IF(I27=0,0,AQ27*1.2/12*I27)</f>
         <v/>
       </c>
+      <c r="L27" s="16">
+        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A27,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A27,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A27,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A27,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <v/>
+      </c>
       <c r="M27" s="4" t="n"/>
       <c r="N27" s="4" t="n"/>
+      <c r="O27" s="16">
+        <f>IFERROR(IFS(L27="A",2.5,L27="B",0.3,L27="C",0.1,L27="D",0.05,TRUE,""),"")</f>
+        <v/>
+      </c>
       <c r="P27" s="4" t="n"/>
+      <c r="Q27" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A27),0)</f>
+        <v/>
+      </c>
       <c r="R27" s="16">
         <f>Q27*10</f>
         <v/>
       </c>
+      <c r="S27" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A27),0)</f>
+        <v/>
+      </c>
       <c r="T27" s="16">
         <f>S27*20</f>
         <v/>
       </c>
+      <c r="U27" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A27)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A27),0)</f>
+        <v/>
+      </c>
       <c r="V27" s="16">
         <f>U27*40</f>
         <v/>
       </c>
       <c r="W27" s="4" t="n"/>
       <c r="X27" s="4" t="n"/>
+      <c r="Y27" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A27,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A27,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
       <c r="Z27" s="4" t="n"/>
+      <c r="AA27" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A27,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
       <c r="AB27" s="4" t="n"/>
+      <c r="AC27" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A27),0)</f>
+        <v/>
+      </c>
+      <c r="AD27" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A27),0)</f>
+        <v/>
+      </c>
       <c r="AE27" s="16">
         <f>IF(AC27=0,0,AC27*1.7/12*AP27)</f>
         <v/>
@@ -16087,6 +17099,26 @@
         <f>IF(AD27=0,0,AD27*1.7/12*AQ27)</f>
         <v/>
       </c>
+      <c r="AG27" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A27,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A27,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AH27" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A27,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
+      <c r="AI27" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A27,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AJ27" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A27),0)</f>
+        <v/>
+      </c>
+      <c r="AK27" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A27),0)</f>
+        <v/>
+      </c>
       <c r="AL27" s="16">
         <f>(IF((AE27)&lt;(AG27+AH27+AI27),(AE27),(AG27+AH27+AI27)))+AJ27*5+AK27*10+R27+T27+V27</f>
         <v/>
@@ -16105,10 +17137,38 @@
       </c>
     </row>
     <row r="28" ht="16.25" customHeight="1">
+      <c r="A28" s="16">
+        <f>IFERROR('SDA'!A74,"")</f>
+        <v/>
+      </c>
+      <c r="B28" s="16">
+        <f>IFERROR('SDA'!F74,0)</f>
+        <v/>
+      </c>
+      <c r="C28" s="16">
+        <f>IFERROR('SDA'!G74,0)</f>
+        <v/>
+      </c>
+      <c r="D28" s="16">
+        <f>IFERROR('SDA'!H74,0)</f>
+        <v/>
+      </c>
       <c r="E28" s="16">
         <f>SUM(B28:D28)</f>
         <v/>
       </c>
+      <c r="F28" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A28,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A28,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <v/>
+      </c>
+      <c r="G28" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A28,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <v/>
+      </c>
+      <c r="H28" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A28,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <v/>
+      </c>
       <c r="I28" s="16">
         <f>SUM(F28:H28)</f>
         <v/>
@@ -16121,25 +17181,61 @@
         <f>IF(I28=0,0,AQ28*1.2/12*I28)</f>
         <v/>
       </c>
+      <c r="L28" s="16">
+        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A28,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A28,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A28,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A28,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <v/>
+      </c>
       <c r="M28" s="4" t="n"/>
       <c r="N28" s="4" t="n"/>
+      <c r="O28" s="16">
+        <f>IFERROR(IFS(L28="A",2.5,L28="B",0.3,L28="C",0.1,L28="D",0.05,TRUE,""),"")</f>
+        <v/>
+      </c>
       <c r="P28" s="4" t="n"/>
+      <c r="Q28" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A28),0)</f>
+        <v/>
+      </c>
       <c r="R28" s="16">
         <f>Q28*10</f>
         <v/>
       </c>
+      <c r="S28" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A28),0)</f>
+        <v/>
+      </c>
       <c r="T28" s="16">
         <f>S28*20</f>
         <v/>
       </c>
+      <c r="U28" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A28)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A28),0)</f>
+        <v/>
+      </c>
       <c r="V28" s="16">
         <f>U28*40</f>
         <v/>
       </c>
       <c r="W28" s="4" t="n"/>
       <c r="X28" s="4" t="n"/>
+      <c r="Y28" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A28,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A28,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
       <c r="Z28" s="4" t="n"/>
+      <c r="AA28" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A28,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
       <c r="AB28" s="4" t="n"/>
+      <c r="AC28" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A28),0)</f>
+        <v/>
+      </c>
+      <c r="AD28" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A28),0)</f>
+        <v/>
+      </c>
       <c r="AE28" s="16">
         <f>IF(AC28=0,0,AC28*1.7/12*AP28)</f>
         <v/>
@@ -16148,6 +17244,26 @@
         <f>IF(AD28=0,0,AD28*1.7/12*AQ28)</f>
         <v/>
       </c>
+      <c r="AG28" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A28,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A28,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AH28" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A28,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
+      <c r="AI28" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A28,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AJ28" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A28),0)</f>
+        <v/>
+      </c>
+      <c r="AK28" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A28),0)</f>
+        <v/>
+      </c>
       <c r="AL28" s="16">
         <f>(IF((AE28)&lt;(AG28+AH28+AI28),(AE28),(AG28+AH28+AI28)))+AJ28*5+AK28*10+R28+T28+V28</f>
         <v/>
@@ -16166,10 +17282,38 @@
       </c>
     </row>
     <row r="29" ht="16.25" customHeight="1">
+      <c r="A29" s="16">
+        <f>IFERROR('SDA'!A75,"")</f>
+        <v/>
+      </c>
+      <c r="B29" s="16">
+        <f>IFERROR('SDA'!F75,0)</f>
+        <v/>
+      </c>
+      <c r="C29" s="16">
+        <f>IFERROR('SDA'!G75,0)</f>
+        <v/>
+      </c>
+      <c r="D29" s="16">
+        <f>IFERROR('SDA'!H75,0)</f>
+        <v/>
+      </c>
       <c r="E29" s="16">
         <f>SUM(B29:D29)</f>
         <v/>
       </c>
+      <c r="F29" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A29,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A29,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <v/>
+      </c>
+      <c r="G29" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A29,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <v/>
+      </c>
+      <c r="H29" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A29,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <v/>
+      </c>
       <c r="I29" s="16">
         <f>SUM(F29:H29)</f>
         <v/>
@@ -16182,25 +17326,61 @@
         <f>IF(I29=0,0,AQ29*1.2/12*I29)</f>
         <v/>
       </c>
+      <c r="L29" s="16">
+        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A29,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A29,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A29,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A29,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <v/>
+      </c>
       <c r="M29" s="4" t="n"/>
       <c r="N29" s="4" t="n"/>
+      <c r="O29" s="16">
+        <f>IFERROR(IFS(L29="A",2.5,L29="B",0.3,L29="C",0.1,L29="D",0.05,TRUE,""),"")</f>
+        <v/>
+      </c>
       <c r="P29" s="4" t="n"/>
+      <c r="Q29" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A29),0)</f>
+        <v/>
+      </c>
       <c r="R29" s="16">
         <f>Q29*10</f>
         <v/>
       </c>
+      <c r="S29" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A29),0)</f>
+        <v/>
+      </c>
       <c r="T29" s="16">
         <f>S29*20</f>
         <v/>
       </c>
+      <c r="U29" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A29)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A29),0)</f>
+        <v/>
+      </c>
       <c r="V29" s="16">
         <f>U29*40</f>
         <v/>
       </c>
       <c r="W29" s="4" t="n"/>
       <c r="X29" s="4" t="n"/>
+      <c r="Y29" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A29,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A29,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
       <c r="Z29" s="4" t="n"/>
+      <c r="AA29" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A29,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
       <c r="AB29" s="4" t="n"/>
+      <c r="AC29" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A29),0)</f>
+        <v/>
+      </c>
+      <c r="AD29" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A29),0)</f>
+        <v/>
+      </c>
       <c r="AE29" s="16">
         <f>IF(AC29=0,0,AC29*1.7/12*AP29)</f>
         <v/>
@@ -16209,6 +17389,26 @@
         <f>IF(AD29=0,0,AD29*1.7/12*AQ29)</f>
         <v/>
       </c>
+      <c r="AG29" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A29,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A29,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AH29" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A29,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
+      <c r="AI29" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A29,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AJ29" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A29),0)</f>
+        <v/>
+      </c>
+      <c r="AK29" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A29),0)</f>
+        <v/>
+      </c>
       <c r="AL29" s="16">
         <f>(IF((AE29)&lt;(AG29+AH29+AI29),(AE29),(AG29+AH29+AI29)))+AJ29*5+AK29*10+R29+T29+V29</f>
         <v/>
@@ -16227,10 +17427,38 @@
       </c>
     </row>
     <row r="30" ht="16.25" customHeight="1">
+      <c r="A30" s="16">
+        <f>IFERROR('SDA'!A76,"")</f>
+        <v/>
+      </c>
+      <c r="B30" s="16">
+        <f>IFERROR('SDA'!F76,0)</f>
+        <v/>
+      </c>
+      <c r="C30" s="16">
+        <f>IFERROR('SDA'!G76,0)</f>
+        <v/>
+      </c>
+      <c r="D30" s="16">
+        <f>IFERROR('SDA'!H76,0)</f>
+        <v/>
+      </c>
       <c r="E30" s="16">
         <f>SUM(B30:D30)</f>
         <v/>
       </c>
+      <c r="F30" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A30,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A30,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <v/>
+      </c>
+      <c r="G30" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A30,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <v/>
+      </c>
+      <c r="H30" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A30,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <v/>
+      </c>
       <c r="I30" s="16">
         <f>SUM(F30:H30)</f>
         <v/>
@@ -16243,25 +17471,61 @@
         <f>IF(I30=0,0,AQ30*1.2/12*I30)</f>
         <v/>
       </c>
+      <c r="L30" s="16">
+        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A30,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A30,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A30,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A30,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <v/>
+      </c>
       <c r="M30" s="4" t="n"/>
       <c r="N30" s="4" t="n"/>
+      <c r="O30" s="16">
+        <f>IFERROR(IFS(L30="A",2.5,L30="B",0.3,L30="C",0.1,L30="D",0.05,TRUE,""),"")</f>
+        <v/>
+      </c>
       <c r="P30" s="4" t="n"/>
+      <c r="Q30" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A30),0)</f>
+        <v/>
+      </c>
       <c r="R30" s="16">
         <f>Q30*10</f>
         <v/>
       </c>
+      <c r="S30" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A30),0)</f>
+        <v/>
+      </c>
       <c r="T30" s="16">
         <f>S30*20</f>
         <v/>
       </c>
+      <c r="U30" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A30)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A30),0)</f>
+        <v/>
+      </c>
       <c r="V30" s="16">
         <f>U30*40</f>
         <v/>
       </c>
       <c r="W30" s="4" t="n"/>
       <c r="X30" s="4" t="n"/>
+      <c r="Y30" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A30,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A30,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
       <c r="Z30" s="4" t="n"/>
+      <c r="AA30" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A30,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
       <c r="AB30" s="4" t="n"/>
+      <c r="AC30" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A30),0)</f>
+        <v/>
+      </c>
+      <c r="AD30" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A30),0)</f>
+        <v/>
+      </c>
       <c r="AE30" s="16">
         <f>IF(AC30=0,0,AC30*1.7/12*AP30)</f>
         <v/>
@@ -16270,6 +17534,26 @@
         <f>IF(AD30=0,0,AD30*1.7/12*AQ30)</f>
         <v/>
       </c>
+      <c r="AG30" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A30,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A30,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AH30" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A30,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
+      <c r="AI30" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A30,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AJ30" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A30),0)</f>
+        <v/>
+      </c>
+      <c r="AK30" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A30),0)</f>
+        <v/>
+      </c>
       <c r="AL30" s="16">
         <f>(IF((AE30)&lt;(AG30+AH30+AI30),(AE30),(AG30+AH30+AI30)))+AJ30*5+AK30*10+R30+T30+V30</f>
         <v/>
@@ -16288,10 +17572,38 @@
       </c>
     </row>
     <row r="31" ht="16.25" customHeight="1">
+      <c r="A31" s="16">
+        <f>IFERROR('SDA'!A77,"")</f>
+        <v/>
+      </c>
+      <c r="B31" s="16">
+        <f>IFERROR('SDA'!F77,0)</f>
+        <v/>
+      </c>
+      <c r="C31" s="16">
+        <f>IFERROR('SDA'!G77,0)</f>
+        <v/>
+      </c>
+      <c r="D31" s="16">
+        <f>IFERROR('SDA'!H77,0)</f>
+        <v/>
+      </c>
       <c r="E31" s="16">
         <f>SUM(B31:D31)</f>
         <v/>
       </c>
+      <c r="F31" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A31,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A31,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <v/>
+      </c>
+      <c r="G31" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A31,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <v/>
+      </c>
+      <c r="H31" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A31,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <v/>
+      </c>
       <c r="I31" s="16">
         <f>SUM(F31:H31)</f>
         <v/>
@@ -16304,25 +17616,61 @@
         <f>IF(I31=0,0,AQ31*1.2/12*I31)</f>
         <v/>
       </c>
+      <c r="L31" s="16">
+        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A31,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A31,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A31,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A31,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <v/>
+      </c>
       <c r="M31" s="4" t="n"/>
       <c r="N31" s="4" t="n"/>
+      <c r="O31" s="16">
+        <f>IFERROR(IFS(L31="A",2.5,L31="B",0.3,L31="C",0.1,L31="D",0.05,TRUE,""),"")</f>
+        <v/>
+      </c>
       <c r="P31" s="4" t="n"/>
+      <c r="Q31" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A31),0)</f>
+        <v/>
+      </c>
       <c r="R31" s="16">
         <f>Q31*10</f>
         <v/>
       </c>
+      <c r="S31" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A31),0)</f>
+        <v/>
+      </c>
       <c r="T31" s="16">
         <f>S31*20</f>
         <v/>
       </c>
+      <c r="U31" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A31)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A31),0)</f>
+        <v/>
+      </c>
       <c r="V31" s="16">
         <f>U31*40</f>
         <v/>
       </c>
       <c r="W31" s="4" t="n"/>
       <c r="X31" s="4" t="n"/>
+      <c r="Y31" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A31,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A31,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
       <c r="Z31" s="4" t="n"/>
+      <c r="AA31" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A31,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
       <c r="AB31" s="4" t="n"/>
+      <c r="AC31" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A31),0)</f>
+        <v/>
+      </c>
+      <c r="AD31" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A31),0)</f>
+        <v/>
+      </c>
       <c r="AE31" s="16">
         <f>IF(AC31=0,0,AC31*1.7/12*AP31)</f>
         <v/>
@@ -16331,6 +17679,26 @@
         <f>IF(AD31=0,0,AD31*1.7/12*AQ31)</f>
         <v/>
       </c>
+      <c r="AG31" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A31,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A31,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AH31" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A31,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
+      <c r="AI31" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A31,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AJ31" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A31),0)</f>
+        <v/>
+      </c>
+      <c r="AK31" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A31),0)</f>
+        <v/>
+      </c>
       <c r="AL31" s="16">
         <f>(IF((AE31)&lt;(AG31+AH31+AI31),(AE31),(AG31+AH31+AI31)))+AJ31*5+AK31*10+R31+T31+V31</f>
         <v/>
@@ -16349,10 +17717,38 @@
       </c>
     </row>
     <row r="32" ht="16.25" customHeight="1">
+      <c r="A32" s="16">
+        <f>IFERROR('SDA'!A78,"")</f>
+        <v/>
+      </c>
+      <c r="B32" s="16">
+        <f>IFERROR('SDA'!F78,0)</f>
+        <v/>
+      </c>
+      <c r="C32" s="16">
+        <f>IFERROR('SDA'!G78,0)</f>
+        <v/>
+      </c>
+      <c r="D32" s="16">
+        <f>IFERROR('SDA'!H78,0)</f>
+        <v/>
+      </c>
       <c r="E32" s="16">
         <f>SUM(B32:D32)</f>
         <v/>
       </c>
+      <c r="F32" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A32,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A32,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <v/>
+      </c>
+      <c r="G32" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A32,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <v/>
+      </c>
+      <c r="H32" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A32,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <v/>
+      </c>
       <c r="I32" s="16">
         <f>SUM(F32:H32)</f>
         <v/>
@@ -16365,25 +17761,61 @@
         <f>IF(I32=0,0,AQ32*1.2/12*I32)</f>
         <v/>
       </c>
+      <c r="L32" s="16">
+        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A32,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A32,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A32,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A32,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <v/>
+      </c>
       <c r="M32" s="4" t="n"/>
       <c r="N32" s="4" t="n"/>
+      <c r="O32" s="16">
+        <f>IFERROR(IFS(L32="A",2.5,L32="B",0.3,L32="C",0.1,L32="D",0.05,TRUE,""),"")</f>
+        <v/>
+      </c>
       <c r="P32" s="4" t="n"/>
+      <c r="Q32" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A32),0)</f>
+        <v/>
+      </c>
       <c r="R32" s="16">
         <f>Q32*10</f>
         <v/>
       </c>
+      <c r="S32" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A32),0)</f>
+        <v/>
+      </c>
       <c r="T32" s="16">
         <f>S32*20</f>
         <v/>
       </c>
+      <c r="U32" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A32)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A32),0)</f>
+        <v/>
+      </c>
       <c r="V32" s="16">
         <f>U32*40</f>
         <v/>
       </c>
       <c r="W32" s="4" t="n"/>
       <c r="X32" s="4" t="n"/>
+      <c r="Y32" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A32,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A32,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
       <c r="Z32" s="4" t="n"/>
+      <c r="AA32" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A32,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
       <c r="AB32" s="4" t="n"/>
+      <c r="AC32" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A32),0)</f>
+        <v/>
+      </c>
+      <c r="AD32" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A32),0)</f>
+        <v/>
+      </c>
       <c r="AE32" s="16">
         <f>IF(AC32=0,0,AC32*1.7/12*AP32)</f>
         <v/>
@@ -16392,6 +17824,26 @@
         <f>IF(AD32=0,0,AD32*1.7/12*AQ32)</f>
         <v/>
       </c>
+      <c r="AG32" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A32,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A32,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AH32" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A32,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
+      <c r="AI32" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A32,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AJ32" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A32),0)</f>
+        <v/>
+      </c>
+      <c r="AK32" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A32),0)</f>
+        <v/>
+      </c>
       <c r="AL32" s="16">
         <f>(IF((AE32)&lt;(AG32+AH32+AI32),(AE32),(AG32+AH32+AI32)))+AJ32*5+AK32*10+R32+T32+V32</f>
         <v/>
@@ -16410,10 +17862,38 @@
       </c>
     </row>
     <row r="33" ht="16.25" customHeight="1">
+      <c r="A33" s="16">
+        <f>IFERROR('SDA'!A79,"")</f>
+        <v/>
+      </c>
+      <c r="B33" s="16">
+        <f>IFERROR('SDA'!F79,0)</f>
+        <v/>
+      </c>
+      <c r="C33" s="16">
+        <f>IFERROR('SDA'!G79,0)</f>
+        <v/>
+      </c>
+      <c r="D33" s="16">
+        <f>IFERROR('SDA'!H79,0)</f>
+        <v/>
+      </c>
       <c r="E33" s="16">
         <f>SUM(B33:D33)</f>
         <v/>
       </c>
+      <c r="F33" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A33,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A33,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <v/>
+      </c>
+      <c r="G33" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A33,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <v/>
+      </c>
+      <c r="H33" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A33,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <v/>
+      </c>
       <c r="I33" s="16">
         <f>SUM(F33:H33)</f>
         <v/>
@@ -16426,25 +17906,61 @@
         <f>IF(I33=0,0,AQ33*1.2/12*I33)</f>
         <v/>
       </c>
+      <c r="L33" s="16">
+        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A33,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A33,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A33,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A33,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <v/>
+      </c>
       <c r="M33" s="4" t="n"/>
       <c r="N33" s="4" t="n"/>
+      <c r="O33" s="16">
+        <f>IFERROR(IFS(L33="A",2.5,L33="B",0.3,L33="C",0.1,L33="D",0.05,TRUE,""),"")</f>
+        <v/>
+      </c>
       <c r="P33" s="4" t="n"/>
+      <c r="Q33" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A33),0)</f>
+        <v/>
+      </c>
       <c r="R33" s="16">
         <f>Q33*10</f>
         <v/>
       </c>
+      <c r="S33" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A33),0)</f>
+        <v/>
+      </c>
       <c r="T33" s="16">
         <f>S33*20</f>
         <v/>
       </c>
+      <c r="U33" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A33)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A33),0)</f>
+        <v/>
+      </c>
       <c r="V33" s="16">
         <f>U33*40</f>
         <v/>
       </c>
       <c r="W33" s="4" t="n"/>
       <c r="X33" s="4" t="n"/>
+      <c r="Y33" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A33,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A33,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
       <c r="Z33" s="4" t="n"/>
+      <c r="AA33" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A33,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
       <c r="AB33" s="4" t="n"/>
+      <c r="AC33" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A33),0)</f>
+        <v/>
+      </c>
+      <c r="AD33" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A33),0)</f>
+        <v/>
+      </c>
       <c r="AE33" s="16">
         <f>IF(AC33=0,0,AC33*1.7/12*AP33)</f>
         <v/>
@@ -16453,6 +17969,26 @@
         <f>IF(AD33=0,0,AD33*1.7/12*AQ33)</f>
         <v/>
       </c>
+      <c r="AG33" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A33,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A33,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AH33" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A33,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
+      <c r="AI33" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A33,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AJ33" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A33),0)</f>
+        <v/>
+      </c>
+      <c r="AK33" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A33),0)</f>
+        <v/>
+      </c>
       <c r="AL33" s="16">
         <f>(IF((AE33)&lt;(AG33+AH33+AI33),(AE33),(AG33+AH33+AI33)))+AJ33*5+AK33*10+R33+T33+V33</f>
         <v/>
@@ -16471,10 +18007,38 @@
       </c>
     </row>
     <row r="34" ht="16.25" customHeight="1">
+      <c r="A34" s="16">
+        <f>IFERROR('SDA'!A80,"")</f>
+        <v/>
+      </c>
+      <c r="B34" s="16">
+        <f>IFERROR('SDA'!F80,0)</f>
+        <v/>
+      </c>
+      <c r="C34" s="16">
+        <f>IFERROR('SDA'!G80,0)</f>
+        <v/>
+      </c>
+      <c r="D34" s="16">
+        <f>IFERROR('SDA'!H80,0)</f>
+        <v/>
+      </c>
       <c r="E34" s="16">
         <f>SUM(B34:D34)</f>
         <v/>
       </c>
+      <c r="F34" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A34,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A34,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <v/>
+      </c>
+      <c r="G34" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A34,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <v/>
+      </c>
+      <c r="H34" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A34,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <v/>
+      </c>
       <c r="I34" s="16">
         <f>SUM(F34:H34)</f>
         <v/>
@@ -16487,25 +18051,61 @@
         <f>IF(I34=0,0,AQ34*1.2/12*I34)</f>
         <v/>
       </c>
+      <c r="L34" s="16">
+        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A34,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A34,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A34,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A34,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <v/>
+      </c>
       <c r="M34" s="4" t="n"/>
       <c r="N34" s="4" t="n"/>
+      <c r="O34" s="16">
+        <f>IFERROR(IFS(L34="A",2.5,L34="B",0.3,L34="C",0.1,L34="D",0.05,TRUE,""),"")</f>
+        <v/>
+      </c>
       <c r="P34" s="4" t="n"/>
+      <c r="Q34" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A34),0)</f>
+        <v/>
+      </c>
       <c r="R34" s="16">
         <f>Q34*10</f>
         <v/>
       </c>
+      <c r="S34" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A34),0)</f>
+        <v/>
+      </c>
       <c r="T34" s="16">
         <f>S34*20</f>
         <v/>
       </c>
+      <c r="U34" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A34)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A34),0)</f>
+        <v/>
+      </c>
       <c r="V34" s="16">
         <f>U34*40</f>
         <v/>
       </c>
       <c r="W34" s="4" t="n"/>
       <c r="X34" s="4" t="n"/>
+      <c r="Y34" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A34,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A34,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
       <c r="Z34" s="4" t="n"/>
+      <c r="AA34" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A34,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
       <c r="AB34" s="4" t="n"/>
+      <c r="AC34" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A34),0)</f>
+        <v/>
+      </c>
+      <c r="AD34" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A34),0)</f>
+        <v/>
+      </c>
       <c r="AE34" s="16">
         <f>IF(AC34=0,0,AC34*1.7/12*AP34)</f>
         <v/>
@@ -16514,6 +18114,26 @@
         <f>IF(AD34=0,0,AD34*1.7/12*AQ34)</f>
         <v/>
       </c>
+      <c r="AG34" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A34,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A34,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AH34" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A34,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
+      <c r="AI34" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A34,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AJ34" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A34),0)</f>
+        <v/>
+      </c>
+      <c r="AK34" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A34),0)</f>
+        <v/>
+      </c>
       <c r="AL34" s="16">
         <f>(IF((AE34)&lt;(AG34+AH34+AI34),(AE34),(AG34+AH34+AI34)))+AJ34*5+AK34*10+R34+T34+V34</f>
         <v/>
@@ -16532,10 +18152,38 @@
       </c>
     </row>
     <row r="35" ht="16.25" customHeight="1">
+      <c r="A35" s="16">
+        <f>IFERROR('SDA'!A81,"")</f>
+        <v/>
+      </c>
+      <c r="B35" s="16">
+        <f>IFERROR('SDA'!F81,0)</f>
+        <v/>
+      </c>
+      <c r="C35" s="16">
+        <f>IFERROR('SDA'!G81,0)</f>
+        <v/>
+      </c>
+      <c r="D35" s="16">
+        <f>IFERROR('SDA'!H81,0)</f>
+        <v/>
+      </c>
       <c r="E35" s="16">
         <f>SUM(B35:D35)</f>
         <v/>
       </c>
+      <c r="F35" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A35,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A35,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <v/>
+      </c>
+      <c r="G35" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A35,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <v/>
+      </c>
+      <c r="H35" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A35,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <v/>
+      </c>
       <c r="I35" s="16">
         <f>SUM(F35:H35)</f>
         <v/>
@@ -16548,25 +18196,61 @@
         <f>IF(I35=0,0,AQ35*1.2/12*I35)</f>
         <v/>
       </c>
+      <c r="L35" s="16">
+        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A35,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A35,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A35,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A35,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <v/>
+      </c>
       <c r="M35" s="4" t="n"/>
       <c r="N35" s="4" t="n"/>
+      <c r="O35" s="16">
+        <f>IFERROR(IFS(L35="A",2.5,L35="B",0.3,L35="C",0.1,L35="D",0.05,TRUE,""),"")</f>
+        <v/>
+      </c>
       <c r="P35" s="4" t="n"/>
+      <c r="Q35" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A35),0)</f>
+        <v/>
+      </c>
       <c r="R35" s="16">
         <f>Q35*10</f>
         <v/>
       </c>
+      <c r="S35" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A35),0)</f>
+        <v/>
+      </c>
       <c r="T35" s="16">
         <f>S35*20</f>
         <v/>
       </c>
+      <c r="U35" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A35)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A35),0)</f>
+        <v/>
+      </c>
       <c r="V35" s="16">
         <f>U35*40</f>
         <v/>
       </c>
       <c r="W35" s="4" t="n"/>
       <c r="X35" s="4" t="n"/>
+      <c r="Y35" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A35,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A35,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
       <c r="Z35" s="4" t="n"/>
+      <c r="AA35" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A35,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
       <c r="AB35" s="4" t="n"/>
+      <c r="AC35" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A35),0)</f>
+        <v/>
+      </c>
+      <c r="AD35" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A35),0)</f>
+        <v/>
+      </c>
       <c r="AE35" s="16">
         <f>IF(AC35=0,0,AC35*1.7/12*AP35)</f>
         <v/>
@@ -16575,6 +18259,26 @@
         <f>IF(AD35=0,0,AD35*1.7/12*AQ35)</f>
         <v/>
       </c>
+      <c r="AG35" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A35,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A35,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AH35" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A35,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
+      <c r="AI35" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A35,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AJ35" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A35),0)</f>
+        <v/>
+      </c>
+      <c r="AK35" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A35),0)</f>
+        <v/>
+      </c>
       <c r="AL35" s="16">
         <f>(IF((AE35)&lt;(AG35+AH35+AI35),(AE35),(AG35+AH35+AI35)))+AJ35*5+AK35*10+R35+T35+V35</f>
         <v/>
@@ -16593,10 +18297,38 @@
       </c>
     </row>
     <row r="36" ht="16.25" customHeight="1">
+      <c r="A36" s="16">
+        <f>IFERROR('SDA'!A82,"")</f>
+        <v/>
+      </c>
+      <c r="B36" s="16">
+        <f>IFERROR('SDA'!F82,0)</f>
+        <v/>
+      </c>
+      <c r="C36" s="16">
+        <f>IFERROR('SDA'!G82,0)</f>
+        <v/>
+      </c>
+      <c r="D36" s="16">
+        <f>IFERROR('SDA'!H82,0)</f>
+        <v/>
+      </c>
       <c r="E36" s="16">
         <f>SUM(B36:D36)</f>
         <v/>
       </c>
+      <c r="F36" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A36,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A36,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <v/>
+      </c>
+      <c r="G36" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A36,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <v/>
+      </c>
+      <c r="H36" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A36,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <v/>
+      </c>
       <c r="I36" s="16">
         <f>SUM(F36:H36)</f>
         <v/>
@@ -16609,25 +18341,61 @@
         <f>IF(I36=0,0,AQ36*1.2/12*I36)</f>
         <v/>
       </c>
+      <c r="L36" s="16">
+        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A36,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A36,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A36,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A36,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <v/>
+      </c>
       <c r="M36" s="4" t="n"/>
       <c r="N36" s="4" t="n"/>
+      <c r="O36" s="16">
+        <f>IFERROR(IFS(L36="A",2.5,L36="B",0.3,L36="C",0.1,L36="D",0.05,TRUE,""),"")</f>
+        <v/>
+      </c>
       <c r="P36" s="4" t="n"/>
+      <c r="Q36" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A36),0)</f>
+        <v/>
+      </c>
       <c r="R36" s="16">
         <f>Q36*10</f>
         <v/>
       </c>
+      <c r="S36" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A36),0)</f>
+        <v/>
+      </c>
       <c r="T36" s="16">
         <f>S36*20</f>
         <v/>
       </c>
+      <c r="U36" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A36)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A36),0)</f>
+        <v/>
+      </c>
       <c r="V36" s="16">
         <f>U36*40</f>
         <v/>
       </c>
       <c r="W36" s="4" t="n"/>
       <c r="X36" s="4" t="n"/>
+      <c r="Y36" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A36,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A36,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
       <c r="Z36" s="4" t="n"/>
+      <c r="AA36" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A36,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
       <c r="AB36" s="4" t="n"/>
+      <c r="AC36" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A36),0)</f>
+        <v/>
+      </c>
+      <c r="AD36" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A36),0)</f>
+        <v/>
+      </c>
       <c r="AE36" s="16">
         <f>IF(AC36=0,0,AC36*1.7/12*AP36)</f>
         <v/>
@@ -16636,6 +18404,26 @@
         <f>IF(AD36=0,0,AD36*1.7/12*AQ36)</f>
         <v/>
       </c>
+      <c r="AG36" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A36,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A36,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AH36" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A36,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
+      <c r="AI36" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A36,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AJ36" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A36),0)</f>
+        <v/>
+      </c>
+      <c r="AK36" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A36),0)</f>
+        <v/>
+      </c>
       <c r="AL36" s="16">
         <f>(IF((AE36)&lt;(AG36+AH36+AI36),(AE36),(AG36+AH36+AI36)))+AJ36*5+AK36*10+R36+T36+V36</f>
         <v/>
@@ -16654,10 +18442,38 @@
       </c>
     </row>
     <row r="37" ht="16.25" customHeight="1">
+      <c r="A37" s="16">
+        <f>IFERROR('SDA'!A83,"")</f>
+        <v/>
+      </c>
+      <c r="B37" s="16">
+        <f>IFERROR('SDA'!F83,0)</f>
+        <v/>
+      </c>
+      <c r="C37" s="16">
+        <f>IFERROR('SDA'!G83,0)</f>
+        <v/>
+      </c>
+      <c r="D37" s="16">
+        <f>IFERROR('SDA'!H83,0)</f>
+        <v/>
+      </c>
       <c r="E37" s="16">
         <f>SUM(B37:D37)</f>
         <v/>
       </c>
+      <c r="F37" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A37,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A37,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <v/>
+      </c>
+      <c r="G37" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A37,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <v/>
+      </c>
+      <c r="H37" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A37,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <v/>
+      </c>
       <c r="I37" s="16">
         <f>SUM(F37:H37)</f>
         <v/>
@@ -16670,25 +18486,61 @@
         <f>IF(I37=0,0,AQ37*1.2/12*I37)</f>
         <v/>
       </c>
+      <c r="L37" s="16">
+        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A37,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A37,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A37,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A37,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <v/>
+      </c>
       <c r="M37" s="4" t="n"/>
       <c r="N37" s="4" t="n"/>
+      <c r="O37" s="16">
+        <f>IFERROR(IFS(L37="A",2.5,L37="B",0.3,L37="C",0.1,L37="D",0.05,TRUE,""),"")</f>
+        <v/>
+      </c>
       <c r="P37" s="4" t="n"/>
+      <c r="Q37" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A37),0)</f>
+        <v/>
+      </c>
       <c r="R37" s="16">
         <f>Q37*10</f>
         <v/>
       </c>
+      <c r="S37" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A37),0)</f>
+        <v/>
+      </c>
       <c r="T37" s="16">
         <f>S37*20</f>
         <v/>
       </c>
+      <c r="U37" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A37)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A37),0)</f>
+        <v/>
+      </c>
       <c r="V37" s="16">
         <f>U37*40</f>
         <v/>
       </c>
       <c r="W37" s="4" t="n"/>
       <c r="X37" s="4" t="n"/>
+      <c r="Y37" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A37,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A37,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
       <c r="Z37" s="4" t="n"/>
+      <c r="AA37" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A37,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
       <c r="AB37" s="4" t="n"/>
+      <c r="AC37" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A37),0)</f>
+        <v/>
+      </c>
+      <c r="AD37" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A37),0)</f>
+        <v/>
+      </c>
       <c r="AE37" s="16">
         <f>IF(AC37=0,0,AC37*1.7/12*AP37)</f>
         <v/>
@@ -16697,6 +18549,26 @@
         <f>IF(AD37=0,0,AD37*1.7/12*AQ37)</f>
         <v/>
       </c>
+      <c r="AG37" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A37,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A37,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AH37" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A37,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
+      <c r="AI37" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A37,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AJ37" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A37),0)</f>
+        <v/>
+      </c>
+      <c r="AK37" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A37),0)</f>
+        <v/>
+      </c>
       <c r="AL37" s="16">
         <f>(IF((AE37)&lt;(AG37+AH37+AI37),(AE37),(AG37+AH37+AI37)))+AJ37*5+AK37*10+R37+T37+V37</f>
         <v/>
@@ -16715,10 +18587,38 @@
       </c>
     </row>
     <row r="38" ht="16.25" customHeight="1">
+      <c r="A38" s="16">
+        <f>IFERROR('SDA'!A84,"")</f>
+        <v/>
+      </c>
+      <c r="B38" s="16">
+        <f>IFERROR('SDA'!F84,0)</f>
+        <v/>
+      </c>
+      <c r="C38" s="16">
+        <f>IFERROR('SDA'!G84,0)</f>
+        <v/>
+      </c>
+      <c r="D38" s="16">
+        <f>IFERROR('SDA'!H84,0)</f>
+        <v/>
+      </c>
       <c r="E38" s="16">
         <f>SUM(B38:D38)</f>
         <v/>
       </c>
+      <c r="F38" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A38,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A38,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <v/>
+      </c>
+      <c r="G38" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A38,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <v/>
+      </c>
+      <c r="H38" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A38,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <v/>
+      </c>
       <c r="I38" s="16">
         <f>SUM(F38:H38)</f>
         <v/>
@@ -16731,25 +18631,61 @@
         <f>IF(I38=0,0,AQ38*1.2/12*I38)</f>
         <v/>
       </c>
+      <c r="L38" s="16">
+        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A38,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A38,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A38,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A38,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <v/>
+      </c>
       <c r="M38" s="4" t="n"/>
       <c r="N38" s="4" t="n"/>
+      <c r="O38" s="16">
+        <f>IFERROR(IFS(L38="A",2.5,L38="B",0.3,L38="C",0.1,L38="D",0.05,TRUE,""),"")</f>
+        <v/>
+      </c>
       <c r="P38" s="4" t="n"/>
+      <c r="Q38" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A38),0)</f>
+        <v/>
+      </c>
       <c r="R38" s="16">
         <f>Q38*10</f>
         <v/>
       </c>
+      <c r="S38" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A38),0)</f>
+        <v/>
+      </c>
       <c r="T38" s="16">
         <f>S38*20</f>
         <v/>
       </c>
+      <c r="U38" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A38)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A38),0)</f>
+        <v/>
+      </c>
       <c r="V38" s="16">
         <f>U38*40</f>
         <v/>
       </c>
       <c r="W38" s="4" t="n"/>
       <c r="X38" s="4" t="n"/>
+      <c r="Y38" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A38,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A38,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
       <c r="Z38" s="4" t="n"/>
+      <c r="AA38" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A38,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
       <c r="AB38" s="4" t="n"/>
+      <c r="AC38" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A38),0)</f>
+        <v/>
+      </c>
+      <c r="AD38" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A38),0)</f>
+        <v/>
+      </c>
       <c r="AE38" s="16">
         <f>IF(AC38=0,0,AC38*1.7/12*AP38)</f>
         <v/>
@@ -16758,6 +18694,26 @@
         <f>IF(AD38=0,0,AD38*1.7/12*AQ38)</f>
         <v/>
       </c>
+      <c r="AG38" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A38,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A38,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AH38" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A38,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
+      <c r="AI38" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A38,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AJ38" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A38),0)</f>
+        <v/>
+      </c>
+      <c r="AK38" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A38),0)</f>
+        <v/>
+      </c>
       <c r="AL38" s="16">
         <f>(IF((AE38)&lt;(AG38+AH38+AI38),(AE38),(AG38+AH38+AI38)))+AJ38*5+AK38*10+R38+T38+V38</f>
         <v/>
@@ -16776,10 +18732,38 @@
       </c>
     </row>
     <row r="39" ht="16.25" customHeight="1">
+      <c r="A39" s="16">
+        <f>IFERROR('SDA'!A85,"")</f>
+        <v/>
+      </c>
+      <c r="B39" s="16">
+        <f>IFERROR('SDA'!F85,0)</f>
+        <v/>
+      </c>
+      <c r="C39" s="16">
+        <f>IFERROR('SDA'!G85,0)</f>
+        <v/>
+      </c>
+      <c r="D39" s="16">
+        <f>IFERROR('SDA'!H85,0)</f>
+        <v/>
+      </c>
       <c r="E39" s="16">
         <f>SUM(B39:D39)</f>
         <v/>
       </c>
+      <c r="F39" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A39,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A39,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <v/>
+      </c>
+      <c r="G39" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A39,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <v/>
+      </c>
+      <c r="H39" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A39,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <v/>
+      </c>
       <c r="I39" s="16">
         <f>SUM(F39:H39)</f>
         <v/>
@@ -16792,25 +18776,61 @@
         <f>IF(I39=0,0,AQ39*1.2/12*I39)</f>
         <v/>
       </c>
+      <c r="L39" s="16">
+        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A39,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A39,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A39,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A39,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <v/>
+      </c>
       <c r="M39" s="4" t="n"/>
       <c r="N39" s="4" t="n"/>
+      <c r="O39" s="16">
+        <f>IFERROR(IFS(L39="A",2.5,L39="B",0.3,L39="C",0.1,L39="D",0.05,TRUE,""),"")</f>
+        <v/>
+      </c>
       <c r="P39" s="4" t="n"/>
+      <c r="Q39" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A39),0)</f>
+        <v/>
+      </c>
       <c r="R39" s="16">
         <f>Q39*10</f>
         <v/>
       </c>
+      <c r="S39" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A39),0)</f>
+        <v/>
+      </c>
       <c r="T39" s="16">
         <f>S39*20</f>
         <v/>
       </c>
+      <c r="U39" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A39)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A39),0)</f>
+        <v/>
+      </c>
       <c r="V39" s="16">
         <f>U39*40</f>
         <v/>
       </c>
       <c r="W39" s="4" t="n"/>
       <c r="X39" s="4" t="n"/>
+      <c r="Y39" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A39,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A39,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
       <c r="Z39" s="4" t="n"/>
+      <c r="AA39" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A39,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
       <c r="AB39" s="4" t="n"/>
+      <c r="AC39" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A39),0)</f>
+        <v/>
+      </c>
+      <c r="AD39" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A39),0)</f>
+        <v/>
+      </c>
       <c r="AE39" s="16">
         <f>IF(AC39=0,0,AC39*1.7/12*AP39)</f>
         <v/>
@@ -16819,6 +18839,26 @@
         <f>IF(AD39=0,0,AD39*1.7/12*AQ39)</f>
         <v/>
       </c>
+      <c r="AG39" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A39,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A39,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AH39" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A39,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
+      <c r="AI39" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A39,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AJ39" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A39),0)</f>
+        <v/>
+      </c>
+      <c r="AK39" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A39),0)</f>
+        <v/>
+      </c>
       <c r="AL39" s="16">
         <f>(IF((AE39)&lt;(AG39+AH39+AI39),(AE39),(AG39+AH39+AI39)))+AJ39*5+AK39*10+R39+T39+V39</f>
         <v/>
@@ -16837,10 +18877,38 @@
       </c>
     </row>
     <row r="40" ht="16.25" customHeight="1">
+      <c r="A40" s="16">
+        <f>IFERROR('SDA'!A86,"")</f>
+        <v/>
+      </c>
+      <c r="B40" s="16">
+        <f>IFERROR('SDA'!F86,0)</f>
+        <v/>
+      </c>
+      <c r="C40" s="16">
+        <f>IFERROR('SDA'!G86,0)</f>
+        <v/>
+      </c>
+      <c r="D40" s="16">
+        <f>IFERROR('SDA'!H86,0)</f>
+        <v/>
+      </c>
       <c r="E40" s="16">
         <f>SUM(B40:D40)</f>
         <v/>
       </c>
+      <c r="F40" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A40,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A40,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <v/>
+      </c>
+      <c r="G40" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A40,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <v/>
+      </c>
+      <c r="H40" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A40,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <v/>
+      </c>
       <c r="I40" s="16">
         <f>SUM(F40:H40)</f>
         <v/>
@@ -16853,25 +18921,61 @@
         <f>IF(I40=0,0,AQ40*1.2/12*I40)</f>
         <v/>
       </c>
+      <c r="L40" s="16">
+        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A40,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A40,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A40,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A40,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <v/>
+      </c>
       <c r="M40" s="4" t="n"/>
       <c r="N40" s="4" t="n"/>
+      <c r="O40" s="16">
+        <f>IFERROR(IFS(L40="A",2.5,L40="B",0.3,L40="C",0.1,L40="D",0.05,TRUE,""),"")</f>
+        <v/>
+      </c>
       <c r="P40" s="4" t="n"/>
+      <c r="Q40" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A40),0)</f>
+        <v/>
+      </c>
       <c r="R40" s="16">
         <f>Q40*10</f>
         <v/>
       </c>
+      <c r="S40" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A40),0)</f>
+        <v/>
+      </c>
       <c r="T40" s="16">
         <f>S40*20</f>
         <v/>
       </c>
+      <c r="U40" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A40)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A40),0)</f>
+        <v/>
+      </c>
       <c r="V40" s="16">
         <f>U40*40</f>
         <v/>
       </c>
       <c r="W40" s="4" t="n"/>
       <c r="X40" s="4" t="n"/>
+      <c r="Y40" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A40,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A40,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
       <c r="Z40" s="4" t="n"/>
+      <c r="AA40" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A40,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
       <c r="AB40" s="4" t="n"/>
+      <c r="AC40" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A40),0)</f>
+        <v/>
+      </c>
+      <c r="AD40" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A40),0)</f>
+        <v/>
+      </c>
       <c r="AE40" s="16">
         <f>IF(AC40=0,0,AC40*1.7/12*AP40)</f>
         <v/>
@@ -16880,6 +18984,26 @@
         <f>IF(AD40=0,0,AD40*1.7/12*AQ40)</f>
         <v/>
       </c>
+      <c r="AG40" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A40,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A40,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AH40" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A40,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
+      <c r="AI40" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A40,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AJ40" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A40),0)</f>
+        <v/>
+      </c>
+      <c r="AK40" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A40),0)</f>
+        <v/>
+      </c>
       <c r="AL40" s="16">
         <f>(IF((AE40)&lt;(AG40+AH40+AI40),(AE40),(AG40+AH40+AI40)))+AJ40*5+AK40*10+R40+T40+V40</f>
         <v/>
@@ -16898,10 +19022,38 @@
       </c>
     </row>
     <row r="41" ht="16.25" customHeight="1">
+      <c r="A41" s="16">
+        <f>IFERROR('SDA'!A87,"")</f>
+        <v/>
+      </c>
+      <c r="B41" s="16">
+        <f>IFERROR('SDA'!F87,0)</f>
+        <v/>
+      </c>
+      <c r="C41" s="16">
+        <f>IFERROR('SDA'!G87,0)</f>
+        <v/>
+      </c>
+      <c r="D41" s="16">
+        <f>IFERROR('SDA'!H87,0)</f>
+        <v/>
+      </c>
       <c r="E41" s="16">
         <f>SUM(B41:D41)</f>
         <v/>
       </c>
+      <c r="F41" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A41,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A41,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <v/>
+      </c>
+      <c r="G41" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A41,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <v/>
+      </c>
+      <c r="H41" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A41,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <v/>
+      </c>
       <c r="I41" s="16">
         <f>SUM(F41:H41)</f>
         <v/>
@@ -16914,25 +19066,61 @@
         <f>IF(I41=0,0,AQ41*1.2/12*I41)</f>
         <v/>
       </c>
+      <c r="L41" s="16">
+        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A41,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A41,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A41,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A41,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <v/>
+      </c>
       <c r="M41" s="4" t="n"/>
       <c r="N41" s="4" t="n"/>
+      <c r="O41" s="16">
+        <f>IFERROR(IFS(L41="A",2.5,L41="B",0.3,L41="C",0.1,L41="D",0.05,TRUE,""),"")</f>
+        <v/>
+      </c>
       <c r="P41" s="4" t="n"/>
+      <c r="Q41" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A41),0)</f>
+        <v/>
+      </c>
       <c r="R41" s="16">
         <f>Q41*10</f>
         <v/>
       </c>
+      <c r="S41" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A41),0)</f>
+        <v/>
+      </c>
       <c r="T41" s="16">
         <f>S41*20</f>
         <v/>
       </c>
+      <c r="U41" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A41)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A41),0)</f>
+        <v/>
+      </c>
       <c r="V41" s="16">
         <f>U41*40</f>
         <v/>
       </c>
       <c r="W41" s="4" t="n"/>
       <c r="X41" s="4" t="n"/>
+      <c r="Y41" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A41,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A41,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
       <c r="Z41" s="4" t="n"/>
+      <c r="AA41" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A41,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
       <c r="AB41" s="4" t="n"/>
+      <c r="AC41" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A41),0)</f>
+        <v/>
+      </c>
+      <c r="AD41" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A41),0)</f>
+        <v/>
+      </c>
       <c r="AE41" s="16">
         <f>IF(AC41=0,0,AC41*1.7/12*AP41)</f>
         <v/>
@@ -16941,6 +19129,26 @@
         <f>IF(AD41=0,0,AD41*1.7/12*AQ41)</f>
         <v/>
       </c>
+      <c r="AG41" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A41,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A41,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AH41" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A41,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
+      <c r="AI41" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A41,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AJ41" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A41),0)</f>
+        <v/>
+      </c>
+      <c r="AK41" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A41),0)</f>
+        <v/>
+      </c>
       <c r="AL41" s="16">
         <f>(IF((AE41)&lt;(AG41+AH41+AI41),(AE41),(AG41+AH41+AI41)))+AJ41*5+AK41*10+R41+T41+V41</f>
         <v/>
@@ -16959,10 +19167,38 @@
       </c>
     </row>
     <row r="42" ht="16.25" customHeight="1">
+      <c r="A42" s="16">
+        <f>IFERROR('SDA'!A88,"")</f>
+        <v/>
+      </c>
+      <c r="B42" s="16">
+        <f>IFERROR('SDA'!F88,0)</f>
+        <v/>
+      </c>
+      <c r="C42" s="16">
+        <f>IFERROR('SDA'!G88,0)</f>
+        <v/>
+      </c>
+      <c r="D42" s="16">
+        <f>IFERROR('SDA'!H88,0)</f>
+        <v/>
+      </c>
       <c r="E42" s="16">
         <f>SUM(B42:D42)</f>
         <v/>
       </c>
+      <c r="F42" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A42,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A42,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <v/>
+      </c>
+      <c r="G42" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A42,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <v/>
+      </c>
+      <c r="H42" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A42,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <v/>
+      </c>
       <c r="I42" s="16">
         <f>SUM(F42:H42)</f>
         <v/>
@@ -16975,25 +19211,61 @@
         <f>IF(I42=0,0,AQ42*1.2/12*I42)</f>
         <v/>
       </c>
+      <c r="L42" s="16">
+        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A42,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A42,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A42,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A42,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <v/>
+      </c>
       <c r="M42" s="4" t="n"/>
       <c r="N42" s="4" t="n"/>
+      <c r="O42" s="16">
+        <f>IFERROR(IFS(L42="A",2.5,L42="B",0.3,L42="C",0.1,L42="D",0.05,TRUE,""),"")</f>
+        <v/>
+      </c>
       <c r="P42" s="4" t="n"/>
+      <c r="Q42" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A42),0)</f>
+        <v/>
+      </c>
       <c r="R42" s="16">
         <f>Q42*10</f>
         <v/>
       </c>
+      <c r="S42" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A42),0)</f>
+        <v/>
+      </c>
       <c r="T42" s="16">
         <f>S42*20</f>
         <v/>
       </c>
+      <c r="U42" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A42)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A42),0)</f>
+        <v/>
+      </c>
       <c r="V42" s="16">
         <f>U42*40</f>
         <v/>
       </c>
       <c r="W42" s="4" t="n"/>
       <c r="X42" s="4" t="n"/>
+      <c r="Y42" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A42,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A42,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
       <c r="Z42" s="4" t="n"/>
+      <c r="AA42" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A42,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
       <c r="AB42" s="4" t="n"/>
+      <c r="AC42" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A42),0)</f>
+        <v/>
+      </c>
+      <c r="AD42" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A42),0)</f>
+        <v/>
+      </c>
       <c r="AE42" s="16">
         <f>IF(AC42=0,0,AC42*1.7/12*AP42)</f>
         <v/>
@@ -17002,6 +19274,26 @@
         <f>IF(AD42=0,0,AD42*1.7/12*AQ42)</f>
         <v/>
       </c>
+      <c r="AG42" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A42,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A42,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AH42" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A42,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
+      <c r="AI42" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A42,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AJ42" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A42),0)</f>
+        <v/>
+      </c>
+      <c r="AK42" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A42),0)</f>
+        <v/>
+      </c>
       <c r="AL42" s="16">
         <f>(IF((AE42)&lt;(AG42+AH42+AI42),(AE42),(AG42+AH42+AI42)))+AJ42*5+AK42*10+R42+T42+V42</f>
         <v/>
@@ -17020,10 +19312,38 @@
       </c>
     </row>
     <row r="43" ht="16.25" customHeight="1">
+      <c r="A43" s="16">
+        <f>IFERROR('SDA'!A89,"")</f>
+        <v/>
+      </c>
+      <c r="B43" s="16">
+        <f>IFERROR('SDA'!F89,0)</f>
+        <v/>
+      </c>
+      <c r="C43" s="16">
+        <f>IFERROR('SDA'!G89,0)</f>
+        <v/>
+      </c>
+      <c r="D43" s="16">
+        <f>IFERROR('SDA'!H89,0)</f>
+        <v/>
+      </c>
       <c r="E43" s="16">
         <f>SUM(B43:D43)</f>
         <v/>
       </c>
+      <c r="F43" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A43,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A43,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <v/>
+      </c>
+      <c r="G43" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A43,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <v/>
+      </c>
+      <c r="H43" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A43,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <v/>
+      </c>
       <c r="I43" s="16">
         <f>SUM(F43:H43)</f>
         <v/>
@@ -17036,25 +19356,61 @@
         <f>IF(I43=0,0,AQ43*1.2/12*I43)</f>
         <v/>
       </c>
+      <c r="L43" s="16">
+        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A43,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A43,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A43,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A43,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <v/>
+      </c>
       <c r="M43" s="4" t="n"/>
       <c r="N43" s="4" t="n"/>
+      <c r="O43" s="16">
+        <f>IFERROR(IFS(L43="A",2.5,L43="B",0.3,L43="C",0.1,L43="D",0.05,TRUE,""),"")</f>
+        <v/>
+      </c>
       <c r="P43" s="4" t="n"/>
+      <c r="Q43" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A43),0)</f>
+        <v/>
+      </c>
       <c r="R43" s="16">
         <f>Q43*10</f>
         <v/>
       </c>
+      <c r="S43" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A43),0)</f>
+        <v/>
+      </c>
       <c r="T43" s="16">
         <f>S43*20</f>
         <v/>
       </c>
+      <c r="U43" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A43)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A43),0)</f>
+        <v/>
+      </c>
       <c r="V43" s="16">
         <f>U43*40</f>
         <v/>
       </c>
       <c r="W43" s="4" t="n"/>
       <c r="X43" s="4" t="n"/>
+      <c r="Y43" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A43,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A43,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
       <c r="Z43" s="4" t="n"/>
+      <c r="AA43" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A43,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
       <c r="AB43" s="4" t="n"/>
+      <c r="AC43" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A43),0)</f>
+        <v/>
+      </c>
+      <c r="AD43" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A43),0)</f>
+        <v/>
+      </c>
       <c r="AE43" s="16">
         <f>IF(AC43=0,0,AC43*1.7/12*AP43)</f>
         <v/>
@@ -17063,6 +19419,26 @@
         <f>IF(AD43=0,0,AD43*1.7/12*AQ43)</f>
         <v/>
       </c>
+      <c r="AG43" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A43,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A43,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AH43" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A43,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
+      <c r="AI43" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A43,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AJ43" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A43),0)</f>
+        <v/>
+      </c>
+      <c r="AK43" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A43),0)</f>
+        <v/>
+      </c>
       <c r="AL43" s="16">
         <f>(IF((AE43)&lt;(AG43+AH43+AI43),(AE43),(AG43+AH43+AI43)))+AJ43*5+AK43*10+R43+T43+V43</f>
         <v/>
@@ -17081,10 +19457,38 @@
       </c>
     </row>
     <row r="44" ht="16.25" customHeight="1">
+      <c r="A44" s="16">
+        <f>IFERROR('SDA'!A90,"")</f>
+        <v/>
+      </c>
+      <c r="B44" s="16">
+        <f>IFERROR('SDA'!F90,0)</f>
+        <v/>
+      </c>
+      <c r="C44" s="16">
+        <f>IFERROR('SDA'!G90,0)</f>
+        <v/>
+      </c>
+      <c r="D44" s="16">
+        <f>IFERROR('SDA'!H90,0)</f>
+        <v/>
+      </c>
       <c r="E44" s="16">
         <f>SUM(B44:D44)</f>
         <v/>
       </c>
+      <c r="F44" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A44,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A44,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <v/>
+      </c>
+      <c r="G44" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A44,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <v/>
+      </c>
+      <c r="H44" s="16">
+        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A44,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <v/>
+      </c>
       <c r="I44" s="16">
         <f>SUM(F44:H44)</f>
         <v/>
@@ -17097,25 +19501,61 @@
         <f>IF(I44=0,0,AQ44*1.2/12*I44)</f>
         <v/>
       </c>
+      <c r="L44" s="16">
+        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A44,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A44,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A44,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A44,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <v/>
+      </c>
       <c r="M44" s="4" t="n"/>
       <c r="N44" s="4" t="n"/>
+      <c r="O44" s="16">
+        <f>IFERROR(IFS(L44="A",2.5,L44="B",0.3,L44="C",0.1,L44="D",0.05,TRUE,""),"")</f>
+        <v/>
+      </c>
       <c r="P44" s="4" t="n"/>
+      <c r="Q44" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A44),0)</f>
+        <v/>
+      </c>
       <c r="R44" s="16">
         <f>Q44*10</f>
         <v/>
       </c>
+      <c r="S44" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A44),0)</f>
+        <v/>
+      </c>
       <c r="T44" s="16">
         <f>S44*20</f>
         <v/>
       </c>
+      <c r="U44" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A44)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A44),0)</f>
+        <v/>
+      </c>
       <c r="V44" s="16">
         <f>U44*40</f>
         <v/>
       </c>
       <c r="W44" s="4" t="n"/>
       <c r="X44" s="4" t="n"/>
+      <c r="Y44" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A44,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A44,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
       <c r="Z44" s="4" t="n"/>
+      <c r="AA44" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A44,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
       <c r="AB44" s="4" t="n"/>
+      <c r="AC44" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A44),0)</f>
+        <v/>
+      </c>
+      <c r="AD44" s="16">
+        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A44),0)</f>
+        <v/>
+      </c>
       <c r="AE44" s="16">
         <f>IF(AC44=0,0,AC44*1.7/12*AP44)</f>
         <v/>
@@ -17124,6 +19564,26 @@
         <f>IF(AD44=0,0,AD44*1.7/12*AQ44)</f>
         <v/>
       </c>
+      <c r="AG44" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A44,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A44,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AH44" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A44,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <v/>
+      </c>
+      <c r="AI44" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A44,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <v/>
+      </c>
+      <c r="AJ44" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A44),0)</f>
+        <v/>
+      </c>
+      <c r="AK44" s="16">
+        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A44),0)</f>
+        <v/>
+      </c>
       <c r="AL44" s="16">
         <f>(IF((AE44)&lt;(AG44+AH44+AI44),(AE44),(AG44+AH44+AI44)))+AJ44*5+AK44*10+R44+T44+V44</f>
         <v/>
@@ -17147,51 +19607,51 @@
           <t>DATOTAL</t>
         </is>
       </c>
-      <c r="E45" s="19">
+      <c r="E45" s="27">
         <f>SUM(E12:E44)</f>
         <v/>
       </c>
-      <c r="I45" s="19">
+      <c r="I45" s="27">
         <f>SUM(I12:I44)</f>
         <v/>
       </c>
-      <c r="J45" s="19">
+      <c r="J45" s="27">
         <f>SUM(J12:J44)</f>
         <v/>
       </c>
-      <c r="K45" s="19">
+      <c r="K45" s="27">
         <f>SUM(K12:K44)</f>
         <v/>
       </c>
-      <c r="Q45" s="19">
+      <c r="Q45" s="27">
         <f>SUM(Q12:Q44)</f>
         <v/>
       </c>
-      <c r="R45" s="19">
+      <c r="R45" s="27">
         <f>SUM(R12:R44)</f>
         <v/>
       </c>
-      <c r="S45" s="19">
+      <c r="S45" s="27">
         <f>SUM(S12:S44)</f>
         <v/>
       </c>
-      <c r="T45" s="19">
+      <c r="T45" s="27">
         <f>SUM(T12:T44)</f>
         <v/>
       </c>
-      <c r="U45" s="19">
+      <c r="U45" s="27">
         <f>SUM(U12:U44)</f>
         <v/>
       </c>
-      <c r="V45" s="19">
+      <c r="V45" s="27">
         <f>SUM(V12:V44)</f>
         <v/>
       </c>
-      <c r="AL45" s="19">
+      <c r="AL45" s="27">
         <f>SUM(AL12:AL44)</f>
         <v/>
       </c>
-      <c r="AM45" s="19">
+      <c r="AM45" s="27">
         <f>SUM(AM12:AM44)</f>
         <v/>
       </c>
@@ -17249,17 +19709,17 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="20" t="inlineStr">
+      <c r="A1" s="28" t="inlineStr">
         <is>
           <t>EISA Section 438 — Direct Determination (Horton infiltration)</t>
         </is>
       </c>
-      <c r="B1" s="21" t="n"/>
-      <c r="C1" s="21" t="n"/>
-      <c r="D1" s="21" t="n"/>
-      <c r="E1" s="21" t="n"/>
-      <c r="F1" s="21" t="n"/>
-      <c r="G1" s="22" t="n"/>
+      <c r="B1" s="29" t="n"/>
+      <c r="C1" s="29" t="n"/>
+      <c r="D1" s="29" t="n"/>
+      <c r="E1" s="29" t="n"/>
+      <c r="F1" s="29" t="n"/>
+      <c r="G1" s="30" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
@@ -17409,37 +19869,37 @@
       <c r="G15" s="8" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="26" t="inlineStr">
         <is>
           <t>Surface</t>
         </is>
       </c>
-      <c r="B16" s="18" t="inlineStr">
+      <c r="B16" s="26" t="inlineStr">
         <is>
           <t>HSG</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C16" s="26" t="inlineStr">
         <is>
           <t>Area (SF)</t>
         </is>
       </c>
-      <c r="D16" s="18" t="inlineStr">
+      <c r="D16" s="26" t="inlineStr">
         <is>
           <t>Runoff HSG B (in)</t>
         </is>
       </c>
-      <c r="E16" s="18" t="inlineStr">
+      <c r="E16" s="26" t="inlineStr">
         <is>
           <t>Runoff HSG C (in)</t>
         </is>
       </c>
-      <c r="F16" s="18" t="inlineStr">
+      <c r="F16" s="26" t="inlineStr">
         <is>
           <t>Vol HSG B (CF)</t>
         </is>
       </c>
-      <c r="G16" s="18" t="inlineStr">
+      <c r="G16" s="26" t="inlineStr">
         <is>
           <t>Vol HSG C (CF)</t>
         </is>
@@ -17830,37 +20290,37 @@
       <c r="G30" s="8" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="inlineStr">
+      <c r="A31" s="26" t="inlineStr">
         <is>
           <t>Surface</t>
         </is>
       </c>
-      <c r="B31" s="18" t="inlineStr">
+      <c r="B31" s="26" t="inlineStr">
         <is>
           <t>HSG</t>
         </is>
       </c>
-      <c r="C31" s="18" t="inlineStr">
+      <c r="C31" s="26" t="inlineStr">
         <is>
           <t>Area (SF)</t>
         </is>
       </c>
-      <c r="D31" s="18" t="inlineStr">
+      <c r="D31" s="26" t="inlineStr">
         <is>
           <t>Runoff HSG B (in)</t>
         </is>
       </c>
-      <c r="E31" s="18" t="inlineStr">
+      <c r="E31" s="26" t="inlineStr">
         <is>
           <t>Runoff HSG C (in)</t>
         </is>
       </c>
-      <c r="F31" s="18" t="inlineStr">
+      <c r="F31" s="26" t="inlineStr">
         <is>
           <t>Vol HSG B (CF)</t>
         </is>
       </c>
-      <c r="G31" s="18" t="inlineStr">
+      <c r="G31" s="26" t="inlineStr">
         <is>
           <t>Vol HSG C (CF)</t>
         </is>
@@ -18238,26 +20698,26 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="20" t="inlineStr">
+      <c r="A45" s="28" t="inlineStr">
         <is>
           <t>Compliance Check</t>
         </is>
       </c>
-      <c r="B45" s="21" t="n"/>
-      <c r="C45" s="22" t="n"/>
+      <c r="B45" s="29" t="n"/>
+      <c r="C45" s="30" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="23" t="inlineStr">
+      <c r="A46" s="31" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B46" s="23" t="inlineStr">
+      <c r="B46" s="31" t="inlineStr">
         <is>
           <t>HSG B</t>
         </is>
       </c>
-      <c r="C46" s="23" t="inlineStr">
+      <c r="C46" s="31" t="inlineStr">
         <is>
           <t>HSG C</t>
         </is>
@@ -18371,16 +20831,16 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="20" t="inlineStr">
+      <c r="A1" s="28" t="inlineStr">
         <is>
           <t>EISA Section 438 — TR-55 CN Method (Method A primary)</t>
         </is>
       </c>
-      <c r="B1" s="21" t="n"/>
-      <c r="C1" s="21" t="n"/>
-      <c r="D1" s="21" t="n"/>
-      <c r="E1" s="21" t="n"/>
-      <c r="F1" s="22" t="n"/>
+      <c r="B1" s="29" t="n"/>
+      <c r="C1" s="29" t="n"/>
+      <c r="D1" s="29" t="n"/>
+      <c r="E1" s="29" t="n"/>
+      <c r="F1" s="30" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
@@ -18440,32 +20900,32 @@
       <c r="F8" s="13" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="23" t="inlineStr">
+      <c r="A9" s="31" t="inlineStr">
         <is>
           <t>Surface</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="31" t="inlineStr">
         <is>
           <t>HSG</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C9" s="31" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D9" s="31" t="inlineStr">
         <is>
           <t>Area (SF)</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="E9" s="31" t="inlineStr">
         <is>
           <t>Q (in)</t>
         </is>
       </c>
-      <c r="F9" s="23" t="inlineStr">
+      <c r="F9" s="31" t="inlineStr">
         <is>
           <t>Vol (CF)</t>
         </is>
@@ -18805,32 +21265,32 @@
       <c r="F23" s="13" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="23" t="inlineStr">
+      <c r="A24" s="31" t="inlineStr">
         <is>
           <t>Surface</t>
         </is>
       </c>
-      <c r="B24" s="23" t="inlineStr">
+      <c r="B24" s="31" t="inlineStr">
         <is>
           <t>HSG</t>
         </is>
       </c>
-      <c r="C24" s="23" t="inlineStr">
+      <c r="C24" s="31" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="D24" s="23" t="inlineStr">
+      <c r="D24" s="31" t="inlineStr">
         <is>
           <t>Area (SF)</t>
         </is>
       </c>
-      <c r="E24" s="23" t="inlineStr">
+      <c r="E24" s="31" t="inlineStr">
         <is>
           <t>Q (in)</t>
         </is>
       </c>
-      <c r="F24" s="23" t="inlineStr">
+      <c r="F24" s="31" t="inlineStr">
         <is>
           <t>Vol (CF)</t>
         </is>
@@ -19158,12 +21618,12 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="20" t="inlineStr">
+      <c r="A38" s="28" t="inlineStr">
         <is>
           <t>Compliance Check (Method A)</t>
         </is>
       </c>
-      <c r="B38" s="22" t="n"/>
+      <c r="B38" s="30" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">

--- a/SW_Required_Provided_DOEE_EISA438.xlsx
+++ b/SW_Required_Provided_DOEE_EISA438.xlsx
@@ -51,7 +51,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -72,6 +72,11 @@
     <font>
       <color rgb="00000000"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="13">
@@ -137,7 +142,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -237,11 +242,31 @@
       <top/>
       <bottom/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -295,6 +320,28 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3739,7 +3786,7 @@
         <f>SUMIFS('BMP'!$AM$4:$AM$53,'BMP'!$B$4:$B$53,A4)</f>
         <v/>
       </c>
-      <c r="D4" s="32">
+      <c r="D4" s="42">
         <f>IFERROR(C4/B4,0)</f>
         <v/>
       </c>
@@ -3765,7 +3812,7 @@
         <f>SUMIFS('BMP'!$AM$4:$AM$53,'BMP'!$B$4:$B$53,A5)</f>
         <v/>
       </c>
-      <c r="D5" s="32">
+      <c r="D5" s="42">
         <f>IFERROR(C5/B5,0)</f>
         <v/>
       </c>
@@ -3791,7 +3838,7 @@
         <f>SUMIFS('BMP'!$AM$4:$AM$53,'BMP'!$B$4:$B$53,A6)</f>
         <v/>
       </c>
-      <c r="D6" s="32">
+      <c r="D6" s="42">
         <f>IFERROR(C6/B6,0)</f>
         <v/>
       </c>
@@ -3817,7 +3864,7 @@
         <f>SUMIFS('BMP'!$AM$4:$AM$53,'BMP'!$B$4:$B$53,A7)</f>
         <v/>
       </c>
-      <c r="D7" s="32">
+      <c r="D7" s="42">
         <f>IFERROR(C7/B7,0)</f>
         <v/>
       </c>
@@ -3843,7 +3890,7 @@
         <f>SUMIFS('BMP'!$AM$4:$AM$53,'BMP'!$B$4:$B$53,A8)</f>
         <v/>
       </c>
-      <c r="D8" s="32">
+      <c r="D8" s="42">
         <f>IFERROR(C8/B8,0)</f>
         <v/>
       </c>
@@ -3869,7 +3916,7 @@
         <f>SUMIFS('BMP'!$AM$4:$AM$53,'BMP'!$B$4:$B$53,A9)</f>
         <v/>
       </c>
-      <c r="D9" s="32">
+      <c r="D9" s="42">
         <f>IFERROR(C9/B9,0)</f>
         <v/>
       </c>
@@ -3895,7 +3942,7 @@
         <f>SUMIFS('BMP'!$AM$4:$AM$53,'BMP'!$B$4:$B$53,A10)</f>
         <v/>
       </c>
-      <c r="D10" s="32">
+      <c r="D10" s="42">
         <f>IFERROR(C10/B10,0)</f>
         <v/>
       </c>
@@ -3921,7 +3968,7 @@
         <f>SUMIFS('BMP'!$AM$4:$AM$53,'BMP'!$B$4:$B$53,A11)</f>
         <v/>
       </c>
-      <c r="D11" s="32">
+      <c r="D11" s="42">
         <f>IFERROR(C11/B11,0)</f>
         <v/>
       </c>
@@ -3947,7 +3994,7 @@
         <f>SUMIFS('BMP'!$AM$4:$AM$53,'BMP'!$B$4:$B$53,A12)</f>
         <v/>
       </c>
-      <c r="D12" s="32">
+      <c r="D12" s="42">
         <f>IFERROR(C12/B12,0)</f>
         <v/>
       </c>
@@ -3973,7 +4020,7 @@
         <f>SUMIFS('BMP'!$AM$4:$AM$53,'BMP'!$B$4:$B$53,A13)</f>
         <v/>
       </c>
-      <c r="D13" s="32">
+      <c r="D13" s="42">
         <f>IFERROR(C13/B13,0)</f>
         <v/>
       </c>
@@ -4000,7 +4047,7 @@
         <f>SUM(C4:C13)</f>
         <v/>
       </c>
-      <c r="D15" s="32">
+      <c r="D15" s="42">
         <f>IFERROR(C15/B15,0)</f>
         <v/>
       </c>
@@ -14085,10 +14132,10 @@
     <col width="13.86" customWidth="1" min="6" max="6"/>
     <col width="12.86" customWidth="1" min="7" max="7"/>
     <col width="13.86" customWidth="1" min="8" max="8"/>
-    <col width="12.86" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
     <col width="12.46" customWidth="1" min="10" max="10"/>
     <col width="10.66" customWidth="1" min="11" max="11"/>
-    <col width="16.53" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
     <col width="11.33" customWidth="1" min="13" max="13"/>
     <col width="13.46" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
@@ -14122,47 +14169,53 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="B1" s="25" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Project Name:</t>
         </is>
       </c>
-      <c r="D1">
+      <c r="D1" s="4">
         <f>PROJECT_Name</f>
         <v/>
       </c>
-      <c r="H1" s="25" t="inlineStr">
+      <c r="E1" s="25" t="n"/>
+      <c r="F1" s="25" t="n"/>
+      <c r="G1" s="26" t="n"/>
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>Project No:</t>
         </is>
       </c>
-      <c r="L1" s="25" t="inlineStr">
-        <is>
-          <t>Check One: MS4         CSS</t>
-        </is>
-      </c>
-      <c r="N1">
+      <c r="I1" s="27" t="n"/>
+      <c r="J1" s="27" t="n"/>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>Check One: MS4 / CSS</t>
+        </is>
+      </c>
+      <c r="N1" s="4">
         <f>PROJECT_MS4</f>
         <v/>
       </c>
-      <c r="P1" s="25" t="inlineStr">
+      <c r="P1" s="3" t="inlineStr">
         <is>
           <t>Check if in AWDZ:</t>
         </is>
       </c>
-      <c r="R1">
+      <c r="R1" s="4">
         <f>PROJECT_AWDZ</f>
         <v/>
       </c>
-      <c r="S1" s="25" t="inlineStr">
+      <c r="S1" s="3" t="inlineStr">
         <is>
           <t>DOEE Plan Review No.:</t>
         </is>
       </c>
-      <c r="T1">
+      <c r="T1" s="4">
         <f>PROJECT_DOEEReview</f>
         <v/>
       </c>
+      <c r="U1" s="26" t="n"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Project Name:</t>
@@ -14182,38 +14235,38 @@
         <v/>
       </c>
     </row>
-    <row r="2" ht="24.75" customHeight="1">
-      <c r="B2" t="inlineStr">
+    <row r="2" ht="22" customHeight="1">
+      <c r="B2" s="28" t="inlineStr">
         <is>
           <t>Summary Data: 90%/Final Design Phase</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>Notes:</t>
         </is>
       </c>
-      <c r="W2">
+      <c r="W2" s="29">
         <f>B2</f>
         <v/>
       </c>
     </row>
-    <row r="3" ht="17.45" customHeight="1">
-      <c r="I3" t="inlineStr">
+    <row r="3" ht="36" customHeight="1">
+      <c r="I3" s="30" t="inlineStr">
         <is>
           <t>Regulated Retention Volume (1.2"):</t>
         </is>
       </c>
-      <c r="J3">
+      <c r="J3" s="31">
         <f>J45</f>
         <v/>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="10" t="inlineStr">
         <is>
           <t>CF</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="32" t="inlineStr">
         <is>
           <t>Blocks in the worksheet that are not shaded are data entry fields for the designer.</t>
         </is>
@@ -14231,31 +14284,31 @@
         <v/>
       </c>
     </row>
-    <row r="4" ht="19.25" customHeight="1">
-      <c r="B4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Disturbance Area (ac.): </t>
-        </is>
-      </c>
-      <c r="E4">
+    <row r="4" ht="36" customHeight="1">
+      <c r="B4" s="30" t="inlineStr">
+        <is>
+          <t>Disturbance Area (ac.):</t>
+        </is>
+      </c>
+      <c r="E4" s="33">
         <f>E45/43560</f>
         <v/>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="30" t="inlineStr">
         <is>
           <t>Volume Retained:</t>
         </is>
       </c>
-      <c r="J4">
+      <c r="J4" s="31">
         <f>AL45</f>
         <v/>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" s="10" t="inlineStr">
         <is>
           <t>CF</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L4" s="32" t="inlineStr">
         <is>
           <t>All shaded blocks are computations internal to the worksheet and should not be edited.</t>
         </is>
@@ -14281,26 +14334,26 @@
         <v/>
       </c>
     </row>
-    <row r="5" ht="19.25" customHeight="1">
-      <c r="B5" t="inlineStr">
+    <row r="5" ht="22" customHeight="1">
+      <c r="B5" s="30" t="inlineStr">
         <is>
           <t>No. of Drainage Areas:</t>
         </is>
       </c>
-      <c r="E5">
+      <c r="E5" s="34">
         <f>COUNTA(A12:A44)</f>
         <v/>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="30" t="inlineStr">
         <is>
           <t>Difference:</t>
         </is>
       </c>
-      <c r="J5">
+      <c r="J5" s="31">
         <f>J4-J3</f>
         <v/>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" s="10" t="inlineStr">
         <is>
           <t>CF</t>
         </is>
@@ -14327,490 +14380,523 @@
       </c>
     </row>
     <row r="6" ht="9.75" customHeight="1"/>
-    <row r="7" ht="16.9" customHeight="1">
-      <c r="B7" t="inlineStr">
+    <row r="7" ht="28" customHeight="1">
+      <c r="B7" s="1" t="inlineStr">
         <is>
           <t>Step 1:  Drainage Area and Regulated Volumes</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="2" t="n"/>
+      <c r="L7" s="1" t="inlineStr">
         <is>
           <t>Step 2:  Consider Infiltration</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+      <c r="P7" s="2" t="n"/>
+      <c r="Q7" s="1" t="inlineStr">
         <is>
           <t>Step 3:  Evaluate Existing Infrastructure Constraints</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="R7" s="5" t="n"/>
+      <c r="S7" s="5" t="n"/>
+      <c r="T7" s="5" t="n"/>
+      <c r="U7" s="5" t="n"/>
+      <c r="V7" s="2" t="n"/>
+      <c r="W7" s="1" t="inlineStr">
         <is>
           <t>Step 4:  Identify Land Conversion and BMP Placement Opportunities</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="X7" s="5" t="n"/>
+      <c r="Y7" s="5" t="n"/>
+      <c r="Z7" s="5" t="n"/>
+      <c r="AA7" s="5" t="n"/>
+      <c r="AB7" s="2" t="n"/>
+      <c r="AC7" s="1" t="inlineStr">
         <is>
           <t>Step 5: Size BMPs and Compute Achieved Retention Volumes</t>
         </is>
       </c>
+      <c r="AD7" s="5" t="n"/>
+      <c r="AE7" s="5" t="n"/>
+      <c r="AF7" s="5" t="n"/>
+      <c r="AG7" s="5" t="n"/>
+      <c r="AH7" s="5" t="n"/>
+      <c r="AI7" s="5" t="n"/>
+      <c r="AJ7" s="5" t="n"/>
+      <c r="AK7" s="5" t="n"/>
+      <c r="AL7" s="5" t="n"/>
+      <c r="AM7" s="2" t="n"/>
     </row>
     <row r="8" ht="102.75" customHeight="1">
-      <c r="B8" s="25" t="inlineStr">
+      <c r="B8" s="35" t="inlineStr">
         <is>
           <t>Update from 65% based on refined or revised design: 
 Number and list each drainage area within the project limits of disturbance (LOD). Provide the drainage area square footage that contributes runoff in the LOD and outside the LOD. The SWRv is calculated for each drainage area. Provide corresponding drainage area identifications on the SWMP.</t>
         </is>
       </c>
-      <c r="L8" s="25" t="inlineStr">
+      <c r="L8" s="35" t="inlineStr">
         <is>
           <t>Record the water table, bedrock concerns, infiltration rate, and hotspot concerns within the LOD for each drainage area.</t>
         </is>
       </c>
-      <c r="Q8" s="25" t="inlineStr">
+      <c r="Q8" s="35" t="inlineStr">
         <is>
           <t>On the SWMP, depict utility locations and conveyance infrastructure to confirm/adjust opportunities for land conversions and BMPs. Delineate areas of potential conflict, and areas without conflict, including areas where minimum depths for BMPs can not be met.  Delineate trees (size, species, condition) and tree protection.</t>
         </is>
       </c>
-      <c r="W8" s="25" t="inlineStr">
+      <c r="W8" s="35" t="inlineStr">
         <is>
           <t>For land conversion and BMP opportunities already defined at 30%, and for new opportunities added, provide the areas below.  Land Conversion and BMP surface areas within the LOD must be reflected in the SWRv computation; update those columns as necessary. Additional allowable BMPs such as impervious surface disconnection, swales, and infiltration should also be considered and described in the narrative. Describe the reason for eliminated Land Conversion/BMP locations.</t>
         </is>
       </c>
-      <c r="AC8" s="25" t="inlineStr">
+      <c r="AC8" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">Provide the contributing drainage area to the BMP locations. The ceiling stormwater runoff volume reaching the BMPs is calculated. </t>
         </is>
       </c>
-      <c r="AG8" s="25" t="inlineStr">
+      <c r="AG8" s="35" t="inlineStr">
         <is>
           <t>Calculate and sum the total maximum possible BMP storage volumes. Total the number of proposed trees meeting the required soil volume to be considered for stormwater retention volume.  Total the maximum retention volume capacity of all facilities and compare to the required regulated volume. If a deficit exists, review BMP placements/sizes to determine if additional volume can be captured.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="42.6" customHeight="1">
-      <c r="A9" s="26" t="inlineStr">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>Drainage Area
 ID</t>
         </is>
       </c>
-      <c r="B9" s="26" t="inlineStr">
+      <c r="B9" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">Drainage Area </t>
         </is>
       </c>
-      <c r="J9" s="26" t="inlineStr">
+      <c r="J9" s="36" t="inlineStr">
         <is>
           <t>SWRv</t>
         </is>
       </c>
-      <c r="L9" s="26" t="inlineStr">
+      <c r="L9" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve"> Hydrologic Soil Group</t>
         </is>
       </c>
-      <c r="M9" s="26" t="inlineStr">
+      <c r="M9" s="36" t="inlineStr">
         <is>
           <t>Water Table OK?</t>
         </is>
       </c>
-      <c r="N9" s="26" t="inlineStr">
+      <c r="N9" s="36" t="inlineStr">
         <is>
           <t>Bedrock Elevation OK?</t>
         </is>
       </c>
-      <c r="O9" s="26" t="inlineStr">
+      <c r="O9" s="36" t="inlineStr">
         <is>
           <t>Infiltration Rate</t>
         </is>
       </c>
-      <c r="P9" s="26" t="inlineStr">
+      <c r="P9" s="36" t="inlineStr">
         <is>
           <t>Hotspot Concern Found?</t>
         </is>
       </c>
-      <c r="Q9" s="26" t="inlineStr">
+      <c r="Q9" s="36" t="inlineStr">
         <is>
           <t>Preservation of Small, Large, and/or Special/Heritage Trees which are in fair or better condition</t>
         </is>
       </c>
-      <c r="W9" s="26" t="inlineStr">
+      <c r="W9" s="36" t="inlineStr">
         <is>
           <t>Land Conversion Area</t>
         </is>
       </c>
-      <c r="Y9" s="26" t="inlineStr">
+      <c r="Y9" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">Bioretention Opportunity Areas </t>
         </is>
       </c>
-      <c r="AA9" s="26" t="inlineStr">
+      <c r="AA9" s="36" t="inlineStr">
         <is>
           <t>Permeable Pavement Opportunity Areas</t>
         </is>
       </c>
-      <c r="AC9" s="26" t="inlineStr">
+      <c r="AC9" s="36" t="inlineStr">
         <is>
           <t>Total BMP Contributing Drainage Area</t>
         </is>
       </c>
-      <c r="AE9" s="26" t="inlineStr">
+      <c r="AE9" s="36" t="inlineStr">
         <is>
           <t>1.7 inch (ceiling) stormwater runoff reaching BMPs</t>
         </is>
       </c>
-      <c r="AG9" s="26" t="inlineStr">
+      <c r="AG9" s="36" t="inlineStr">
         <is>
           <t>Max. Storage Volume of Bioretention Based on Size (Total in DA - See separate sizing computations)</t>
         </is>
       </c>
-      <c r="AH9" s="26" t="inlineStr">
+      <c r="AH9" s="36" t="inlineStr">
         <is>
           <t>Max. Storage Volume of Permeable Pavement. Based on Size (Total in DA - See separate sizing computations)</t>
         </is>
       </c>
-      <c r="AI9" s="26" t="inlineStr">
+      <c r="AI9" s="36" t="inlineStr">
         <is>
           <t>Max. "Other" Storage Volume - (Total in DA - See separate sizing computations)</t>
         </is>
       </c>
-      <c r="AJ9" s="26" t="inlineStr">
+      <c r="AJ9" s="36" t="inlineStr">
         <is>
           <t>No. of proposed small trees meeting soil volume requirement</t>
         </is>
       </c>
-      <c r="AK9" s="26" t="inlineStr">
+      <c r="AK9" s="36" t="inlineStr">
         <is>
           <t>No. of proposed large trees meeting soil volume requirement</t>
         </is>
       </c>
-      <c r="AL9" s="26" t="inlineStr">
+      <c r="AL9" s="36" t="inlineStr">
         <is>
           <t>Total Sv Practice -Maximum Retention Volume Achievable (BMPs and Trees)</t>
         </is>
       </c>
-      <c r="AM9" s="26" t="inlineStr">
+      <c r="AM9" s="36" t="inlineStr">
         <is>
           <t>Overage / (Deficit) Volume (as compared to SWRv)</t>
         </is>
       </c>
-      <c r="AP9" s="26" t="inlineStr">
+      <c r="AP9" s="36" t="inlineStr">
         <is>
           <t>Runoff Coefficient</t>
         </is>
       </c>
     </row>
     <row r="10" ht="48.75" customHeight="1">
-      <c r="B10" s="26" t="inlineStr">
+      <c r="B10" s="36" t="inlineStr">
         <is>
           <t>Impervious 
 within LOD</t>
         </is>
       </c>
-      <c r="C10" s="26" t="inlineStr">
+      <c r="C10" s="36" t="inlineStr">
         <is>
           <t>Compacted    within LOD</t>
         </is>
       </c>
-      <c r="D10" s="26" t="inlineStr">
+      <c r="D10" s="36" t="inlineStr">
         <is>
           <t>Natural 
 within LOD</t>
         </is>
       </c>
-      <c r="E10" s="26" t="inlineStr">
+      <c r="E10" s="36" t="inlineStr">
         <is>
           <t>Total within LOD</t>
         </is>
       </c>
-      <c r="F10" s="26" t="inlineStr">
+      <c r="F10" s="36" t="inlineStr">
         <is>
           <t>Impervious outside LOD</t>
         </is>
       </c>
-      <c r="G10" s="26" t="inlineStr">
+      <c r="G10" s="36" t="inlineStr">
         <is>
           <t>Compacted outside LOD</t>
         </is>
       </c>
-      <c r="H10" s="26" t="inlineStr">
+      <c r="H10" s="36" t="inlineStr">
         <is>
           <t>Natural outside LOD</t>
         </is>
       </c>
-      <c r="I10" s="26" t="inlineStr">
+      <c r="I10" s="36" t="inlineStr">
         <is>
           <t>Total outside LOD</t>
         </is>
       </c>
-      <c r="J10" s="26" t="inlineStr">
+      <c r="J10" s="36" t="inlineStr">
         <is>
           <t>Within LOD</t>
         </is>
       </c>
-      <c r="K10" s="26" t="inlineStr">
+      <c r="K10" s="36" t="inlineStr">
         <is>
           <t>Outside LOD</t>
         </is>
       </c>
-      <c r="W10" s="26" t="inlineStr">
+      <c r="W10" s="36" t="inlineStr">
         <is>
           <t>Within LOD</t>
         </is>
       </c>
-      <c r="X10" s="26" t="inlineStr">
+      <c r="X10" s="36" t="inlineStr">
         <is>
           <t>Adjacent to LOD</t>
         </is>
       </c>
-      <c r="Y10" s="26" t="inlineStr">
+      <c r="Y10" s="36" t="inlineStr">
         <is>
           <t>Within LOD</t>
         </is>
       </c>
-      <c r="Z10" s="26" t="inlineStr">
+      <c r="Z10" s="36" t="inlineStr">
         <is>
           <t>Adjacent to LOD</t>
         </is>
       </c>
-      <c r="AA10" s="26" t="inlineStr">
+      <c r="AA10" s="36" t="inlineStr">
         <is>
           <t>Within LOD</t>
         </is>
       </c>
-      <c r="AB10" s="26" t="inlineStr">
+      <c r="AB10" s="36" t="inlineStr">
         <is>
           <t>Adjacent to LOD</t>
         </is>
       </c>
-      <c r="AC10" s="26" t="inlineStr">
+      <c r="AC10" s="36" t="inlineStr">
         <is>
           <t>Within LOD</t>
         </is>
       </c>
-      <c r="AD10" s="26" t="inlineStr">
+      <c r="AD10" s="36" t="inlineStr">
         <is>
           <t>Adjacent to LOD</t>
         </is>
       </c>
-      <c r="AE10" s="26" t="inlineStr">
+      <c r="AE10" s="36" t="inlineStr">
         <is>
           <t>Within LOD</t>
         </is>
       </c>
-      <c r="AF10" s="26" t="inlineStr">
+      <c r="AF10" s="36" t="inlineStr">
         <is>
           <t>Adjacent to LOD</t>
         </is>
       </c>
-      <c r="AP10" s="26" t="inlineStr">
+      <c r="AP10" s="36" t="inlineStr">
         <is>
           <t>Within LOD</t>
         </is>
       </c>
-      <c r="AQ10" s="26" t="inlineStr">
+      <c r="AQ10" s="36" t="inlineStr">
         <is>
           <t>Outside LOD</t>
         </is>
       </c>
     </row>
     <row r="11" ht="32.45" customHeight="1">
-      <c r="B11" s="26" t="inlineStr">
+      <c r="B11" s="36" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="C11" s="26" t="inlineStr">
+      <c r="C11" s="36" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="D11" s="26" t="inlineStr">
+      <c r="D11" s="36" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="E11" s="26" t="inlineStr">
+      <c r="E11" s="36" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="F11" s="26" t="inlineStr">
+      <c r="F11" s="36" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="G11" s="26" t="inlineStr">
+      <c r="G11" s="36" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="H11" s="26" t="inlineStr">
+      <c r="H11" s="36" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="I11" s="26" t="inlineStr">
+      <c r="I11" s="36" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="J11" s="26" t="inlineStr">
+      <c r="J11" s="36" t="inlineStr">
         <is>
           <t>CF</t>
         </is>
       </c>
-      <c r="K11" s="26" t="inlineStr">
+      <c r="K11" s="36" t="inlineStr">
         <is>
           <t>CF</t>
         </is>
       </c>
-      <c r="L11" s="26" t="inlineStr">
+      <c r="L11" s="36" t="inlineStr">
         <is>
           <t>A, B, C, D, or Urban Land</t>
         </is>
       </c>
-      <c r="M11" s="26" t="inlineStr">
+      <c r="M11" s="36" t="inlineStr">
         <is>
           <t>Y/N</t>
         </is>
       </c>
-      <c r="N11" s="26" t="inlineStr">
+      <c r="N11" s="36" t="inlineStr">
         <is>
           <t>Y/N</t>
         </is>
       </c>
-      <c r="O11" s="26" t="inlineStr">
+      <c r="O11" s="36" t="inlineStr">
         <is>
           <t>in-hr</t>
         </is>
       </c>
-      <c r="P11" s="26" t="inlineStr">
+      <c r="P11" s="36" t="inlineStr">
         <is>
           <t>Y/N</t>
         </is>
       </c>
-      <c r="Q11" s="26" t="inlineStr">
+      <c r="Q11" s="36" t="inlineStr">
         <is>
           <t># of Small Trees</t>
         </is>
       </c>
-      <c r="R11" s="26" t="inlineStr">
+      <c r="R11" s="36" t="inlineStr">
         <is>
           <t>Tree Volume Credit (CF)</t>
         </is>
       </c>
-      <c r="S11" s="26" t="inlineStr">
+      <c r="S11" s="36" t="inlineStr">
         <is>
           <t># of Large Trees</t>
         </is>
       </c>
-      <c r="T11" s="26" t="inlineStr">
+      <c r="T11" s="36" t="inlineStr">
         <is>
           <t>Tree Volume Credit (CF)</t>
         </is>
       </c>
-      <c r="U11" s="26" t="inlineStr">
+      <c r="U11" s="36" t="inlineStr">
         <is>
           <t># of Special/ Heritage Trees</t>
         </is>
       </c>
-      <c r="V11" s="26" t="inlineStr">
+      <c r="V11" s="36" t="inlineStr">
         <is>
           <t>Tree Volume Credit (CF)</t>
         </is>
       </c>
-      <c r="W11" s="26" t="inlineStr">
+      <c r="W11" s="36" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="X11" s="26" t="inlineStr">
+      <c r="X11" s="36" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="Y11" s="26" t="inlineStr">
+      <c r="Y11" s="36" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="Z11" s="26" t="inlineStr">
+      <c r="Z11" s="36" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="AA11" s="26" t="inlineStr">
+      <c r="AA11" s="36" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="AB11" s="26" t="inlineStr">
+      <c r="AB11" s="36" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="AC11" s="26" t="inlineStr">
+      <c r="AC11" s="36" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="AD11" s="26" t="inlineStr">
+      <c r="AD11" s="36" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="AE11" s="26" t="inlineStr">
+      <c r="AE11" s="36" t="inlineStr">
         <is>
           <t>CF</t>
         </is>
       </c>
-      <c r="AF11" s="26" t="inlineStr">
+      <c r="AF11" s="36" t="inlineStr">
         <is>
           <t>CF</t>
         </is>
       </c>
-      <c r="AG11" s="26" t="inlineStr">
+      <c r="AG11" s="36" t="inlineStr">
         <is>
           <t>CF</t>
         </is>
       </c>
-      <c r="AH11" s="26" t="inlineStr">
+      <c r="AH11" s="36" t="inlineStr">
         <is>
           <t>CF</t>
         </is>
       </c>
-      <c r="AI11" s="26" t="inlineStr">
+      <c r="AI11" s="36" t="inlineStr">
         <is>
           <t>CF</t>
         </is>
       </c>
-      <c r="AJ11" s="26" t="inlineStr">
+      <c r="AJ11" s="36" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="AK11" s="26" t="inlineStr">
+      <c r="AK11" s="36" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="AL11" s="26" t="inlineStr">
+      <c r="AL11" s="36" t="inlineStr">
         <is>
           <t>CF</t>
         </is>
       </c>
-      <c r="AM11" s="26" t="inlineStr">
+      <c r="AM11" s="36" t="inlineStr">
         <is>
           <t>CF</t>
         </is>
       </c>
-      <c r="AP11" s="26" t="inlineStr">
+      <c r="AP11" s="36" t="inlineStr">
         <is>
           <t>(unitless)</t>
         </is>
       </c>
-      <c r="AQ11" s="26" t="inlineStr">
+      <c r="AQ11" s="36" t="inlineStr">
         <is>
           <t>(unitless)</t>
         </is>
@@ -14818,4786 +14904,4786 @@
     </row>
     <row r="12" ht="16.25" customHeight="1">
       <c r="A12" s="16">
-        <f>IFERROR('SDA'!A58,"")</f>
+        <f>IF('SDA'!A58="","",'SDA'!A58)</f>
         <v/>
       </c>
       <c r="B12" s="16">
-        <f>IFERROR('SDA'!F58,0)</f>
+        <f>IF(A12="","",'SDA'!F58)</f>
         <v/>
       </c>
       <c r="C12" s="16">
-        <f>IFERROR('SDA'!G58,0)</f>
+        <f>IF(A12="","",'SDA'!G58)</f>
         <v/>
       </c>
       <c r="D12" s="16">
-        <f>IFERROR('SDA'!H58,0)</f>
+        <f>IF(A12="","",'SDA'!H58)</f>
         <v/>
       </c>
       <c r="E12" s="16">
-        <f>SUM(B12:D12)</f>
+        <f>IF(A12="","",SUM(B12:D12))</f>
         <v/>
       </c>
       <c r="F12" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A12,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A12,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <f>IF(A12="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A12,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A12,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"))</f>
         <v/>
       </c>
       <c r="G12" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A12,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <f>IF(A12="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A12,'SDA'!$C$4:$C$53,"Compacted (Open Space)"))</f>
         <v/>
       </c>
       <c r="H12" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A12,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <f>IF(A12="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A12,'SDA'!$C$4:$C$53,"Natural (Woods)"))</f>
         <v/>
       </c>
       <c r="I12" s="16">
-        <f>SUM(F12:H12)</f>
+        <f>IF(A12="","",SUM(F12:H12))</f>
         <v/>
       </c>
       <c r="J12" s="16">
-        <f>IF(E12=0,0,AP12*1.2/12*E12)</f>
+        <f>IF(A12="","",IF(E12=0,0,AP12*1.2/12*E12))</f>
         <v/>
       </c>
       <c r="K12" s="16">
-        <f>IF(I12=0,0,AQ12*1.2/12*I12)</f>
+        <f>IF(A12="","",IF(I12=0,0,AQ12*1.2/12*I12))</f>
         <v/>
       </c>
       <c r="L12" s="16">
-        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A12,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A12,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A12,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A12,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <f>IF(A12="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A12,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A12,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A12,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A12,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
         <v/>
       </c>
       <c r="M12" s="4" t="n"/>
       <c r="N12" s="4" t="n"/>
       <c r="O12" s="16">
-        <f>IFERROR(IFS(L12="A",2.5,L12="B",0.3,L12="C",0.1,L12="D",0.05,TRUE,""),"")</f>
+        <f>IF(A12="","",IFS(L12="A",2.5,L12="B",0.3,L12="C",0.1,L12="D",0.05,TRUE,""))</f>
         <v/>
       </c>
       <c r="P12" s="4" t="n"/>
       <c r="Q12" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A12),0)</f>
+        <f>IF(A12="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A12))</f>
         <v/>
       </c>
       <c r="R12" s="16">
-        <f>Q12*10</f>
+        <f>IF(A12="","",Q12*10)</f>
         <v/>
       </c>
       <c r="S12" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A12),0)</f>
+        <f>IF(A12="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A12))</f>
         <v/>
       </c>
       <c r="T12" s="16">
-        <f>S12*20</f>
+        <f>IF(A12="","",S12*20)</f>
         <v/>
       </c>
       <c r="U12" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A12)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A12),0)</f>
+        <f>IF(A12="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A12)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A12))</f>
         <v/>
       </c>
       <c r="V12" s="16">
-        <f>U12*40</f>
+        <f>IF(A12="","",U12*40)</f>
         <v/>
       </c>
       <c r="W12" s="4" t="n"/>
       <c r="X12" s="4" t="n"/>
       <c r="Y12" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A12,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A12,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A12="","",SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A12,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A12,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="Z12" s="4" t="n"/>
       <c r="AA12" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A12,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A12="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A12,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AB12" s="4" t="n"/>
       <c r="AC12" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A12),0)</f>
+        <f>IF(A12="","",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A12))</f>
         <v/>
       </c>
       <c r="AD12" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A12),0)</f>
+        <f>IF(A12="","",SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A12))</f>
         <v/>
       </c>
       <c r="AE12" s="16">
-        <f>IF(AC12=0,0,AC12*1.7/12*AP12)</f>
+        <f>IF(A12="","",IF(AC12=0,0,AC12*1.7/12*AP12))</f>
         <v/>
       </c>
       <c r="AF12" s="16">
-        <f>IF(AD12=0,0,AD12*1.7/12*AQ12)</f>
+        <f>IF(A12="","",IF(AD12=0,0,AD12*1.7/12*AQ12))</f>
         <v/>
       </c>
       <c r="AG12" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A12,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A12,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A12="","",SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A12,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A12,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="AH12" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A12,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A12="","",SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A12,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AI12" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A12,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <f>IF(A12="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A12,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
       <c r="AJ12" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A12),0)</f>
+        <f>IF(A12="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A12))</f>
         <v/>
       </c>
       <c r="AK12" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A12),0)</f>
+        <f>IF(A12="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A12))</f>
         <v/>
       </c>
       <c r="AL12" s="16">
-        <f>(IF((AE12)&lt;(AG12+AH12+AI12),(AE12),(AG12+AH12+AI12)))+AJ12*5+AK12*10+R12+T12+V12</f>
+        <f>IF(A12="","",(IF((AE12)&lt;(AG12+AH12+AI12),(AE12),(AG12+AH12+AI12)))+AJ12*5+AK12*10+R12+T12+V12)</f>
         <v/>
       </c>
       <c r="AM12" s="16">
-        <f>AL12-J12</f>
+        <f>IF(A12="","",AL12-J12)</f>
         <v/>
       </c>
       <c r="AP12" s="16">
-        <f>IF(E12=0,"",(B12*0.95+C12*0.25+D12*0)/E12)</f>
+        <f>IF(A12="","",IF(E12=0,"",(B12*0.95+C12*0.25+D12*0)/E12))</f>
         <v/>
       </c>
       <c r="AQ12" s="16">
-        <f>IF(I12=0,"",(F12*0.95+G12*0.25+H12*0)/I12)</f>
+        <f>IF(A12="","",IF(I12=0,"",(F12*0.95+G12*0.25+H12*0)/I12))</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="16.25" customHeight="1">
       <c r="A13" s="16">
-        <f>IFERROR('SDA'!A59,"")</f>
+        <f>IF('SDA'!A59="","",'SDA'!A59)</f>
         <v/>
       </c>
       <c r="B13" s="16">
-        <f>IFERROR('SDA'!F59,0)</f>
+        <f>IF(A13="","",'SDA'!F59)</f>
         <v/>
       </c>
       <c r="C13" s="16">
-        <f>IFERROR('SDA'!G59,0)</f>
+        <f>IF(A13="","",'SDA'!G59)</f>
         <v/>
       </c>
       <c r="D13" s="16">
-        <f>IFERROR('SDA'!H59,0)</f>
+        <f>IF(A13="","",'SDA'!H59)</f>
         <v/>
       </c>
       <c r="E13" s="16">
-        <f>SUM(B13:D13)</f>
+        <f>IF(A13="","",SUM(B13:D13))</f>
         <v/>
       </c>
       <c r="F13" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A13,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A13,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <f>IF(A13="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A13,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A13,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"))</f>
         <v/>
       </c>
       <c r="G13" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A13,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <f>IF(A13="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A13,'SDA'!$C$4:$C$53,"Compacted (Open Space)"))</f>
         <v/>
       </c>
       <c r="H13" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A13,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <f>IF(A13="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A13,'SDA'!$C$4:$C$53,"Natural (Woods)"))</f>
         <v/>
       </c>
       <c r="I13" s="16">
-        <f>SUM(F13:H13)</f>
+        <f>IF(A13="","",SUM(F13:H13))</f>
         <v/>
       </c>
       <c r="J13" s="16">
-        <f>IF(E13=0,0,AP13*1.2/12*E13)</f>
+        <f>IF(A13="","",IF(E13=0,0,AP13*1.2/12*E13))</f>
         <v/>
       </c>
       <c r="K13" s="16">
-        <f>IF(I13=0,0,AQ13*1.2/12*I13)</f>
+        <f>IF(A13="","",IF(I13=0,0,AQ13*1.2/12*I13))</f>
         <v/>
       </c>
       <c r="L13" s="16">
-        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A13,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A13,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A13,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A13,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <f>IF(A13="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A13,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A13,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A13,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A13,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
         <v/>
       </c>
       <c r="M13" s="4" t="n"/>
       <c r="N13" s="4" t="n"/>
       <c r="O13" s="16">
-        <f>IFERROR(IFS(L13="A",2.5,L13="B",0.3,L13="C",0.1,L13="D",0.05,TRUE,""),"")</f>
+        <f>IF(A13="","",IFS(L13="A",2.5,L13="B",0.3,L13="C",0.1,L13="D",0.05,TRUE,""))</f>
         <v/>
       </c>
       <c r="P13" s="4" t="n"/>
       <c r="Q13" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A13),0)</f>
+        <f>IF(A13="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A13))</f>
         <v/>
       </c>
       <c r="R13" s="16">
-        <f>Q13*10</f>
+        <f>IF(A13="","",Q13*10)</f>
         <v/>
       </c>
       <c r="S13" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A13),0)</f>
+        <f>IF(A13="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A13))</f>
         <v/>
       </c>
       <c r="T13" s="16">
-        <f>S13*20</f>
+        <f>IF(A13="","",S13*20)</f>
         <v/>
       </c>
       <c r="U13" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A13)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A13),0)</f>
+        <f>IF(A13="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A13)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A13))</f>
         <v/>
       </c>
       <c r="V13" s="16">
-        <f>U13*40</f>
+        <f>IF(A13="","",U13*40)</f>
         <v/>
       </c>
       <c r="W13" s="4" t="n"/>
       <c r="X13" s="4" t="n"/>
       <c r="Y13" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A13,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A13,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A13="","",SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A13,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A13,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="Z13" s="4" t="n"/>
       <c r="AA13" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A13,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A13="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A13,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AB13" s="4" t="n"/>
       <c r="AC13" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A13),0)</f>
+        <f>IF(A13="","",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A13))</f>
         <v/>
       </c>
       <c r="AD13" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A13),0)</f>
+        <f>IF(A13="","",SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A13))</f>
         <v/>
       </c>
       <c r="AE13" s="16">
-        <f>IF(AC13=0,0,AC13*1.7/12*AP13)</f>
+        <f>IF(A13="","",IF(AC13=0,0,AC13*1.7/12*AP13))</f>
         <v/>
       </c>
       <c r="AF13" s="16">
-        <f>IF(AD13=0,0,AD13*1.7/12*AQ13)</f>
+        <f>IF(A13="","",IF(AD13=0,0,AD13*1.7/12*AQ13))</f>
         <v/>
       </c>
       <c r="AG13" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A13,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A13,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A13="","",SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A13,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A13,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="AH13" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A13,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A13="","",SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A13,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AI13" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A13,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <f>IF(A13="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A13,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
       <c r="AJ13" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A13),0)</f>
+        <f>IF(A13="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A13))</f>
         <v/>
       </c>
       <c r="AK13" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A13),0)</f>
+        <f>IF(A13="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A13))</f>
         <v/>
       </c>
       <c r="AL13" s="16">
-        <f>(IF((AE13)&lt;(AG13+AH13+AI13),(AE13),(AG13+AH13+AI13)))+AJ13*5+AK13*10+R13+T13+V13</f>
+        <f>IF(A13="","",(IF((AE13)&lt;(AG13+AH13+AI13),(AE13),(AG13+AH13+AI13)))+AJ13*5+AK13*10+R13+T13+V13)</f>
         <v/>
       </c>
       <c r="AM13" s="16">
-        <f>AL13-J13</f>
+        <f>IF(A13="","",AL13-J13)</f>
         <v/>
       </c>
       <c r="AP13" s="16">
-        <f>IF(E13=0,"",(B13*0.95+C13*0.25+D13*0)/E13)</f>
+        <f>IF(A13="","",IF(E13=0,"",(B13*0.95+C13*0.25+D13*0)/E13))</f>
         <v/>
       </c>
       <c r="AQ13" s="16">
-        <f>IF(I13=0,"",(F13*0.95+G13*0.25+H13*0)/I13)</f>
+        <f>IF(A13="","",IF(I13=0,"",(F13*0.95+G13*0.25+H13*0)/I13))</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="16.25" customHeight="1">
       <c r="A14" s="16">
-        <f>IFERROR('SDA'!A60,"")</f>
+        <f>IF('SDA'!A60="","",'SDA'!A60)</f>
         <v/>
       </c>
       <c r="B14" s="16">
-        <f>IFERROR('SDA'!F60,0)</f>
+        <f>IF(A14="","",'SDA'!F60)</f>
         <v/>
       </c>
       <c r="C14" s="16">
-        <f>IFERROR('SDA'!G60,0)</f>
+        <f>IF(A14="","",'SDA'!G60)</f>
         <v/>
       </c>
       <c r="D14" s="16">
-        <f>IFERROR('SDA'!H60,0)</f>
+        <f>IF(A14="","",'SDA'!H60)</f>
         <v/>
       </c>
       <c r="E14" s="16">
-        <f>SUM(B14:D14)</f>
+        <f>IF(A14="","",SUM(B14:D14))</f>
         <v/>
       </c>
       <c r="F14" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A14,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A14,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <f>IF(A14="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A14,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A14,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"))</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A14,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <f>IF(A14="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A14,'SDA'!$C$4:$C$53,"Compacted (Open Space)"))</f>
         <v/>
       </c>
       <c r="H14" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A14,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <f>IF(A14="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A14,'SDA'!$C$4:$C$53,"Natural (Woods)"))</f>
         <v/>
       </c>
       <c r="I14" s="16">
-        <f>SUM(F14:H14)</f>
+        <f>IF(A14="","",SUM(F14:H14))</f>
         <v/>
       </c>
       <c r="J14" s="16">
-        <f>IF(E14=0,0,AP14*1.2/12*E14)</f>
+        <f>IF(A14="","",IF(E14=0,0,AP14*1.2/12*E14))</f>
         <v/>
       </c>
       <c r="K14" s="16">
-        <f>IF(I14=0,0,AQ14*1.2/12*I14)</f>
+        <f>IF(A14="","",IF(I14=0,0,AQ14*1.2/12*I14))</f>
         <v/>
       </c>
       <c r="L14" s="16">
-        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A14,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A14,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A14,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A14,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <f>IF(A14="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A14,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A14,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A14,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A14,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
         <v/>
       </c>
       <c r="M14" s="4" t="n"/>
       <c r="N14" s="4" t="n"/>
       <c r="O14" s="16">
-        <f>IFERROR(IFS(L14="A",2.5,L14="B",0.3,L14="C",0.1,L14="D",0.05,TRUE,""),"")</f>
+        <f>IF(A14="","",IFS(L14="A",2.5,L14="B",0.3,L14="C",0.1,L14="D",0.05,TRUE,""))</f>
         <v/>
       </c>
       <c r="P14" s="4" t="n"/>
       <c r="Q14" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A14),0)</f>
+        <f>IF(A14="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A14))</f>
         <v/>
       </c>
       <c r="R14" s="16">
-        <f>Q14*10</f>
+        <f>IF(A14="","",Q14*10)</f>
         <v/>
       </c>
       <c r="S14" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A14),0)</f>
+        <f>IF(A14="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A14))</f>
         <v/>
       </c>
       <c r="T14" s="16">
-        <f>S14*20</f>
+        <f>IF(A14="","",S14*20)</f>
         <v/>
       </c>
       <c r="U14" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A14)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A14),0)</f>
+        <f>IF(A14="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A14)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A14))</f>
         <v/>
       </c>
       <c r="V14" s="16">
-        <f>U14*40</f>
+        <f>IF(A14="","",U14*40)</f>
         <v/>
       </c>
       <c r="W14" s="4" t="n"/>
       <c r="X14" s="4" t="n"/>
       <c r="Y14" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A14,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A14,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A14="","",SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A14,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A14,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="Z14" s="4" t="n"/>
       <c r="AA14" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A14,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A14="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A14,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AB14" s="4" t="n"/>
       <c r="AC14" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A14),0)</f>
+        <f>IF(A14="","",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A14))</f>
         <v/>
       </c>
       <c r="AD14" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A14),0)</f>
+        <f>IF(A14="","",SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A14))</f>
         <v/>
       </c>
       <c r="AE14" s="16">
-        <f>IF(AC14=0,0,AC14*1.7/12*AP14)</f>
+        <f>IF(A14="","",IF(AC14=0,0,AC14*1.7/12*AP14))</f>
         <v/>
       </c>
       <c r="AF14" s="16">
-        <f>IF(AD14=0,0,AD14*1.7/12*AQ14)</f>
+        <f>IF(A14="","",IF(AD14=0,0,AD14*1.7/12*AQ14))</f>
         <v/>
       </c>
       <c r="AG14" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A14,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A14,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A14="","",SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A14,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A14,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="AH14" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A14,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A14="","",SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A14,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AI14" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A14,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <f>IF(A14="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A14,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
       <c r="AJ14" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A14),0)</f>
+        <f>IF(A14="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A14))</f>
         <v/>
       </c>
       <c r="AK14" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A14),0)</f>
+        <f>IF(A14="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A14))</f>
         <v/>
       </c>
       <c r="AL14" s="16">
-        <f>(IF((AE14)&lt;(AG14+AH14+AI14),(AE14),(AG14+AH14+AI14)))+AJ14*5+AK14*10+R14+T14+V14</f>
+        <f>IF(A14="","",(IF((AE14)&lt;(AG14+AH14+AI14),(AE14),(AG14+AH14+AI14)))+AJ14*5+AK14*10+R14+T14+V14)</f>
         <v/>
       </c>
       <c r="AM14" s="16">
-        <f>AL14-J14</f>
+        <f>IF(A14="","",AL14-J14)</f>
         <v/>
       </c>
       <c r="AP14" s="16">
-        <f>IF(E14=0,"",(B14*0.95+C14*0.25+D14*0)/E14)</f>
+        <f>IF(A14="","",IF(E14=0,"",(B14*0.95+C14*0.25+D14*0)/E14))</f>
         <v/>
       </c>
       <c r="AQ14" s="16">
-        <f>IF(I14=0,"",(F14*0.95+G14*0.25+H14*0)/I14)</f>
+        <f>IF(A14="","",IF(I14=0,"",(F14*0.95+G14*0.25+H14*0)/I14))</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="16.25" customHeight="1">
       <c r="A15" s="16">
-        <f>IFERROR('SDA'!A61,"")</f>
+        <f>IF('SDA'!A61="","",'SDA'!A61)</f>
         <v/>
       </c>
       <c r="B15" s="16">
-        <f>IFERROR('SDA'!F61,0)</f>
+        <f>IF(A15="","",'SDA'!F61)</f>
         <v/>
       </c>
       <c r="C15" s="16">
-        <f>IFERROR('SDA'!G61,0)</f>
+        <f>IF(A15="","",'SDA'!G61)</f>
         <v/>
       </c>
       <c r="D15" s="16">
-        <f>IFERROR('SDA'!H61,0)</f>
+        <f>IF(A15="","",'SDA'!H61)</f>
         <v/>
       </c>
       <c r="E15" s="16">
-        <f>SUM(B15:D15)</f>
+        <f>IF(A15="","",SUM(B15:D15))</f>
         <v/>
       </c>
       <c r="F15" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A15,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A15,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <f>IF(A15="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A15,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A15,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"))</f>
         <v/>
       </c>
       <c r="G15" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A15,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <f>IF(A15="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A15,'SDA'!$C$4:$C$53,"Compacted (Open Space)"))</f>
         <v/>
       </c>
       <c r="H15" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A15,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <f>IF(A15="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A15,'SDA'!$C$4:$C$53,"Natural (Woods)"))</f>
         <v/>
       </c>
       <c r="I15" s="16">
-        <f>SUM(F15:H15)</f>
+        <f>IF(A15="","",SUM(F15:H15))</f>
         <v/>
       </c>
       <c r="J15" s="16">
-        <f>IF(E15=0,0,AP15*1.2/12*E15)</f>
+        <f>IF(A15="","",IF(E15=0,0,AP15*1.2/12*E15))</f>
         <v/>
       </c>
       <c r="K15" s="16">
-        <f>IF(I15=0,0,AQ15*1.2/12*I15)</f>
+        <f>IF(A15="","",IF(I15=0,0,AQ15*1.2/12*I15))</f>
         <v/>
       </c>
       <c r="L15" s="16">
-        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A15,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A15,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A15,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A15,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <f>IF(A15="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A15,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A15,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A15,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A15,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
         <v/>
       </c>
       <c r="M15" s="4" t="n"/>
       <c r="N15" s="4" t="n"/>
       <c r="O15" s="16">
-        <f>IFERROR(IFS(L15="A",2.5,L15="B",0.3,L15="C",0.1,L15="D",0.05,TRUE,""),"")</f>
+        <f>IF(A15="","",IFS(L15="A",2.5,L15="B",0.3,L15="C",0.1,L15="D",0.05,TRUE,""))</f>
         <v/>
       </c>
       <c r="P15" s="4" t="n"/>
       <c r="Q15" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A15),0)</f>
+        <f>IF(A15="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A15))</f>
         <v/>
       </c>
       <c r="R15" s="16">
-        <f>Q15*10</f>
+        <f>IF(A15="","",Q15*10)</f>
         <v/>
       </c>
       <c r="S15" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A15),0)</f>
+        <f>IF(A15="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A15))</f>
         <v/>
       </c>
       <c r="T15" s="16">
-        <f>S15*20</f>
+        <f>IF(A15="","",S15*20)</f>
         <v/>
       </c>
       <c r="U15" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A15)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A15),0)</f>
+        <f>IF(A15="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A15)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A15))</f>
         <v/>
       </c>
       <c r="V15" s="16">
-        <f>U15*40</f>
+        <f>IF(A15="","",U15*40)</f>
         <v/>
       </c>
       <c r="W15" s="4" t="n"/>
       <c r="X15" s="4" t="n"/>
       <c r="Y15" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A15,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A15,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A15="","",SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A15,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A15,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="Z15" s="4" t="n"/>
       <c r="AA15" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A15,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A15="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A15,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AB15" s="4" t="n"/>
       <c r="AC15" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A15),0)</f>
+        <f>IF(A15="","",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A15))</f>
         <v/>
       </c>
       <c r="AD15" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A15),0)</f>
+        <f>IF(A15="","",SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A15))</f>
         <v/>
       </c>
       <c r="AE15" s="16">
-        <f>IF(AC15=0,0,AC15*1.7/12*AP15)</f>
+        <f>IF(A15="","",IF(AC15=0,0,AC15*1.7/12*AP15))</f>
         <v/>
       </c>
       <c r="AF15" s="16">
-        <f>IF(AD15=0,0,AD15*1.7/12*AQ15)</f>
+        <f>IF(A15="","",IF(AD15=0,0,AD15*1.7/12*AQ15))</f>
         <v/>
       </c>
       <c r="AG15" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A15,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A15,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A15="","",SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A15,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A15,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="AH15" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A15,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A15="","",SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A15,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AI15" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A15,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <f>IF(A15="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A15,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
       <c r="AJ15" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A15),0)</f>
+        <f>IF(A15="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A15))</f>
         <v/>
       </c>
       <c r="AK15" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A15),0)</f>
+        <f>IF(A15="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A15))</f>
         <v/>
       </c>
       <c r="AL15" s="16">
-        <f>(IF((AE15)&lt;(AG15+AH15+AI15),(AE15),(AG15+AH15+AI15)))+AJ15*5+AK15*10+R15+T15+V15</f>
+        <f>IF(A15="","",(IF((AE15)&lt;(AG15+AH15+AI15),(AE15),(AG15+AH15+AI15)))+AJ15*5+AK15*10+R15+T15+V15)</f>
         <v/>
       </c>
       <c r="AM15" s="16">
-        <f>AL15-J15</f>
+        <f>IF(A15="","",AL15-J15)</f>
         <v/>
       </c>
       <c r="AP15" s="16">
-        <f>IF(E15=0,"",(B15*0.95+C15*0.25+D15*0)/E15)</f>
+        <f>IF(A15="","",IF(E15=0,"",(B15*0.95+C15*0.25+D15*0)/E15))</f>
         <v/>
       </c>
       <c r="AQ15" s="16">
-        <f>IF(I15=0,"",(F15*0.95+G15*0.25+H15*0)/I15)</f>
+        <f>IF(A15="","",IF(I15=0,"",(F15*0.95+G15*0.25+H15*0)/I15))</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="16.25" customHeight="1">
       <c r="A16" s="16">
-        <f>IFERROR('SDA'!A62,"")</f>
+        <f>IF('SDA'!A62="","",'SDA'!A62)</f>
         <v/>
       </c>
       <c r="B16" s="16">
-        <f>IFERROR('SDA'!F62,0)</f>
+        <f>IF(A16="","",'SDA'!F62)</f>
         <v/>
       </c>
       <c r="C16" s="16">
-        <f>IFERROR('SDA'!G62,0)</f>
+        <f>IF(A16="","",'SDA'!G62)</f>
         <v/>
       </c>
       <c r="D16" s="16">
-        <f>IFERROR('SDA'!H62,0)</f>
+        <f>IF(A16="","",'SDA'!H62)</f>
         <v/>
       </c>
       <c r="E16" s="16">
-        <f>SUM(B16:D16)</f>
+        <f>IF(A16="","",SUM(B16:D16))</f>
         <v/>
       </c>
       <c r="F16" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A16,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A16,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <f>IF(A16="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A16,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A16,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"))</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A16,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <f>IF(A16="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A16,'SDA'!$C$4:$C$53,"Compacted (Open Space)"))</f>
         <v/>
       </c>
       <c r="H16" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A16,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <f>IF(A16="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A16,'SDA'!$C$4:$C$53,"Natural (Woods)"))</f>
         <v/>
       </c>
       <c r="I16" s="16">
-        <f>SUM(F16:H16)</f>
+        <f>IF(A16="","",SUM(F16:H16))</f>
         <v/>
       </c>
       <c r="J16" s="16">
-        <f>IF(E16=0,0,AP16*1.2/12*E16)</f>
+        <f>IF(A16="","",IF(E16=0,0,AP16*1.2/12*E16))</f>
         <v/>
       </c>
       <c r="K16" s="16">
-        <f>IF(I16=0,0,AQ16*1.2/12*I16)</f>
+        <f>IF(A16="","",IF(I16=0,0,AQ16*1.2/12*I16))</f>
         <v/>
       </c>
       <c r="L16" s="16">
-        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A16,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A16,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A16,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A16,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <f>IF(A16="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A16,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A16,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A16,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A16,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
         <v/>
       </c>
       <c r="M16" s="4" t="n"/>
       <c r="N16" s="4" t="n"/>
       <c r="O16" s="16">
-        <f>IFERROR(IFS(L16="A",2.5,L16="B",0.3,L16="C",0.1,L16="D",0.05,TRUE,""),"")</f>
+        <f>IF(A16="","",IFS(L16="A",2.5,L16="B",0.3,L16="C",0.1,L16="D",0.05,TRUE,""))</f>
         <v/>
       </c>
       <c r="P16" s="4" t="n"/>
       <c r="Q16" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A16),0)</f>
+        <f>IF(A16="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A16))</f>
         <v/>
       </c>
       <c r="R16" s="16">
-        <f>Q16*10</f>
+        <f>IF(A16="","",Q16*10)</f>
         <v/>
       </c>
       <c r="S16" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A16),0)</f>
+        <f>IF(A16="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A16))</f>
         <v/>
       </c>
       <c r="T16" s="16">
-        <f>S16*20</f>
+        <f>IF(A16="","",S16*20)</f>
         <v/>
       </c>
       <c r="U16" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A16)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A16),0)</f>
+        <f>IF(A16="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A16)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A16))</f>
         <v/>
       </c>
       <c r="V16" s="16">
-        <f>U16*40</f>
+        <f>IF(A16="","",U16*40)</f>
         <v/>
       </c>
       <c r="W16" s="4" t="n"/>
       <c r="X16" s="4" t="n"/>
       <c r="Y16" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A16,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A16,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A16="","",SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A16,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A16,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="Z16" s="4" t="n"/>
       <c r="AA16" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A16,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A16="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A16,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AB16" s="4" t="n"/>
       <c r="AC16" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A16),0)</f>
+        <f>IF(A16="","",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A16))</f>
         <v/>
       </c>
       <c r="AD16" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A16),0)</f>
+        <f>IF(A16="","",SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A16))</f>
         <v/>
       </c>
       <c r="AE16" s="16">
-        <f>IF(AC16=0,0,AC16*1.7/12*AP16)</f>
+        <f>IF(A16="","",IF(AC16=0,0,AC16*1.7/12*AP16))</f>
         <v/>
       </c>
       <c r="AF16" s="16">
-        <f>IF(AD16=0,0,AD16*1.7/12*AQ16)</f>
+        <f>IF(A16="","",IF(AD16=0,0,AD16*1.7/12*AQ16))</f>
         <v/>
       </c>
       <c r="AG16" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A16,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A16,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A16="","",SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A16,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A16,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="AH16" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A16,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A16="","",SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A16,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AI16" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A16,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <f>IF(A16="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A16,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
       <c r="AJ16" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A16),0)</f>
+        <f>IF(A16="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A16))</f>
         <v/>
       </c>
       <c r="AK16" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A16),0)</f>
+        <f>IF(A16="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A16))</f>
         <v/>
       </c>
       <c r="AL16" s="16">
-        <f>(IF((AE16)&lt;(AG16+AH16+AI16),(AE16),(AG16+AH16+AI16)))+AJ16*5+AK16*10+R16+T16+V16</f>
+        <f>IF(A16="","",(IF((AE16)&lt;(AG16+AH16+AI16),(AE16),(AG16+AH16+AI16)))+AJ16*5+AK16*10+R16+T16+V16)</f>
         <v/>
       </c>
       <c r="AM16" s="16">
-        <f>AL16-J16</f>
+        <f>IF(A16="","",AL16-J16)</f>
         <v/>
       </c>
       <c r="AP16" s="16">
-        <f>IF(E16=0,"",(B16*0.95+C16*0.25+D16*0)/E16)</f>
+        <f>IF(A16="","",IF(E16=0,"",(B16*0.95+C16*0.25+D16*0)/E16))</f>
         <v/>
       </c>
       <c r="AQ16" s="16">
-        <f>IF(I16=0,"",(F16*0.95+G16*0.25+H16*0)/I16)</f>
+        <f>IF(A16="","",IF(I16=0,"",(F16*0.95+G16*0.25+H16*0)/I16))</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="16.25" customHeight="1">
       <c r="A17" s="16">
-        <f>IFERROR('SDA'!A63,"")</f>
+        <f>IF('SDA'!A63="","",'SDA'!A63)</f>
         <v/>
       </c>
       <c r="B17" s="16">
-        <f>IFERROR('SDA'!F63,0)</f>
+        <f>IF(A17="","",'SDA'!F63)</f>
         <v/>
       </c>
       <c r="C17" s="16">
-        <f>IFERROR('SDA'!G63,0)</f>
+        <f>IF(A17="","",'SDA'!G63)</f>
         <v/>
       </c>
       <c r="D17" s="16">
-        <f>IFERROR('SDA'!H63,0)</f>
+        <f>IF(A17="","",'SDA'!H63)</f>
         <v/>
       </c>
       <c r="E17" s="16">
-        <f>SUM(B17:D17)</f>
+        <f>IF(A17="","",SUM(B17:D17))</f>
         <v/>
       </c>
       <c r="F17" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A17,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A17,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <f>IF(A17="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A17,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A17,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"))</f>
         <v/>
       </c>
       <c r="G17" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A17,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <f>IF(A17="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A17,'SDA'!$C$4:$C$53,"Compacted (Open Space)"))</f>
         <v/>
       </c>
       <c r="H17" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A17,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <f>IF(A17="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A17,'SDA'!$C$4:$C$53,"Natural (Woods)"))</f>
         <v/>
       </c>
       <c r="I17" s="16">
-        <f>SUM(F17:H17)</f>
+        <f>IF(A17="","",SUM(F17:H17))</f>
         <v/>
       </c>
       <c r="J17" s="16">
-        <f>IF(E17=0,0,AP17*1.2/12*E17)</f>
+        <f>IF(A17="","",IF(E17=0,0,AP17*1.2/12*E17))</f>
         <v/>
       </c>
       <c r="K17" s="16">
-        <f>IF(I17=0,0,AQ17*1.2/12*I17)</f>
+        <f>IF(A17="","",IF(I17=0,0,AQ17*1.2/12*I17))</f>
         <v/>
       </c>
       <c r="L17" s="16">
-        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A17,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A17,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A17,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A17,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <f>IF(A17="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A17,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A17,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A17,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A17,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
         <v/>
       </c>
       <c r="M17" s="4" t="n"/>
       <c r="N17" s="4" t="n"/>
       <c r="O17" s="16">
-        <f>IFERROR(IFS(L17="A",2.5,L17="B",0.3,L17="C",0.1,L17="D",0.05,TRUE,""),"")</f>
+        <f>IF(A17="","",IFS(L17="A",2.5,L17="B",0.3,L17="C",0.1,L17="D",0.05,TRUE,""))</f>
         <v/>
       </c>
       <c r="P17" s="4" t="n"/>
       <c r="Q17" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A17),0)</f>
+        <f>IF(A17="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A17))</f>
         <v/>
       </c>
       <c r="R17" s="16">
-        <f>Q17*10</f>
+        <f>IF(A17="","",Q17*10)</f>
         <v/>
       </c>
       <c r="S17" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A17),0)</f>
+        <f>IF(A17="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A17))</f>
         <v/>
       </c>
       <c r="T17" s="16">
-        <f>S17*20</f>
+        <f>IF(A17="","",S17*20)</f>
         <v/>
       </c>
       <c r="U17" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A17)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A17),0)</f>
+        <f>IF(A17="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A17)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A17))</f>
         <v/>
       </c>
       <c r="V17" s="16">
-        <f>U17*40</f>
+        <f>IF(A17="","",U17*40)</f>
         <v/>
       </c>
       <c r="W17" s="4" t="n"/>
       <c r="X17" s="4" t="n"/>
       <c r="Y17" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A17,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A17,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A17="","",SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A17,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A17,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="Z17" s="4" t="n"/>
       <c r="AA17" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A17,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A17="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A17,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AB17" s="4" t="n"/>
       <c r="AC17" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A17),0)</f>
+        <f>IF(A17="","",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A17))</f>
         <v/>
       </c>
       <c r="AD17" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A17),0)</f>
+        <f>IF(A17="","",SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A17))</f>
         <v/>
       </c>
       <c r="AE17" s="16">
-        <f>IF(AC17=0,0,AC17*1.7/12*AP17)</f>
+        <f>IF(A17="","",IF(AC17=0,0,AC17*1.7/12*AP17))</f>
         <v/>
       </c>
       <c r="AF17" s="16">
-        <f>IF(AD17=0,0,AD17*1.7/12*AQ17)</f>
+        <f>IF(A17="","",IF(AD17=0,0,AD17*1.7/12*AQ17))</f>
         <v/>
       </c>
       <c r="AG17" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A17,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A17,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A17="","",SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A17,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A17,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="AH17" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A17,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A17="","",SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A17,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AI17" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A17,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <f>IF(A17="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A17,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
       <c r="AJ17" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A17),0)</f>
+        <f>IF(A17="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A17))</f>
         <v/>
       </c>
       <c r="AK17" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A17),0)</f>
+        <f>IF(A17="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A17))</f>
         <v/>
       </c>
       <c r="AL17" s="16">
-        <f>(IF((AE17)&lt;(AG17+AH17+AI17),(AE17),(AG17+AH17+AI17)))+AJ17*5+AK17*10+R17+T17+V17</f>
+        <f>IF(A17="","",(IF((AE17)&lt;(AG17+AH17+AI17),(AE17),(AG17+AH17+AI17)))+AJ17*5+AK17*10+R17+T17+V17)</f>
         <v/>
       </c>
       <c r="AM17" s="16">
-        <f>AL17-J17</f>
+        <f>IF(A17="","",AL17-J17)</f>
         <v/>
       </c>
       <c r="AP17" s="16">
-        <f>IF(E17=0,"",(B17*0.95+C17*0.25+D17*0)/E17)</f>
+        <f>IF(A17="","",IF(E17=0,"",(B17*0.95+C17*0.25+D17*0)/E17))</f>
         <v/>
       </c>
       <c r="AQ17" s="16">
-        <f>IF(I17=0,"",(F17*0.95+G17*0.25+H17*0)/I17)</f>
+        <f>IF(A17="","",IF(I17=0,"",(F17*0.95+G17*0.25+H17*0)/I17))</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="16.25" customHeight="1">
       <c r="A18" s="16">
-        <f>IFERROR('SDA'!A64,"")</f>
+        <f>IF('SDA'!A64="","",'SDA'!A64)</f>
         <v/>
       </c>
       <c r="B18" s="16">
-        <f>IFERROR('SDA'!F64,0)</f>
+        <f>IF(A18="","",'SDA'!F64)</f>
         <v/>
       </c>
       <c r="C18" s="16">
-        <f>IFERROR('SDA'!G64,0)</f>
+        <f>IF(A18="","",'SDA'!G64)</f>
         <v/>
       </c>
       <c r="D18" s="16">
-        <f>IFERROR('SDA'!H64,0)</f>
+        <f>IF(A18="","",'SDA'!H64)</f>
         <v/>
       </c>
       <c r="E18" s="16">
-        <f>SUM(B18:D18)</f>
+        <f>IF(A18="","",SUM(B18:D18))</f>
         <v/>
       </c>
       <c r="F18" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A18,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A18,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <f>IF(A18="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A18,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A18,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"))</f>
         <v/>
       </c>
       <c r="G18" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A18,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <f>IF(A18="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A18,'SDA'!$C$4:$C$53,"Compacted (Open Space)"))</f>
         <v/>
       </c>
       <c r="H18" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A18,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <f>IF(A18="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A18,'SDA'!$C$4:$C$53,"Natural (Woods)"))</f>
         <v/>
       </c>
       <c r="I18" s="16">
-        <f>SUM(F18:H18)</f>
+        <f>IF(A18="","",SUM(F18:H18))</f>
         <v/>
       </c>
       <c r="J18" s="16">
-        <f>IF(E18=0,0,AP18*1.2/12*E18)</f>
+        <f>IF(A18="","",IF(E18=0,0,AP18*1.2/12*E18))</f>
         <v/>
       </c>
       <c r="K18" s="16">
-        <f>IF(I18=0,0,AQ18*1.2/12*I18)</f>
+        <f>IF(A18="","",IF(I18=0,0,AQ18*1.2/12*I18))</f>
         <v/>
       </c>
       <c r="L18" s="16">
-        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A18,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A18,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A18,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A18,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <f>IF(A18="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A18,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A18,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A18,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A18,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
         <v/>
       </c>
       <c r="M18" s="4" t="n"/>
       <c r="N18" s="4" t="n"/>
       <c r="O18" s="16">
-        <f>IFERROR(IFS(L18="A",2.5,L18="B",0.3,L18="C",0.1,L18="D",0.05,TRUE,""),"")</f>
+        <f>IF(A18="","",IFS(L18="A",2.5,L18="B",0.3,L18="C",0.1,L18="D",0.05,TRUE,""))</f>
         <v/>
       </c>
       <c r="P18" s="4" t="n"/>
       <c r="Q18" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A18),0)</f>
+        <f>IF(A18="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A18))</f>
         <v/>
       </c>
       <c r="R18" s="16">
-        <f>Q18*10</f>
+        <f>IF(A18="","",Q18*10)</f>
         <v/>
       </c>
       <c r="S18" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A18),0)</f>
+        <f>IF(A18="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A18))</f>
         <v/>
       </c>
       <c r="T18" s="16">
-        <f>S18*20</f>
+        <f>IF(A18="","",S18*20)</f>
         <v/>
       </c>
       <c r="U18" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A18)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A18),0)</f>
+        <f>IF(A18="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A18)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A18))</f>
         <v/>
       </c>
       <c r="V18" s="16">
-        <f>U18*40</f>
+        <f>IF(A18="","",U18*40)</f>
         <v/>
       </c>
       <c r="W18" s="4" t="n"/>
       <c r="X18" s="4" t="n"/>
       <c r="Y18" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A18,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A18,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A18="","",SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A18,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A18,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="Z18" s="4" t="n"/>
       <c r="AA18" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A18,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A18="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A18,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AB18" s="4" t="n"/>
       <c r="AC18" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A18),0)</f>
+        <f>IF(A18="","",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A18))</f>
         <v/>
       </c>
       <c r="AD18" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A18),0)</f>
+        <f>IF(A18="","",SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A18))</f>
         <v/>
       </c>
       <c r="AE18" s="16">
-        <f>IF(AC18=0,0,AC18*1.7/12*AP18)</f>
+        <f>IF(A18="","",IF(AC18=0,0,AC18*1.7/12*AP18))</f>
         <v/>
       </c>
       <c r="AF18" s="16">
-        <f>IF(AD18=0,0,AD18*1.7/12*AQ18)</f>
+        <f>IF(A18="","",IF(AD18=0,0,AD18*1.7/12*AQ18))</f>
         <v/>
       </c>
       <c r="AG18" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A18,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A18,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A18="","",SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A18,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A18,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="AH18" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A18,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A18="","",SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A18,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AI18" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A18,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <f>IF(A18="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A18,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
       <c r="AJ18" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A18),0)</f>
+        <f>IF(A18="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A18))</f>
         <v/>
       </c>
       <c r="AK18" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A18),0)</f>
+        <f>IF(A18="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A18))</f>
         <v/>
       </c>
       <c r="AL18" s="16">
-        <f>(IF((AE18)&lt;(AG18+AH18+AI18),(AE18),(AG18+AH18+AI18)))+AJ18*5+AK18*10+R18+T18+V18</f>
+        <f>IF(A18="","",(IF((AE18)&lt;(AG18+AH18+AI18),(AE18),(AG18+AH18+AI18)))+AJ18*5+AK18*10+R18+T18+V18)</f>
         <v/>
       </c>
       <c r="AM18" s="16">
-        <f>AL18-J18</f>
+        <f>IF(A18="","",AL18-J18)</f>
         <v/>
       </c>
       <c r="AP18" s="16">
-        <f>IF(E18=0,"",(B18*0.95+C18*0.25+D18*0)/E18)</f>
+        <f>IF(A18="","",IF(E18=0,"",(B18*0.95+C18*0.25+D18*0)/E18))</f>
         <v/>
       </c>
       <c r="AQ18" s="16">
-        <f>IF(I18=0,"",(F18*0.95+G18*0.25+H18*0)/I18)</f>
+        <f>IF(A18="","",IF(I18=0,"",(F18*0.95+G18*0.25+H18*0)/I18))</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="16.25" customHeight="1">
       <c r="A19" s="16">
-        <f>IFERROR('SDA'!A65,"")</f>
+        <f>IF('SDA'!A65="","",'SDA'!A65)</f>
         <v/>
       </c>
       <c r="B19" s="16">
-        <f>IFERROR('SDA'!F65,0)</f>
+        <f>IF(A19="","",'SDA'!F65)</f>
         <v/>
       </c>
       <c r="C19" s="16">
-        <f>IFERROR('SDA'!G65,0)</f>
+        <f>IF(A19="","",'SDA'!G65)</f>
         <v/>
       </c>
       <c r="D19" s="16">
-        <f>IFERROR('SDA'!H65,0)</f>
+        <f>IF(A19="","",'SDA'!H65)</f>
         <v/>
       </c>
       <c r="E19" s="16">
-        <f>SUM(B19:D19)</f>
+        <f>IF(A19="","",SUM(B19:D19))</f>
         <v/>
       </c>
       <c r="F19" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A19,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A19,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <f>IF(A19="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A19,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A19,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"))</f>
         <v/>
       </c>
       <c r="G19" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A19,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <f>IF(A19="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A19,'SDA'!$C$4:$C$53,"Compacted (Open Space)"))</f>
         <v/>
       </c>
       <c r="H19" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A19,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <f>IF(A19="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A19,'SDA'!$C$4:$C$53,"Natural (Woods)"))</f>
         <v/>
       </c>
       <c r="I19" s="16">
-        <f>SUM(F19:H19)</f>
+        <f>IF(A19="","",SUM(F19:H19))</f>
         <v/>
       </c>
       <c r="J19" s="16">
-        <f>IF(E19=0,0,AP19*1.2/12*E19)</f>
+        <f>IF(A19="","",IF(E19=0,0,AP19*1.2/12*E19))</f>
         <v/>
       </c>
       <c r="K19" s="16">
-        <f>IF(I19=0,0,AQ19*1.2/12*I19)</f>
+        <f>IF(A19="","",IF(I19=0,0,AQ19*1.2/12*I19))</f>
         <v/>
       </c>
       <c r="L19" s="16">
-        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A19,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A19,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A19,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A19,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <f>IF(A19="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A19,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A19,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A19,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A19,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
         <v/>
       </c>
       <c r="M19" s="4" t="n"/>
       <c r="N19" s="4" t="n"/>
       <c r="O19" s="16">
-        <f>IFERROR(IFS(L19="A",2.5,L19="B",0.3,L19="C",0.1,L19="D",0.05,TRUE,""),"")</f>
+        <f>IF(A19="","",IFS(L19="A",2.5,L19="B",0.3,L19="C",0.1,L19="D",0.05,TRUE,""))</f>
         <v/>
       </c>
       <c r="P19" s="4" t="n"/>
       <c r="Q19" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A19),0)</f>
+        <f>IF(A19="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A19))</f>
         <v/>
       </c>
       <c r="R19" s="16">
-        <f>Q19*10</f>
+        <f>IF(A19="","",Q19*10)</f>
         <v/>
       </c>
       <c r="S19" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A19),0)</f>
+        <f>IF(A19="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A19))</f>
         <v/>
       </c>
       <c r="T19" s="16">
-        <f>S19*20</f>
+        <f>IF(A19="","",S19*20)</f>
         <v/>
       </c>
       <c r="U19" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A19)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A19),0)</f>
+        <f>IF(A19="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A19)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A19))</f>
         <v/>
       </c>
       <c r="V19" s="16">
-        <f>U19*40</f>
+        <f>IF(A19="","",U19*40)</f>
         <v/>
       </c>
       <c r="W19" s="4" t="n"/>
       <c r="X19" s="4" t="n"/>
       <c r="Y19" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A19,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A19,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A19="","",SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A19,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A19,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="Z19" s="4" t="n"/>
       <c r="AA19" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A19,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A19="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A19,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AB19" s="4" t="n"/>
       <c r="AC19" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A19),0)</f>
+        <f>IF(A19="","",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A19))</f>
         <v/>
       </c>
       <c r="AD19" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A19),0)</f>
+        <f>IF(A19="","",SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A19))</f>
         <v/>
       </c>
       <c r="AE19" s="16">
-        <f>IF(AC19=0,0,AC19*1.7/12*AP19)</f>
+        <f>IF(A19="","",IF(AC19=0,0,AC19*1.7/12*AP19))</f>
         <v/>
       </c>
       <c r="AF19" s="16">
-        <f>IF(AD19=0,0,AD19*1.7/12*AQ19)</f>
+        <f>IF(A19="","",IF(AD19=0,0,AD19*1.7/12*AQ19))</f>
         <v/>
       </c>
       <c r="AG19" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A19,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A19,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A19="","",SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A19,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A19,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="AH19" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A19,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A19="","",SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A19,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AI19" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A19,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <f>IF(A19="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A19,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
       <c r="AJ19" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A19),0)</f>
+        <f>IF(A19="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A19))</f>
         <v/>
       </c>
       <c r="AK19" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A19),0)</f>
+        <f>IF(A19="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A19))</f>
         <v/>
       </c>
       <c r="AL19" s="16">
-        <f>(IF((AE19)&lt;(AG19+AH19+AI19),(AE19),(AG19+AH19+AI19)))+AJ19*5+AK19*10+R19+T19+V19</f>
+        <f>IF(A19="","",(IF((AE19)&lt;(AG19+AH19+AI19),(AE19),(AG19+AH19+AI19)))+AJ19*5+AK19*10+R19+T19+V19)</f>
         <v/>
       </c>
       <c r="AM19" s="16">
-        <f>AL19-J19</f>
+        <f>IF(A19="","",AL19-J19)</f>
         <v/>
       </c>
       <c r="AP19" s="16">
-        <f>IF(E19=0,"",(B19*0.95+C19*0.25+D19*0)/E19)</f>
+        <f>IF(A19="","",IF(E19=0,"",(B19*0.95+C19*0.25+D19*0)/E19))</f>
         <v/>
       </c>
       <c r="AQ19" s="16">
-        <f>IF(I19=0,"",(F19*0.95+G19*0.25+H19*0)/I19)</f>
+        <f>IF(A19="","",IF(I19=0,"",(F19*0.95+G19*0.25+H19*0)/I19))</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="16.25" customHeight="1">
       <c r="A20" s="16">
-        <f>IFERROR('SDA'!A66,"")</f>
+        <f>IF('SDA'!A66="","",'SDA'!A66)</f>
         <v/>
       </c>
       <c r="B20" s="16">
-        <f>IFERROR('SDA'!F66,0)</f>
+        <f>IF(A20="","",'SDA'!F66)</f>
         <v/>
       </c>
       <c r="C20" s="16">
-        <f>IFERROR('SDA'!G66,0)</f>
+        <f>IF(A20="","",'SDA'!G66)</f>
         <v/>
       </c>
       <c r="D20" s="16">
-        <f>IFERROR('SDA'!H66,0)</f>
+        <f>IF(A20="","",'SDA'!H66)</f>
         <v/>
       </c>
       <c r="E20" s="16">
-        <f>SUM(B20:D20)</f>
+        <f>IF(A20="","",SUM(B20:D20))</f>
         <v/>
       </c>
       <c r="F20" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A20,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A20,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <f>IF(A20="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A20,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A20,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"))</f>
         <v/>
       </c>
       <c r="G20" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A20,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <f>IF(A20="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A20,'SDA'!$C$4:$C$53,"Compacted (Open Space)"))</f>
         <v/>
       </c>
       <c r="H20" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A20,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <f>IF(A20="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A20,'SDA'!$C$4:$C$53,"Natural (Woods)"))</f>
         <v/>
       </c>
       <c r="I20" s="16">
-        <f>SUM(F20:H20)</f>
+        <f>IF(A20="","",SUM(F20:H20))</f>
         <v/>
       </c>
       <c r="J20" s="16">
-        <f>IF(E20=0,0,AP20*1.2/12*E20)</f>
+        <f>IF(A20="","",IF(E20=0,0,AP20*1.2/12*E20))</f>
         <v/>
       </c>
       <c r="K20" s="16">
-        <f>IF(I20=0,0,AQ20*1.2/12*I20)</f>
+        <f>IF(A20="","",IF(I20=0,0,AQ20*1.2/12*I20))</f>
         <v/>
       </c>
       <c r="L20" s="16">
-        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A20,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A20,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A20,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A20,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <f>IF(A20="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A20,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A20,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A20,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A20,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
         <v/>
       </c>
       <c r="M20" s="4" t="n"/>
       <c r="N20" s="4" t="n"/>
       <c r="O20" s="16">
-        <f>IFERROR(IFS(L20="A",2.5,L20="B",0.3,L20="C",0.1,L20="D",0.05,TRUE,""),"")</f>
+        <f>IF(A20="","",IFS(L20="A",2.5,L20="B",0.3,L20="C",0.1,L20="D",0.05,TRUE,""))</f>
         <v/>
       </c>
       <c r="P20" s="4" t="n"/>
       <c r="Q20" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A20),0)</f>
+        <f>IF(A20="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A20))</f>
         <v/>
       </c>
       <c r="R20" s="16">
-        <f>Q20*10</f>
+        <f>IF(A20="","",Q20*10)</f>
         <v/>
       </c>
       <c r="S20" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A20),0)</f>
+        <f>IF(A20="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A20))</f>
         <v/>
       </c>
       <c r="T20" s="16">
-        <f>S20*20</f>
+        <f>IF(A20="","",S20*20)</f>
         <v/>
       </c>
       <c r="U20" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A20)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A20),0)</f>
+        <f>IF(A20="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A20)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A20))</f>
         <v/>
       </c>
       <c r="V20" s="16">
-        <f>U20*40</f>
+        <f>IF(A20="","",U20*40)</f>
         <v/>
       </c>
       <c r="W20" s="4" t="n"/>
       <c r="X20" s="4" t="n"/>
       <c r="Y20" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A20,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A20,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A20="","",SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A20,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A20,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="Z20" s="4" t="n"/>
       <c r="AA20" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A20,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A20="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A20,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AB20" s="4" t="n"/>
       <c r="AC20" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A20),0)</f>
+        <f>IF(A20="","",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A20))</f>
         <v/>
       </c>
       <c r="AD20" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A20),0)</f>
+        <f>IF(A20="","",SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A20))</f>
         <v/>
       </c>
       <c r="AE20" s="16">
-        <f>IF(AC20=0,0,AC20*1.7/12*AP20)</f>
+        <f>IF(A20="","",IF(AC20=0,0,AC20*1.7/12*AP20))</f>
         <v/>
       </c>
       <c r="AF20" s="16">
-        <f>IF(AD20=0,0,AD20*1.7/12*AQ20)</f>
+        <f>IF(A20="","",IF(AD20=0,0,AD20*1.7/12*AQ20))</f>
         <v/>
       </c>
       <c r="AG20" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A20,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A20,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A20="","",SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A20,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A20,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="AH20" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A20,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A20="","",SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A20,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AI20" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A20,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <f>IF(A20="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A20,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
       <c r="AJ20" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A20),0)</f>
+        <f>IF(A20="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A20))</f>
         <v/>
       </c>
       <c r="AK20" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A20),0)</f>
+        <f>IF(A20="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A20))</f>
         <v/>
       </c>
       <c r="AL20" s="16">
-        <f>(IF((AE20)&lt;(AG20+AH20+AI20),(AE20),(AG20+AH20+AI20)))+AJ20*5+AK20*10+R20+T20+V20</f>
+        <f>IF(A20="","",(IF((AE20)&lt;(AG20+AH20+AI20),(AE20),(AG20+AH20+AI20)))+AJ20*5+AK20*10+R20+T20+V20)</f>
         <v/>
       </c>
       <c r="AM20" s="16">
-        <f>AL20-J20</f>
+        <f>IF(A20="","",AL20-J20)</f>
         <v/>
       </c>
       <c r="AP20" s="16">
-        <f>IF(E20=0,"",(B20*0.95+C20*0.25+D20*0)/E20)</f>
+        <f>IF(A20="","",IF(E20=0,"",(B20*0.95+C20*0.25+D20*0)/E20))</f>
         <v/>
       </c>
       <c r="AQ20" s="16">
-        <f>IF(I20=0,"",(F20*0.95+G20*0.25+H20*0)/I20)</f>
+        <f>IF(A20="","",IF(I20=0,"",(F20*0.95+G20*0.25+H20*0)/I20))</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="16.25" customHeight="1">
       <c r="A21" s="16">
-        <f>IFERROR('SDA'!A67,"")</f>
+        <f>IF('SDA'!A67="","",'SDA'!A67)</f>
         <v/>
       </c>
       <c r="B21" s="16">
-        <f>IFERROR('SDA'!F67,0)</f>
+        <f>IF(A21="","",'SDA'!F67)</f>
         <v/>
       </c>
       <c r="C21" s="16">
-        <f>IFERROR('SDA'!G67,0)</f>
+        <f>IF(A21="","",'SDA'!G67)</f>
         <v/>
       </c>
       <c r="D21" s="16">
-        <f>IFERROR('SDA'!H67,0)</f>
+        <f>IF(A21="","",'SDA'!H67)</f>
         <v/>
       </c>
       <c r="E21" s="16">
-        <f>SUM(B21:D21)</f>
+        <f>IF(A21="","",SUM(B21:D21))</f>
         <v/>
       </c>
       <c r="F21" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A21,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A21,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <f>IF(A21="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A21,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A21,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"))</f>
         <v/>
       </c>
       <c r="G21" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A21,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <f>IF(A21="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A21,'SDA'!$C$4:$C$53,"Compacted (Open Space)"))</f>
         <v/>
       </c>
       <c r="H21" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A21,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <f>IF(A21="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A21,'SDA'!$C$4:$C$53,"Natural (Woods)"))</f>
         <v/>
       </c>
       <c r="I21" s="16">
-        <f>SUM(F21:H21)</f>
+        <f>IF(A21="","",SUM(F21:H21))</f>
         <v/>
       </c>
       <c r="J21" s="16">
-        <f>IF(E21=0,0,AP21*1.2/12*E21)</f>
+        <f>IF(A21="","",IF(E21=0,0,AP21*1.2/12*E21))</f>
         <v/>
       </c>
       <c r="K21" s="16">
-        <f>IF(I21=0,0,AQ21*1.2/12*I21)</f>
+        <f>IF(A21="","",IF(I21=0,0,AQ21*1.2/12*I21))</f>
         <v/>
       </c>
       <c r="L21" s="16">
-        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A21,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A21,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A21,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A21,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <f>IF(A21="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A21,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A21,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A21,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A21,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
         <v/>
       </c>
       <c r="M21" s="4" t="n"/>
       <c r="N21" s="4" t="n"/>
       <c r="O21" s="16">
-        <f>IFERROR(IFS(L21="A",2.5,L21="B",0.3,L21="C",0.1,L21="D",0.05,TRUE,""),"")</f>
+        <f>IF(A21="","",IFS(L21="A",2.5,L21="B",0.3,L21="C",0.1,L21="D",0.05,TRUE,""))</f>
         <v/>
       </c>
       <c r="P21" s="4" t="n"/>
       <c r="Q21" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A21),0)</f>
+        <f>IF(A21="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A21))</f>
         <v/>
       </c>
       <c r="R21" s="16">
-        <f>Q21*10</f>
+        <f>IF(A21="","",Q21*10)</f>
         <v/>
       </c>
       <c r="S21" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A21),0)</f>
+        <f>IF(A21="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A21))</f>
         <v/>
       </c>
       <c r="T21" s="16">
-        <f>S21*20</f>
+        <f>IF(A21="","",S21*20)</f>
         <v/>
       </c>
       <c r="U21" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A21)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A21),0)</f>
+        <f>IF(A21="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A21)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A21))</f>
         <v/>
       </c>
       <c r="V21" s="16">
-        <f>U21*40</f>
+        <f>IF(A21="","",U21*40)</f>
         <v/>
       </c>
       <c r="W21" s="4" t="n"/>
       <c r="X21" s="4" t="n"/>
       <c r="Y21" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A21,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A21,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A21="","",SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A21,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A21,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="Z21" s="4" t="n"/>
       <c r="AA21" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A21,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A21="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A21,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AB21" s="4" t="n"/>
       <c r="AC21" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A21),0)</f>
+        <f>IF(A21="","",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A21))</f>
         <v/>
       </c>
       <c r="AD21" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A21),0)</f>
+        <f>IF(A21="","",SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A21))</f>
         <v/>
       </c>
       <c r="AE21" s="16">
-        <f>IF(AC21=0,0,AC21*1.7/12*AP21)</f>
+        <f>IF(A21="","",IF(AC21=0,0,AC21*1.7/12*AP21))</f>
         <v/>
       </c>
       <c r="AF21" s="16">
-        <f>IF(AD21=0,0,AD21*1.7/12*AQ21)</f>
+        <f>IF(A21="","",IF(AD21=0,0,AD21*1.7/12*AQ21))</f>
         <v/>
       </c>
       <c r="AG21" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A21,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A21,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A21="","",SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A21,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A21,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="AH21" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A21,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A21="","",SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A21,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AI21" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A21,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <f>IF(A21="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A21,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
       <c r="AJ21" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A21),0)</f>
+        <f>IF(A21="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A21))</f>
         <v/>
       </c>
       <c r="AK21" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A21),0)</f>
+        <f>IF(A21="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A21))</f>
         <v/>
       </c>
       <c r="AL21" s="16">
-        <f>(IF((AE21)&lt;(AG21+AH21+AI21),(AE21),(AG21+AH21+AI21)))+AJ21*5+AK21*10+R21+T21+V21</f>
+        <f>IF(A21="","",(IF((AE21)&lt;(AG21+AH21+AI21),(AE21),(AG21+AH21+AI21)))+AJ21*5+AK21*10+R21+T21+V21)</f>
         <v/>
       </c>
       <c r="AM21" s="16">
-        <f>AL21-J21</f>
+        <f>IF(A21="","",AL21-J21)</f>
         <v/>
       </c>
       <c r="AP21" s="16">
-        <f>IF(E21=0,"",(B21*0.95+C21*0.25+D21*0)/E21)</f>
+        <f>IF(A21="","",IF(E21=0,"",(B21*0.95+C21*0.25+D21*0)/E21))</f>
         <v/>
       </c>
       <c r="AQ21" s="16">
-        <f>IF(I21=0,"",(F21*0.95+G21*0.25+H21*0)/I21)</f>
+        <f>IF(A21="","",IF(I21=0,"",(F21*0.95+G21*0.25+H21*0)/I21))</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="16.25" customHeight="1">
       <c r="A22" s="16">
-        <f>IFERROR('SDA'!A68,"")</f>
+        <f>IF('SDA'!A68="","",'SDA'!A68)</f>
         <v/>
       </c>
       <c r="B22" s="16">
-        <f>IFERROR('SDA'!F68,0)</f>
+        <f>IF(A22="","",'SDA'!F68)</f>
         <v/>
       </c>
       <c r="C22" s="16">
-        <f>IFERROR('SDA'!G68,0)</f>
+        <f>IF(A22="","",'SDA'!G68)</f>
         <v/>
       </c>
       <c r="D22" s="16">
-        <f>IFERROR('SDA'!H68,0)</f>
+        <f>IF(A22="","",'SDA'!H68)</f>
         <v/>
       </c>
       <c r="E22" s="16">
-        <f>SUM(B22:D22)</f>
+        <f>IF(A22="","",SUM(B22:D22))</f>
         <v/>
       </c>
       <c r="F22" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A22,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A22,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <f>IF(A22="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A22,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A22,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"))</f>
         <v/>
       </c>
       <c r="G22" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A22,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <f>IF(A22="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A22,'SDA'!$C$4:$C$53,"Compacted (Open Space)"))</f>
         <v/>
       </c>
       <c r="H22" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A22,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <f>IF(A22="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A22,'SDA'!$C$4:$C$53,"Natural (Woods)"))</f>
         <v/>
       </c>
       <c r="I22" s="16">
-        <f>SUM(F22:H22)</f>
+        <f>IF(A22="","",SUM(F22:H22))</f>
         <v/>
       </c>
       <c r="J22" s="16">
-        <f>IF(E22=0,0,AP22*1.2/12*E22)</f>
+        <f>IF(A22="","",IF(E22=0,0,AP22*1.2/12*E22))</f>
         <v/>
       </c>
       <c r="K22" s="16">
-        <f>IF(I22=0,0,AQ22*1.2/12*I22)</f>
+        <f>IF(A22="","",IF(I22=0,0,AQ22*1.2/12*I22))</f>
         <v/>
       </c>
       <c r="L22" s="16">
-        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A22,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A22,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A22,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A22,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <f>IF(A22="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A22,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A22,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A22,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A22,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
         <v/>
       </c>
       <c r="M22" s="4" t="n"/>
       <c r="N22" s="4" t="n"/>
       <c r="O22" s="16">
-        <f>IFERROR(IFS(L22="A",2.5,L22="B",0.3,L22="C",0.1,L22="D",0.05,TRUE,""),"")</f>
+        <f>IF(A22="","",IFS(L22="A",2.5,L22="B",0.3,L22="C",0.1,L22="D",0.05,TRUE,""))</f>
         <v/>
       </c>
       <c r="P22" s="4" t="n"/>
       <c r="Q22" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A22),0)</f>
+        <f>IF(A22="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A22))</f>
         <v/>
       </c>
       <c r="R22" s="16">
-        <f>Q22*10</f>
+        <f>IF(A22="","",Q22*10)</f>
         <v/>
       </c>
       <c r="S22" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A22),0)</f>
+        <f>IF(A22="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A22))</f>
         <v/>
       </c>
       <c r="T22" s="16">
-        <f>S22*20</f>
+        <f>IF(A22="","",S22*20)</f>
         <v/>
       </c>
       <c r="U22" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A22)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A22),0)</f>
+        <f>IF(A22="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A22)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A22))</f>
         <v/>
       </c>
       <c r="V22" s="16">
-        <f>U22*40</f>
+        <f>IF(A22="","",U22*40)</f>
         <v/>
       </c>
       <c r="W22" s="4" t="n"/>
       <c r="X22" s="4" t="n"/>
       <c r="Y22" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A22,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A22,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A22="","",SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A22,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A22,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="Z22" s="4" t="n"/>
       <c r="AA22" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A22,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A22="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A22,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AB22" s="4" t="n"/>
       <c r="AC22" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A22),0)</f>
+        <f>IF(A22="","",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A22))</f>
         <v/>
       </c>
       <c r="AD22" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A22),0)</f>
+        <f>IF(A22="","",SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A22))</f>
         <v/>
       </c>
       <c r="AE22" s="16">
-        <f>IF(AC22=0,0,AC22*1.7/12*AP22)</f>
+        <f>IF(A22="","",IF(AC22=0,0,AC22*1.7/12*AP22))</f>
         <v/>
       </c>
       <c r="AF22" s="16">
-        <f>IF(AD22=0,0,AD22*1.7/12*AQ22)</f>
+        <f>IF(A22="","",IF(AD22=0,0,AD22*1.7/12*AQ22))</f>
         <v/>
       </c>
       <c r="AG22" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A22,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A22,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A22="","",SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A22,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A22,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="AH22" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A22,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A22="","",SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A22,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AI22" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A22,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <f>IF(A22="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A22,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
       <c r="AJ22" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A22),0)</f>
+        <f>IF(A22="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A22))</f>
         <v/>
       </c>
       <c r="AK22" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A22),0)</f>
+        <f>IF(A22="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A22))</f>
         <v/>
       </c>
       <c r="AL22" s="16">
-        <f>(IF((AE22)&lt;(AG22+AH22+AI22),(AE22),(AG22+AH22+AI22)))+AJ22*5+AK22*10+R22+T22+V22</f>
+        <f>IF(A22="","",(IF((AE22)&lt;(AG22+AH22+AI22),(AE22),(AG22+AH22+AI22)))+AJ22*5+AK22*10+R22+T22+V22)</f>
         <v/>
       </c>
       <c r="AM22" s="16">
-        <f>AL22-J22</f>
+        <f>IF(A22="","",AL22-J22)</f>
         <v/>
       </c>
       <c r="AP22" s="16">
-        <f>IF(E22=0,"",(B22*0.95+C22*0.25+D22*0)/E22)</f>
+        <f>IF(A22="","",IF(E22=0,"",(B22*0.95+C22*0.25+D22*0)/E22))</f>
         <v/>
       </c>
       <c r="AQ22" s="16">
-        <f>IF(I22=0,"",(F22*0.95+G22*0.25+H22*0)/I22)</f>
+        <f>IF(A22="","",IF(I22=0,"",(F22*0.95+G22*0.25+H22*0)/I22))</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="16.25" customHeight="1">
       <c r="A23" s="16">
-        <f>IFERROR('SDA'!A69,"")</f>
+        <f>IF('SDA'!A69="","",'SDA'!A69)</f>
         <v/>
       </c>
       <c r="B23" s="16">
-        <f>IFERROR('SDA'!F69,0)</f>
+        <f>IF(A23="","",'SDA'!F69)</f>
         <v/>
       </c>
       <c r="C23" s="16">
-        <f>IFERROR('SDA'!G69,0)</f>
+        <f>IF(A23="","",'SDA'!G69)</f>
         <v/>
       </c>
       <c r="D23" s="16">
-        <f>IFERROR('SDA'!H69,0)</f>
+        <f>IF(A23="","",'SDA'!H69)</f>
         <v/>
       </c>
       <c r="E23" s="16">
-        <f>SUM(B23:D23)</f>
+        <f>IF(A23="","",SUM(B23:D23))</f>
         <v/>
       </c>
       <c r="F23" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A23,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A23,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <f>IF(A23="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A23,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A23,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"))</f>
         <v/>
       </c>
       <c r="G23" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A23,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <f>IF(A23="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A23,'SDA'!$C$4:$C$53,"Compacted (Open Space)"))</f>
         <v/>
       </c>
       <c r="H23" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A23,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <f>IF(A23="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A23,'SDA'!$C$4:$C$53,"Natural (Woods)"))</f>
         <v/>
       </c>
       <c r="I23" s="16">
-        <f>SUM(F23:H23)</f>
+        <f>IF(A23="","",SUM(F23:H23))</f>
         <v/>
       </c>
       <c r="J23" s="16">
-        <f>IF(E23=0,0,AP23*1.2/12*E23)</f>
+        <f>IF(A23="","",IF(E23=0,0,AP23*1.2/12*E23))</f>
         <v/>
       </c>
       <c r="K23" s="16">
-        <f>IF(I23=0,0,AQ23*1.2/12*I23)</f>
+        <f>IF(A23="","",IF(I23=0,0,AQ23*1.2/12*I23))</f>
         <v/>
       </c>
       <c r="L23" s="16">
-        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A23,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A23,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A23,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A23,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <f>IF(A23="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A23,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A23,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A23,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A23,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
         <v/>
       </c>
       <c r="M23" s="4" t="n"/>
       <c r="N23" s="4" t="n"/>
       <c r="O23" s="16">
-        <f>IFERROR(IFS(L23="A",2.5,L23="B",0.3,L23="C",0.1,L23="D",0.05,TRUE,""),"")</f>
+        <f>IF(A23="","",IFS(L23="A",2.5,L23="B",0.3,L23="C",0.1,L23="D",0.05,TRUE,""))</f>
         <v/>
       </c>
       <c r="P23" s="4" t="n"/>
       <c r="Q23" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A23),0)</f>
+        <f>IF(A23="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A23))</f>
         <v/>
       </c>
       <c r="R23" s="16">
-        <f>Q23*10</f>
+        <f>IF(A23="","",Q23*10)</f>
         <v/>
       </c>
       <c r="S23" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A23),0)</f>
+        <f>IF(A23="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A23))</f>
         <v/>
       </c>
       <c r="T23" s="16">
-        <f>S23*20</f>
+        <f>IF(A23="","",S23*20)</f>
         <v/>
       </c>
       <c r="U23" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A23)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A23),0)</f>
+        <f>IF(A23="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A23)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A23))</f>
         <v/>
       </c>
       <c r="V23" s="16">
-        <f>U23*40</f>
+        <f>IF(A23="","",U23*40)</f>
         <v/>
       </c>
       <c r="W23" s="4" t="n"/>
       <c r="X23" s="4" t="n"/>
       <c r="Y23" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A23,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A23,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A23="","",SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A23,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A23,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="Z23" s="4" t="n"/>
       <c r="AA23" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A23,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A23="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A23,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AB23" s="4" t="n"/>
       <c r="AC23" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A23),0)</f>
+        <f>IF(A23="","",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A23))</f>
         <v/>
       </c>
       <c r="AD23" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A23),0)</f>
+        <f>IF(A23="","",SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A23))</f>
         <v/>
       </c>
       <c r="AE23" s="16">
-        <f>IF(AC23=0,0,AC23*1.7/12*AP23)</f>
+        <f>IF(A23="","",IF(AC23=0,0,AC23*1.7/12*AP23))</f>
         <v/>
       </c>
       <c r="AF23" s="16">
-        <f>IF(AD23=0,0,AD23*1.7/12*AQ23)</f>
+        <f>IF(A23="","",IF(AD23=0,0,AD23*1.7/12*AQ23))</f>
         <v/>
       </c>
       <c r="AG23" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A23,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A23,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A23="","",SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A23,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A23,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="AH23" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A23,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A23="","",SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A23,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AI23" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A23,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <f>IF(A23="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A23,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
       <c r="AJ23" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A23),0)</f>
+        <f>IF(A23="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A23))</f>
         <v/>
       </c>
       <c r="AK23" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A23),0)</f>
+        <f>IF(A23="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A23))</f>
         <v/>
       </c>
       <c r="AL23" s="16">
-        <f>(IF((AE23)&lt;(AG23+AH23+AI23),(AE23),(AG23+AH23+AI23)))+AJ23*5+AK23*10+R23+T23+V23</f>
+        <f>IF(A23="","",(IF((AE23)&lt;(AG23+AH23+AI23),(AE23),(AG23+AH23+AI23)))+AJ23*5+AK23*10+R23+T23+V23)</f>
         <v/>
       </c>
       <c r="AM23" s="16">
-        <f>AL23-J23</f>
+        <f>IF(A23="","",AL23-J23)</f>
         <v/>
       </c>
       <c r="AP23" s="16">
-        <f>IF(E23=0,"",(B23*0.95+C23*0.25+D23*0)/E23)</f>
+        <f>IF(A23="","",IF(E23=0,"",(B23*0.95+C23*0.25+D23*0)/E23))</f>
         <v/>
       </c>
       <c r="AQ23" s="16">
-        <f>IF(I23=0,"",(F23*0.95+G23*0.25+H23*0)/I23)</f>
+        <f>IF(A23="","",IF(I23=0,"",(F23*0.95+G23*0.25+H23*0)/I23))</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="16.25" customHeight="1">
       <c r="A24" s="16">
-        <f>IFERROR('SDA'!A70,"")</f>
+        <f>IF('SDA'!A70="","",'SDA'!A70)</f>
         <v/>
       </c>
       <c r="B24" s="16">
-        <f>IFERROR('SDA'!F70,0)</f>
+        <f>IF(A24="","",'SDA'!F70)</f>
         <v/>
       </c>
       <c r="C24" s="16">
-        <f>IFERROR('SDA'!G70,0)</f>
+        <f>IF(A24="","",'SDA'!G70)</f>
         <v/>
       </c>
       <c r="D24" s="16">
-        <f>IFERROR('SDA'!H70,0)</f>
+        <f>IF(A24="","",'SDA'!H70)</f>
         <v/>
       </c>
       <c r="E24" s="16">
-        <f>SUM(B24:D24)</f>
+        <f>IF(A24="","",SUM(B24:D24))</f>
         <v/>
       </c>
       <c r="F24" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A24,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A24,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <f>IF(A24="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A24,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A24,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"))</f>
         <v/>
       </c>
       <c r="G24" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A24,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <f>IF(A24="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A24,'SDA'!$C$4:$C$53,"Compacted (Open Space)"))</f>
         <v/>
       </c>
       <c r="H24" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A24,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <f>IF(A24="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A24,'SDA'!$C$4:$C$53,"Natural (Woods)"))</f>
         <v/>
       </c>
       <c r="I24" s="16">
-        <f>SUM(F24:H24)</f>
+        <f>IF(A24="","",SUM(F24:H24))</f>
         <v/>
       </c>
       <c r="J24" s="16">
-        <f>IF(E24=0,0,AP24*1.2/12*E24)</f>
+        <f>IF(A24="","",IF(E24=0,0,AP24*1.2/12*E24))</f>
         <v/>
       </c>
       <c r="K24" s="16">
-        <f>IF(I24=0,0,AQ24*1.2/12*I24)</f>
+        <f>IF(A24="","",IF(I24=0,0,AQ24*1.2/12*I24))</f>
         <v/>
       </c>
       <c r="L24" s="16">
-        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A24,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A24,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A24,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A24,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <f>IF(A24="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A24,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A24,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A24,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A24,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
         <v/>
       </c>
       <c r="M24" s="4" t="n"/>
       <c r="N24" s="4" t="n"/>
       <c r="O24" s="16">
-        <f>IFERROR(IFS(L24="A",2.5,L24="B",0.3,L24="C",0.1,L24="D",0.05,TRUE,""),"")</f>
+        <f>IF(A24="","",IFS(L24="A",2.5,L24="B",0.3,L24="C",0.1,L24="D",0.05,TRUE,""))</f>
         <v/>
       </c>
       <c r="P24" s="4" t="n"/>
       <c r="Q24" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A24),0)</f>
+        <f>IF(A24="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A24))</f>
         <v/>
       </c>
       <c r="R24" s="16">
-        <f>Q24*10</f>
+        <f>IF(A24="","",Q24*10)</f>
         <v/>
       </c>
       <c r="S24" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A24),0)</f>
+        <f>IF(A24="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A24))</f>
         <v/>
       </c>
       <c r="T24" s="16">
-        <f>S24*20</f>
+        <f>IF(A24="","",S24*20)</f>
         <v/>
       </c>
       <c r="U24" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A24)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A24),0)</f>
+        <f>IF(A24="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A24)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A24))</f>
         <v/>
       </c>
       <c r="V24" s="16">
-        <f>U24*40</f>
+        <f>IF(A24="","",U24*40)</f>
         <v/>
       </c>
       <c r="W24" s="4" t="n"/>
       <c r="X24" s="4" t="n"/>
       <c r="Y24" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A24,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A24,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A24="","",SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A24,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A24,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="Z24" s="4" t="n"/>
       <c r="AA24" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A24,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A24="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A24,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AB24" s="4" t="n"/>
       <c r="AC24" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A24),0)</f>
+        <f>IF(A24="","",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A24))</f>
         <v/>
       </c>
       <c r="AD24" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A24),0)</f>
+        <f>IF(A24="","",SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A24))</f>
         <v/>
       </c>
       <c r="AE24" s="16">
-        <f>IF(AC24=0,0,AC24*1.7/12*AP24)</f>
+        <f>IF(A24="","",IF(AC24=0,0,AC24*1.7/12*AP24))</f>
         <v/>
       </c>
       <c r="AF24" s="16">
-        <f>IF(AD24=0,0,AD24*1.7/12*AQ24)</f>
+        <f>IF(A24="","",IF(AD24=0,0,AD24*1.7/12*AQ24))</f>
         <v/>
       </c>
       <c r="AG24" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A24,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A24,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A24="","",SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A24,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A24,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="AH24" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A24,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A24="","",SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A24,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AI24" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A24,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <f>IF(A24="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A24,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
       <c r="AJ24" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A24),0)</f>
+        <f>IF(A24="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A24))</f>
         <v/>
       </c>
       <c r="AK24" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A24),0)</f>
+        <f>IF(A24="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A24))</f>
         <v/>
       </c>
       <c r="AL24" s="16">
-        <f>(IF((AE24)&lt;(AG24+AH24+AI24),(AE24),(AG24+AH24+AI24)))+AJ24*5+AK24*10+R24+T24+V24</f>
+        <f>IF(A24="","",(IF((AE24)&lt;(AG24+AH24+AI24),(AE24),(AG24+AH24+AI24)))+AJ24*5+AK24*10+R24+T24+V24)</f>
         <v/>
       </c>
       <c r="AM24" s="16">
-        <f>AL24-J24</f>
+        <f>IF(A24="","",AL24-J24)</f>
         <v/>
       </c>
       <c r="AP24" s="16">
-        <f>IF(E24=0,"",(B24*0.95+C24*0.25+D24*0)/E24)</f>
+        <f>IF(A24="","",IF(E24=0,"",(B24*0.95+C24*0.25+D24*0)/E24))</f>
         <v/>
       </c>
       <c r="AQ24" s="16">
-        <f>IF(I24=0,"",(F24*0.95+G24*0.25+H24*0)/I24)</f>
+        <f>IF(A24="","",IF(I24=0,"",(F24*0.95+G24*0.25+H24*0)/I24))</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="16.25" customHeight="1">
       <c r="A25" s="16">
-        <f>IFERROR('SDA'!A71,"")</f>
+        <f>IF('SDA'!A71="","",'SDA'!A71)</f>
         <v/>
       </c>
       <c r="B25" s="16">
-        <f>IFERROR('SDA'!F71,0)</f>
+        <f>IF(A25="","",'SDA'!F71)</f>
         <v/>
       </c>
       <c r="C25" s="16">
-        <f>IFERROR('SDA'!G71,0)</f>
+        <f>IF(A25="","",'SDA'!G71)</f>
         <v/>
       </c>
       <c r="D25" s="16">
-        <f>IFERROR('SDA'!H71,0)</f>
+        <f>IF(A25="","",'SDA'!H71)</f>
         <v/>
       </c>
       <c r="E25" s="16">
-        <f>SUM(B25:D25)</f>
+        <f>IF(A25="","",SUM(B25:D25))</f>
         <v/>
       </c>
       <c r="F25" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A25,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A25,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <f>IF(A25="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A25,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A25,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"))</f>
         <v/>
       </c>
       <c r="G25" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A25,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <f>IF(A25="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A25,'SDA'!$C$4:$C$53,"Compacted (Open Space)"))</f>
         <v/>
       </c>
       <c r="H25" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A25,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <f>IF(A25="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A25,'SDA'!$C$4:$C$53,"Natural (Woods)"))</f>
         <v/>
       </c>
       <c r="I25" s="16">
-        <f>SUM(F25:H25)</f>
+        <f>IF(A25="","",SUM(F25:H25))</f>
         <v/>
       </c>
       <c r="J25" s="16">
-        <f>IF(E25=0,0,AP25*1.2/12*E25)</f>
+        <f>IF(A25="","",IF(E25=0,0,AP25*1.2/12*E25))</f>
         <v/>
       </c>
       <c r="K25" s="16">
-        <f>IF(I25=0,0,AQ25*1.2/12*I25)</f>
+        <f>IF(A25="","",IF(I25=0,0,AQ25*1.2/12*I25))</f>
         <v/>
       </c>
       <c r="L25" s="16">
-        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A25,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A25,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A25,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A25,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <f>IF(A25="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A25,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A25,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A25,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A25,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
         <v/>
       </c>
       <c r="M25" s="4" t="n"/>
       <c r="N25" s="4" t="n"/>
       <c r="O25" s="16">
-        <f>IFERROR(IFS(L25="A",2.5,L25="B",0.3,L25="C",0.1,L25="D",0.05,TRUE,""),"")</f>
+        <f>IF(A25="","",IFS(L25="A",2.5,L25="B",0.3,L25="C",0.1,L25="D",0.05,TRUE,""))</f>
         <v/>
       </c>
       <c r="P25" s="4" t="n"/>
       <c r="Q25" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A25),0)</f>
+        <f>IF(A25="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A25))</f>
         <v/>
       </c>
       <c r="R25" s="16">
-        <f>Q25*10</f>
+        <f>IF(A25="","",Q25*10)</f>
         <v/>
       </c>
       <c r="S25" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A25),0)</f>
+        <f>IF(A25="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A25))</f>
         <v/>
       </c>
       <c r="T25" s="16">
-        <f>S25*20</f>
+        <f>IF(A25="","",S25*20)</f>
         <v/>
       </c>
       <c r="U25" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A25)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A25),0)</f>
+        <f>IF(A25="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A25)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A25))</f>
         <v/>
       </c>
       <c r="V25" s="16">
-        <f>U25*40</f>
+        <f>IF(A25="","",U25*40)</f>
         <v/>
       </c>
       <c r="W25" s="4" t="n"/>
       <c r="X25" s="4" t="n"/>
       <c r="Y25" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A25,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A25,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A25="","",SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A25,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A25,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="Z25" s="4" t="n"/>
       <c r="AA25" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A25,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A25="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A25,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AB25" s="4" t="n"/>
       <c r="AC25" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A25),0)</f>
+        <f>IF(A25="","",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A25))</f>
         <v/>
       </c>
       <c r="AD25" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A25),0)</f>
+        <f>IF(A25="","",SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A25))</f>
         <v/>
       </c>
       <c r="AE25" s="16">
-        <f>IF(AC25=0,0,AC25*1.7/12*AP25)</f>
+        <f>IF(A25="","",IF(AC25=0,0,AC25*1.7/12*AP25))</f>
         <v/>
       </c>
       <c r="AF25" s="16">
-        <f>IF(AD25=0,0,AD25*1.7/12*AQ25)</f>
+        <f>IF(A25="","",IF(AD25=0,0,AD25*1.7/12*AQ25))</f>
         <v/>
       </c>
       <c r="AG25" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A25,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A25,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A25="","",SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A25,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A25,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="AH25" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A25,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A25="","",SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A25,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AI25" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A25,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <f>IF(A25="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A25,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
       <c r="AJ25" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A25),0)</f>
+        <f>IF(A25="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A25))</f>
         <v/>
       </c>
       <c r="AK25" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A25),0)</f>
+        <f>IF(A25="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A25))</f>
         <v/>
       </c>
       <c r="AL25" s="16">
-        <f>(IF((AE25)&lt;(AG25+AH25+AI25),(AE25),(AG25+AH25+AI25)))+AJ25*5+AK25*10+R25+T25+V25</f>
+        <f>IF(A25="","",(IF((AE25)&lt;(AG25+AH25+AI25),(AE25),(AG25+AH25+AI25)))+AJ25*5+AK25*10+R25+T25+V25)</f>
         <v/>
       </c>
       <c r="AM25" s="16">
-        <f>AL25-J25</f>
+        <f>IF(A25="","",AL25-J25)</f>
         <v/>
       </c>
       <c r="AP25" s="16">
-        <f>IF(E25=0,"",(B25*0.95+C25*0.25+D25*0)/E25)</f>
+        <f>IF(A25="","",IF(E25=0,"",(B25*0.95+C25*0.25+D25*0)/E25))</f>
         <v/>
       </c>
       <c r="AQ25" s="16">
-        <f>IF(I25=0,"",(F25*0.95+G25*0.25+H25*0)/I25)</f>
+        <f>IF(A25="","",IF(I25=0,"",(F25*0.95+G25*0.25+H25*0)/I25))</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="16.25" customHeight="1">
       <c r="A26" s="16">
-        <f>IFERROR('SDA'!A72,"")</f>
+        <f>IF('SDA'!A72="","",'SDA'!A72)</f>
         <v/>
       </c>
       <c r="B26" s="16">
-        <f>IFERROR('SDA'!F72,0)</f>
+        <f>IF(A26="","",'SDA'!F72)</f>
         <v/>
       </c>
       <c r="C26" s="16">
-        <f>IFERROR('SDA'!G72,0)</f>
+        <f>IF(A26="","",'SDA'!G72)</f>
         <v/>
       </c>
       <c r="D26" s="16">
-        <f>IFERROR('SDA'!H72,0)</f>
+        <f>IF(A26="","",'SDA'!H72)</f>
         <v/>
       </c>
       <c r="E26" s="16">
-        <f>SUM(B26:D26)</f>
+        <f>IF(A26="","",SUM(B26:D26))</f>
         <v/>
       </c>
       <c r="F26" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A26,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A26,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <f>IF(A26="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A26,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A26,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"))</f>
         <v/>
       </c>
       <c r="G26" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A26,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <f>IF(A26="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A26,'SDA'!$C$4:$C$53,"Compacted (Open Space)"))</f>
         <v/>
       </c>
       <c r="H26" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A26,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <f>IF(A26="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A26,'SDA'!$C$4:$C$53,"Natural (Woods)"))</f>
         <v/>
       </c>
       <c r="I26" s="16">
-        <f>SUM(F26:H26)</f>
+        <f>IF(A26="","",SUM(F26:H26))</f>
         <v/>
       </c>
       <c r="J26" s="16">
-        <f>IF(E26=0,0,AP26*1.2/12*E26)</f>
+        <f>IF(A26="","",IF(E26=0,0,AP26*1.2/12*E26))</f>
         <v/>
       </c>
       <c r="K26" s="16">
-        <f>IF(I26=0,0,AQ26*1.2/12*I26)</f>
+        <f>IF(A26="","",IF(I26=0,0,AQ26*1.2/12*I26))</f>
         <v/>
       </c>
       <c r="L26" s="16">
-        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A26,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A26,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A26,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A26,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <f>IF(A26="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A26,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A26,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A26,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A26,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
         <v/>
       </c>
       <c r="M26" s="4" t="n"/>
       <c r="N26" s="4" t="n"/>
       <c r="O26" s="16">
-        <f>IFERROR(IFS(L26="A",2.5,L26="B",0.3,L26="C",0.1,L26="D",0.05,TRUE,""),"")</f>
+        <f>IF(A26="","",IFS(L26="A",2.5,L26="B",0.3,L26="C",0.1,L26="D",0.05,TRUE,""))</f>
         <v/>
       </c>
       <c r="P26" s="4" t="n"/>
       <c r="Q26" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A26),0)</f>
+        <f>IF(A26="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A26))</f>
         <v/>
       </c>
       <c r="R26" s="16">
-        <f>Q26*10</f>
+        <f>IF(A26="","",Q26*10)</f>
         <v/>
       </c>
       <c r="S26" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A26),0)</f>
+        <f>IF(A26="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A26))</f>
         <v/>
       </c>
       <c r="T26" s="16">
-        <f>S26*20</f>
+        <f>IF(A26="","",S26*20)</f>
         <v/>
       </c>
       <c r="U26" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A26)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A26),0)</f>
+        <f>IF(A26="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A26)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A26))</f>
         <v/>
       </c>
       <c r="V26" s="16">
-        <f>U26*40</f>
+        <f>IF(A26="","",U26*40)</f>
         <v/>
       </c>
       <c r="W26" s="4" t="n"/>
       <c r="X26" s="4" t="n"/>
       <c r="Y26" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A26,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A26,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A26="","",SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A26,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A26,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="Z26" s="4" t="n"/>
       <c r="AA26" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A26,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A26="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A26,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AB26" s="4" t="n"/>
       <c r="AC26" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A26),0)</f>
+        <f>IF(A26="","",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A26))</f>
         <v/>
       </c>
       <c r="AD26" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A26),0)</f>
+        <f>IF(A26="","",SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A26))</f>
         <v/>
       </c>
       <c r="AE26" s="16">
-        <f>IF(AC26=0,0,AC26*1.7/12*AP26)</f>
+        <f>IF(A26="","",IF(AC26=0,0,AC26*1.7/12*AP26))</f>
         <v/>
       </c>
       <c r="AF26" s="16">
-        <f>IF(AD26=0,0,AD26*1.7/12*AQ26)</f>
+        <f>IF(A26="","",IF(AD26=0,0,AD26*1.7/12*AQ26))</f>
         <v/>
       </c>
       <c r="AG26" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A26,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A26,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A26="","",SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A26,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A26,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="AH26" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A26,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A26="","",SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A26,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AI26" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A26,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <f>IF(A26="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A26,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
       <c r="AJ26" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A26),0)</f>
+        <f>IF(A26="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A26))</f>
         <v/>
       </c>
       <c r="AK26" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A26),0)</f>
+        <f>IF(A26="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A26))</f>
         <v/>
       </c>
       <c r="AL26" s="16">
-        <f>(IF((AE26)&lt;(AG26+AH26+AI26),(AE26),(AG26+AH26+AI26)))+AJ26*5+AK26*10+R26+T26+V26</f>
+        <f>IF(A26="","",(IF((AE26)&lt;(AG26+AH26+AI26),(AE26),(AG26+AH26+AI26)))+AJ26*5+AK26*10+R26+T26+V26)</f>
         <v/>
       </c>
       <c r="AM26" s="16">
-        <f>AL26-J26</f>
+        <f>IF(A26="","",AL26-J26)</f>
         <v/>
       </c>
       <c r="AP26" s="16">
-        <f>IF(E26=0,"",(B26*0.95+C26*0.25+D26*0)/E26)</f>
+        <f>IF(A26="","",IF(E26=0,"",(B26*0.95+C26*0.25+D26*0)/E26))</f>
         <v/>
       </c>
       <c r="AQ26" s="16">
-        <f>IF(I26=0,"",(F26*0.95+G26*0.25+H26*0)/I26)</f>
+        <f>IF(A26="","",IF(I26=0,"",(F26*0.95+G26*0.25+H26*0)/I26))</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="16.25" customHeight="1">
       <c r="A27" s="16">
-        <f>IFERROR('SDA'!A73,"")</f>
+        <f>IF('SDA'!A73="","",'SDA'!A73)</f>
         <v/>
       </c>
       <c r="B27" s="16">
-        <f>IFERROR('SDA'!F73,0)</f>
+        <f>IF(A27="","",'SDA'!F73)</f>
         <v/>
       </c>
       <c r="C27" s="16">
-        <f>IFERROR('SDA'!G73,0)</f>
+        <f>IF(A27="","",'SDA'!G73)</f>
         <v/>
       </c>
       <c r="D27" s="16">
-        <f>IFERROR('SDA'!H73,0)</f>
+        <f>IF(A27="","",'SDA'!H73)</f>
         <v/>
       </c>
       <c r="E27" s="16">
-        <f>SUM(B27:D27)</f>
+        <f>IF(A27="","",SUM(B27:D27))</f>
         <v/>
       </c>
       <c r="F27" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A27,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A27,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <f>IF(A27="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A27,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A27,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"))</f>
         <v/>
       </c>
       <c r="G27" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A27,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <f>IF(A27="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A27,'SDA'!$C$4:$C$53,"Compacted (Open Space)"))</f>
         <v/>
       </c>
       <c r="H27" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A27,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <f>IF(A27="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A27,'SDA'!$C$4:$C$53,"Natural (Woods)"))</f>
         <v/>
       </c>
       <c r="I27" s="16">
-        <f>SUM(F27:H27)</f>
+        <f>IF(A27="","",SUM(F27:H27))</f>
         <v/>
       </c>
       <c r="J27" s="16">
-        <f>IF(E27=0,0,AP27*1.2/12*E27)</f>
+        <f>IF(A27="","",IF(E27=0,0,AP27*1.2/12*E27))</f>
         <v/>
       </c>
       <c r="K27" s="16">
-        <f>IF(I27=0,0,AQ27*1.2/12*I27)</f>
+        <f>IF(A27="","",IF(I27=0,0,AQ27*1.2/12*I27))</f>
         <v/>
       </c>
       <c r="L27" s="16">
-        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A27,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A27,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A27,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A27,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <f>IF(A27="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A27,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A27,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A27,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A27,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
         <v/>
       </c>
       <c r="M27" s="4" t="n"/>
       <c r="N27" s="4" t="n"/>
       <c r="O27" s="16">
-        <f>IFERROR(IFS(L27="A",2.5,L27="B",0.3,L27="C",0.1,L27="D",0.05,TRUE,""),"")</f>
+        <f>IF(A27="","",IFS(L27="A",2.5,L27="B",0.3,L27="C",0.1,L27="D",0.05,TRUE,""))</f>
         <v/>
       </c>
       <c r="P27" s="4" t="n"/>
       <c r="Q27" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A27),0)</f>
+        <f>IF(A27="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A27))</f>
         <v/>
       </c>
       <c r="R27" s="16">
-        <f>Q27*10</f>
+        <f>IF(A27="","",Q27*10)</f>
         <v/>
       </c>
       <c r="S27" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A27),0)</f>
+        <f>IF(A27="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A27))</f>
         <v/>
       </c>
       <c r="T27" s="16">
-        <f>S27*20</f>
+        <f>IF(A27="","",S27*20)</f>
         <v/>
       </c>
       <c r="U27" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A27)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A27),0)</f>
+        <f>IF(A27="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A27)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A27))</f>
         <v/>
       </c>
       <c r="V27" s="16">
-        <f>U27*40</f>
+        <f>IF(A27="","",U27*40)</f>
         <v/>
       </c>
       <c r="W27" s="4" t="n"/>
       <c r="X27" s="4" t="n"/>
       <c r="Y27" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A27,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A27,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A27="","",SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A27,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A27,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="Z27" s="4" t="n"/>
       <c r="AA27" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A27,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A27="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A27,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AB27" s="4" t="n"/>
       <c r="AC27" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A27),0)</f>
+        <f>IF(A27="","",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A27))</f>
         <v/>
       </c>
       <c r="AD27" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A27),0)</f>
+        <f>IF(A27="","",SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A27))</f>
         <v/>
       </c>
       <c r="AE27" s="16">
-        <f>IF(AC27=0,0,AC27*1.7/12*AP27)</f>
+        <f>IF(A27="","",IF(AC27=0,0,AC27*1.7/12*AP27))</f>
         <v/>
       </c>
       <c r="AF27" s="16">
-        <f>IF(AD27=0,0,AD27*1.7/12*AQ27)</f>
+        <f>IF(A27="","",IF(AD27=0,0,AD27*1.7/12*AQ27))</f>
         <v/>
       </c>
       <c r="AG27" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A27,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A27,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A27="","",SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A27,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A27,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="AH27" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A27,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A27="","",SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A27,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AI27" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A27,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <f>IF(A27="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A27,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
       <c r="AJ27" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A27),0)</f>
+        <f>IF(A27="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A27))</f>
         <v/>
       </c>
       <c r="AK27" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A27),0)</f>
+        <f>IF(A27="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A27))</f>
         <v/>
       </c>
       <c r="AL27" s="16">
-        <f>(IF((AE27)&lt;(AG27+AH27+AI27),(AE27),(AG27+AH27+AI27)))+AJ27*5+AK27*10+R27+T27+V27</f>
+        <f>IF(A27="","",(IF((AE27)&lt;(AG27+AH27+AI27),(AE27),(AG27+AH27+AI27)))+AJ27*5+AK27*10+R27+T27+V27)</f>
         <v/>
       </c>
       <c r="AM27" s="16">
-        <f>AL27-J27</f>
+        <f>IF(A27="","",AL27-J27)</f>
         <v/>
       </c>
       <c r="AP27" s="16">
-        <f>IF(E27=0,"",(B27*0.95+C27*0.25+D27*0)/E27)</f>
+        <f>IF(A27="","",IF(E27=0,"",(B27*0.95+C27*0.25+D27*0)/E27))</f>
         <v/>
       </c>
       <c r="AQ27" s="16">
-        <f>IF(I27=0,"",(F27*0.95+G27*0.25+H27*0)/I27)</f>
+        <f>IF(A27="","",IF(I27=0,"",(F27*0.95+G27*0.25+H27*0)/I27))</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="16.25" customHeight="1">
       <c r="A28" s="16">
-        <f>IFERROR('SDA'!A74,"")</f>
+        <f>IF('SDA'!A74="","",'SDA'!A74)</f>
         <v/>
       </c>
       <c r="B28" s="16">
-        <f>IFERROR('SDA'!F74,0)</f>
+        <f>IF(A28="","",'SDA'!F74)</f>
         <v/>
       </c>
       <c r="C28" s="16">
-        <f>IFERROR('SDA'!G74,0)</f>
+        <f>IF(A28="","",'SDA'!G74)</f>
         <v/>
       </c>
       <c r="D28" s="16">
-        <f>IFERROR('SDA'!H74,0)</f>
+        <f>IF(A28="","",'SDA'!H74)</f>
         <v/>
       </c>
       <c r="E28" s="16">
-        <f>SUM(B28:D28)</f>
+        <f>IF(A28="","",SUM(B28:D28))</f>
         <v/>
       </c>
       <c r="F28" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A28,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A28,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <f>IF(A28="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A28,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A28,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"))</f>
         <v/>
       </c>
       <c r="G28" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A28,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <f>IF(A28="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A28,'SDA'!$C$4:$C$53,"Compacted (Open Space)"))</f>
         <v/>
       </c>
       <c r="H28" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A28,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <f>IF(A28="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A28,'SDA'!$C$4:$C$53,"Natural (Woods)"))</f>
         <v/>
       </c>
       <c r="I28" s="16">
-        <f>SUM(F28:H28)</f>
+        <f>IF(A28="","",SUM(F28:H28))</f>
         <v/>
       </c>
       <c r="J28" s="16">
-        <f>IF(E28=0,0,AP28*1.2/12*E28)</f>
+        <f>IF(A28="","",IF(E28=0,0,AP28*1.2/12*E28))</f>
         <v/>
       </c>
       <c r="K28" s="16">
-        <f>IF(I28=0,0,AQ28*1.2/12*I28)</f>
+        <f>IF(A28="","",IF(I28=0,0,AQ28*1.2/12*I28))</f>
         <v/>
       </c>
       <c r="L28" s="16">
-        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A28,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A28,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A28,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A28,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <f>IF(A28="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A28,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A28,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A28,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A28,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
         <v/>
       </c>
       <c r="M28" s="4" t="n"/>
       <c r="N28" s="4" t="n"/>
       <c r="O28" s="16">
-        <f>IFERROR(IFS(L28="A",2.5,L28="B",0.3,L28="C",0.1,L28="D",0.05,TRUE,""),"")</f>
+        <f>IF(A28="","",IFS(L28="A",2.5,L28="B",0.3,L28="C",0.1,L28="D",0.05,TRUE,""))</f>
         <v/>
       </c>
       <c r="P28" s="4" t="n"/>
       <c r="Q28" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A28),0)</f>
+        <f>IF(A28="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A28))</f>
         <v/>
       </c>
       <c r="R28" s="16">
-        <f>Q28*10</f>
+        <f>IF(A28="","",Q28*10)</f>
         <v/>
       </c>
       <c r="S28" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A28),0)</f>
+        <f>IF(A28="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A28))</f>
         <v/>
       </c>
       <c r="T28" s="16">
-        <f>S28*20</f>
+        <f>IF(A28="","",S28*20)</f>
         <v/>
       </c>
       <c r="U28" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A28)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A28),0)</f>
+        <f>IF(A28="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A28)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A28))</f>
         <v/>
       </c>
       <c r="V28" s="16">
-        <f>U28*40</f>
+        <f>IF(A28="","",U28*40)</f>
         <v/>
       </c>
       <c r="W28" s="4" t="n"/>
       <c r="X28" s="4" t="n"/>
       <c r="Y28" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A28,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A28,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A28="","",SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A28,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A28,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="Z28" s="4" t="n"/>
       <c r="AA28" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A28,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A28="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A28,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AB28" s="4" t="n"/>
       <c r="AC28" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A28),0)</f>
+        <f>IF(A28="","",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A28))</f>
         <v/>
       </c>
       <c r="AD28" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A28),0)</f>
+        <f>IF(A28="","",SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A28))</f>
         <v/>
       </c>
       <c r="AE28" s="16">
-        <f>IF(AC28=0,0,AC28*1.7/12*AP28)</f>
+        <f>IF(A28="","",IF(AC28=0,0,AC28*1.7/12*AP28))</f>
         <v/>
       </c>
       <c r="AF28" s="16">
-        <f>IF(AD28=0,0,AD28*1.7/12*AQ28)</f>
+        <f>IF(A28="","",IF(AD28=0,0,AD28*1.7/12*AQ28))</f>
         <v/>
       </c>
       <c r="AG28" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A28,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A28,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A28="","",SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A28,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A28,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="AH28" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A28,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A28="","",SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A28,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AI28" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A28,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <f>IF(A28="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A28,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
       <c r="AJ28" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A28),0)</f>
+        <f>IF(A28="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A28))</f>
         <v/>
       </c>
       <c r="AK28" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A28),0)</f>
+        <f>IF(A28="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A28))</f>
         <v/>
       </c>
       <c r="AL28" s="16">
-        <f>(IF((AE28)&lt;(AG28+AH28+AI28),(AE28),(AG28+AH28+AI28)))+AJ28*5+AK28*10+R28+T28+V28</f>
+        <f>IF(A28="","",(IF((AE28)&lt;(AG28+AH28+AI28),(AE28),(AG28+AH28+AI28)))+AJ28*5+AK28*10+R28+T28+V28)</f>
         <v/>
       </c>
       <c r="AM28" s="16">
-        <f>AL28-J28</f>
+        <f>IF(A28="","",AL28-J28)</f>
         <v/>
       </c>
       <c r="AP28" s="16">
-        <f>IF(E28=0,"",(B28*0.95+C28*0.25+D28*0)/E28)</f>
+        <f>IF(A28="","",IF(E28=0,"",(B28*0.95+C28*0.25+D28*0)/E28))</f>
         <v/>
       </c>
       <c r="AQ28" s="16">
-        <f>IF(I28=0,"",(F28*0.95+G28*0.25+H28*0)/I28)</f>
+        <f>IF(A28="","",IF(I28=0,"",(F28*0.95+G28*0.25+H28*0)/I28))</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="16.25" customHeight="1">
       <c r="A29" s="16">
-        <f>IFERROR('SDA'!A75,"")</f>
+        <f>IF('SDA'!A75="","",'SDA'!A75)</f>
         <v/>
       </c>
       <c r="B29" s="16">
-        <f>IFERROR('SDA'!F75,0)</f>
+        <f>IF(A29="","",'SDA'!F75)</f>
         <v/>
       </c>
       <c r="C29" s="16">
-        <f>IFERROR('SDA'!G75,0)</f>
+        <f>IF(A29="","",'SDA'!G75)</f>
         <v/>
       </c>
       <c r="D29" s="16">
-        <f>IFERROR('SDA'!H75,0)</f>
+        <f>IF(A29="","",'SDA'!H75)</f>
         <v/>
       </c>
       <c r="E29" s="16">
-        <f>SUM(B29:D29)</f>
+        <f>IF(A29="","",SUM(B29:D29))</f>
         <v/>
       </c>
       <c r="F29" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A29,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A29,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <f>IF(A29="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A29,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A29,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"))</f>
         <v/>
       </c>
       <c r="G29" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A29,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <f>IF(A29="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A29,'SDA'!$C$4:$C$53,"Compacted (Open Space)"))</f>
         <v/>
       </c>
       <c r="H29" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A29,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <f>IF(A29="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A29,'SDA'!$C$4:$C$53,"Natural (Woods)"))</f>
         <v/>
       </c>
       <c r="I29" s="16">
-        <f>SUM(F29:H29)</f>
+        <f>IF(A29="","",SUM(F29:H29))</f>
         <v/>
       </c>
       <c r="J29" s="16">
-        <f>IF(E29=0,0,AP29*1.2/12*E29)</f>
+        <f>IF(A29="","",IF(E29=0,0,AP29*1.2/12*E29))</f>
         <v/>
       </c>
       <c r="K29" s="16">
-        <f>IF(I29=0,0,AQ29*1.2/12*I29)</f>
+        <f>IF(A29="","",IF(I29=0,0,AQ29*1.2/12*I29))</f>
         <v/>
       </c>
       <c r="L29" s="16">
-        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A29,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A29,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A29,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A29,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <f>IF(A29="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A29,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A29,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A29,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A29,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
         <v/>
       </c>
       <c r="M29" s="4" t="n"/>
       <c r="N29" s="4" t="n"/>
       <c r="O29" s="16">
-        <f>IFERROR(IFS(L29="A",2.5,L29="B",0.3,L29="C",0.1,L29="D",0.05,TRUE,""),"")</f>
+        <f>IF(A29="","",IFS(L29="A",2.5,L29="B",0.3,L29="C",0.1,L29="D",0.05,TRUE,""))</f>
         <v/>
       </c>
       <c r="P29" s="4" t="n"/>
       <c r="Q29" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A29),0)</f>
+        <f>IF(A29="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A29))</f>
         <v/>
       </c>
       <c r="R29" s="16">
-        <f>Q29*10</f>
+        <f>IF(A29="","",Q29*10)</f>
         <v/>
       </c>
       <c r="S29" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A29),0)</f>
+        <f>IF(A29="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A29))</f>
         <v/>
       </c>
       <c r="T29" s="16">
-        <f>S29*20</f>
+        <f>IF(A29="","",S29*20)</f>
         <v/>
       </c>
       <c r="U29" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A29)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A29),0)</f>
+        <f>IF(A29="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A29)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A29))</f>
         <v/>
       </c>
       <c r="V29" s="16">
-        <f>U29*40</f>
+        <f>IF(A29="","",U29*40)</f>
         <v/>
       </c>
       <c r="W29" s="4" t="n"/>
       <c r="X29" s="4" t="n"/>
       <c r="Y29" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A29,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A29,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A29="","",SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A29,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A29,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="Z29" s="4" t="n"/>
       <c r="AA29" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A29,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A29="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A29,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AB29" s="4" t="n"/>
       <c r="AC29" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A29),0)</f>
+        <f>IF(A29="","",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A29))</f>
         <v/>
       </c>
       <c r="AD29" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A29),0)</f>
+        <f>IF(A29="","",SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A29))</f>
         <v/>
       </c>
       <c r="AE29" s="16">
-        <f>IF(AC29=0,0,AC29*1.7/12*AP29)</f>
+        <f>IF(A29="","",IF(AC29=0,0,AC29*1.7/12*AP29))</f>
         <v/>
       </c>
       <c r="AF29" s="16">
-        <f>IF(AD29=0,0,AD29*1.7/12*AQ29)</f>
+        <f>IF(A29="","",IF(AD29=0,0,AD29*1.7/12*AQ29))</f>
         <v/>
       </c>
       <c r="AG29" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A29,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A29,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A29="","",SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A29,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A29,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="AH29" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A29,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A29="","",SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A29,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AI29" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A29,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <f>IF(A29="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A29,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
       <c r="AJ29" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A29),0)</f>
+        <f>IF(A29="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A29))</f>
         <v/>
       </c>
       <c r="AK29" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A29),0)</f>
+        <f>IF(A29="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A29))</f>
         <v/>
       </c>
       <c r="AL29" s="16">
-        <f>(IF((AE29)&lt;(AG29+AH29+AI29),(AE29),(AG29+AH29+AI29)))+AJ29*5+AK29*10+R29+T29+V29</f>
+        <f>IF(A29="","",(IF((AE29)&lt;(AG29+AH29+AI29),(AE29),(AG29+AH29+AI29)))+AJ29*5+AK29*10+R29+T29+V29)</f>
         <v/>
       </c>
       <c r="AM29" s="16">
-        <f>AL29-J29</f>
+        <f>IF(A29="","",AL29-J29)</f>
         <v/>
       </c>
       <c r="AP29" s="16">
-        <f>IF(E29=0,"",(B29*0.95+C29*0.25+D29*0)/E29)</f>
+        <f>IF(A29="","",IF(E29=0,"",(B29*0.95+C29*0.25+D29*0)/E29))</f>
         <v/>
       </c>
       <c r="AQ29" s="16">
-        <f>IF(I29=0,"",(F29*0.95+G29*0.25+H29*0)/I29)</f>
+        <f>IF(A29="","",IF(I29=0,"",(F29*0.95+G29*0.25+H29*0)/I29))</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="16.25" customHeight="1">
       <c r="A30" s="16">
-        <f>IFERROR('SDA'!A76,"")</f>
+        <f>IF('SDA'!A76="","",'SDA'!A76)</f>
         <v/>
       </c>
       <c r="B30" s="16">
-        <f>IFERROR('SDA'!F76,0)</f>
+        <f>IF(A30="","",'SDA'!F76)</f>
         <v/>
       </c>
       <c r="C30" s="16">
-        <f>IFERROR('SDA'!G76,0)</f>
+        <f>IF(A30="","",'SDA'!G76)</f>
         <v/>
       </c>
       <c r="D30" s="16">
-        <f>IFERROR('SDA'!H76,0)</f>
+        <f>IF(A30="","",'SDA'!H76)</f>
         <v/>
       </c>
       <c r="E30" s="16">
-        <f>SUM(B30:D30)</f>
+        <f>IF(A30="","",SUM(B30:D30))</f>
         <v/>
       </c>
       <c r="F30" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A30,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A30,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <f>IF(A30="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A30,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A30,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"))</f>
         <v/>
       </c>
       <c r="G30" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A30,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <f>IF(A30="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A30,'SDA'!$C$4:$C$53,"Compacted (Open Space)"))</f>
         <v/>
       </c>
       <c r="H30" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A30,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <f>IF(A30="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A30,'SDA'!$C$4:$C$53,"Natural (Woods)"))</f>
         <v/>
       </c>
       <c r="I30" s="16">
-        <f>SUM(F30:H30)</f>
+        <f>IF(A30="","",SUM(F30:H30))</f>
         <v/>
       </c>
       <c r="J30" s="16">
-        <f>IF(E30=0,0,AP30*1.2/12*E30)</f>
+        <f>IF(A30="","",IF(E30=0,0,AP30*1.2/12*E30))</f>
         <v/>
       </c>
       <c r="K30" s="16">
-        <f>IF(I30=0,0,AQ30*1.2/12*I30)</f>
+        <f>IF(A30="","",IF(I30=0,0,AQ30*1.2/12*I30))</f>
         <v/>
       </c>
       <c r="L30" s="16">
-        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A30,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A30,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A30,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A30,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <f>IF(A30="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A30,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A30,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A30,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A30,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
         <v/>
       </c>
       <c r="M30" s="4" t="n"/>
       <c r="N30" s="4" t="n"/>
       <c r="O30" s="16">
-        <f>IFERROR(IFS(L30="A",2.5,L30="B",0.3,L30="C",0.1,L30="D",0.05,TRUE,""),"")</f>
+        <f>IF(A30="","",IFS(L30="A",2.5,L30="B",0.3,L30="C",0.1,L30="D",0.05,TRUE,""))</f>
         <v/>
       </c>
       <c r="P30" s="4" t="n"/>
       <c r="Q30" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A30),0)</f>
+        <f>IF(A30="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A30))</f>
         <v/>
       </c>
       <c r="R30" s="16">
-        <f>Q30*10</f>
+        <f>IF(A30="","",Q30*10)</f>
         <v/>
       </c>
       <c r="S30" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A30),0)</f>
+        <f>IF(A30="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A30))</f>
         <v/>
       </c>
       <c r="T30" s="16">
-        <f>S30*20</f>
+        <f>IF(A30="","",S30*20)</f>
         <v/>
       </c>
       <c r="U30" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A30)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A30),0)</f>
+        <f>IF(A30="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A30)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A30))</f>
         <v/>
       </c>
       <c r="V30" s="16">
-        <f>U30*40</f>
+        <f>IF(A30="","",U30*40)</f>
         <v/>
       </c>
       <c r="W30" s="4" t="n"/>
       <c r="X30" s="4" t="n"/>
       <c r="Y30" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A30,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A30,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A30="","",SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A30,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A30,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="Z30" s="4" t="n"/>
       <c r="AA30" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A30,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A30="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A30,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AB30" s="4" t="n"/>
       <c r="AC30" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A30),0)</f>
+        <f>IF(A30="","",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A30))</f>
         <v/>
       </c>
       <c r="AD30" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A30),0)</f>
+        <f>IF(A30="","",SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A30))</f>
         <v/>
       </c>
       <c r="AE30" s="16">
-        <f>IF(AC30=0,0,AC30*1.7/12*AP30)</f>
+        <f>IF(A30="","",IF(AC30=0,0,AC30*1.7/12*AP30))</f>
         <v/>
       </c>
       <c r="AF30" s="16">
-        <f>IF(AD30=0,0,AD30*1.7/12*AQ30)</f>
+        <f>IF(A30="","",IF(AD30=0,0,AD30*1.7/12*AQ30))</f>
         <v/>
       </c>
       <c r="AG30" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A30,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A30,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A30="","",SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A30,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A30,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="AH30" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A30,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A30="","",SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A30,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AI30" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A30,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <f>IF(A30="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A30,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
       <c r="AJ30" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A30),0)</f>
+        <f>IF(A30="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A30))</f>
         <v/>
       </c>
       <c r="AK30" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A30),0)</f>
+        <f>IF(A30="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A30))</f>
         <v/>
       </c>
       <c r="AL30" s="16">
-        <f>(IF((AE30)&lt;(AG30+AH30+AI30),(AE30),(AG30+AH30+AI30)))+AJ30*5+AK30*10+R30+T30+V30</f>
+        <f>IF(A30="","",(IF((AE30)&lt;(AG30+AH30+AI30),(AE30),(AG30+AH30+AI30)))+AJ30*5+AK30*10+R30+T30+V30)</f>
         <v/>
       </c>
       <c r="AM30" s="16">
-        <f>AL30-J30</f>
+        <f>IF(A30="","",AL30-J30)</f>
         <v/>
       </c>
       <c r="AP30" s="16">
-        <f>IF(E30=0,"",(B30*0.95+C30*0.25+D30*0)/E30)</f>
+        <f>IF(A30="","",IF(E30=0,"",(B30*0.95+C30*0.25+D30*0)/E30))</f>
         <v/>
       </c>
       <c r="AQ30" s="16">
-        <f>IF(I30=0,"",(F30*0.95+G30*0.25+H30*0)/I30)</f>
+        <f>IF(A30="","",IF(I30=0,"",(F30*0.95+G30*0.25+H30*0)/I30))</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="16.25" customHeight="1">
       <c r="A31" s="16">
-        <f>IFERROR('SDA'!A77,"")</f>
+        <f>IF('SDA'!A77="","",'SDA'!A77)</f>
         <v/>
       </c>
       <c r="B31" s="16">
-        <f>IFERROR('SDA'!F77,0)</f>
+        <f>IF(A31="","",'SDA'!F77)</f>
         <v/>
       </c>
       <c r="C31" s="16">
-        <f>IFERROR('SDA'!G77,0)</f>
+        <f>IF(A31="","",'SDA'!G77)</f>
         <v/>
       </c>
       <c r="D31" s="16">
-        <f>IFERROR('SDA'!H77,0)</f>
+        <f>IF(A31="","",'SDA'!H77)</f>
         <v/>
       </c>
       <c r="E31" s="16">
-        <f>SUM(B31:D31)</f>
+        <f>IF(A31="","",SUM(B31:D31))</f>
         <v/>
       </c>
       <c r="F31" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A31,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A31,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <f>IF(A31="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A31,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A31,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"))</f>
         <v/>
       </c>
       <c r="G31" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A31,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <f>IF(A31="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A31,'SDA'!$C$4:$C$53,"Compacted (Open Space)"))</f>
         <v/>
       </c>
       <c r="H31" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A31,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <f>IF(A31="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A31,'SDA'!$C$4:$C$53,"Natural (Woods)"))</f>
         <v/>
       </c>
       <c r="I31" s="16">
-        <f>SUM(F31:H31)</f>
+        <f>IF(A31="","",SUM(F31:H31))</f>
         <v/>
       </c>
       <c r="J31" s="16">
-        <f>IF(E31=0,0,AP31*1.2/12*E31)</f>
+        <f>IF(A31="","",IF(E31=0,0,AP31*1.2/12*E31))</f>
         <v/>
       </c>
       <c r="K31" s="16">
-        <f>IF(I31=0,0,AQ31*1.2/12*I31)</f>
+        <f>IF(A31="","",IF(I31=0,0,AQ31*1.2/12*I31))</f>
         <v/>
       </c>
       <c r="L31" s="16">
-        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A31,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A31,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A31,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A31,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <f>IF(A31="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A31,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A31,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A31,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A31,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
         <v/>
       </c>
       <c r="M31" s="4" t="n"/>
       <c r="N31" s="4" t="n"/>
       <c r="O31" s="16">
-        <f>IFERROR(IFS(L31="A",2.5,L31="B",0.3,L31="C",0.1,L31="D",0.05,TRUE,""),"")</f>
+        <f>IF(A31="","",IFS(L31="A",2.5,L31="B",0.3,L31="C",0.1,L31="D",0.05,TRUE,""))</f>
         <v/>
       </c>
       <c r="P31" s="4" t="n"/>
       <c r="Q31" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A31),0)</f>
+        <f>IF(A31="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A31))</f>
         <v/>
       </c>
       <c r="R31" s="16">
-        <f>Q31*10</f>
+        <f>IF(A31="","",Q31*10)</f>
         <v/>
       </c>
       <c r="S31" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A31),0)</f>
+        <f>IF(A31="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A31))</f>
         <v/>
       </c>
       <c r="T31" s="16">
-        <f>S31*20</f>
+        <f>IF(A31="","",S31*20)</f>
         <v/>
       </c>
       <c r="U31" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A31)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A31),0)</f>
+        <f>IF(A31="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A31)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A31))</f>
         <v/>
       </c>
       <c r="V31" s="16">
-        <f>U31*40</f>
+        <f>IF(A31="","",U31*40)</f>
         <v/>
       </c>
       <c r="W31" s="4" t="n"/>
       <c r="X31" s="4" t="n"/>
       <c r="Y31" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A31,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A31,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A31="","",SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A31,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A31,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="Z31" s="4" t="n"/>
       <c r="AA31" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A31,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A31="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A31,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AB31" s="4" t="n"/>
       <c r="AC31" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A31),0)</f>
+        <f>IF(A31="","",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A31))</f>
         <v/>
       </c>
       <c r="AD31" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A31),0)</f>
+        <f>IF(A31="","",SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A31))</f>
         <v/>
       </c>
       <c r="AE31" s="16">
-        <f>IF(AC31=0,0,AC31*1.7/12*AP31)</f>
+        <f>IF(A31="","",IF(AC31=0,0,AC31*1.7/12*AP31))</f>
         <v/>
       </c>
       <c r="AF31" s="16">
-        <f>IF(AD31=0,0,AD31*1.7/12*AQ31)</f>
+        <f>IF(A31="","",IF(AD31=0,0,AD31*1.7/12*AQ31))</f>
         <v/>
       </c>
       <c r="AG31" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A31,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A31,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A31="","",SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A31,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A31,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="AH31" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A31,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A31="","",SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A31,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AI31" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A31,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <f>IF(A31="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A31,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
       <c r="AJ31" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A31),0)</f>
+        <f>IF(A31="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A31))</f>
         <v/>
       </c>
       <c r="AK31" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A31),0)</f>
+        <f>IF(A31="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A31))</f>
         <v/>
       </c>
       <c r="AL31" s="16">
-        <f>(IF((AE31)&lt;(AG31+AH31+AI31),(AE31),(AG31+AH31+AI31)))+AJ31*5+AK31*10+R31+T31+V31</f>
+        <f>IF(A31="","",(IF((AE31)&lt;(AG31+AH31+AI31),(AE31),(AG31+AH31+AI31)))+AJ31*5+AK31*10+R31+T31+V31)</f>
         <v/>
       </c>
       <c r="AM31" s="16">
-        <f>AL31-J31</f>
+        <f>IF(A31="","",AL31-J31)</f>
         <v/>
       </c>
       <c r="AP31" s="16">
-        <f>IF(E31=0,"",(B31*0.95+C31*0.25+D31*0)/E31)</f>
+        <f>IF(A31="","",IF(E31=0,"",(B31*0.95+C31*0.25+D31*0)/E31))</f>
         <v/>
       </c>
       <c r="AQ31" s="16">
-        <f>IF(I31=0,"",(F31*0.95+G31*0.25+H31*0)/I31)</f>
+        <f>IF(A31="","",IF(I31=0,"",(F31*0.95+G31*0.25+H31*0)/I31))</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="16.25" customHeight="1">
       <c r="A32" s="16">
-        <f>IFERROR('SDA'!A78,"")</f>
+        <f>IF('SDA'!A78="","",'SDA'!A78)</f>
         <v/>
       </c>
       <c r="B32" s="16">
-        <f>IFERROR('SDA'!F78,0)</f>
+        <f>IF(A32="","",'SDA'!F78)</f>
         <v/>
       </c>
       <c r="C32" s="16">
-        <f>IFERROR('SDA'!G78,0)</f>
+        <f>IF(A32="","",'SDA'!G78)</f>
         <v/>
       </c>
       <c r="D32" s="16">
-        <f>IFERROR('SDA'!H78,0)</f>
+        <f>IF(A32="","",'SDA'!H78)</f>
         <v/>
       </c>
       <c r="E32" s="16">
-        <f>SUM(B32:D32)</f>
+        <f>IF(A32="","",SUM(B32:D32))</f>
         <v/>
       </c>
       <c r="F32" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A32,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A32,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <f>IF(A32="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A32,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A32,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"))</f>
         <v/>
       </c>
       <c r="G32" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A32,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <f>IF(A32="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A32,'SDA'!$C$4:$C$53,"Compacted (Open Space)"))</f>
         <v/>
       </c>
       <c r="H32" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A32,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <f>IF(A32="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A32,'SDA'!$C$4:$C$53,"Natural (Woods)"))</f>
         <v/>
       </c>
       <c r="I32" s="16">
-        <f>SUM(F32:H32)</f>
+        <f>IF(A32="","",SUM(F32:H32))</f>
         <v/>
       </c>
       <c r="J32" s="16">
-        <f>IF(E32=0,0,AP32*1.2/12*E32)</f>
+        <f>IF(A32="","",IF(E32=0,0,AP32*1.2/12*E32))</f>
         <v/>
       </c>
       <c r="K32" s="16">
-        <f>IF(I32=0,0,AQ32*1.2/12*I32)</f>
+        <f>IF(A32="","",IF(I32=0,0,AQ32*1.2/12*I32))</f>
         <v/>
       </c>
       <c r="L32" s="16">
-        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A32,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A32,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A32,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A32,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <f>IF(A32="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A32,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A32,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A32,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A32,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
         <v/>
       </c>
       <c r="M32" s="4" t="n"/>
       <c r="N32" s="4" t="n"/>
       <c r="O32" s="16">
-        <f>IFERROR(IFS(L32="A",2.5,L32="B",0.3,L32="C",0.1,L32="D",0.05,TRUE,""),"")</f>
+        <f>IF(A32="","",IFS(L32="A",2.5,L32="B",0.3,L32="C",0.1,L32="D",0.05,TRUE,""))</f>
         <v/>
       </c>
       <c r="P32" s="4" t="n"/>
       <c r="Q32" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A32),0)</f>
+        <f>IF(A32="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A32))</f>
         <v/>
       </c>
       <c r="R32" s="16">
-        <f>Q32*10</f>
+        <f>IF(A32="","",Q32*10)</f>
         <v/>
       </c>
       <c r="S32" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A32),0)</f>
+        <f>IF(A32="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A32))</f>
         <v/>
       </c>
       <c r="T32" s="16">
-        <f>S32*20</f>
+        <f>IF(A32="","",S32*20)</f>
         <v/>
       </c>
       <c r="U32" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A32)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A32),0)</f>
+        <f>IF(A32="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A32)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A32))</f>
         <v/>
       </c>
       <c r="V32" s="16">
-        <f>U32*40</f>
+        <f>IF(A32="","",U32*40)</f>
         <v/>
       </c>
       <c r="W32" s="4" t="n"/>
       <c r="X32" s="4" t="n"/>
       <c r="Y32" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A32,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A32,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A32="","",SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A32,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A32,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="Z32" s="4" t="n"/>
       <c r="AA32" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A32,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A32="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A32,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AB32" s="4" t="n"/>
       <c r="AC32" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A32),0)</f>
+        <f>IF(A32="","",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A32))</f>
         <v/>
       </c>
       <c r="AD32" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A32),0)</f>
+        <f>IF(A32="","",SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A32))</f>
         <v/>
       </c>
       <c r="AE32" s="16">
-        <f>IF(AC32=0,0,AC32*1.7/12*AP32)</f>
+        <f>IF(A32="","",IF(AC32=0,0,AC32*1.7/12*AP32))</f>
         <v/>
       </c>
       <c r="AF32" s="16">
-        <f>IF(AD32=0,0,AD32*1.7/12*AQ32)</f>
+        <f>IF(A32="","",IF(AD32=0,0,AD32*1.7/12*AQ32))</f>
         <v/>
       </c>
       <c r="AG32" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A32,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A32,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A32="","",SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A32,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A32,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="AH32" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A32,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A32="","",SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A32,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AI32" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A32,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <f>IF(A32="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A32,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
       <c r="AJ32" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A32),0)</f>
+        <f>IF(A32="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A32))</f>
         <v/>
       </c>
       <c r="AK32" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A32),0)</f>
+        <f>IF(A32="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A32))</f>
         <v/>
       </c>
       <c r="AL32" s="16">
-        <f>(IF((AE32)&lt;(AG32+AH32+AI32),(AE32),(AG32+AH32+AI32)))+AJ32*5+AK32*10+R32+T32+V32</f>
+        <f>IF(A32="","",(IF((AE32)&lt;(AG32+AH32+AI32),(AE32),(AG32+AH32+AI32)))+AJ32*5+AK32*10+R32+T32+V32)</f>
         <v/>
       </c>
       <c r="AM32" s="16">
-        <f>AL32-J32</f>
+        <f>IF(A32="","",AL32-J32)</f>
         <v/>
       </c>
       <c r="AP32" s="16">
-        <f>IF(E32=0,"",(B32*0.95+C32*0.25+D32*0)/E32)</f>
+        <f>IF(A32="","",IF(E32=0,"",(B32*0.95+C32*0.25+D32*0)/E32))</f>
         <v/>
       </c>
       <c r="AQ32" s="16">
-        <f>IF(I32=0,"",(F32*0.95+G32*0.25+H32*0)/I32)</f>
+        <f>IF(A32="","",IF(I32=0,"",(F32*0.95+G32*0.25+H32*0)/I32))</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="16.25" customHeight="1">
       <c r="A33" s="16">
-        <f>IFERROR('SDA'!A79,"")</f>
+        <f>IF('SDA'!A79="","",'SDA'!A79)</f>
         <v/>
       </c>
       <c r="B33" s="16">
-        <f>IFERROR('SDA'!F79,0)</f>
+        <f>IF(A33="","",'SDA'!F79)</f>
         <v/>
       </c>
       <c r="C33" s="16">
-        <f>IFERROR('SDA'!G79,0)</f>
+        <f>IF(A33="","",'SDA'!G79)</f>
         <v/>
       </c>
       <c r="D33" s="16">
-        <f>IFERROR('SDA'!H79,0)</f>
+        <f>IF(A33="","",'SDA'!H79)</f>
         <v/>
       </c>
       <c r="E33" s="16">
-        <f>SUM(B33:D33)</f>
+        <f>IF(A33="","",SUM(B33:D33))</f>
         <v/>
       </c>
       <c r="F33" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A33,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A33,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <f>IF(A33="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A33,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A33,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"))</f>
         <v/>
       </c>
       <c r="G33" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A33,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <f>IF(A33="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A33,'SDA'!$C$4:$C$53,"Compacted (Open Space)"))</f>
         <v/>
       </c>
       <c r="H33" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A33,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <f>IF(A33="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A33,'SDA'!$C$4:$C$53,"Natural (Woods)"))</f>
         <v/>
       </c>
       <c r="I33" s="16">
-        <f>SUM(F33:H33)</f>
+        <f>IF(A33="","",SUM(F33:H33))</f>
         <v/>
       </c>
       <c r="J33" s="16">
-        <f>IF(E33=0,0,AP33*1.2/12*E33)</f>
+        <f>IF(A33="","",IF(E33=0,0,AP33*1.2/12*E33))</f>
         <v/>
       </c>
       <c r="K33" s="16">
-        <f>IF(I33=0,0,AQ33*1.2/12*I33)</f>
+        <f>IF(A33="","",IF(I33=0,0,AQ33*1.2/12*I33))</f>
         <v/>
       </c>
       <c r="L33" s="16">
-        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A33,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A33,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A33,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A33,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <f>IF(A33="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A33,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A33,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A33,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A33,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
         <v/>
       </c>
       <c r="M33" s="4" t="n"/>
       <c r="N33" s="4" t="n"/>
       <c r="O33" s="16">
-        <f>IFERROR(IFS(L33="A",2.5,L33="B",0.3,L33="C",0.1,L33="D",0.05,TRUE,""),"")</f>
+        <f>IF(A33="","",IFS(L33="A",2.5,L33="B",0.3,L33="C",0.1,L33="D",0.05,TRUE,""))</f>
         <v/>
       </c>
       <c r="P33" s="4" t="n"/>
       <c r="Q33" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A33),0)</f>
+        <f>IF(A33="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A33))</f>
         <v/>
       </c>
       <c r="R33" s="16">
-        <f>Q33*10</f>
+        <f>IF(A33="","",Q33*10)</f>
         <v/>
       </c>
       <c r="S33" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A33),0)</f>
+        <f>IF(A33="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A33))</f>
         <v/>
       </c>
       <c r="T33" s="16">
-        <f>S33*20</f>
+        <f>IF(A33="","",S33*20)</f>
         <v/>
       </c>
       <c r="U33" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A33)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A33),0)</f>
+        <f>IF(A33="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A33)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A33))</f>
         <v/>
       </c>
       <c r="V33" s="16">
-        <f>U33*40</f>
+        <f>IF(A33="","",U33*40)</f>
         <v/>
       </c>
       <c r="W33" s="4" t="n"/>
       <c r="X33" s="4" t="n"/>
       <c r="Y33" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A33,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A33,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A33="","",SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A33,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A33,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="Z33" s="4" t="n"/>
       <c r="AA33" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A33,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A33="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A33,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AB33" s="4" t="n"/>
       <c r="AC33" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A33),0)</f>
+        <f>IF(A33="","",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A33))</f>
         <v/>
       </c>
       <c r="AD33" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A33),0)</f>
+        <f>IF(A33="","",SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A33))</f>
         <v/>
       </c>
       <c r="AE33" s="16">
-        <f>IF(AC33=0,0,AC33*1.7/12*AP33)</f>
+        <f>IF(A33="","",IF(AC33=0,0,AC33*1.7/12*AP33))</f>
         <v/>
       </c>
       <c r="AF33" s="16">
-        <f>IF(AD33=0,0,AD33*1.7/12*AQ33)</f>
+        <f>IF(A33="","",IF(AD33=0,0,AD33*1.7/12*AQ33))</f>
         <v/>
       </c>
       <c r="AG33" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A33,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A33,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A33="","",SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A33,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A33,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="AH33" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A33,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A33="","",SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A33,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AI33" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A33,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <f>IF(A33="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A33,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
       <c r="AJ33" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A33),0)</f>
+        <f>IF(A33="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A33))</f>
         <v/>
       </c>
       <c r="AK33" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A33),0)</f>
+        <f>IF(A33="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A33))</f>
         <v/>
       </c>
       <c r="AL33" s="16">
-        <f>(IF((AE33)&lt;(AG33+AH33+AI33),(AE33),(AG33+AH33+AI33)))+AJ33*5+AK33*10+R33+T33+V33</f>
+        <f>IF(A33="","",(IF((AE33)&lt;(AG33+AH33+AI33),(AE33),(AG33+AH33+AI33)))+AJ33*5+AK33*10+R33+T33+V33)</f>
         <v/>
       </c>
       <c r="AM33" s="16">
-        <f>AL33-J33</f>
+        <f>IF(A33="","",AL33-J33)</f>
         <v/>
       </c>
       <c r="AP33" s="16">
-        <f>IF(E33=0,"",(B33*0.95+C33*0.25+D33*0)/E33)</f>
+        <f>IF(A33="","",IF(E33=0,"",(B33*0.95+C33*0.25+D33*0)/E33))</f>
         <v/>
       </c>
       <c r="AQ33" s="16">
-        <f>IF(I33=0,"",(F33*0.95+G33*0.25+H33*0)/I33)</f>
+        <f>IF(A33="","",IF(I33=0,"",(F33*0.95+G33*0.25+H33*0)/I33))</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="16.25" customHeight="1">
       <c r="A34" s="16">
-        <f>IFERROR('SDA'!A80,"")</f>
+        <f>IF('SDA'!A80="","",'SDA'!A80)</f>
         <v/>
       </c>
       <c r="B34" s="16">
-        <f>IFERROR('SDA'!F80,0)</f>
+        <f>IF(A34="","",'SDA'!F80)</f>
         <v/>
       </c>
       <c r="C34" s="16">
-        <f>IFERROR('SDA'!G80,0)</f>
+        <f>IF(A34="","",'SDA'!G80)</f>
         <v/>
       </c>
       <c r="D34" s="16">
-        <f>IFERROR('SDA'!H80,0)</f>
+        <f>IF(A34="","",'SDA'!H80)</f>
         <v/>
       </c>
       <c r="E34" s="16">
-        <f>SUM(B34:D34)</f>
+        <f>IF(A34="","",SUM(B34:D34))</f>
         <v/>
       </c>
       <c r="F34" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A34,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A34,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <f>IF(A34="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A34,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A34,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"))</f>
         <v/>
       </c>
       <c r="G34" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A34,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <f>IF(A34="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A34,'SDA'!$C$4:$C$53,"Compacted (Open Space)"))</f>
         <v/>
       </c>
       <c r="H34" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A34,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <f>IF(A34="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A34,'SDA'!$C$4:$C$53,"Natural (Woods)"))</f>
         <v/>
       </c>
       <c r="I34" s="16">
-        <f>SUM(F34:H34)</f>
+        <f>IF(A34="","",SUM(F34:H34))</f>
         <v/>
       </c>
       <c r="J34" s="16">
-        <f>IF(E34=0,0,AP34*1.2/12*E34)</f>
+        <f>IF(A34="","",IF(E34=0,0,AP34*1.2/12*E34))</f>
         <v/>
       </c>
       <c r="K34" s="16">
-        <f>IF(I34=0,0,AQ34*1.2/12*I34)</f>
+        <f>IF(A34="","",IF(I34=0,0,AQ34*1.2/12*I34))</f>
         <v/>
       </c>
       <c r="L34" s="16">
-        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A34,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A34,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A34,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A34,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <f>IF(A34="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A34,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A34,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A34,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A34,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
         <v/>
       </c>
       <c r="M34" s="4" t="n"/>
       <c r="N34" s="4" t="n"/>
       <c r="O34" s="16">
-        <f>IFERROR(IFS(L34="A",2.5,L34="B",0.3,L34="C",0.1,L34="D",0.05,TRUE,""),"")</f>
+        <f>IF(A34="","",IFS(L34="A",2.5,L34="B",0.3,L34="C",0.1,L34="D",0.05,TRUE,""))</f>
         <v/>
       </c>
       <c r="P34" s="4" t="n"/>
       <c r="Q34" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A34),0)</f>
+        <f>IF(A34="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A34))</f>
         <v/>
       </c>
       <c r="R34" s="16">
-        <f>Q34*10</f>
+        <f>IF(A34="","",Q34*10)</f>
         <v/>
       </c>
       <c r="S34" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A34),0)</f>
+        <f>IF(A34="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A34))</f>
         <v/>
       </c>
       <c r="T34" s="16">
-        <f>S34*20</f>
+        <f>IF(A34="","",S34*20)</f>
         <v/>
       </c>
       <c r="U34" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A34)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A34),0)</f>
+        <f>IF(A34="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A34)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A34))</f>
         <v/>
       </c>
       <c r="V34" s="16">
-        <f>U34*40</f>
+        <f>IF(A34="","",U34*40)</f>
         <v/>
       </c>
       <c r="W34" s="4" t="n"/>
       <c r="X34" s="4" t="n"/>
       <c r="Y34" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A34,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A34,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A34="","",SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A34,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A34,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="Z34" s="4" t="n"/>
       <c r="AA34" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A34,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A34="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A34,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AB34" s="4" t="n"/>
       <c r="AC34" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A34),0)</f>
+        <f>IF(A34="","",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A34))</f>
         <v/>
       </c>
       <c r="AD34" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A34),0)</f>
+        <f>IF(A34="","",SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A34))</f>
         <v/>
       </c>
       <c r="AE34" s="16">
-        <f>IF(AC34=0,0,AC34*1.7/12*AP34)</f>
+        <f>IF(A34="","",IF(AC34=0,0,AC34*1.7/12*AP34))</f>
         <v/>
       </c>
       <c r="AF34" s="16">
-        <f>IF(AD34=0,0,AD34*1.7/12*AQ34)</f>
+        <f>IF(A34="","",IF(AD34=0,0,AD34*1.7/12*AQ34))</f>
         <v/>
       </c>
       <c r="AG34" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A34,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A34,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A34="","",SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A34,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A34,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="AH34" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A34,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A34="","",SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A34,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AI34" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A34,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <f>IF(A34="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A34,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
       <c r="AJ34" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A34),0)</f>
+        <f>IF(A34="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A34))</f>
         <v/>
       </c>
       <c r="AK34" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A34),0)</f>
+        <f>IF(A34="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A34))</f>
         <v/>
       </c>
       <c r="AL34" s="16">
-        <f>(IF((AE34)&lt;(AG34+AH34+AI34),(AE34),(AG34+AH34+AI34)))+AJ34*5+AK34*10+R34+T34+V34</f>
+        <f>IF(A34="","",(IF((AE34)&lt;(AG34+AH34+AI34),(AE34),(AG34+AH34+AI34)))+AJ34*5+AK34*10+R34+T34+V34)</f>
         <v/>
       </c>
       <c r="AM34" s="16">
-        <f>AL34-J34</f>
+        <f>IF(A34="","",AL34-J34)</f>
         <v/>
       </c>
       <c r="AP34" s="16">
-        <f>IF(E34=0,"",(B34*0.95+C34*0.25+D34*0)/E34)</f>
+        <f>IF(A34="","",IF(E34=0,"",(B34*0.95+C34*0.25+D34*0)/E34))</f>
         <v/>
       </c>
       <c r="AQ34" s="16">
-        <f>IF(I34=0,"",(F34*0.95+G34*0.25+H34*0)/I34)</f>
+        <f>IF(A34="","",IF(I34=0,"",(F34*0.95+G34*0.25+H34*0)/I34))</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="16.25" customHeight="1">
       <c r="A35" s="16">
-        <f>IFERROR('SDA'!A81,"")</f>
+        <f>IF('SDA'!A81="","",'SDA'!A81)</f>
         <v/>
       </c>
       <c r="B35" s="16">
-        <f>IFERROR('SDA'!F81,0)</f>
+        <f>IF(A35="","",'SDA'!F81)</f>
         <v/>
       </c>
       <c r="C35" s="16">
-        <f>IFERROR('SDA'!G81,0)</f>
+        <f>IF(A35="","",'SDA'!G81)</f>
         <v/>
       </c>
       <c r="D35" s="16">
-        <f>IFERROR('SDA'!H81,0)</f>
+        <f>IF(A35="","",'SDA'!H81)</f>
         <v/>
       </c>
       <c r="E35" s="16">
-        <f>SUM(B35:D35)</f>
+        <f>IF(A35="","",SUM(B35:D35))</f>
         <v/>
       </c>
       <c r="F35" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A35,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A35,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <f>IF(A35="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A35,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A35,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"))</f>
         <v/>
       </c>
       <c r="G35" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A35,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <f>IF(A35="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A35,'SDA'!$C$4:$C$53,"Compacted (Open Space)"))</f>
         <v/>
       </c>
       <c r="H35" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A35,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <f>IF(A35="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A35,'SDA'!$C$4:$C$53,"Natural (Woods)"))</f>
         <v/>
       </c>
       <c r="I35" s="16">
-        <f>SUM(F35:H35)</f>
+        <f>IF(A35="","",SUM(F35:H35))</f>
         <v/>
       </c>
       <c r="J35" s="16">
-        <f>IF(E35=0,0,AP35*1.2/12*E35)</f>
+        <f>IF(A35="","",IF(E35=0,0,AP35*1.2/12*E35))</f>
         <v/>
       </c>
       <c r="K35" s="16">
-        <f>IF(I35=0,0,AQ35*1.2/12*I35)</f>
+        <f>IF(A35="","",IF(I35=0,0,AQ35*1.2/12*I35))</f>
         <v/>
       </c>
       <c r="L35" s="16">
-        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A35,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A35,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A35,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A35,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <f>IF(A35="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A35,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A35,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A35,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A35,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
         <v/>
       </c>
       <c r="M35" s="4" t="n"/>
       <c r="N35" s="4" t="n"/>
       <c r="O35" s="16">
-        <f>IFERROR(IFS(L35="A",2.5,L35="B",0.3,L35="C",0.1,L35="D",0.05,TRUE,""),"")</f>
+        <f>IF(A35="","",IFS(L35="A",2.5,L35="B",0.3,L35="C",0.1,L35="D",0.05,TRUE,""))</f>
         <v/>
       </c>
       <c r="P35" s="4" t="n"/>
       <c r="Q35" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A35),0)</f>
+        <f>IF(A35="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A35))</f>
         <v/>
       </c>
       <c r="R35" s="16">
-        <f>Q35*10</f>
+        <f>IF(A35="","",Q35*10)</f>
         <v/>
       </c>
       <c r="S35" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A35),0)</f>
+        <f>IF(A35="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A35))</f>
         <v/>
       </c>
       <c r="T35" s="16">
-        <f>S35*20</f>
+        <f>IF(A35="","",S35*20)</f>
         <v/>
       </c>
       <c r="U35" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A35)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A35),0)</f>
+        <f>IF(A35="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A35)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A35))</f>
         <v/>
       </c>
       <c r="V35" s="16">
-        <f>U35*40</f>
+        <f>IF(A35="","",U35*40)</f>
         <v/>
       </c>
       <c r="W35" s="4" t="n"/>
       <c r="X35" s="4" t="n"/>
       <c r="Y35" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A35,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A35,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A35="","",SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A35,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A35,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="Z35" s="4" t="n"/>
       <c r="AA35" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A35,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A35="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A35,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AB35" s="4" t="n"/>
       <c r="AC35" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A35),0)</f>
+        <f>IF(A35="","",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A35))</f>
         <v/>
       </c>
       <c r="AD35" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A35),0)</f>
+        <f>IF(A35="","",SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A35))</f>
         <v/>
       </c>
       <c r="AE35" s="16">
-        <f>IF(AC35=0,0,AC35*1.7/12*AP35)</f>
+        <f>IF(A35="","",IF(AC35=0,0,AC35*1.7/12*AP35))</f>
         <v/>
       </c>
       <c r="AF35" s="16">
-        <f>IF(AD35=0,0,AD35*1.7/12*AQ35)</f>
+        <f>IF(A35="","",IF(AD35=0,0,AD35*1.7/12*AQ35))</f>
         <v/>
       </c>
       <c r="AG35" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A35,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A35,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A35="","",SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A35,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A35,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="AH35" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A35,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A35="","",SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A35,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AI35" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A35,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <f>IF(A35="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A35,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
       <c r="AJ35" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A35),0)</f>
+        <f>IF(A35="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A35))</f>
         <v/>
       </c>
       <c r="AK35" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A35),0)</f>
+        <f>IF(A35="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A35))</f>
         <v/>
       </c>
       <c r="AL35" s="16">
-        <f>(IF((AE35)&lt;(AG35+AH35+AI35),(AE35),(AG35+AH35+AI35)))+AJ35*5+AK35*10+R35+T35+V35</f>
+        <f>IF(A35="","",(IF((AE35)&lt;(AG35+AH35+AI35),(AE35),(AG35+AH35+AI35)))+AJ35*5+AK35*10+R35+T35+V35)</f>
         <v/>
       </c>
       <c r="AM35" s="16">
-        <f>AL35-J35</f>
+        <f>IF(A35="","",AL35-J35)</f>
         <v/>
       </c>
       <c r="AP35" s="16">
-        <f>IF(E35=0,"",(B35*0.95+C35*0.25+D35*0)/E35)</f>
+        <f>IF(A35="","",IF(E35=0,"",(B35*0.95+C35*0.25+D35*0)/E35))</f>
         <v/>
       </c>
       <c r="AQ35" s="16">
-        <f>IF(I35=0,"",(F35*0.95+G35*0.25+H35*0)/I35)</f>
+        <f>IF(A35="","",IF(I35=0,"",(F35*0.95+G35*0.25+H35*0)/I35))</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="16.25" customHeight="1">
       <c r="A36" s="16">
-        <f>IFERROR('SDA'!A82,"")</f>
+        <f>IF('SDA'!A82="","",'SDA'!A82)</f>
         <v/>
       </c>
       <c r="B36" s="16">
-        <f>IFERROR('SDA'!F82,0)</f>
+        <f>IF(A36="","",'SDA'!F82)</f>
         <v/>
       </c>
       <c r="C36" s="16">
-        <f>IFERROR('SDA'!G82,0)</f>
+        <f>IF(A36="","",'SDA'!G82)</f>
         <v/>
       </c>
       <c r="D36" s="16">
-        <f>IFERROR('SDA'!H82,0)</f>
+        <f>IF(A36="","",'SDA'!H82)</f>
         <v/>
       </c>
       <c r="E36" s="16">
-        <f>SUM(B36:D36)</f>
+        <f>IF(A36="","",SUM(B36:D36))</f>
         <v/>
       </c>
       <c r="F36" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A36,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A36,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <f>IF(A36="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A36,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A36,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"))</f>
         <v/>
       </c>
       <c r="G36" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A36,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <f>IF(A36="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A36,'SDA'!$C$4:$C$53,"Compacted (Open Space)"))</f>
         <v/>
       </c>
       <c r="H36" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A36,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <f>IF(A36="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A36,'SDA'!$C$4:$C$53,"Natural (Woods)"))</f>
         <v/>
       </c>
       <c r="I36" s="16">
-        <f>SUM(F36:H36)</f>
+        <f>IF(A36="","",SUM(F36:H36))</f>
         <v/>
       </c>
       <c r="J36" s="16">
-        <f>IF(E36=0,0,AP36*1.2/12*E36)</f>
+        <f>IF(A36="","",IF(E36=0,0,AP36*1.2/12*E36))</f>
         <v/>
       </c>
       <c r="K36" s="16">
-        <f>IF(I36=0,0,AQ36*1.2/12*I36)</f>
+        <f>IF(A36="","",IF(I36=0,0,AQ36*1.2/12*I36))</f>
         <v/>
       </c>
       <c r="L36" s="16">
-        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A36,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A36,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A36,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A36,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <f>IF(A36="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A36,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A36,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A36,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A36,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
         <v/>
       </c>
       <c r="M36" s="4" t="n"/>
       <c r="N36" s="4" t="n"/>
       <c r="O36" s="16">
-        <f>IFERROR(IFS(L36="A",2.5,L36="B",0.3,L36="C",0.1,L36="D",0.05,TRUE,""),"")</f>
+        <f>IF(A36="","",IFS(L36="A",2.5,L36="B",0.3,L36="C",0.1,L36="D",0.05,TRUE,""))</f>
         <v/>
       </c>
       <c r="P36" s="4" t="n"/>
       <c r="Q36" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A36),0)</f>
+        <f>IF(A36="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A36))</f>
         <v/>
       </c>
       <c r="R36" s="16">
-        <f>Q36*10</f>
+        <f>IF(A36="","",Q36*10)</f>
         <v/>
       </c>
       <c r="S36" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A36),0)</f>
+        <f>IF(A36="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A36))</f>
         <v/>
       </c>
       <c r="T36" s="16">
-        <f>S36*20</f>
+        <f>IF(A36="","",S36*20)</f>
         <v/>
       </c>
       <c r="U36" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A36)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A36),0)</f>
+        <f>IF(A36="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A36)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A36))</f>
         <v/>
       </c>
       <c r="V36" s="16">
-        <f>U36*40</f>
+        <f>IF(A36="","",U36*40)</f>
         <v/>
       </c>
       <c r="W36" s="4" t="n"/>
       <c r="X36" s="4" t="n"/>
       <c r="Y36" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A36,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A36,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A36="","",SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A36,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A36,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="Z36" s="4" t="n"/>
       <c r="AA36" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A36,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A36="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A36,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AB36" s="4" t="n"/>
       <c r="AC36" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A36),0)</f>
+        <f>IF(A36="","",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A36))</f>
         <v/>
       </c>
       <c r="AD36" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A36),0)</f>
+        <f>IF(A36="","",SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A36))</f>
         <v/>
       </c>
       <c r="AE36" s="16">
-        <f>IF(AC36=0,0,AC36*1.7/12*AP36)</f>
+        <f>IF(A36="","",IF(AC36=0,0,AC36*1.7/12*AP36))</f>
         <v/>
       </c>
       <c r="AF36" s="16">
-        <f>IF(AD36=0,0,AD36*1.7/12*AQ36)</f>
+        <f>IF(A36="","",IF(AD36=0,0,AD36*1.7/12*AQ36))</f>
         <v/>
       </c>
       <c r="AG36" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A36,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A36,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A36="","",SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A36,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A36,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="AH36" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A36,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A36="","",SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A36,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AI36" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A36,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <f>IF(A36="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A36,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
       <c r="AJ36" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A36),0)</f>
+        <f>IF(A36="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A36))</f>
         <v/>
       </c>
       <c r="AK36" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A36),0)</f>
+        <f>IF(A36="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A36))</f>
         <v/>
       </c>
       <c r="AL36" s="16">
-        <f>(IF((AE36)&lt;(AG36+AH36+AI36),(AE36),(AG36+AH36+AI36)))+AJ36*5+AK36*10+R36+T36+V36</f>
+        <f>IF(A36="","",(IF((AE36)&lt;(AG36+AH36+AI36),(AE36),(AG36+AH36+AI36)))+AJ36*5+AK36*10+R36+T36+V36)</f>
         <v/>
       </c>
       <c r="AM36" s="16">
-        <f>AL36-J36</f>
+        <f>IF(A36="","",AL36-J36)</f>
         <v/>
       </c>
       <c r="AP36" s="16">
-        <f>IF(E36=0,"",(B36*0.95+C36*0.25+D36*0)/E36)</f>
+        <f>IF(A36="","",IF(E36=0,"",(B36*0.95+C36*0.25+D36*0)/E36))</f>
         <v/>
       </c>
       <c r="AQ36" s="16">
-        <f>IF(I36=0,"",(F36*0.95+G36*0.25+H36*0)/I36)</f>
+        <f>IF(A36="","",IF(I36=0,"",(F36*0.95+G36*0.25+H36*0)/I36))</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="16.25" customHeight="1">
       <c r="A37" s="16">
-        <f>IFERROR('SDA'!A83,"")</f>
+        <f>IF('SDA'!A83="","",'SDA'!A83)</f>
         <v/>
       </c>
       <c r="B37" s="16">
-        <f>IFERROR('SDA'!F83,0)</f>
+        <f>IF(A37="","",'SDA'!F83)</f>
         <v/>
       </c>
       <c r="C37" s="16">
-        <f>IFERROR('SDA'!G83,0)</f>
+        <f>IF(A37="","",'SDA'!G83)</f>
         <v/>
       </c>
       <c r="D37" s="16">
-        <f>IFERROR('SDA'!H83,0)</f>
+        <f>IF(A37="","",'SDA'!H83)</f>
         <v/>
       </c>
       <c r="E37" s="16">
-        <f>SUM(B37:D37)</f>
+        <f>IF(A37="","",SUM(B37:D37))</f>
         <v/>
       </c>
       <c r="F37" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A37,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A37,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <f>IF(A37="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A37,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A37,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"))</f>
         <v/>
       </c>
       <c r="G37" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A37,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <f>IF(A37="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A37,'SDA'!$C$4:$C$53,"Compacted (Open Space)"))</f>
         <v/>
       </c>
       <c r="H37" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A37,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <f>IF(A37="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A37,'SDA'!$C$4:$C$53,"Natural (Woods)"))</f>
         <v/>
       </c>
       <c r="I37" s="16">
-        <f>SUM(F37:H37)</f>
+        <f>IF(A37="","",SUM(F37:H37))</f>
         <v/>
       </c>
       <c r="J37" s="16">
-        <f>IF(E37=0,0,AP37*1.2/12*E37)</f>
+        <f>IF(A37="","",IF(E37=0,0,AP37*1.2/12*E37))</f>
         <v/>
       </c>
       <c r="K37" s="16">
-        <f>IF(I37=0,0,AQ37*1.2/12*I37)</f>
+        <f>IF(A37="","",IF(I37=0,0,AQ37*1.2/12*I37))</f>
         <v/>
       </c>
       <c r="L37" s="16">
-        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A37,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A37,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A37,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A37,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <f>IF(A37="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A37,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A37,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A37,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A37,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
         <v/>
       </c>
       <c r="M37" s="4" t="n"/>
       <c r="N37" s="4" t="n"/>
       <c r="O37" s="16">
-        <f>IFERROR(IFS(L37="A",2.5,L37="B",0.3,L37="C",0.1,L37="D",0.05,TRUE,""),"")</f>
+        <f>IF(A37="","",IFS(L37="A",2.5,L37="B",0.3,L37="C",0.1,L37="D",0.05,TRUE,""))</f>
         <v/>
       </c>
       <c r="P37" s="4" t="n"/>
       <c r="Q37" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A37),0)</f>
+        <f>IF(A37="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A37))</f>
         <v/>
       </c>
       <c r="R37" s="16">
-        <f>Q37*10</f>
+        <f>IF(A37="","",Q37*10)</f>
         <v/>
       </c>
       <c r="S37" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A37),0)</f>
+        <f>IF(A37="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A37))</f>
         <v/>
       </c>
       <c r="T37" s="16">
-        <f>S37*20</f>
+        <f>IF(A37="","",S37*20)</f>
         <v/>
       </c>
       <c r="U37" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A37)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A37),0)</f>
+        <f>IF(A37="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A37)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A37))</f>
         <v/>
       </c>
       <c r="V37" s="16">
-        <f>U37*40</f>
+        <f>IF(A37="","",U37*40)</f>
         <v/>
       </c>
       <c r="W37" s="4" t="n"/>
       <c r="X37" s="4" t="n"/>
       <c r="Y37" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A37,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A37,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A37="","",SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A37,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A37,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="Z37" s="4" t="n"/>
       <c r="AA37" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A37,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A37="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A37,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AB37" s="4" t="n"/>
       <c r="AC37" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A37),0)</f>
+        <f>IF(A37="","",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A37))</f>
         <v/>
       </c>
       <c r="AD37" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A37),0)</f>
+        <f>IF(A37="","",SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A37))</f>
         <v/>
       </c>
       <c r="AE37" s="16">
-        <f>IF(AC37=0,0,AC37*1.7/12*AP37)</f>
+        <f>IF(A37="","",IF(AC37=0,0,AC37*1.7/12*AP37))</f>
         <v/>
       </c>
       <c r="AF37" s="16">
-        <f>IF(AD37=0,0,AD37*1.7/12*AQ37)</f>
+        <f>IF(A37="","",IF(AD37=0,0,AD37*1.7/12*AQ37))</f>
         <v/>
       </c>
       <c r="AG37" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A37,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A37,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A37="","",SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A37,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A37,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="AH37" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A37,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A37="","",SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A37,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AI37" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A37,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <f>IF(A37="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A37,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
       <c r="AJ37" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A37),0)</f>
+        <f>IF(A37="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A37))</f>
         <v/>
       </c>
       <c r="AK37" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A37),0)</f>
+        <f>IF(A37="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A37))</f>
         <v/>
       </c>
       <c r="AL37" s="16">
-        <f>(IF((AE37)&lt;(AG37+AH37+AI37),(AE37),(AG37+AH37+AI37)))+AJ37*5+AK37*10+R37+T37+V37</f>
+        <f>IF(A37="","",(IF((AE37)&lt;(AG37+AH37+AI37),(AE37),(AG37+AH37+AI37)))+AJ37*5+AK37*10+R37+T37+V37)</f>
         <v/>
       </c>
       <c r="AM37" s="16">
-        <f>AL37-J37</f>
+        <f>IF(A37="","",AL37-J37)</f>
         <v/>
       </c>
       <c r="AP37" s="16">
-        <f>IF(E37=0,"",(B37*0.95+C37*0.25+D37*0)/E37)</f>
+        <f>IF(A37="","",IF(E37=0,"",(B37*0.95+C37*0.25+D37*0)/E37))</f>
         <v/>
       </c>
       <c r="AQ37" s="16">
-        <f>IF(I37=0,"",(F37*0.95+G37*0.25+H37*0)/I37)</f>
+        <f>IF(A37="","",IF(I37=0,"",(F37*0.95+G37*0.25+H37*0)/I37))</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="16.25" customHeight="1">
       <c r="A38" s="16">
-        <f>IFERROR('SDA'!A84,"")</f>
+        <f>IF('SDA'!A84="","",'SDA'!A84)</f>
         <v/>
       </c>
       <c r="B38" s="16">
-        <f>IFERROR('SDA'!F84,0)</f>
+        <f>IF(A38="","",'SDA'!F84)</f>
         <v/>
       </c>
       <c r="C38" s="16">
-        <f>IFERROR('SDA'!G84,0)</f>
+        <f>IF(A38="","",'SDA'!G84)</f>
         <v/>
       </c>
       <c r="D38" s="16">
-        <f>IFERROR('SDA'!H84,0)</f>
+        <f>IF(A38="","",'SDA'!H84)</f>
         <v/>
       </c>
       <c r="E38" s="16">
-        <f>SUM(B38:D38)</f>
+        <f>IF(A38="","",SUM(B38:D38))</f>
         <v/>
       </c>
       <c r="F38" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A38,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A38,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <f>IF(A38="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A38,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A38,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"))</f>
         <v/>
       </c>
       <c r="G38" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A38,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <f>IF(A38="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A38,'SDA'!$C$4:$C$53,"Compacted (Open Space)"))</f>
         <v/>
       </c>
       <c r="H38" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A38,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <f>IF(A38="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A38,'SDA'!$C$4:$C$53,"Natural (Woods)"))</f>
         <v/>
       </c>
       <c r="I38" s="16">
-        <f>SUM(F38:H38)</f>
+        <f>IF(A38="","",SUM(F38:H38))</f>
         <v/>
       </c>
       <c r="J38" s="16">
-        <f>IF(E38=0,0,AP38*1.2/12*E38)</f>
+        <f>IF(A38="","",IF(E38=0,0,AP38*1.2/12*E38))</f>
         <v/>
       </c>
       <c r="K38" s="16">
-        <f>IF(I38=0,0,AQ38*1.2/12*I38)</f>
+        <f>IF(A38="","",IF(I38=0,0,AQ38*1.2/12*I38))</f>
         <v/>
       </c>
       <c r="L38" s="16">
-        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A38,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A38,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A38,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A38,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <f>IF(A38="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A38,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A38,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A38,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A38,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
         <v/>
       </c>
       <c r="M38" s="4" t="n"/>
       <c r="N38" s="4" t="n"/>
       <c r="O38" s="16">
-        <f>IFERROR(IFS(L38="A",2.5,L38="B",0.3,L38="C",0.1,L38="D",0.05,TRUE,""),"")</f>
+        <f>IF(A38="","",IFS(L38="A",2.5,L38="B",0.3,L38="C",0.1,L38="D",0.05,TRUE,""))</f>
         <v/>
       </c>
       <c r="P38" s="4" t="n"/>
       <c r="Q38" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A38),0)</f>
+        <f>IF(A38="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A38))</f>
         <v/>
       </c>
       <c r="R38" s="16">
-        <f>Q38*10</f>
+        <f>IF(A38="","",Q38*10)</f>
         <v/>
       </c>
       <c r="S38" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A38),0)</f>
+        <f>IF(A38="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A38))</f>
         <v/>
       </c>
       <c r="T38" s="16">
-        <f>S38*20</f>
+        <f>IF(A38="","",S38*20)</f>
         <v/>
       </c>
       <c r="U38" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A38)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A38),0)</f>
+        <f>IF(A38="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A38)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A38))</f>
         <v/>
       </c>
       <c r="V38" s="16">
-        <f>U38*40</f>
+        <f>IF(A38="","",U38*40)</f>
         <v/>
       </c>
       <c r="W38" s="4" t="n"/>
       <c r="X38" s="4" t="n"/>
       <c r="Y38" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A38,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A38,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A38="","",SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A38,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A38,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="Z38" s="4" t="n"/>
       <c r="AA38" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A38,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A38="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A38,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AB38" s="4" t="n"/>
       <c r="AC38" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A38),0)</f>
+        <f>IF(A38="","",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A38))</f>
         <v/>
       </c>
       <c r="AD38" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A38),0)</f>
+        <f>IF(A38="","",SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A38))</f>
         <v/>
       </c>
       <c r="AE38" s="16">
-        <f>IF(AC38=0,0,AC38*1.7/12*AP38)</f>
+        <f>IF(A38="","",IF(AC38=0,0,AC38*1.7/12*AP38))</f>
         <v/>
       </c>
       <c r="AF38" s="16">
-        <f>IF(AD38=0,0,AD38*1.7/12*AQ38)</f>
+        <f>IF(A38="","",IF(AD38=0,0,AD38*1.7/12*AQ38))</f>
         <v/>
       </c>
       <c r="AG38" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A38,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A38,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A38="","",SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A38,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A38,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="AH38" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A38,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A38="","",SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A38,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AI38" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A38,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <f>IF(A38="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A38,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
       <c r="AJ38" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A38),0)</f>
+        <f>IF(A38="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A38))</f>
         <v/>
       </c>
       <c r="AK38" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A38),0)</f>
+        <f>IF(A38="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A38))</f>
         <v/>
       </c>
       <c r="AL38" s="16">
-        <f>(IF((AE38)&lt;(AG38+AH38+AI38),(AE38),(AG38+AH38+AI38)))+AJ38*5+AK38*10+R38+T38+V38</f>
+        <f>IF(A38="","",(IF((AE38)&lt;(AG38+AH38+AI38),(AE38),(AG38+AH38+AI38)))+AJ38*5+AK38*10+R38+T38+V38)</f>
         <v/>
       </c>
       <c r="AM38" s="16">
-        <f>AL38-J38</f>
+        <f>IF(A38="","",AL38-J38)</f>
         <v/>
       </c>
       <c r="AP38" s="16">
-        <f>IF(E38=0,"",(B38*0.95+C38*0.25+D38*0)/E38)</f>
+        <f>IF(A38="","",IF(E38=0,"",(B38*0.95+C38*0.25+D38*0)/E38))</f>
         <v/>
       </c>
       <c r="AQ38" s="16">
-        <f>IF(I38=0,"",(F38*0.95+G38*0.25+H38*0)/I38)</f>
+        <f>IF(A38="","",IF(I38=0,"",(F38*0.95+G38*0.25+H38*0)/I38))</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="16.25" customHeight="1">
       <c r="A39" s="16">
-        <f>IFERROR('SDA'!A85,"")</f>
+        <f>IF('SDA'!A85="","",'SDA'!A85)</f>
         <v/>
       </c>
       <c r="B39" s="16">
-        <f>IFERROR('SDA'!F85,0)</f>
+        <f>IF(A39="","",'SDA'!F85)</f>
         <v/>
       </c>
       <c r="C39" s="16">
-        <f>IFERROR('SDA'!G85,0)</f>
+        <f>IF(A39="","",'SDA'!G85)</f>
         <v/>
       </c>
       <c r="D39" s="16">
-        <f>IFERROR('SDA'!H85,0)</f>
+        <f>IF(A39="","",'SDA'!H85)</f>
         <v/>
       </c>
       <c r="E39" s="16">
-        <f>SUM(B39:D39)</f>
+        <f>IF(A39="","",SUM(B39:D39))</f>
         <v/>
       </c>
       <c r="F39" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A39,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A39,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <f>IF(A39="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A39,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A39,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"))</f>
         <v/>
       </c>
       <c r="G39" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A39,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <f>IF(A39="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A39,'SDA'!$C$4:$C$53,"Compacted (Open Space)"))</f>
         <v/>
       </c>
       <c r="H39" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A39,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <f>IF(A39="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A39,'SDA'!$C$4:$C$53,"Natural (Woods)"))</f>
         <v/>
       </c>
       <c r="I39" s="16">
-        <f>SUM(F39:H39)</f>
+        <f>IF(A39="","",SUM(F39:H39))</f>
         <v/>
       </c>
       <c r="J39" s="16">
-        <f>IF(E39=0,0,AP39*1.2/12*E39)</f>
+        <f>IF(A39="","",IF(E39=0,0,AP39*1.2/12*E39))</f>
         <v/>
       </c>
       <c r="K39" s="16">
-        <f>IF(I39=0,0,AQ39*1.2/12*I39)</f>
+        <f>IF(A39="","",IF(I39=0,0,AQ39*1.2/12*I39))</f>
         <v/>
       </c>
       <c r="L39" s="16">
-        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A39,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A39,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A39,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A39,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <f>IF(A39="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A39,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A39,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A39,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A39,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
         <v/>
       </c>
       <c r="M39" s="4" t="n"/>
       <c r="N39" s="4" t="n"/>
       <c r="O39" s="16">
-        <f>IFERROR(IFS(L39="A",2.5,L39="B",0.3,L39="C",0.1,L39="D",0.05,TRUE,""),"")</f>
+        <f>IF(A39="","",IFS(L39="A",2.5,L39="B",0.3,L39="C",0.1,L39="D",0.05,TRUE,""))</f>
         <v/>
       </c>
       <c r="P39" s="4" t="n"/>
       <c r="Q39" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A39),0)</f>
+        <f>IF(A39="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A39))</f>
         <v/>
       </c>
       <c r="R39" s="16">
-        <f>Q39*10</f>
+        <f>IF(A39="","",Q39*10)</f>
         <v/>
       </c>
       <c r="S39" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A39),0)</f>
+        <f>IF(A39="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A39))</f>
         <v/>
       </c>
       <c r="T39" s="16">
-        <f>S39*20</f>
+        <f>IF(A39="","",S39*20)</f>
         <v/>
       </c>
       <c r="U39" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A39)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A39),0)</f>
+        <f>IF(A39="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A39)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A39))</f>
         <v/>
       </c>
       <c r="V39" s="16">
-        <f>U39*40</f>
+        <f>IF(A39="","",U39*40)</f>
         <v/>
       </c>
       <c r="W39" s="4" t="n"/>
       <c r="X39" s="4" t="n"/>
       <c r="Y39" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A39,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A39,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A39="","",SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A39,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A39,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="Z39" s="4" t="n"/>
       <c r="AA39" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A39,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A39="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A39,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AB39" s="4" t="n"/>
       <c r="AC39" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A39),0)</f>
+        <f>IF(A39="","",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A39))</f>
         <v/>
       </c>
       <c r="AD39" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A39),0)</f>
+        <f>IF(A39="","",SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A39))</f>
         <v/>
       </c>
       <c r="AE39" s="16">
-        <f>IF(AC39=0,0,AC39*1.7/12*AP39)</f>
+        <f>IF(A39="","",IF(AC39=0,0,AC39*1.7/12*AP39))</f>
         <v/>
       </c>
       <c r="AF39" s="16">
-        <f>IF(AD39=0,0,AD39*1.7/12*AQ39)</f>
+        <f>IF(A39="","",IF(AD39=0,0,AD39*1.7/12*AQ39))</f>
         <v/>
       </c>
       <c r="AG39" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A39,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A39,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A39="","",SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A39,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A39,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="AH39" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A39,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A39="","",SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A39,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AI39" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A39,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <f>IF(A39="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A39,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
       <c r="AJ39" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A39),0)</f>
+        <f>IF(A39="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A39))</f>
         <v/>
       </c>
       <c r="AK39" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A39),0)</f>
+        <f>IF(A39="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A39))</f>
         <v/>
       </c>
       <c r="AL39" s="16">
-        <f>(IF((AE39)&lt;(AG39+AH39+AI39),(AE39),(AG39+AH39+AI39)))+AJ39*5+AK39*10+R39+T39+V39</f>
+        <f>IF(A39="","",(IF((AE39)&lt;(AG39+AH39+AI39),(AE39),(AG39+AH39+AI39)))+AJ39*5+AK39*10+R39+T39+V39)</f>
         <v/>
       </c>
       <c r="AM39" s="16">
-        <f>AL39-J39</f>
+        <f>IF(A39="","",AL39-J39)</f>
         <v/>
       </c>
       <c r="AP39" s="16">
-        <f>IF(E39=0,"",(B39*0.95+C39*0.25+D39*0)/E39)</f>
+        <f>IF(A39="","",IF(E39=0,"",(B39*0.95+C39*0.25+D39*0)/E39))</f>
         <v/>
       </c>
       <c r="AQ39" s="16">
-        <f>IF(I39=0,"",(F39*0.95+G39*0.25+H39*0)/I39)</f>
+        <f>IF(A39="","",IF(I39=0,"",(F39*0.95+G39*0.25+H39*0)/I39))</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="16.25" customHeight="1">
       <c r="A40" s="16">
-        <f>IFERROR('SDA'!A86,"")</f>
+        <f>IF('SDA'!A86="","",'SDA'!A86)</f>
         <v/>
       </c>
       <c r="B40" s="16">
-        <f>IFERROR('SDA'!F86,0)</f>
+        <f>IF(A40="","",'SDA'!F86)</f>
         <v/>
       </c>
       <c r="C40" s="16">
-        <f>IFERROR('SDA'!G86,0)</f>
+        <f>IF(A40="","",'SDA'!G86)</f>
         <v/>
       </c>
       <c r="D40" s="16">
-        <f>IFERROR('SDA'!H86,0)</f>
+        <f>IF(A40="","",'SDA'!H86)</f>
         <v/>
       </c>
       <c r="E40" s="16">
-        <f>SUM(B40:D40)</f>
+        <f>IF(A40="","",SUM(B40:D40))</f>
         <v/>
       </c>
       <c r="F40" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A40,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A40,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <f>IF(A40="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A40,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A40,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"))</f>
         <v/>
       </c>
       <c r="G40" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A40,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <f>IF(A40="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A40,'SDA'!$C$4:$C$53,"Compacted (Open Space)"))</f>
         <v/>
       </c>
       <c r="H40" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A40,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <f>IF(A40="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A40,'SDA'!$C$4:$C$53,"Natural (Woods)"))</f>
         <v/>
       </c>
       <c r="I40" s="16">
-        <f>SUM(F40:H40)</f>
+        <f>IF(A40="","",SUM(F40:H40))</f>
         <v/>
       </c>
       <c r="J40" s="16">
-        <f>IF(E40=0,0,AP40*1.2/12*E40)</f>
+        <f>IF(A40="","",IF(E40=0,0,AP40*1.2/12*E40))</f>
         <v/>
       </c>
       <c r="K40" s="16">
-        <f>IF(I40=0,0,AQ40*1.2/12*I40)</f>
+        <f>IF(A40="","",IF(I40=0,0,AQ40*1.2/12*I40))</f>
         <v/>
       </c>
       <c r="L40" s="16">
-        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A40,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A40,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A40,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A40,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <f>IF(A40="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A40,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A40,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A40,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A40,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
         <v/>
       </c>
       <c r="M40" s="4" t="n"/>
       <c r="N40" s="4" t="n"/>
       <c r="O40" s="16">
-        <f>IFERROR(IFS(L40="A",2.5,L40="B",0.3,L40="C",0.1,L40="D",0.05,TRUE,""),"")</f>
+        <f>IF(A40="","",IFS(L40="A",2.5,L40="B",0.3,L40="C",0.1,L40="D",0.05,TRUE,""))</f>
         <v/>
       </c>
       <c r="P40" s="4" t="n"/>
       <c r="Q40" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A40),0)</f>
+        <f>IF(A40="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A40))</f>
         <v/>
       </c>
       <c r="R40" s="16">
-        <f>Q40*10</f>
+        <f>IF(A40="","",Q40*10)</f>
         <v/>
       </c>
       <c r="S40" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A40),0)</f>
+        <f>IF(A40="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A40))</f>
         <v/>
       </c>
       <c r="T40" s="16">
-        <f>S40*20</f>
+        <f>IF(A40="","",S40*20)</f>
         <v/>
       </c>
       <c r="U40" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A40)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A40),0)</f>
+        <f>IF(A40="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A40)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A40))</f>
         <v/>
       </c>
       <c r="V40" s="16">
-        <f>U40*40</f>
+        <f>IF(A40="","",U40*40)</f>
         <v/>
       </c>
       <c r="W40" s="4" t="n"/>
       <c r="X40" s="4" t="n"/>
       <c r="Y40" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A40,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A40,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A40="","",SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A40,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A40,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="Z40" s="4" t="n"/>
       <c r="AA40" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A40,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A40="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A40,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AB40" s="4" t="n"/>
       <c r="AC40" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A40),0)</f>
+        <f>IF(A40="","",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A40))</f>
         <v/>
       </c>
       <c r="AD40" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A40),0)</f>
+        <f>IF(A40="","",SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A40))</f>
         <v/>
       </c>
       <c r="AE40" s="16">
-        <f>IF(AC40=0,0,AC40*1.7/12*AP40)</f>
+        <f>IF(A40="","",IF(AC40=0,0,AC40*1.7/12*AP40))</f>
         <v/>
       </c>
       <c r="AF40" s="16">
-        <f>IF(AD40=0,0,AD40*1.7/12*AQ40)</f>
+        <f>IF(A40="","",IF(AD40=0,0,AD40*1.7/12*AQ40))</f>
         <v/>
       </c>
       <c r="AG40" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A40,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A40,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A40="","",SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A40,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A40,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="AH40" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A40,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A40="","",SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A40,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AI40" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A40,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <f>IF(A40="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A40,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
       <c r="AJ40" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A40),0)</f>
+        <f>IF(A40="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A40))</f>
         <v/>
       </c>
       <c r="AK40" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A40),0)</f>
+        <f>IF(A40="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A40))</f>
         <v/>
       </c>
       <c r="AL40" s="16">
-        <f>(IF((AE40)&lt;(AG40+AH40+AI40),(AE40),(AG40+AH40+AI40)))+AJ40*5+AK40*10+R40+T40+V40</f>
+        <f>IF(A40="","",(IF((AE40)&lt;(AG40+AH40+AI40),(AE40),(AG40+AH40+AI40)))+AJ40*5+AK40*10+R40+T40+V40)</f>
         <v/>
       </c>
       <c r="AM40" s="16">
-        <f>AL40-J40</f>
+        <f>IF(A40="","",AL40-J40)</f>
         <v/>
       </c>
       <c r="AP40" s="16">
-        <f>IF(E40=0,"",(B40*0.95+C40*0.25+D40*0)/E40)</f>
+        <f>IF(A40="","",IF(E40=0,"",(B40*0.95+C40*0.25+D40*0)/E40))</f>
         <v/>
       </c>
       <c r="AQ40" s="16">
-        <f>IF(I40=0,"",(F40*0.95+G40*0.25+H40*0)/I40)</f>
+        <f>IF(A40="","",IF(I40=0,"",(F40*0.95+G40*0.25+H40*0)/I40))</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="16.25" customHeight="1">
       <c r="A41" s="16">
-        <f>IFERROR('SDA'!A87,"")</f>
+        <f>IF('SDA'!A87="","",'SDA'!A87)</f>
         <v/>
       </c>
       <c r="B41" s="16">
-        <f>IFERROR('SDA'!F87,0)</f>
+        <f>IF(A41="","",'SDA'!F87)</f>
         <v/>
       </c>
       <c r="C41" s="16">
-        <f>IFERROR('SDA'!G87,0)</f>
+        <f>IF(A41="","",'SDA'!G87)</f>
         <v/>
       </c>
       <c r="D41" s="16">
-        <f>IFERROR('SDA'!H87,0)</f>
+        <f>IF(A41="","",'SDA'!H87)</f>
         <v/>
       </c>
       <c r="E41" s="16">
-        <f>SUM(B41:D41)</f>
+        <f>IF(A41="","",SUM(B41:D41))</f>
         <v/>
       </c>
       <c r="F41" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A41,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A41,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <f>IF(A41="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A41,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A41,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"))</f>
         <v/>
       </c>
       <c r="G41" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A41,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <f>IF(A41="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A41,'SDA'!$C$4:$C$53,"Compacted (Open Space)"))</f>
         <v/>
       </c>
       <c r="H41" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A41,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <f>IF(A41="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A41,'SDA'!$C$4:$C$53,"Natural (Woods)"))</f>
         <v/>
       </c>
       <c r="I41" s="16">
-        <f>SUM(F41:H41)</f>
+        <f>IF(A41="","",SUM(F41:H41))</f>
         <v/>
       </c>
       <c r="J41" s="16">
-        <f>IF(E41=0,0,AP41*1.2/12*E41)</f>
+        <f>IF(A41="","",IF(E41=0,0,AP41*1.2/12*E41))</f>
         <v/>
       </c>
       <c r="K41" s="16">
-        <f>IF(I41=0,0,AQ41*1.2/12*I41)</f>
+        <f>IF(A41="","",IF(I41=0,0,AQ41*1.2/12*I41))</f>
         <v/>
       </c>
       <c r="L41" s="16">
-        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A41,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A41,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A41,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A41,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <f>IF(A41="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A41,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A41,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A41,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A41,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
         <v/>
       </c>
       <c r="M41" s="4" t="n"/>
       <c r="N41" s="4" t="n"/>
       <c r="O41" s="16">
-        <f>IFERROR(IFS(L41="A",2.5,L41="B",0.3,L41="C",0.1,L41="D",0.05,TRUE,""),"")</f>
+        <f>IF(A41="","",IFS(L41="A",2.5,L41="B",0.3,L41="C",0.1,L41="D",0.05,TRUE,""))</f>
         <v/>
       </c>
       <c r="P41" s="4" t="n"/>
       <c r="Q41" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A41),0)</f>
+        <f>IF(A41="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A41))</f>
         <v/>
       </c>
       <c r="R41" s="16">
-        <f>Q41*10</f>
+        <f>IF(A41="","",Q41*10)</f>
         <v/>
       </c>
       <c r="S41" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A41),0)</f>
+        <f>IF(A41="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A41))</f>
         <v/>
       </c>
       <c r="T41" s="16">
-        <f>S41*20</f>
+        <f>IF(A41="","",S41*20)</f>
         <v/>
       </c>
       <c r="U41" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A41)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A41),0)</f>
+        <f>IF(A41="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A41)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A41))</f>
         <v/>
       </c>
       <c r="V41" s="16">
-        <f>U41*40</f>
+        <f>IF(A41="","",U41*40)</f>
         <v/>
       </c>
       <c r="W41" s="4" t="n"/>
       <c r="X41" s="4" t="n"/>
       <c r="Y41" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A41,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A41,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A41="","",SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A41,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A41,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="Z41" s="4" t="n"/>
       <c r="AA41" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A41,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A41="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A41,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AB41" s="4" t="n"/>
       <c r="AC41" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A41),0)</f>
+        <f>IF(A41="","",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A41))</f>
         <v/>
       </c>
       <c r="AD41" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A41),0)</f>
+        <f>IF(A41="","",SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A41))</f>
         <v/>
       </c>
       <c r="AE41" s="16">
-        <f>IF(AC41=0,0,AC41*1.7/12*AP41)</f>
+        <f>IF(A41="","",IF(AC41=0,0,AC41*1.7/12*AP41))</f>
         <v/>
       </c>
       <c r="AF41" s="16">
-        <f>IF(AD41=0,0,AD41*1.7/12*AQ41)</f>
+        <f>IF(A41="","",IF(AD41=0,0,AD41*1.7/12*AQ41))</f>
         <v/>
       </c>
       <c r="AG41" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A41,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A41,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A41="","",SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A41,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A41,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="AH41" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A41,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A41="","",SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A41,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AI41" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A41,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <f>IF(A41="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A41,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
       <c r="AJ41" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A41),0)</f>
+        <f>IF(A41="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A41))</f>
         <v/>
       </c>
       <c r="AK41" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A41),0)</f>
+        <f>IF(A41="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A41))</f>
         <v/>
       </c>
       <c r="AL41" s="16">
-        <f>(IF((AE41)&lt;(AG41+AH41+AI41),(AE41),(AG41+AH41+AI41)))+AJ41*5+AK41*10+R41+T41+V41</f>
+        <f>IF(A41="","",(IF((AE41)&lt;(AG41+AH41+AI41),(AE41),(AG41+AH41+AI41)))+AJ41*5+AK41*10+R41+T41+V41)</f>
         <v/>
       </c>
       <c r="AM41" s="16">
-        <f>AL41-J41</f>
+        <f>IF(A41="","",AL41-J41)</f>
         <v/>
       </c>
       <c r="AP41" s="16">
-        <f>IF(E41=0,"",(B41*0.95+C41*0.25+D41*0)/E41)</f>
+        <f>IF(A41="","",IF(E41=0,"",(B41*0.95+C41*0.25+D41*0)/E41))</f>
         <v/>
       </c>
       <c r="AQ41" s="16">
-        <f>IF(I41=0,"",(F41*0.95+G41*0.25+H41*0)/I41)</f>
+        <f>IF(A41="","",IF(I41=0,"",(F41*0.95+G41*0.25+H41*0)/I41))</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="16.25" customHeight="1">
       <c r="A42" s="16">
-        <f>IFERROR('SDA'!A88,"")</f>
+        <f>IF('SDA'!A88="","",'SDA'!A88)</f>
         <v/>
       </c>
       <c r="B42" s="16">
-        <f>IFERROR('SDA'!F88,0)</f>
+        <f>IF(A42="","",'SDA'!F88)</f>
         <v/>
       </c>
       <c r="C42" s="16">
-        <f>IFERROR('SDA'!G88,0)</f>
+        <f>IF(A42="","",'SDA'!G88)</f>
         <v/>
       </c>
       <c r="D42" s="16">
-        <f>IFERROR('SDA'!H88,0)</f>
+        <f>IF(A42="","",'SDA'!H88)</f>
         <v/>
       </c>
       <c r="E42" s="16">
-        <f>SUM(B42:D42)</f>
+        <f>IF(A42="","",SUM(B42:D42))</f>
         <v/>
       </c>
       <c r="F42" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A42,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A42,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <f>IF(A42="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A42,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A42,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"))</f>
         <v/>
       </c>
       <c r="G42" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A42,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <f>IF(A42="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A42,'SDA'!$C$4:$C$53,"Compacted (Open Space)"))</f>
         <v/>
       </c>
       <c r="H42" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A42,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <f>IF(A42="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A42,'SDA'!$C$4:$C$53,"Natural (Woods)"))</f>
         <v/>
       </c>
       <c r="I42" s="16">
-        <f>SUM(F42:H42)</f>
+        <f>IF(A42="","",SUM(F42:H42))</f>
         <v/>
       </c>
       <c r="J42" s="16">
-        <f>IF(E42=0,0,AP42*1.2/12*E42)</f>
+        <f>IF(A42="","",IF(E42=0,0,AP42*1.2/12*E42))</f>
         <v/>
       </c>
       <c r="K42" s="16">
-        <f>IF(I42=0,0,AQ42*1.2/12*I42)</f>
+        <f>IF(A42="","",IF(I42=0,0,AQ42*1.2/12*I42))</f>
         <v/>
       </c>
       <c r="L42" s="16">
-        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A42,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A42,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A42,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A42,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <f>IF(A42="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A42,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A42,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A42,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A42,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
         <v/>
       </c>
       <c r="M42" s="4" t="n"/>
       <c r="N42" s="4" t="n"/>
       <c r="O42" s="16">
-        <f>IFERROR(IFS(L42="A",2.5,L42="B",0.3,L42="C",0.1,L42="D",0.05,TRUE,""),"")</f>
+        <f>IF(A42="","",IFS(L42="A",2.5,L42="B",0.3,L42="C",0.1,L42="D",0.05,TRUE,""))</f>
         <v/>
       </c>
       <c r="P42" s="4" t="n"/>
       <c r="Q42" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A42),0)</f>
+        <f>IF(A42="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A42))</f>
         <v/>
       </c>
       <c r="R42" s="16">
-        <f>Q42*10</f>
+        <f>IF(A42="","",Q42*10)</f>
         <v/>
       </c>
       <c r="S42" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A42),0)</f>
+        <f>IF(A42="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A42))</f>
         <v/>
       </c>
       <c r="T42" s="16">
-        <f>S42*20</f>
+        <f>IF(A42="","",S42*20)</f>
         <v/>
       </c>
       <c r="U42" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A42)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A42),0)</f>
+        <f>IF(A42="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A42)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A42))</f>
         <v/>
       </c>
       <c r="V42" s="16">
-        <f>U42*40</f>
+        <f>IF(A42="","",U42*40)</f>
         <v/>
       </c>
       <c r="W42" s="4" t="n"/>
       <c r="X42" s="4" t="n"/>
       <c r="Y42" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A42,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A42,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A42="","",SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A42,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A42,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="Z42" s="4" t="n"/>
       <c r="AA42" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A42,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A42="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A42,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AB42" s="4" t="n"/>
       <c r="AC42" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A42),0)</f>
+        <f>IF(A42="","",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A42))</f>
         <v/>
       </c>
       <c r="AD42" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A42),0)</f>
+        <f>IF(A42="","",SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A42))</f>
         <v/>
       </c>
       <c r="AE42" s="16">
-        <f>IF(AC42=0,0,AC42*1.7/12*AP42)</f>
+        <f>IF(A42="","",IF(AC42=0,0,AC42*1.7/12*AP42))</f>
         <v/>
       </c>
       <c r="AF42" s="16">
-        <f>IF(AD42=0,0,AD42*1.7/12*AQ42)</f>
+        <f>IF(A42="","",IF(AD42=0,0,AD42*1.7/12*AQ42))</f>
         <v/>
       </c>
       <c r="AG42" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A42,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A42,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A42="","",SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A42,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A42,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="AH42" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A42,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A42="","",SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A42,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AI42" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A42,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <f>IF(A42="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A42,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
       <c r="AJ42" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A42),0)</f>
+        <f>IF(A42="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A42))</f>
         <v/>
       </c>
       <c r="AK42" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A42),0)</f>
+        <f>IF(A42="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A42))</f>
         <v/>
       </c>
       <c r="AL42" s="16">
-        <f>(IF((AE42)&lt;(AG42+AH42+AI42),(AE42),(AG42+AH42+AI42)))+AJ42*5+AK42*10+R42+T42+V42</f>
+        <f>IF(A42="","",(IF((AE42)&lt;(AG42+AH42+AI42),(AE42),(AG42+AH42+AI42)))+AJ42*5+AK42*10+R42+T42+V42)</f>
         <v/>
       </c>
       <c r="AM42" s="16">
-        <f>AL42-J42</f>
+        <f>IF(A42="","",AL42-J42)</f>
         <v/>
       </c>
       <c r="AP42" s="16">
-        <f>IF(E42=0,"",(B42*0.95+C42*0.25+D42*0)/E42)</f>
+        <f>IF(A42="","",IF(E42=0,"",(B42*0.95+C42*0.25+D42*0)/E42))</f>
         <v/>
       </c>
       <c r="AQ42" s="16">
-        <f>IF(I42=0,"",(F42*0.95+G42*0.25+H42*0)/I42)</f>
+        <f>IF(A42="","",IF(I42=0,"",(F42*0.95+G42*0.25+H42*0)/I42))</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="16.25" customHeight="1">
       <c r="A43" s="16">
-        <f>IFERROR('SDA'!A89,"")</f>
+        <f>IF('SDA'!A89="","",'SDA'!A89)</f>
         <v/>
       </c>
       <c r="B43" s="16">
-        <f>IFERROR('SDA'!F89,0)</f>
+        <f>IF(A43="","",'SDA'!F89)</f>
         <v/>
       </c>
       <c r="C43" s="16">
-        <f>IFERROR('SDA'!G89,0)</f>
+        <f>IF(A43="","",'SDA'!G89)</f>
         <v/>
       </c>
       <c r="D43" s="16">
-        <f>IFERROR('SDA'!H89,0)</f>
+        <f>IF(A43="","",'SDA'!H89)</f>
         <v/>
       </c>
       <c r="E43" s="16">
-        <f>SUM(B43:D43)</f>
+        <f>IF(A43="","",SUM(B43:D43))</f>
         <v/>
       </c>
       <c r="F43" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A43,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A43,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <f>IF(A43="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A43,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A43,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"))</f>
         <v/>
       </c>
       <c r="G43" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A43,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <f>IF(A43="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A43,'SDA'!$C$4:$C$53,"Compacted (Open Space)"))</f>
         <v/>
       </c>
       <c r="H43" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A43,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <f>IF(A43="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A43,'SDA'!$C$4:$C$53,"Natural (Woods)"))</f>
         <v/>
       </c>
       <c r="I43" s="16">
-        <f>SUM(F43:H43)</f>
+        <f>IF(A43="","",SUM(F43:H43))</f>
         <v/>
       </c>
       <c r="J43" s="16">
-        <f>IF(E43=0,0,AP43*1.2/12*E43)</f>
+        <f>IF(A43="","",IF(E43=0,0,AP43*1.2/12*E43))</f>
         <v/>
       </c>
       <c r="K43" s="16">
-        <f>IF(I43=0,0,AQ43*1.2/12*I43)</f>
+        <f>IF(A43="","",IF(I43=0,0,AQ43*1.2/12*I43))</f>
         <v/>
       </c>
       <c r="L43" s="16">
-        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A43,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A43,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A43,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A43,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <f>IF(A43="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A43,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A43,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A43,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A43,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
         <v/>
       </c>
       <c r="M43" s="4" t="n"/>
       <c r="N43" s="4" t="n"/>
       <c r="O43" s="16">
-        <f>IFERROR(IFS(L43="A",2.5,L43="B",0.3,L43="C",0.1,L43="D",0.05,TRUE,""),"")</f>
+        <f>IF(A43="","",IFS(L43="A",2.5,L43="B",0.3,L43="C",0.1,L43="D",0.05,TRUE,""))</f>
         <v/>
       </c>
       <c r="P43" s="4" t="n"/>
       <c r="Q43" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A43),0)</f>
+        <f>IF(A43="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A43))</f>
         <v/>
       </c>
       <c r="R43" s="16">
-        <f>Q43*10</f>
+        <f>IF(A43="","",Q43*10)</f>
         <v/>
       </c>
       <c r="S43" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A43),0)</f>
+        <f>IF(A43="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A43))</f>
         <v/>
       </c>
       <c r="T43" s="16">
-        <f>S43*20</f>
+        <f>IF(A43="","",S43*20)</f>
         <v/>
       </c>
       <c r="U43" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A43)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A43),0)</f>
+        <f>IF(A43="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A43)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A43))</f>
         <v/>
       </c>
       <c r="V43" s="16">
-        <f>U43*40</f>
+        <f>IF(A43="","",U43*40)</f>
         <v/>
       </c>
       <c r="W43" s="4" t="n"/>
       <c r="X43" s="4" t="n"/>
       <c r="Y43" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A43,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A43,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A43="","",SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A43,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A43,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="Z43" s="4" t="n"/>
       <c r="AA43" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A43,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A43="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A43,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AB43" s="4" t="n"/>
       <c r="AC43" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A43),0)</f>
+        <f>IF(A43="","",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A43))</f>
         <v/>
       </c>
       <c r="AD43" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A43),0)</f>
+        <f>IF(A43="","",SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A43))</f>
         <v/>
       </c>
       <c r="AE43" s="16">
-        <f>IF(AC43=0,0,AC43*1.7/12*AP43)</f>
+        <f>IF(A43="","",IF(AC43=0,0,AC43*1.7/12*AP43))</f>
         <v/>
       </c>
       <c r="AF43" s="16">
-        <f>IF(AD43=0,0,AD43*1.7/12*AQ43)</f>
+        <f>IF(A43="","",IF(AD43=0,0,AD43*1.7/12*AQ43))</f>
         <v/>
       </c>
       <c r="AG43" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A43,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A43,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A43="","",SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A43,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A43,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="AH43" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A43,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A43="","",SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A43,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AI43" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A43,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <f>IF(A43="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A43,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
       <c r="AJ43" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A43),0)</f>
+        <f>IF(A43="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A43))</f>
         <v/>
       </c>
       <c r="AK43" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A43),0)</f>
+        <f>IF(A43="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A43))</f>
         <v/>
       </c>
       <c r="AL43" s="16">
-        <f>(IF((AE43)&lt;(AG43+AH43+AI43),(AE43),(AG43+AH43+AI43)))+AJ43*5+AK43*10+R43+T43+V43</f>
+        <f>IF(A43="","",(IF((AE43)&lt;(AG43+AH43+AI43),(AE43),(AG43+AH43+AI43)))+AJ43*5+AK43*10+R43+T43+V43)</f>
         <v/>
       </c>
       <c r="AM43" s="16">
-        <f>AL43-J43</f>
+        <f>IF(A43="","",AL43-J43)</f>
         <v/>
       </c>
       <c r="AP43" s="16">
-        <f>IF(E43=0,"",(B43*0.95+C43*0.25+D43*0)/E43)</f>
+        <f>IF(A43="","",IF(E43=0,"",(B43*0.95+C43*0.25+D43*0)/E43))</f>
         <v/>
       </c>
       <c r="AQ43" s="16">
-        <f>IF(I43=0,"",(F43*0.95+G43*0.25+H43*0)/I43)</f>
+        <f>IF(A43="","",IF(I43=0,"",(F43*0.95+G43*0.25+H43*0)/I43))</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="16.25" customHeight="1">
       <c r="A44" s="16">
-        <f>IFERROR('SDA'!A90,"")</f>
+        <f>IF('SDA'!A90="","",'SDA'!A90)</f>
         <v/>
       </c>
       <c r="B44" s="16">
-        <f>IFERROR('SDA'!F90,0)</f>
+        <f>IF(A44="","",'SDA'!F90)</f>
         <v/>
       </c>
       <c r="C44" s="16">
-        <f>IFERROR('SDA'!G90,0)</f>
+        <f>IF(A44="","",'SDA'!G90)</f>
         <v/>
       </c>
       <c r="D44" s="16">
-        <f>IFERROR('SDA'!H90,0)</f>
+        <f>IF(A44="","",'SDA'!H90)</f>
         <v/>
       </c>
       <c r="E44" s="16">
-        <f>SUM(B44:D44)</f>
+        <f>IF(A44="","",SUM(B44:D44))</f>
         <v/>
       </c>
       <c r="F44" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A44,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A44,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"),0)</f>
+        <f>IF(A44="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A44,'SDA'!$C$4:$C$53,"Impervious Vehicular")+SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A44,'SDA'!$C$4:$C$53,"Impervious Non-Vehicular"))</f>
         <v/>
       </c>
       <c r="G44" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A44,'SDA'!$C$4:$C$53,"Compacted (Open Space)"),0)</f>
+        <f>IF(A44="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A44,'SDA'!$C$4:$C$53,"Compacted (Open Space)"))</f>
         <v/>
       </c>
       <c r="H44" s="16">
-        <f>IFERROR(SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A44,'SDA'!$C$4:$C$53,"Natural (Woods)"),0)</f>
+        <f>IF(A44="","",SUMIFS('SDA'!$H$4:$H$53,'SDA'!$A$4:$A$53,A44,'SDA'!$C$4:$C$53,"Natural (Woods)"))</f>
         <v/>
       </c>
       <c r="I44" s="16">
-        <f>SUM(F44:H44)</f>
+        <f>IF(A44="","",SUM(F44:H44))</f>
         <v/>
       </c>
       <c r="J44" s="16">
-        <f>IF(E44=0,0,AP44*1.2/12*E44)</f>
+        <f>IF(A44="","",IF(E44=0,0,AP44*1.2/12*E44))</f>
         <v/>
       </c>
       <c r="K44" s="16">
-        <f>IF(I44=0,0,AQ44*1.2/12*I44)</f>
+        <f>IF(A44="","",IF(I44=0,0,AQ44*1.2/12*I44))</f>
         <v/>
       </c>
       <c r="L44" s="16">
-        <f>IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A44,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A44,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A44,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A44,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),"")</f>
+        <f>IF(A44="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A44,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A44,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A44,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A44,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
         <v/>
       </c>
       <c r="M44" s="4" t="n"/>
       <c r="N44" s="4" t="n"/>
       <c r="O44" s="16">
-        <f>IFERROR(IFS(L44="A",2.5,L44="B",0.3,L44="C",0.1,L44="D",0.05,TRUE,""),"")</f>
+        <f>IF(A44="","",IFS(L44="A",2.5,L44="B",0.3,L44="C",0.1,L44="D",0.05,TRUE,""))</f>
         <v/>
       </c>
       <c r="P44" s="4" t="n"/>
       <c r="Q44" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A44),0)</f>
+        <f>IF(A44="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A44))</f>
         <v/>
       </c>
       <c r="R44" s="16">
-        <f>Q44*10</f>
+        <f>IF(A44="","",Q44*10)</f>
         <v/>
       </c>
       <c r="S44" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A44),0)</f>
+        <f>IF(A44="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A44))</f>
         <v/>
       </c>
       <c r="T44" s="16">
-        <f>S44*20</f>
+        <f>IF(A44="","",S44*20)</f>
         <v/>
       </c>
       <c r="U44" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A44)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A44),0)</f>
+        <f>IF(A44="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A44)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A44))</f>
         <v/>
       </c>
       <c r="V44" s="16">
-        <f>U44*40</f>
+        <f>IF(A44="","",U44*40)</f>
         <v/>
       </c>
       <c r="W44" s="4" t="n"/>
       <c r="X44" s="4" t="n"/>
       <c r="Y44" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A44,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A44,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A44="","",SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A44,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$N$4:$N$53,'BMP'!$B$4:$B$53,A44,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="Z44" s="4" t="n"/>
       <c r="AA44" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A44,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A44="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A44,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AB44" s="4" t="n"/>
       <c r="AC44" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A44),0)</f>
+        <f>IF(A44="","",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$B$4:$B$53,A44))</f>
         <v/>
       </c>
       <c r="AD44" s="16">
-        <f>IFERROR(SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A44),0)</f>
+        <f>IF(A44="","",SUMIFS('CDA'!$F$4:$F$53,'CDA'!$B$4:$B$53,A44))</f>
         <v/>
       </c>
       <c r="AE44" s="16">
-        <f>IF(AC44=0,0,AC44*1.7/12*AP44)</f>
+        <f>IF(A44="","",IF(AC44=0,0,AC44*1.7/12*AP44))</f>
         <v/>
       </c>
       <c r="AF44" s="16">
-        <f>IF(AD44=0,0,AD44*1.7/12*AQ44)</f>
+        <f>IF(A44="","",IF(AD44=0,0,AD44*1.7/12*AQ44))</f>
         <v/>
       </c>
       <c r="AG44" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A44,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A44,'BMP'!$D$4:$D$53,"Dry Swale"),0)</f>
+        <f>IF(A44="","",SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A44,'BMP'!$D$4:$D$53,"Bioretention")+SUMIFS('BMP'!$W$4:$W$53,'BMP'!$B$4:$B$53,A44,'BMP'!$D$4:$D$53,"Dry Swale"))</f>
         <v/>
       </c>
       <c r="AH44" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A44,'BMP'!$D$4:$D$53,"Permeable Pavement"),0)</f>
+        <f>IF(A44="","",SUMIFS('BMP'!$K$4:$K$53,'BMP'!$B$4:$B$53,A44,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
       <c r="AI44" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A44,'BMP'!$D$4:$D$53,"Wet Swale"),0)</f>
+        <f>IF(A44="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A44,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
       <c r="AJ44" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A44),0)</f>
+        <f>IF(A44="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A44))</f>
         <v/>
       </c>
       <c r="AK44" s="16">
-        <f>IFERROR(SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A44),0)</f>
+        <f>IF(A44="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A44))</f>
         <v/>
       </c>
       <c r="AL44" s="16">
-        <f>(IF((AE44)&lt;(AG44+AH44+AI44),(AE44),(AG44+AH44+AI44)))+AJ44*5+AK44*10+R44+T44+V44</f>
+        <f>IF(A44="","",(IF((AE44)&lt;(AG44+AH44+AI44),(AE44),(AG44+AH44+AI44)))+AJ44*5+AK44*10+R44+T44+V44)</f>
         <v/>
       </c>
       <c r="AM44" s="16">
-        <f>AL44-J44</f>
+        <f>IF(A44="","",AL44-J44)</f>
         <v/>
       </c>
       <c r="AP44" s="16">
-        <f>IF(E44=0,"",(B44*0.95+C44*0.25+D44*0)/E44)</f>
+        <f>IF(A44="","",IF(E44=0,"",(B44*0.95+C44*0.25+D44*0)/E44))</f>
         <v/>
       </c>
       <c r="AQ44" s="16">
-        <f>IF(I44=0,"",(F44*0.95+G44*0.25+H44*0)/I44)</f>
+        <f>IF(A44="","",IF(I44=0,"",(F44*0.95+G44*0.25+H44*0)/I44))</f>
         <v/>
       </c>
     </row>
@@ -19607,57 +19693,60 @@
           <t>DATOTAL</t>
         </is>
       </c>
-      <c r="E45" s="27">
+      <c r="E45" s="37">
         <f>SUM(E12:E44)</f>
         <v/>
       </c>
-      <c r="I45" s="27">
+      <c r="I45" s="37">
         <f>SUM(I12:I44)</f>
         <v/>
       </c>
-      <c r="J45" s="27">
+      <c r="J45" s="37">
         <f>SUM(J12:J44)</f>
         <v/>
       </c>
-      <c r="K45" s="27">
+      <c r="K45" s="37">
         <f>SUM(K12:K44)</f>
         <v/>
       </c>
-      <c r="Q45" s="27">
+      <c r="Q45" s="37">
         <f>SUM(Q12:Q44)</f>
         <v/>
       </c>
-      <c r="R45" s="27">
+      <c r="R45" s="37">
         <f>SUM(R12:R44)</f>
         <v/>
       </c>
-      <c r="S45" s="27">
+      <c r="S45" s="37">
         <f>SUM(S12:S44)</f>
         <v/>
       </c>
-      <c r="T45" s="27">
+      <c r="T45" s="37">
         <f>SUM(T12:T44)</f>
         <v/>
       </c>
-      <c r="U45" s="27">
+      <c r="U45" s="37">
         <f>SUM(U12:U44)</f>
         <v/>
       </c>
-      <c r="V45" s="27">
+      <c r="V45" s="37">
         <f>SUM(V12:V44)</f>
         <v/>
       </c>
-      <c r="AL45" s="27">
+      <c r="AL45" s="37">
         <f>SUM(AL12:AL44)</f>
         <v/>
       </c>
-      <c r="AM45" s="27">
+      <c r="AM45" s="37">
         <f>SUM(AM12:AM44)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="27">
+  <mergeCells count="35">
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="L7:P7"/>
+    <mergeCell ref="AC7:AM7"/>
     <mergeCell ref="P9:P10"/>
     <mergeCell ref="AG9:AG10"/>
     <mergeCell ref="AI9:AI10"/>
@@ -19665,20 +19754,25 @@
     <mergeCell ref="AM9:AM10"/>
     <mergeCell ref="Y9:Z9"/>
     <mergeCell ref="AP9:AQ9"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="W7:AB7"/>
     <mergeCell ref="AA9:AB9"/>
-    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="L3:V3"/>
     <mergeCell ref="AH9:AH10"/>
+    <mergeCell ref="B7:K7"/>
     <mergeCell ref="D1:G1"/>
     <mergeCell ref="L9:L10"/>
+    <mergeCell ref="L4:V4"/>
     <mergeCell ref="N9:N10"/>
     <mergeCell ref="T1:U1"/>
+    <mergeCell ref="Q7:V7"/>
     <mergeCell ref="Q9:V10"/>
-    <mergeCell ref="W9:X9"/>
     <mergeCell ref="Y1:AB1"/>
     <mergeCell ref="I1:J1"/>
+    <mergeCell ref="W9:X9"/>
     <mergeCell ref="B9:I9"/>
+    <mergeCell ref="AC9:AD9"/>
     <mergeCell ref="AE9:AF9"/>
-    <mergeCell ref="AC9:AD9"/>
     <mergeCell ref="AF1:AG1"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="M9:M10"/>
@@ -19709,17 +19803,17 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="28" t="inlineStr">
+      <c r="A1" s="38" t="inlineStr">
         <is>
           <t>EISA Section 438 — Direct Determination (Horton infiltration)</t>
         </is>
       </c>
-      <c r="B1" s="29" t="n"/>
-      <c r="C1" s="29" t="n"/>
-      <c r="D1" s="29" t="n"/>
-      <c r="E1" s="29" t="n"/>
-      <c r="F1" s="29" t="n"/>
-      <c r="G1" s="30" t="n"/>
+      <c r="B1" s="39" t="n"/>
+      <c r="C1" s="39" t="n"/>
+      <c r="D1" s="39" t="n"/>
+      <c r="E1" s="39" t="n"/>
+      <c r="F1" s="39" t="n"/>
+      <c r="G1" s="40" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
@@ -19869,37 +19963,37 @@
       <c r="G15" s="8" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="26" t="inlineStr">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>Surface</t>
         </is>
       </c>
-      <c r="B16" s="26" t="inlineStr">
+      <c r="B16" s="36" t="inlineStr">
         <is>
           <t>HSG</t>
         </is>
       </c>
-      <c r="C16" s="26" t="inlineStr">
+      <c r="C16" s="36" t="inlineStr">
         <is>
           <t>Area (SF)</t>
         </is>
       </c>
-      <c r="D16" s="26" t="inlineStr">
+      <c r="D16" s="36" t="inlineStr">
         <is>
           <t>Runoff HSG B (in)</t>
         </is>
       </c>
-      <c r="E16" s="26" t="inlineStr">
+      <c r="E16" s="36" t="inlineStr">
         <is>
           <t>Runoff HSG C (in)</t>
         </is>
       </c>
-      <c r="F16" s="26" t="inlineStr">
+      <c r="F16" s="36" t="inlineStr">
         <is>
           <t>Vol HSG B (CF)</t>
         </is>
       </c>
-      <c r="G16" s="26" t="inlineStr">
+      <c r="G16" s="36" t="inlineStr">
         <is>
           <t>Vol HSG C (CF)</t>
         </is>
@@ -20290,37 +20384,37 @@
       <c r="G30" s="8" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="26" t="inlineStr">
+      <c r="A31" s="36" t="inlineStr">
         <is>
           <t>Surface</t>
         </is>
       </c>
-      <c r="B31" s="26" t="inlineStr">
+      <c r="B31" s="36" t="inlineStr">
         <is>
           <t>HSG</t>
         </is>
       </c>
-      <c r="C31" s="26" t="inlineStr">
+      <c r="C31" s="36" t="inlineStr">
         <is>
           <t>Area (SF)</t>
         </is>
       </c>
-      <c r="D31" s="26" t="inlineStr">
+      <c r="D31" s="36" t="inlineStr">
         <is>
           <t>Runoff HSG B (in)</t>
         </is>
       </c>
-      <c r="E31" s="26" t="inlineStr">
+      <c r="E31" s="36" t="inlineStr">
         <is>
           <t>Runoff HSG C (in)</t>
         </is>
       </c>
-      <c r="F31" s="26" t="inlineStr">
+      <c r="F31" s="36" t="inlineStr">
         <is>
           <t>Vol HSG B (CF)</t>
         </is>
       </c>
-      <c r="G31" s="26" t="inlineStr">
+      <c r="G31" s="36" t="inlineStr">
         <is>
           <t>Vol HSG C (CF)</t>
         </is>
@@ -20698,26 +20792,26 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="28" t="inlineStr">
+      <c r="A45" s="38" t="inlineStr">
         <is>
           <t>Compliance Check</t>
         </is>
       </c>
-      <c r="B45" s="29" t="n"/>
-      <c r="C45" s="30" t="n"/>
+      <c r="B45" s="39" t="n"/>
+      <c r="C45" s="40" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="31" t="inlineStr">
+      <c r="A46" s="41" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B46" s="31" t="inlineStr">
+      <c r="B46" s="41" t="inlineStr">
         <is>
           <t>HSG B</t>
         </is>
       </c>
-      <c r="C46" s="31" t="inlineStr">
+      <c r="C46" s="41" t="inlineStr">
         <is>
           <t>HSG C</t>
         </is>
@@ -20831,16 +20925,16 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="28" t="inlineStr">
+      <c r="A1" s="38" t="inlineStr">
         <is>
           <t>EISA Section 438 — TR-55 CN Method (Method A primary)</t>
         </is>
       </c>
-      <c r="B1" s="29" t="n"/>
-      <c r="C1" s="29" t="n"/>
-      <c r="D1" s="29" t="n"/>
-      <c r="E1" s="29" t="n"/>
-      <c r="F1" s="30" t="n"/>
+      <c r="B1" s="39" t="n"/>
+      <c r="C1" s="39" t="n"/>
+      <c r="D1" s="39" t="n"/>
+      <c r="E1" s="39" t="n"/>
+      <c r="F1" s="40" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
@@ -20900,32 +20994,32 @@
       <c r="F8" s="13" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="31" t="inlineStr">
+      <c r="A9" s="41" t="inlineStr">
         <is>
           <t>Surface</t>
         </is>
       </c>
-      <c r="B9" s="31" t="inlineStr">
+      <c r="B9" s="41" t="inlineStr">
         <is>
           <t>HSG</t>
         </is>
       </c>
-      <c r="C9" s="31" t="inlineStr">
+      <c r="C9" s="41" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="D9" s="31" t="inlineStr">
+      <c r="D9" s="41" t="inlineStr">
         <is>
           <t>Area (SF)</t>
         </is>
       </c>
-      <c r="E9" s="31" t="inlineStr">
+      <c r="E9" s="41" t="inlineStr">
         <is>
           <t>Q (in)</t>
         </is>
       </c>
-      <c r="F9" s="31" t="inlineStr">
+      <c r="F9" s="41" t="inlineStr">
         <is>
           <t>Vol (CF)</t>
         </is>
@@ -21265,32 +21359,32 @@
       <c r="F23" s="13" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="31" t="inlineStr">
+      <c r="A24" s="41" t="inlineStr">
         <is>
           <t>Surface</t>
         </is>
       </c>
-      <c r="B24" s="31" t="inlineStr">
+      <c r="B24" s="41" t="inlineStr">
         <is>
           <t>HSG</t>
         </is>
       </c>
-      <c r="C24" s="31" t="inlineStr">
+      <c r="C24" s="41" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="D24" s="31" t="inlineStr">
+      <c r="D24" s="41" t="inlineStr">
         <is>
           <t>Area (SF)</t>
         </is>
       </c>
-      <c r="E24" s="31" t="inlineStr">
+      <c r="E24" s="41" t="inlineStr">
         <is>
           <t>Q (in)</t>
         </is>
       </c>
-      <c r="F24" s="31" t="inlineStr">
+      <c r="F24" s="41" t="inlineStr">
         <is>
           <t>Vol (CF)</t>
         </is>
@@ -21618,12 +21712,12 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="28" t="inlineStr">
+      <c r="A38" s="38" t="inlineStr">
         <is>
           <t>Compliance Check (Method A)</t>
         </is>
       </c>
-      <c r="B38" s="30" t="n"/>
+      <c r="B38" s="40" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">

--- a/SW_Required_Provided_DOEE_EISA438.xlsx
+++ b/SW_Required_Provided_DOEE_EISA438.xlsx
@@ -9176,11 +9176,11 @@
       <c r="G4" s="4" t="n"/>
       <c r="H4" s="4" t="n"/>
       <c r="I4" s="4">
-        <f>IFERROR(IF(OR(E4="Enhanced",E4="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C4,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C4,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C4,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C4,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E4="Enhanced",E4="Underdrained Enhanced"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C4,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C4,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C4,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C4,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="J4" s="17">
-        <f>IFERROR(IFS(AND(D4="Permeable Pavement",E4="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D4="Permeable Pavement",E4="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D4="Bioretention",E4="Standard"),INDEX(PARAMS_BMP,3,5),AND(D4="Bioretention",E4="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D4="Bioretention",E4="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D4="Dry Swale",E4="—"),INDEX(PARAMS_BMP,6,5),AND(D4="Wet Swale",E4="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D4="Permeable Pavement",E4="Enhanced"),INDEX(PARAMS_BMP,1,5),IF(AND(D4="Permeable Pavement",E4="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),IF(AND(D4="Bioretention",E4="Standard"),INDEX(PARAMS_BMP,3,5),IF(AND(D4="Bioretention",E4="Enhanced"),INDEX(PARAMS_BMP,4,5),IF(AND(D4="Bioretention",E4="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),IF(AND(D4="Dry Swale",E4="—"),INDEX(PARAMS_BMP,6,5),IF(AND(D4="Wet Swale",E4="—"),INDEX(PARAMS_BMP,7,5),""))))))),"")</f>
         <v/>
       </c>
       <c r="K4" s="17">
@@ -9203,17 +9203,17 @@
       </c>
       <c r="Q4" s="4" t="n"/>
       <c r="R4" s="17">
-        <f>IFERROR(IFS(AND(D4="Permeable Pavement",E4="Enhanced"),INDEX(PARAMS_BMP,1,3),AND(D4="Permeable Pavement",E4="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),AND(D4="Bioretention",E4="Standard"),INDEX(PARAMS_BMP,3,3),AND(D4="Bioretention",E4="Enhanced"),INDEX(PARAMS_BMP,4,3),AND(D4="Bioretention",E4="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),AND(D4="Dry Swale",E4="—"),INDEX(PARAMS_BMP,6,3),AND(D4="Wet Swale",E4="—"),INDEX(PARAMS_BMP,7,3),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D4="Permeable Pavement",E4="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D4="Permeable Pavement",E4="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D4="Bioretention",E4="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D4="Bioretention",E4="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D4="Bioretention",E4="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D4="Dry Swale",E4="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D4="Wet Swale",E4="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
       <c r="S4" s="4" t="n"/>
       <c r="T4" s="17">
-        <f>IFERROR(IFS(AND(D4="Permeable Pavement",E4="Enhanced"),INDEX(PARAMS_BMP,1,4),AND(D4="Permeable Pavement",E4="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),AND(D4="Bioretention",E4="Standard"),INDEX(PARAMS_BMP,3,4),AND(D4="Bioretention",E4="Enhanced"),INDEX(PARAMS_BMP,4,4),AND(D4="Bioretention",E4="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),AND(D4="Dry Swale",E4="—"),INDEX(PARAMS_BMP,6,4),AND(D4="Wet Swale",E4="—"),INDEX(PARAMS_BMP,7,4),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D4="Permeable Pavement",E4="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D4="Permeable Pavement",E4="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D4="Bioretention",E4="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D4="Bioretention",E4="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D4="Bioretention",E4="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D4="Dry Swale",E4="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D4="Wet Swale",E4="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
       <c r="U4" s="4" t="n"/>
       <c r="V4" s="4">
-        <f>IFERROR(IF(OR(E4="Enhanced",E4="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C4,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C4,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C4,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C4,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E4="Enhanced",E4="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C4,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C4,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C4,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C4,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="W4" s="17">
@@ -9245,7 +9245,7 @@
         <v/>
       </c>
       <c r="AJ4" s="17">
-        <f>IFERROR(IFS(AND(D4="Permeable Pavement",E4="Enhanced"),INDEX(PARAMS_BMP,1,6),AND(D4="Permeable Pavement",E4="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),AND(D4="Bioretention",E4="Standard"),INDEX(PARAMS_BMP,3,6),AND(D4="Bioretention",E4="Enhanced"),INDEX(PARAMS_BMP,4,6),AND(D4="Bioretention",E4="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),AND(D4="Dry Swale",E4="—"),INDEX(PARAMS_BMP,6,6),AND(D4="Wet Swale",E4="—"),INDEX(PARAMS_BMP,7,6),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D4="Permeable Pavement",E4="Enhanced"),INDEX(PARAMS_BMP,1,6),IF(AND(D4="Permeable Pavement",E4="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),IF(AND(D4="Bioretention",E4="Standard"),INDEX(PARAMS_BMP,3,6),IF(AND(D4="Bioretention",E4="Enhanced"),INDEX(PARAMS_BMP,4,6),IF(AND(D4="Bioretention",E4="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),IF(AND(D4="Dry Swale",E4="—"),INDEX(PARAMS_BMP,6,6),IF(AND(D4="Wet Swale",E4="—"),INDEX(PARAMS_BMP,7,6),""))))))),"")</f>
         <v/>
       </c>
       <c r="AK4" s="17">
@@ -9271,11 +9271,11 @@
       <c r="G5" s="4" t="n"/>
       <c r="H5" s="4" t="n"/>
       <c r="I5" s="4">
-        <f>IFERROR(IF(OR(E5="Enhanced",E5="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C5,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C5,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C5,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C5,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E5="Enhanced",E5="Underdrained Enhanced"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C5,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C5,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C5,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C5,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="J5" s="17">
-        <f>IFERROR(IFS(AND(D5="Permeable Pavement",E5="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D5="Permeable Pavement",E5="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D5="Bioretention",E5="Standard"),INDEX(PARAMS_BMP,3,5),AND(D5="Bioretention",E5="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D5="Bioretention",E5="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D5="Dry Swale",E5="—"),INDEX(PARAMS_BMP,6,5),AND(D5="Wet Swale",E5="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D5="Permeable Pavement",E5="Enhanced"),INDEX(PARAMS_BMP,1,5),IF(AND(D5="Permeable Pavement",E5="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),IF(AND(D5="Bioretention",E5="Standard"),INDEX(PARAMS_BMP,3,5),IF(AND(D5="Bioretention",E5="Enhanced"),INDEX(PARAMS_BMP,4,5),IF(AND(D5="Bioretention",E5="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),IF(AND(D5="Dry Swale",E5="—"),INDEX(PARAMS_BMP,6,5),IF(AND(D5="Wet Swale",E5="—"),INDEX(PARAMS_BMP,7,5),""))))))),"")</f>
         <v/>
       </c>
       <c r="K5" s="17">
@@ -9298,17 +9298,17 @@
       </c>
       <c r="Q5" s="4" t="n"/>
       <c r="R5" s="17">
-        <f>IFERROR(IFS(AND(D5="Permeable Pavement",E5="Enhanced"),INDEX(PARAMS_BMP,1,3),AND(D5="Permeable Pavement",E5="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),AND(D5="Bioretention",E5="Standard"),INDEX(PARAMS_BMP,3,3),AND(D5="Bioretention",E5="Enhanced"),INDEX(PARAMS_BMP,4,3),AND(D5="Bioretention",E5="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),AND(D5="Dry Swale",E5="—"),INDEX(PARAMS_BMP,6,3),AND(D5="Wet Swale",E5="—"),INDEX(PARAMS_BMP,7,3),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D5="Permeable Pavement",E5="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D5="Permeable Pavement",E5="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D5="Bioretention",E5="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D5="Bioretention",E5="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D5="Bioretention",E5="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D5="Dry Swale",E5="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D5="Wet Swale",E5="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
       <c r="S5" s="4" t="n"/>
       <c r="T5" s="17">
-        <f>IFERROR(IFS(AND(D5="Permeable Pavement",E5="Enhanced"),INDEX(PARAMS_BMP,1,4),AND(D5="Permeable Pavement",E5="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),AND(D5="Bioretention",E5="Standard"),INDEX(PARAMS_BMP,3,4),AND(D5="Bioretention",E5="Enhanced"),INDEX(PARAMS_BMP,4,4),AND(D5="Bioretention",E5="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),AND(D5="Dry Swale",E5="—"),INDEX(PARAMS_BMP,6,4),AND(D5="Wet Swale",E5="—"),INDEX(PARAMS_BMP,7,4),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D5="Permeable Pavement",E5="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D5="Permeable Pavement",E5="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D5="Bioretention",E5="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D5="Bioretention",E5="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D5="Bioretention",E5="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D5="Dry Swale",E5="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D5="Wet Swale",E5="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
       <c r="U5" s="4" t="n"/>
       <c r="V5" s="4">
-        <f>IFERROR(IF(OR(E5="Enhanced",E5="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C5,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C5,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C5,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C5,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E5="Enhanced",E5="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C5,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C5,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C5,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C5,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="W5" s="17">
@@ -9340,7 +9340,7 @@
         <v/>
       </c>
       <c r="AJ5" s="17">
-        <f>IFERROR(IFS(AND(D5="Permeable Pavement",E5="Enhanced"),INDEX(PARAMS_BMP,1,6),AND(D5="Permeable Pavement",E5="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),AND(D5="Bioretention",E5="Standard"),INDEX(PARAMS_BMP,3,6),AND(D5="Bioretention",E5="Enhanced"),INDEX(PARAMS_BMP,4,6),AND(D5="Bioretention",E5="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),AND(D5="Dry Swale",E5="—"),INDEX(PARAMS_BMP,6,6),AND(D5="Wet Swale",E5="—"),INDEX(PARAMS_BMP,7,6),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D5="Permeable Pavement",E5="Enhanced"),INDEX(PARAMS_BMP,1,6),IF(AND(D5="Permeable Pavement",E5="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),IF(AND(D5="Bioretention",E5="Standard"),INDEX(PARAMS_BMP,3,6),IF(AND(D5="Bioretention",E5="Enhanced"),INDEX(PARAMS_BMP,4,6),IF(AND(D5="Bioretention",E5="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),IF(AND(D5="Dry Swale",E5="—"),INDEX(PARAMS_BMP,6,6),IF(AND(D5="Wet Swale",E5="—"),INDEX(PARAMS_BMP,7,6),""))))))),"")</f>
         <v/>
       </c>
       <c r="AK5" s="17">
@@ -9366,11 +9366,11 @@
       <c r="G6" s="4" t="n"/>
       <c r="H6" s="4" t="n"/>
       <c r="I6" s="4">
-        <f>IFERROR(IF(OR(E6="Enhanced",E6="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C6,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C6,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C6,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C6,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E6="Enhanced",E6="Underdrained Enhanced"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C6,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C6,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C6,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C6,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="J6" s="17">
-        <f>IFERROR(IFS(AND(D6="Permeable Pavement",E6="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D6="Permeable Pavement",E6="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D6="Bioretention",E6="Standard"),INDEX(PARAMS_BMP,3,5),AND(D6="Bioretention",E6="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D6="Bioretention",E6="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D6="Dry Swale",E6="—"),INDEX(PARAMS_BMP,6,5),AND(D6="Wet Swale",E6="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D6="Permeable Pavement",E6="Enhanced"),INDEX(PARAMS_BMP,1,5),IF(AND(D6="Permeable Pavement",E6="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),IF(AND(D6="Bioretention",E6="Standard"),INDEX(PARAMS_BMP,3,5),IF(AND(D6="Bioretention",E6="Enhanced"),INDEX(PARAMS_BMP,4,5),IF(AND(D6="Bioretention",E6="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),IF(AND(D6="Dry Swale",E6="—"),INDEX(PARAMS_BMP,6,5),IF(AND(D6="Wet Swale",E6="—"),INDEX(PARAMS_BMP,7,5),""))))))),"")</f>
         <v/>
       </c>
       <c r="K6" s="17">
@@ -9393,17 +9393,17 @@
       </c>
       <c r="Q6" s="4" t="n"/>
       <c r="R6" s="17">
-        <f>IFERROR(IFS(AND(D6="Permeable Pavement",E6="Enhanced"),INDEX(PARAMS_BMP,1,3),AND(D6="Permeable Pavement",E6="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),AND(D6="Bioretention",E6="Standard"),INDEX(PARAMS_BMP,3,3),AND(D6="Bioretention",E6="Enhanced"),INDEX(PARAMS_BMP,4,3),AND(D6="Bioretention",E6="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),AND(D6="Dry Swale",E6="—"),INDEX(PARAMS_BMP,6,3),AND(D6="Wet Swale",E6="—"),INDEX(PARAMS_BMP,7,3),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D6="Permeable Pavement",E6="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D6="Permeable Pavement",E6="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D6="Bioretention",E6="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D6="Bioretention",E6="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D6="Bioretention",E6="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D6="Dry Swale",E6="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D6="Wet Swale",E6="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
       <c r="S6" s="4" t="n"/>
       <c r="T6" s="17">
-        <f>IFERROR(IFS(AND(D6="Permeable Pavement",E6="Enhanced"),INDEX(PARAMS_BMP,1,4),AND(D6="Permeable Pavement",E6="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),AND(D6="Bioretention",E6="Standard"),INDEX(PARAMS_BMP,3,4),AND(D6="Bioretention",E6="Enhanced"),INDEX(PARAMS_BMP,4,4),AND(D6="Bioretention",E6="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),AND(D6="Dry Swale",E6="—"),INDEX(PARAMS_BMP,6,4),AND(D6="Wet Swale",E6="—"),INDEX(PARAMS_BMP,7,4),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D6="Permeable Pavement",E6="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D6="Permeable Pavement",E6="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D6="Bioretention",E6="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D6="Bioretention",E6="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D6="Bioretention",E6="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D6="Dry Swale",E6="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D6="Wet Swale",E6="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
       <c r="U6" s="4" t="n"/>
       <c r="V6" s="4">
-        <f>IFERROR(IF(OR(E6="Enhanced",E6="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C6,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C6,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C6,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C6,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E6="Enhanced",E6="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C6,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C6,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C6,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C6,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="W6" s="17">
@@ -9435,7 +9435,7 @@
         <v/>
       </c>
       <c r="AJ6" s="17">
-        <f>IFERROR(IFS(AND(D6="Permeable Pavement",E6="Enhanced"),INDEX(PARAMS_BMP,1,6),AND(D6="Permeable Pavement",E6="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),AND(D6="Bioretention",E6="Standard"),INDEX(PARAMS_BMP,3,6),AND(D6="Bioretention",E6="Enhanced"),INDEX(PARAMS_BMP,4,6),AND(D6="Bioretention",E6="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),AND(D6="Dry Swale",E6="—"),INDEX(PARAMS_BMP,6,6),AND(D6="Wet Swale",E6="—"),INDEX(PARAMS_BMP,7,6),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D6="Permeable Pavement",E6="Enhanced"),INDEX(PARAMS_BMP,1,6),IF(AND(D6="Permeable Pavement",E6="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),IF(AND(D6="Bioretention",E6="Standard"),INDEX(PARAMS_BMP,3,6),IF(AND(D6="Bioretention",E6="Enhanced"),INDEX(PARAMS_BMP,4,6),IF(AND(D6="Bioretention",E6="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),IF(AND(D6="Dry Swale",E6="—"),INDEX(PARAMS_BMP,6,6),IF(AND(D6="Wet Swale",E6="—"),INDEX(PARAMS_BMP,7,6),""))))))),"")</f>
         <v/>
       </c>
       <c r="AK6" s="17">
@@ -9461,11 +9461,11 @@
       <c r="G7" s="4" t="n"/>
       <c r="H7" s="4" t="n"/>
       <c r="I7" s="4">
-        <f>IFERROR(IF(OR(E7="Enhanced",E7="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C7,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C7,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C7,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C7,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E7="Enhanced",E7="Underdrained Enhanced"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C7,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C7,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C7,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C7,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="J7" s="17">
-        <f>IFERROR(IFS(AND(D7="Permeable Pavement",E7="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D7="Permeable Pavement",E7="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D7="Bioretention",E7="Standard"),INDEX(PARAMS_BMP,3,5),AND(D7="Bioretention",E7="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D7="Bioretention",E7="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D7="Dry Swale",E7="—"),INDEX(PARAMS_BMP,6,5),AND(D7="Wet Swale",E7="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D7="Permeable Pavement",E7="Enhanced"),INDEX(PARAMS_BMP,1,5),IF(AND(D7="Permeable Pavement",E7="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),IF(AND(D7="Bioretention",E7="Standard"),INDEX(PARAMS_BMP,3,5),IF(AND(D7="Bioretention",E7="Enhanced"),INDEX(PARAMS_BMP,4,5),IF(AND(D7="Bioretention",E7="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),IF(AND(D7="Dry Swale",E7="—"),INDEX(PARAMS_BMP,6,5),IF(AND(D7="Wet Swale",E7="—"),INDEX(PARAMS_BMP,7,5),""))))))),"")</f>
         <v/>
       </c>
       <c r="K7" s="17">
@@ -9488,17 +9488,17 @@
       </c>
       <c r="Q7" s="4" t="n"/>
       <c r="R7" s="17">
-        <f>IFERROR(IFS(AND(D7="Permeable Pavement",E7="Enhanced"),INDEX(PARAMS_BMP,1,3),AND(D7="Permeable Pavement",E7="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),AND(D7="Bioretention",E7="Standard"),INDEX(PARAMS_BMP,3,3),AND(D7="Bioretention",E7="Enhanced"),INDEX(PARAMS_BMP,4,3),AND(D7="Bioretention",E7="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),AND(D7="Dry Swale",E7="—"),INDEX(PARAMS_BMP,6,3),AND(D7="Wet Swale",E7="—"),INDEX(PARAMS_BMP,7,3),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D7="Permeable Pavement",E7="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D7="Permeable Pavement",E7="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D7="Bioretention",E7="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D7="Bioretention",E7="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D7="Bioretention",E7="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D7="Dry Swale",E7="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D7="Wet Swale",E7="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
       <c r="S7" s="4" t="n"/>
       <c r="T7" s="17">
-        <f>IFERROR(IFS(AND(D7="Permeable Pavement",E7="Enhanced"),INDEX(PARAMS_BMP,1,4),AND(D7="Permeable Pavement",E7="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),AND(D7="Bioretention",E7="Standard"),INDEX(PARAMS_BMP,3,4),AND(D7="Bioretention",E7="Enhanced"),INDEX(PARAMS_BMP,4,4),AND(D7="Bioretention",E7="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),AND(D7="Dry Swale",E7="—"),INDEX(PARAMS_BMP,6,4),AND(D7="Wet Swale",E7="—"),INDEX(PARAMS_BMP,7,4),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D7="Permeable Pavement",E7="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D7="Permeable Pavement",E7="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D7="Bioretention",E7="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D7="Bioretention",E7="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D7="Bioretention",E7="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D7="Dry Swale",E7="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D7="Wet Swale",E7="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
       <c r="U7" s="4" t="n"/>
       <c r="V7" s="4">
-        <f>IFERROR(IF(OR(E7="Enhanced",E7="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C7,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C7,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C7,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C7,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E7="Enhanced",E7="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C7,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C7,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C7,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C7,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="W7" s="17">
@@ -9530,7 +9530,7 @@
         <v/>
       </c>
       <c r="AJ7" s="17">
-        <f>IFERROR(IFS(AND(D7="Permeable Pavement",E7="Enhanced"),INDEX(PARAMS_BMP,1,6),AND(D7="Permeable Pavement",E7="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),AND(D7="Bioretention",E7="Standard"),INDEX(PARAMS_BMP,3,6),AND(D7="Bioretention",E7="Enhanced"),INDEX(PARAMS_BMP,4,6),AND(D7="Bioretention",E7="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),AND(D7="Dry Swale",E7="—"),INDEX(PARAMS_BMP,6,6),AND(D7="Wet Swale",E7="—"),INDEX(PARAMS_BMP,7,6),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D7="Permeable Pavement",E7="Enhanced"),INDEX(PARAMS_BMP,1,6),IF(AND(D7="Permeable Pavement",E7="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),IF(AND(D7="Bioretention",E7="Standard"),INDEX(PARAMS_BMP,3,6),IF(AND(D7="Bioretention",E7="Enhanced"),INDEX(PARAMS_BMP,4,6),IF(AND(D7="Bioretention",E7="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),IF(AND(D7="Dry Swale",E7="—"),INDEX(PARAMS_BMP,6,6),IF(AND(D7="Wet Swale",E7="—"),INDEX(PARAMS_BMP,7,6),""))))))),"")</f>
         <v/>
       </c>
       <c r="AK7" s="17">
@@ -9556,11 +9556,11 @@
       <c r="G8" s="4" t="n"/>
       <c r="H8" s="4" t="n"/>
       <c r="I8" s="4">
-        <f>IFERROR(IF(OR(E8="Enhanced",E8="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C8,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C8,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C8,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C8,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E8="Enhanced",E8="Underdrained Enhanced"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C8,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C8,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C8,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C8,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="J8" s="17">
-        <f>IFERROR(IFS(AND(D8="Permeable Pavement",E8="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D8="Permeable Pavement",E8="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D8="Bioretention",E8="Standard"),INDEX(PARAMS_BMP,3,5),AND(D8="Bioretention",E8="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D8="Bioretention",E8="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D8="Dry Swale",E8="—"),INDEX(PARAMS_BMP,6,5),AND(D8="Wet Swale",E8="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D8="Permeable Pavement",E8="Enhanced"),INDEX(PARAMS_BMP,1,5),IF(AND(D8="Permeable Pavement",E8="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),IF(AND(D8="Bioretention",E8="Standard"),INDEX(PARAMS_BMP,3,5),IF(AND(D8="Bioretention",E8="Enhanced"),INDEX(PARAMS_BMP,4,5),IF(AND(D8="Bioretention",E8="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),IF(AND(D8="Dry Swale",E8="—"),INDEX(PARAMS_BMP,6,5),IF(AND(D8="Wet Swale",E8="—"),INDEX(PARAMS_BMP,7,5),""))))))),"")</f>
         <v/>
       </c>
       <c r="K8" s="17">
@@ -9583,17 +9583,17 @@
       </c>
       <c r="Q8" s="4" t="n"/>
       <c r="R8" s="17">
-        <f>IFERROR(IFS(AND(D8="Permeable Pavement",E8="Enhanced"),INDEX(PARAMS_BMP,1,3),AND(D8="Permeable Pavement",E8="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),AND(D8="Bioretention",E8="Standard"),INDEX(PARAMS_BMP,3,3),AND(D8="Bioretention",E8="Enhanced"),INDEX(PARAMS_BMP,4,3),AND(D8="Bioretention",E8="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),AND(D8="Dry Swale",E8="—"),INDEX(PARAMS_BMP,6,3),AND(D8="Wet Swale",E8="—"),INDEX(PARAMS_BMP,7,3),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D8="Permeable Pavement",E8="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D8="Permeable Pavement",E8="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D8="Bioretention",E8="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D8="Bioretention",E8="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D8="Bioretention",E8="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D8="Dry Swale",E8="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D8="Wet Swale",E8="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
       <c r="S8" s="4" t="n"/>
       <c r="T8" s="17">
-        <f>IFERROR(IFS(AND(D8="Permeable Pavement",E8="Enhanced"),INDEX(PARAMS_BMP,1,4),AND(D8="Permeable Pavement",E8="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),AND(D8="Bioretention",E8="Standard"),INDEX(PARAMS_BMP,3,4),AND(D8="Bioretention",E8="Enhanced"),INDEX(PARAMS_BMP,4,4),AND(D8="Bioretention",E8="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),AND(D8="Dry Swale",E8="—"),INDEX(PARAMS_BMP,6,4),AND(D8="Wet Swale",E8="—"),INDEX(PARAMS_BMP,7,4),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D8="Permeable Pavement",E8="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D8="Permeable Pavement",E8="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D8="Bioretention",E8="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D8="Bioretention",E8="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D8="Bioretention",E8="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D8="Dry Swale",E8="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D8="Wet Swale",E8="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
       <c r="U8" s="4" t="n"/>
       <c r="V8" s="4">
-        <f>IFERROR(IF(OR(E8="Enhanced",E8="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C8,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C8,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C8,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C8,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E8="Enhanced",E8="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C8,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C8,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C8,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C8,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="W8" s="17">
@@ -9625,7 +9625,7 @@
         <v/>
       </c>
       <c r="AJ8" s="17">
-        <f>IFERROR(IFS(AND(D8="Permeable Pavement",E8="Enhanced"),INDEX(PARAMS_BMP,1,6),AND(D8="Permeable Pavement",E8="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),AND(D8="Bioretention",E8="Standard"),INDEX(PARAMS_BMP,3,6),AND(D8="Bioretention",E8="Enhanced"),INDEX(PARAMS_BMP,4,6),AND(D8="Bioretention",E8="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),AND(D8="Dry Swale",E8="—"),INDEX(PARAMS_BMP,6,6),AND(D8="Wet Swale",E8="—"),INDEX(PARAMS_BMP,7,6),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D8="Permeable Pavement",E8="Enhanced"),INDEX(PARAMS_BMP,1,6),IF(AND(D8="Permeable Pavement",E8="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),IF(AND(D8="Bioretention",E8="Standard"),INDEX(PARAMS_BMP,3,6),IF(AND(D8="Bioretention",E8="Enhanced"),INDEX(PARAMS_BMP,4,6),IF(AND(D8="Bioretention",E8="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),IF(AND(D8="Dry Swale",E8="—"),INDEX(PARAMS_BMP,6,6),IF(AND(D8="Wet Swale",E8="—"),INDEX(PARAMS_BMP,7,6),""))))))),"")</f>
         <v/>
       </c>
       <c r="AK8" s="17">
@@ -9651,11 +9651,11 @@
       <c r="G9" s="4" t="n"/>
       <c r="H9" s="4" t="n"/>
       <c r="I9" s="4">
-        <f>IFERROR(IF(OR(E9="Enhanced",E9="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C9,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C9,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C9,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C9,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E9="Enhanced",E9="Underdrained Enhanced"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C9,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C9,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C9,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C9,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="J9" s="17">
-        <f>IFERROR(IFS(AND(D9="Permeable Pavement",E9="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D9="Permeable Pavement",E9="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D9="Bioretention",E9="Standard"),INDEX(PARAMS_BMP,3,5),AND(D9="Bioretention",E9="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D9="Bioretention",E9="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D9="Dry Swale",E9="—"),INDEX(PARAMS_BMP,6,5),AND(D9="Wet Swale",E9="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D9="Permeable Pavement",E9="Enhanced"),INDEX(PARAMS_BMP,1,5),IF(AND(D9="Permeable Pavement",E9="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),IF(AND(D9="Bioretention",E9="Standard"),INDEX(PARAMS_BMP,3,5),IF(AND(D9="Bioretention",E9="Enhanced"),INDEX(PARAMS_BMP,4,5),IF(AND(D9="Bioretention",E9="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),IF(AND(D9="Dry Swale",E9="—"),INDEX(PARAMS_BMP,6,5),IF(AND(D9="Wet Swale",E9="—"),INDEX(PARAMS_BMP,7,5),""))))))),"")</f>
         <v/>
       </c>
       <c r="K9" s="17">
@@ -9678,17 +9678,17 @@
       </c>
       <c r="Q9" s="4" t="n"/>
       <c r="R9" s="17">
-        <f>IFERROR(IFS(AND(D9="Permeable Pavement",E9="Enhanced"),INDEX(PARAMS_BMP,1,3),AND(D9="Permeable Pavement",E9="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),AND(D9="Bioretention",E9="Standard"),INDEX(PARAMS_BMP,3,3),AND(D9="Bioretention",E9="Enhanced"),INDEX(PARAMS_BMP,4,3),AND(D9="Bioretention",E9="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),AND(D9="Dry Swale",E9="—"),INDEX(PARAMS_BMP,6,3),AND(D9="Wet Swale",E9="—"),INDEX(PARAMS_BMP,7,3),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D9="Permeable Pavement",E9="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D9="Permeable Pavement",E9="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D9="Bioretention",E9="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D9="Bioretention",E9="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D9="Bioretention",E9="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D9="Dry Swale",E9="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D9="Wet Swale",E9="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
       <c r="S9" s="4" t="n"/>
       <c r="T9" s="17">
-        <f>IFERROR(IFS(AND(D9="Permeable Pavement",E9="Enhanced"),INDEX(PARAMS_BMP,1,4),AND(D9="Permeable Pavement",E9="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),AND(D9="Bioretention",E9="Standard"),INDEX(PARAMS_BMP,3,4),AND(D9="Bioretention",E9="Enhanced"),INDEX(PARAMS_BMP,4,4),AND(D9="Bioretention",E9="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),AND(D9="Dry Swale",E9="—"),INDEX(PARAMS_BMP,6,4),AND(D9="Wet Swale",E9="—"),INDEX(PARAMS_BMP,7,4),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D9="Permeable Pavement",E9="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D9="Permeable Pavement",E9="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D9="Bioretention",E9="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D9="Bioretention",E9="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D9="Bioretention",E9="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D9="Dry Swale",E9="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D9="Wet Swale",E9="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
       <c r="U9" s="4" t="n"/>
       <c r="V9" s="4">
-        <f>IFERROR(IF(OR(E9="Enhanced",E9="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C9,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C9,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C9,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C9,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E9="Enhanced",E9="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C9,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C9,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C9,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C9,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="W9" s="17">
@@ -9720,7 +9720,7 @@
         <v/>
       </c>
       <c r="AJ9" s="17">
-        <f>IFERROR(IFS(AND(D9="Permeable Pavement",E9="Enhanced"),INDEX(PARAMS_BMP,1,6),AND(D9="Permeable Pavement",E9="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),AND(D9="Bioretention",E9="Standard"),INDEX(PARAMS_BMP,3,6),AND(D9="Bioretention",E9="Enhanced"),INDEX(PARAMS_BMP,4,6),AND(D9="Bioretention",E9="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),AND(D9="Dry Swale",E9="—"),INDEX(PARAMS_BMP,6,6),AND(D9="Wet Swale",E9="—"),INDEX(PARAMS_BMP,7,6),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D9="Permeable Pavement",E9="Enhanced"),INDEX(PARAMS_BMP,1,6),IF(AND(D9="Permeable Pavement",E9="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),IF(AND(D9="Bioretention",E9="Standard"),INDEX(PARAMS_BMP,3,6),IF(AND(D9="Bioretention",E9="Enhanced"),INDEX(PARAMS_BMP,4,6),IF(AND(D9="Bioretention",E9="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),IF(AND(D9="Dry Swale",E9="—"),INDEX(PARAMS_BMP,6,6),IF(AND(D9="Wet Swale",E9="—"),INDEX(PARAMS_BMP,7,6),""))))))),"")</f>
         <v/>
       </c>
       <c r="AK9" s="17">
@@ -9746,11 +9746,11 @@
       <c r="G10" s="4" t="n"/>
       <c r="H10" s="4" t="n"/>
       <c r="I10" s="4">
-        <f>IFERROR(IF(OR(E10="Enhanced",E10="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C10,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C10,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C10,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C10,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E10="Enhanced",E10="Underdrained Enhanced"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C10,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C10,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C10,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C10,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="J10" s="17">
-        <f>IFERROR(IFS(AND(D10="Permeable Pavement",E10="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D10="Permeable Pavement",E10="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D10="Bioretention",E10="Standard"),INDEX(PARAMS_BMP,3,5),AND(D10="Bioretention",E10="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D10="Bioretention",E10="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D10="Dry Swale",E10="—"),INDEX(PARAMS_BMP,6,5),AND(D10="Wet Swale",E10="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D10="Permeable Pavement",E10="Enhanced"),INDEX(PARAMS_BMP,1,5),IF(AND(D10="Permeable Pavement",E10="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),IF(AND(D10="Bioretention",E10="Standard"),INDEX(PARAMS_BMP,3,5),IF(AND(D10="Bioretention",E10="Enhanced"),INDEX(PARAMS_BMP,4,5),IF(AND(D10="Bioretention",E10="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),IF(AND(D10="Dry Swale",E10="—"),INDEX(PARAMS_BMP,6,5),IF(AND(D10="Wet Swale",E10="—"),INDEX(PARAMS_BMP,7,5),""))))))),"")</f>
         <v/>
       </c>
       <c r="K10" s="17">
@@ -9773,17 +9773,17 @@
       </c>
       <c r="Q10" s="4" t="n"/>
       <c r="R10" s="17">
-        <f>IFERROR(IFS(AND(D10="Permeable Pavement",E10="Enhanced"),INDEX(PARAMS_BMP,1,3),AND(D10="Permeable Pavement",E10="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),AND(D10="Bioretention",E10="Standard"),INDEX(PARAMS_BMP,3,3),AND(D10="Bioretention",E10="Enhanced"),INDEX(PARAMS_BMP,4,3),AND(D10="Bioretention",E10="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),AND(D10="Dry Swale",E10="—"),INDEX(PARAMS_BMP,6,3),AND(D10="Wet Swale",E10="—"),INDEX(PARAMS_BMP,7,3),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D10="Permeable Pavement",E10="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D10="Permeable Pavement",E10="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D10="Bioretention",E10="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D10="Bioretention",E10="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D10="Bioretention",E10="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D10="Dry Swale",E10="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D10="Wet Swale",E10="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
       <c r="S10" s="4" t="n"/>
       <c r="T10" s="17">
-        <f>IFERROR(IFS(AND(D10="Permeable Pavement",E10="Enhanced"),INDEX(PARAMS_BMP,1,4),AND(D10="Permeable Pavement",E10="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),AND(D10="Bioretention",E10="Standard"),INDEX(PARAMS_BMP,3,4),AND(D10="Bioretention",E10="Enhanced"),INDEX(PARAMS_BMP,4,4),AND(D10="Bioretention",E10="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),AND(D10="Dry Swale",E10="—"),INDEX(PARAMS_BMP,6,4),AND(D10="Wet Swale",E10="—"),INDEX(PARAMS_BMP,7,4),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D10="Permeable Pavement",E10="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D10="Permeable Pavement",E10="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D10="Bioretention",E10="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D10="Bioretention",E10="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D10="Bioretention",E10="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D10="Dry Swale",E10="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D10="Wet Swale",E10="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
       <c r="U10" s="4" t="n"/>
       <c r="V10" s="4">
-        <f>IFERROR(IF(OR(E10="Enhanced",E10="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C10,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C10,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C10,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C10,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E10="Enhanced",E10="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C10,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C10,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C10,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C10,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="W10" s="17">
@@ -9815,7 +9815,7 @@
         <v/>
       </c>
       <c r="AJ10" s="17">
-        <f>IFERROR(IFS(AND(D10="Permeable Pavement",E10="Enhanced"),INDEX(PARAMS_BMP,1,6),AND(D10="Permeable Pavement",E10="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),AND(D10="Bioretention",E10="Standard"),INDEX(PARAMS_BMP,3,6),AND(D10="Bioretention",E10="Enhanced"),INDEX(PARAMS_BMP,4,6),AND(D10="Bioretention",E10="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),AND(D10="Dry Swale",E10="—"),INDEX(PARAMS_BMP,6,6),AND(D10="Wet Swale",E10="—"),INDEX(PARAMS_BMP,7,6),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D10="Permeable Pavement",E10="Enhanced"),INDEX(PARAMS_BMP,1,6),IF(AND(D10="Permeable Pavement",E10="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),IF(AND(D10="Bioretention",E10="Standard"),INDEX(PARAMS_BMP,3,6),IF(AND(D10="Bioretention",E10="Enhanced"),INDEX(PARAMS_BMP,4,6),IF(AND(D10="Bioretention",E10="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),IF(AND(D10="Dry Swale",E10="—"),INDEX(PARAMS_BMP,6,6),IF(AND(D10="Wet Swale",E10="—"),INDEX(PARAMS_BMP,7,6),""))))))),"")</f>
         <v/>
       </c>
       <c r="AK10" s="17">
@@ -9841,11 +9841,11 @@
       <c r="G11" s="4" t="n"/>
       <c r="H11" s="4" t="n"/>
       <c r="I11" s="4">
-        <f>IFERROR(IF(OR(E11="Enhanced",E11="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C11,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C11,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C11,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C11,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E11="Enhanced",E11="Underdrained Enhanced"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C11,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C11,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C11,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C11,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="J11" s="17">
-        <f>IFERROR(IFS(AND(D11="Permeable Pavement",E11="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D11="Permeable Pavement",E11="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D11="Bioretention",E11="Standard"),INDEX(PARAMS_BMP,3,5),AND(D11="Bioretention",E11="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D11="Bioretention",E11="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D11="Dry Swale",E11="—"),INDEX(PARAMS_BMP,6,5),AND(D11="Wet Swale",E11="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D11="Permeable Pavement",E11="Enhanced"),INDEX(PARAMS_BMP,1,5),IF(AND(D11="Permeable Pavement",E11="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),IF(AND(D11="Bioretention",E11="Standard"),INDEX(PARAMS_BMP,3,5),IF(AND(D11="Bioretention",E11="Enhanced"),INDEX(PARAMS_BMP,4,5),IF(AND(D11="Bioretention",E11="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),IF(AND(D11="Dry Swale",E11="—"),INDEX(PARAMS_BMP,6,5),IF(AND(D11="Wet Swale",E11="—"),INDEX(PARAMS_BMP,7,5),""))))))),"")</f>
         <v/>
       </c>
       <c r="K11" s="17">
@@ -9868,17 +9868,17 @@
       </c>
       <c r="Q11" s="4" t="n"/>
       <c r="R11" s="17">
-        <f>IFERROR(IFS(AND(D11="Permeable Pavement",E11="Enhanced"),INDEX(PARAMS_BMP,1,3),AND(D11="Permeable Pavement",E11="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),AND(D11="Bioretention",E11="Standard"),INDEX(PARAMS_BMP,3,3),AND(D11="Bioretention",E11="Enhanced"),INDEX(PARAMS_BMP,4,3),AND(D11="Bioretention",E11="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),AND(D11="Dry Swale",E11="—"),INDEX(PARAMS_BMP,6,3),AND(D11="Wet Swale",E11="—"),INDEX(PARAMS_BMP,7,3),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D11="Permeable Pavement",E11="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D11="Permeable Pavement",E11="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D11="Bioretention",E11="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D11="Bioretention",E11="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D11="Bioretention",E11="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D11="Dry Swale",E11="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D11="Wet Swale",E11="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
       <c r="S11" s="4" t="n"/>
       <c r="T11" s="17">
-        <f>IFERROR(IFS(AND(D11="Permeable Pavement",E11="Enhanced"),INDEX(PARAMS_BMP,1,4),AND(D11="Permeable Pavement",E11="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),AND(D11="Bioretention",E11="Standard"),INDEX(PARAMS_BMP,3,4),AND(D11="Bioretention",E11="Enhanced"),INDEX(PARAMS_BMP,4,4),AND(D11="Bioretention",E11="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),AND(D11="Dry Swale",E11="—"),INDEX(PARAMS_BMP,6,4),AND(D11="Wet Swale",E11="—"),INDEX(PARAMS_BMP,7,4),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D11="Permeable Pavement",E11="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D11="Permeable Pavement",E11="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D11="Bioretention",E11="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D11="Bioretention",E11="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D11="Bioretention",E11="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D11="Dry Swale",E11="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D11="Wet Swale",E11="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
       <c r="U11" s="4" t="n"/>
       <c r="V11" s="4">
-        <f>IFERROR(IF(OR(E11="Enhanced",E11="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C11,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C11,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C11,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C11,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E11="Enhanced",E11="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C11,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C11,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C11,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C11,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="W11" s="17">
@@ -9910,7 +9910,7 @@
         <v/>
       </c>
       <c r="AJ11" s="17">
-        <f>IFERROR(IFS(AND(D11="Permeable Pavement",E11="Enhanced"),INDEX(PARAMS_BMP,1,6),AND(D11="Permeable Pavement",E11="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),AND(D11="Bioretention",E11="Standard"),INDEX(PARAMS_BMP,3,6),AND(D11="Bioretention",E11="Enhanced"),INDEX(PARAMS_BMP,4,6),AND(D11="Bioretention",E11="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),AND(D11="Dry Swale",E11="—"),INDEX(PARAMS_BMP,6,6),AND(D11="Wet Swale",E11="—"),INDEX(PARAMS_BMP,7,6),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D11="Permeable Pavement",E11="Enhanced"),INDEX(PARAMS_BMP,1,6),IF(AND(D11="Permeable Pavement",E11="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),IF(AND(D11="Bioretention",E11="Standard"),INDEX(PARAMS_BMP,3,6),IF(AND(D11="Bioretention",E11="Enhanced"),INDEX(PARAMS_BMP,4,6),IF(AND(D11="Bioretention",E11="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),IF(AND(D11="Dry Swale",E11="—"),INDEX(PARAMS_BMP,6,6),IF(AND(D11="Wet Swale",E11="—"),INDEX(PARAMS_BMP,7,6),""))))))),"")</f>
         <v/>
       </c>
       <c r="AK11" s="17">
@@ -9936,11 +9936,11 @@
       <c r="G12" s="4" t="n"/>
       <c r="H12" s="4" t="n"/>
       <c r="I12" s="4">
-        <f>IFERROR(IF(OR(E12="Enhanced",E12="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C12,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C12,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C12,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C12,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E12="Enhanced",E12="Underdrained Enhanced"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C12,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C12,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C12,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C12,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="J12" s="17">
-        <f>IFERROR(IFS(AND(D12="Permeable Pavement",E12="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D12="Permeable Pavement",E12="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D12="Bioretention",E12="Standard"),INDEX(PARAMS_BMP,3,5),AND(D12="Bioretention",E12="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D12="Bioretention",E12="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D12="Dry Swale",E12="—"),INDEX(PARAMS_BMP,6,5),AND(D12="Wet Swale",E12="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D12="Permeable Pavement",E12="Enhanced"),INDEX(PARAMS_BMP,1,5),IF(AND(D12="Permeable Pavement",E12="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),IF(AND(D12="Bioretention",E12="Standard"),INDEX(PARAMS_BMP,3,5),IF(AND(D12="Bioretention",E12="Enhanced"),INDEX(PARAMS_BMP,4,5),IF(AND(D12="Bioretention",E12="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),IF(AND(D12="Dry Swale",E12="—"),INDEX(PARAMS_BMP,6,5),IF(AND(D12="Wet Swale",E12="—"),INDEX(PARAMS_BMP,7,5),""))))))),"")</f>
         <v/>
       </c>
       <c r="K12" s="17">
@@ -9963,17 +9963,17 @@
       </c>
       <c r="Q12" s="4" t="n"/>
       <c r="R12" s="17">
-        <f>IFERROR(IFS(AND(D12="Permeable Pavement",E12="Enhanced"),INDEX(PARAMS_BMP,1,3),AND(D12="Permeable Pavement",E12="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),AND(D12="Bioretention",E12="Standard"),INDEX(PARAMS_BMP,3,3),AND(D12="Bioretention",E12="Enhanced"),INDEX(PARAMS_BMP,4,3),AND(D12="Bioretention",E12="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),AND(D12="Dry Swale",E12="—"),INDEX(PARAMS_BMP,6,3),AND(D12="Wet Swale",E12="—"),INDEX(PARAMS_BMP,7,3),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D12="Permeable Pavement",E12="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D12="Permeable Pavement",E12="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D12="Bioretention",E12="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D12="Bioretention",E12="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D12="Bioretention",E12="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D12="Dry Swale",E12="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D12="Wet Swale",E12="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
       <c r="S12" s="4" t="n"/>
       <c r="T12" s="17">
-        <f>IFERROR(IFS(AND(D12="Permeable Pavement",E12="Enhanced"),INDEX(PARAMS_BMP,1,4),AND(D12="Permeable Pavement",E12="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),AND(D12="Bioretention",E12="Standard"),INDEX(PARAMS_BMP,3,4),AND(D12="Bioretention",E12="Enhanced"),INDEX(PARAMS_BMP,4,4),AND(D12="Bioretention",E12="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),AND(D12="Dry Swale",E12="—"),INDEX(PARAMS_BMP,6,4),AND(D12="Wet Swale",E12="—"),INDEX(PARAMS_BMP,7,4),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D12="Permeable Pavement",E12="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D12="Permeable Pavement",E12="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D12="Bioretention",E12="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D12="Bioretention",E12="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D12="Bioretention",E12="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D12="Dry Swale",E12="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D12="Wet Swale",E12="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
       <c r="U12" s="4" t="n"/>
       <c r="V12" s="4">
-        <f>IFERROR(IF(OR(E12="Enhanced",E12="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C12,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C12,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C12,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C12,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E12="Enhanced",E12="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C12,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C12,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C12,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C12,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="W12" s="17">
@@ -10005,7 +10005,7 @@
         <v/>
       </c>
       <c r="AJ12" s="17">
-        <f>IFERROR(IFS(AND(D12="Permeable Pavement",E12="Enhanced"),INDEX(PARAMS_BMP,1,6),AND(D12="Permeable Pavement",E12="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),AND(D12="Bioretention",E12="Standard"),INDEX(PARAMS_BMP,3,6),AND(D12="Bioretention",E12="Enhanced"),INDEX(PARAMS_BMP,4,6),AND(D12="Bioretention",E12="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),AND(D12="Dry Swale",E12="—"),INDEX(PARAMS_BMP,6,6),AND(D12="Wet Swale",E12="—"),INDEX(PARAMS_BMP,7,6),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D12="Permeable Pavement",E12="Enhanced"),INDEX(PARAMS_BMP,1,6),IF(AND(D12="Permeable Pavement",E12="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),IF(AND(D12="Bioretention",E12="Standard"),INDEX(PARAMS_BMP,3,6),IF(AND(D12="Bioretention",E12="Enhanced"),INDEX(PARAMS_BMP,4,6),IF(AND(D12="Bioretention",E12="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),IF(AND(D12="Dry Swale",E12="—"),INDEX(PARAMS_BMP,6,6),IF(AND(D12="Wet Swale",E12="—"),INDEX(PARAMS_BMP,7,6),""))))))),"")</f>
         <v/>
       </c>
       <c r="AK12" s="17">
@@ -10031,11 +10031,11 @@
       <c r="G13" s="4" t="n"/>
       <c r="H13" s="4" t="n"/>
       <c r="I13" s="4">
-        <f>IFERROR(IF(OR(E13="Enhanced",E13="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C13,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C13,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C13,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C13,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E13="Enhanced",E13="Underdrained Enhanced"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C13,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C13,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C13,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C13,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="J13" s="17">
-        <f>IFERROR(IFS(AND(D13="Permeable Pavement",E13="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D13="Permeable Pavement",E13="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D13="Bioretention",E13="Standard"),INDEX(PARAMS_BMP,3,5),AND(D13="Bioretention",E13="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D13="Bioretention",E13="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D13="Dry Swale",E13="—"),INDEX(PARAMS_BMP,6,5),AND(D13="Wet Swale",E13="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D13="Permeable Pavement",E13="Enhanced"),INDEX(PARAMS_BMP,1,5),IF(AND(D13="Permeable Pavement",E13="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),IF(AND(D13="Bioretention",E13="Standard"),INDEX(PARAMS_BMP,3,5),IF(AND(D13="Bioretention",E13="Enhanced"),INDEX(PARAMS_BMP,4,5),IF(AND(D13="Bioretention",E13="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),IF(AND(D13="Dry Swale",E13="—"),INDEX(PARAMS_BMP,6,5),IF(AND(D13="Wet Swale",E13="—"),INDEX(PARAMS_BMP,7,5),""))))))),"")</f>
         <v/>
       </c>
       <c r="K13" s="17">
@@ -10058,17 +10058,17 @@
       </c>
       <c r="Q13" s="4" t="n"/>
       <c r="R13" s="17">
-        <f>IFERROR(IFS(AND(D13="Permeable Pavement",E13="Enhanced"),INDEX(PARAMS_BMP,1,3),AND(D13="Permeable Pavement",E13="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),AND(D13="Bioretention",E13="Standard"),INDEX(PARAMS_BMP,3,3),AND(D13="Bioretention",E13="Enhanced"),INDEX(PARAMS_BMP,4,3),AND(D13="Bioretention",E13="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),AND(D13="Dry Swale",E13="—"),INDEX(PARAMS_BMP,6,3),AND(D13="Wet Swale",E13="—"),INDEX(PARAMS_BMP,7,3),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D13="Permeable Pavement",E13="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D13="Permeable Pavement",E13="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D13="Bioretention",E13="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D13="Bioretention",E13="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D13="Bioretention",E13="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D13="Dry Swale",E13="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D13="Wet Swale",E13="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
       <c r="S13" s="4" t="n"/>
       <c r="T13" s="17">
-        <f>IFERROR(IFS(AND(D13="Permeable Pavement",E13="Enhanced"),INDEX(PARAMS_BMP,1,4),AND(D13="Permeable Pavement",E13="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),AND(D13="Bioretention",E13="Standard"),INDEX(PARAMS_BMP,3,4),AND(D13="Bioretention",E13="Enhanced"),INDEX(PARAMS_BMP,4,4),AND(D13="Bioretention",E13="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),AND(D13="Dry Swale",E13="—"),INDEX(PARAMS_BMP,6,4),AND(D13="Wet Swale",E13="—"),INDEX(PARAMS_BMP,7,4),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D13="Permeable Pavement",E13="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D13="Permeable Pavement",E13="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D13="Bioretention",E13="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D13="Bioretention",E13="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D13="Bioretention",E13="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D13="Dry Swale",E13="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D13="Wet Swale",E13="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
       <c r="U13" s="4" t="n"/>
       <c r="V13" s="4">
-        <f>IFERROR(IF(OR(E13="Enhanced",E13="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C13,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C13,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C13,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C13,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E13="Enhanced",E13="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C13,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C13,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C13,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C13,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="W13" s="17">
@@ -10100,7 +10100,7 @@
         <v/>
       </c>
       <c r="AJ13" s="17">
-        <f>IFERROR(IFS(AND(D13="Permeable Pavement",E13="Enhanced"),INDEX(PARAMS_BMP,1,6),AND(D13="Permeable Pavement",E13="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),AND(D13="Bioretention",E13="Standard"),INDEX(PARAMS_BMP,3,6),AND(D13="Bioretention",E13="Enhanced"),INDEX(PARAMS_BMP,4,6),AND(D13="Bioretention",E13="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),AND(D13="Dry Swale",E13="—"),INDEX(PARAMS_BMP,6,6),AND(D13="Wet Swale",E13="—"),INDEX(PARAMS_BMP,7,6),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D13="Permeable Pavement",E13="Enhanced"),INDEX(PARAMS_BMP,1,6),IF(AND(D13="Permeable Pavement",E13="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),IF(AND(D13="Bioretention",E13="Standard"),INDEX(PARAMS_BMP,3,6),IF(AND(D13="Bioretention",E13="Enhanced"),INDEX(PARAMS_BMP,4,6),IF(AND(D13="Bioretention",E13="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),IF(AND(D13="Dry Swale",E13="—"),INDEX(PARAMS_BMP,6,6),IF(AND(D13="Wet Swale",E13="—"),INDEX(PARAMS_BMP,7,6),""))))))),"")</f>
         <v/>
       </c>
       <c r="AK13" s="17">
@@ -10126,11 +10126,11 @@
       <c r="G14" s="4" t="n"/>
       <c r="H14" s="4" t="n"/>
       <c r="I14" s="4">
-        <f>IFERROR(IF(OR(E14="Enhanced",E14="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C14,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C14,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C14,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C14,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E14="Enhanced",E14="Underdrained Enhanced"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C14,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C14,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C14,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C14,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="J14" s="17">
-        <f>IFERROR(IFS(AND(D14="Permeable Pavement",E14="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D14="Permeable Pavement",E14="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D14="Bioretention",E14="Standard"),INDEX(PARAMS_BMP,3,5),AND(D14="Bioretention",E14="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D14="Bioretention",E14="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D14="Dry Swale",E14="—"),INDEX(PARAMS_BMP,6,5),AND(D14="Wet Swale",E14="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D14="Permeable Pavement",E14="Enhanced"),INDEX(PARAMS_BMP,1,5),IF(AND(D14="Permeable Pavement",E14="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),IF(AND(D14="Bioretention",E14="Standard"),INDEX(PARAMS_BMP,3,5),IF(AND(D14="Bioretention",E14="Enhanced"),INDEX(PARAMS_BMP,4,5),IF(AND(D14="Bioretention",E14="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),IF(AND(D14="Dry Swale",E14="—"),INDEX(PARAMS_BMP,6,5),IF(AND(D14="Wet Swale",E14="—"),INDEX(PARAMS_BMP,7,5),""))))))),"")</f>
         <v/>
       </c>
       <c r="K14" s="17">
@@ -10153,17 +10153,17 @@
       </c>
       <c r="Q14" s="4" t="n"/>
       <c r="R14" s="17">
-        <f>IFERROR(IFS(AND(D14="Permeable Pavement",E14="Enhanced"),INDEX(PARAMS_BMP,1,3),AND(D14="Permeable Pavement",E14="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),AND(D14="Bioretention",E14="Standard"),INDEX(PARAMS_BMP,3,3),AND(D14="Bioretention",E14="Enhanced"),INDEX(PARAMS_BMP,4,3),AND(D14="Bioretention",E14="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),AND(D14="Dry Swale",E14="—"),INDEX(PARAMS_BMP,6,3),AND(D14="Wet Swale",E14="—"),INDEX(PARAMS_BMP,7,3),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D14="Permeable Pavement",E14="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D14="Permeable Pavement",E14="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D14="Bioretention",E14="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D14="Bioretention",E14="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D14="Bioretention",E14="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D14="Dry Swale",E14="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D14="Wet Swale",E14="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
       <c r="S14" s="4" t="n"/>
       <c r="T14" s="17">
-        <f>IFERROR(IFS(AND(D14="Permeable Pavement",E14="Enhanced"),INDEX(PARAMS_BMP,1,4),AND(D14="Permeable Pavement",E14="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),AND(D14="Bioretention",E14="Standard"),INDEX(PARAMS_BMP,3,4),AND(D14="Bioretention",E14="Enhanced"),INDEX(PARAMS_BMP,4,4),AND(D14="Bioretention",E14="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),AND(D14="Dry Swale",E14="—"),INDEX(PARAMS_BMP,6,4),AND(D14="Wet Swale",E14="—"),INDEX(PARAMS_BMP,7,4),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D14="Permeable Pavement",E14="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D14="Permeable Pavement",E14="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D14="Bioretention",E14="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D14="Bioretention",E14="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D14="Bioretention",E14="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D14="Dry Swale",E14="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D14="Wet Swale",E14="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
       <c r="U14" s="4" t="n"/>
       <c r="V14" s="4">
-        <f>IFERROR(IF(OR(E14="Enhanced",E14="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C14,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C14,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C14,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C14,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E14="Enhanced",E14="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C14,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C14,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C14,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C14,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="W14" s="17">
@@ -10195,7 +10195,7 @@
         <v/>
       </c>
       <c r="AJ14" s="17">
-        <f>IFERROR(IFS(AND(D14="Permeable Pavement",E14="Enhanced"),INDEX(PARAMS_BMP,1,6),AND(D14="Permeable Pavement",E14="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),AND(D14="Bioretention",E14="Standard"),INDEX(PARAMS_BMP,3,6),AND(D14="Bioretention",E14="Enhanced"),INDEX(PARAMS_BMP,4,6),AND(D14="Bioretention",E14="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),AND(D14="Dry Swale",E14="—"),INDEX(PARAMS_BMP,6,6),AND(D14="Wet Swale",E14="—"),INDEX(PARAMS_BMP,7,6),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D14="Permeable Pavement",E14="Enhanced"),INDEX(PARAMS_BMP,1,6),IF(AND(D14="Permeable Pavement",E14="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),IF(AND(D14="Bioretention",E14="Standard"),INDEX(PARAMS_BMP,3,6),IF(AND(D14="Bioretention",E14="Enhanced"),INDEX(PARAMS_BMP,4,6),IF(AND(D14="Bioretention",E14="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),IF(AND(D14="Dry Swale",E14="—"),INDEX(PARAMS_BMP,6,6),IF(AND(D14="Wet Swale",E14="—"),INDEX(PARAMS_BMP,7,6),""))))))),"")</f>
         <v/>
       </c>
       <c r="AK14" s="17">
@@ -10221,11 +10221,11 @@
       <c r="G15" s="4" t="n"/>
       <c r="H15" s="4" t="n"/>
       <c r="I15" s="4">
-        <f>IFERROR(IF(OR(E15="Enhanced",E15="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C15,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C15,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C15,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C15,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E15="Enhanced",E15="Underdrained Enhanced"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C15,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C15,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C15,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C15,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="J15" s="17">
-        <f>IFERROR(IFS(AND(D15="Permeable Pavement",E15="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D15="Permeable Pavement",E15="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D15="Bioretention",E15="Standard"),INDEX(PARAMS_BMP,3,5),AND(D15="Bioretention",E15="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D15="Bioretention",E15="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D15="Dry Swale",E15="—"),INDEX(PARAMS_BMP,6,5),AND(D15="Wet Swale",E15="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D15="Permeable Pavement",E15="Enhanced"),INDEX(PARAMS_BMP,1,5),IF(AND(D15="Permeable Pavement",E15="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),IF(AND(D15="Bioretention",E15="Standard"),INDEX(PARAMS_BMP,3,5),IF(AND(D15="Bioretention",E15="Enhanced"),INDEX(PARAMS_BMP,4,5),IF(AND(D15="Bioretention",E15="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),IF(AND(D15="Dry Swale",E15="—"),INDEX(PARAMS_BMP,6,5),IF(AND(D15="Wet Swale",E15="—"),INDEX(PARAMS_BMP,7,5),""))))))),"")</f>
         <v/>
       </c>
       <c r="K15" s="17">
@@ -10248,17 +10248,17 @@
       </c>
       <c r="Q15" s="4" t="n"/>
       <c r="R15" s="17">
-        <f>IFERROR(IFS(AND(D15="Permeable Pavement",E15="Enhanced"),INDEX(PARAMS_BMP,1,3),AND(D15="Permeable Pavement",E15="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),AND(D15="Bioretention",E15="Standard"),INDEX(PARAMS_BMP,3,3),AND(D15="Bioretention",E15="Enhanced"),INDEX(PARAMS_BMP,4,3),AND(D15="Bioretention",E15="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),AND(D15="Dry Swale",E15="—"),INDEX(PARAMS_BMP,6,3),AND(D15="Wet Swale",E15="—"),INDEX(PARAMS_BMP,7,3),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D15="Permeable Pavement",E15="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D15="Permeable Pavement",E15="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D15="Bioretention",E15="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D15="Bioretention",E15="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D15="Bioretention",E15="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D15="Dry Swale",E15="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D15="Wet Swale",E15="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
       <c r="S15" s="4" t="n"/>
       <c r="T15" s="17">
-        <f>IFERROR(IFS(AND(D15="Permeable Pavement",E15="Enhanced"),INDEX(PARAMS_BMP,1,4),AND(D15="Permeable Pavement",E15="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),AND(D15="Bioretention",E15="Standard"),INDEX(PARAMS_BMP,3,4),AND(D15="Bioretention",E15="Enhanced"),INDEX(PARAMS_BMP,4,4),AND(D15="Bioretention",E15="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),AND(D15="Dry Swale",E15="—"),INDEX(PARAMS_BMP,6,4),AND(D15="Wet Swale",E15="—"),INDEX(PARAMS_BMP,7,4),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D15="Permeable Pavement",E15="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D15="Permeable Pavement",E15="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D15="Bioretention",E15="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D15="Bioretention",E15="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D15="Bioretention",E15="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D15="Dry Swale",E15="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D15="Wet Swale",E15="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
       <c r="U15" s="4" t="n"/>
       <c r="V15" s="4">
-        <f>IFERROR(IF(OR(E15="Enhanced",E15="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C15,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C15,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C15,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C15,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E15="Enhanced",E15="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C15,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C15,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C15,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C15,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="W15" s="17">
@@ -10290,7 +10290,7 @@
         <v/>
       </c>
       <c r="AJ15" s="17">
-        <f>IFERROR(IFS(AND(D15="Permeable Pavement",E15="Enhanced"),INDEX(PARAMS_BMP,1,6),AND(D15="Permeable Pavement",E15="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),AND(D15="Bioretention",E15="Standard"),INDEX(PARAMS_BMP,3,6),AND(D15="Bioretention",E15="Enhanced"),INDEX(PARAMS_BMP,4,6),AND(D15="Bioretention",E15="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),AND(D15="Dry Swale",E15="—"),INDEX(PARAMS_BMP,6,6),AND(D15="Wet Swale",E15="—"),INDEX(PARAMS_BMP,7,6),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D15="Permeable Pavement",E15="Enhanced"),INDEX(PARAMS_BMP,1,6),IF(AND(D15="Permeable Pavement",E15="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),IF(AND(D15="Bioretention",E15="Standard"),INDEX(PARAMS_BMP,3,6),IF(AND(D15="Bioretention",E15="Enhanced"),INDEX(PARAMS_BMP,4,6),IF(AND(D15="Bioretention",E15="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),IF(AND(D15="Dry Swale",E15="—"),INDEX(PARAMS_BMP,6,6),IF(AND(D15="Wet Swale",E15="—"),INDEX(PARAMS_BMP,7,6),""))))))),"")</f>
         <v/>
       </c>
       <c r="AK15" s="17">
@@ -10316,11 +10316,11 @@
       <c r="G16" s="4" t="n"/>
       <c r="H16" s="4" t="n"/>
       <c r="I16" s="4">
-        <f>IFERROR(IF(OR(E16="Enhanced",E16="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C16,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C16,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C16,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C16,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E16="Enhanced",E16="Underdrained Enhanced"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C16,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C16,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C16,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C16,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="J16" s="17">
-        <f>IFERROR(IFS(AND(D16="Permeable Pavement",E16="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D16="Permeable Pavement",E16="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D16="Bioretention",E16="Standard"),INDEX(PARAMS_BMP,3,5),AND(D16="Bioretention",E16="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D16="Bioretention",E16="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D16="Dry Swale",E16="—"),INDEX(PARAMS_BMP,6,5),AND(D16="Wet Swale",E16="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D16="Permeable Pavement",E16="Enhanced"),INDEX(PARAMS_BMP,1,5),IF(AND(D16="Permeable Pavement",E16="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),IF(AND(D16="Bioretention",E16="Standard"),INDEX(PARAMS_BMP,3,5),IF(AND(D16="Bioretention",E16="Enhanced"),INDEX(PARAMS_BMP,4,5),IF(AND(D16="Bioretention",E16="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),IF(AND(D16="Dry Swale",E16="—"),INDEX(PARAMS_BMP,6,5),IF(AND(D16="Wet Swale",E16="—"),INDEX(PARAMS_BMP,7,5),""))))))),"")</f>
         <v/>
       </c>
       <c r="K16" s="17">
@@ -10343,17 +10343,17 @@
       </c>
       <c r="Q16" s="4" t="n"/>
       <c r="R16" s="17">
-        <f>IFERROR(IFS(AND(D16="Permeable Pavement",E16="Enhanced"),INDEX(PARAMS_BMP,1,3),AND(D16="Permeable Pavement",E16="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),AND(D16="Bioretention",E16="Standard"),INDEX(PARAMS_BMP,3,3),AND(D16="Bioretention",E16="Enhanced"),INDEX(PARAMS_BMP,4,3),AND(D16="Bioretention",E16="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),AND(D16="Dry Swale",E16="—"),INDEX(PARAMS_BMP,6,3),AND(D16="Wet Swale",E16="—"),INDEX(PARAMS_BMP,7,3),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D16="Permeable Pavement",E16="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D16="Permeable Pavement",E16="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D16="Bioretention",E16="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D16="Bioretention",E16="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D16="Bioretention",E16="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D16="Dry Swale",E16="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D16="Wet Swale",E16="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
       <c r="S16" s="4" t="n"/>
       <c r="T16" s="17">
-        <f>IFERROR(IFS(AND(D16="Permeable Pavement",E16="Enhanced"),INDEX(PARAMS_BMP,1,4),AND(D16="Permeable Pavement",E16="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),AND(D16="Bioretention",E16="Standard"),INDEX(PARAMS_BMP,3,4),AND(D16="Bioretention",E16="Enhanced"),INDEX(PARAMS_BMP,4,4),AND(D16="Bioretention",E16="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),AND(D16="Dry Swale",E16="—"),INDEX(PARAMS_BMP,6,4),AND(D16="Wet Swale",E16="—"),INDEX(PARAMS_BMP,7,4),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D16="Permeable Pavement",E16="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D16="Permeable Pavement",E16="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D16="Bioretention",E16="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D16="Bioretention",E16="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D16="Bioretention",E16="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D16="Dry Swale",E16="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D16="Wet Swale",E16="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
       <c r="U16" s="4" t="n"/>
       <c r="V16" s="4">
-        <f>IFERROR(IF(OR(E16="Enhanced",E16="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C16,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C16,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C16,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C16,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E16="Enhanced",E16="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C16,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C16,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C16,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C16,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="W16" s="17">
@@ -10385,7 +10385,7 @@
         <v/>
       </c>
       <c r="AJ16" s="17">
-        <f>IFERROR(IFS(AND(D16="Permeable Pavement",E16="Enhanced"),INDEX(PARAMS_BMP,1,6),AND(D16="Permeable Pavement",E16="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),AND(D16="Bioretention",E16="Standard"),INDEX(PARAMS_BMP,3,6),AND(D16="Bioretention",E16="Enhanced"),INDEX(PARAMS_BMP,4,6),AND(D16="Bioretention",E16="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),AND(D16="Dry Swale",E16="—"),INDEX(PARAMS_BMP,6,6),AND(D16="Wet Swale",E16="—"),INDEX(PARAMS_BMP,7,6),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D16="Permeable Pavement",E16="Enhanced"),INDEX(PARAMS_BMP,1,6),IF(AND(D16="Permeable Pavement",E16="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),IF(AND(D16="Bioretention",E16="Standard"),INDEX(PARAMS_BMP,3,6),IF(AND(D16="Bioretention",E16="Enhanced"),INDEX(PARAMS_BMP,4,6),IF(AND(D16="Bioretention",E16="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),IF(AND(D16="Dry Swale",E16="—"),INDEX(PARAMS_BMP,6,6),IF(AND(D16="Wet Swale",E16="—"),INDEX(PARAMS_BMP,7,6),""))))))),"")</f>
         <v/>
       </c>
       <c r="AK16" s="17">
@@ -10411,11 +10411,11 @@
       <c r="G17" s="4" t="n"/>
       <c r="H17" s="4" t="n"/>
       <c r="I17" s="4">
-        <f>IFERROR(IF(OR(E17="Enhanced",E17="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C17,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C17,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C17,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C17,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E17="Enhanced",E17="Underdrained Enhanced"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C17,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C17,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C17,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C17,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="J17" s="17">
-        <f>IFERROR(IFS(AND(D17="Permeable Pavement",E17="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D17="Permeable Pavement",E17="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D17="Bioretention",E17="Standard"),INDEX(PARAMS_BMP,3,5),AND(D17="Bioretention",E17="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D17="Bioretention",E17="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D17="Dry Swale",E17="—"),INDEX(PARAMS_BMP,6,5),AND(D17="Wet Swale",E17="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D17="Permeable Pavement",E17="Enhanced"),INDEX(PARAMS_BMP,1,5),IF(AND(D17="Permeable Pavement",E17="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),IF(AND(D17="Bioretention",E17="Standard"),INDEX(PARAMS_BMP,3,5),IF(AND(D17="Bioretention",E17="Enhanced"),INDEX(PARAMS_BMP,4,5),IF(AND(D17="Bioretention",E17="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),IF(AND(D17="Dry Swale",E17="—"),INDEX(PARAMS_BMP,6,5),IF(AND(D17="Wet Swale",E17="—"),INDEX(PARAMS_BMP,7,5),""))))))),"")</f>
         <v/>
       </c>
       <c r="K17" s="17">
@@ -10438,17 +10438,17 @@
       </c>
       <c r="Q17" s="4" t="n"/>
       <c r="R17" s="17">
-        <f>IFERROR(IFS(AND(D17="Permeable Pavement",E17="Enhanced"),INDEX(PARAMS_BMP,1,3),AND(D17="Permeable Pavement",E17="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),AND(D17="Bioretention",E17="Standard"),INDEX(PARAMS_BMP,3,3),AND(D17="Bioretention",E17="Enhanced"),INDEX(PARAMS_BMP,4,3),AND(D17="Bioretention",E17="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),AND(D17="Dry Swale",E17="—"),INDEX(PARAMS_BMP,6,3),AND(D17="Wet Swale",E17="—"),INDEX(PARAMS_BMP,7,3),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D17="Permeable Pavement",E17="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D17="Permeable Pavement",E17="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D17="Bioretention",E17="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D17="Bioretention",E17="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D17="Bioretention",E17="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D17="Dry Swale",E17="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D17="Wet Swale",E17="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
       <c r="S17" s="4" t="n"/>
       <c r="T17" s="17">
-        <f>IFERROR(IFS(AND(D17="Permeable Pavement",E17="Enhanced"),INDEX(PARAMS_BMP,1,4),AND(D17="Permeable Pavement",E17="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),AND(D17="Bioretention",E17="Standard"),INDEX(PARAMS_BMP,3,4),AND(D17="Bioretention",E17="Enhanced"),INDEX(PARAMS_BMP,4,4),AND(D17="Bioretention",E17="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),AND(D17="Dry Swale",E17="—"),INDEX(PARAMS_BMP,6,4),AND(D17="Wet Swale",E17="—"),INDEX(PARAMS_BMP,7,4),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D17="Permeable Pavement",E17="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D17="Permeable Pavement",E17="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D17="Bioretention",E17="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D17="Bioretention",E17="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D17="Bioretention",E17="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D17="Dry Swale",E17="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D17="Wet Swale",E17="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
       <c r="U17" s="4" t="n"/>
       <c r="V17" s="4">
-        <f>IFERROR(IF(OR(E17="Enhanced",E17="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C17,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C17,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C17,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C17,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E17="Enhanced",E17="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C17,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C17,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C17,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C17,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="W17" s="17">
@@ -10480,7 +10480,7 @@
         <v/>
       </c>
       <c r="AJ17" s="17">
-        <f>IFERROR(IFS(AND(D17="Permeable Pavement",E17="Enhanced"),INDEX(PARAMS_BMP,1,6),AND(D17="Permeable Pavement",E17="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),AND(D17="Bioretention",E17="Standard"),INDEX(PARAMS_BMP,3,6),AND(D17="Bioretention",E17="Enhanced"),INDEX(PARAMS_BMP,4,6),AND(D17="Bioretention",E17="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),AND(D17="Dry Swale",E17="—"),INDEX(PARAMS_BMP,6,6),AND(D17="Wet Swale",E17="—"),INDEX(PARAMS_BMP,7,6),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D17="Permeable Pavement",E17="Enhanced"),INDEX(PARAMS_BMP,1,6),IF(AND(D17="Permeable Pavement",E17="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),IF(AND(D17="Bioretention",E17="Standard"),INDEX(PARAMS_BMP,3,6),IF(AND(D17="Bioretention",E17="Enhanced"),INDEX(PARAMS_BMP,4,6),IF(AND(D17="Bioretention",E17="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),IF(AND(D17="Dry Swale",E17="—"),INDEX(PARAMS_BMP,6,6),IF(AND(D17="Wet Swale",E17="—"),INDEX(PARAMS_BMP,7,6),""))))))),"")</f>
         <v/>
       </c>
       <c r="AK17" s="17">
@@ -10506,11 +10506,11 @@
       <c r="G18" s="4" t="n"/>
       <c r="H18" s="4" t="n"/>
       <c r="I18" s="4">
-        <f>IFERROR(IF(OR(E18="Enhanced",E18="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C18,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C18,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C18,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C18,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E18="Enhanced",E18="Underdrained Enhanced"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C18,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C18,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C18,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C18,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="J18" s="17">
-        <f>IFERROR(IFS(AND(D18="Permeable Pavement",E18="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D18="Permeable Pavement",E18="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D18="Bioretention",E18="Standard"),INDEX(PARAMS_BMP,3,5),AND(D18="Bioretention",E18="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D18="Bioretention",E18="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D18="Dry Swale",E18="—"),INDEX(PARAMS_BMP,6,5),AND(D18="Wet Swale",E18="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D18="Permeable Pavement",E18="Enhanced"),INDEX(PARAMS_BMP,1,5),IF(AND(D18="Permeable Pavement",E18="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),IF(AND(D18="Bioretention",E18="Standard"),INDEX(PARAMS_BMP,3,5),IF(AND(D18="Bioretention",E18="Enhanced"),INDEX(PARAMS_BMP,4,5),IF(AND(D18="Bioretention",E18="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),IF(AND(D18="Dry Swale",E18="—"),INDEX(PARAMS_BMP,6,5),IF(AND(D18="Wet Swale",E18="—"),INDEX(PARAMS_BMP,7,5),""))))))),"")</f>
         <v/>
       </c>
       <c r="K18" s="17">
@@ -10533,17 +10533,17 @@
       </c>
       <c r="Q18" s="4" t="n"/>
       <c r="R18" s="17">
-        <f>IFERROR(IFS(AND(D18="Permeable Pavement",E18="Enhanced"),INDEX(PARAMS_BMP,1,3),AND(D18="Permeable Pavement",E18="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),AND(D18="Bioretention",E18="Standard"),INDEX(PARAMS_BMP,3,3),AND(D18="Bioretention",E18="Enhanced"),INDEX(PARAMS_BMP,4,3),AND(D18="Bioretention",E18="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),AND(D18="Dry Swale",E18="—"),INDEX(PARAMS_BMP,6,3),AND(D18="Wet Swale",E18="—"),INDEX(PARAMS_BMP,7,3),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D18="Permeable Pavement",E18="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D18="Permeable Pavement",E18="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D18="Bioretention",E18="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D18="Bioretention",E18="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D18="Bioretention",E18="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D18="Dry Swale",E18="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D18="Wet Swale",E18="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
       <c r="S18" s="4" t="n"/>
       <c r="T18" s="17">
-        <f>IFERROR(IFS(AND(D18="Permeable Pavement",E18="Enhanced"),INDEX(PARAMS_BMP,1,4),AND(D18="Permeable Pavement",E18="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),AND(D18="Bioretention",E18="Standard"),INDEX(PARAMS_BMP,3,4),AND(D18="Bioretention",E18="Enhanced"),INDEX(PARAMS_BMP,4,4),AND(D18="Bioretention",E18="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),AND(D18="Dry Swale",E18="—"),INDEX(PARAMS_BMP,6,4),AND(D18="Wet Swale",E18="—"),INDEX(PARAMS_BMP,7,4),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D18="Permeable Pavement",E18="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D18="Permeable Pavement",E18="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D18="Bioretention",E18="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D18="Bioretention",E18="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D18="Bioretention",E18="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D18="Dry Swale",E18="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D18="Wet Swale",E18="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
       <c r="U18" s="4" t="n"/>
       <c r="V18" s="4">
-        <f>IFERROR(IF(OR(E18="Enhanced",E18="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C18,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C18,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C18,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C18,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E18="Enhanced",E18="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C18,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C18,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C18,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C18,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="W18" s="17">
@@ -10575,7 +10575,7 @@
         <v/>
       </c>
       <c r="AJ18" s="17">
-        <f>IFERROR(IFS(AND(D18="Permeable Pavement",E18="Enhanced"),INDEX(PARAMS_BMP,1,6),AND(D18="Permeable Pavement",E18="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),AND(D18="Bioretention",E18="Standard"),INDEX(PARAMS_BMP,3,6),AND(D18="Bioretention",E18="Enhanced"),INDEX(PARAMS_BMP,4,6),AND(D18="Bioretention",E18="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),AND(D18="Dry Swale",E18="—"),INDEX(PARAMS_BMP,6,6),AND(D18="Wet Swale",E18="—"),INDEX(PARAMS_BMP,7,6),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D18="Permeable Pavement",E18="Enhanced"),INDEX(PARAMS_BMP,1,6),IF(AND(D18="Permeable Pavement",E18="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),IF(AND(D18="Bioretention",E18="Standard"),INDEX(PARAMS_BMP,3,6),IF(AND(D18="Bioretention",E18="Enhanced"),INDEX(PARAMS_BMP,4,6),IF(AND(D18="Bioretention",E18="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),IF(AND(D18="Dry Swale",E18="—"),INDEX(PARAMS_BMP,6,6),IF(AND(D18="Wet Swale",E18="—"),INDEX(PARAMS_BMP,7,6),""))))))),"")</f>
         <v/>
       </c>
       <c r="AK18" s="17">
@@ -10601,11 +10601,11 @@
       <c r="G19" s="4" t="n"/>
       <c r="H19" s="4" t="n"/>
       <c r="I19" s="4">
-        <f>IFERROR(IF(OR(E19="Enhanced",E19="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C19,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C19,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C19,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C19,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E19="Enhanced",E19="Underdrained Enhanced"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C19,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C19,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C19,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C19,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="J19" s="17">
-        <f>IFERROR(IFS(AND(D19="Permeable Pavement",E19="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D19="Permeable Pavement",E19="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D19="Bioretention",E19="Standard"),INDEX(PARAMS_BMP,3,5),AND(D19="Bioretention",E19="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D19="Bioretention",E19="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D19="Dry Swale",E19="—"),INDEX(PARAMS_BMP,6,5),AND(D19="Wet Swale",E19="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D19="Permeable Pavement",E19="Enhanced"),INDEX(PARAMS_BMP,1,5),IF(AND(D19="Permeable Pavement",E19="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),IF(AND(D19="Bioretention",E19="Standard"),INDEX(PARAMS_BMP,3,5),IF(AND(D19="Bioretention",E19="Enhanced"),INDEX(PARAMS_BMP,4,5),IF(AND(D19="Bioretention",E19="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),IF(AND(D19="Dry Swale",E19="—"),INDEX(PARAMS_BMP,6,5),IF(AND(D19="Wet Swale",E19="—"),INDEX(PARAMS_BMP,7,5),""))))))),"")</f>
         <v/>
       </c>
       <c r="K19" s="17">
@@ -10628,17 +10628,17 @@
       </c>
       <c r="Q19" s="4" t="n"/>
       <c r="R19" s="17">
-        <f>IFERROR(IFS(AND(D19="Permeable Pavement",E19="Enhanced"),INDEX(PARAMS_BMP,1,3),AND(D19="Permeable Pavement",E19="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),AND(D19="Bioretention",E19="Standard"),INDEX(PARAMS_BMP,3,3),AND(D19="Bioretention",E19="Enhanced"),INDEX(PARAMS_BMP,4,3),AND(D19="Bioretention",E19="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),AND(D19="Dry Swale",E19="—"),INDEX(PARAMS_BMP,6,3),AND(D19="Wet Swale",E19="—"),INDEX(PARAMS_BMP,7,3),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D19="Permeable Pavement",E19="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D19="Permeable Pavement",E19="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D19="Bioretention",E19="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D19="Bioretention",E19="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D19="Bioretention",E19="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D19="Dry Swale",E19="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D19="Wet Swale",E19="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
       <c r="S19" s="4" t="n"/>
       <c r="T19" s="17">
-        <f>IFERROR(IFS(AND(D19="Permeable Pavement",E19="Enhanced"),INDEX(PARAMS_BMP,1,4),AND(D19="Permeable Pavement",E19="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),AND(D19="Bioretention",E19="Standard"),INDEX(PARAMS_BMP,3,4),AND(D19="Bioretention",E19="Enhanced"),INDEX(PARAMS_BMP,4,4),AND(D19="Bioretention",E19="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),AND(D19="Dry Swale",E19="—"),INDEX(PARAMS_BMP,6,4),AND(D19="Wet Swale",E19="—"),INDEX(PARAMS_BMP,7,4),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D19="Permeable Pavement",E19="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D19="Permeable Pavement",E19="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D19="Bioretention",E19="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D19="Bioretention",E19="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D19="Bioretention",E19="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D19="Dry Swale",E19="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D19="Wet Swale",E19="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
       <c r="U19" s="4" t="n"/>
       <c r="V19" s="4">
-        <f>IFERROR(IF(OR(E19="Enhanced",E19="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C19,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C19,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C19,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C19,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E19="Enhanced",E19="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C19,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C19,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C19,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C19,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="W19" s="17">
@@ -10670,7 +10670,7 @@
         <v/>
       </c>
       <c r="AJ19" s="17">
-        <f>IFERROR(IFS(AND(D19="Permeable Pavement",E19="Enhanced"),INDEX(PARAMS_BMP,1,6),AND(D19="Permeable Pavement",E19="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),AND(D19="Bioretention",E19="Standard"),INDEX(PARAMS_BMP,3,6),AND(D19="Bioretention",E19="Enhanced"),INDEX(PARAMS_BMP,4,6),AND(D19="Bioretention",E19="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),AND(D19="Dry Swale",E19="—"),INDEX(PARAMS_BMP,6,6),AND(D19="Wet Swale",E19="—"),INDEX(PARAMS_BMP,7,6),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D19="Permeable Pavement",E19="Enhanced"),INDEX(PARAMS_BMP,1,6),IF(AND(D19="Permeable Pavement",E19="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),IF(AND(D19="Bioretention",E19="Standard"),INDEX(PARAMS_BMP,3,6),IF(AND(D19="Bioretention",E19="Enhanced"),INDEX(PARAMS_BMP,4,6),IF(AND(D19="Bioretention",E19="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),IF(AND(D19="Dry Swale",E19="—"),INDEX(PARAMS_BMP,6,6),IF(AND(D19="Wet Swale",E19="—"),INDEX(PARAMS_BMP,7,6),""))))))),"")</f>
         <v/>
       </c>
       <c r="AK19" s="17">
@@ -10696,11 +10696,11 @@
       <c r="G20" s="4" t="n"/>
       <c r="H20" s="4" t="n"/>
       <c r="I20" s="4">
-        <f>IFERROR(IF(OR(E20="Enhanced",E20="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C20,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C20,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C20,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C20,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E20="Enhanced",E20="Underdrained Enhanced"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C20,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C20,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C20,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C20,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="J20" s="17">
-        <f>IFERROR(IFS(AND(D20="Permeable Pavement",E20="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D20="Permeable Pavement",E20="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D20="Bioretention",E20="Standard"),INDEX(PARAMS_BMP,3,5),AND(D20="Bioretention",E20="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D20="Bioretention",E20="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D20="Dry Swale",E20="—"),INDEX(PARAMS_BMP,6,5),AND(D20="Wet Swale",E20="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D20="Permeable Pavement",E20="Enhanced"),INDEX(PARAMS_BMP,1,5),IF(AND(D20="Permeable Pavement",E20="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),IF(AND(D20="Bioretention",E20="Standard"),INDEX(PARAMS_BMP,3,5),IF(AND(D20="Bioretention",E20="Enhanced"),INDEX(PARAMS_BMP,4,5),IF(AND(D20="Bioretention",E20="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),IF(AND(D20="Dry Swale",E20="—"),INDEX(PARAMS_BMP,6,5),IF(AND(D20="Wet Swale",E20="—"),INDEX(PARAMS_BMP,7,5),""))))))),"")</f>
         <v/>
       </c>
       <c r="K20" s="17">
@@ -10723,17 +10723,17 @@
       </c>
       <c r="Q20" s="4" t="n"/>
       <c r="R20" s="17">
-        <f>IFERROR(IFS(AND(D20="Permeable Pavement",E20="Enhanced"),INDEX(PARAMS_BMP,1,3),AND(D20="Permeable Pavement",E20="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),AND(D20="Bioretention",E20="Standard"),INDEX(PARAMS_BMP,3,3),AND(D20="Bioretention",E20="Enhanced"),INDEX(PARAMS_BMP,4,3),AND(D20="Bioretention",E20="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),AND(D20="Dry Swale",E20="—"),INDEX(PARAMS_BMP,6,3),AND(D20="Wet Swale",E20="—"),INDEX(PARAMS_BMP,7,3),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D20="Permeable Pavement",E20="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D20="Permeable Pavement",E20="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D20="Bioretention",E20="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D20="Bioretention",E20="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D20="Bioretention",E20="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D20="Dry Swale",E20="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D20="Wet Swale",E20="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
       <c r="S20" s="4" t="n"/>
       <c r="T20" s="17">
-        <f>IFERROR(IFS(AND(D20="Permeable Pavement",E20="Enhanced"),INDEX(PARAMS_BMP,1,4),AND(D20="Permeable Pavement",E20="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),AND(D20="Bioretention",E20="Standard"),INDEX(PARAMS_BMP,3,4),AND(D20="Bioretention",E20="Enhanced"),INDEX(PARAMS_BMP,4,4),AND(D20="Bioretention",E20="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),AND(D20="Dry Swale",E20="—"),INDEX(PARAMS_BMP,6,4),AND(D20="Wet Swale",E20="—"),INDEX(PARAMS_BMP,7,4),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D20="Permeable Pavement",E20="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D20="Permeable Pavement",E20="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D20="Bioretention",E20="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D20="Bioretention",E20="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D20="Bioretention",E20="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D20="Dry Swale",E20="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D20="Wet Swale",E20="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
       <c r="U20" s="4" t="n"/>
       <c r="V20" s="4">
-        <f>IFERROR(IF(OR(E20="Enhanced",E20="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C20,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C20,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C20,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C20,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E20="Enhanced",E20="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C20,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C20,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C20,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C20,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="W20" s="17">
@@ -10765,7 +10765,7 @@
         <v/>
       </c>
       <c r="AJ20" s="17">
-        <f>IFERROR(IFS(AND(D20="Permeable Pavement",E20="Enhanced"),INDEX(PARAMS_BMP,1,6),AND(D20="Permeable Pavement",E20="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),AND(D20="Bioretention",E20="Standard"),INDEX(PARAMS_BMP,3,6),AND(D20="Bioretention",E20="Enhanced"),INDEX(PARAMS_BMP,4,6),AND(D20="Bioretention",E20="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),AND(D20="Dry Swale",E20="—"),INDEX(PARAMS_BMP,6,6),AND(D20="Wet Swale",E20="—"),INDEX(PARAMS_BMP,7,6),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D20="Permeable Pavement",E20="Enhanced"),INDEX(PARAMS_BMP,1,6),IF(AND(D20="Permeable Pavement",E20="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),IF(AND(D20="Bioretention",E20="Standard"),INDEX(PARAMS_BMP,3,6),IF(AND(D20="Bioretention",E20="Enhanced"),INDEX(PARAMS_BMP,4,6),IF(AND(D20="Bioretention",E20="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),IF(AND(D20="Dry Swale",E20="—"),INDEX(PARAMS_BMP,6,6),IF(AND(D20="Wet Swale",E20="—"),INDEX(PARAMS_BMP,7,6),""))))))),"")</f>
         <v/>
       </c>
       <c r="AK20" s="17">
@@ -10791,11 +10791,11 @@
       <c r="G21" s="4" t="n"/>
       <c r="H21" s="4" t="n"/>
       <c r="I21" s="4">
-        <f>IFERROR(IF(OR(E21="Enhanced",E21="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C21,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C21,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C21,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C21,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E21="Enhanced",E21="Underdrained Enhanced"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C21,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C21,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C21,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C21,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="J21" s="17">
-        <f>IFERROR(IFS(AND(D21="Permeable Pavement",E21="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D21="Permeable Pavement",E21="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D21="Bioretention",E21="Standard"),INDEX(PARAMS_BMP,3,5),AND(D21="Bioretention",E21="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D21="Bioretention",E21="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D21="Dry Swale",E21="—"),INDEX(PARAMS_BMP,6,5),AND(D21="Wet Swale",E21="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D21="Permeable Pavement",E21="Enhanced"),INDEX(PARAMS_BMP,1,5),IF(AND(D21="Permeable Pavement",E21="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),IF(AND(D21="Bioretention",E21="Standard"),INDEX(PARAMS_BMP,3,5),IF(AND(D21="Bioretention",E21="Enhanced"),INDEX(PARAMS_BMP,4,5),IF(AND(D21="Bioretention",E21="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),IF(AND(D21="Dry Swale",E21="—"),INDEX(PARAMS_BMP,6,5),IF(AND(D21="Wet Swale",E21="—"),INDEX(PARAMS_BMP,7,5),""))))))),"")</f>
         <v/>
       </c>
       <c r="K21" s="17">
@@ -10818,17 +10818,17 @@
       </c>
       <c r="Q21" s="4" t="n"/>
       <c r="R21" s="17">
-        <f>IFERROR(IFS(AND(D21="Permeable Pavement",E21="Enhanced"),INDEX(PARAMS_BMP,1,3),AND(D21="Permeable Pavement",E21="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),AND(D21="Bioretention",E21="Standard"),INDEX(PARAMS_BMP,3,3),AND(D21="Bioretention",E21="Enhanced"),INDEX(PARAMS_BMP,4,3),AND(D21="Bioretention",E21="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),AND(D21="Dry Swale",E21="—"),INDEX(PARAMS_BMP,6,3),AND(D21="Wet Swale",E21="—"),INDEX(PARAMS_BMP,7,3),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D21="Permeable Pavement",E21="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D21="Permeable Pavement",E21="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D21="Bioretention",E21="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D21="Bioretention",E21="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D21="Bioretention",E21="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D21="Dry Swale",E21="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D21="Wet Swale",E21="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
       <c r="S21" s="4" t="n"/>
       <c r="T21" s="17">
-        <f>IFERROR(IFS(AND(D21="Permeable Pavement",E21="Enhanced"),INDEX(PARAMS_BMP,1,4),AND(D21="Permeable Pavement",E21="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),AND(D21="Bioretention",E21="Standard"),INDEX(PARAMS_BMP,3,4),AND(D21="Bioretention",E21="Enhanced"),INDEX(PARAMS_BMP,4,4),AND(D21="Bioretention",E21="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),AND(D21="Dry Swale",E21="—"),INDEX(PARAMS_BMP,6,4),AND(D21="Wet Swale",E21="—"),INDEX(PARAMS_BMP,7,4),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D21="Permeable Pavement",E21="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D21="Permeable Pavement",E21="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D21="Bioretention",E21="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D21="Bioretention",E21="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D21="Bioretention",E21="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D21="Dry Swale",E21="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D21="Wet Swale",E21="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
       <c r="U21" s="4" t="n"/>
       <c r="V21" s="4">
-        <f>IFERROR(IF(OR(E21="Enhanced",E21="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C21,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C21,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C21,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C21,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E21="Enhanced",E21="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C21,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C21,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C21,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C21,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="W21" s="17">
@@ -10860,7 +10860,7 @@
         <v/>
       </c>
       <c r="AJ21" s="17">
-        <f>IFERROR(IFS(AND(D21="Permeable Pavement",E21="Enhanced"),INDEX(PARAMS_BMP,1,6),AND(D21="Permeable Pavement",E21="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),AND(D21="Bioretention",E21="Standard"),INDEX(PARAMS_BMP,3,6),AND(D21="Bioretention",E21="Enhanced"),INDEX(PARAMS_BMP,4,6),AND(D21="Bioretention",E21="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),AND(D21="Dry Swale",E21="—"),INDEX(PARAMS_BMP,6,6),AND(D21="Wet Swale",E21="—"),INDEX(PARAMS_BMP,7,6),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D21="Permeable Pavement",E21="Enhanced"),INDEX(PARAMS_BMP,1,6),IF(AND(D21="Permeable Pavement",E21="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),IF(AND(D21="Bioretention",E21="Standard"),INDEX(PARAMS_BMP,3,6),IF(AND(D21="Bioretention",E21="Enhanced"),INDEX(PARAMS_BMP,4,6),IF(AND(D21="Bioretention",E21="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),IF(AND(D21="Dry Swale",E21="—"),INDEX(PARAMS_BMP,6,6),IF(AND(D21="Wet Swale",E21="—"),INDEX(PARAMS_BMP,7,6),""))))))),"")</f>
         <v/>
       </c>
       <c r="AK21" s="17">
@@ -10886,11 +10886,11 @@
       <c r="G22" s="4" t="n"/>
       <c r="H22" s="4" t="n"/>
       <c r="I22" s="4">
-        <f>IFERROR(IF(OR(E22="Enhanced",E22="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C22,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C22,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C22,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C22,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E22="Enhanced",E22="Underdrained Enhanced"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C22,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C22,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C22,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C22,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="J22" s="17">
-        <f>IFERROR(IFS(AND(D22="Permeable Pavement",E22="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D22="Permeable Pavement",E22="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D22="Bioretention",E22="Standard"),INDEX(PARAMS_BMP,3,5),AND(D22="Bioretention",E22="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D22="Bioretention",E22="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D22="Dry Swale",E22="—"),INDEX(PARAMS_BMP,6,5),AND(D22="Wet Swale",E22="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D22="Permeable Pavement",E22="Enhanced"),INDEX(PARAMS_BMP,1,5),IF(AND(D22="Permeable Pavement",E22="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),IF(AND(D22="Bioretention",E22="Standard"),INDEX(PARAMS_BMP,3,5),IF(AND(D22="Bioretention",E22="Enhanced"),INDEX(PARAMS_BMP,4,5),IF(AND(D22="Bioretention",E22="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),IF(AND(D22="Dry Swale",E22="—"),INDEX(PARAMS_BMP,6,5),IF(AND(D22="Wet Swale",E22="—"),INDEX(PARAMS_BMP,7,5),""))))))),"")</f>
         <v/>
       </c>
       <c r="K22" s="17">
@@ -10913,17 +10913,17 @@
       </c>
       <c r="Q22" s="4" t="n"/>
       <c r="R22" s="17">
-        <f>IFERROR(IFS(AND(D22="Permeable Pavement",E22="Enhanced"),INDEX(PARAMS_BMP,1,3),AND(D22="Permeable Pavement",E22="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),AND(D22="Bioretention",E22="Standard"),INDEX(PARAMS_BMP,3,3),AND(D22="Bioretention",E22="Enhanced"),INDEX(PARAMS_BMP,4,3),AND(D22="Bioretention",E22="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),AND(D22="Dry Swale",E22="—"),INDEX(PARAMS_BMP,6,3),AND(D22="Wet Swale",E22="—"),INDEX(PARAMS_BMP,7,3),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D22="Permeable Pavement",E22="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D22="Permeable Pavement",E22="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D22="Bioretention",E22="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D22="Bioretention",E22="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D22="Bioretention",E22="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D22="Dry Swale",E22="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D22="Wet Swale",E22="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
       <c r="S22" s="4" t="n"/>
       <c r="T22" s="17">
-        <f>IFERROR(IFS(AND(D22="Permeable Pavement",E22="Enhanced"),INDEX(PARAMS_BMP,1,4),AND(D22="Permeable Pavement",E22="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),AND(D22="Bioretention",E22="Standard"),INDEX(PARAMS_BMP,3,4),AND(D22="Bioretention",E22="Enhanced"),INDEX(PARAMS_BMP,4,4),AND(D22="Bioretention",E22="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),AND(D22="Dry Swale",E22="—"),INDEX(PARAMS_BMP,6,4),AND(D22="Wet Swale",E22="—"),INDEX(PARAMS_BMP,7,4),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D22="Permeable Pavement",E22="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D22="Permeable Pavement",E22="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D22="Bioretention",E22="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D22="Bioretention",E22="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D22="Bioretention",E22="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D22="Dry Swale",E22="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D22="Wet Swale",E22="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
       <c r="U22" s="4" t="n"/>
       <c r="V22" s="4">
-        <f>IFERROR(IF(OR(E22="Enhanced",E22="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C22,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C22,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C22,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C22,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E22="Enhanced",E22="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C22,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C22,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C22,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C22,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="W22" s="17">
@@ -10955,7 +10955,7 @@
         <v/>
       </c>
       <c r="AJ22" s="17">
-        <f>IFERROR(IFS(AND(D22="Permeable Pavement",E22="Enhanced"),INDEX(PARAMS_BMP,1,6),AND(D22="Permeable Pavement",E22="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),AND(D22="Bioretention",E22="Standard"),INDEX(PARAMS_BMP,3,6),AND(D22="Bioretention",E22="Enhanced"),INDEX(PARAMS_BMP,4,6),AND(D22="Bioretention",E22="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),AND(D22="Dry Swale",E22="—"),INDEX(PARAMS_BMP,6,6),AND(D22="Wet Swale",E22="—"),INDEX(PARAMS_BMP,7,6),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D22="Permeable Pavement",E22="Enhanced"),INDEX(PARAMS_BMP,1,6),IF(AND(D22="Permeable Pavement",E22="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),IF(AND(D22="Bioretention",E22="Standard"),INDEX(PARAMS_BMP,3,6),IF(AND(D22="Bioretention",E22="Enhanced"),INDEX(PARAMS_BMP,4,6),IF(AND(D22="Bioretention",E22="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),IF(AND(D22="Dry Swale",E22="—"),INDEX(PARAMS_BMP,6,6),IF(AND(D22="Wet Swale",E22="—"),INDEX(PARAMS_BMP,7,6),""))))))),"")</f>
         <v/>
       </c>
       <c r="AK22" s="17">
@@ -10981,11 +10981,11 @@
       <c r="G23" s="4" t="n"/>
       <c r="H23" s="4" t="n"/>
       <c r="I23" s="4">
-        <f>IFERROR(IF(OR(E23="Enhanced",E23="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C23,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C23,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C23,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C23,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E23="Enhanced",E23="Underdrained Enhanced"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C23,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C23,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C23,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C23,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="J23" s="17">
-        <f>IFERROR(IFS(AND(D23="Permeable Pavement",E23="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D23="Permeable Pavement",E23="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D23="Bioretention",E23="Standard"),INDEX(PARAMS_BMP,3,5),AND(D23="Bioretention",E23="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D23="Bioretention",E23="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D23="Dry Swale",E23="—"),INDEX(PARAMS_BMP,6,5),AND(D23="Wet Swale",E23="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D23="Permeable Pavement",E23="Enhanced"),INDEX(PARAMS_BMP,1,5),IF(AND(D23="Permeable Pavement",E23="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),IF(AND(D23="Bioretention",E23="Standard"),INDEX(PARAMS_BMP,3,5),IF(AND(D23="Bioretention",E23="Enhanced"),INDEX(PARAMS_BMP,4,5),IF(AND(D23="Bioretention",E23="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),IF(AND(D23="Dry Swale",E23="—"),INDEX(PARAMS_BMP,6,5),IF(AND(D23="Wet Swale",E23="—"),INDEX(PARAMS_BMP,7,5),""))))))),"")</f>
         <v/>
       </c>
       <c r="K23" s="17">
@@ -11008,17 +11008,17 @@
       </c>
       <c r="Q23" s="4" t="n"/>
       <c r="R23" s="17">
-        <f>IFERROR(IFS(AND(D23="Permeable Pavement",E23="Enhanced"),INDEX(PARAMS_BMP,1,3),AND(D23="Permeable Pavement",E23="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),AND(D23="Bioretention",E23="Standard"),INDEX(PARAMS_BMP,3,3),AND(D23="Bioretention",E23="Enhanced"),INDEX(PARAMS_BMP,4,3),AND(D23="Bioretention",E23="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),AND(D23="Dry Swale",E23="—"),INDEX(PARAMS_BMP,6,3),AND(D23="Wet Swale",E23="—"),INDEX(PARAMS_BMP,7,3),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D23="Permeable Pavement",E23="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D23="Permeable Pavement",E23="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D23="Bioretention",E23="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D23="Bioretention",E23="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D23="Bioretention",E23="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D23="Dry Swale",E23="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D23="Wet Swale",E23="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
       <c r="S23" s="4" t="n"/>
       <c r="T23" s="17">
-        <f>IFERROR(IFS(AND(D23="Permeable Pavement",E23="Enhanced"),INDEX(PARAMS_BMP,1,4),AND(D23="Permeable Pavement",E23="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),AND(D23="Bioretention",E23="Standard"),INDEX(PARAMS_BMP,3,4),AND(D23="Bioretention",E23="Enhanced"),INDEX(PARAMS_BMP,4,4),AND(D23="Bioretention",E23="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),AND(D23="Dry Swale",E23="—"),INDEX(PARAMS_BMP,6,4),AND(D23="Wet Swale",E23="—"),INDEX(PARAMS_BMP,7,4),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D23="Permeable Pavement",E23="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D23="Permeable Pavement",E23="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D23="Bioretention",E23="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D23="Bioretention",E23="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D23="Bioretention",E23="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D23="Dry Swale",E23="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D23="Wet Swale",E23="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
       <c r="U23" s="4" t="n"/>
       <c r="V23" s="4">
-        <f>IFERROR(IF(OR(E23="Enhanced",E23="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C23,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C23,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C23,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C23,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E23="Enhanced",E23="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C23,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C23,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C23,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C23,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="W23" s="17">
@@ -11050,7 +11050,7 @@
         <v/>
       </c>
       <c r="AJ23" s="17">
-        <f>IFERROR(IFS(AND(D23="Permeable Pavement",E23="Enhanced"),INDEX(PARAMS_BMP,1,6),AND(D23="Permeable Pavement",E23="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),AND(D23="Bioretention",E23="Standard"),INDEX(PARAMS_BMP,3,6),AND(D23="Bioretention",E23="Enhanced"),INDEX(PARAMS_BMP,4,6),AND(D23="Bioretention",E23="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),AND(D23="Dry Swale",E23="—"),INDEX(PARAMS_BMP,6,6),AND(D23="Wet Swale",E23="—"),INDEX(PARAMS_BMP,7,6),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D23="Permeable Pavement",E23="Enhanced"),INDEX(PARAMS_BMP,1,6),IF(AND(D23="Permeable Pavement",E23="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),IF(AND(D23="Bioretention",E23="Standard"),INDEX(PARAMS_BMP,3,6),IF(AND(D23="Bioretention",E23="Enhanced"),INDEX(PARAMS_BMP,4,6),IF(AND(D23="Bioretention",E23="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),IF(AND(D23="Dry Swale",E23="—"),INDEX(PARAMS_BMP,6,6),IF(AND(D23="Wet Swale",E23="—"),INDEX(PARAMS_BMP,7,6),""))))))),"")</f>
         <v/>
       </c>
       <c r="AK23" s="17">
@@ -11076,11 +11076,11 @@
       <c r="G24" s="4" t="n"/>
       <c r="H24" s="4" t="n"/>
       <c r="I24" s="4">
-        <f>IFERROR(IF(OR(E24="Enhanced",E24="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C24,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C24,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C24,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C24,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E24="Enhanced",E24="Underdrained Enhanced"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C24,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C24,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C24,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C24,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="J24" s="17">
-        <f>IFERROR(IFS(AND(D24="Permeable Pavement",E24="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D24="Permeable Pavement",E24="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D24="Bioretention",E24="Standard"),INDEX(PARAMS_BMP,3,5),AND(D24="Bioretention",E24="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D24="Bioretention",E24="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D24="Dry Swale",E24="—"),INDEX(PARAMS_BMP,6,5),AND(D24="Wet Swale",E24="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D24="Permeable Pavement",E24="Enhanced"),INDEX(PARAMS_BMP,1,5),IF(AND(D24="Permeable Pavement",E24="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),IF(AND(D24="Bioretention",E24="Standard"),INDEX(PARAMS_BMP,3,5),IF(AND(D24="Bioretention",E24="Enhanced"),INDEX(PARAMS_BMP,4,5),IF(AND(D24="Bioretention",E24="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),IF(AND(D24="Dry Swale",E24="—"),INDEX(PARAMS_BMP,6,5),IF(AND(D24="Wet Swale",E24="—"),INDEX(PARAMS_BMP,7,5),""))))))),"")</f>
         <v/>
       </c>
       <c r="K24" s="17">
@@ -11103,17 +11103,17 @@
       </c>
       <c r="Q24" s="4" t="n"/>
       <c r="R24" s="17">
-        <f>IFERROR(IFS(AND(D24="Permeable Pavement",E24="Enhanced"),INDEX(PARAMS_BMP,1,3),AND(D24="Permeable Pavement",E24="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),AND(D24="Bioretention",E24="Standard"),INDEX(PARAMS_BMP,3,3),AND(D24="Bioretention",E24="Enhanced"),INDEX(PARAMS_BMP,4,3),AND(D24="Bioretention",E24="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),AND(D24="Dry Swale",E24="—"),INDEX(PARAMS_BMP,6,3),AND(D24="Wet Swale",E24="—"),INDEX(PARAMS_BMP,7,3),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D24="Permeable Pavement",E24="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D24="Permeable Pavement",E24="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D24="Bioretention",E24="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D24="Bioretention",E24="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D24="Bioretention",E24="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D24="Dry Swale",E24="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D24="Wet Swale",E24="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
       <c r="S24" s="4" t="n"/>
       <c r="T24" s="17">
-        <f>IFERROR(IFS(AND(D24="Permeable Pavement",E24="Enhanced"),INDEX(PARAMS_BMP,1,4),AND(D24="Permeable Pavement",E24="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),AND(D24="Bioretention",E24="Standard"),INDEX(PARAMS_BMP,3,4),AND(D24="Bioretention",E24="Enhanced"),INDEX(PARAMS_BMP,4,4),AND(D24="Bioretention",E24="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),AND(D24="Dry Swale",E24="—"),INDEX(PARAMS_BMP,6,4),AND(D24="Wet Swale",E24="—"),INDEX(PARAMS_BMP,7,4),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D24="Permeable Pavement",E24="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D24="Permeable Pavement",E24="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D24="Bioretention",E24="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D24="Bioretention",E24="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D24="Bioretention",E24="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D24="Dry Swale",E24="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D24="Wet Swale",E24="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
       <c r="U24" s="4" t="n"/>
       <c r="V24" s="4">
-        <f>IFERROR(IF(OR(E24="Enhanced",E24="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C24,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C24,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C24,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C24,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E24="Enhanced",E24="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C24,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C24,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C24,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C24,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="W24" s="17">
@@ -11145,7 +11145,7 @@
         <v/>
       </c>
       <c r="AJ24" s="17">
-        <f>IFERROR(IFS(AND(D24="Permeable Pavement",E24="Enhanced"),INDEX(PARAMS_BMP,1,6),AND(D24="Permeable Pavement",E24="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),AND(D24="Bioretention",E24="Standard"),INDEX(PARAMS_BMP,3,6),AND(D24="Bioretention",E24="Enhanced"),INDEX(PARAMS_BMP,4,6),AND(D24="Bioretention",E24="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),AND(D24="Dry Swale",E24="—"),INDEX(PARAMS_BMP,6,6),AND(D24="Wet Swale",E24="—"),INDEX(PARAMS_BMP,7,6),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D24="Permeable Pavement",E24="Enhanced"),INDEX(PARAMS_BMP,1,6),IF(AND(D24="Permeable Pavement",E24="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),IF(AND(D24="Bioretention",E24="Standard"),INDEX(PARAMS_BMP,3,6),IF(AND(D24="Bioretention",E24="Enhanced"),INDEX(PARAMS_BMP,4,6),IF(AND(D24="Bioretention",E24="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),IF(AND(D24="Dry Swale",E24="—"),INDEX(PARAMS_BMP,6,6),IF(AND(D24="Wet Swale",E24="—"),INDEX(PARAMS_BMP,7,6),""))))))),"")</f>
         <v/>
       </c>
       <c r="AK24" s="17">
@@ -11171,11 +11171,11 @@
       <c r="G25" s="4" t="n"/>
       <c r="H25" s="4" t="n"/>
       <c r="I25" s="4">
-        <f>IFERROR(IF(OR(E25="Enhanced",E25="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C25,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C25,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C25,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C25,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E25="Enhanced",E25="Underdrained Enhanced"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C25,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C25,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C25,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C25,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="J25" s="17">
-        <f>IFERROR(IFS(AND(D25="Permeable Pavement",E25="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D25="Permeable Pavement",E25="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D25="Bioretention",E25="Standard"),INDEX(PARAMS_BMP,3,5),AND(D25="Bioretention",E25="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D25="Bioretention",E25="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D25="Dry Swale",E25="—"),INDEX(PARAMS_BMP,6,5),AND(D25="Wet Swale",E25="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D25="Permeable Pavement",E25="Enhanced"),INDEX(PARAMS_BMP,1,5),IF(AND(D25="Permeable Pavement",E25="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),IF(AND(D25="Bioretention",E25="Standard"),INDEX(PARAMS_BMP,3,5),IF(AND(D25="Bioretention",E25="Enhanced"),INDEX(PARAMS_BMP,4,5),IF(AND(D25="Bioretention",E25="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),IF(AND(D25="Dry Swale",E25="—"),INDEX(PARAMS_BMP,6,5),IF(AND(D25="Wet Swale",E25="—"),INDEX(PARAMS_BMP,7,5),""))))))),"")</f>
         <v/>
       </c>
       <c r="K25" s="17">
@@ -11198,17 +11198,17 @@
       </c>
       <c r="Q25" s="4" t="n"/>
       <c r="R25" s="17">
-        <f>IFERROR(IFS(AND(D25="Permeable Pavement",E25="Enhanced"),INDEX(PARAMS_BMP,1,3),AND(D25="Permeable Pavement",E25="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),AND(D25="Bioretention",E25="Standard"),INDEX(PARAMS_BMP,3,3),AND(D25="Bioretention",E25="Enhanced"),INDEX(PARAMS_BMP,4,3),AND(D25="Bioretention",E25="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),AND(D25="Dry Swale",E25="—"),INDEX(PARAMS_BMP,6,3),AND(D25="Wet Swale",E25="—"),INDEX(PARAMS_BMP,7,3),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D25="Permeable Pavement",E25="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D25="Permeable Pavement",E25="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D25="Bioretention",E25="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D25="Bioretention",E25="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D25="Bioretention",E25="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D25="Dry Swale",E25="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D25="Wet Swale",E25="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
       <c r="S25" s="4" t="n"/>
       <c r="T25" s="17">
-        <f>IFERROR(IFS(AND(D25="Permeable Pavement",E25="Enhanced"),INDEX(PARAMS_BMP,1,4),AND(D25="Permeable Pavement",E25="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),AND(D25="Bioretention",E25="Standard"),INDEX(PARAMS_BMP,3,4),AND(D25="Bioretention",E25="Enhanced"),INDEX(PARAMS_BMP,4,4),AND(D25="Bioretention",E25="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),AND(D25="Dry Swale",E25="—"),INDEX(PARAMS_BMP,6,4),AND(D25="Wet Swale",E25="—"),INDEX(PARAMS_BMP,7,4),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D25="Permeable Pavement",E25="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D25="Permeable Pavement",E25="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D25="Bioretention",E25="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D25="Bioretention",E25="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D25="Bioretention",E25="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D25="Dry Swale",E25="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D25="Wet Swale",E25="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
       <c r="U25" s="4" t="n"/>
       <c r="V25" s="4">
-        <f>IFERROR(IF(OR(E25="Enhanced",E25="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C25,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C25,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C25,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C25,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E25="Enhanced",E25="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C25,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C25,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C25,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C25,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="W25" s="17">
@@ -11240,7 +11240,7 @@
         <v/>
       </c>
       <c r="AJ25" s="17">
-        <f>IFERROR(IFS(AND(D25="Permeable Pavement",E25="Enhanced"),INDEX(PARAMS_BMP,1,6),AND(D25="Permeable Pavement",E25="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),AND(D25="Bioretention",E25="Standard"),INDEX(PARAMS_BMP,3,6),AND(D25="Bioretention",E25="Enhanced"),INDEX(PARAMS_BMP,4,6),AND(D25="Bioretention",E25="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),AND(D25="Dry Swale",E25="—"),INDEX(PARAMS_BMP,6,6),AND(D25="Wet Swale",E25="—"),INDEX(PARAMS_BMP,7,6),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D25="Permeable Pavement",E25="Enhanced"),INDEX(PARAMS_BMP,1,6),IF(AND(D25="Permeable Pavement",E25="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),IF(AND(D25="Bioretention",E25="Standard"),INDEX(PARAMS_BMP,3,6),IF(AND(D25="Bioretention",E25="Enhanced"),INDEX(PARAMS_BMP,4,6),IF(AND(D25="Bioretention",E25="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),IF(AND(D25="Dry Swale",E25="—"),INDEX(PARAMS_BMP,6,6),IF(AND(D25="Wet Swale",E25="—"),INDEX(PARAMS_BMP,7,6),""))))))),"")</f>
         <v/>
       </c>
       <c r="AK25" s="17">
@@ -11266,11 +11266,11 @@
       <c r="G26" s="4" t="n"/>
       <c r="H26" s="4" t="n"/>
       <c r="I26" s="4">
-        <f>IFERROR(IF(OR(E26="Enhanced",E26="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C26,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C26,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C26,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C26,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E26="Enhanced",E26="Underdrained Enhanced"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C26,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C26,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C26,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C26,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="J26" s="17">
-        <f>IFERROR(IFS(AND(D26="Permeable Pavement",E26="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D26="Permeable Pavement",E26="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D26="Bioretention",E26="Standard"),INDEX(PARAMS_BMP,3,5),AND(D26="Bioretention",E26="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D26="Bioretention",E26="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D26="Dry Swale",E26="—"),INDEX(PARAMS_BMP,6,5),AND(D26="Wet Swale",E26="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D26="Permeable Pavement",E26="Enhanced"),INDEX(PARAMS_BMP,1,5),IF(AND(D26="Permeable Pavement",E26="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),IF(AND(D26="Bioretention",E26="Standard"),INDEX(PARAMS_BMP,3,5),IF(AND(D26="Bioretention",E26="Enhanced"),INDEX(PARAMS_BMP,4,5),IF(AND(D26="Bioretention",E26="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),IF(AND(D26="Dry Swale",E26="—"),INDEX(PARAMS_BMP,6,5),IF(AND(D26="Wet Swale",E26="—"),INDEX(PARAMS_BMP,7,5),""))))))),"")</f>
         <v/>
       </c>
       <c r="K26" s="17">
@@ -11293,17 +11293,17 @@
       </c>
       <c r="Q26" s="4" t="n"/>
       <c r="R26" s="17">
-        <f>IFERROR(IFS(AND(D26="Permeable Pavement",E26="Enhanced"),INDEX(PARAMS_BMP,1,3),AND(D26="Permeable Pavement",E26="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),AND(D26="Bioretention",E26="Standard"),INDEX(PARAMS_BMP,3,3),AND(D26="Bioretention",E26="Enhanced"),INDEX(PARAMS_BMP,4,3),AND(D26="Bioretention",E26="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),AND(D26="Dry Swale",E26="—"),INDEX(PARAMS_BMP,6,3),AND(D26="Wet Swale",E26="—"),INDEX(PARAMS_BMP,7,3),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D26="Permeable Pavement",E26="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D26="Permeable Pavement",E26="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D26="Bioretention",E26="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D26="Bioretention",E26="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D26="Bioretention",E26="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D26="Dry Swale",E26="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D26="Wet Swale",E26="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
       <c r="S26" s="4" t="n"/>
       <c r="T26" s="17">
-        <f>IFERROR(IFS(AND(D26="Permeable Pavement",E26="Enhanced"),INDEX(PARAMS_BMP,1,4),AND(D26="Permeable Pavement",E26="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),AND(D26="Bioretention",E26="Standard"),INDEX(PARAMS_BMP,3,4),AND(D26="Bioretention",E26="Enhanced"),INDEX(PARAMS_BMP,4,4),AND(D26="Bioretention",E26="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),AND(D26="Dry Swale",E26="—"),INDEX(PARAMS_BMP,6,4),AND(D26="Wet Swale",E26="—"),INDEX(PARAMS_BMP,7,4),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D26="Permeable Pavement",E26="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D26="Permeable Pavement",E26="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D26="Bioretention",E26="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D26="Bioretention",E26="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D26="Bioretention",E26="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D26="Dry Swale",E26="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D26="Wet Swale",E26="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
       <c r="U26" s="4" t="n"/>
       <c r="V26" s="4">
-        <f>IFERROR(IF(OR(E26="Enhanced",E26="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C26,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C26,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C26,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C26,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E26="Enhanced",E26="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C26,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C26,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C26,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C26,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="W26" s="17">
@@ -11335,7 +11335,7 @@
         <v/>
       </c>
       <c r="AJ26" s="17">
-        <f>IFERROR(IFS(AND(D26="Permeable Pavement",E26="Enhanced"),INDEX(PARAMS_BMP,1,6),AND(D26="Permeable Pavement",E26="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),AND(D26="Bioretention",E26="Standard"),INDEX(PARAMS_BMP,3,6),AND(D26="Bioretention",E26="Enhanced"),INDEX(PARAMS_BMP,4,6),AND(D26="Bioretention",E26="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),AND(D26="Dry Swale",E26="—"),INDEX(PARAMS_BMP,6,6),AND(D26="Wet Swale",E26="—"),INDEX(PARAMS_BMP,7,6),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D26="Permeable Pavement",E26="Enhanced"),INDEX(PARAMS_BMP,1,6),IF(AND(D26="Permeable Pavement",E26="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),IF(AND(D26="Bioretention",E26="Standard"),INDEX(PARAMS_BMP,3,6),IF(AND(D26="Bioretention",E26="Enhanced"),INDEX(PARAMS_BMP,4,6),IF(AND(D26="Bioretention",E26="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),IF(AND(D26="Dry Swale",E26="—"),INDEX(PARAMS_BMP,6,6),IF(AND(D26="Wet Swale",E26="—"),INDEX(PARAMS_BMP,7,6),""))))))),"")</f>
         <v/>
       </c>
       <c r="AK26" s="17">
@@ -11361,11 +11361,11 @@
       <c r="G27" s="4" t="n"/>
       <c r="H27" s="4" t="n"/>
       <c r="I27" s="4">
-        <f>IFERROR(IF(OR(E27="Enhanced",E27="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C27,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C27,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C27,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C27,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E27="Enhanced",E27="Underdrained Enhanced"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C27,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C27,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C27,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C27,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="J27" s="17">
-        <f>IFERROR(IFS(AND(D27="Permeable Pavement",E27="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D27="Permeable Pavement",E27="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D27="Bioretention",E27="Standard"),INDEX(PARAMS_BMP,3,5),AND(D27="Bioretention",E27="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D27="Bioretention",E27="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D27="Dry Swale",E27="—"),INDEX(PARAMS_BMP,6,5),AND(D27="Wet Swale",E27="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D27="Permeable Pavement",E27="Enhanced"),INDEX(PARAMS_BMP,1,5),IF(AND(D27="Permeable Pavement",E27="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),IF(AND(D27="Bioretention",E27="Standard"),INDEX(PARAMS_BMP,3,5),IF(AND(D27="Bioretention",E27="Enhanced"),INDEX(PARAMS_BMP,4,5),IF(AND(D27="Bioretention",E27="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),IF(AND(D27="Dry Swale",E27="—"),INDEX(PARAMS_BMP,6,5),IF(AND(D27="Wet Swale",E27="—"),INDEX(PARAMS_BMP,7,5),""))))))),"")</f>
         <v/>
       </c>
       <c r="K27" s="17">
@@ -11388,17 +11388,17 @@
       </c>
       <c r="Q27" s="4" t="n"/>
       <c r="R27" s="17">
-        <f>IFERROR(IFS(AND(D27="Permeable Pavement",E27="Enhanced"),INDEX(PARAMS_BMP,1,3),AND(D27="Permeable Pavement",E27="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),AND(D27="Bioretention",E27="Standard"),INDEX(PARAMS_BMP,3,3),AND(D27="Bioretention",E27="Enhanced"),INDEX(PARAMS_BMP,4,3),AND(D27="Bioretention",E27="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),AND(D27="Dry Swale",E27="—"),INDEX(PARAMS_BMP,6,3),AND(D27="Wet Swale",E27="—"),INDEX(PARAMS_BMP,7,3),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D27="Permeable Pavement",E27="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D27="Permeable Pavement",E27="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D27="Bioretention",E27="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D27="Bioretention",E27="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D27="Bioretention",E27="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D27="Dry Swale",E27="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D27="Wet Swale",E27="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
       <c r="S27" s="4" t="n"/>
       <c r="T27" s="17">
-        <f>IFERROR(IFS(AND(D27="Permeable Pavement",E27="Enhanced"),INDEX(PARAMS_BMP,1,4),AND(D27="Permeable Pavement",E27="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),AND(D27="Bioretention",E27="Standard"),INDEX(PARAMS_BMP,3,4),AND(D27="Bioretention",E27="Enhanced"),INDEX(PARAMS_BMP,4,4),AND(D27="Bioretention",E27="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),AND(D27="Dry Swale",E27="—"),INDEX(PARAMS_BMP,6,4),AND(D27="Wet Swale",E27="—"),INDEX(PARAMS_BMP,7,4),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D27="Permeable Pavement",E27="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D27="Permeable Pavement",E27="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D27="Bioretention",E27="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D27="Bioretention",E27="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D27="Bioretention",E27="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D27="Dry Swale",E27="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D27="Wet Swale",E27="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
       <c r="U27" s="4" t="n"/>
       <c r="V27" s="4">
-        <f>IFERROR(IF(OR(E27="Enhanced",E27="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C27,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C27,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C27,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C27,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E27="Enhanced",E27="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C27,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C27,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C27,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C27,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="W27" s="17">
@@ -11430,7 +11430,7 @@
         <v/>
       </c>
       <c r="AJ27" s="17">
-        <f>IFERROR(IFS(AND(D27="Permeable Pavement",E27="Enhanced"),INDEX(PARAMS_BMP,1,6),AND(D27="Permeable Pavement",E27="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),AND(D27="Bioretention",E27="Standard"),INDEX(PARAMS_BMP,3,6),AND(D27="Bioretention",E27="Enhanced"),INDEX(PARAMS_BMP,4,6),AND(D27="Bioretention",E27="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),AND(D27="Dry Swale",E27="—"),INDEX(PARAMS_BMP,6,6),AND(D27="Wet Swale",E27="—"),INDEX(PARAMS_BMP,7,6),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D27="Permeable Pavement",E27="Enhanced"),INDEX(PARAMS_BMP,1,6),IF(AND(D27="Permeable Pavement",E27="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),IF(AND(D27="Bioretention",E27="Standard"),INDEX(PARAMS_BMP,3,6),IF(AND(D27="Bioretention",E27="Enhanced"),INDEX(PARAMS_BMP,4,6),IF(AND(D27="Bioretention",E27="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),IF(AND(D27="Dry Swale",E27="—"),INDEX(PARAMS_BMP,6,6),IF(AND(D27="Wet Swale",E27="—"),INDEX(PARAMS_BMP,7,6),""))))))),"")</f>
         <v/>
       </c>
       <c r="AK27" s="17">
@@ -11456,11 +11456,11 @@
       <c r="G28" s="4" t="n"/>
       <c r="H28" s="4" t="n"/>
       <c r="I28" s="4">
-        <f>IFERROR(IF(OR(E28="Enhanced",E28="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C28,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C28,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C28,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C28,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E28="Enhanced",E28="Underdrained Enhanced"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C28,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C28,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C28,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C28,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="J28" s="17">
-        <f>IFERROR(IFS(AND(D28="Permeable Pavement",E28="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D28="Permeable Pavement",E28="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D28="Bioretention",E28="Standard"),INDEX(PARAMS_BMP,3,5),AND(D28="Bioretention",E28="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D28="Bioretention",E28="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D28="Dry Swale",E28="—"),INDEX(PARAMS_BMP,6,5),AND(D28="Wet Swale",E28="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D28="Permeable Pavement",E28="Enhanced"),INDEX(PARAMS_BMP,1,5),IF(AND(D28="Permeable Pavement",E28="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),IF(AND(D28="Bioretention",E28="Standard"),INDEX(PARAMS_BMP,3,5),IF(AND(D28="Bioretention",E28="Enhanced"),INDEX(PARAMS_BMP,4,5),IF(AND(D28="Bioretention",E28="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),IF(AND(D28="Dry Swale",E28="—"),INDEX(PARAMS_BMP,6,5),IF(AND(D28="Wet Swale",E28="—"),INDEX(PARAMS_BMP,7,5),""))))))),"")</f>
         <v/>
       </c>
       <c r="K28" s="17">
@@ -11483,17 +11483,17 @@
       </c>
       <c r="Q28" s="4" t="n"/>
       <c r="R28" s="17">
-        <f>IFERROR(IFS(AND(D28="Permeable Pavement",E28="Enhanced"),INDEX(PARAMS_BMP,1,3),AND(D28="Permeable Pavement",E28="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),AND(D28="Bioretention",E28="Standard"),INDEX(PARAMS_BMP,3,3),AND(D28="Bioretention",E28="Enhanced"),INDEX(PARAMS_BMP,4,3),AND(D28="Bioretention",E28="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),AND(D28="Dry Swale",E28="—"),INDEX(PARAMS_BMP,6,3),AND(D28="Wet Swale",E28="—"),INDEX(PARAMS_BMP,7,3),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D28="Permeable Pavement",E28="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D28="Permeable Pavement",E28="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D28="Bioretention",E28="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D28="Bioretention",E28="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D28="Bioretention",E28="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D28="Dry Swale",E28="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D28="Wet Swale",E28="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
       <c r="S28" s="4" t="n"/>
       <c r="T28" s="17">
-        <f>IFERROR(IFS(AND(D28="Permeable Pavement",E28="Enhanced"),INDEX(PARAMS_BMP,1,4),AND(D28="Permeable Pavement",E28="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),AND(D28="Bioretention",E28="Standard"),INDEX(PARAMS_BMP,3,4),AND(D28="Bioretention",E28="Enhanced"),INDEX(PARAMS_BMP,4,4),AND(D28="Bioretention",E28="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),AND(D28="Dry Swale",E28="—"),INDEX(PARAMS_BMP,6,4),AND(D28="Wet Swale",E28="—"),INDEX(PARAMS_BMP,7,4),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D28="Permeable Pavement",E28="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D28="Permeable Pavement",E28="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D28="Bioretention",E28="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D28="Bioretention",E28="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D28="Bioretention",E28="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D28="Dry Swale",E28="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D28="Wet Swale",E28="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
       <c r="U28" s="4" t="n"/>
       <c r="V28" s="4">
-        <f>IFERROR(IF(OR(E28="Enhanced",E28="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C28,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C28,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C28,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C28,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E28="Enhanced",E28="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C28,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C28,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C28,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C28,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="W28" s="17">
@@ -11525,7 +11525,7 @@
         <v/>
       </c>
       <c r="AJ28" s="17">
-        <f>IFERROR(IFS(AND(D28="Permeable Pavement",E28="Enhanced"),INDEX(PARAMS_BMP,1,6),AND(D28="Permeable Pavement",E28="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),AND(D28="Bioretention",E28="Standard"),INDEX(PARAMS_BMP,3,6),AND(D28="Bioretention",E28="Enhanced"),INDEX(PARAMS_BMP,4,6),AND(D28="Bioretention",E28="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),AND(D28="Dry Swale",E28="—"),INDEX(PARAMS_BMP,6,6),AND(D28="Wet Swale",E28="—"),INDEX(PARAMS_BMP,7,6),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D28="Permeable Pavement",E28="Enhanced"),INDEX(PARAMS_BMP,1,6),IF(AND(D28="Permeable Pavement",E28="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),IF(AND(D28="Bioretention",E28="Standard"),INDEX(PARAMS_BMP,3,6),IF(AND(D28="Bioretention",E28="Enhanced"),INDEX(PARAMS_BMP,4,6),IF(AND(D28="Bioretention",E28="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),IF(AND(D28="Dry Swale",E28="—"),INDEX(PARAMS_BMP,6,6),IF(AND(D28="Wet Swale",E28="—"),INDEX(PARAMS_BMP,7,6),""))))))),"")</f>
         <v/>
       </c>
       <c r="AK28" s="17">
@@ -11551,11 +11551,11 @@
       <c r="G29" s="4" t="n"/>
       <c r="H29" s="4" t="n"/>
       <c r="I29" s="4">
-        <f>IFERROR(IF(OR(E29="Enhanced",E29="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C29,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C29,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C29,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C29,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E29="Enhanced",E29="Underdrained Enhanced"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C29,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C29,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C29,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C29,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="J29" s="17">
-        <f>IFERROR(IFS(AND(D29="Permeable Pavement",E29="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D29="Permeable Pavement",E29="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D29="Bioretention",E29="Standard"),INDEX(PARAMS_BMP,3,5),AND(D29="Bioretention",E29="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D29="Bioretention",E29="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D29="Dry Swale",E29="—"),INDEX(PARAMS_BMP,6,5),AND(D29="Wet Swale",E29="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D29="Permeable Pavement",E29="Enhanced"),INDEX(PARAMS_BMP,1,5),IF(AND(D29="Permeable Pavement",E29="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),IF(AND(D29="Bioretention",E29="Standard"),INDEX(PARAMS_BMP,3,5),IF(AND(D29="Bioretention",E29="Enhanced"),INDEX(PARAMS_BMP,4,5),IF(AND(D29="Bioretention",E29="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),IF(AND(D29="Dry Swale",E29="—"),INDEX(PARAMS_BMP,6,5),IF(AND(D29="Wet Swale",E29="—"),INDEX(PARAMS_BMP,7,5),""))))))),"")</f>
         <v/>
       </c>
       <c r="K29" s="17">
@@ -11578,17 +11578,17 @@
       </c>
       <c r="Q29" s="4" t="n"/>
       <c r="R29" s="17">
-        <f>IFERROR(IFS(AND(D29="Permeable Pavement",E29="Enhanced"),INDEX(PARAMS_BMP,1,3),AND(D29="Permeable Pavement",E29="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),AND(D29="Bioretention",E29="Standard"),INDEX(PARAMS_BMP,3,3),AND(D29="Bioretention",E29="Enhanced"),INDEX(PARAMS_BMP,4,3),AND(D29="Bioretention",E29="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),AND(D29="Dry Swale",E29="—"),INDEX(PARAMS_BMP,6,3),AND(D29="Wet Swale",E29="—"),INDEX(PARAMS_BMP,7,3),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D29="Permeable Pavement",E29="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D29="Permeable Pavement",E29="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D29="Bioretention",E29="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D29="Bioretention",E29="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D29="Bioretention",E29="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D29="Dry Swale",E29="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D29="Wet Swale",E29="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
       <c r="S29" s="4" t="n"/>
       <c r="T29" s="17">
-        <f>IFERROR(IFS(AND(D29="Permeable Pavement",E29="Enhanced"),INDEX(PARAMS_BMP,1,4),AND(D29="Permeable Pavement",E29="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),AND(D29="Bioretention",E29="Standard"),INDEX(PARAMS_BMP,3,4),AND(D29="Bioretention",E29="Enhanced"),INDEX(PARAMS_BMP,4,4),AND(D29="Bioretention",E29="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),AND(D29="Dry Swale",E29="—"),INDEX(PARAMS_BMP,6,4),AND(D29="Wet Swale",E29="—"),INDEX(PARAMS_BMP,7,4),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D29="Permeable Pavement",E29="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D29="Permeable Pavement",E29="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D29="Bioretention",E29="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D29="Bioretention",E29="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D29="Bioretention",E29="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D29="Dry Swale",E29="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D29="Wet Swale",E29="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
       <c r="U29" s="4" t="n"/>
       <c r="V29" s="4">
-        <f>IFERROR(IF(OR(E29="Enhanced",E29="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C29,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C29,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C29,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C29,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E29="Enhanced",E29="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C29,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C29,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C29,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C29,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="W29" s="17">
@@ -11620,7 +11620,7 @@
         <v/>
       </c>
       <c r="AJ29" s="17">
-        <f>IFERROR(IFS(AND(D29="Permeable Pavement",E29="Enhanced"),INDEX(PARAMS_BMP,1,6),AND(D29="Permeable Pavement",E29="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),AND(D29="Bioretention",E29="Standard"),INDEX(PARAMS_BMP,3,6),AND(D29="Bioretention",E29="Enhanced"),INDEX(PARAMS_BMP,4,6),AND(D29="Bioretention",E29="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),AND(D29="Dry Swale",E29="—"),INDEX(PARAMS_BMP,6,6),AND(D29="Wet Swale",E29="—"),INDEX(PARAMS_BMP,7,6),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D29="Permeable Pavement",E29="Enhanced"),INDEX(PARAMS_BMP,1,6),IF(AND(D29="Permeable Pavement",E29="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),IF(AND(D29="Bioretention",E29="Standard"),INDEX(PARAMS_BMP,3,6),IF(AND(D29="Bioretention",E29="Enhanced"),INDEX(PARAMS_BMP,4,6),IF(AND(D29="Bioretention",E29="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),IF(AND(D29="Dry Swale",E29="—"),INDEX(PARAMS_BMP,6,6),IF(AND(D29="Wet Swale",E29="—"),INDEX(PARAMS_BMP,7,6),""))))))),"")</f>
         <v/>
       </c>
       <c r="AK29" s="17">
@@ -11646,11 +11646,11 @@
       <c r="G30" s="4" t="n"/>
       <c r="H30" s="4" t="n"/>
       <c r="I30" s="4">
-        <f>IFERROR(IF(OR(E30="Enhanced",E30="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C30,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C30,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C30,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C30,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E30="Enhanced",E30="Underdrained Enhanced"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C30,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C30,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C30,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C30,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="J30" s="17">
-        <f>IFERROR(IFS(AND(D30="Permeable Pavement",E30="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D30="Permeable Pavement",E30="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D30="Bioretention",E30="Standard"),INDEX(PARAMS_BMP,3,5),AND(D30="Bioretention",E30="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D30="Bioretention",E30="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D30="Dry Swale",E30="—"),INDEX(PARAMS_BMP,6,5),AND(D30="Wet Swale",E30="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D30="Permeable Pavement",E30="Enhanced"),INDEX(PARAMS_BMP,1,5),IF(AND(D30="Permeable Pavement",E30="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),IF(AND(D30="Bioretention",E30="Standard"),INDEX(PARAMS_BMP,3,5),IF(AND(D30="Bioretention",E30="Enhanced"),INDEX(PARAMS_BMP,4,5),IF(AND(D30="Bioretention",E30="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),IF(AND(D30="Dry Swale",E30="—"),INDEX(PARAMS_BMP,6,5),IF(AND(D30="Wet Swale",E30="—"),INDEX(PARAMS_BMP,7,5),""))))))),"")</f>
         <v/>
       </c>
       <c r="K30" s="17">
@@ -11673,17 +11673,17 @@
       </c>
       <c r="Q30" s="4" t="n"/>
       <c r="R30" s="17">
-        <f>IFERROR(IFS(AND(D30="Permeable Pavement",E30="Enhanced"),INDEX(PARAMS_BMP,1,3),AND(D30="Permeable Pavement",E30="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),AND(D30="Bioretention",E30="Standard"),INDEX(PARAMS_BMP,3,3),AND(D30="Bioretention",E30="Enhanced"),INDEX(PARAMS_BMP,4,3),AND(D30="Bioretention",E30="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),AND(D30="Dry Swale",E30="—"),INDEX(PARAMS_BMP,6,3),AND(D30="Wet Swale",E30="—"),INDEX(PARAMS_BMP,7,3),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D30="Permeable Pavement",E30="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D30="Permeable Pavement",E30="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D30="Bioretention",E30="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D30="Bioretention",E30="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D30="Bioretention",E30="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D30="Dry Swale",E30="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D30="Wet Swale",E30="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
       <c r="S30" s="4" t="n"/>
       <c r="T30" s="17">
-        <f>IFERROR(IFS(AND(D30="Permeable Pavement",E30="Enhanced"),INDEX(PARAMS_BMP,1,4),AND(D30="Permeable Pavement",E30="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),AND(D30="Bioretention",E30="Standard"),INDEX(PARAMS_BMP,3,4),AND(D30="Bioretention",E30="Enhanced"),INDEX(PARAMS_BMP,4,4),AND(D30="Bioretention",E30="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),AND(D30="Dry Swale",E30="—"),INDEX(PARAMS_BMP,6,4),AND(D30="Wet Swale",E30="—"),INDEX(PARAMS_BMP,7,4),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D30="Permeable Pavement",E30="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D30="Permeable Pavement",E30="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D30="Bioretention",E30="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D30="Bioretention",E30="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D30="Bioretention",E30="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D30="Dry Swale",E30="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D30="Wet Swale",E30="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
       <c r="U30" s="4" t="n"/>
       <c r="V30" s="4">
-        <f>IFERROR(IF(OR(E30="Enhanced",E30="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C30,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C30,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C30,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C30,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E30="Enhanced",E30="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C30,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C30,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C30,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C30,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="W30" s="17">
@@ -11715,7 +11715,7 @@
         <v/>
       </c>
       <c r="AJ30" s="17">
-        <f>IFERROR(IFS(AND(D30="Permeable Pavement",E30="Enhanced"),INDEX(PARAMS_BMP,1,6),AND(D30="Permeable Pavement",E30="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),AND(D30="Bioretention",E30="Standard"),INDEX(PARAMS_BMP,3,6),AND(D30="Bioretention",E30="Enhanced"),INDEX(PARAMS_BMP,4,6),AND(D30="Bioretention",E30="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),AND(D30="Dry Swale",E30="—"),INDEX(PARAMS_BMP,6,6),AND(D30="Wet Swale",E30="—"),INDEX(PARAMS_BMP,7,6),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D30="Permeable Pavement",E30="Enhanced"),INDEX(PARAMS_BMP,1,6),IF(AND(D30="Permeable Pavement",E30="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),IF(AND(D30="Bioretention",E30="Standard"),INDEX(PARAMS_BMP,3,6),IF(AND(D30="Bioretention",E30="Enhanced"),INDEX(PARAMS_BMP,4,6),IF(AND(D30="Bioretention",E30="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),IF(AND(D30="Dry Swale",E30="—"),INDEX(PARAMS_BMP,6,6),IF(AND(D30="Wet Swale",E30="—"),INDEX(PARAMS_BMP,7,6),""))))))),"")</f>
         <v/>
       </c>
       <c r="AK30" s="17">
@@ -11741,11 +11741,11 @@
       <c r="G31" s="4" t="n"/>
       <c r="H31" s="4" t="n"/>
       <c r="I31" s="4">
-        <f>IFERROR(IF(OR(E31="Enhanced",E31="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C31,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C31,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C31,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C31,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E31="Enhanced",E31="Underdrained Enhanced"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C31,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C31,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C31,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C31,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="J31" s="17">
-        <f>IFERROR(IFS(AND(D31="Permeable Pavement",E31="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D31="Permeable Pavement",E31="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D31="Bioretention",E31="Standard"),INDEX(PARAMS_BMP,3,5),AND(D31="Bioretention",E31="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D31="Bioretention",E31="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D31="Dry Swale",E31="—"),INDEX(PARAMS_BMP,6,5),AND(D31="Wet Swale",E31="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D31="Permeable Pavement",E31="Enhanced"),INDEX(PARAMS_BMP,1,5),IF(AND(D31="Permeable Pavement",E31="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),IF(AND(D31="Bioretention",E31="Standard"),INDEX(PARAMS_BMP,3,5),IF(AND(D31="Bioretention",E31="Enhanced"),INDEX(PARAMS_BMP,4,5),IF(AND(D31="Bioretention",E31="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),IF(AND(D31="Dry Swale",E31="—"),INDEX(PARAMS_BMP,6,5),IF(AND(D31="Wet Swale",E31="—"),INDEX(PARAMS_BMP,7,5),""))))))),"")</f>
         <v/>
       </c>
       <c r="K31" s="17">
@@ -11768,17 +11768,17 @@
       </c>
       <c r="Q31" s="4" t="n"/>
       <c r="R31" s="17">
-        <f>IFERROR(IFS(AND(D31="Permeable Pavement",E31="Enhanced"),INDEX(PARAMS_BMP,1,3),AND(D31="Permeable Pavement",E31="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),AND(D31="Bioretention",E31="Standard"),INDEX(PARAMS_BMP,3,3),AND(D31="Bioretention",E31="Enhanced"),INDEX(PARAMS_BMP,4,3),AND(D31="Bioretention",E31="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),AND(D31="Dry Swale",E31="—"),INDEX(PARAMS_BMP,6,3),AND(D31="Wet Swale",E31="—"),INDEX(PARAMS_BMP,7,3),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D31="Permeable Pavement",E31="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D31="Permeable Pavement",E31="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D31="Bioretention",E31="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D31="Bioretention",E31="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D31="Bioretention",E31="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D31="Dry Swale",E31="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D31="Wet Swale",E31="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
       <c r="S31" s="4" t="n"/>
       <c r="T31" s="17">
-        <f>IFERROR(IFS(AND(D31="Permeable Pavement",E31="Enhanced"),INDEX(PARAMS_BMP,1,4),AND(D31="Permeable Pavement",E31="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),AND(D31="Bioretention",E31="Standard"),INDEX(PARAMS_BMP,3,4),AND(D31="Bioretention",E31="Enhanced"),INDEX(PARAMS_BMP,4,4),AND(D31="Bioretention",E31="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),AND(D31="Dry Swale",E31="—"),INDEX(PARAMS_BMP,6,4),AND(D31="Wet Swale",E31="—"),INDEX(PARAMS_BMP,7,4),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D31="Permeable Pavement",E31="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D31="Permeable Pavement",E31="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D31="Bioretention",E31="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D31="Bioretention",E31="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D31="Bioretention",E31="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D31="Dry Swale",E31="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D31="Wet Swale",E31="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
       <c r="U31" s="4" t="n"/>
       <c r="V31" s="4">
-        <f>IFERROR(IF(OR(E31="Enhanced",E31="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C31,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C31,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C31,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C31,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E31="Enhanced",E31="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C31,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C31,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C31,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C31,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="W31" s="17">
@@ -11810,7 +11810,7 @@
         <v/>
       </c>
       <c r="AJ31" s="17">
-        <f>IFERROR(IFS(AND(D31="Permeable Pavement",E31="Enhanced"),INDEX(PARAMS_BMP,1,6),AND(D31="Permeable Pavement",E31="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),AND(D31="Bioretention",E31="Standard"),INDEX(PARAMS_BMP,3,6),AND(D31="Bioretention",E31="Enhanced"),INDEX(PARAMS_BMP,4,6),AND(D31="Bioretention",E31="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),AND(D31="Dry Swale",E31="—"),INDEX(PARAMS_BMP,6,6),AND(D31="Wet Swale",E31="—"),INDEX(PARAMS_BMP,7,6),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D31="Permeable Pavement",E31="Enhanced"),INDEX(PARAMS_BMP,1,6),IF(AND(D31="Permeable Pavement",E31="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),IF(AND(D31="Bioretention",E31="Standard"),INDEX(PARAMS_BMP,3,6),IF(AND(D31="Bioretention",E31="Enhanced"),INDEX(PARAMS_BMP,4,6),IF(AND(D31="Bioretention",E31="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),IF(AND(D31="Dry Swale",E31="—"),INDEX(PARAMS_BMP,6,6),IF(AND(D31="Wet Swale",E31="—"),INDEX(PARAMS_BMP,7,6),""))))))),"")</f>
         <v/>
       </c>
       <c r="AK31" s="17">
@@ -11836,11 +11836,11 @@
       <c r="G32" s="4" t="n"/>
       <c r="H32" s="4" t="n"/>
       <c r="I32" s="4">
-        <f>IFERROR(IF(OR(E32="Enhanced",E32="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C32,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C32,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C32,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C32,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E32="Enhanced",E32="Underdrained Enhanced"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C32,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C32,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C32,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C32,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="J32" s="17">
-        <f>IFERROR(IFS(AND(D32="Permeable Pavement",E32="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D32="Permeable Pavement",E32="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D32="Bioretention",E32="Standard"),INDEX(PARAMS_BMP,3,5),AND(D32="Bioretention",E32="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D32="Bioretention",E32="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D32="Dry Swale",E32="—"),INDEX(PARAMS_BMP,6,5),AND(D32="Wet Swale",E32="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D32="Permeable Pavement",E32="Enhanced"),INDEX(PARAMS_BMP,1,5),IF(AND(D32="Permeable Pavement",E32="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),IF(AND(D32="Bioretention",E32="Standard"),INDEX(PARAMS_BMP,3,5),IF(AND(D32="Bioretention",E32="Enhanced"),INDEX(PARAMS_BMP,4,5),IF(AND(D32="Bioretention",E32="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),IF(AND(D32="Dry Swale",E32="—"),INDEX(PARAMS_BMP,6,5),IF(AND(D32="Wet Swale",E32="—"),INDEX(PARAMS_BMP,7,5),""))))))),"")</f>
         <v/>
       </c>
       <c r="K32" s="17">
@@ -11863,17 +11863,17 @@
       </c>
       <c r="Q32" s="4" t="n"/>
       <c r="R32" s="17">
-        <f>IFERROR(IFS(AND(D32="Permeable Pavement",E32="Enhanced"),INDEX(PARAMS_BMP,1,3),AND(D32="Permeable Pavement",E32="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),AND(D32="Bioretention",E32="Standard"),INDEX(PARAMS_BMP,3,3),AND(D32="Bioretention",E32="Enhanced"),INDEX(PARAMS_BMP,4,3),AND(D32="Bioretention",E32="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),AND(D32="Dry Swale",E32="—"),INDEX(PARAMS_BMP,6,3),AND(D32="Wet Swale",E32="—"),INDEX(PARAMS_BMP,7,3),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D32="Permeable Pavement",E32="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D32="Permeable Pavement",E32="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D32="Bioretention",E32="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D32="Bioretention",E32="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D32="Bioretention",E32="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D32="Dry Swale",E32="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D32="Wet Swale",E32="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
       <c r="S32" s="4" t="n"/>
       <c r="T32" s="17">
-        <f>IFERROR(IFS(AND(D32="Permeable Pavement",E32="Enhanced"),INDEX(PARAMS_BMP,1,4),AND(D32="Permeable Pavement",E32="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),AND(D32="Bioretention",E32="Standard"),INDEX(PARAMS_BMP,3,4),AND(D32="Bioretention",E32="Enhanced"),INDEX(PARAMS_BMP,4,4),AND(D32="Bioretention",E32="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),AND(D32="Dry Swale",E32="—"),INDEX(PARAMS_BMP,6,4),AND(D32="Wet Swale",E32="—"),INDEX(PARAMS_BMP,7,4),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D32="Permeable Pavement",E32="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D32="Permeable Pavement",E32="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D32="Bioretention",E32="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D32="Bioretention",E32="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D32="Bioretention",E32="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D32="Dry Swale",E32="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D32="Wet Swale",E32="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
       <c r="U32" s="4" t="n"/>
       <c r="V32" s="4">
-        <f>IFERROR(IF(OR(E32="Enhanced",E32="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C32,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C32,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C32,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C32,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E32="Enhanced",E32="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C32,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C32,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C32,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C32,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="W32" s="17">
@@ -11905,7 +11905,7 @@
         <v/>
       </c>
       <c r="AJ32" s="17">
-        <f>IFERROR(IFS(AND(D32="Permeable Pavement",E32="Enhanced"),INDEX(PARAMS_BMP,1,6),AND(D32="Permeable Pavement",E32="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),AND(D32="Bioretention",E32="Standard"),INDEX(PARAMS_BMP,3,6),AND(D32="Bioretention",E32="Enhanced"),INDEX(PARAMS_BMP,4,6),AND(D32="Bioretention",E32="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),AND(D32="Dry Swale",E32="—"),INDEX(PARAMS_BMP,6,6),AND(D32="Wet Swale",E32="—"),INDEX(PARAMS_BMP,7,6),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D32="Permeable Pavement",E32="Enhanced"),INDEX(PARAMS_BMP,1,6),IF(AND(D32="Permeable Pavement",E32="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),IF(AND(D32="Bioretention",E32="Standard"),INDEX(PARAMS_BMP,3,6),IF(AND(D32="Bioretention",E32="Enhanced"),INDEX(PARAMS_BMP,4,6),IF(AND(D32="Bioretention",E32="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),IF(AND(D32="Dry Swale",E32="—"),INDEX(PARAMS_BMP,6,6),IF(AND(D32="Wet Swale",E32="—"),INDEX(PARAMS_BMP,7,6),""))))))),"")</f>
         <v/>
       </c>
       <c r="AK32" s="17">
@@ -11931,11 +11931,11 @@
       <c r="G33" s="4" t="n"/>
       <c r="H33" s="4" t="n"/>
       <c r="I33" s="4">
-        <f>IFERROR(IF(OR(E33="Enhanced",E33="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C33,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C33,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C33,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C33,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E33="Enhanced",E33="Underdrained Enhanced"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C33,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C33,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C33,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C33,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="J33" s="17">
-        <f>IFERROR(IFS(AND(D33="Permeable Pavement",E33="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D33="Permeable Pavement",E33="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D33="Bioretention",E33="Standard"),INDEX(PARAMS_BMP,3,5),AND(D33="Bioretention",E33="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D33="Bioretention",E33="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D33="Dry Swale",E33="—"),INDEX(PARAMS_BMP,6,5),AND(D33="Wet Swale",E33="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D33="Permeable Pavement",E33="Enhanced"),INDEX(PARAMS_BMP,1,5),IF(AND(D33="Permeable Pavement",E33="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),IF(AND(D33="Bioretention",E33="Standard"),INDEX(PARAMS_BMP,3,5),IF(AND(D33="Bioretention",E33="Enhanced"),INDEX(PARAMS_BMP,4,5),IF(AND(D33="Bioretention",E33="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),IF(AND(D33="Dry Swale",E33="—"),INDEX(PARAMS_BMP,6,5),IF(AND(D33="Wet Swale",E33="—"),INDEX(PARAMS_BMP,7,5),""))))))),"")</f>
         <v/>
       </c>
       <c r="K33" s="17">
@@ -11958,17 +11958,17 @@
       </c>
       <c r="Q33" s="4" t="n"/>
       <c r="R33" s="17">
-        <f>IFERROR(IFS(AND(D33="Permeable Pavement",E33="Enhanced"),INDEX(PARAMS_BMP,1,3),AND(D33="Permeable Pavement",E33="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),AND(D33="Bioretention",E33="Standard"),INDEX(PARAMS_BMP,3,3),AND(D33="Bioretention",E33="Enhanced"),INDEX(PARAMS_BMP,4,3),AND(D33="Bioretention",E33="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),AND(D33="Dry Swale",E33="—"),INDEX(PARAMS_BMP,6,3),AND(D33="Wet Swale",E33="—"),INDEX(PARAMS_BMP,7,3),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D33="Permeable Pavement",E33="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D33="Permeable Pavement",E33="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D33="Bioretention",E33="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D33="Bioretention",E33="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D33="Bioretention",E33="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D33="Dry Swale",E33="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D33="Wet Swale",E33="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
       <c r="S33" s="4" t="n"/>
       <c r="T33" s="17">
-        <f>IFERROR(IFS(AND(D33="Permeable Pavement",E33="Enhanced"),INDEX(PARAMS_BMP,1,4),AND(D33="Permeable Pavement",E33="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),AND(D33="Bioretention",E33="Standard"),INDEX(PARAMS_BMP,3,4),AND(D33="Bioretention",E33="Enhanced"),INDEX(PARAMS_BMP,4,4),AND(D33="Bioretention",E33="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),AND(D33="Dry Swale",E33="—"),INDEX(PARAMS_BMP,6,4),AND(D33="Wet Swale",E33="—"),INDEX(PARAMS_BMP,7,4),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D33="Permeable Pavement",E33="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D33="Permeable Pavement",E33="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D33="Bioretention",E33="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D33="Bioretention",E33="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D33="Bioretention",E33="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D33="Dry Swale",E33="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D33="Wet Swale",E33="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
       <c r="U33" s="4" t="n"/>
       <c r="V33" s="4">
-        <f>IFERROR(IF(OR(E33="Enhanced",E33="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C33,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C33,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C33,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C33,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E33="Enhanced",E33="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C33,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C33,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C33,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C33,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="W33" s="17">
@@ -12000,7 +12000,7 @@
         <v/>
       </c>
       <c r="AJ33" s="17">
-        <f>IFERROR(IFS(AND(D33="Permeable Pavement",E33="Enhanced"),INDEX(PARAMS_BMP,1,6),AND(D33="Permeable Pavement",E33="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),AND(D33="Bioretention",E33="Standard"),INDEX(PARAMS_BMP,3,6),AND(D33="Bioretention",E33="Enhanced"),INDEX(PARAMS_BMP,4,6),AND(D33="Bioretention",E33="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),AND(D33="Dry Swale",E33="—"),INDEX(PARAMS_BMP,6,6),AND(D33="Wet Swale",E33="—"),INDEX(PARAMS_BMP,7,6),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D33="Permeable Pavement",E33="Enhanced"),INDEX(PARAMS_BMP,1,6),IF(AND(D33="Permeable Pavement",E33="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),IF(AND(D33="Bioretention",E33="Standard"),INDEX(PARAMS_BMP,3,6),IF(AND(D33="Bioretention",E33="Enhanced"),INDEX(PARAMS_BMP,4,6),IF(AND(D33="Bioretention",E33="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),IF(AND(D33="Dry Swale",E33="—"),INDEX(PARAMS_BMP,6,6),IF(AND(D33="Wet Swale",E33="—"),INDEX(PARAMS_BMP,7,6),""))))))),"")</f>
         <v/>
       </c>
       <c r="AK33" s="17">
@@ -12026,11 +12026,11 @@
       <c r="G34" s="4" t="n"/>
       <c r="H34" s="4" t="n"/>
       <c r="I34" s="4">
-        <f>IFERROR(IF(OR(E34="Enhanced",E34="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C34,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C34,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C34,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C34,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E34="Enhanced",E34="Underdrained Enhanced"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C34,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C34,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C34,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C34,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="J34" s="17">
-        <f>IFERROR(IFS(AND(D34="Permeable Pavement",E34="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D34="Permeable Pavement",E34="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D34="Bioretention",E34="Standard"),INDEX(PARAMS_BMP,3,5),AND(D34="Bioretention",E34="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D34="Bioretention",E34="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D34="Dry Swale",E34="—"),INDEX(PARAMS_BMP,6,5),AND(D34="Wet Swale",E34="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D34="Permeable Pavement",E34="Enhanced"),INDEX(PARAMS_BMP,1,5),IF(AND(D34="Permeable Pavement",E34="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),IF(AND(D34="Bioretention",E34="Standard"),INDEX(PARAMS_BMP,3,5),IF(AND(D34="Bioretention",E34="Enhanced"),INDEX(PARAMS_BMP,4,5),IF(AND(D34="Bioretention",E34="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),IF(AND(D34="Dry Swale",E34="—"),INDEX(PARAMS_BMP,6,5),IF(AND(D34="Wet Swale",E34="—"),INDEX(PARAMS_BMP,7,5),""))))))),"")</f>
         <v/>
       </c>
       <c r="K34" s="17">
@@ -12053,17 +12053,17 @@
       </c>
       <c r="Q34" s="4" t="n"/>
       <c r="R34" s="17">
-        <f>IFERROR(IFS(AND(D34="Permeable Pavement",E34="Enhanced"),INDEX(PARAMS_BMP,1,3),AND(D34="Permeable Pavement",E34="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),AND(D34="Bioretention",E34="Standard"),INDEX(PARAMS_BMP,3,3),AND(D34="Bioretention",E34="Enhanced"),INDEX(PARAMS_BMP,4,3),AND(D34="Bioretention",E34="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),AND(D34="Dry Swale",E34="—"),INDEX(PARAMS_BMP,6,3),AND(D34="Wet Swale",E34="—"),INDEX(PARAMS_BMP,7,3),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D34="Permeable Pavement",E34="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D34="Permeable Pavement",E34="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D34="Bioretention",E34="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D34="Bioretention",E34="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D34="Bioretention",E34="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D34="Dry Swale",E34="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D34="Wet Swale",E34="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
       <c r="S34" s="4" t="n"/>
       <c r="T34" s="17">
-        <f>IFERROR(IFS(AND(D34="Permeable Pavement",E34="Enhanced"),INDEX(PARAMS_BMP,1,4),AND(D34="Permeable Pavement",E34="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),AND(D34="Bioretention",E34="Standard"),INDEX(PARAMS_BMP,3,4),AND(D34="Bioretention",E34="Enhanced"),INDEX(PARAMS_BMP,4,4),AND(D34="Bioretention",E34="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),AND(D34="Dry Swale",E34="—"),INDEX(PARAMS_BMP,6,4),AND(D34="Wet Swale",E34="—"),INDEX(PARAMS_BMP,7,4),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D34="Permeable Pavement",E34="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D34="Permeable Pavement",E34="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D34="Bioretention",E34="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D34="Bioretention",E34="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D34="Bioretention",E34="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D34="Dry Swale",E34="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D34="Wet Swale",E34="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
       <c r="U34" s="4" t="n"/>
       <c r="V34" s="4">
-        <f>IFERROR(IF(OR(E34="Enhanced",E34="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C34,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C34,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C34,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C34,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E34="Enhanced",E34="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C34,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C34,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C34,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C34,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="W34" s="17">
@@ -12095,7 +12095,7 @@
         <v/>
       </c>
       <c r="AJ34" s="17">
-        <f>IFERROR(IFS(AND(D34="Permeable Pavement",E34="Enhanced"),INDEX(PARAMS_BMP,1,6),AND(D34="Permeable Pavement",E34="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),AND(D34="Bioretention",E34="Standard"),INDEX(PARAMS_BMP,3,6),AND(D34="Bioretention",E34="Enhanced"),INDEX(PARAMS_BMP,4,6),AND(D34="Bioretention",E34="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),AND(D34="Dry Swale",E34="—"),INDEX(PARAMS_BMP,6,6),AND(D34="Wet Swale",E34="—"),INDEX(PARAMS_BMP,7,6),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D34="Permeable Pavement",E34="Enhanced"),INDEX(PARAMS_BMP,1,6),IF(AND(D34="Permeable Pavement",E34="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),IF(AND(D34="Bioretention",E34="Standard"),INDEX(PARAMS_BMP,3,6),IF(AND(D34="Bioretention",E34="Enhanced"),INDEX(PARAMS_BMP,4,6),IF(AND(D34="Bioretention",E34="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),IF(AND(D34="Dry Swale",E34="—"),INDEX(PARAMS_BMP,6,6),IF(AND(D34="Wet Swale",E34="—"),INDEX(PARAMS_BMP,7,6),""))))))),"")</f>
         <v/>
       </c>
       <c r="AK34" s="17">
@@ -12121,11 +12121,11 @@
       <c r="G35" s="4" t="n"/>
       <c r="H35" s="4" t="n"/>
       <c r="I35" s="4">
-        <f>IFERROR(IF(OR(E35="Enhanced",E35="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C35,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C35,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C35,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C35,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E35="Enhanced",E35="Underdrained Enhanced"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C35,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C35,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C35,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C35,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="J35" s="17">
-        <f>IFERROR(IFS(AND(D35="Permeable Pavement",E35="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D35="Permeable Pavement",E35="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D35="Bioretention",E35="Standard"),INDEX(PARAMS_BMP,3,5),AND(D35="Bioretention",E35="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D35="Bioretention",E35="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D35="Dry Swale",E35="—"),INDEX(PARAMS_BMP,6,5),AND(D35="Wet Swale",E35="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D35="Permeable Pavement",E35="Enhanced"),INDEX(PARAMS_BMP,1,5),IF(AND(D35="Permeable Pavement",E35="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),IF(AND(D35="Bioretention",E35="Standard"),INDEX(PARAMS_BMP,3,5),IF(AND(D35="Bioretention",E35="Enhanced"),INDEX(PARAMS_BMP,4,5),IF(AND(D35="Bioretention",E35="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),IF(AND(D35="Dry Swale",E35="—"),INDEX(PARAMS_BMP,6,5),IF(AND(D35="Wet Swale",E35="—"),INDEX(PARAMS_BMP,7,5),""))))))),"")</f>
         <v/>
       </c>
       <c r="K35" s="17">
@@ -12148,17 +12148,17 @@
       </c>
       <c r="Q35" s="4" t="n"/>
       <c r="R35" s="17">
-        <f>IFERROR(IFS(AND(D35="Permeable Pavement",E35="Enhanced"),INDEX(PARAMS_BMP,1,3),AND(D35="Permeable Pavement",E35="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),AND(D35="Bioretention",E35="Standard"),INDEX(PARAMS_BMP,3,3),AND(D35="Bioretention",E35="Enhanced"),INDEX(PARAMS_BMP,4,3),AND(D35="Bioretention",E35="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),AND(D35="Dry Swale",E35="—"),INDEX(PARAMS_BMP,6,3),AND(D35="Wet Swale",E35="—"),INDEX(PARAMS_BMP,7,3),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D35="Permeable Pavement",E35="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D35="Permeable Pavement",E35="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D35="Bioretention",E35="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D35="Bioretention",E35="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D35="Bioretention",E35="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D35="Dry Swale",E35="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D35="Wet Swale",E35="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
       <c r="S35" s="4" t="n"/>
       <c r="T35" s="17">
-        <f>IFERROR(IFS(AND(D35="Permeable Pavement",E35="Enhanced"),INDEX(PARAMS_BMP,1,4),AND(D35="Permeable Pavement",E35="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),AND(D35="Bioretention",E35="Standard"),INDEX(PARAMS_BMP,3,4),AND(D35="Bioretention",E35="Enhanced"),INDEX(PARAMS_BMP,4,4),AND(D35="Bioretention",E35="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),AND(D35="Dry Swale",E35="—"),INDEX(PARAMS_BMP,6,4),AND(D35="Wet Swale",E35="—"),INDEX(PARAMS_BMP,7,4),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D35="Permeable Pavement",E35="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D35="Permeable Pavement",E35="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D35="Bioretention",E35="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D35="Bioretention",E35="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D35="Bioretention",E35="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D35="Dry Swale",E35="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D35="Wet Swale",E35="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
       <c r="U35" s="4" t="n"/>
       <c r="V35" s="4">
-        <f>IFERROR(IF(OR(E35="Enhanced",E35="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C35,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C35,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C35,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C35,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E35="Enhanced",E35="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C35,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C35,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C35,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C35,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="W35" s="17">
@@ -12190,7 +12190,7 @@
         <v/>
       </c>
       <c r="AJ35" s="17">
-        <f>IFERROR(IFS(AND(D35="Permeable Pavement",E35="Enhanced"),INDEX(PARAMS_BMP,1,6),AND(D35="Permeable Pavement",E35="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),AND(D35="Bioretention",E35="Standard"),INDEX(PARAMS_BMP,3,6),AND(D35="Bioretention",E35="Enhanced"),INDEX(PARAMS_BMP,4,6),AND(D35="Bioretention",E35="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),AND(D35="Dry Swale",E35="—"),INDEX(PARAMS_BMP,6,6),AND(D35="Wet Swale",E35="—"),INDEX(PARAMS_BMP,7,6),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D35="Permeable Pavement",E35="Enhanced"),INDEX(PARAMS_BMP,1,6),IF(AND(D35="Permeable Pavement",E35="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),IF(AND(D35="Bioretention",E35="Standard"),INDEX(PARAMS_BMP,3,6),IF(AND(D35="Bioretention",E35="Enhanced"),INDEX(PARAMS_BMP,4,6),IF(AND(D35="Bioretention",E35="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),IF(AND(D35="Dry Swale",E35="—"),INDEX(PARAMS_BMP,6,6),IF(AND(D35="Wet Swale",E35="—"),INDEX(PARAMS_BMP,7,6),""))))))),"")</f>
         <v/>
       </c>
       <c r="AK35" s="17">
@@ -12216,11 +12216,11 @@
       <c r="G36" s="4" t="n"/>
       <c r="H36" s="4" t="n"/>
       <c r="I36" s="4">
-        <f>IFERROR(IF(OR(E36="Enhanced",E36="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C36,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C36,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C36,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C36,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E36="Enhanced",E36="Underdrained Enhanced"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C36,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C36,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C36,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C36,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="J36" s="17">
-        <f>IFERROR(IFS(AND(D36="Permeable Pavement",E36="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D36="Permeable Pavement",E36="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D36="Bioretention",E36="Standard"),INDEX(PARAMS_BMP,3,5),AND(D36="Bioretention",E36="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D36="Bioretention",E36="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D36="Dry Swale",E36="—"),INDEX(PARAMS_BMP,6,5),AND(D36="Wet Swale",E36="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D36="Permeable Pavement",E36="Enhanced"),INDEX(PARAMS_BMP,1,5),IF(AND(D36="Permeable Pavement",E36="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),IF(AND(D36="Bioretention",E36="Standard"),INDEX(PARAMS_BMP,3,5),IF(AND(D36="Bioretention",E36="Enhanced"),INDEX(PARAMS_BMP,4,5),IF(AND(D36="Bioretention",E36="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),IF(AND(D36="Dry Swale",E36="—"),INDEX(PARAMS_BMP,6,5),IF(AND(D36="Wet Swale",E36="—"),INDEX(PARAMS_BMP,7,5),""))))))),"")</f>
         <v/>
       </c>
       <c r="K36" s="17">
@@ -12243,17 +12243,17 @@
       </c>
       <c r="Q36" s="4" t="n"/>
       <c r="R36" s="17">
-        <f>IFERROR(IFS(AND(D36="Permeable Pavement",E36="Enhanced"),INDEX(PARAMS_BMP,1,3),AND(D36="Permeable Pavement",E36="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),AND(D36="Bioretention",E36="Standard"),INDEX(PARAMS_BMP,3,3),AND(D36="Bioretention",E36="Enhanced"),INDEX(PARAMS_BMP,4,3),AND(D36="Bioretention",E36="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),AND(D36="Dry Swale",E36="—"),INDEX(PARAMS_BMP,6,3),AND(D36="Wet Swale",E36="—"),INDEX(PARAMS_BMP,7,3),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D36="Permeable Pavement",E36="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D36="Permeable Pavement",E36="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D36="Bioretention",E36="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D36="Bioretention",E36="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D36="Bioretention",E36="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D36="Dry Swale",E36="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D36="Wet Swale",E36="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
       <c r="S36" s="4" t="n"/>
       <c r="T36" s="17">
-        <f>IFERROR(IFS(AND(D36="Permeable Pavement",E36="Enhanced"),INDEX(PARAMS_BMP,1,4),AND(D36="Permeable Pavement",E36="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),AND(D36="Bioretention",E36="Standard"),INDEX(PARAMS_BMP,3,4),AND(D36="Bioretention",E36="Enhanced"),INDEX(PARAMS_BMP,4,4),AND(D36="Bioretention",E36="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),AND(D36="Dry Swale",E36="—"),INDEX(PARAMS_BMP,6,4),AND(D36="Wet Swale",E36="—"),INDEX(PARAMS_BMP,7,4),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D36="Permeable Pavement",E36="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D36="Permeable Pavement",E36="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D36="Bioretention",E36="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D36="Bioretention",E36="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D36="Bioretention",E36="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D36="Dry Swale",E36="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D36="Wet Swale",E36="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
       <c r="U36" s="4" t="n"/>
       <c r="V36" s="4">
-        <f>IFERROR(IF(OR(E36="Enhanced",E36="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C36,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C36,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C36,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C36,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E36="Enhanced",E36="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C36,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C36,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C36,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C36,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="W36" s="17">
@@ -12285,7 +12285,7 @@
         <v/>
       </c>
       <c r="AJ36" s="17">
-        <f>IFERROR(IFS(AND(D36="Permeable Pavement",E36="Enhanced"),INDEX(PARAMS_BMP,1,6),AND(D36="Permeable Pavement",E36="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),AND(D36="Bioretention",E36="Standard"),INDEX(PARAMS_BMP,3,6),AND(D36="Bioretention",E36="Enhanced"),INDEX(PARAMS_BMP,4,6),AND(D36="Bioretention",E36="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),AND(D36="Dry Swale",E36="—"),INDEX(PARAMS_BMP,6,6),AND(D36="Wet Swale",E36="—"),INDEX(PARAMS_BMP,7,6),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D36="Permeable Pavement",E36="Enhanced"),INDEX(PARAMS_BMP,1,6),IF(AND(D36="Permeable Pavement",E36="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),IF(AND(D36="Bioretention",E36="Standard"),INDEX(PARAMS_BMP,3,6),IF(AND(D36="Bioretention",E36="Enhanced"),INDEX(PARAMS_BMP,4,6),IF(AND(D36="Bioretention",E36="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),IF(AND(D36="Dry Swale",E36="—"),INDEX(PARAMS_BMP,6,6),IF(AND(D36="Wet Swale",E36="—"),INDEX(PARAMS_BMP,7,6),""))))))),"")</f>
         <v/>
       </c>
       <c r="AK36" s="17">
@@ -12311,11 +12311,11 @@
       <c r="G37" s="4" t="n"/>
       <c r="H37" s="4" t="n"/>
       <c r="I37" s="4">
-        <f>IFERROR(IF(OR(E37="Enhanced",E37="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C37,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C37,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C37,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C37,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E37="Enhanced",E37="Underdrained Enhanced"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C37,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C37,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C37,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C37,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="J37" s="17">
-        <f>IFERROR(IFS(AND(D37="Permeable Pavement",E37="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D37="Permeable Pavement",E37="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D37="Bioretention",E37="Standard"),INDEX(PARAMS_BMP,3,5),AND(D37="Bioretention",E37="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D37="Bioretention",E37="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D37="Dry Swale",E37="—"),INDEX(PARAMS_BMP,6,5),AND(D37="Wet Swale",E37="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D37="Permeable Pavement",E37="Enhanced"),INDEX(PARAMS_BMP,1,5),IF(AND(D37="Permeable Pavement",E37="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),IF(AND(D37="Bioretention",E37="Standard"),INDEX(PARAMS_BMP,3,5),IF(AND(D37="Bioretention",E37="Enhanced"),INDEX(PARAMS_BMP,4,5),IF(AND(D37="Bioretention",E37="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),IF(AND(D37="Dry Swale",E37="—"),INDEX(PARAMS_BMP,6,5),IF(AND(D37="Wet Swale",E37="—"),INDEX(PARAMS_BMP,7,5),""))))))),"")</f>
         <v/>
       </c>
       <c r="K37" s="17">
@@ -12338,17 +12338,17 @@
       </c>
       <c r="Q37" s="4" t="n"/>
       <c r="R37" s="17">
-        <f>IFERROR(IFS(AND(D37="Permeable Pavement",E37="Enhanced"),INDEX(PARAMS_BMP,1,3),AND(D37="Permeable Pavement",E37="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),AND(D37="Bioretention",E37="Standard"),INDEX(PARAMS_BMP,3,3),AND(D37="Bioretention",E37="Enhanced"),INDEX(PARAMS_BMP,4,3),AND(D37="Bioretention",E37="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),AND(D37="Dry Swale",E37="—"),INDEX(PARAMS_BMP,6,3),AND(D37="Wet Swale",E37="—"),INDEX(PARAMS_BMP,7,3),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D37="Permeable Pavement",E37="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D37="Permeable Pavement",E37="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D37="Bioretention",E37="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D37="Bioretention",E37="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D37="Bioretention",E37="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D37="Dry Swale",E37="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D37="Wet Swale",E37="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
       <c r="S37" s="4" t="n"/>
       <c r="T37" s="17">
-        <f>IFERROR(IFS(AND(D37="Permeable Pavement",E37="Enhanced"),INDEX(PARAMS_BMP,1,4),AND(D37="Permeable Pavement",E37="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),AND(D37="Bioretention",E37="Standard"),INDEX(PARAMS_BMP,3,4),AND(D37="Bioretention",E37="Enhanced"),INDEX(PARAMS_BMP,4,4),AND(D37="Bioretention",E37="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),AND(D37="Dry Swale",E37="—"),INDEX(PARAMS_BMP,6,4),AND(D37="Wet Swale",E37="—"),INDEX(PARAMS_BMP,7,4),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D37="Permeable Pavement",E37="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D37="Permeable Pavement",E37="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D37="Bioretention",E37="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D37="Bioretention",E37="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D37="Bioretention",E37="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D37="Dry Swale",E37="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D37="Wet Swale",E37="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
       <c r="U37" s="4" t="n"/>
       <c r="V37" s="4">
-        <f>IFERROR(IF(OR(E37="Enhanced",E37="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C37,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C37,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C37,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C37,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E37="Enhanced",E37="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C37,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C37,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C37,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C37,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="W37" s="17">
@@ -12380,7 +12380,7 @@
         <v/>
       </c>
       <c r="AJ37" s="17">
-        <f>IFERROR(IFS(AND(D37="Permeable Pavement",E37="Enhanced"),INDEX(PARAMS_BMP,1,6),AND(D37="Permeable Pavement",E37="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),AND(D37="Bioretention",E37="Standard"),INDEX(PARAMS_BMP,3,6),AND(D37="Bioretention",E37="Enhanced"),INDEX(PARAMS_BMP,4,6),AND(D37="Bioretention",E37="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),AND(D37="Dry Swale",E37="—"),INDEX(PARAMS_BMP,6,6),AND(D37="Wet Swale",E37="—"),INDEX(PARAMS_BMP,7,6),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D37="Permeable Pavement",E37="Enhanced"),INDEX(PARAMS_BMP,1,6),IF(AND(D37="Permeable Pavement",E37="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),IF(AND(D37="Bioretention",E37="Standard"),INDEX(PARAMS_BMP,3,6),IF(AND(D37="Bioretention",E37="Enhanced"),INDEX(PARAMS_BMP,4,6),IF(AND(D37="Bioretention",E37="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),IF(AND(D37="Dry Swale",E37="—"),INDEX(PARAMS_BMP,6,6),IF(AND(D37="Wet Swale",E37="—"),INDEX(PARAMS_BMP,7,6),""))))))),"")</f>
         <v/>
       </c>
       <c r="AK37" s="17">
@@ -12406,11 +12406,11 @@
       <c r="G38" s="4" t="n"/>
       <c r="H38" s="4" t="n"/>
       <c r="I38" s="4">
-        <f>IFERROR(IF(OR(E38="Enhanced",E38="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C38,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C38,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C38,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C38,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E38="Enhanced",E38="Underdrained Enhanced"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C38,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C38,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C38,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C38,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="J38" s="17">
-        <f>IFERROR(IFS(AND(D38="Permeable Pavement",E38="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D38="Permeable Pavement",E38="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D38="Bioretention",E38="Standard"),INDEX(PARAMS_BMP,3,5),AND(D38="Bioretention",E38="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D38="Bioretention",E38="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D38="Dry Swale",E38="—"),INDEX(PARAMS_BMP,6,5),AND(D38="Wet Swale",E38="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D38="Permeable Pavement",E38="Enhanced"),INDEX(PARAMS_BMP,1,5),IF(AND(D38="Permeable Pavement",E38="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),IF(AND(D38="Bioretention",E38="Standard"),INDEX(PARAMS_BMP,3,5),IF(AND(D38="Bioretention",E38="Enhanced"),INDEX(PARAMS_BMP,4,5),IF(AND(D38="Bioretention",E38="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),IF(AND(D38="Dry Swale",E38="—"),INDEX(PARAMS_BMP,6,5),IF(AND(D38="Wet Swale",E38="—"),INDEX(PARAMS_BMP,7,5),""))))))),"")</f>
         <v/>
       </c>
       <c r="K38" s="17">
@@ -12433,17 +12433,17 @@
       </c>
       <c r="Q38" s="4" t="n"/>
       <c r="R38" s="17">
-        <f>IFERROR(IFS(AND(D38="Permeable Pavement",E38="Enhanced"),INDEX(PARAMS_BMP,1,3),AND(D38="Permeable Pavement",E38="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),AND(D38="Bioretention",E38="Standard"),INDEX(PARAMS_BMP,3,3),AND(D38="Bioretention",E38="Enhanced"),INDEX(PARAMS_BMP,4,3),AND(D38="Bioretention",E38="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),AND(D38="Dry Swale",E38="—"),INDEX(PARAMS_BMP,6,3),AND(D38="Wet Swale",E38="—"),INDEX(PARAMS_BMP,7,3),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D38="Permeable Pavement",E38="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D38="Permeable Pavement",E38="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D38="Bioretention",E38="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D38="Bioretention",E38="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D38="Bioretention",E38="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D38="Dry Swale",E38="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D38="Wet Swale",E38="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
       <c r="S38" s="4" t="n"/>
       <c r="T38" s="17">
-        <f>IFERROR(IFS(AND(D38="Permeable Pavement",E38="Enhanced"),INDEX(PARAMS_BMP,1,4),AND(D38="Permeable Pavement",E38="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),AND(D38="Bioretention",E38="Standard"),INDEX(PARAMS_BMP,3,4),AND(D38="Bioretention",E38="Enhanced"),INDEX(PARAMS_BMP,4,4),AND(D38="Bioretention",E38="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),AND(D38="Dry Swale",E38="—"),INDEX(PARAMS_BMP,6,4),AND(D38="Wet Swale",E38="—"),INDEX(PARAMS_BMP,7,4),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D38="Permeable Pavement",E38="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D38="Permeable Pavement",E38="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D38="Bioretention",E38="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D38="Bioretention",E38="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D38="Bioretention",E38="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D38="Dry Swale",E38="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D38="Wet Swale",E38="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
       <c r="U38" s="4" t="n"/>
       <c r="V38" s="4">
-        <f>IFERROR(IF(OR(E38="Enhanced",E38="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C38,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C38,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C38,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C38,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E38="Enhanced",E38="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C38,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C38,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C38,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C38,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="W38" s="17">
@@ -12475,7 +12475,7 @@
         <v/>
       </c>
       <c r="AJ38" s="17">
-        <f>IFERROR(IFS(AND(D38="Permeable Pavement",E38="Enhanced"),INDEX(PARAMS_BMP,1,6),AND(D38="Permeable Pavement",E38="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),AND(D38="Bioretention",E38="Standard"),INDEX(PARAMS_BMP,3,6),AND(D38="Bioretention",E38="Enhanced"),INDEX(PARAMS_BMP,4,6),AND(D38="Bioretention",E38="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),AND(D38="Dry Swale",E38="—"),INDEX(PARAMS_BMP,6,6),AND(D38="Wet Swale",E38="—"),INDEX(PARAMS_BMP,7,6),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D38="Permeable Pavement",E38="Enhanced"),INDEX(PARAMS_BMP,1,6),IF(AND(D38="Permeable Pavement",E38="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),IF(AND(D38="Bioretention",E38="Standard"),INDEX(PARAMS_BMP,3,6),IF(AND(D38="Bioretention",E38="Enhanced"),INDEX(PARAMS_BMP,4,6),IF(AND(D38="Bioretention",E38="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),IF(AND(D38="Dry Swale",E38="—"),INDEX(PARAMS_BMP,6,6),IF(AND(D38="Wet Swale",E38="—"),INDEX(PARAMS_BMP,7,6),""))))))),"")</f>
         <v/>
       </c>
       <c r="AK38" s="17">
@@ -12501,11 +12501,11 @@
       <c r="G39" s="4" t="n"/>
       <c r="H39" s="4" t="n"/>
       <c r="I39" s="4">
-        <f>IFERROR(IF(OR(E39="Enhanced",E39="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C39,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C39,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C39,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C39,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E39="Enhanced",E39="Underdrained Enhanced"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C39,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C39,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C39,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C39,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="J39" s="17">
-        <f>IFERROR(IFS(AND(D39="Permeable Pavement",E39="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D39="Permeable Pavement",E39="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D39="Bioretention",E39="Standard"),INDEX(PARAMS_BMP,3,5),AND(D39="Bioretention",E39="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D39="Bioretention",E39="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D39="Dry Swale",E39="—"),INDEX(PARAMS_BMP,6,5),AND(D39="Wet Swale",E39="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D39="Permeable Pavement",E39="Enhanced"),INDEX(PARAMS_BMP,1,5),IF(AND(D39="Permeable Pavement",E39="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),IF(AND(D39="Bioretention",E39="Standard"),INDEX(PARAMS_BMP,3,5),IF(AND(D39="Bioretention",E39="Enhanced"),INDEX(PARAMS_BMP,4,5),IF(AND(D39="Bioretention",E39="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),IF(AND(D39="Dry Swale",E39="—"),INDEX(PARAMS_BMP,6,5),IF(AND(D39="Wet Swale",E39="—"),INDEX(PARAMS_BMP,7,5),""))))))),"")</f>
         <v/>
       </c>
       <c r="K39" s="17">
@@ -12528,17 +12528,17 @@
       </c>
       <c r="Q39" s="4" t="n"/>
       <c r="R39" s="17">
-        <f>IFERROR(IFS(AND(D39="Permeable Pavement",E39="Enhanced"),INDEX(PARAMS_BMP,1,3),AND(D39="Permeable Pavement",E39="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),AND(D39="Bioretention",E39="Standard"),INDEX(PARAMS_BMP,3,3),AND(D39="Bioretention",E39="Enhanced"),INDEX(PARAMS_BMP,4,3),AND(D39="Bioretention",E39="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),AND(D39="Dry Swale",E39="—"),INDEX(PARAMS_BMP,6,3),AND(D39="Wet Swale",E39="—"),INDEX(PARAMS_BMP,7,3),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D39="Permeable Pavement",E39="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D39="Permeable Pavement",E39="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D39="Bioretention",E39="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D39="Bioretention",E39="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D39="Bioretention",E39="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D39="Dry Swale",E39="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D39="Wet Swale",E39="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
       <c r="S39" s="4" t="n"/>
       <c r="T39" s="17">
-        <f>IFERROR(IFS(AND(D39="Permeable Pavement",E39="Enhanced"),INDEX(PARAMS_BMP,1,4),AND(D39="Permeable Pavement",E39="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),AND(D39="Bioretention",E39="Standard"),INDEX(PARAMS_BMP,3,4),AND(D39="Bioretention",E39="Enhanced"),INDEX(PARAMS_BMP,4,4),AND(D39="Bioretention",E39="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),AND(D39="Dry Swale",E39="—"),INDEX(PARAMS_BMP,6,4),AND(D39="Wet Swale",E39="—"),INDEX(PARAMS_BMP,7,4),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D39="Permeable Pavement",E39="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D39="Permeable Pavement",E39="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D39="Bioretention",E39="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D39="Bioretention",E39="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D39="Bioretention",E39="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D39="Dry Swale",E39="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D39="Wet Swale",E39="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
       <c r="U39" s="4" t="n"/>
       <c r="V39" s="4">
-        <f>IFERROR(IF(OR(E39="Enhanced",E39="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C39,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C39,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C39,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C39,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E39="Enhanced",E39="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C39,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C39,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C39,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C39,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="W39" s="17">
@@ -12570,7 +12570,7 @@
         <v/>
       </c>
       <c r="AJ39" s="17">
-        <f>IFERROR(IFS(AND(D39="Permeable Pavement",E39="Enhanced"),INDEX(PARAMS_BMP,1,6),AND(D39="Permeable Pavement",E39="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),AND(D39="Bioretention",E39="Standard"),INDEX(PARAMS_BMP,3,6),AND(D39="Bioretention",E39="Enhanced"),INDEX(PARAMS_BMP,4,6),AND(D39="Bioretention",E39="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),AND(D39="Dry Swale",E39="—"),INDEX(PARAMS_BMP,6,6),AND(D39="Wet Swale",E39="—"),INDEX(PARAMS_BMP,7,6),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D39="Permeable Pavement",E39="Enhanced"),INDEX(PARAMS_BMP,1,6),IF(AND(D39="Permeable Pavement",E39="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),IF(AND(D39="Bioretention",E39="Standard"),INDEX(PARAMS_BMP,3,6),IF(AND(D39="Bioretention",E39="Enhanced"),INDEX(PARAMS_BMP,4,6),IF(AND(D39="Bioretention",E39="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),IF(AND(D39="Dry Swale",E39="—"),INDEX(PARAMS_BMP,6,6),IF(AND(D39="Wet Swale",E39="—"),INDEX(PARAMS_BMP,7,6),""))))))),"")</f>
         <v/>
       </c>
       <c r="AK39" s="17">
@@ -12596,11 +12596,11 @@
       <c r="G40" s="4" t="n"/>
       <c r="H40" s="4" t="n"/>
       <c r="I40" s="4">
-        <f>IFERROR(IF(OR(E40="Enhanced",E40="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C40,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C40,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C40,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C40,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E40="Enhanced",E40="Underdrained Enhanced"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C40,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C40,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C40,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C40,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="J40" s="17">
-        <f>IFERROR(IFS(AND(D40="Permeable Pavement",E40="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D40="Permeable Pavement",E40="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D40="Bioretention",E40="Standard"),INDEX(PARAMS_BMP,3,5),AND(D40="Bioretention",E40="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D40="Bioretention",E40="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D40="Dry Swale",E40="—"),INDEX(PARAMS_BMP,6,5),AND(D40="Wet Swale",E40="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D40="Permeable Pavement",E40="Enhanced"),INDEX(PARAMS_BMP,1,5),IF(AND(D40="Permeable Pavement",E40="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),IF(AND(D40="Bioretention",E40="Standard"),INDEX(PARAMS_BMP,3,5),IF(AND(D40="Bioretention",E40="Enhanced"),INDEX(PARAMS_BMP,4,5),IF(AND(D40="Bioretention",E40="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),IF(AND(D40="Dry Swale",E40="—"),INDEX(PARAMS_BMP,6,5),IF(AND(D40="Wet Swale",E40="—"),INDEX(PARAMS_BMP,7,5),""))))))),"")</f>
         <v/>
       </c>
       <c r="K40" s="17">
@@ -12623,17 +12623,17 @@
       </c>
       <c r="Q40" s="4" t="n"/>
       <c r="R40" s="17">
-        <f>IFERROR(IFS(AND(D40="Permeable Pavement",E40="Enhanced"),INDEX(PARAMS_BMP,1,3),AND(D40="Permeable Pavement",E40="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),AND(D40="Bioretention",E40="Standard"),INDEX(PARAMS_BMP,3,3),AND(D40="Bioretention",E40="Enhanced"),INDEX(PARAMS_BMP,4,3),AND(D40="Bioretention",E40="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),AND(D40="Dry Swale",E40="—"),INDEX(PARAMS_BMP,6,3),AND(D40="Wet Swale",E40="—"),INDEX(PARAMS_BMP,7,3),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D40="Permeable Pavement",E40="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D40="Permeable Pavement",E40="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D40="Bioretention",E40="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D40="Bioretention",E40="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D40="Bioretention",E40="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D40="Dry Swale",E40="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D40="Wet Swale",E40="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
       <c r="S40" s="4" t="n"/>
       <c r="T40" s="17">
-        <f>IFERROR(IFS(AND(D40="Permeable Pavement",E40="Enhanced"),INDEX(PARAMS_BMP,1,4),AND(D40="Permeable Pavement",E40="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),AND(D40="Bioretention",E40="Standard"),INDEX(PARAMS_BMP,3,4),AND(D40="Bioretention",E40="Enhanced"),INDEX(PARAMS_BMP,4,4),AND(D40="Bioretention",E40="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),AND(D40="Dry Swale",E40="—"),INDEX(PARAMS_BMP,6,4),AND(D40="Wet Swale",E40="—"),INDEX(PARAMS_BMP,7,4),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D40="Permeable Pavement",E40="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D40="Permeable Pavement",E40="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D40="Bioretention",E40="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D40="Bioretention",E40="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D40="Bioretention",E40="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D40="Dry Swale",E40="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D40="Wet Swale",E40="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
       <c r="U40" s="4" t="n"/>
       <c r="V40" s="4">
-        <f>IFERROR(IF(OR(E40="Enhanced",E40="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C40,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C40,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C40,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C40,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E40="Enhanced",E40="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C40,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C40,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C40,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C40,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="W40" s="17">
@@ -12665,7 +12665,7 @@
         <v/>
       </c>
       <c r="AJ40" s="17">
-        <f>IFERROR(IFS(AND(D40="Permeable Pavement",E40="Enhanced"),INDEX(PARAMS_BMP,1,6),AND(D40="Permeable Pavement",E40="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),AND(D40="Bioretention",E40="Standard"),INDEX(PARAMS_BMP,3,6),AND(D40="Bioretention",E40="Enhanced"),INDEX(PARAMS_BMP,4,6),AND(D40="Bioretention",E40="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),AND(D40="Dry Swale",E40="—"),INDEX(PARAMS_BMP,6,6),AND(D40="Wet Swale",E40="—"),INDEX(PARAMS_BMP,7,6),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D40="Permeable Pavement",E40="Enhanced"),INDEX(PARAMS_BMP,1,6),IF(AND(D40="Permeable Pavement",E40="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),IF(AND(D40="Bioretention",E40="Standard"),INDEX(PARAMS_BMP,3,6),IF(AND(D40="Bioretention",E40="Enhanced"),INDEX(PARAMS_BMP,4,6),IF(AND(D40="Bioretention",E40="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),IF(AND(D40="Dry Swale",E40="—"),INDEX(PARAMS_BMP,6,6),IF(AND(D40="Wet Swale",E40="—"),INDEX(PARAMS_BMP,7,6),""))))))),"")</f>
         <v/>
       </c>
       <c r="AK40" s="17">
@@ -12691,11 +12691,11 @@
       <c r="G41" s="4" t="n"/>
       <c r="H41" s="4" t="n"/>
       <c r="I41" s="4">
-        <f>IFERROR(IF(OR(E41="Enhanced",E41="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C41,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C41,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C41,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C41,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E41="Enhanced",E41="Underdrained Enhanced"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C41,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C41,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C41,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C41,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="J41" s="17">
-        <f>IFERROR(IFS(AND(D41="Permeable Pavement",E41="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D41="Permeable Pavement",E41="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D41="Bioretention",E41="Standard"),INDEX(PARAMS_BMP,3,5),AND(D41="Bioretention",E41="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D41="Bioretention",E41="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D41="Dry Swale",E41="—"),INDEX(PARAMS_BMP,6,5),AND(D41="Wet Swale",E41="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D41="Permeable Pavement",E41="Enhanced"),INDEX(PARAMS_BMP,1,5),IF(AND(D41="Permeable Pavement",E41="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),IF(AND(D41="Bioretention",E41="Standard"),INDEX(PARAMS_BMP,3,5),IF(AND(D41="Bioretention",E41="Enhanced"),INDEX(PARAMS_BMP,4,5),IF(AND(D41="Bioretention",E41="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),IF(AND(D41="Dry Swale",E41="—"),INDEX(PARAMS_BMP,6,5),IF(AND(D41="Wet Swale",E41="—"),INDEX(PARAMS_BMP,7,5),""))))))),"")</f>
         <v/>
       </c>
       <c r="K41" s="17">
@@ -12718,17 +12718,17 @@
       </c>
       <c r="Q41" s="4" t="n"/>
       <c r="R41" s="17">
-        <f>IFERROR(IFS(AND(D41="Permeable Pavement",E41="Enhanced"),INDEX(PARAMS_BMP,1,3),AND(D41="Permeable Pavement",E41="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),AND(D41="Bioretention",E41="Standard"),INDEX(PARAMS_BMP,3,3),AND(D41="Bioretention",E41="Enhanced"),INDEX(PARAMS_BMP,4,3),AND(D41="Bioretention",E41="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),AND(D41="Dry Swale",E41="—"),INDEX(PARAMS_BMP,6,3),AND(D41="Wet Swale",E41="—"),INDEX(PARAMS_BMP,7,3),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D41="Permeable Pavement",E41="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D41="Permeable Pavement",E41="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D41="Bioretention",E41="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D41="Bioretention",E41="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D41="Bioretention",E41="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D41="Dry Swale",E41="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D41="Wet Swale",E41="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
       <c r="S41" s="4" t="n"/>
       <c r="T41" s="17">
-        <f>IFERROR(IFS(AND(D41="Permeable Pavement",E41="Enhanced"),INDEX(PARAMS_BMP,1,4),AND(D41="Permeable Pavement",E41="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),AND(D41="Bioretention",E41="Standard"),INDEX(PARAMS_BMP,3,4),AND(D41="Bioretention",E41="Enhanced"),INDEX(PARAMS_BMP,4,4),AND(D41="Bioretention",E41="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),AND(D41="Dry Swale",E41="—"),INDEX(PARAMS_BMP,6,4),AND(D41="Wet Swale",E41="—"),INDEX(PARAMS_BMP,7,4),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D41="Permeable Pavement",E41="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D41="Permeable Pavement",E41="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D41="Bioretention",E41="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D41="Bioretention",E41="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D41="Bioretention",E41="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D41="Dry Swale",E41="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D41="Wet Swale",E41="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
       <c r="U41" s="4" t="n"/>
       <c r="V41" s="4">
-        <f>IFERROR(IF(OR(E41="Enhanced",E41="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C41,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C41,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C41,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C41,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E41="Enhanced",E41="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C41,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C41,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C41,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C41,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="W41" s="17">
@@ -12760,7 +12760,7 @@
         <v/>
       </c>
       <c r="AJ41" s="17">
-        <f>IFERROR(IFS(AND(D41="Permeable Pavement",E41="Enhanced"),INDEX(PARAMS_BMP,1,6),AND(D41="Permeable Pavement",E41="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),AND(D41="Bioretention",E41="Standard"),INDEX(PARAMS_BMP,3,6),AND(D41="Bioretention",E41="Enhanced"),INDEX(PARAMS_BMP,4,6),AND(D41="Bioretention",E41="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),AND(D41="Dry Swale",E41="—"),INDEX(PARAMS_BMP,6,6),AND(D41="Wet Swale",E41="—"),INDEX(PARAMS_BMP,7,6),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D41="Permeable Pavement",E41="Enhanced"),INDEX(PARAMS_BMP,1,6),IF(AND(D41="Permeable Pavement",E41="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),IF(AND(D41="Bioretention",E41="Standard"),INDEX(PARAMS_BMP,3,6),IF(AND(D41="Bioretention",E41="Enhanced"),INDEX(PARAMS_BMP,4,6),IF(AND(D41="Bioretention",E41="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),IF(AND(D41="Dry Swale",E41="—"),INDEX(PARAMS_BMP,6,6),IF(AND(D41="Wet Swale",E41="—"),INDEX(PARAMS_BMP,7,6),""))))))),"")</f>
         <v/>
       </c>
       <c r="AK41" s="17">
@@ -12786,11 +12786,11 @@
       <c r="G42" s="4" t="n"/>
       <c r="H42" s="4" t="n"/>
       <c r="I42" s="4">
-        <f>IFERROR(IF(OR(E42="Enhanced",E42="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C42,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C42,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C42,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C42,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E42="Enhanced",E42="Underdrained Enhanced"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C42,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C42,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C42,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C42,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="J42" s="17">
-        <f>IFERROR(IFS(AND(D42="Permeable Pavement",E42="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D42="Permeable Pavement",E42="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D42="Bioretention",E42="Standard"),INDEX(PARAMS_BMP,3,5),AND(D42="Bioretention",E42="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D42="Bioretention",E42="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D42="Dry Swale",E42="—"),INDEX(PARAMS_BMP,6,5),AND(D42="Wet Swale",E42="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D42="Permeable Pavement",E42="Enhanced"),INDEX(PARAMS_BMP,1,5),IF(AND(D42="Permeable Pavement",E42="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),IF(AND(D42="Bioretention",E42="Standard"),INDEX(PARAMS_BMP,3,5),IF(AND(D42="Bioretention",E42="Enhanced"),INDEX(PARAMS_BMP,4,5),IF(AND(D42="Bioretention",E42="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),IF(AND(D42="Dry Swale",E42="—"),INDEX(PARAMS_BMP,6,5),IF(AND(D42="Wet Swale",E42="—"),INDEX(PARAMS_BMP,7,5),""))))))),"")</f>
         <v/>
       </c>
       <c r="K42" s="17">
@@ -12813,17 +12813,17 @@
       </c>
       <c r="Q42" s="4" t="n"/>
       <c r="R42" s="17">
-        <f>IFERROR(IFS(AND(D42="Permeable Pavement",E42="Enhanced"),INDEX(PARAMS_BMP,1,3),AND(D42="Permeable Pavement",E42="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),AND(D42="Bioretention",E42="Standard"),INDEX(PARAMS_BMP,3,3),AND(D42="Bioretention",E42="Enhanced"),INDEX(PARAMS_BMP,4,3),AND(D42="Bioretention",E42="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),AND(D42="Dry Swale",E42="—"),INDEX(PARAMS_BMP,6,3),AND(D42="Wet Swale",E42="—"),INDEX(PARAMS_BMP,7,3),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D42="Permeable Pavement",E42="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D42="Permeable Pavement",E42="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D42="Bioretention",E42="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D42="Bioretention",E42="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D42="Bioretention",E42="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D42="Dry Swale",E42="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D42="Wet Swale",E42="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
       <c r="S42" s="4" t="n"/>
       <c r="T42" s="17">
-        <f>IFERROR(IFS(AND(D42="Permeable Pavement",E42="Enhanced"),INDEX(PARAMS_BMP,1,4),AND(D42="Permeable Pavement",E42="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),AND(D42="Bioretention",E42="Standard"),INDEX(PARAMS_BMP,3,4),AND(D42="Bioretention",E42="Enhanced"),INDEX(PARAMS_BMP,4,4),AND(D42="Bioretention",E42="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),AND(D42="Dry Swale",E42="—"),INDEX(PARAMS_BMP,6,4),AND(D42="Wet Swale",E42="—"),INDEX(PARAMS_BMP,7,4),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D42="Permeable Pavement",E42="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D42="Permeable Pavement",E42="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D42="Bioretention",E42="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D42="Bioretention",E42="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D42="Bioretention",E42="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D42="Dry Swale",E42="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D42="Wet Swale",E42="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
       <c r="U42" s="4" t="n"/>
       <c r="V42" s="4">
-        <f>IFERROR(IF(OR(E42="Enhanced",E42="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C42,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C42,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C42,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C42,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E42="Enhanced",E42="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C42,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C42,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C42,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C42,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="W42" s="17">
@@ -12855,7 +12855,7 @@
         <v/>
       </c>
       <c r="AJ42" s="17">
-        <f>IFERROR(IFS(AND(D42="Permeable Pavement",E42="Enhanced"),INDEX(PARAMS_BMP,1,6),AND(D42="Permeable Pavement",E42="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),AND(D42="Bioretention",E42="Standard"),INDEX(PARAMS_BMP,3,6),AND(D42="Bioretention",E42="Enhanced"),INDEX(PARAMS_BMP,4,6),AND(D42="Bioretention",E42="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),AND(D42="Dry Swale",E42="—"),INDEX(PARAMS_BMP,6,6),AND(D42="Wet Swale",E42="—"),INDEX(PARAMS_BMP,7,6),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D42="Permeable Pavement",E42="Enhanced"),INDEX(PARAMS_BMP,1,6),IF(AND(D42="Permeable Pavement",E42="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),IF(AND(D42="Bioretention",E42="Standard"),INDEX(PARAMS_BMP,3,6),IF(AND(D42="Bioretention",E42="Enhanced"),INDEX(PARAMS_BMP,4,6),IF(AND(D42="Bioretention",E42="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),IF(AND(D42="Dry Swale",E42="—"),INDEX(PARAMS_BMP,6,6),IF(AND(D42="Wet Swale",E42="—"),INDEX(PARAMS_BMP,7,6),""))))))),"")</f>
         <v/>
       </c>
       <c r="AK42" s="17">
@@ -12881,11 +12881,11 @@
       <c r="G43" s="4" t="n"/>
       <c r="H43" s="4" t="n"/>
       <c r="I43" s="4">
-        <f>IFERROR(IF(OR(E43="Enhanced",E43="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C43,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C43,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C43,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C43,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E43="Enhanced",E43="Underdrained Enhanced"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C43,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C43,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C43,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C43,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="J43" s="17">
-        <f>IFERROR(IFS(AND(D43="Permeable Pavement",E43="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D43="Permeable Pavement",E43="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D43="Bioretention",E43="Standard"),INDEX(PARAMS_BMP,3,5),AND(D43="Bioretention",E43="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D43="Bioretention",E43="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D43="Dry Swale",E43="—"),INDEX(PARAMS_BMP,6,5),AND(D43="Wet Swale",E43="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D43="Permeable Pavement",E43="Enhanced"),INDEX(PARAMS_BMP,1,5),IF(AND(D43="Permeable Pavement",E43="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),IF(AND(D43="Bioretention",E43="Standard"),INDEX(PARAMS_BMP,3,5),IF(AND(D43="Bioretention",E43="Enhanced"),INDEX(PARAMS_BMP,4,5),IF(AND(D43="Bioretention",E43="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),IF(AND(D43="Dry Swale",E43="—"),INDEX(PARAMS_BMP,6,5),IF(AND(D43="Wet Swale",E43="—"),INDEX(PARAMS_BMP,7,5),""))))))),"")</f>
         <v/>
       </c>
       <c r="K43" s="17">
@@ -12908,17 +12908,17 @@
       </c>
       <c r="Q43" s="4" t="n"/>
       <c r="R43" s="17">
-        <f>IFERROR(IFS(AND(D43="Permeable Pavement",E43="Enhanced"),INDEX(PARAMS_BMP,1,3),AND(D43="Permeable Pavement",E43="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),AND(D43="Bioretention",E43="Standard"),INDEX(PARAMS_BMP,3,3),AND(D43="Bioretention",E43="Enhanced"),INDEX(PARAMS_BMP,4,3),AND(D43="Bioretention",E43="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),AND(D43="Dry Swale",E43="—"),INDEX(PARAMS_BMP,6,3),AND(D43="Wet Swale",E43="—"),INDEX(PARAMS_BMP,7,3),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D43="Permeable Pavement",E43="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D43="Permeable Pavement",E43="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D43="Bioretention",E43="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D43="Bioretention",E43="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D43="Bioretention",E43="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D43="Dry Swale",E43="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D43="Wet Swale",E43="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
       <c r="S43" s="4" t="n"/>
       <c r="T43" s="17">
-        <f>IFERROR(IFS(AND(D43="Permeable Pavement",E43="Enhanced"),INDEX(PARAMS_BMP,1,4),AND(D43="Permeable Pavement",E43="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),AND(D43="Bioretention",E43="Standard"),INDEX(PARAMS_BMP,3,4),AND(D43="Bioretention",E43="Enhanced"),INDEX(PARAMS_BMP,4,4),AND(D43="Bioretention",E43="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),AND(D43="Dry Swale",E43="—"),INDEX(PARAMS_BMP,6,4),AND(D43="Wet Swale",E43="—"),INDEX(PARAMS_BMP,7,4),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D43="Permeable Pavement",E43="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D43="Permeable Pavement",E43="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D43="Bioretention",E43="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D43="Bioretention",E43="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D43="Bioretention",E43="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D43="Dry Swale",E43="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D43="Wet Swale",E43="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
       <c r="U43" s="4" t="n"/>
       <c r="V43" s="4">
-        <f>IFERROR(IF(OR(E43="Enhanced",E43="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C43,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C43,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C43,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C43,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E43="Enhanced",E43="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C43,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C43,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C43,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C43,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="W43" s="17">
@@ -12950,7 +12950,7 @@
         <v/>
       </c>
       <c r="AJ43" s="17">
-        <f>IFERROR(IFS(AND(D43="Permeable Pavement",E43="Enhanced"),INDEX(PARAMS_BMP,1,6),AND(D43="Permeable Pavement",E43="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),AND(D43="Bioretention",E43="Standard"),INDEX(PARAMS_BMP,3,6),AND(D43="Bioretention",E43="Enhanced"),INDEX(PARAMS_BMP,4,6),AND(D43="Bioretention",E43="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),AND(D43="Dry Swale",E43="—"),INDEX(PARAMS_BMP,6,6),AND(D43="Wet Swale",E43="—"),INDEX(PARAMS_BMP,7,6),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D43="Permeable Pavement",E43="Enhanced"),INDEX(PARAMS_BMP,1,6),IF(AND(D43="Permeable Pavement",E43="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),IF(AND(D43="Bioretention",E43="Standard"),INDEX(PARAMS_BMP,3,6),IF(AND(D43="Bioretention",E43="Enhanced"),INDEX(PARAMS_BMP,4,6),IF(AND(D43="Bioretention",E43="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),IF(AND(D43="Dry Swale",E43="—"),INDEX(PARAMS_BMP,6,6),IF(AND(D43="Wet Swale",E43="—"),INDEX(PARAMS_BMP,7,6),""))))))),"")</f>
         <v/>
       </c>
       <c r="AK43" s="17">
@@ -12976,11 +12976,11 @@
       <c r="G44" s="4" t="n"/>
       <c r="H44" s="4" t="n"/>
       <c r="I44" s="4">
-        <f>IFERROR(IF(OR(E44="Enhanced",E44="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C44,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C44,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C44,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C44,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E44="Enhanced",E44="Underdrained Enhanced"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C44,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C44,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C44,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C44,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="J44" s="17">
-        <f>IFERROR(IFS(AND(D44="Permeable Pavement",E44="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D44="Permeable Pavement",E44="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D44="Bioretention",E44="Standard"),INDEX(PARAMS_BMP,3,5),AND(D44="Bioretention",E44="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D44="Bioretention",E44="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D44="Dry Swale",E44="—"),INDEX(PARAMS_BMP,6,5),AND(D44="Wet Swale",E44="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D44="Permeable Pavement",E44="Enhanced"),INDEX(PARAMS_BMP,1,5),IF(AND(D44="Permeable Pavement",E44="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),IF(AND(D44="Bioretention",E44="Standard"),INDEX(PARAMS_BMP,3,5),IF(AND(D44="Bioretention",E44="Enhanced"),INDEX(PARAMS_BMP,4,5),IF(AND(D44="Bioretention",E44="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),IF(AND(D44="Dry Swale",E44="—"),INDEX(PARAMS_BMP,6,5),IF(AND(D44="Wet Swale",E44="—"),INDEX(PARAMS_BMP,7,5),""))))))),"")</f>
         <v/>
       </c>
       <c r="K44" s="17">
@@ -13003,17 +13003,17 @@
       </c>
       <c r="Q44" s="4" t="n"/>
       <c r="R44" s="17">
-        <f>IFERROR(IFS(AND(D44="Permeable Pavement",E44="Enhanced"),INDEX(PARAMS_BMP,1,3),AND(D44="Permeable Pavement",E44="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),AND(D44="Bioretention",E44="Standard"),INDEX(PARAMS_BMP,3,3),AND(D44="Bioretention",E44="Enhanced"),INDEX(PARAMS_BMP,4,3),AND(D44="Bioretention",E44="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),AND(D44="Dry Swale",E44="—"),INDEX(PARAMS_BMP,6,3),AND(D44="Wet Swale",E44="—"),INDEX(PARAMS_BMP,7,3),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D44="Permeable Pavement",E44="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D44="Permeable Pavement",E44="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D44="Bioretention",E44="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D44="Bioretention",E44="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D44="Bioretention",E44="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D44="Dry Swale",E44="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D44="Wet Swale",E44="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
       <c r="S44" s="4" t="n"/>
       <c r="T44" s="17">
-        <f>IFERROR(IFS(AND(D44="Permeable Pavement",E44="Enhanced"),INDEX(PARAMS_BMP,1,4),AND(D44="Permeable Pavement",E44="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),AND(D44="Bioretention",E44="Standard"),INDEX(PARAMS_BMP,3,4),AND(D44="Bioretention",E44="Enhanced"),INDEX(PARAMS_BMP,4,4),AND(D44="Bioretention",E44="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),AND(D44="Dry Swale",E44="—"),INDEX(PARAMS_BMP,6,4),AND(D44="Wet Swale",E44="—"),INDEX(PARAMS_BMP,7,4),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D44="Permeable Pavement",E44="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D44="Permeable Pavement",E44="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D44="Bioretention",E44="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D44="Bioretention",E44="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D44="Bioretention",E44="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D44="Dry Swale",E44="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D44="Wet Swale",E44="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
       <c r="U44" s="4" t="n"/>
       <c r="V44" s="4">
-        <f>IFERROR(IF(OR(E44="Enhanced",E44="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C44,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C44,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C44,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C44,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E44="Enhanced",E44="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C44,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C44,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C44,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C44,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="W44" s="17">
@@ -13045,7 +13045,7 @@
         <v/>
       </c>
       <c r="AJ44" s="17">
-        <f>IFERROR(IFS(AND(D44="Permeable Pavement",E44="Enhanced"),INDEX(PARAMS_BMP,1,6),AND(D44="Permeable Pavement",E44="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),AND(D44="Bioretention",E44="Standard"),INDEX(PARAMS_BMP,3,6),AND(D44="Bioretention",E44="Enhanced"),INDEX(PARAMS_BMP,4,6),AND(D44="Bioretention",E44="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),AND(D44="Dry Swale",E44="—"),INDEX(PARAMS_BMP,6,6),AND(D44="Wet Swale",E44="—"),INDEX(PARAMS_BMP,7,6),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D44="Permeable Pavement",E44="Enhanced"),INDEX(PARAMS_BMP,1,6),IF(AND(D44="Permeable Pavement",E44="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),IF(AND(D44="Bioretention",E44="Standard"),INDEX(PARAMS_BMP,3,6),IF(AND(D44="Bioretention",E44="Enhanced"),INDEX(PARAMS_BMP,4,6),IF(AND(D44="Bioretention",E44="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),IF(AND(D44="Dry Swale",E44="—"),INDEX(PARAMS_BMP,6,6),IF(AND(D44="Wet Swale",E44="—"),INDEX(PARAMS_BMP,7,6),""))))))),"")</f>
         <v/>
       </c>
       <c r="AK44" s="17">
@@ -13071,11 +13071,11 @@
       <c r="G45" s="4" t="n"/>
       <c r="H45" s="4" t="n"/>
       <c r="I45" s="4">
-        <f>IFERROR(IF(OR(E45="Enhanced",E45="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C45,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C45,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C45,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C45,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E45="Enhanced",E45="Underdrained Enhanced"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C45,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C45,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C45,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C45,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="J45" s="17">
-        <f>IFERROR(IFS(AND(D45="Permeable Pavement",E45="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D45="Permeable Pavement",E45="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D45="Bioretention",E45="Standard"),INDEX(PARAMS_BMP,3,5),AND(D45="Bioretention",E45="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D45="Bioretention",E45="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D45="Dry Swale",E45="—"),INDEX(PARAMS_BMP,6,5),AND(D45="Wet Swale",E45="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D45="Permeable Pavement",E45="Enhanced"),INDEX(PARAMS_BMP,1,5),IF(AND(D45="Permeable Pavement",E45="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),IF(AND(D45="Bioretention",E45="Standard"),INDEX(PARAMS_BMP,3,5),IF(AND(D45="Bioretention",E45="Enhanced"),INDEX(PARAMS_BMP,4,5),IF(AND(D45="Bioretention",E45="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),IF(AND(D45="Dry Swale",E45="—"),INDEX(PARAMS_BMP,6,5),IF(AND(D45="Wet Swale",E45="—"),INDEX(PARAMS_BMP,7,5),""))))))),"")</f>
         <v/>
       </c>
       <c r="K45" s="17">
@@ -13098,17 +13098,17 @@
       </c>
       <c r="Q45" s="4" t="n"/>
       <c r="R45" s="17">
-        <f>IFERROR(IFS(AND(D45="Permeable Pavement",E45="Enhanced"),INDEX(PARAMS_BMP,1,3),AND(D45="Permeable Pavement",E45="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),AND(D45="Bioretention",E45="Standard"),INDEX(PARAMS_BMP,3,3),AND(D45="Bioretention",E45="Enhanced"),INDEX(PARAMS_BMP,4,3),AND(D45="Bioretention",E45="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),AND(D45="Dry Swale",E45="—"),INDEX(PARAMS_BMP,6,3),AND(D45="Wet Swale",E45="—"),INDEX(PARAMS_BMP,7,3),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D45="Permeable Pavement",E45="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D45="Permeable Pavement",E45="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D45="Bioretention",E45="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D45="Bioretention",E45="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D45="Bioretention",E45="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D45="Dry Swale",E45="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D45="Wet Swale",E45="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
       <c r="S45" s="4" t="n"/>
       <c r="T45" s="17">
-        <f>IFERROR(IFS(AND(D45="Permeable Pavement",E45="Enhanced"),INDEX(PARAMS_BMP,1,4),AND(D45="Permeable Pavement",E45="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),AND(D45="Bioretention",E45="Standard"),INDEX(PARAMS_BMP,3,4),AND(D45="Bioretention",E45="Enhanced"),INDEX(PARAMS_BMP,4,4),AND(D45="Bioretention",E45="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),AND(D45="Dry Swale",E45="—"),INDEX(PARAMS_BMP,6,4),AND(D45="Wet Swale",E45="—"),INDEX(PARAMS_BMP,7,4),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D45="Permeable Pavement",E45="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D45="Permeable Pavement",E45="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D45="Bioretention",E45="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D45="Bioretention",E45="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D45="Bioretention",E45="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D45="Dry Swale",E45="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D45="Wet Swale",E45="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
       <c r="U45" s="4" t="n"/>
       <c r="V45" s="4">
-        <f>IFERROR(IF(OR(E45="Enhanced",E45="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C45,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C45,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C45,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C45,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E45="Enhanced",E45="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C45,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C45,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C45,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C45,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="W45" s="17">
@@ -13140,7 +13140,7 @@
         <v/>
       </c>
       <c r="AJ45" s="17">
-        <f>IFERROR(IFS(AND(D45="Permeable Pavement",E45="Enhanced"),INDEX(PARAMS_BMP,1,6),AND(D45="Permeable Pavement",E45="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),AND(D45="Bioretention",E45="Standard"),INDEX(PARAMS_BMP,3,6),AND(D45="Bioretention",E45="Enhanced"),INDEX(PARAMS_BMP,4,6),AND(D45="Bioretention",E45="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),AND(D45="Dry Swale",E45="—"),INDEX(PARAMS_BMP,6,6),AND(D45="Wet Swale",E45="—"),INDEX(PARAMS_BMP,7,6),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D45="Permeable Pavement",E45="Enhanced"),INDEX(PARAMS_BMP,1,6),IF(AND(D45="Permeable Pavement",E45="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),IF(AND(D45="Bioretention",E45="Standard"),INDEX(PARAMS_BMP,3,6),IF(AND(D45="Bioretention",E45="Enhanced"),INDEX(PARAMS_BMP,4,6),IF(AND(D45="Bioretention",E45="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),IF(AND(D45="Dry Swale",E45="—"),INDEX(PARAMS_BMP,6,6),IF(AND(D45="Wet Swale",E45="—"),INDEX(PARAMS_BMP,7,6),""))))))),"")</f>
         <v/>
       </c>
       <c r="AK45" s="17">
@@ -13166,11 +13166,11 @@
       <c r="G46" s="4" t="n"/>
       <c r="H46" s="4" t="n"/>
       <c r="I46" s="4">
-        <f>IFERROR(IF(OR(E46="Enhanced",E46="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C46,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C46,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C46,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C46,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E46="Enhanced",E46="Underdrained Enhanced"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C46,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C46,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C46,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C46,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="J46" s="17">
-        <f>IFERROR(IFS(AND(D46="Permeable Pavement",E46="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D46="Permeable Pavement",E46="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D46="Bioretention",E46="Standard"),INDEX(PARAMS_BMP,3,5),AND(D46="Bioretention",E46="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D46="Bioretention",E46="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D46="Dry Swale",E46="—"),INDEX(PARAMS_BMP,6,5),AND(D46="Wet Swale",E46="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D46="Permeable Pavement",E46="Enhanced"),INDEX(PARAMS_BMP,1,5),IF(AND(D46="Permeable Pavement",E46="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),IF(AND(D46="Bioretention",E46="Standard"),INDEX(PARAMS_BMP,3,5),IF(AND(D46="Bioretention",E46="Enhanced"),INDEX(PARAMS_BMP,4,5),IF(AND(D46="Bioretention",E46="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),IF(AND(D46="Dry Swale",E46="—"),INDEX(PARAMS_BMP,6,5),IF(AND(D46="Wet Swale",E46="—"),INDEX(PARAMS_BMP,7,5),""))))))),"")</f>
         <v/>
       </c>
       <c r="K46" s="17">
@@ -13193,17 +13193,17 @@
       </c>
       <c r="Q46" s="4" t="n"/>
       <c r="R46" s="17">
-        <f>IFERROR(IFS(AND(D46="Permeable Pavement",E46="Enhanced"),INDEX(PARAMS_BMP,1,3),AND(D46="Permeable Pavement",E46="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),AND(D46="Bioretention",E46="Standard"),INDEX(PARAMS_BMP,3,3),AND(D46="Bioretention",E46="Enhanced"),INDEX(PARAMS_BMP,4,3),AND(D46="Bioretention",E46="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),AND(D46="Dry Swale",E46="—"),INDEX(PARAMS_BMP,6,3),AND(D46="Wet Swale",E46="—"),INDEX(PARAMS_BMP,7,3),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D46="Permeable Pavement",E46="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D46="Permeable Pavement",E46="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D46="Bioretention",E46="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D46="Bioretention",E46="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D46="Bioretention",E46="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D46="Dry Swale",E46="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D46="Wet Swale",E46="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
       <c r="S46" s="4" t="n"/>
       <c r="T46" s="17">
-        <f>IFERROR(IFS(AND(D46="Permeable Pavement",E46="Enhanced"),INDEX(PARAMS_BMP,1,4),AND(D46="Permeable Pavement",E46="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),AND(D46="Bioretention",E46="Standard"),INDEX(PARAMS_BMP,3,4),AND(D46="Bioretention",E46="Enhanced"),INDEX(PARAMS_BMP,4,4),AND(D46="Bioretention",E46="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),AND(D46="Dry Swale",E46="—"),INDEX(PARAMS_BMP,6,4),AND(D46="Wet Swale",E46="—"),INDEX(PARAMS_BMP,7,4),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D46="Permeable Pavement",E46="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D46="Permeable Pavement",E46="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D46="Bioretention",E46="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D46="Bioretention",E46="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D46="Bioretention",E46="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D46="Dry Swale",E46="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D46="Wet Swale",E46="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
       <c r="U46" s="4" t="n"/>
       <c r="V46" s="4">
-        <f>IFERROR(IF(OR(E46="Enhanced",E46="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C46,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C46,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C46,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C46,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E46="Enhanced",E46="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C46,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C46,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C46,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C46,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="W46" s="17">
@@ -13235,7 +13235,7 @@
         <v/>
       </c>
       <c r="AJ46" s="17">
-        <f>IFERROR(IFS(AND(D46="Permeable Pavement",E46="Enhanced"),INDEX(PARAMS_BMP,1,6),AND(D46="Permeable Pavement",E46="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),AND(D46="Bioretention",E46="Standard"),INDEX(PARAMS_BMP,3,6),AND(D46="Bioretention",E46="Enhanced"),INDEX(PARAMS_BMP,4,6),AND(D46="Bioretention",E46="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),AND(D46="Dry Swale",E46="—"),INDEX(PARAMS_BMP,6,6),AND(D46="Wet Swale",E46="—"),INDEX(PARAMS_BMP,7,6),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D46="Permeable Pavement",E46="Enhanced"),INDEX(PARAMS_BMP,1,6),IF(AND(D46="Permeable Pavement",E46="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),IF(AND(D46="Bioretention",E46="Standard"),INDEX(PARAMS_BMP,3,6),IF(AND(D46="Bioretention",E46="Enhanced"),INDEX(PARAMS_BMP,4,6),IF(AND(D46="Bioretention",E46="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),IF(AND(D46="Dry Swale",E46="—"),INDEX(PARAMS_BMP,6,6),IF(AND(D46="Wet Swale",E46="—"),INDEX(PARAMS_BMP,7,6),""))))))),"")</f>
         <v/>
       </c>
       <c r="AK46" s="17">
@@ -13261,11 +13261,11 @@
       <c r="G47" s="4" t="n"/>
       <c r="H47" s="4" t="n"/>
       <c r="I47" s="4">
-        <f>IFERROR(IF(OR(E47="Enhanced",E47="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C47,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C47,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C47,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C47,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E47="Enhanced",E47="Underdrained Enhanced"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C47,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C47,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C47,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C47,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="J47" s="17">
-        <f>IFERROR(IFS(AND(D47="Permeable Pavement",E47="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D47="Permeable Pavement",E47="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D47="Bioretention",E47="Standard"),INDEX(PARAMS_BMP,3,5),AND(D47="Bioretention",E47="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D47="Bioretention",E47="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D47="Dry Swale",E47="—"),INDEX(PARAMS_BMP,6,5),AND(D47="Wet Swale",E47="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D47="Permeable Pavement",E47="Enhanced"),INDEX(PARAMS_BMP,1,5),IF(AND(D47="Permeable Pavement",E47="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),IF(AND(D47="Bioretention",E47="Standard"),INDEX(PARAMS_BMP,3,5),IF(AND(D47="Bioretention",E47="Enhanced"),INDEX(PARAMS_BMP,4,5),IF(AND(D47="Bioretention",E47="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),IF(AND(D47="Dry Swale",E47="—"),INDEX(PARAMS_BMP,6,5),IF(AND(D47="Wet Swale",E47="—"),INDEX(PARAMS_BMP,7,5),""))))))),"")</f>
         <v/>
       </c>
       <c r="K47" s="17">
@@ -13288,17 +13288,17 @@
       </c>
       <c r="Q47" s="4" t="n"/>
       <c r="R47" s="17">
-        <f>IFERROR(IFS(AND(D47="Permeable Pavement",E47="Enhanced"),INDEX(PARAMS_BMP,1,3),AND(D47="Permeable Pavement",E47="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),AND(D47="Bioretention",E47="Standard"),INDEX(PARAMS_BMP,3,3),AND(D47="Bioretention",E47="Enhanced"),INDEX(PARAMS_BMP,4,3),AND(D47="Bioretention",E47="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),AND(D47="Dry Swale",E47="—"),INDEX(PARAMS_BMP,6,3),AND(D47="Wet Swale",E47="—"),INDEX(PARAMS_BMP,7,3),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D47="Permeable Pavement",E47="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D47="Permeable Pavement",E47="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D47="Bioretention",E47="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D47="Bioretention",E47="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D47="Bioretention",E47="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D47="Dry Swale",E47="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D47="Wet Swale",E47="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
       <c r="S47" s="4" t="n"/>
       <c r="T47" s="17">
-        <f>IFERROR(IFS(AND(D47="Permeable Pavement",E47="Enhanced"),INDEX(PARAMS_BMP,1,4),AND(D47="Permeable Pavement",E47="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),AND(D47="Bioretention",E47="Standard"),INDEX(PARAMS_BMP,3,4),AND(D47="Bioretention",E47="Enhanced"),INDEX(PARAMS_BMP,4,4),AND(D47="Bioretention",E47="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),AND(D47="Dry Swale",E47="—"),INDEX(PARAMS_BMP,6,4),AND(D47="Wet Swale",E47="—"),INDEX(PARAMS_BMP,7,4),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D47="Permeable Pavement",E47="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D47="Permeable Pavement",E47="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D47="Bioretention",E47="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D47="Bioretention",E47="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D47="Bioretention",E47="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D47="Dry Swale",E47="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D47="Wet Swale",E47="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
       <c r="U47" s="4" t="n"/>
       <c r="V47" s="4">
-        <f>IFERROR(IF(OR(E47="Enhanced",E47="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C47,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C47,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C47,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C47,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E47="Enhanced",E47="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C47,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C47,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C47,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C47,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="W47" s="17">
@@ -13330,7 +13330,7 @@
         <v/>
       </c>
       <c r="AJ47" s="17">
-        <f>IFERROR(IFS(AND(D47="Permeable Pavement",E47="Enhanced"),INDEX(PARAMS_BMP,1,6),AND(D47="Permeable Pavement",E47="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),AND(D47="Bioretention",E47="Standard"),INDEX(PARAMS_BMP,3,6),AND(D47="Bioretention",E47="Enhanced"),INDEX(PARAMS_BMP,4,6),AND(D47="Bioretention",E47="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),AND(D47="Dry Swale",E47="—"),INDEX(PARAMS_BMP,6,6),AND(D47="Wet Swale",E47="—"),INDEX(PARAMS_BMP,7,6),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D47="Permeable Pavement",E47="Enhanced"),INDEX(PARAMS_BMP,1,6),IF(AND(D47="Permeable Pavement",E47="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),IF(AND(D47="Bioretention",E47="Standard"),INDEX(PARAMS_BMP,3,6),IF(AND(D47="Bioretention",E47="Enhanced"),INDEX(PARAMS_BMP,4,6),IF(AND(D47="Bioretention",E47="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),IF(AND(D47="Dry Swale",E47="—"),INDEX(PARAMS_BMP,6,6),IF(AND(D47="Wet Swale",E47="—"),INDEX(PARAMS_BMP,7,6),""))))))),"")</f>
         <v/>
       </c>
       <c r="AK47" s="17">
@@ -13356,11 +13356,11 @@
       <c r="G48" s="4" t="n"/>
       <c r="H48" s="4" t="n"/>
       <c r="I48" s="4">
-        <f>IFERROR(IF(OR(E48="Enhanced",E48="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C48,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C48,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C48,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C48,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E48="Enhanced",E48="Underdrained Enhanced"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C48,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C48,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C48,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C48,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="J48" s="17">
-        <f>IFERROR(IFS(AND(D48="Permeable Pavement",E48="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D48="Permeable Pavement",E48="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D48="Bioretention",E48="Standard"),INDEX(PARAMS_BMP,3,5),AND(D48="Bioretention",E48="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D48="Bioretention",E48="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D48="Dry Swale",E48="—"),INDEX(PARAMS_BMP,6,5),AND(D48="Wet Swale",E48="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D48="Permeable Pavement",E48="Enhanced"),INDEX(PARAMS_BMP,1,5),IF(AND(D48="Permeable Pavement",E48="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),IF(AND(D48="Bioretention",E48="Standard"),INDEX(PARAMS_BMP,3,5),IF(AND(D48="Bioretention",E48="Enhanced"),INDEX(PARAMS_BMP,4,5),IF(AND(D48="Bioretention",E48="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),IF(AND(D48="Dry Swale",E48="—"),INDEX(PARAMS_BMP,6,5),IF(AND(D48="Wet Swale",E48="—"),INDEX(PARAMS_BMP,7,5),""))))))),"")</f>
         <v/>
       </c>
       <c r="K48" s="17">
@@ -13383,17 +13383,17 @@
       </c>
       <c r="Q48" s="4" t="n"/>
       <c r="R48" s="17">
-        <f>IFERROR(IFS(AND(D48="Permeable Pavement",E48="Enhanced"),INDEX(PARAMS_BMP,1,3),AND(D48="Permeable Pavement",E48="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),AND(D48="Bioretention",E48="Standard"),INDEX(PARAMS_BMP,3,3),AND(D48="Bioretention",E48="Enhanced"),INDEX(PARAMS_BMP,4,3),AND(D48="Bioretention",E48="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),AND(D48="Dry Swale",E48="—"),INDEX(PARAMS_BMP,6,3),AND(D48="Wet Swale",E48="—"),INDEX(PARAMS_BMP,7,3),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D48="Permeable Pavement",E48="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D48="Permeable Pavement",E48="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D48="Bioretention",E48="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D48="Bioretention",E48="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D48="Bioretention",E48="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D48="Dry Swale",E48="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D48="Wet Swale",E48="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
       <c r="S48" s="4" t="n"/>
       <c r="T48" s="17">
-        <f>IFERROR(IFS(AND(D48="Permeable Pavement",E48="Enhanced"),INDEX(PARAMS_BMP,1,4),AND(D48="Permeable Pavement",E48="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),AND(D48="Bioretention",E48="Standard"),INDEX(PARAMS_BMP,3,4),AND(D48="Bioretention",E48="Enhanced"),INDEX(PARAMS_BMP,4,4),AND(D48="Bioretention",E48="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),AND(D48="Dry Swale",E48="—"),INDEX(PARAMS_BMP,6,4),AND(D48="Wet Swale",E48="—"),INDEX(PARAMS_BMP,7,4),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D48="Permeable Pavement",E48="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D48="Permeable Pavement",E48="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D48="Bioretention",E48="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D48="Bioretention",E48="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D48="Bioretention",E48="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D48="Dry Swale",E48="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D48="Wet Swale",E48="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
       <c r="U48" s="4" t="n"/>
       <c r="V48" s="4">
-        <f>IFERROR(IF(OR(E48="Enhanced",E48="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C48,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C48,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C48,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C48,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E48="Enhanced",E48="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C48,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C48,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C48,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C48,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="W48" s="17">
@@ -13425,7 +13425,7 @@
         <v/>
       </c>
       <c r="AJ48" s="17">
-        <f>IFERROR(IFS(AND(D48="Permeable Pavement",E48="Enhanced"),INDEX(PARAMS_BMP,1,6),AND(D48="Permeable Pavement",E48="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),AND(D48="Bioretention",E48="Standard"),INDEX(PARAMS_BMP,3,6),AND(D48="Bioretention",E48="Enhanced"),INDEX(PARAMS_BMP,4,6),AND(D48="Bioretention",E48="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),AND(D48="Dry Swale",E48="—"),INDEX(PARAMS_BMP,6,6),AND(D48="Wet Swale",E48="—"),INDEX(PARAMS_BMP,7,6),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D48="Permeable Pavement",E48="Enhanced"),INDEX(PARAMS_BMP,1,6),IF(AND(D48="Permeable Pavement",E48="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),IF(AND(D48="Bioretention",E48="Standard"),INDEX(PARAMS_BMP,3,6),IF(AND(D48="Bioretention",E48="Enhanced"),INDEX(PARAMS_BMP,4,6),IF(AND(D48="Bioretention",E48="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),IF(AND(D48="Dry Swale",E48="—"),INDEX(PARAMS_BMP,6,6),IF(AND(D48="Wet Swale",E48="—"),INDEX(PARAMS_BMP,7,6),""))))))),"")</f>
         <v/>
       </c>
       <c r="AK48" s="17">
@@ -13451,11 +13451,11 @@
       <c r="G49" s="4" t="n"/>
       <c r="H49" s="4" t="n"/>
       <c r="I49" s="4">
-        <f>IFERROR(IF(OR(E49="Enhanced",E49="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C49,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C49,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C49,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C49,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E49="Enhanced",E49="Underdrained Enhanced"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C49,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C49,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C49,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C49,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="J49" s="17">
-        <f>IFERROR(IFS(AND(D49="Permeable Pavement",E49="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D49="Permeable Pavement",E49="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D49="Bioretention",E49="Standard"),INDEX(PARAMS_BMP,3,5),AND(D49="Bioretention",E49="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D49="Bioretention",E49="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D49="Dry Swale",E49="—"),INDEX(PARAMS_BMP,6,5),AND(D49="Wet Swale",E49="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D49="Permeable Pavement",E49="Enhanced"),INDEX(PARAMS_BMP,1,5),IF(AND(D49="Permeable Pavement",E49="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),IF(AND(D49="Bioretention",E49="Standard"),INDEX(PARAMS_BMP,3,5),IF(AND(D49="Bioretention",E49="Enhanced"),INDEX(PARAMS_BMP,4,5),IF(AND(D49="Bioretention",E49="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),IF(AND(D49="Dry Swale",E49="—"),INDEX(PARAMS_BMP,6,5),IF(AND(D49="Wet Swale",E49="—"),INDEX(PARAMS_BMP,7,5),""))))))),"")</f>
         <v/>
       </c>
       <c r="K49" s="17">
@@ -13478,17 +13478,17 @@
       </c>
       <c r="Q49" s="4" t="n"/>
       <c r="R49" s="17">
-        <f>IFERROR(IFS(AND(D49="Permeable Pavement",E49="Enhanced"),INDEX(PARAMS_BMP,1,3),AND(D49="Permeable Pavement",E49="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),AND(D49="Bioretention",E49="Standard"),INDEX(PARAMS_BMP,3,3),AND(D49="Bioretention",E49="Enhanced"),INDEX(PARAMS_BMP,4,3),AND(D49="Bioretention",E49="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),AND(D49="Dry Swale",E49="—"),INDEX(PARAMS_BMP,6,3),AND(D49="Wet Swale",E49="—"),INDEX(PARAMS_BMP,7,3),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D49="Permeable Pavement",E49="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D49="Permeable Pavement",E49="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D49="Bioretention",E49="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D49="Bioretention",E49="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D49="Bioretention",E49="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D49="Dry Swale",E49="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D49="Wet Swale",E49="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
       <c r="S49" s="4" t="n"/>
       <c r="T49" s="17">
-        <f>IFERROR(IFS(AND(D49="Permeable Pavement",E49="Enhanced"),INDEX(PARAMS_BMP,1,4),AND(D49="Permeable Pavement",E49="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),AND(D49="Bioretention",E49="Standard"),INDEX(PARAMS_BMP,3,4),AND(D49="Bioretention",E49="Enhanced"),INDEX(PARAMS_BMP,4,4),AND(D49="Bioretention",E49="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),AND(D49="Dry Swale",E49="—"),INDEX(PARAMS_BMP,6,4),AND(D49="Wet Swale",E49="—"),INDEX(PARAMS_BMP,7,4),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D49="Permeable Pavement",E49="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D49="Permeable Pavement",E49="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D49="Bioretention",E49="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D49="Bioretention",E49="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D49="Bioretention",E49="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D49="Dry Swale",E49="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D49="Wet Swale",E49="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
       <c r="U49" s="4" t="n"/>
       <c r="V49" s="4">
-        <f>IFERROR(IF(OR(E49="Enhanced",E49="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C49,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C49,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C49,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C49,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E49="Enhanced",E49="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C49,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C49,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C49,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C49,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="W49" s="17">
@@ -13520,7 +13520,7 @@
         <v/>
       </c>
       <c r="AJ49" s="17">
-        <f>IFERROR(IFS(AND(D49="Permeable Pavement",E49="Enhanced"),INDEX(PARAMS_BMP,1,6),AND(D49="Permeable Pavement",E49="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),AND(D49="Bioretention",E49="Standard"),INDEX(PARAMS_BMP,3,6),AND(D49="Bioretention",E49="Enhanced"),INDEX(PARAMS_BMP,4,6),AND(D49="Bioretention",E49="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),AND(D49="Dry Swale",E49="—"),INDEX(PARAMS_BMP,6,6),AND(D49="Wet Swale",E49="—"),INDEX(PARAMS_BMP,7,6),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D49="Permeable Pavement",E49="Enhanced"),INDEX(PARAMS_BMP,1,6),IF(AND(D49="Permeable Pavement",E49="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),IF(AND(D49="Bioretention",E49="Standard"),INDEX(PARAMS_BMP,3,6),IF(AND(D49="Bioretention",E49="Enhanced"),INDEX(PARAMS_BMP,4,6),IF(AND(D49="Bioretention",E49="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),IF(AND(D49="Dry Swale",E49="—"),INDEX(PARAMS_BMP,6,6),IF(AND(D49="Wet Swale",E49="—"),INDEX(PARAMS_BMP,7,6),""))))))),"")</f>
         <v/>
       </c>
       <c r="AK49" s="17">
@@ -13546,11 +13546,11 @@
       <c r="G50" s="4" t="n"/>
       <c r="H50" s="4" t="n"/>
       <c r="I50" s="4">
-        <f>IFERROR(IF(OR(E50="Enhanced",E50="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C50,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C50,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C50,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C50,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E50="Enhanced",E50="Underdrained Enhanced"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C50,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C50,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C50,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C50,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="J50" s="17">
-        <f>IFERROR(IFS(AND(D50="Permeable Pavement",E50="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D50="Permeable Pavement",E50="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D50="Bioretention",E50="Standard"),INDEX(PARAMS_BMP,3,5),AND(D50="Bioretention",E50="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D50="Bioretention",E50="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D50="Dry Swale",E50="—"),INDEX(PARAMS_BMP,6,5),AND(D50="Wet Swale",E50="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D50="Permeable Pavement",E50="Enhanced"),INDEX(PARAMS_BMP,1,5),IF(AND(D50="Permeable Pavement",E50="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),IF(AND(D50="Bioretention",E50="Standard"),INDEX(PARAMS_BMP,3,5),IF(AND(D50="Bioretention",E50="Enhanced"),INDEX(PARAMS_BMP,4,5),IF(AND(D50="Bioretention",E50="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),IF(AND(D50="Dry Swale",E50="—"),INDEX(PARAMS_BMP,6,5),IF(AND(D50="Wet Swale",E50="—"),INDEX(PARAMS_BMP,7,5),""))))))),"")</f>
         <v/>
       </c>
       <c r="K50" s="17">
@@ -13573,17 +13573,17 @@
       </c>
       <c r="Q50" s="4" t="n"/>
       <c r="R50" s="17">
-        <f>IFERROR(IFS(AND(D50="Permeable Pavement",E50="Enhanced"),INDEX(PARAMS_BMP,1,3),AND(D50="Permeable Pavement",E50="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),AND(D50="Bioretention",E50="Standard"),INDEX(PARAMS_BMP,3,3),AND(D50="Bioretention",E50="Enhanced"),INDEX(PARAMS_BMP,4,3),AND(D50="Bioretention",E50="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),AND(D50="Dry Swale",E50="—"),INDEX(PARAMS_BMP,6,3),AND(D50="Wet Swale",E50="—"),INDEX(PARAMS_BMP,7,3),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D50="Permeable Pavement",E50="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D50="Permeable Pavement",E50="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D50="Bioretention",E50="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D50="Bioretention",E50="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D50="Bioretention",E50="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D50="Dry Swale",E50="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D50="Wet Swale",E50="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
       <c r="S50" s="4" t="n"/>
       <c r="T50" s="17">
-        <f>IFERROR(IFS(AND(D50="Permeable Pavement",E50="Enhanced"),INDEX(PARAMS_BMP,1,4),AND(D50="Permeable Pavement",E50="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),AND(D50="Bioretention",E50="Standard"),INDEX(PARAMS_BMP,3,4),AND(D50="Bioretention",E50="Enhanced"),INDEX(PARAMS_BMP,4,4),AND(D50="Bioretention",E50="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),AND(D50="Dry Swale",E50="—"),INDEX(PARAMS_BMP,6,4),AND(D50="Wet Swale",E50="—"),INDEX(PARAMS_BMP,7,4),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D50="Permeable Pavement",E50="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D50="Permeable Pavement",E50="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D50="Bioretention",E50="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D50="Bioretention",E50="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D50="Bioretention",E50="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D50="Dry Swale",E50="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D50="Wet Swale",E50="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
       <c r="U50" s="4" t="n"/>
       <c r="V50" s="4">
-        <f>IFERROR(IF(OR(E50="Enhanced",E50="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C50,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C50,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C50,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C50,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E50="Enhanced",E50="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C50,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C50,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C50,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C50,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="W50" s="17">
@@ -13615,7 +13615,7 @@
         <v/>
       </c>
       <c r="AJ50" s="17">
-        <f>IFERROR(IFS(AND(D50="Permeable Pavement",E50="Enhanced"),INDEX(PARAMS_BMP,1,6),AND(D50="Permeable Pavement",E50="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),AND(D50="Bioretention",E50="Standard"),INDEX(PARAMS_BMP,3,6),AND(D50="Bioretention",E50="Enhanced"),INDEX(PARAMS_BMP,4,6),AND(D50="Bioretention",E50="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),AND(D50="Dry Swale",E50="—"),INDEX(PARAMS_BMP,6,6),AND(D50="Wet Swale",E50="—"),INDEX(PARAMS_BMP,7,6),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D50="Permeable Pavement",E50="Enhanced"),INDEX(PARAMS_BMP,1,6),IF(AND(D50="Permeable Pavement",E50="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),IF(AND(D50="Bioretention",E50="Standard"),INDEX(PARAMS_BMP,3,6),IF(AND(D50="Bioretention",E50="Enhanced"),INDEX(PARAMS_BMP,4,6),IF(AND(D50="Bioretention",E50="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),IF(AND(D50="Dry Swale",E50="—"),INDEX(PARAMS_BMP,6,6),IF(AND(D50="Wet Swale",E50="—"),INDEX(PARAMS_BMP,7,6),""))))))),"")</f>
         <v/>
       </c>
       <c r="AK50" s="17">
@@ -13641,11 +13641,11 @@
       <c r="G51" s="4" t="n"/>
       <c r="H51" s="4" t="n"/>
       <c r="I51" s="4">
-        <f>IFERROR(IF(OR(E51="Enhanced",E51="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C51,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C51,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C51,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C51,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E51="Enhanced",E51="Underdrained Enhanced"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C51,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C51,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C51,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C51,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="J51" s="17">
-        <f>IFERROR(IFS(AND(D51="Permeable Pavement",E51="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D51="Permeable Pavement",E51="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D51="Bioretention",E51="Standard"),INDEX(PARAMS_BMP,3,5),AND(D51="Bioretention",E51="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D51="Bioretention",E51="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D51="Dry Swale",E51="—"),INDEX(PARAMS_BMP,6,5),AND(D51="Wet Swale",E51="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D51="Permeable Pavement",E51="Enhanced"),INDEX(PARAMS_BMP,1,5),IF(AND(D51="Permeable Pavement",E51="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),IF(AND(D51="Bioretention",E51="Standard"),INDEX(PARAMS_BMP,3,5),IF(AND(D51="Bioretention",E51="Enhanced"),INDEX(PARAMS_BMP,4,5),IF(AND(D51="Bioretention",E51="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),IF(AND(D51="Dry Swale",E51="—"),INDEX(PARAMS_BMP,6,5),IF(AND(D51="Wet Swale",E51="—"),INDEX(PARAMS_BMP,7,5),""))))))),"")</f>
         <v/>
       </c>
       <c r="K51" s="17">
@@ -13668,17 +13668,17 @@
       </c>
       <c r="Q51" s="4" t="n"/>
       <c r="R51" s="17">
-        <f>IFERROR(IFS(AND(D51="Permeable Pavement",E51="Enhanced"),INDEX(PARAMS_BMP,1,3),AND(D51="Permeable Pavement",E51="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),AND(D51="Bioretention",E51="Standard"),INDEX(PARAMS_BMP,3,3),AND(D51="Bioretention",E51="Enhanced"),INDEX(PARAMS_BMP,4,3),AND(D51="Bioretention",E51="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),AND(D51="Dry Swale",E51="—"),INDEX(PARAMS_BMP,6,3),AND(D51="Wet Swale",E51="—"),INDEX(PARAMS_BMP,7,3),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D51="Permeable Pavement",E51="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D51="Permeable Pavement",E51="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D51="Bioretention",E51="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D51="Bioretention",E51="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D51="Bioretention",E51="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D51="Dry Swale",E51="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D51="Wet Swale",E51="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
       <c r="S51" s="4" t="n"/>
       <c r="T51" s="17">
-        <f>IFERROR(IFS(AND(D51="Permeable Pavement",E51="Enhanced"),INDEX(PARAMS_BMP,1,4),AND(D51="Permeable Pavement",E51="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),AND(D51="Bioretention",E51="Standard"),INDEX(PARAMS_BMP,3,4),AND(D51="Bioretention",E51="Enhanced"),INDEX(PARAMS_BMP,4,4),AND(D51="Bioretention",E51="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),AND(D51="Dry Swale",E51="—"),INDEX(PARAMS_BMP,6,4),AND(D51="Wet Swale",E51="—"),INDEX(PARAMS_BMP,7,4),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D51="Permeable Pavement",E51="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D51="Permeable Pavement",E51="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D51="Bioretention",E51="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D51="Bioretention",E51="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D51="Bioretention",E51="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D51="Dry Swale",E51="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D51="Wet Swale",E51="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
       <c r="U51" s="4" t="n"/>
       <c r="V51" s="4">
-        <f>IFERROR(IF(OR(E51="Enhanced",E51="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C51,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C51,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C51,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C51,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E51="Enhanced",E51="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C51,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C51,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C51,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C51,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="W51" s="17">
@@ -13710,7 +13710,7 @@
         <v/>
       </c>
       <c r="AJ51" s="17">
-        <f>IFERROR(IFS(AND(D51="Permeable Pavement",E51="Enhanced"),INDEX(PARAMS_BMP,1,6),AND(D51="Permeable Pavement",E51="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),AND(D51="Bioretention",E51="Standard"),INDEX(PARAMS_BMP,3,6),AND(D51="Bioretention",E51="Enhanced"),INDEX(PARAMS_BMP,4,6),AND(D51="Bioretention",E51="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),AND(D51="Dry Swale",E51="—"),INDEX(PARAMS_BMP,6,6),AND(D51="Wet Swale",E51="—"),INDEX(PARAMS_BMP,7,6),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D51="Permeable Pavement",E51="Enhanced"),INDEX(PARAMS_BMP,1,6),IF(AND(D51="Permeable Pavement",E51="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),IF(AND(D51="Bioretention",E51="Standard"),INDEX(PARAMS_BMP,3,6),IF(AND(D51="Bioretention",E51="Enhanced"),INDEX(PARAMS_BMP,4,6),IF(AND(D51="Bioretention",E51="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),IF(AND(D51="Dry Swale",E51="—"),INDEX(PARAMS_BMP,6,6),IF(AND(D51="Wet Swale",E51="—"),INDEX(PARAMS_BMP,7,6),""))))))),"")</f>
         <v/>
       </c>
       <c r="AK51" s="17">
@@ -13736,11 +13736,11 @@
       <c r="G52" s="4" t="n"/>
       <c r="H52" s="4" t="n"/>
       <c r="I52" s="4">
-        <f>IFERROR(IF(OR(E52="Enhanced",E52="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C52,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C52,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C52,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C52,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E52="Enhanced",E52="Underdrained Enhanced"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C52,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C52,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C52,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C52,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="J52" s="17">
-        <f>IFERROR(IFS(AND(D52="Permeable Pavement",E52="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D52="Permeable Pavement",E52="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D52="Bioretention",E52="Standard"),INDEX(PARAMS_BMP,3,5),AND(D52="Bioretention",E52="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D52="Bioretention",E52="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D52="Dry Swale",E52="—"),INDEX(PARAMS_BMP,6,5),AND(D52="Wet Swale",E52="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D52="Permeable Pavement",E52="Enhanced"),INDEX(PARAMS_BMP,1,5),IF(AND(D52="Permeable Pavement",E52="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),IF(AND(D52="Bioretention",E52="Standard"),INDEX(PARAMS_BMP,3,5),IF(AND(D52="Bioretention",E52="Enhanced"),INDEX(PARAMS_BMP,4,5),IF(AND(D52="Bioretention",E52="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),IF(AND(D52="Dry Swale",E52="—"),INDEX(PARAMS_BMP,6,5),IF(AND(D52="Wet Swale",E52="—"),INDEX(PARAMS_BMP,7,5),""))))))),"")</f>
         <v/>
       </c>
       <c r="K52" s="17">
@@ -13763,17 +13763,17 @@
       </c>
       <c r="Q52" s="4" t="n"/>
       <c r="R52" s="17">
-        <f>IFERROR(IFS(AND(D52="Permeable Pavement",E52="Enhanced"),INDEX(PARAMS_BMP,1,3),AND(D52="Permeable Pavement",E52="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),AND(D52="Bioretention",E52="Standard"),INDEX(PARAMS_BMP,3,3),AND(D52="Bioretention",E52="Enhanced"),INDEX(PARAMS_BMP,4,3),AND(D52="Bioretention",E52="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),AND(D52="Dry Swale",E52="—"),INDEX(PARAMS_BMP,6,3),AND(D52="Wet Swale",E52="—"),INDEX(PARAMS_BMP,7,3),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D52="Permeable Pavement",E52="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D52="Permeable Pavement",E52="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D52="Bioretention",E52="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D52="Bioretention",E52="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D52="Bioretention",E52="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D52="Dry Swale",E52="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D52="Wet Swale",E52="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
       <c r="S52" s="4" t="n"/>
       <c r="T52" s="17">
-        <f>IFERROR(IFS(AND(D52="Permeable Pavement",E52="Enhanced"),INDEX(PARAMS_BMP,1,4),AND(D52="Permeable Pavement",E52="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),AND(D52="Bioretention",E52="Standard"),INDEX(PARAMS_BMP,3,4),AND(D52="Bioretention",E52="Enhanced"),INDEX(PARAMS_BMP,4,4),AND(D52="Bioretention",E52="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),AND(D52="Dry Swale",E52="—"),INDEX(PARAMS_BMP,6,4),AND(D52="Wet Swale",E52="—"),INDEX(PARAMS_BMP,7,4),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D52="Permeable Pavement",E52="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D52="Permeable Pavement",E52="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D52="Bioretention",E52="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D52="Bioretention",E52="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D52="Bioretention",E52="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D52="Dry Swale",E52="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D52="Wet Swale",E52="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
       <c r="U52" s="4" t="n"/>
       <c r="V52" s="4">
-        <f>IFERROR(IF(OR(E52="Enhanced",E52="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C52,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C52,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C52,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C52,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E52="Enhanced",E52="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C52,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C52,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C52,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C52,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="W52" s="17">
@@ -13805,7 +13805,7 @@
         <v/>
       </c>
       <c r="AJ52" s="17">
-        <f>IFERROR(IFS(AND(D52="Permeable Pavement",E52="Enhanced"),INDEX(PARAMS_BMP,1,6),AND(D52="Permeable Pavement",E52="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),AND(D52="Bioretention",E52="Standard"),INDEX(PARAMS_BMP,3,6),AND(D52="Bioretention",E52="Enhanced"),INDEX(PARAMS_BMP,4,6),AND(D52="Bioretention",E52="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),AND(D52="Dry Swale",E52="—"),INDEX(PARAMS_BMP,6,6),AND(D52="Wet Swale",E52="—"),INDEX(PARAMS_BMP,7,6),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D52="Permeable Pavement",E52="Enhanced"),INDEX(PARAMS_BMP,1,6),IF(AND(D52="Permeable Pavement",E52="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),IF(AND(D52="Bioretention",E52="Standard"),INDEX(PARAMS_BMP,3,6),IF(AND(D52="Bioretention",E52="Enhanced"),INDEX(PARAMS_BMP,4,6),IF(AND(D52="Bioretention",E52="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),IF(AND(D52="Dry Swale",E52="—"),INDEX(PARAMS_BMP,6,6),IF(AND(D52="Wet Swale",E52="—"),INDEX(PARAMS_BMP,7,6),""))))))),"")</f>
         <v/>
       </c>
       <c r="AK52" s="17">
@@ -13831,11 +13831,11 @@
       <c r="G53" s="4" t="n"/>
       <c r="H53" s="4" t="n"/>
       <c r="I53" s="4">
-        <f>IFERROR(IF(OR(E53="Enhanced",E53="Underdrained Enhanced"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C53,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C53,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C53,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C53,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E53="Enhanced",E53="Underdrained Enhanced"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C53,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C53,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C53,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C53,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="J53" s="17">
-        <f>IFERROR(IFS(AND(D53="Permeable Pavement",E53="Enhanced"),INDEX(PARAMS_BMP,1,5),AND(D53="Permeable Pavement",E53="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),AND(D53="Bioretention",E53="Standard"),INDEX(PARAMS_BMP,3,5),AND(D53="Bioretention",E53="Enhanced"),INDEX(PARAMS_BMP,4,5),AND(D53="Bioretention",E53="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),AND(D53="Dry Swale",E53="—"),INDEX(PARAMS_BMP,6,5),AND(D53="Wet Swale",E53="—"),INDEX(PARAMS_BMP,7,5),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D53="Permeable Pavement",E53="Enhanced"),INDEX(PARAMS_BMP,1,5),IF(AND(D53="Permeable Pavement",E53="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,5),IF(AND(D53="Bioretention",E53="Standard"),INDEX(PARAMS_BMP,3,5),IF(AND(D53="Bioretention",E53="Enhanced"),INDEX(PARAMS_BMP,4,5),IF(AND(D53="Bioretention",E53="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,5),IF(AND(D53="Dry Swale",E53="—"),INDEX(PARAMS_BMP,6,5),IF(AND(D53="Wet Swale",E53="—"),INDEX(PARAMS_BMP,7,5),""))))))),"")</f>
         <v/>
       </c>
       <c r="K53" s="17">
@@ -13858,17 +13858,17 @@
       </c>
       <c r="Q53" s="4" t="n"/>
       <c r="R53" s="17">
-        <f>IFERROR(IFS(AND(D53="Permeable Pavement",E53="Enhanced"),INDEX(PARAMS_BMP,1,3),AND(D53="Permeable Pavement",E53="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),AND(D53="Bioretention",E53="Standard"),INDEX(PARAMS_BMP,3,3),AND(D53="Bioretention",E53="Enhanced"),INDEX(PARAMS_BMP,4,3),AND(D53="Bioretention",E53="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),AND(D53="Dry Swale",E53="—"),INDEX(PARAMS_BMP,6,3),AND(D53="Wet Swale",E53="—"),INDEX(PARAMS_BMP,7,3),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D53="Permeable Pavement",E53="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D53="Permeable Pavement",E53="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D53="Bioretention",E53="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D53="Bioretention",E53="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D53="Bioretention",E53="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D53="Dry Swale",E53="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D53="Wet Swale",E53="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
       <c r="S53" s="4" t="n"/>
       <c r="T53" s="17">
-        <f>IFERROR(IFS(AND(D53="Permeable Pavement",E53="Enhanced"),INDEX(PARAMS_BMP,1,4),AND(D53="Permeable Pavement",E53="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),AND(D53="Bioretention",E53="Standard"),INDEX(PARAMS_BMP,3,4),AND(D53="Bioretention",E53="Enhanced"),INDEX(PARAMS_BMP,4,4),AND(D53="Bioretention",E53="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),AND(D53="Dry Swale",E53="—"),INDEX(PARAMS_BMP,6,4),AND(D53="Wet Swale",E53="—"),INDEX(PARAMS_BMP,7,4),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D53="Permeable Pavement",E53="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D53="Permeable Pavement",E53="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D53="Bioretention",E53="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D53="Bioretention",E53="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D53="Bioretention",E53="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D53="Dry Swale",E53="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D53="Wet Swale",E53="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
       <c r="U53" s="4" t="n"/>
       <c r="V53" s="4">
-        <f>IFERROR(IF(OR(E53="Enhanced",E53="Enhanced w/ Underdrain"),VLOOKUP(IFS(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C53,'CDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C53,'CDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C53,'CDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C53,'CDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),PARAMS_Ksat,2,FALSE),0),0)</f>
+        <f>IFERROR(IF(OR(E53="Enhanced",E53="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C53,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C53,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C53,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$E$4:$E$53,'CDA'!$A$4:$A$53,C53,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
       </c>
       <c r="W53" s="17">
@@ -13900,7 +13900,7 @@
         <v/>
       </c>
       <c r="AJ53" s="17">
-        <f>IFERROR(IFS(AND(D53="Permeable Pavement",E53="Enhanced"),INDEX(PARAMS_BMP,1,6),AND(D53="Permeable Pavement",E53="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),AND(D53="Bioretention",E53="Standard"),INDEX(PARAMS_BMP,3,6),AND(D53="Bioretention",E53="Enhanced"),INDEX(PARAMS_BMP,4,6),AND(D53="Bioretention",E53="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),AND(D53="Dry Swale",E53="—"),INDEX(PARAMS_BMP,6,6),AND(D53="Wet Swale",E53="—"),INDEX(PARAMS_BMP,7,6),TRUE,""),"")</f>
+        <f>IFERROR(IF(AND(D53="Permeable Pavement",E53="Enhanced"),INDEX(PARAMS_BMP,1,6),IF(AND(D53="Permeable Pavement",E53="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,6),IF(AND(D53="Bioretention",E53="Standard"),INDEX(PARAMS_BMP,3,6),IF(AND(D53="Bioretention",E53="Enhanced"),INDEX(PARAMS_BMP,4,6),IF(AND(D53="Bioretention",E53="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,6),IF(AND(D53="Dry Swale",E53="—"),INDEX(PARAMS_BMP,6,6),IF(AND(D53="Wet Swale",E53="—"),INDEX(PARAMS_BMP,7,6),""))))))),"")</f>
         <v/>
       </c>
       <c r="AK53" s="17">
@@ -15128,13 +15128,13 @@
         <v/>
       </c>
       <c r="L12" s="17">
-        <f>IF(A12="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A12,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A12,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A12,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A12,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
+        <f>IF(A12="","",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A12,'SDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A12,'SDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A12,'SDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A12,'SDA'!$D$4:$D$53,"A")&gt;0,"A","")))))</f>
         <v/>
       </c>
       <c r="M12" s="4" t="n"/>
       <c r="N12" s="4" t="n"/>
       <c r="O12" s="17">
-        <f>IF(A12="","",IFS(L12="A",2.5,L12="B",0.3,L12="C",0.1,L12="D",0.05,TRUE,""))</f>
+        <f>IF(A12="","",IF(L12="A",2.5,IF(L12="B",0.3,IF(L12="C",0.1,IF(L12="D",0.05,"")))))</f>
         <v/>
       </c>
       <c r="P12" s="27" t="n"/>
@@ -15273,13 +15273,13 @@
         <v/>
       </c>
       <c r="L13" s="17">
-        <f>IF(A13="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A13,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A13,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A13,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A13,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
+        <f>IF(A13="","",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A13,'SDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A13,'SDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A13,'SDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A13,'SDA'!$D$4:$D$53,"A")&gt;0,"A","")))))</f>
         <v/>
       </c>
       <c r="M13" s="4" t="n"/>
       <c r="N13" s="4" t="n"/>
       <c r="O13" s="17">
-        <f>IF(A13="","",IFS(L13="A",2.5,L13="B",0.3,L13="C",0.1,L13="D",0.05,TRUE,""))</f>
+        <f>IF(A13="","",IF(L13="A",2.5,IF(L13="B",0.3,IF(L13="C",0.1,IF(L13="D",0.05,"")))))</f>
         <v/>
       </c>
       <c r="P13" s="27" t="n"/>
@@ -15418,13 +15418,13 @@
         <v/>
       </c>
       <c r="L14" s="17">
-        <f>IF(A14="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A14,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A14,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A14,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A14,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
+        <f>IF(A14="","",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A14,'SDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A14,'SDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A14,'SDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A14,'SDA'!$D$4:$D$53,"A")&gt;0,"A","")))))</f>
         <v/>
       </c>
       <c r="M14" s="4" t="n"/>
       <c r="N14" s="4" t="n"/>
       <c r="O14" s="17">
-        <f>IF(A14="","",IFS(L14="A",2.5,L14="B",0.3,L14="C",0.1,L14="D",0.05,TRUE,""))</f>
+        <f>IF(A14="","",IF(L14="A",2.5,IF(L14="B",0.3,IF(L14="C",0.1,IF(L14="D",0.05,"")))))</f>
         <v/>
       </c>
       <c r="P14" s="27" t="n"/>
@@ -15563,13 +15563,13 @@
         <v/>
       </c>
       <c r="L15" s="17">
-        <f>IF(A15="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A15,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A15,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A15,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A15,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
+        <f>IF(A15="","",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A15,'SDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A15,'SDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A15,'SDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A15,'SDA'!$D$4:$D$53,"A")&gt;0,"A","")))))</f>
         <v/>
       </c>
       <c r="M15" s="4" t="n"/>
       <c r="N15" s="4" t="n"/>
       <c r="O15" s="17">
-        <f>IF(A15="","",IFS(L15="A",2.5,L15="B",0.3,L15="C",0.1,L15="D",0.05,TRUE,""))</f>
+        <f>IF(A15="","",IF(L15="A",2.5,IF(L15="B",0.3,IF(L15="C",0.1,IF(L15="D",0.05,"")))))</f>
         <v/>
       </c>
       <c r="P15" s="27" t="n"/>
@@ -15708,13 +15708,13 @@
         <v/>
       </c>
       <c r="L16" s="17">
-        <f>IF(A16="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A16,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A16,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A16,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A16,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
+        <f>IF(A16="","",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A16,'SDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A16,'SDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A16,'SDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A16,'SDA'!$D$4:$D$53,"A")&gt;0,"A","")))))</f>
         <v/>
       </c>
       <c r="M16" s="4" t="n"/>
       <c r="N16" s="4" t="n"/>
       <c r="O16" s="17">
-        <f>IF(A16="","",IFS(L16="A",2.5,L16="B",0.3,L16="C",0.1,L16="D",0.05,TRUE,""))</f>
+        <f>IF(A16="","",IF(L16="A",2.5,IF(L16="B",0.3,IF(L16="C",0.1,IF(L16="D",0.05,"")))))</f>
         <v/>
       </c>
       <c r="P16" s="27" t="n"/>
@@ -15853,13 +15853,13 @@
         <v/>
       </c>
       <c r="L17" s="17">
-        <f>IF(A17="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A17,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A17,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A17,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A17,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
+        <f>IF(A17="","",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A17,'SDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A17,'SDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A17,'SDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A17,'SDA'!$D$4:$D$53,"A")&gt;0,"A","")))))</f>
         <v/>
       </c>
       <c r="M17" s="4" t="n"/>
       <c r="N17" s="4" t="n"/>
       <c r="O17" s="17">
-        <f>IF(A17="","",IFS(L17="A",2.5,L17="B",0.3,L17="C",0.1,L17="D",0.05,TRUE,""))</f>
+        <f>IF(A17="","",IF(L17="A",2.5,IF(L17="B",0.3,IF(L17="C",0.1,IF(L17="D",0.05,"")))))</f>
         <v/>
       </c>
       <c r="P17" s="27" t="n"/>
@@ -15998,13 +15998,13 @@
         <v/>
       </c>
       <c r="L18" s="17">
-        <f>IF(A18="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A18,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A18,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A18,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A18,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
+        <f>IF(A18="","",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A18,'SDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A18,'SDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A18,'SDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A18,'SDA'!$D$4:$D$53,"A")&gt;0,"A","")))))</f>
         <v/>
       </c>
       <c r="M18" s="4" t="n"/>
       <c r="N18" s="4" t="n"/>
       <c r="O18" s="17">
-        <f>IF(A18="","",IFS(L18="A",2.5,L18="B",0.3,L18="C",0.1,L18="D",0.05,TRUE,""))</f>
+        <f>IF(A18="","",IF(L18="A",2.5,IF(L18="B",0.3,IF(L18="C",0.1,IF(L18="D",0.05,"")))))</f>
         <v/>
       </c>
       <c r="P18" s="27" t="n"/>
@@ -16143,13 +16143,13 @@
         <v/>
       </c>
       <c r="L19" s="17">
-        <f>IF(A19="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A19,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A19,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A19,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A19,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
+        <f>IF(A19="","",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A19,'SDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A19,'SDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A19,'SDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A19,'SDA'!$D$4:$D$53,"A")&gt;0,"A","")))))</f>
         <v/>
       </c>
       <c r="M19" s="4" t="n"/>
       <c r="N19" s="4" t="n"/>
       <c r="O19" s="17">
-        <f>IF(A19="","",IFS(L19="A",2.5,L19="B",0.3,L19="C",0.1,L19="D",0.05,TRUE,""))</f>
+        <f>IF(A19="","",IF(L19="A",2.5,IF(L19="B",0.3,IF(L19="C",0.1,IF(L19="D",0.05,"")))))</f>
         <v/>
       </c>
       <c r="P19" s="27" t="n"/>
@@ -16288,13 +16288,13 @@
         <v/>
       </c>
       <c r="L20" s="17">
-        <f>IF(A20="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A20,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A20,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A20,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A20,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
+        <f>IF(A20="","",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A20,'SDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A20,'SDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A20,'SDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A20,'SDA'!$D$4:$D$53,"A")&gt;0,"A","")))))</f>
         <v/>
       </c>
       <c r="M20" s="4" t="n"/>
       <c r="N20" s="4" t="n"/>
       <c r="O20" s="17">
-        <f>IF(A20="","",IFS(L20="A",2.5,L20="B",0.3,L20="C",0.1,L20="D",0.05,TRUE,""))</f>
+        <f>IF(A20="","",IF(L20="A",2.5,IF(L20="B",0.3,IF(L20="C",0.1,IF(L20="D",0.05,"")))))</f>
         <v/>
       </c>
       <c r="P20" s="27" t="n"/>
@@ -16433,13 +16433,13 @@
         <v/>
       </c>
       <c r="L21" s="17">
-        <f>IF(A21="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A21,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A21,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A21,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A21,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
+        <f>IF(A21="","",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A21,'SDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A21,'SDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A21,'SDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A21,'SDA'!$D$4:$D$53,"A")&gt;0,"A","")))))</f>
         <v/>
       </c>
       <c r="M21" s="4" t="n"/>
       <c r="N21" s="4" t="n"/>
       <c r="O21" s="17">
-        <f>IF(A21="","",IFS(L21="A",2.5,L21="B",0.3,L21="C",0.1,L21="D",0.05,TRUE,""))</f>
+        <f>IF(A21="","",IF(L21="A",2.5,IF(L21="B",0.3,IF(L21="C",0.1,IF(L21="D",0.05,"")))))</f>
         <v/>
       </c>
       <c r="P21" s="27" t="n"/>
@@ -16578,13 +16578,13 @@
         <v/>
       </c>
       <c r="L22" s="17">
-        <f>IF(A22="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A22,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A22,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A22,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A22,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
+        <f>IF(A22="","",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A22,'SDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A22,'SDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A22,'SDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A22,'SDA'!$D$4:$D$53,"A")&gt;0,"A","")))))</f>
         <v/>
       </c>
       <c r="M22" s="4" t="n"/>
       <c r="N22" s="4" t="n"/>
       <c r="O22" s="17">
-        <f>IF(A22="","",IFS(L22="A",2.5,L22="B",0.3,L22="C",0.1,L22="D",0.05,TRUE,""))</f>
+        <f>IF(A22="","",IF(L22="A",2.5,IF(L22="B",0.3,IF(L22="C",0.1,IF(L22="D",0.05,"")))))</f>
         <v/>
       </c>
       <c r="P22" s="27" t="n"/>
@@ -16723,13 +16723,13 @@
         <v/>
       </c>
       <c r="L23" s="17">
-        <f>IF(A23="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A23,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A23,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A23,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A23,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
+        <f>IF(A23="","",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A23,'SDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A23,'SDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A23,'SDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A23,'SDA'!$D$4:$D$53,"A")&gt;0,"A","")))))</f>
         <v/>
       </c>
       <c r="M23" s="4" t="n"/>
       <c r="N23" s="4" t="n"/>
       <c r="O23" s="17">
-        <f>IF(A23="","",IFS(L23="A",2.5,L23="B",0.3,L23="C",0.1,L23="D",0.05,TRUE,""))</f>
+        <f>IF(A23="","",IF(L23="A",2.5,IF(L23="B",0.3,IF(L23="C",0.1,IF(L23="D",0.05,"")))))</f>
         <v/>
       </c>
       <c r="P23" s="27" t="n"/>
@@ -16868,13 +16868,13 @@
         <v/>
       </c>
       <c r="L24" s="17">
-        <f>IF(A24="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A24,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A24,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A24,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A24,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
+        <f>IF(A24="","",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A24,'SDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A24,'SDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A24,'SDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A24,'SDA'!$D$4:$D$53,"A")&gt;0,"A","")))))</f>
         <v/>
       </c>
       <c r="M24" s="4" t="n"/>
       <c r="N24" s="4" t="n"/>
       <c r="O24" s="17">
-        <f>IF(A24="","",IFS(L24="A",2.5,L24="B",0.3,L24="C",0.1,L24="D",0.05,TRUE,""))</f>
+        <f>IF(A24="","",IF(L24="A",2.5,IF(L24="B",0.3,IF(L24="C",0.1,IF(L24="D",0.05,"")))))</f>
         <v/>
       </c>
       <c r="P24" s="27" t="n"/>
@@ -17013,13 +17013,13 @@
         <v/>
       </c>
       <c r="L25" s="17">
-        <f>IF(A25="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A25,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A25,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A25,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A25,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
+        <f>IF(A25="","",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A25,'SDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A25,'SDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A25,'SDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A25,'SDA'!$D$4:$D$53,"A")&gt;0,"A","")))))</f>
         <v/>
       </c>
       <c r="M25" s="4" t="n"/>
       <c r="N25" s="4" t="n"/>
       <c r="O25" s="17">
-        <f>IF(A25="","",IFS(L25="A",2.5,L25="B",0.3,L25="C",0.1,L25="D",0.05,TRUE,""))</f>
+        <f>IF(A25="","",IF(L25="A",2.5,IF(L25="B",0.3,IF(L25="C",0.1,IF(L25="D",0.05,"")))))</f>
         <v/>
       </c>
       <c r="P25" s="27" t="n"/>
@@ -17158,13 +17158,13 @@
         <v/>
       </c>
       <c r="L26" s="17">
-        <f>IF(A26="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A26,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A26,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A26,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A26,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
+        <f>IF(A26="","",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A26,'SDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A26,'SDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A26,'SDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A26,'SDA'!$D$4:$D$53,"A")&gt;0,"A","")))))</f>
         <v/>
       </c>
       <c r="M26" s="4" t="n"/>
       <c r="N26" s="4" t="n"/>
       <c r="O26" s="17">
-        <f>IF(A26="","",IFS(L26="A",2.5,L26="B",0.3,L26="C",0.1,L26="D",0.05,TRUE,""))</f>
+        <f>IF(A26="","",IF(L26="A",2.5,IF(L26="B",0.3,IF(L26="C",0.1,IF(L26="D",0.05,"")))))</f>
         <v/>
       </c>
       <c r="P26" s="27" t="n"/>
@@ -17303,13 +17303,13 @@
         <v/>
       </c>
       <c r="L27" s="17">
-        <f>IF(A27="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A27,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A27,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A27,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A27,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
+        <f>IF(A27="","",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A27,'SDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A27,'SDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A27,'SDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A27,'SDA'!$D$4:$D$53,"A")&gt;0,"A","")))))</f>
         <v/>
       </c>
       <c r="M27" s="4" t="n"/>
       <c r="N27" s="4" t="n"/>
       <c r="O27" s="17">
-        <f>IF(A27="","",IFS(L27="A",2.5,L27="B",0.3,L27="C",0.1,L27="D",0.05,TRUE,""))</f>
+        <f>IF(A27="","",IF(L27="A",2.5,IF(L27="B",0.3,IF(L27="C",0.1,IF(L27="D",0.05,"")))))</f>
         <v/>
       </c>
       <c r="P27" s="27" t="n"/>
@@ -17448,13 +17448,13 @@
         <v/>
       </c>
       <c r="L28" s="17">
-        <f>IF(A28="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A28,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A28,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A28,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A28,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
+        <f>IF(A28="","",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A28,'SDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A28,'SDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A28,'SDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A28,'SDA'!$D$4:$D$53,"A")&gt;0,"A","")))))</f>
         <v/>
       </c>
       <c r="M28" s="4" t="n"/>
       <c r="N28" s="4" t="n"/>
       <c r="O28" s="17">
-        <f>IF(A28="","",IFS(L28="A",2.5,L28="B",0.3,L28="C",0.1,L28="D",0.05,TRUE,""))</f>
+        <f>IF(A28="","",IF(L28="A",2.5,IF(L28="B",0.3,IF(L28="C",0.1,IF(L28="D",0.05,"")))))</f>
         <v/>
       </c>
       <c r="P28" s="27" t="n"/>
@@ -17593,13 +17593,13 @@
         <v/>
       </c>
       <c r="L29" s="17">
-        <f>IF(A29="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A29,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A29,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A29,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A29,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
+        <f>IF(A29="","",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A29,'SDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A29,'SDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A29,'SDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A29,'SDA'!$D$4:$D$53,"A")&gt;0,"A","")))))</f>
         <v/>
       </c>
       <c r="M29" s="4" t="n"/>
       <c r="N29" s="4" t="n"/>
       <c r="O29" s="17">
-        <f>IF(A29="","",IFS(L29="A",2.5,L29="B",0.3,L29="C",0.1,L29="D",0.05,TRUE,""))</f>
+        <f>IF(A29="","",IF(L29="A",2.5,IF(L29="B",0.3,IF(L29="C",0.1,IF(L29="D",0.05,"")))))</f>
         <v/>
       </c>
       <c r="P29" s="27" t="n"/>
@@ -17738,13 +17738,13 @@
         <v/>
       </c>
       <c r="L30" s="17">
-        <f>IF(A30="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A30,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A30,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A30,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A30,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
+        <f>IF(A30="","",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A30,'SDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A30,'SDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A30,'SDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A30,'SDA'!$D$4:$D$53,"A")&gt;0,"A","")))))</f>
         <v/>
       </c>
       <c r="M30" s="4" t="n"/>
       <c r="N30" s="4" t="n"/>
       <c r="O30" s="17">
-        <f>IF(A30="","",IFS(L30="A",2.5,L30="B",0.3,L30="C",0.1,L30="D",0.05,TRUE,""))</f>
+        <f>IF(A30="","",IF(L30="A",2.5,IF(L30="B",0.3,IF(L30="C",0.1,IF(L30="D",0.05,"")))))</f>
         <v/>
       </c>
       <c r="P30" s="27" t="n"/>
@@ -17883,13 +17883,13 @@
         <v/>
       </c>
       <c r="L31" s="17">
-        <f>IF(A31="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A31,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A31,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A31,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A31,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
+        <f>IF(A31="","",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A31,'SDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A31,'SDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A31,'SDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A31,'SDA'!$D$4:$D$53,"A")&gt;0,"A","")))))</f>
         <v/>
       </c>
       <c r="M31" s="4" t="n"/>
       <c r="N31" s="4" t="n"/>
       <c r="O31" s="17">
-        <f>IF(A31="","",IFS(L31="A",2.5,L31="B",0.3,L31="C",0.1,L31="D",0.05,TRUE,""))</f>
+        <f>IF(A31="","",IF(L31="A",2.5,IF(L31="B",0.3,IF(L31="C",0.1,IF(L31="D",0.05,"")))))</f>
         <v/>
       </c>
       <c r="P31" s="27" t="n"/>
@@ -18028,13 +18028,13 @@
         <v/>
       </c>
       <c r="L32" s="17">
-        <f>IF(A32="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A32,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A32,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A32,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A32,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
+        <f>IF(A32="","",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A32,'SDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A32,'SDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A32,'SDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A32,'SDA'!$D$4:$D$53,"A")&gt;0,"A","")))))</f>
         <v/>
       </c>
       <c r="M32" s="4" t="n"/>
       <c r="N32" s="4" t="n"/>
       <c r="O32" s="17">
-        <f>IF(A32="","",IFS(L32="A",2.5,L32="B",0.3,L32="C",0.1,L32="D",0.05,TRUE,""))</f>
+        <f>IF(A32="","",IF(L32="A",2.5,IF(L32="B",0.3,IF(L32="C",0.1,IF(L32="D",0.05,"")))))</f>
         <v/>
       </c>
       <c r="P32" s="27" t="n"/>
@@ -18173,13 +18173,13 @@
         <v/>
       </c>
       <c r="L33" s="17">
-        <f>IF(A33="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A33,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A33,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A33,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A33,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
+        <f>IF(A33="","",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A33,'SDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A33,'SDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A33,'SDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A33,'SDA'!$D$4:$D$53,"A")&gt;0,"A","")))))</f>
         <v/>
       </c>
       <c r="M33" s="4" t="n"/>
       <c r="N33" s="4" t="n"/>
       <c r="O33" s="17">
-        <f>IF(A33="","",IFS(L33="A",2.5,L33="B",0.3,L33="C",0.1,L33="D",0.05,TRUE,""))</f>
+        <f>IF(A33="","",IF(L33="A",2.5,IF(L33="B",0.3,IF(L33="C",0.1,IF(L33="D",0.05,"")))))</f>
         <v/>
       </c>
       <c r="P33" s="27" t="n"/>
@@ -18318,13 +18318,13 @@
         <v/>
       </c>
       <c r="L34" s="17">
-        <f>IF(A34="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A34,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A34,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A34,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A34,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
+        <f>IF(A34="","",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A34,'SDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A34,'SDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A34,'SDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A34,'SDA'!$D$4:$D$53,"A")&gt;0,"A","")))))</f>
         <v/>
       </c>
       <c r="M34" s="4" t="n"/>
       <c r="N34" s="4" t="n"/>
       <c r="O34" s="17">
-        <f>IF(A34="","",IFS(L34="A",2.5,L34="B",0.3,L34="C",0.1,L34="D",0.05,TRUE,""))</f>
+        <f>IF(A34="","",IF(L34="A",2.5,IF(L34="B",0.3,IF(L34="C",0.1,IF(L34="D",0.05,"")))))</f>
         <v/>
       </c>
       <c r="P34" s="27" t="n"/>
@@ -18463,13 +18463,13 @@
         <v/>
       </c>
       <c r="L35" s="17">
-        <f>IF(A35="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A35,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A35,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A35,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A35,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
+        <f>IF(A35="","",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A35,'SDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A35,'SDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A35,'SDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A35,'SDA'!$D$4:$D$53,"A")&gt;0,"A","")))))</f>
         <v/>
       </c>
       <c r="M35" s="4" t="n"/>
       <c r="N35" s="4" t="n"/>
       <c r="O35" s="17">
-        <f>IF(A35="","",IFS(L35="A",2.5,L35="B",0.3,L35="C",0.1,L35="D",0.05,TRUE,""))</f>
+        <f>IF(A35="","",IF(L35="A",2.5,IF(L35="B",0.3,IF(L35="C",0.1,IF(L35="D",0.05,"")))))</f>
         <v/>
       </c>
       <c r="P35" s="27" t="n"/>
@@ -18608,13 +18608,13 @@
         <v/>
       </c>
       <c r="L36" s="17">
-        <f>IF(A36="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A36,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A36,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A36,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A36,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
+        <f>IF(A36="","",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A36,'SDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A36,'SDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A36,'SDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A36,'SDA'!$D$4:$D$53,"A")&gt;0,"A","")))))</f>
         <v/>
       </c>
       <c r="M36" s="4" t="n"/>
       <c r="N36" s="4" t="n"/>
       <c r="O36" s="17">
-        <f>IF(A36="","",IFS(L36="A",2.5,L36="B",0.3,L36="C",0.1,L36="D",0.05,TRUE,""))</f>
+        <f>IF(A36="","",IF(L36="A",2.5,IF(L36="B",0.3,IF(L36="C",0.1,IF(L36="D",0.05,"")))))</f>
         <v/>
       </c>
       <c r="P36" s="27" t="n"/>
@@ -18753,13 +18753,13 @@
         <v/>
       </c>
       <c r="L37" s="17">
-        <f>IF(A37="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A37,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A37,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A37,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A37,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
+        <f>IF(A37="","",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A37,'SDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A37,'SDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A37,'SDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A37,'SDA'!$D$4:$D$53,"A")&gt;0,"A","")))))</f>
         <v/>
       </c>
       <c r="M37" s="4" t="n"/>
       <c r="N37" s="4" t="n"/>
       <c r="O37" s="17">
-        <f>IF(A37="","",IFS(L37="A",2.5,L37="B",0.3,L37="C",0.1,L37="D",0.05,TRUE,""))</f>
+        <f>IF(A37="","",IF(L37="A",2.5,IF(L37="B",0.3,IF(L37="C",0.1,IF(L37="D",0.05,"")))))</f>
         <v/>
       </c>
       <c r="P37" s="27" t="n"/>
@@ -18898,13 +18898,13 @@
         <v/>
       </c>
       <c r="L38" s="17">
-        <f>IF(A38="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A38,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A38,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A38,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A38,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
+        <f>IF(A38="","",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A38,'SDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A38,'SDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A38,'SDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A38,'SDA'!$D$4:$D$53,"A")&gt;0,"A","")))))</f>
         <v/>
       </c>
       <c r="M38" s="4" t="n"/>
       <c r="N38" s="4" t="n"/>
       <c r="O38" s="17">
-        <f>IF(A38="","",IFS(L38="A",2.5,L38="B",0.3,L38="C",0.1,L38="D",0.05,TRUE,""))</f>
+        <f>IF(A38="","",IF(L38="A",2.5,IF(L38="B",0.3,IF(L38="C",0.1,IF(L38="D",0.05,"")))))</f>
         <v/>
       </c>
       <c r="P38" s="27" t="n"/>
@@ -19043,13 +19043,13 @@
         <v/>
       </c>
       <c r="L39" s="17">
-        <f>IF(A39="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A39,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A39,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A39,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A39,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
+        <f>IF(A39="","",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A39,'SDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A39,'SDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A39,'SDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A39,'SDA'!$D$4:$D$53,"A")&gt;0,"A","")))))</f>
         <v/>
       </c>
       <c r="M39" s="4" t="n"/>
       <c r="N39" s="4" t="n"/>
       <c r="O39" s="17">
-        <f>IF(A39="","",IFS(L39="A",2.5,L39="B",0.3,L39="C",0.1,L39="D",0.05,TRUE,""))</f>
+        <f>IF(A39="","",IF(L39="A",2.5,IF(L39="B",0.3,IF(L39="C",0.1,IF(L39="D",0.05,"")))))</f>
         <v/>
       </c>
       <c r="P39" s="27" t="n"/>
@@ -19188,13 +19188,13 @@
         <v/>
       </c>
       <c r="L40" s="17">
-        <f>IF(A40="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A40,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A40,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A40,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A40,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
+        <f>IF(A40="","",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A40,'SDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A40,'SDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A40,'SDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A40,'SDA'!$D$4:$D$53,"A")&gt;0,"A","")))))</f>
         <v/>
       </c>
       <c r="M40" s="4" t="n"/>
       <c r="N40" s="4" t="n"/>
       <c r="O40" s="17">
-        <f>IF(A40="","",IFS(L40="A",2.5,L40="B",0.3,L40="C",0.1,L40="D",0.05,TRUE,""))</f>
+        <f>IF(A40="","",IF(L40="A",2.5,IF(L40="B",0.3,IF(L40="C",0.1,IF(L40="D",0.05,"")))))</f>
         <v/>
       </c>
       <c r="P40" s="27" t="n"/>
@@ -19333,13 +19333,13 @@
         <v/>
       </c>
       <c r="L41" s="17">
-        <f>IF(A41="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A41,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A41,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A41,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A41,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
+        <f>IF(A41="","",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A41,'SDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A41,'SDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A41,'SDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A41,'SDA'!$D$4:$D$53,"A")&gt;0,"A","")))))</f>
         <v/>
       </c>
       <c r="M41" s="4" t="n"/>
       <c r="N41" s="4" t="n"/>
       <c r="O41" s="17">
-        <f>IF(A41="","",IFS(L41="A",2.5,L41="B",0.3,L41="C",0.1,L41="D",0.05,TRUE,""))</f>
+        <f>IF(A41="","",IF(L41="A",2.5,IF(L41="B",0.3,IF(L41="C",0.1,IF(L41="D",0.05,"")))))</f>
         <v/>
       </c>
       <c r="P41" s="27" t="n"/>
@@ -19478,13 +19478,13 @@
         <v/>
       </c>
       <c r="L42" s="17">
-        <f>IF(A42="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A42,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A42,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A42,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A42,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
+        <f>IF(A42="","",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A42,'SDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A42,'SDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A42,'SDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A42,'SDA'!$D$4:$D$53,"A")&gt;0,"A","")))))</f>
         <v/>
       </c>
       <c r="M42" s="4" t="n"/>
       <c r="N42" s="4" t="n"/>
       <c r="O42" s="17">
-        <f>IF(A42="","",IFS(L42="A",2.5,L42="B",0.3,L42="C",0.1,L42="D",0.05,TRUE,""))</f>
+        <f>IF(A42="","",IF(L42="A",2.5,IF(L42="B",0.3,IF(L42="C",0.1,IF(L42="D",0.05,"")))))</f>
         <v/>
       </c>
       <c r="P42" s="27" t="n"/>
@@ -19623,13 +19623,13 @@
         <v/>
       </c>
       <c r="L43" s="17">
-        <f>IF(A43="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A43,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A43,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A43,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A43,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
+        <f>IF(A43="","",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A43,'SDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A43,'SDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A43,'SDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A43,'SDA'!$D$4:$D$53,"A")&gt;0,"A","")))))</f>
         <v/>
       </c>
       <c r="M43" s="4" t="n"/>
       <c r="N43" s="4" t="n"/>
       <c r="O43" s="17">
-        <f>IF(A43="","",IFS(L43="A",2.5,L43="B",0.3,L43="C",0.1,L43="D",0.05,TRUE,""))</f>
+        <f>IF(A43="","",IF(L43="A",2.5,IF(L43="B",0.3,IF(L43="C",0.1,IF(L43="D",0.05,"")))))</f>
         <v/>
       </c>
       <c r="P43" s="27" t="n"/>
@@ -19768,13 +19768,13 @@
         <v/>
       </c>
       <c r="L44" s="17">
-        <f>IF(A44="","",IFERROR(IFS(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A44,'SDA'!$D$4:$D$53,"D")&gt;0,"D",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A44,'SDA'!$D$4:$D$53,"C")&gt;0,"C",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A44,'SDA'!$D$4:$D$53,"B")&gt;0,"B",SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A44,'SDA'!$D$4:$D$53,"A")&gt;0,"A",TRUE,""),""))</f>
+        <f>IF(A44="","",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A44,'SDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A44,'SDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A44,'SDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('SDA'!$G$4:$G$53,'SDA'!$A$4:$A$53,A44,'SDA'!$D$4:$D$53,"A")&gt;0,"A","")))))</f>
         <v/>
       </c>
       <c r="M44" s="4" t="n"/>
       <c r="N44" s="4" t="n"/>
       <c r="O44" s="17">
-        <f>IF(A44="","",IFS(L44="A",2.5,L44="B",0.3,L44="C",0.1,L44="D",0.05,TRUE,""))</f>
+        <f>IF(A44="","",IF(L44="A",2.5,IF(L44="B",0.3,IF(L44="C",0.1,IF(L44="D",0.05,"")))))</f>
         <v/>
       </c>
       <c r="P44" s="27" t="n"/>

--- a/SW_Required_Provided_DOEE_EISA438.xlsx
+++ b/SW_Required_Provided_DOEE_EISA438.xlsx
@@ -457,7 +457,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -19925,7 +19925,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="35">
+  <mergeCells count="41">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="L7:P7"/>
     <mergeCell ref="AC7:AM7"/>
@@ -19936,13 +19936,16 @@
     <mergeCell ref="AM9:AM10"/>
     <mergeCell ref="Y9:Z9"/>
     <mergeCell ref="AP9:AQ9"/>
+    <mergeCell ref="W7:AB7"/>
     <mergeCell ref="J9:K9"/>
-    <mergeCell ref="W7:AB7"/>
     <mergeCell ref="AA9:AB9"/>
     <mergeCell ref="L3:V3"/>
+    <mergeCell ref="AG8:AM8"/>
     <mergeCell ref="AH9:AH10"/>
     <mergeCell ref="B7:K7"/>
     <mergeCell ref="D1:G1"/>
+    <mergeCell ref="W8:AB8"/>
+    <mergeCell ref="L8:P8"/>
     <mergeCell ref="L9:L10"/>
     <mergeCell ref="L4:V4"/>
     <mergeCell ref="N9:N10"/>
@@ -19955,12 +19958,15 @@
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="AC9:AD9"/>
     <mergeCell ref="AE9:AF9"/>
+    <mergeCell ref="AC8:AF8"/>
+    <mergeCell ref="B8:K8"/>
     <mergeCell ref="AF1:AG1"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="M9:M10"/>
     <mergeCell ref="AJ9:AJ10"/>
     <mergeCell ref="O9:O10"/>
     <mergeCell ref="AL9:AL10"/>
+    <mergeCell ref="Q8:V8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
